--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="882">
   <si>
     <t>Наименование</t>
   </si>
@@ -395,6 +395,9 @@
     <t>Ganza - Ascension (NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Ganza - MILK MANIAC Гуава (milkshake), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Ganza - Say My Name (APA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1235,7 +1238,7 @@
     <t>Velka Morava - Bavorske (Hell), РОЗЛИВ, Россия</t>
   </si>
   <si>
-    <t>Velka Morava - Jungle Boogie (NEIPA), РОЗЛИВ, Россия</t>
+    <t>Velka Morava - Codename LBD (NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>Velka Morava - Take Five (APA), РОЗЛИВ, Россия</t>
@@ -3011,7 +3014,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B881"/>
+  <dimension ref="A1:B882"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -4023,7 +4026,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -4031,7 +4034,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -4039,7 +4042,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -4047,7 +4050,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -4055,7 +4058,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -4063,7 +4066,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>420</v>
+        <v>680</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -4071,7 +4074,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -4079,7 +4082,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -4087,7 +4090,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -4095,7 +4098,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -4103,7 +4106,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -4111,7 +4114,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -4119,7 +4122,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -4127,7 +4130,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>580</v>
+        <v>880</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -4135,7 +4138,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -4143,7 +4146,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -4151,7 +4154,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -4159,7 +4162,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -4167,7 +4170,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -4175,7 +4178,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -4183,7 +4186,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>900</v>
+        <v>960</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -4191,7 +4194,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -4199,7 +4202,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -4207,7 +4210,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -4215,7 +4218,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>500</v>
+        <v>780</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -4223,7 +4226,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>580</v>
+        <v>500</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -4231,7 +4234,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -4239,7 +4242,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -4247,7 +4250,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>1100</v>
+        <v>520</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -4255,7 +4258,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>1060</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -4271,7 +4274,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>1100</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -4287,7 +4290,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -4295,7 +4298,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>1080</v>
+        <v>560</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -4303,12 +4306,12 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>840</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B162" s="1">
         <v>840</v>
@@ -4327,7 +4330,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="1">
-        <v>420</v>
+        <v>840</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -4335,7 +4338,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="1">
-        <v>520</v>
+        <v>420</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -4343,7 +4346,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -4351,7 +4354,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="1">
-        <v>460</v>
+        <v>720</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -4359,7 +4362,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="1">
-        <v>560</v>
+        <v>460</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4367,7 +4370,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -4375,7 +4378,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -4383,7 +4386,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -4391,7 +4394,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4399,7 +4402,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="1">
-        <v>980</v>
+        <v>520</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4407,7 +4410,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="1">
-        <v>540</v>
+        <v>980</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4415,7 +4418,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4423,7 +4426,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4431,7 +4434,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4439,7 +4442,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="1">
-        <v>560</v>
+        <v>760</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4447,7 +4450,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="1">
-        <v>1100</v>
+        <v>560</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4479,7 +4482,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4487,7 +4490,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4495,7 +4498,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4503,7 +4506,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4535,7 +4538,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4543,7 +4546,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4551,7 +4554,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4559,7 +4562,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4567,7 +4570,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4575,7 +4578,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4583,7 +4586,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="1">
-        <v>460</v>
+        <v>700</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4591,7 +4594,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4599,7 +4602,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="1">
-        <v>720</v>
+        <v>580</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4607,7 +4610,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4615,7 +4618,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4623,7 +4626,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="1">
-        <v>260</v>
+        <v>780</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4639,7 +4642,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4655,7 +4658,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4663,7 +4666,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4671,7 +4674,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4679,7 +4682,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4687,7 +4690,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4695,7 +4698,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="1">
-        <v>740</v>
+        <v>400</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4703,7 +4706,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4711,7 +4714,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4719,7 +4722,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4727,7 +4730,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4735,7 +4738,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4743,7 +4746,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4759,7 +4762,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4767,7 +4770,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4775,7 +4778,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4783,7 +4786,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4791,7 +4794,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="1">
-        <v>580</v>
+        <v>860</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4799,7 +4802,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4807,7 +4810,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="1">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4815,7 +4818,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4823,7 +4826,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4831,7 +4834,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4839,7 +4842,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4847,7 +4850,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4855,7 +4858,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4863,7 +4866,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4871,7 +4874,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4879,7 +4882,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4887,7 +4890,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="1">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4895,7 +4898,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="1">
-        <v>480</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4903,7 +4906,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4911,7 +4914,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4919,7 +4922,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4927,7 +4930,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4935,7 +4938,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4943,7 +4946,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4951,7 +4954,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4959,7 +4962,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4967,7 +4970,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="1">
-        <v>900</v>
+        <v>520</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4975,7 +4978,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4983,7 +4986,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4991,7 +4994,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4999,7 +5002,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -5015,7 +5018,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -5031,7 +5034,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -5039,7 +5042,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -5047,7 +5050,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -5055,7 +5058,7 @@
         <v>254</v>
       </c>
       <c r="B255" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -5063,7 +5066,7 @@
         <v>255</v>
       </c>
       <c r="B256" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -5071,7 +5074,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -5079,7 +5082,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="1">
-        <v>960</v>
+        <v>840</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -5087,7 +5090,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -5103,7 +5106,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -5111,7 +5114,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -5119,7 +5122,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -5127,7 +5130,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -5135,7 +5138,7 @@
         <v>264</v>
       </c>
       <c r="B265" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -5143,7 +5146,7 @@
         <v>265</v>
       </c>
       <c r="B266" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -5159,7 +5162,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="1">
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -5167,7 +5170,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -5175,7 +5178,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="1">
-        <v>758</v>
+        <v>500</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -5183,7 +5186,7 @@
         <v>270</v>
       </c>
       <c r="B271" s="1">
-        <v>2273</v>
+        <v>758</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -5191,7 +5194,7 @@
         <v>271</v>
       </c>
       <c r="B272" s="1">
-        <v>1515</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -5199,7 +5202,7 @@
         <v>272</v>
       </c>
       <c r="B273" s="1">
-        <v>520</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -5207,7 +5210,7 @@
         <v>273</v>
       </c>
       <c r="B274" s="1">
-        <v>4000</v>
+        <v>520</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -5215,7 +5218,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="1">
-        <v>560</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -5223,7 +5226,7 @@
         <v>275</v>
       </c>
       <c r="B276" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -5231,7 +5234,7 @@
         <v>276</v>
       </c>
       <c r="B277" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -5247,7 +5250,7 @@
         <v>278</v>
       </c>
       <c r="B279" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -5255,7 +5258,7 @@
         <v>279</v>
       </c>
       <c r="B280" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -5263,7 +5266,7 @@
         <v>280</v>
       </c>
       <c r="B281" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -5271,7 +5274,7 @@
         <v>281</v>
       </c>
       <c r="B282" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -5279,7 +5282,7 @@
         <v>282</v>
       </c>
       <c r="B283" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -5287,7 +5290,7 @@
         <v>283</v>
       </c>
       <c r="B284" s="1">
-        <v>680</v>
+        <v>520</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -5295,7 +5298,7 @@
         <v>284</v>
       </c>
       <c r="B285" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -5303,7 +5306,7 @@
         <v>285</v>
       </c>
       <c r="B286" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5311,7 +5314,7 @@
         <v>286</v>
       </c>
       <c r="B287" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5319,7 +5322,7 @@
         <v>287</v>
       </c>
       <c r="B288" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5327,7 +5330,7 @@
         <v>288</v>
       </c>
       <c r="B289" s="1">
-        <v>660</v>
+        <v>380</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5335,7 +5338,7 @@
         <v>289</v>
       </c>
       <c r="B290" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5343,7 +5346,7 @@
         <v>290</v>
       </c>
       <c r="B291" s="1">
-        <v>540</v>
+        <v>900</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5351,7 +5354,7 @@
         <v>291</v>
       </c>
       <c r="B292" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5359,7 +5362,7 @@
         <v>292</v>
       </c>
       <c r="B293" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5367,7 +5370,7 @@
         <v>293</v>
       </c>
       <c r="B294" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5375,7 +5378,7 @@
         <v>294</v>
       </c>
       <c r="B295" s="1">
-        <v>460</v>
+        <v>580</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5383,7 +5386,7 @@
         <v>295</v>
       </c>
       <c r="B296" s="1">
-        <v>520</v>
+        <v>460</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5391,7 +5394,7 @@
         <v>296</v>
       </c>
       <c r="B297" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5399,7 +5402,7 @@
         <v>297</v>
       </c>
       <c r="B298" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5407,7 +5410,7 @@
         <v>298</v>
       </c>
       <c r="B299" s="1">
-        <v>860</v>
+        <v>900</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5415,7 +5418,7 @@
         <v>299</v>
       </c>
       <c r="B300" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5439,7 +5442,7 @@
         <v>302</v>
       </c>
       <c r="B303" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5455,7 +5458,7 @@
         <v>304</v>
       </c>
       <c r="B305" s="1">
-        <v>980</v>
+        <v>560</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5463,7 +5466,7 @@
         <v>305</v>
       </c>
       <c r="B306" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5479,7 +5482,7 @@
         <v>307</v>
       </c>
       <c r="B308" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5487,7 +5490,7 @@
         <v>308</v>
       </c>
       <c r="B309" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5495,7 +5498,7 @@
         <v>309</v>
       </c>
       <c r="B310" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5503,7 +5506,7 @@
         <v>310</v>
       </c>
       <c r="B311" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5511,7 +5514,7 @@
         <v>311</v>
       </c>
       <c r="B312" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5519,7 +5522,7 @@
         <v>312</v>
       </c>
       <c r="B313" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5527,7 +5530,7 @@
         <v>313</v>
       </c>
       <c r="B314" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5535,7 +5538,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5543,7 +5546,7 @@
         <v>315</v>
       </c>
       <c r="B316" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5551,7 +5554,7 @@
         <v>316</v>
       </c>
       <c r="B317" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5559,7 +5562,7 @@
         <v>317</v>
       </c>
       <c r="B318" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5567,7 +5570,7 @@
         <v>318</v>
       </c>
       <c r="B319" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5575,7 +5578,7 @@
         <v>319</v>
       </c>
       <c r="B320" s="1">
-        <v>520</v>
+        <v>680</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5583,7 +5586,7 @@
         <v>320</v>
       </c>
       <c r="B321" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5591,7 +5594,7 @@
         <v>321</v>
       </c>
       <c r="B322" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5599,7 +5602,7 @@
         <v>322</v>
       </c>
       <c r="B323" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5607,7 +5610,7 @@
         <v>323</v>
       </c>
       <c r="B324" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5615,7 +5618,7 @@
         <v>324</v>
       </c>
       <c r="B325" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5623,7 +5626,7 @@
         <v>325</v>
       </c>
       <c r="B326" s="1">
-        <v>580</v>
+        <v>840</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5631,7 +5634,7 @@
         <v>326</v>
       </c>
       <c r="B327" s="1">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5639,7 +5642,7 @@
         <v>327</v>
       </c>
       <c r="B328" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5647,7 +5650,7 @@
         <v>328</v>
       </c>
       <c r="B329" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5655,7 +5658,7 @@
         <v>329</v>
       </c>
       <c r="B330" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5663,7 +5666,7 @@
         <v>330</v>
       </c>
       <c r="B331" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5671,7 +5674,7 @@
         <v>331</v>
       </c>
       <c r="B332" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5679,7 +5682,7 @@
         <v>332</v>
       </c>
       <c r="B333" s="1">
-        <v>1000</v>
+        <v>880</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5687,7 +5690,7 @@
         <v>333</v>
       </c>
       <c r="B334" s="1">
-        <v>520</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5695,7 +5698,7 @@
         <v>334</v>
       </c>
       <c r="B335" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5703,7 +5706,7 @@
         <v>335</v>
       </c>
       <c r="B336" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5711,7 +5714,7 @@
         <v>336</v>
       </c>
       <c r="B337" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5719,7 +5722,7 @@
         <v>337</v>
       </c>
       <c r="B338" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5727,7 +5730,7 @@
         <v>338</v>
       </c>
       <c r="B339" s="1">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5735,7 +5738,7 @@
         <v>339</v>
       </c>
       <c r="B340" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5743,7 +5746,7 @@
         <v>340</v>
       </c>
       <c r="B341" s="1">
-        <v>320</v>
+        <v>520</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5751,7 +5754,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="1">
-        <v>540</v>
+        <v>320</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5759,7 +5762,7 @@
         <v>342</v>
       </c>
       <c r="B343" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5767,7 +5770,7 @@
         <v>343</v>
       </c>
       <c r="B344" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5783,7 +5786,7 @@
         <v>345</v>
       </c>
       <c r="B346" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5791,7 +5794,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="1">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5799,7 +5802,7 @@
         <v>347</v>
       </c>
       <c r="B348" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5807,7 +5810,7 @@
         <v>348</v>
       </c>
       <c r="B349" s="1">
-        <v>480</v>
+        <v>800</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5815,7 +5818,7 @@
         <v>349</v>
       </c>
       <c r="B350" s="1">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5823,7 +5826,7 @@
         <v>350</v>
       </c>
       <c r="B351" s="1">
-        <v>520</v>
+        <v>800</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5831,7 +5834,7 @@
         <v>351</v>
       </c>
       <c r="B352" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5839,7 +5842,7 @@
         <v>352</v>
       </c>
       <c r="B353" s="1">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5847,7 +5850,7 @@
         <v>353</v>
       </c>
       <c r="B354" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5863,7 +5866,7 @@
         <v>355</v>
       </c>
       <c r="B356" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5871,7 +5874,7 @@
         <v>356</v>
       </c>
       <c r="B357" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5879,7 +5882,7 @@
         <v>357</v>
       </c>
       <c r="B358" s="1">
-        <v>860</v>
+        <v>720</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5887,7 +5890,7 @@
         <v>358</v>
       </c>
       <c r="B359" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5895,7 +5898,7 @@
         <v>359</v>
       </c>
       <c r="B360" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5903,7 +5906,7 @@
         <v>360</v>
       </c>
       <c r="B361" s="1">
-        <v>880</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5911,7 +5914,7 @@
         <v>361</v>
       </c>
       <c r="B362" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5919,7 +5922,7 @@
         <v>362</v>
       </c>
       <c r="B363" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5927,7 +5930,7 @@
         <v>363</v>
       </c>
       <c r="B364" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5935,7 +5938,7 @@
         <v>364</v>
       </c>
       <c r="B365" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5943,7 +5946,7 @@
         <v>365</v>
       </c>
       <c r="B366" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5951,7 +5954,7 @@
         <v>366</v>
       </c>
       <c r="B367" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5959,7 +5962,7 @@
         <v>367</v>
       </c>
       <c r="B368" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5967,7 +5970,7 @@
         <v>368</v>
       </c>
       <c r="B369" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5983,7 +5986,7 @@
         <v>370</v>
       </c>
       <c r="B371" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5999,7 +6002,7 @@
         <v>372</v>
       </c>
       <c r="B373" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -6007,7 +6010,7 @@
         <v>373</v>
       </c>
       <c r="B374" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -6015,7 +6018,7 @@
         <v>374</v>
       </c>
       <c r="B375" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -6023,7 +6026,7 @@
         <v>375</v>
       </c>
       <c r="B376" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -6031,7 +6034,7 @@
         <v>376</v>
       </c>
       <c r="B377" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -6039,7 +6042,7 @@
         <v>377</v>
       </c>
       <c r="B378" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -6047,7 +6050,7 @@
         <v>378</v>
       </c>
       <c r="B379" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -6055,7 +6058,7 @@
         <v>379</v>
       </c>
       <c r="B380" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -6063,7 +6066,7 @@
         <v>380</v>
       </c>
       <c r="B381" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -6071,7 +6074,7 @@
         <v>381</v>
       </c>
       <c r="B382" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -6079,7 +6082,7 @@
         <v>382</v>
       </c>
       <c r="B383" s="1">
-        <v>640</v>
+        <v>480</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -6087,7 +6090,7 @@
         <v>383</v>
       </c>
       <c r="B384" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -6095,7 +6098,7 @@
         <v>384</v>
       </c>
       <c r="B385" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -6103,7 +6106,7 @@
         <v>385</v>
       </c>
       <c r="B386" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -6111,7 +6114,7 @@
         <v>386</v>
       </c>
       <c r="B387" s="1">
-        <v>520</v>
+        <v>860</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -6119,7 +6122,7 @@
         <v>387</v>
       </c>
       <c r="B388" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -6127,7 +6130,7 @@
         <v>388</v>
       </c>
       <c r="B389" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -6143,7 +6146,7 @@
         <v>390</v>
       </c>
       <c r="B391" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -6151,7 +6154,7 @@
         <v>391</v>
       </c>
       <c r="B392" s="1">
-        <v>700</v>
+        <v>420</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -6159,7 +6162,7 @@
         <v>392</v>
       </c>
       <c r="B393" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -6167,7 +6170,7 @@
         <v>393</v>
       </c>
       <c r="B394" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -6175,7 +6178,7 @@
         <v>394</v>
       </c>
       <c r="B395" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -6183,7 +6186,7 @@
         <v>395</v>
       </c>
       <c r="B396" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -6191,7 +6194,7 @@
         <v>396</v>
       </c>
       <c r="B397" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -6199,7 +6202,7 @@
         <v>397</v>
       </c>
       <c r="B398" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -6207,7 +6210,7 @@
         <v>398</v>
       </c>
       <c r="B399" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -6215,7 +6218,7 @@
         <v>399</v>
       </c>
       <c r="B400" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -6223,7 +6226,7 @@
         <v>400</v>
       </c>
       <c r="B401" s="1">
-        <v>440</v>
+        <v>620</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -6231,7 +6234,7 @@
         <v>401</v>
       </c>
       <c r="B402" s="1">
-        <v>1100</v>
+        <v>440</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -6247,7 +6250,7 @@
         <v>403</v>
       </c>
       <c r="B404" s="1">
-        <v>320</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -6255,7 +6258,7 @@
         <v>404</v>
       </c>
       <c r="B405" s="1">
-        <v>940</v>
+        <v>320</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -6263,7 +6266,7 @@
         <v>405</v>
       </c>
       <c r="B406" s="1">
-        <v>320</v>
+        <v>940</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -6271,7 +6274,7 @@
         <v>406</v>
       </c>
       <c r="B407" s="1">
-        <v>940</v>
+        <v>320</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -6279,7 +6282,7 @@
         <v>407</v>
       </c>
       <c r="B408" s="1">
-        <v>820</v>
+        <v>960</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -6287,7 +6290,7 @@
         <v>408</v>
       </c>
       <c r="B409" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -6295,7 +6298,7 @@
         <v>409</v>
       </c>
       <c r="B410" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -6311,7 +6314,7 @@
         <v>411</v>
       </c>
       <c r="B412" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -6319,7 +6322,7 @@
         <v>412</v>
       </c>
       <c r="B413" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -6335,7 +6338,7 @@
         <v>414</v>
       </c>
       <c r="B415" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -6343,7 +6346,7 @@
         <v>415</v>
       </c>
       <c r="B416" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -6351,7 +6354,7 @@
         <v>416</v>
       </c>
       <c r="B417" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -6359,7 +6362,7 @@
         <v>417</v>
       </c>
       <c r="B418" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -6367,7 +6370,7 @@
         <v>418</v>
       </c>
       <c r="B419" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -6375,7 +6378,7 @@
         <v>419</v>
       </c>
       <c r="B420" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -6383,7 +6386,7 @@
         <v>420</v>
       </c>
       <c r="B421" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -6399,7 +6402,7 @@
         <v>422</v>
       </c>
       <c r="B423" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -6407,7 +6410,7 @@
         <v>423</v>
       </c>
       <c r="B424" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -6415,7 +6418,7 @@
         <v>424</v>
       </c>
       <c r="B425" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -6423,7 +6426,7 @@
         <v>425</v>
       </c>
       <c r="B426" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -6431,7 +6434,7 @@
         <v>426</v>
       </c>
       <c r="B427" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -6439,7 +6442,7 @@
         <v>427</v>
       </c>
       <c r="B428" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6447,7 +6450,7 @@
         <v>428</v>
       </c>
       <c r="B429" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6455,7 +6458,7 @@
         <v>429</v>
       </c>
       <c r="B430" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6463,7 +6466,7 @@
         <v>430</v>
       </c>
       <c r="B431" s="1">
-        <v>700</v>
+        <v>440</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6471,7 +6474,7 @@
         <v>431</v>
       </c>
       <c r="B432" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6487,7 +6490,7 @@
         <v>433</v>
       </c>
       <c r="B434" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6495,7 +6498,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="1">
-        <v>560</v>
+        <v>800</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6503,7 +6506,7 @@
         <v>435</v>
       </c>
       <c r="B436" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6511,7 +6514,7 @@
         <v>436</v>
       </c>
       <c r="B437" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6519,7 +6522,7 @@
         <v>437</v>
       </c>
       <c r="B438" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6527,7 +6530,7 @@
         <v>438</v>
       </c>
       <c r="B439" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6535,7 +6538,7 @@
         <v>439</v>
       </c>
       <c r="B440" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6543,7 +6546,7 @@
         <v>440</v>
       </c>
       <c r="B441" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6551,7 +6554,7 @@
         <v>441</v>
       </c>
       <c r="B442" s="1">
-        <v>720</v>
+        <v>620</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6559,7 +6562,7 @@
         <v>442</v>
       </c>
       <c r="B443" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6567,7 +6570,7 @@
         <v>443</v>
       </c>
       <c r="B444" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6583,7 +6586,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6591,7 +6594,7 @@
         <v>446</v>
       </c>
       <c r="B447" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6599,7 +6602,7 @@
         <v>447</v>
       </c>
       <c r="B448" s="1">
-        <v>900</v>
+        <v>880</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6607,7 +6610,7 @@
         <v>448</v>
       </c>
       <c r="B449" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6615,7 +6618,7 @@
         <v>449</v>
       </c>
       <c r="B450" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6623,7 +6626,7 @@
         <v>450</v>
       </c>
       <c r="B451" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6631,7 +6634,7 @@
         <v>451</v>
       </c>
       <c r="B452" s="1">
-        <v>800</v>
+        <v>920</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6639,7 +6642,7 @@
         <v>452</v>
       </c>
       <c r="B453" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6647,7 +6650,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6655,7 +6658,7 @@
         <v>454</v>
       </c>
       <c r="B455" s="1">
-        <v>980</v>
+        <v>940</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6663,7 +6666,7 @@
         <v>455</v>
       </c>
       <c r="B456" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6671,7 +6674,7 @@
         <v>456</v>
       </c>
       <c r="B457" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6679,7 +6682,7 @@
         <v>457</v>
       </c>
       <c r="B458" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6687,7 +6690,7 @@
         <v>458</v>
       </c>
       <c r="B459" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6695,7 +6698,7 @@
         <v>459</v>
       </c>
       <c r="B460" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6711,7 +6714,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6719,7 +6722,7 @@
         <v>462</v>
       </c>
       <c r="B463" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6727,7 +6730,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="1">
-        <v>640</v>
+        <v>920</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6735,7 +6738,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6743,7 +6746,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6751,7 +6754,7 @@
         <v>466</v>
       </c>
       <c r="B467" s="1">
-        <v>960</v>
+        <v>820</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6759,7 +6762,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6767,7 +6770,7 @@
         <v>468</v>
       </c>
       <c r="B469" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6775,7 +6778,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6783,7 +6786,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="1">
-        <v>860</v>
+        <v>640</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6791,7 +6794,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6799,7 +6802,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6807,7 +6810,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6815,7 +6818,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6823,7 +6826,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6831,7 +6834,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6839,7 +6842,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6847,7 +6850,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="1">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6855,7 +6858,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="1">
-        <v>620</v>
+        <v>480</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6863,7 +6866,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6871,7 +6874,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6879,7 +6882,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6887,7 +6890,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6895,7 +6898,7 @@
         <v>484</v>
       </c>
       <c r="B485" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6903,7 +6906,7 @@
         <v>485</v>
       </c>
       <c r="B486" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6911,7 +6914,7 @@
         <v>486</v>
       </c>
       <c r="B487" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6919,7 +6922,7 @@
         <v>487</v>
       </c>
       <c r="B488" s="1">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6927,7 +6930,7 @@
         <v>488</v>
       </c>
       <c r="B489" s="1">
-        <v>840</v>
+        <v>480</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6935,7 +6938,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6943,7 +6946,7 @@
         <v>490</v>
       </c>
       <c r="B491" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6951,7 +6954,7 @@
         <v>491</v>
       </c>
       <c r="B492" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6967,7 +6970,7 @@
         <v>493</v>
       </c>
       <c r="B494" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6975,7 +6978,7 @@
         <v>494</v>
       </c>
       <c r="B495" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6983,7 +6986,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="1">
-        <v>880</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6999,7 +7002,7 @@
         <v>497</v>
       </c>
       <c r="B498" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -7007,7 +7010,7 @@
         <v>498</v>
       </c>
       <c r="B499" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -7015,7 +7018,7 @@
         <v>499</v>
       </c>
       <c r="B500" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -7023,7 +7026,7 @@
         <v>500</v>
       </c>
       <c r="B501" s="1">
-        <v>1100</v>
+        <v>660</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -7031,7 +7034,7 @@
         <v>501</v>
       </c>
       <c r="B502" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -7039,7 +7042,7 @@
         <v>502</v>
       </c>
       <c r="B503" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -7047,7 +7050,7 @@
         <v>503</v>
       </c>
       <c r="B504" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -7055,7 +7058,7 @@
         <v>504</v>
       </c>
       <c r="B505" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -7063,7 +7066,7 @@
         <v>505</v>
       </c>
       <c r="B506" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -7079,7 +7082,7 @@
         <v>507</v>
       </c>
       <c r="B508" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -7087,7 +7090,7 @@
         <v>508</v>
       </c>
       <c r="B509" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -7095,7 +7098,7 @@
         <v>509</v>
       </c>
       <c r="B510" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -7103,7 +7106,7 @@
         <v>510</v>
       </c>
       <c r="B511" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -7111,7 +7114,7 @@
         <v>511</v>
       </c>
       <c r="B512" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -7119,7 +7122,7 @@
         <v>512</v>
       </c>
       <c r="B513" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -7135,7 +7138,7 @@
         <v>514</v>
       </c>
       <c r="B515" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -7143,7 +7146,7 @@
         <v>515</v>
       </c>
       <c r="B516" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -7151,7 +7154,7 @@
         <v>516</v>
       </c>
       <c r="B517" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -7159,7 +7162,7 @@
         <v>517</v>
       </c>
       <c r="B518" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -7167,7 +7170,7 @@
         <v>518</v>
       </c>
       <c r="B519" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -7175,7 +7178,7 @@
         <v>519</v>
       </c>
       <c r="B520" s="1">
-        <v>840</v>
+        <v>620</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -7183,7 +7186,7 @@
         <v>520</v>
       </c>
       <c r="B521" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -7191,7 +7194,7 @@
         <v>521</v>
       </c>
       <c r="B522" s="1">
-        <v>1060</v>
+        <v>880</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -7199,7 +7202,7 @@
         <v>522</v>
       </c>
       <c r="B523" s="1">
-        <v>860</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -7215,7 +7218,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="1">
-        <v>800</v>
+        <v>860</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -7223,7 +7226,7 @@
         <v>525</v>
       </c>
       <c r="B526" s="1">
-        <v>860</v>
+        <v>800</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -7231,7 +7234,7 @@
         <v>526</v>
       </c>
       <c r="B527" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -7239,7 +7242,7 @@
         <v>527</v>
       </c>
       <c r="B528" s="1">
-        <v>760</v>
+        <v>960</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -7247,7 +7250,7 @@
         <v>528</v>
       </c>
       <c r="B529" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -7255,7 +7258,7 @@
         <v>529</v>
       </c>
       <c r="B530" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -7263,7 +7266,7 @@
         <v>530</v>
       </c>
       <c r="B531" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -7279,7 +7282,7 @@
         <v>532</v>
       </c>
       <c r="B533" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -7287,7 +7290,7 @@
         <v>533</v>
       </c>
       <c r="B534" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -7295,7 +7298,7 @@
         <v>534</v>
       </c>
       <c r="B535" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -7311,7 +7314,7 @@
         <v>536</v>
       </c>
       <c r="B537" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -7319,7 +7322,7 @@
         <v>537</v>
       </c>
       <c r="B538" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -7327,7 +7330,7 @@
         <v>538</v>
       </c>
       <c r="B539" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -7335,7 +7338,7 @@
         <v>539</v>
       </c>
       <c r="B540" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -7343,7 +7346,7 @@
         <v>540</v>
       </c>
       <c r="B541" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -7351,7 +7354,7 @@
         <v>541</v>
       </c>
       <c r="B542" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -7359,7 +7362,7 @@
         <v>542</v>
       </c>
       <c r="B543" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -7367,7 +7370,7 @@
         <v>543</v>
       </c>
       <c r="B544" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -7375,7 +7378,7 @@
         <v>544</v>
       </c>
       <c r="B545" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -7391,7 +7394,7 @@
         <v>546</v>
       </c>
       <c r="B547" s="1">
-        <v>880</v>
+        <v>700</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -7399,7 +7402,7 @@
         <v>547</v>
       </c>
       <c r="B548" s="1">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -7407,7 +7410,7 @@
         <v>548</v>
       </c>
       <c r="B549" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -7415,7 +7418,7 @@
         <v>549</v>
       </c>
       <c r="B550" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -7423,7 +7426,7 @@
         <v>550</v>
       </c>
       <c r="B551" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -7431,7 +7434,7 @@
         <v>551</v>
       </c>
       <c r="B552" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7439,7 +7442,7 @@
         <v>552</v>
       </c>
       <c r="B553" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7447,7 +7450,7 @@
         <v>553</v>
       </c>
       <c r="B554" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7455,7 +7458,7 @@
         <v>554</v>
       </c>
       <c r="B555" s="1">
-        <v>640</v>
+        <v>880</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7463,7 +7466,7 @@
         <v>555</v>
       </c>
       <c r="B556" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7471,7 +7474,7 @@
         <v>556</v>
       </c>
       <c r="B557" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7479,7 +7482,7 @@
         <v>557</v>
       </c>
       <c r="B558" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7495,7 +7498,7 @@
         <v>559</v>
       </c>
       <c r="B560" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7503,7 +7506,7 @@
         <v>560</v>
       </c>
       <c r="B561" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7519,7 +7522,7 @@
         <v>562</v>
       </c>
       <c r="B563" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7527,7 +7530,7 @@
         <v>563</v>
       </c>
       <c r="B564" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7535,7 +7538,7 @@
         <v>564</v>
       </c>
       <c r="B565" s="1">
-        <v>940</v>
+        <v>960</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7543,7 +7546,7 @@
         <v>565</v>
       </c>
       <c r="B566" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7559,7 +7562,7 @@
         <v>567</v>
       </c>
       <c r="B568" s="1">
-        <v>940</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7567,7 +7570,7 @@
         <v>568</v>
       </c>
       <c r="B569" s="1">
-        <v>860</v>
+        <v>940</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7575,7 +7578,7 @@
         <v>569</v>
       </c>
       <c r="B570" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7583,7 +7586,7 @@
         <v>570</v>
       </c>
       <c r="B571" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7591,7 +7594,7 @@
         <v>571</v>
       </c>
       <c r="B572" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7599,7 +7602,7 @@
         <v>572</v>
       </c>
       <c r="B573" s="1">
-        <v>840</v>
+        <v>680</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7607,7 +7610,7 @@
         <v>573</v>
       </c>
       <c r="B574" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7615,7 +7618,7 @@
         <v>574</v>
       </c>
       <c r="B575" s="1">
-        <v>580</v>
+        <v>880</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7623,7 +7626,7 @@
         <v>575</v>
       </c>
       <c r="B576" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7631,7 +7634,7 @@
         <v>576</v>
       </c>
       <c r="B577" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7639,7 +7642,7 @@
         <v>577</v>
       </c>
       <c r="B578" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7647,7 +7650,7 @@
         <v>578</v>
       </c>
       <c r="B579" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7655,7 +7658,7 @@
         <v>579</v>
       </c>
       <c r="B580" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7663,7 +7666,7 @@
         <v>580</v>
       </c>
       <c r="B581" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7671,7 +7674,7 @@
         <v>581</v>
       </c>
       <c r="B582" s="1">
-        <v>900</v>
+        <v>960</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7679,7 +7682,7 @@
         <v>582</v>
       </c>
       <c r="B583" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7687,7 +7690,7 @@
         <v>583</v>
       </c>
       <c r="B584" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7695,7 +7698,7 @@
         <v>584</v>
       </c>
       <c r="B585" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7703,7 +7706,7 @@
         <v>585</v>
       </c>
       <c r="B586" s="1">
-        <v>540</v>
+        <v>780</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7711,7 +7714,7 @@
         <v>586</v>
       </c>
       <c r="B587" s="1">
-        <v>1100</v>
+        <v>540</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7719,7 +7722,7 @@
         <v>587</v>
       </c>
       <c r="B588" s="1">
-        <v>1060</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7727,7 +7730,7 @@
         <v>588</v>
       </c>
       <c r="B589" s="1">
-        <v>1100</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7743,7 +7746,7 @@
         <v>590</v>
       </c>
       <c r="B591" s="1">
-        <v>1080</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7751,7 +7754,7 @@
         <v>591</v>
       </c>
       <c r="B592" s="1">
-        <v>840</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7767,7 +7770,7 @@
         <v>593</v>
       </c>
       <c r="B594" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7775,7 +7778,7 @@
         <v>594</v>
       </c>
       <c r="B595" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7783,7 +7786,7 @@
         <v>595</v>
       </c>
       <c r="B596" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7791,7 +7794,7 @@
         <v>596</v>
       </c>
       <c r="B597" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7799,7 +7802,7 @@
         <v>597</v>
       </c>
       <c r="B598" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7807,7 +7810,7 @@
         <v>598</v>
       </c>
       <c r="B599" s="1">
-        <v>980</v>
+        <v>860</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7815,7 +7818,7 @@
         <v>599</v>
       </c>
       <c r="B600" s="1">
-        <v>740</v>
+        <v>980</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7823,7 +7826,7 @@
         <v>600</v>
       </c>
       <c r="B601" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7831,7 +7834,7 @@
         <v>601</v>
       </c>
       <c r="B602" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7855,7 +7858,7 @@
         <v>604</v>
       </c>
       <c r="B605" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7879,7 +7882,7 @@
         <v>607</v>
       </c>
       <c r="B608" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7887,7 +7890,7 @@
         <v>608</v>
       </c>
       <c r="B609" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7895,7 +7898,7 @@
         <v>609</v>
       </c>
       <c r="B610" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7903,7 +7906,7 @@
         <v>610</v>
       </c>
       <c r="B611" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7911,7 +7914,7 @@
         <v>611</v>
       </c>
       <c r="B612" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7919,7 +7922,7 @@
         <v>612</v>
       </c>
       <c r="B613" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7927,7 +7930,7 @@
         <v>613</v>
       </c>
       <c r="B614" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -7935,7 +7938,7 @@
         <v>614</v>
       </c>
       <c r="B615" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -7943,7 +7946,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -7951,7 +7954,7 @@
         <v>616</v>
       </c>
       <c r="B617" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -7959,7 +7962,7 @@
         <v>617</v>
       </c>
       <c r="B618" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -7967,7 +7970,7 @@
         <v>618</v>
       </c>
       <c r="B619" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -7975,7 +7978,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="1">
-        <v>860</v>
+        <v>680</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -7983,7 +7986,7 @@
         <v>620</v>
       </c>
       <c r="B621" s="1">
-        <v>700</v>
+        <v>860</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -7991,7 +7994,7 @@
         <v>621</v>
       </c>
       <c r="B622" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -7999,7 +8002,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -8007,7 +8010,7 @@
         <v>623</v>
       </c>
       <c r="B624" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -8015,7 +8018,7 @@
         <v>624</v>
       </c>
       <c r="B625" s="1">
-        <v>1400</v>
+        <v>720</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -8023,7 +8026,7 @@
         <v>625</v>
       </c>
       <c r="B626" s="1">
-        <v>720</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -8031,7 +8034,7 @@
         <v>626</v>
       </c>
       <c r="B627" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -8039,7 +8042,7 @@
         <v>627</v>
       </c>
       <c r="B628" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -8047,7 +8050,7 @@
         <v>628</v>
       </c>
       <c r="B629" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -8055,7 +8058,7 @@
         <v>629</v>
       </c>
       <c r="B630" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -8063,7 +8066,7 @@
         <v>630</v>
       </c>
       <c r="B631" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -8071,7 +8074,7 @@
         <v>631</v>
       </c>
       <c r="B632" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -8087,7 +8090,7 @@
         <v>633</v>
       </c>
       <c r="B634" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -8095,7 +8098,7 @@
         <v>634</v>
       </c>
       <c r="B635" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -8103,7 +8106,7 @@
         <v>635</v>
       </c>
       <c r="B636" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -8111,7 +8114,7 @@
         <v>636</v>
       </c>
       <c r="B637" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -8119,7 +8122,7 @@
         <v>637</v>
       </c>
       <c r="B638" s="1">
-        <v>960</v>
+        <v>840</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -8127,7 +8130,7 @@
         <v>638</v>
       </c>
       <c r="B639" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -8143,7 +8146,7 @@
         <v>640</v>
       </c>
       <c r="B641" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -8151,7 +8154,7 @@
         <v>641</v>
       </c>
       <c r="B642" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -8167,7 +8170,7 @@
         <v>643</v>
       </c>
       <c r="B644" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -8175,7 +8178,7 @@
         <v>644</v>
       </c>
       <c r="B645" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -8191,7 +8194,7 @@
         <v>646</v>
       </c>
       <c r="B647" s="1">
-        <v>4000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -8199,7 +8202,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="1">
-        <v>720</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -8215,7 +8218,7 @@
         <v>649</v>
       </c>
       <c r="B650" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -8223,7 +8226,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -8231,7 +8234,7 @@
         <v>651</v>
       </c>
       <c r="B652" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -8239,7 +8242,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -8247,7 +8250,7 @@
         <v>653</v>
       </c>
       <c r="B654" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -8255,7 +8258,7 @@
         <v>654</v>
       </c>
       <c r="B655" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -8263,7 +8266,7 @@
         <v>655</v>
       </c>
       <c r="B656" s="1">
-        <v>540</v>
+        <v>900</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -8271,7 +8274,7 @@
         <v>656</v>
       </c>
       <c r="B657" s="1">
-        <v>660</v>
+        <v>540</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -8279,7 +8282,7 @@
         <v>657</v>
       </c>
       <c r="B658" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -8287,7 +8290,7 @@
         <v>658</v>
       </c>
       <c r="B659" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -8295,7 +8298,7 @@
         <v>659</v>
       </c>
       <c r="B660" s="1">
-        <v>860</v>
+        <v>900</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -8303,7 +8306,7 @@
         <v>660</v>
       </c>
       <c r="B661" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -8327,7 +8330,7 @@
         <v>663</v>
       </c>
       <c r="B664" s="1">
-        <v>980</v>
+        <v>900</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -8335,7 +8338,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -8351,7 +8354,7 @@
         <v>666</v>
       </c>
       <c r="B667" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -8359,7 +8362,7 @@
         <v>667</v>
       </c>
       <c r="B668" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -8367,7 +8370,7 @@
         <v>668</v>
       </c>
       <c r="B669" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -8375,7 +8378,7 @@
         <v>669</v>
       </c>
       <c r="B670" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -8383,7 +8386,7 @@
         <v>670</v>
       </c>
       <c r="B671" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -8391,7 +8394,7 @@
         <v>671</v>
       </c>
       <c r="B672" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -8399,7 +8402,7 @@
         <v>672</v>
       </c>
       <c r="B673" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -8407,7 +8410,7 @@
         <v>673</v>
       </c>
       <c r="B674" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -8415,7 +8418,7 @@
         <v>674</v>
       </c>
       <c r="B675" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8423,7 +8426,7 @@
         <v>675</v>
       </c>
       <c r="B676" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -8431,7 +8434,7 @@
         <v>676</v>
       </c>
       <c r="B677" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8439,7 +8442,7 @@
         <v>677</v>
       </c>
       <c r="B678" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8447,7 +8450,7 @@
         <v>678</v>
       </c>
       <c r="B679" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8455,7 +8458,7 @@
         <v>679</v>
       </c>
       <c r="B680" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8463,7 +8466,7 @@
         <v>680</v>
       </c>
       <c r="B681" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8471,7 +8474,7 @@
         <v>681</v>
       </c>
       <c r="B682" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8479,7 +8482,7 @@
         <v>682</v>
       </c>
       <c r="B683" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8487,7 +8490,7 @@
         <v>683</v>
       </c>
       <c r="B684" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8495,7 +8498,7 @@
         <v>684</v>
       </c>
       <c r="B685" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8503,7 +8506,7 @@
         <v>685</v>
       </c>
       <c r="B686" s="1">
-        <v>1000</v>
+        <v>880</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8511,7 +8514,7 @@
         <v>686</v>
       </c>
       <c r="B687" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8519,7 +8522,7 @@
         <v>687</v>
       </c>
       <c r="B688" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8527,7 +8530,7 @@
         <v>688</v>
       </c>
       <c r="B689" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8535,7 +8538,7 @@
         <v>689</v>
       </c>
       <c r="B690" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8543,7 +8546,7 @@
         <v>690</v>
       </c>
       <c r="B691" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8551,7 +8554,7 @@
         <v>691</v>
       </c>
       <c r="B692" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8559,7 +8562,7 @@
         <v>692</v>
       </c>
       <c r="B693" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8567,7 +8570,7 @@
         <v>693</v>
       </c>
       <c r="B694" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8583,7 +8586,7 @@
         <v>695</v>
       </c>
       <c r="B696" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8591,7 +8594,7 @@
         <v>696</v>
       </c>
       <c r="B697" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8599,7 +8602,7 @@
         <v>697</v>
       </c>
       <c r="B698" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8607,7 +8610,7 @@
         <v>698</v>
       </c>
       <c r="B699" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8615,7 +8618,7 @@
         <v>699</v>
       </c>
       <c r="B700" s="1">
-        <v>880</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8623,7 +8626,7 @@
         <v>700</v>
       </c>
       <c r="B701" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8631,7 +8634,7 @@
         <v>701</v>
       </c>
       <c r="B702" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8639,7 +8642,7 @@
         <v>702</v>
       </c>
       <c r="B703" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8647,7 +8650,7 @@
         <v>703</v>
       </c>
       <c r="B704" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8655,7 +8658,7 @@
         <v>704</v>
       </c>
       <c r="B705" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8663,7 +8666,7 @@
         <v>705</v>
       </c>
       <c r="B706" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8671,7 +8674,7 @@
         <v>706</v>
       </c>
       <c r="B707" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8679,7 +8682,7 @@
         <v>707</v>
       </c>
       <c r="B708" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8695,7 +8698,7 @@
         <v>709</v>
       </c>
       <c r="B710" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8711,7 +8714,7 @@
         <v>711</v>
       </c>
       <c r="B712" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8719,7 +8722,7 @@
         <v>712</v>
       </c>
       <c r="B713" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8727,7 +8730,7 @@
         <v>713</v>
       </c>
       <c r="B714" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8735,7 +8738,7 @@
         <v>714</v>
       </c>
       <c r="B715" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8743,7 +8746,7 @@
         <v>715</v>
       </c>
       <c r="B716" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8751,7 +8754,7 @@
         <v>716</v>
       </c>
       <c r="B717" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8759,7 +8762,7 @@
         <v>717</v>
       </c>
       <c r="B718" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8767,7 +8770,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8775,7 +8778,7 @@
         <v>719</v>
       </c>
       <c r="B720" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8783,7 +8786,7 @@
         <v>720</v>
       </c>
       <c r="B721" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8791,7 +8794,7 @@
         <v>721</v>
       </c>
       <c r="B722" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8799,7 +8802,7 @@
         <v>722</v>
       </c>
       <c r="B723" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8807,7 +8810,7 @@
         <v>723</v>
       </c>
       <c r="B724" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8815,7 +8818,7 @@
         <v>724</v>
       </c>
       <c r="B725" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8823,7 +8826,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8831,7 +8834,7 @@
         <v>726</v>
       </c>
       <c r="B727" s="1">
-        <v>1100</v>
+        <v>720</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8839,7 +8842,7 @@
         <v>727</v>
       </c>
       <c r="B728" s="1">
-        <v>940</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8855,7 +8858,7 @@
         <v>729</v>
       </c>
       <c r="B730" s="1">
-        <v>820</v>
+        <v>940</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8863,7 +8866,7 @@
         <v>730</v>
       </c>
       <c r="B731" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8871,7 +8874,7 @@
         <v>731</v>
       </c>
       <c r="B732" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -8887,7 +8890,7 @@
         <v>733</v>
       </c>
       <c r="B734" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -8895,7 +8898,7 @@
         <v>734</v>
       </c>
       <c r="B735" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -8903,7 +8906,7 @@
         <v>735</v>
       </c>
       <c r="B736" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -8911,7 +8914,7 @@
         <v>736</v>
       </c>
       <c r="B737" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -8919,7 +8922,7 @@
         <v>737</v>
       </c>
       <c r="B738" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="739" spans="1:2">
@@ -8935,7 +8938,7 @@
         <v>739</v>
       </c>
       <c r="B740" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -8943,7 +8946,7 @@
         <v>740</v>
       </c>
       <c r="B741" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="742" spans="1:2">
@@ -8951,7 +8954,7 @@
         <v>741</v>
       </c>
       <c r="B742" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -8959,7 +8962,7 @@
         <v>742</v>
       </c>
       <c r="B743" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="744" spans="1:2">
@@ -8967,7 +8970,7 @@
         <v>743</v>
       </c>
       <c r="B744" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="745" spans="1:2">
@@ -8975,7 +8978,7 @@
         <v>744</v>
       </c>
       <c r="B745" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -8983,7 +8986,7 @@
         <v>745</v>
       </c>
       <c r="B746" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="747" spans="1:2">
@@ -8991,7 +8994,7 @@
         <v>746</v>
       </c>
       <c r="B747" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="748" spans="1:2">
@@ -8999,7 +9002,7 @@
         <v>747</v>
       </c>
       <c r="B748" s="1">
-        <v>700</v>
+        <v>440</v>
       </c>
     </row>
     <row r="749" spans="1:2">
@@ -9007,7 +9010,7 @@
         <v>748</v>
       </c>
       <c r="B749" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -9023,7 +9026,7 @@
         <v>750</v>
       </c>
       <c r="B751" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="752" spans="1:2">
@@ -9031,7 +9034,7 @@
         <v>751</v>
       </c>
       <c r="B752" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="753" spans="1:2">
@@ -9039,7 +9042,7 @@
         <v>752</v>
       </c>
       <c r="B753" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="754" spans="1:2">
@@ -9047,7 +9050,7 @@
         <v>753</v>
       </c>
       <c r="B754" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -9055,7 +9058,7 @@
         <v>754</v>
       </c>
       <c r="B755" s="1">
-        <v>900</v>
+        <v>560</v>
       </c>
     </row>
     <row r="756" spans="1:2">
@@ -9063,7 +9066,7 @@
         <v>755</v>
       </c>
       <c r="B756" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="757" spans="1:2">
@@ -9071,7 +9074,7 @@
         <v>756</v>
       </c>
       <c r="B757" s="1">
-        <v>800</v>
+        <v>880</v>
       </c>
     </row>
     <row r="758" spans="1:2">
@@ -9079,7 +9082,7 @@
         <v>757</v>
       </c>
       <c r="B758" s="1">
-        <v>880</v>
+        <v>800</v>
       </c>
     </row>
     <row r="759" spans="1:2">
@@ -9087,7 +9090,7 @@
         <v>758</v>
       </c>
       <c r="B759" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="760" spans="1:2">
@@ -9095,7 +9098,7 @@
         <v>759</v>
       </c>
       <c r="B760" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="761" spans="1:2">
@@ -9103,7 +9106,7 @@
         <v>760</v>
       </c>
       <c r="B761" s="1">
-        <v>800</v>
+        <v>920</v>
       </c>
     </row>
     <row r="762" spans="1:2">
@@ -9111,7 +9114,7 @@
         <v>761</v>
       </c>
       <c r="B762" s="1">
-        <v>940</v>
+        <v>800</v>
       </c>
     </row>
     <row r="763" spans="1:2">
@@ -9119,7 +9122,7 @@
         <v>762</v>
       </c>
       <c r="B763" s="1">
-        <v>980</v>
+        <v>940</v>
       </c>
     </row>
     <row r="764" spans="1:2">
@@ -9127,7 +9130,7 @@
         <v>763</v>
       </c>
       <c r="B764" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="765" spans="1:2">
@@ -9135,7 +9138,7 @@
         <v>764</v>
       </c>
       <c r="B765" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="766" spans="1:2">
@@ -9143,7 +9146,7 @@
         <v>765</v>
       </c>
       <c r="B766" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="767" spans="1:2">
@@ -9151,7 +9154,7 @@
         <v>766</v>
       </c>
       <c r="B767" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="768" spans="1:2">
@@ -9159,7 +9162,7 @@
         <v>767</v>
       </c>
       <c r="B768" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="769" spans="1:2">
@@ -9167,7 +9170,7 @@
         <v>768</v>
       </c>
       <c r="B769" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="770" spans="1:2">
@@ -9175,7 +9178,7 @@
         <v>769</v>
       </c>
       <c r="B770" s="1">
-        <v>960</v>
+        <v>820</v>
       </c>
     </row>
     <row r="771" spans="1:2">
@@ -9183,7 +9186,7 @@
         <v>770</v>
       </c>
       <c r="B771" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="772" spans="1:2">
@@ -9191,7 +9194,7 @@
         <v>771</v>
       </c>
       <c r="B772" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="773" spans="1:2">
@@ -9199,7 +9202,7 @@
         <v>772</v>
       </c>
       <c r="B773" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="774" spans="1:2">
@@ -9207,7 +9210,7 @@
         <v>773</v>
       </c>
       <c r="B774" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="775" spans="1:2">
@@ -9215,7 +9218,7 @@
         <v>774</v>
       </c>
       <c r="B775" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="776" spans="1:2">
@@ -9223,7 +9226,7 @@
         <v>775</v>
       </c>
       <c r="B776" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="777" spans="1:2">
@@ -9231,7 +9234,7 @@
         <v>776</v>
       </c>
       <c r="B777" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="778" spans="1:2">
@@ -9239,7 +9242,7 @@
         <v>777</v>
       </c>
       <c r="B778" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="779" spans="1:2">
@@ -9247,7 +9250,7 @@
         <v>778</v>
       </c>
       <c r="B779" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="780" spans="1:2">
@@ -9255,7 +9258,7 @@
         <v>779</v>
       </c>
       <c r="B780" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="781" spans="1:2">
@@ -9263,7 +9266,7 @@
         <v>780</v>
       </c>
       <c r="B781" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="782" spans="1:2">
@@ -9271,7 +9274,7 @@
         <v>781</v>
       </c>
       <c r="B782" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="783" spans="1:2">
@@ -9279,7 +9282,7 @@
         <v>782</v>
       </c>
       <c r="B783" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="784" spans="1:2">
@@ -9287,7 +9290,7 @@
         <v>783</v>
       </c>
       <c r="B784" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="785" spans="1:2">
@@ -9295,7 +9298,7 @@
         <v>784</v>
       </c>
       <c r="B785" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="786" spans="1:2">
@@ -9303,7 +9306,7 @@
         <v>785</v>
       </c>
       <c r="B786" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="787" spans="1:2">
@@ -9311,7 +9314,7 @@
         <v>786</v>
       </c>
       <c r="B787" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="788" spans="1:2">
@@ -9319,7 +9322,7 @@
         <v>787</v>
       </c>
       <c r="B788" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="789" spans="1:2">
@@ -9327,7 +9330,7 @@
         <v>788</v>
       </c>
       <c r="B789" s="1">
-        <v>860</v>
+        <v>800</v>
       </c>
     </row>
     <row r="790" spans="1:2">
@@ -9335,7 +9338,7 @@
         <v>789</v>
       </c>
       <c r="B790" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="791" spans="1:2">
@@ -9343,7 +9346,7 @@
         <v>790</v>
       </c>
       <c r="B791" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="792" spans="1:2">
@@ -9351,7 +9354,7 @@
         <v>791</v>
       </c>
       <c r="B792" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="793" spans="1:2">
@@ -9359,7 +9362,7 @@
         <v>792</v>
       </c>
       <c r="B793" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="794" spans="1:2">
@@ -9367,7 +9370,7 @@
         <v>793</v>
       </c>
       <c r="B794" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="795" spans="1:2">
@@ -9383,7 +9386,7 @@
         <v>795</v>
       </c>
       <c r="B796" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="797" spans="1:2">
@@ -9399,7 +9402,7 @@
         <v>797</v>
       </c>
       <c r="B798" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="799" spans="1:2">
@@ -9407,7 +9410,7 @@
         <v>798</v>
       </c>
       <c r="B799" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="800" spans="1:2">
@@ -9415,7 +9418,7 @@
         <v>799</v>
       </c>
       <c r="B800" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="801" spans="1:2">
@@ -9423,7 +9426,7 @@
         <v>800</v>
       </c>
       <c r="B801" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="802" spans="1:2">
@@ -9431,7 +9434,7 @@
         <v>801</v>
       </c>
       <c r="B802" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="803" spans="1:2">
@@ -9439,7 +9442,7 @@
         <v>802</v>
       </c>
       <c r="B803" s="1">
-        <v>940</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="804" spans="1:2">
@@ -9447,7 +9450,7 @@
         <v>803</v>
       </c>
       <c r="B804" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="805" spans="1:2">
@@ -9455,7 +9458,7 @@
         <v>804</v>
       </c>
       <c r="B805" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="806" spans="1:2">
@@ -9463,7 +9466,7 @@
         <v>805</v>
       </c>
       <c r="B806" s="1">
-        <v>1100</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="807" spans="1:2">
@@ -9471,7 +9474,7 @@
         <v>806</v>
       </c>
       <c r="B807" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="808" spans="1:2">
@@ -9487,7 +9490,7 @@
         <v>808</v>
       </c>
       <c r="B809" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="810" spans="1:2">
@@ -9495,7 +9498,7 @@
         <v>809</v>
       </c>
       <c r="B810" s="1">
-        <v>740</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="811" spans="1:2">
@@ -9503,7 +9506,7 @@
         <v>810</v>
       </c>
       <c r="B811" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="812" spans="1:2">
@@ -9511,7 +9514,7 @@
         <v>811</v>
       </c>
       <c r="B812" s="1">
-        <v>440</v>
+        <v>820</v>
       </c>
     </row>
     <row r="813" spans="1:2">
@@ -9519,7 +9522,7 @@
         <v>812</v>
       </c>
       <c r="B813" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="814" spans="1:2">
@@ -9527,7 +9530,7 @@
         <v>813</v>
       </c>
       <c r="B814" s="1">
-        <v>440</v>
+        <v>500</v>
       </c>
     </row>
     <row r="815" spans="1:2">
@@ -9535,7 +9538,7 @@
         <v>814</v>
       </c>
       <c r="B815" s="1">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="816" spans="1:2">
@@ -9543,7 +9546,7 @@
         <v>815</v>
       </c>
       <c r="B816" s="1">
-        <v>500</v>
+        <v>560</v>
       </c>
     </row>
     <row r="817" spans="1:2">
@@ -9551,7 +9554,7 @@
         <v>816</v>
       </c>
       <c r="B817" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="818" spans="1:2">
@@ -9567,7 +9570,7 @@
         <v>818</v>
       </c>
       <c r="B819" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="820" spans="1:2">
@@ -9575,7 +9578,7 @@
         <v>819</v>
       </c>
       <c r="B820" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="821" spans="1:2">
@@ -9583,7 +9586,7 @@
         <v>820</v>
       </c>
       <c r="B821" s="1">
-        <v>400</v>
+        <v>840</v>
       </c>
     </row>
     <row r="822" spans="1:2">
@@ -9599,7 +9602,7 @@
         <v>822</v>
       </c>
       <c r="B823" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="824" spans="1:2">
@@ -9607,7 +9610,7 @@
         <v>823</v>
       </c>
       <c r="B824" s="1">
-        <v>840</v>
+        <v>380</v>
       </c>
     </row>
     <row r="825" spans="1:2">
@@ -9615,7 +9618,7 @@
         <v>824</v>
       </c>
       <c r="B825" s="1">
-        <v>380</v>
+        <v>840</v>
       </c>
     </row>
     <row r="826" spans="1:2">
@@ -9631,7 +9634,7 @@
         <v>826</v>
       </c>
       <c r="B827" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="828" spans="1:2">
@@ -9639,7 +9642,7 @@
         <v>827</v>
       </c>
       <c r="B828" s="1">
-        <v>700</v>
+        <v>520</v>
       </c>
     </row>
     <row r="829" spans="1:2">
@@ -9647,7 +9650,7 @@
         <v>828</v>
       </c>
       <c r="B829" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="830" spans="1:2">
@@ -9655,7 +9658,7 @@
         <v>829</v>
       </c>
       <c r="B830" s="1">
-        <v>860</v>
+        <v>800</v>
       </c>
     </row>
     <row r="831" spans="1:2">
@@ -9663,7 +9666,7 @@
         <v>830</v>
       </c>
       <c r="B831" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="832" spans="1:2">
@@ -9671,7 +9674,7 @@
         <v>831</v>
       </c>
       <c r="B832" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="833" spans="1:2">
@@ -9687,7 +9690,7 @@
         <v>833</v>
       </c>
       <c r="B834" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="835" spans="1:2">
@@ -9695,7 +9698,7 @@
         <v>834</v>
       </c>
       <c r="B835" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="836" spans="1:2">
@@ -9703,7 +9706,7 @@
         <v>835</v>
       </c>
       <c r="B836" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="837" spans="1:2">
@@ -9719,7 +9722,7 @@
         <v>837</v>
       </c>
       <c r="B838" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="839" spans="1:2">
@@ -9735,7 +9738,7 @@
         <v>839</v>
       </c>
       <c r="B840" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="841" spans="1:2">
@@ -9743,7 +9746,7 @@
         <v>840</v>
       </c>
       <c r="B841" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="842" spans="1:2">
@@ -9751,7 +9754,7 @@
         <v>841</v>
       </c>
       <c r="B842" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="843" spans="1:2">
@@ -9759,7 +9762,7 @@
         <v>842</v>
       </c>
       <c r="B843" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="844" spans="1:2">
@@ -9775,7 +9778,7 @@
         <v>844</v>
       </c>
       <c r="B845" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="846" spans="1:2">
@@ -9783,7 +9786,7 @@
         <v>845</v>
       </c>
       <c r="B846" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="847" spans="1:2">
@@ -9791,7 +9794,7 @@
         <v>846</v>
       </c>
       <c r="B847" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="848" spans="1:2">
@@ -9799,7 +9802,7 @@
         <v>847</v>
       </c>
       <c r="B848" s="1">
-        <v>940</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="849" spans="1:2">
@@ -9807,7 +9810,7 @@
         <v>848</v>
       </c>
       <c r="B849" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="850" spans="1:2">
@@ -9815,7 +9818,7 @@
         <v>849</v>
       </c>
       <c r="B850" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="851" spans="1:2">
@@ -9823,7 +9826,7 @@
         <v>850</v>
       </c>
       <c r="B851" s="1">
-        <v>1100</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="852" spans="1:2">
@@ -9831,7 +9834,7 @@
         <v>851</v>
       </c>
       <c r="B852" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="853" spans="1:2">
@@ -9847,7 +9850,7 @@
         <v>853</v>
       </c>
       <c r="B854" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="855" spans="1:2">
@@ -9855,7 +9858,7 @@
         <v>854</v>
       </c>
       <c r="B855" s="1">
-        <v>740</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="856" spans="1:2">
@@ -9863,7 +9866,7 @@
         <v>855</v>
       </c>
       <c r="B856" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="857" spans="1:2">
@@ -9871,7 +9874,7 @@
         <v>856</v>
       </c>
       <c r="B857" s="1">
-        <v>440</v>
+        <v>820</v>
       </c>
     </row>
     <row r="858" spans="1:2">
@@ -9879,7 +9882,7 @@
         <v>857</v>
       </c>
       <c r="B858" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="859" spans="1:2">
@@ -9887,7 +9890,7 @@
         <v>858</v>
       </c>
       <c r="B859" s="1">
-        <v>440</v>
+        <v>500</v>
       </c>
     </row>
     <row r="860" spans="1:2">
@@ -9895,7 +9898,7 @@
         <v>859</v>
       </c>
       <c r="B860" s="1">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="861" spans="1:2">
@@ -9903,7 +9906,7 @@
         <v>860</v>
       </c>
       <c r="B861" s="1">
-        <v>500</v>
+        <v>560</v>
       </c>
     </row>
     <row r="862" spans="1:2">
@@ -9911,7 +9914,7 @@
         <v>861</v>
       </c>
       <c r="B862" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="863" spans="1:2">
@@ -9919,7 +9922,7 @@
         <v>862</v>
       </c>
       <c r="B863" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="864" spans="1:2">
@@ -9943,7 +9946,7 @@
         <v>865</v>
       </c>
       <c r="B866" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="867" spans="1:2">
@@ -9967,7 +9970,7 @@
         <v>868</v>
       </c>
       <c r="B869" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="870" spans="1:2">
@@ -9983,7 +9986,7 @@
         <v>870</v>
       </c>
       <c r="B871" s="1">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="872" spans="1:2">
@@ -9991,7 +9994,7 @@
         <v>871</v>
       </c>
       <c r="B872" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="873" spans="1:2">
@@ -9999,7 +10002,7 @@
         <v>872</v>
       </c>
       <c r="B873" s="1">
-        <v>600</v>
+        <v>380</v>
       </c>
     </row>
     <row r="874" spans="1:2">
@@ -10007,7 +10010,7 @@
         <v>873</v>
       </c>
       <c r="B874" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="875" spans="1:2">
@@ -10015,7 +10018,7 @@
         <v>874</v>
       </c>
       <c r="B875" s="1">
-        <v>660</v>
+        <v>820</v>
       </c>
     </row>
     <row r="876" spans="1:2">
@@ -10023,7 +10026,7 @@
         <v>875</v>
       </c>
       <c r="B876" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="877" spans="1:2">
@@ -10031,7 +10034,7 @@
         <v>876</v>
       </c>
       <c r="B877" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="878" spans="1:2">
@@ -10039,7 +10042,7 @@
         <v>877</v>
       </c>
       <c r="B878" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="879" spans="1:2">
@@ -10047,7 +10050,7 @@
         <v>878</v>
       </c>
       <c r="B879" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="880" spans="1:2">
@@ -10055,7 +10058,7 @@
         <v>879</v>
       </c>
       <c r="B880" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="881" spans="1:2">
@@ -10063,6 +10066,14 @@
         <v>880</v>
       </c>
       <c r="B881" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="882" spans="1:2">
+      <c r="A882" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="B882" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="898">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="901">
   <si>
     <t>Наименование</t>
   </si>
@@ -440,6 +440,9 @@
     <t>GUSI - HIGH LAND 7 | cascade • simcoe (APA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>GUSI - Octoberfest 2026 (Festbeer), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>GUSI - Seven Days 25 (NE APA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1766,6 +1769,9 @@
     <t>вынос_GUSI - HIGH LAND 7 | cascade х simcoe (APA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_GUSI - Octoberfest 2026 (Festbeer), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_GUSI - Seven Days 25 (NE APA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -2412,6 +2418,9 @@
   </si>
   <si>
     <t xml:space="preserve">вынос_Заповедник - Абанамат (Сухой Сидр), РОЗЛИВ, Россия </t>
+  </si>
+  <si>
+    <t xml:space="preserve">вынос_Как С Куста - Полусухой, РОЗЛИВ, Россия </t>
   </si>
   <si>
     <t>вынос_Одна тонна - Gruner Gold, РОЗЛИВ, Россия</t>
@@ -3062,7 +3071,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B898"/>
+  <dimension ref="A1:B901"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -4194,7 +4203,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -4202,7 +4211,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>580</v>
+        <v>880</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -4210,7 +4219,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -4218,7 +4227,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -4226,7 +4235,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>620</v>
+        <v>860</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -4234,7 +4243,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -4242,7 +4251,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -4250,7 +4259,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -4258,7 +4267,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -4266,7 +4275,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>900</v>
+        <v>960</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -4274,7 +4283,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -4282,7 +4291,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -4290,7 +4299,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -4298,7 +4307,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>500</v>
+        <v>780</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -4306,7 +4315,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>580</v>
+        <v>500</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -4314,7 +4323,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -4322,7 +4331,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -4330,7 +4339,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>1100</v>
+        <v>520</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -4338,7 +4347,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>1060</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -4354,7 +4363,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>1100</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -4370,7 +4379,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -4378,7 +4387,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>1080</v>
+        <v>560</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -4386,12 +4395,12 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>840</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B166" s="1">
         <v>840</v>
@@ -4410,7 +4419,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="1">
-        <v>420</v>
+        <v>840</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4418,7 +4427,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="1">
-        <v>520</v>
+        <v>420</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -4426,7 +4435,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -4434,7 +4443,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="1">
-        <v>460</v>
+        <v>720</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -4442,7 +4451,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="1">
-        <v>560</v>
+        <v>460</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4450,7 +4459,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4458,7 +4467,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4466,7 +4475,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4474,7 +4483,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4482,7 +4491,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="1">
-        <v>980</v>
+        <v>520</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4490,7 +4499,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="1">
-        <v>540</v>
+        <v>980</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4498,7 +4507,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4506,7 +4515,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4514,7 +4523,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4522,7 +4531,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="1">
-        <v>560</v>
+        <v>760</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4530,7 +4539,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="1">
-        <v>1100</v>
+        <v>560</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4562,7 +4571,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4570,7 +4579,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4578,7 +4587,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4586,7 +4595,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4618,7 +4627,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4626,7 +4635,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4634,7 +4643,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4642,7 +4651,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4650,7 +4659,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4658,7 +4667,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4666,7 +4675,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="1">
-        <v>460</v>
+        <v>700</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4674,7 +4683,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4682,7 +4691,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="1">
-        <v>720</v>
+        <v>580</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4690,7 +4699,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4698,7 +4707,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4706,7 +4715,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="1">
-        <v>260</v>
+        <v>780</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4722,7 +4731,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4738,7 +4747,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4746,7 +4755,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4754,7 +4763,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4762,7 +4771,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="1">
-        <v>500</v>
+        <v>760</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4770,7 +4779,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4778,7 +4787,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="1">
-        <v>740</v>
+        <v>400</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4786,7 +4795,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4794,7 +4803,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4802,7 +4811,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4810,7 +4819,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4818,7 +4827,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4826,7 +4835,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4842,7 +4851,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4850,7 +4859,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4858,7 +4867,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4866,7 +4875,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4874,7 +4883,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="1">
-        <v>580</v>
+        <v>860</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4882,7 +4891,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4890,7 +4899,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="1">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4898,7 +4907,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4906,7 +4915,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4914,7 +4923,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4922,7 +4931,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4930,7 +4939,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4938,7 +4947,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4946,7 +4955,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4954,7 +4963,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4962,7 +4971,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4970,7 +4979,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="1">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4978,7 +4987,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="1">
-        <v>480</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4986,7 +4995,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4994,7 +5003,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -5002,7 +5011,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -5010,7 +5019,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -5018,7 +5027,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -5026,7 +5035,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -5034,7 +5043,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -5042,7 +5051,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -5050,7 +5059,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="1">
-        <v>900</v>
+        <v>520</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -5058,7 +5067,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -5066,7 +5075,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -5074,7 +5083,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -5082,7 +5091,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -5098,7 +5107,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -5114,7 +5123,7 @@
         <v>255</v>
       </c>
       <c r="B256" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -5122,7 +5131,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -5130,7 +5139,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -5138,7 +5147,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -5146,7 +5155,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -5154,7 +5163,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -5162,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="1">
-        <v>960</v>
+        <v>840</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -5170,7 +5179,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -5186,7 +5195,7 @@
         <v>264</v>
       </c>
       <c r="B265" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -5194,7 +5203,7 @@
         <v>265</v>
       </c>
       <c r="B266" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -5202,7 +5211,7 @@
         <v>266</v>
       </c>
       <c r="B267" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -5210,7 +5219,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -5218,7 +5227,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -5226,7 +5235,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -5242,7 +5251,7 @@
         <v>271</v>
       </c>
       <c r="B272" s="1">
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -5250,7 +5259,7 @@
         <v>272</v>
       </c>
       <c r="B273" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -5258,7 +5267,7 @@
         <v>273</v>
       </c>
       <c r="B274" s="1">
-        <v>758</v>
+        <v>500</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -5266,7 +5275,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="1">
-        <v>2273</v>
+        <v>758</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -5274,7 +5283,7 @@
         <v>275</v>
       </c>
       <c r="B276" s="1">
-        <v>1515</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -5282,7 +5291,7 @@
         <v>276</v>
       </c>
       <c r="B277" s="1">
-        <v>520</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -5290,7 +5299,7 @@
         <v>277</v>
       </c>
       <c r="B278" s="1">
-        <v>4000</v>
+        <v>520</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -5298,7 +5307,7 @@
         <v>278</v>
       </c>
       <c r="B279" s="1">
-        <v>560</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -5306,7 +5315,7 @@
         <v>279</v>
       </c>
       <c r="B280" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -5314,7 +5323,7 @@
         <v>280</v>
       </c>
       <c r="B281" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -5330,7 +5339,7 @@
         <v>282</v>
       </c>
       <c r="B283" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -5338,7 +5347,7 @@
         <v>283</v>
       </c>
       <c r="B284" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -5346,7 +5355,7 @@
         <v>284</v>
       </c>
       <c r="B285" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -5354,7 +5363,7 @@
         <v>285</v>
       </c>
       <c r="B286" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5362,7 +5371,7 @@
         <v>286</v>
       </c>
       <c r="B287" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5370,7 +5379,7 @@
         <v>287</v>
       </c>
       <c r="B288" s="1">
-        <v>680</v>
+        <v>520</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5378,7 +5387,7 @@
         <v>288</v>
       </c>
       <c r="B289" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5386,7 +5395,7 @@
         <v>289</v>
       </c>
       <c r="B290" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5394,7 +5403,7 @@
         <v>290</v>
       </c>
       <c r="B291" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5402,7 +5411,7 @@
         <v>291</v>
       </c>
       <c r="B292" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5410,7 +5419,7 @@
         <v>292</v>
       </c>
       <c r="B293" s="1">
-        <v>660</v>
+        <v>380</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5418,7 +5427,7 @@
         <v>293</v>
       </c>
       <c r="B294" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5426,7 +5435,7 @@
         <v>294</v>
       </c>
       <c r="B295" s="1">
-        <v>540</v>
+        <v>900</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5434,7 +5443,7 @@
         <v>295</v>
       </c>
       <c r="B296" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5442,7 +5451,7 @@
         <v>296</v>
       </c>
       <c r="B297" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5450,7 +5459,7 @@
         <v>297</v>
       </c>
       <c r="B298" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5458,7 +5467,7 @@
         <v>298</v>
       </c>
       <c r="B299" s="1">
-        <v>460</v>
+        <v>580</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5466,7 +5475,7 @@
         <v>299</v>
       </c>
       <c r="B300" s="1">
-        <v>520</v>
+        <v>460</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5474,7 +5483,7 @@
         <v>300</v>
       </c>
       <c r="B301" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5482,7 +5491,7 @@
         <v>301</v>
       </c>
       <c r="B302" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5490,7 +5499,7 @@
         <v>302</v>
       </c>
       <c r="B303" s="1">
-        <v>860</v>
+        <v>900</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5498,7 +5507,7 @@
         <v>303</v>
       </c>
       <c r="B304" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5522,7 +5531,7 @@
         <v>306</v>
       </c>
       <c r="B307" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5538,7 +5547,7 @@
         <v>308</v>
       </c>
       <c r="B309" s="1">
-        <v>980</v>
+        <v>560</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5546,7 +5555,7 @@
         <v>309</v>
       </c>
       <c r="B310" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5562,7 +5571,7 @@
         <v>311</v>
       </c>
       <c r="B312" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5570,7 +5579,7 @@
         <v>312</v>
       </c>
       <c r="B313" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5578,7 +5587,7 @@
         <v>313</v>
       </c>
       <c r="B314" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5586,7 +5595,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5594,7 +5603,7 @@
         <v>315</v>
       </c>
       <c r="B316" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5602,7 +5611,7 @@
         <v>316</v>
       </c>
       <c r="B317" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5610,7 +5619,7 @@
         <v>317</v>
       </c>
       <c r="B318" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5618,7 +5627,7 @@
         <v>318</v>
       </c>
       <c r="B319" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5626,7 +5635,7 @@
         <v>319</v>
       </c>
       <c r="B320" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5634,7 +5643,7 @@
         <v>320</v>
       </c>
       <c r="B321" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5642,7 +5651,7 @@
         <v>321</v>
       </c>
       <c r="B322" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5650,7 +5659,7 @@
         <v>322</v>
       </c>
       <c r="B323" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5658,7 +5667,7 @@
         <v>323</v>
       </c>
       <c r="B324" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5666,7 +5675,7 @@
         <v>324</v>
       </c>
       <c r="B325" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5674,7 +5683,7 @@
         <v>325</v>
       </c>
       <c r="B326" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5682,7 +5691,7 @@
         <v>326</v>
       </c>
       <c r="B327" s="1">
-        <v>520</v>
+        <v>680</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5690,7 +5699,7 @@
         <v>327</v>
       </c>
       <c r="B328" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5698,7 +5707,7 @@
         <v>328</v>
       </c>
       <c r="B329" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5706,7 +5715,7 @@
         <v>329</v>
       </c>
       <c r="B330" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5714,7 +5723,7 @@
         <v>330</v>
       </c>
       <c r="B331" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5722,7 +5731,7 @@
         <v>331</v>
       </c>
       <c r="B332" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5730,7 +5739,7 @@
         <v>332</v>
       </c>
       <c r="B333" s="1">
-        <v>580</v>
+        <v>840</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5738,7 +5747,7 @@
         <v>333</v>
       </c>
       <c r="B334" s="1">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5746,7 +5755,7 @@
         <v>334</v>
       </c>
       <c r="B335" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5754,7 +5763,7 @@
         <v>335</v>
       </c>
       <c r="B336" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5762,7 +5771,7 @@
         <v>336</v>
       </c>
       <c r="B337" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5770,7 +5779,7 @@
         <v>337</v>
       </c>
       <c r="B338" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5778,7 +5787,7 @@
         <v>338</v>
       </c>
       <c r="B339" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5786,7 +5795,7 @@
         <v>339</v>
       </c>
       <c r="B340" s="1">
-        <v>1000</v>
+        <v>880</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5794,7 +5803,7 @@
         <v>340</v>
       </c>
       <c r="B341" s="1">
-        <v>520</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5802,7 +5811,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5810,7 +5819,7 @@
         <v>342</v>
       </c>
       <c r="B343" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5818,7 +5827,7 @@
         <v>343</v>
       </c>
       <c r="B344" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5826,7 +5835,7 @@
         <v>344</v>
       </c>
       <c r="B345" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5834,7 +5843,7 @@
         <v>345</v>
       </c>
       <c r="B346" s="1">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5842,7 +5851,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5850,7 +5859,7 @@
         <v>347</v>
       </c>
       <c r="B348" s="1">
-        <v>320</v>
+        <v>520</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5858,7 +5867,7 @@
         <v>348</v>
       </c>
       <c r="B349" s="1">
-        <v>540</v>
+        <v>320</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5866,7 +5875,7 @@
         <v>349</v>
       </c>
       <c r="B350" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5874,7 +5883,7 @@
         <v>350</v>
       </c>
       <c r="B351" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5890,7 +5899,7 @@
         <v>352</v>
       </c>
       <c r="B353" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5898,7 +5907,7 @@
         <v>353</v>
       </c>
       <c r="B354" s="1">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5906,7 +5915,7 @@
         <v>354</v>
       </c>
       <c r="B355" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5914,7 +5923,7 @@
         <v>355</v>
       </c>
       <c r="B356" s="1">
-        <v>480</v>
+        <v>800</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5922,7 +5931,7 @@
         <v>356</v>
       </c>
       <c r="B357" s="1">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5930,7 +5939,7 @@
         <v>357</v>
       </c>
       <c r="B358" s="1">
-        <v>520</v>
+        <v>800</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5938,7 +5947,7 @@
         <v>358</v>
       </c>
       <c r="B359" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5946,7 +5955,7 @@
         <v>359</v>
       </c>
       <c r="B360" s="1">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5954,7 +5963,7 @@
         <v>360</v>
       </c>
       <c r="B361" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5970,7 +5979,7 @@
         <v>362</v>
       </c>
       <c r="B363" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5986,7 +5995,7 @@
         <v>364</v>
       </c>
       <c r="B365" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5994,7 +6003,7 @@
         <v>365</v>
       </c>
       <c r="B366" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -6002,7 +6011,7 @@
         <v>366</v>
       </c>
       <c r="B367" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -6010,7 +6019,7 @@
         <v>367</v>
       </c>
       <c r="B368" s="1">
-        <v>880</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -6018,7 +6027,7 @@
         <v>368</v>
       </c>
       <c r="B369" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -6026,7 +6035,7 @@
         <v>369</v>
       </c>
       <c r="B370" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -6034,7 +6043,7 @@
         <v>370</v>
       </c>
       <c r="B371" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -6042,7 +6051,7 @@
         <v>371</v>
       </c>
       <c r="B372" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -6050,7 +6059,7 @@
         <v>372</v>
       </c>
       <c r="B373" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -6058,7 +6067,7 @@
         <v>373</v>
       </c>
       <c r="B374" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -6066,7 +6075,7 @@
         <v>374</v>
       </c>
       <c r="B375" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -6074,7 +6083,7 @@
         <v>375</v>
       </c>
       <c r="B376" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -6090,7 +6099,7 @@
         <v>377</v>
       </c>
       <c r="B378" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -6106,7 +6115,7 @@
         <v>379</v>
       </c>
       <c r="B380" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -6114,7 +6123,7 @@
         <v>380</v>
       </c>
       <c r="B381" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -6122,7 +6131,7 @@
         <v>381</v>
       </c>
       <c r="B382" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -6130,7 +6139,7 @@
         <v>382</v>
       </c>
       <c r="B383" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -6138,7 +6147,7 @@
         <v>383</v>
       </c>
       <c r="B384" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -6146,7 +6155,7 @@
         <v>384</v>
       </c>
       <c r="B385" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -6154,7 +6163,7 @@
         <v>385</v>
       </c>
       <c r="B386" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -6162,7 +6171,7 @@
         <v>386</v>
       </c>
       <c r="B387" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -6170,7 +6179,7 @@
         <v>387</v>
       </c>
       <c r="B388" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -6178,7 +6187,7 @@
         <v>388</v>
       </c>
       <c r="B389" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -6186,7 +6195,7 @@
         <v>389</v>
       </c>
       <c r="B390" s="1">
-        <v>640</v>
+        <v>480</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -6194,7 +6203,7 @@
         <v>390</v>
       </c>
       <c r="B391" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -6202,7 +6211,7 @@
         <v>391</v>
       </c>
       <c r="B392" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -6210,7 +6219,7 @@
         <v>392</v>
       </c>
       <c r="B393" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -6218,7 +6227,7 @@
         <v>393</v>
       </c>
       <c r="B394" s="1">
-        <v>520</v>
+        <v>860</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -6226,7 +6235,7 @@
         <v>394</v>
       </c>
       <c r="B395" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -6234,7 +6243,7 @@
         <v>395</v>
       </c>
       <c r="B396" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -6250,7 +6259,7 @@
         <v>397</v>
       </c>
       <c r="B398" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -6258,7 +6267,7 @@
         <v>398</v>
       </c>
       <c r="B399" s="1">
-        <v>700</v>
+        <v>420</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -6266,7 +6275,7 @@
         <v>399</v>
       </c>
       <c r="B400" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -6274,7 +6283,7 @@
         <v>400</v>
       </c>
       <c r="B401" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -6282,7 +6291,7 @@
         <v>401</v>
       </c>
       <c r="B402" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -6290,7 +6299,7 @@
         <v>402</v>
       </c>
       <c r="B403" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -6298,7 +6307,7 @@
         <v>403</v>
       </c>
       <c r="B404" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -6306,7 +6315,7 @@
         <v>404</v>
       </c>
       <c r="B405" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -6314,7 +6323,7 @@
         <v>405</v>
       </c>
       <c r="B406" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -6322,7 +6331,7 @@
         <v>406</v>
       </c>
       <c r="B407" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -6330,7 +6339,7 @@
         <v>407</v>
       </c>
       <c r="B408" s="1">
-        <v>440</v>
+        <v>620</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -6338,7 +6347,7 @@
         <v>408</v>
       </c>
       <c r="B409" s="1">
-        <v>1100</v>
+        <v>440</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -6354,7 +6363,7 @@
         <v>410</v>
       </c>
       <c r="B411" s="1">
-        <v>320</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -6362,7 +6371,7 @@
         <v>411</v>
       </c>
       <c r="B412" s="1">
-        <v>940</v>
+        <v>320</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -6370,7 +6379,7 @@
         <v>412</v>
       </c>
       <c r="B413" s="1">
-        <v>320</v>
+        <v>940</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -6378,7 +6387,7 @@
         <v>413</v>
       </c>
       <c r="B414" s="1">
-        <v>960</v>
+        <v>320</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -6386,7 +6395,7 @@
         <v>414</v>
       </c>
       <c r="B415" s="1">
-        <v>820</v>
+        <v>960</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -6394,7 +6403,7 @@
         <v>415</v>
       </c>
       <c r="B416" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -6402,7 +6411,7 @@
         <v>416</v>
       </c>
       <c r="B417" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -6418,7 +6427,7 @@
         <v>418</v>
       </c>
       <c r="B419" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -6426,7 +6435,7 @@
         <v>419</v>
       </c>
       <c r="B420" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -6442,7 +6451,7 @@
         <v>421</v>
       </c>
       <c r="B422" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -6450,7 +6459,7 @@
         <v>422</v>
       </c>
       <c r="B423" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -6458,7 +6467,7 @@
         <v>423</v>
       </c>
       <c r="B424" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -6466,7 +6475,7 @@
         <v>424</v>
       </c>
       <c r="B425" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -6474,7 +6483,7 @@
         <v>425</v>
       </c>
       <c r="B426" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -6482,7 +6491,7 @@
         <v>426</v>
       </c>
       <c r="B427" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -6490,7 +6499,7 @@
         <v>427</v>
       </c>
       <c r="B428" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6506,7 +6515,7 @@
         <v>429</v>
       </c>
       <c r="B430" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6514,7 +6523,7 @@
         <v>430</v>
       </c>
       <c r="B431" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6522,7 +6531,7 @@
         <v>431</v>
       </c>
       <c r="B432" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6530,7 +6539,7 @@
         <v>432</v>
       </c>
       <c r="B433" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6538,7 +6547,7 @@
         <v>433</v>
       </c>
       <c r="B434" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6546,7 +6555,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6554,7 +6563,7 @@
         <v>435</v>
       </c>
       <c r="B436" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6562,7 +6571,7 @@
         <v>436</v>
       </c>
       <c r="B437" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6570,7 +6579,7 @@
         <v>437</v>
       </c>
       <c r="B438" s="1">
-        <v>700</v>
+        <v>440</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6578,7 +6587,7 @@
         <v>438</v>
       </c>
       <c r="B439" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6594,7 +6603,7 @@
         <v>440</v>
       </c>
       <c r="B441" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6602,7 +6611,7 @@
         <v>441</v>
       </c>
       <c r="B442" s="1">
-        <v>560</v>
+        <v>800</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6610,7 +6619,7 @@
         <v>442</v>
       </c>
       <c r="B443" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6618,7 +6627,7 @@
         <v>443</v>
       </c>
       <c r="B444" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6626,7 +6635,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6634,7 +6643,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6642,7 +6651,7 @@
         <v>446</v>
       </c>
       <c r="B447" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6650,7 +6659,7 @@
         <v>447</v>
       </c>
       <c r="B448" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6658,7 +6667,7 @@
         <v>448</v>
       </c>
       <c r="B449" s="1">
-        <v>720</v>
+        <v>620</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6666,7 +6675,7 @@
         <v>449</v>
       </c>
       <c r="B450" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6674,7 +6683,7 @@
         <v>450</v>
       </c>
       <c r="B451" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6690,7 +6699,7 @@
         <v>452</v>
       </c>
       <c r="B453" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6698,7 +6707,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6706,7 +6715,7 @@
         <v>454</v>
       </c>
       <c r="B455" s="1">
-        <v>900</v>
+        <v>880</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6714,7 +6723,7 @@
         <v>455</v>
       </c>
       <c r="B456" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6722,7 +6731,7 @@
         <v>456</v>
       </c>
       <c r="B457" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6730,7 +6739,7 @@
         <v>457</v>
       </c>
       <c r="B458" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6738,7 +6747,7 @@
         <v>458</v>
       </c>
       <c r="B459" s="1">
-        <v>800</v>
+        <v>920</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6746,7 +6755,7 @@
         <v>459</v>
       </c>
       <c r="B460" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6754,7 +6763,7 @@
         <v>460</v>
       </c>
       <c r="B461" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6762,7 +6771,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="1">
-        <v>980</v>
+        <v>940</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6770,7 +6779,7 @@
         <v>462</v>
       </c>
       <c r="B463" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6778,7 +6787,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6786,7 +6795,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6794,7 +6803,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6802,7 +6811,7 @@
         <v>466</v>
       </c>
       <c r="B467" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6818,7 +6827,7 @@
         <v>468</v>
       </c>
       <c r="B469" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6826,7 +6835,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6834,7 +6843,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="1">
-        <v>640</v>
+        <v>920</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6842,7 +6851,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6850,7 +6859,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6858,7 +6867,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="1">
-        <v>960</v>
+        <v>820</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6866,7 +6875,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6874,7 +6883,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6882,7 +6891,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6890,7 +6899,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="1">
-        <v>860</v>
+        <v>640</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6898,7 +6907,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6906,7 +6915,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6914,7 +6923,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6922,7 +6931,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6930,7 +6939,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6938,7 +6947,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6946,7 +6955,7 @@
         <v>484</v>
       </c>
       <c r="B485" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6954,7 +6963,7 @@
         <v>485</v>
       </c>
       <c r="B486" s="1">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6962,7 +6971,7 @@
         <v>486</v>
       </c>
       <c r="B487" s="1">
-        <v>620</v>
+        <v>480</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6970,7 +6979,7 @@
         <v>487</v>
       </c>
       <c r="B488" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6978,7 +6987,7 @@
         <v>488</v>
       </c>
       <c r="B489" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6986,7 +6995,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6994,7 +7003,7 @@
         <v>490</v>
       </c>
       <c r="B491" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -7002,7 +7011,7 @@
         <v>491</v>
       </c>
       <c r="B492" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -7010,7 +7019,7 @@
         <v>492</v>
       </c>
       <c r="B493" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -7018,7 +7027,7 @@
         <v>493</v>
       </c>
       <c r="B494" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -7026,7 +7035,7 @@
         <v>494</v>
       </c>
       <c r="B495" s="1">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -7034,7 +7043,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="1">
-        <v>840</v>
+        <v>480</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -7042,7 +7051,7 @@
         <v>496</v>
       </c>
       <c r="B497" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -7050,7 +7059,7 @@
         <v>497</v>
       </c>
       <c r="B498" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -7058,7 +7067,7 @@
         <v>498</v>
       </c>
       <c r="B499" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -7074,7 +7083,7 @@
         <v>500</v>
       </c>
       <c r="B501" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -7082,7 +7091,7 @@
         <v>501</v>
       </c>
       <c r="B502" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -7090,7 +7099,7 @@
         <v>502</v>
       </c>
       <c r="B503" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -7098,7 +7107,7 @@
         <v>503</v>
       </c>
       <c r="B504" s="1">
-        <v>880</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -7114,7 +7123,7 @@
         <v>505</v>
       </c>
       <c r="B506" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -7122,7 +7131,7 @@
         <v>506</v>
       </c>
       <c r="B507" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -7130,7 +7139,7 @@
         <v>507</v>
       </c>
       <c r="B508" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -7138,7 +7147,7 @@
         <v>508</v>
       </c>
       <c r="B509" s="1">
-        <v>1100</v>
+        <v>660</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -7146,7 +7155,7 @@
         <v>509</v>
       </c>
       <c r="B510" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -7154,7 +7163,7 @@
         <v>510</v>
       </c>
       <c r="B511" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -7162,7 +7171,7 @@
         <v>511</v>
       </c>
       <c r="B512" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -7170,7 +7179,7 @@
         <v>512</v>
       </c>
       <c r="B513" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -7178,7 +7187,7 @@
         <v>513</v>
       </c>
       <c r="B514" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -7194,7 +7203,7 @@
         <v>515</v>
       </c>
       <c r="B516" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -7202,7 +7211,7 @@
         <v>516</v>
       </c>
       <c r="B517" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -7210,7 +7219,7 @@
         <v>517</v>
       </c>
       <c r="B518" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -7218,7 +7227,7 @@
         <v>518</v>
       </c>
       <c r="B519" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -7226,7 +7235,7 @@
         <v>519</v>
       </c>
       <c r="B520" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -7234,7 +7243,7 @@
         <v>520</v>
       </c>
       <c r="B521" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -7250,7 +7259,7 @@
         <v>522</v>
       </c>
       <c r="B523" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -7258,7 +7267,7 @@
         <v>523</v>
       </c>
       <c r="B524" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -7266,7 +7275,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -7274,7 +7283,7 @@
         <v>525</v>
       </c>
       <c r="B526" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -7282,7 +7291,7 @@
         <v>526</v>
       </c>
       <c r="B527" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -7290,7 +7299,7 @@
         <v>527</v>
       </c>
       <c r="B528" s="1">
-        <v>840</v>
+        <v>620</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -7298,7 +7307,7 @@
         <v>528</v>
       </c>
       <c r="B529" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -7306,7 +7315,7 @@
         <v>529</v>
       </c>
       <c r="B530" s="1">
-        <v>1060</v>
+        <v>880</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -7314,7 +7323,7 @@
         <v>530</v>
       </c>
       <c r="B531" s="1">
-        <v>860</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -7330,7 +7339,7 @@
         <v>532</v>
       </c>
       <c r="B533" s="1">
-        <v>800</v>
+        <v>860</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -7338,7 +7347,7 @@
         <v>533</v>
       </c>
       <c r="B534" s="1">
-        <v>860</v>
+        <v>800</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -7346,7 +7355,7 @@
         <v>534</v>
       </c>
       <c r="B535" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -7354,7 +7363,7 @@
         <v>535</v>
       </c>
       <c r="B536" s="1">
-        <v>760</v>
+        <v>960</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -7362,7 +7371,7 @@
         <v>536</v>
       </c>
       <c r="B537" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -7370,7 +7379,7 @@
         <v>537</v>
       </c>
       <c r="B538" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -7378,7 +7387,7 @@
         <v>538</v>
       </c>
       <c r="B539" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -7394,7 +7403,7 @@
         <v>540</v>
       </c>
       <c r="B541" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -7402,7 +7411,7 @@
         <v>541</v>
       </c>
       <c r="B542" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -7410,7 +7419,7 @@
         <v>542</v>
       </c>
       <c r="B543" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -7426,7 +7435,7 @@
         <v>544</v>
       </c>
       <c r="B545" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -7434,7 +7443,7 @@
         <v>545</v>
       </c>
       <c r="B546" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -7442,7 +7451,7 @@
         <v>546</v>
       </c>
       <c r="B547" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -7450,7 +7459,7 @@
         <v>547</v>
       </c>
       <c r="B548" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -7458,7 +7467,7 @@
         <v>548</v>
       </c>
       <c r="B549" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -7466,7 +7475,7 @@
         <v>549</v>
       </c>
       <c r="B550" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -7474,7 +7483,7 @@
         <v>550</v>
       </c>
       <c r="B551" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -7482,7 +7491,7 @@
         <v>551</v>
       </c>
       <c r="B552" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7490,7 +7499,7 @@
         <v>552</v>
       </c>
       <c r="B553" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7506,7 +7515,7 @@
         <v>554</v>
       </c>
       <c r="B555" s="1">
-        <v>880</v>
+        <v>700</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7514,7 +7523,7 @@
         <v>555</v>
       </c>
       <c r="B556" s="1">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7522,7 +7531,7 @@
         <v>556</v>
       </c>
       <c r="B557" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7530,7 +7539,7 @@
         <v>557</v>
       </c>
       <c r="B558" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7538,7 +7547,7 @@
         <v>558</v>
       </c>
       <c r="B559" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7546,7 +7555,7 @@
         <v>559</v>
       </c>
       <c r="B560" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7554,7 +7563,7 @@
         <v>560</v>
       </c>
       <c r="B561" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7562,7 +7571,7 @@
         <v>561</v>
       </c>
       <c r="B562" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7570,7 +7579,7 @@
         <v>562</v>
       </c>
       <c r="B563" s="1">
-        <v>640</v>
+        <v>880</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7578,7 +7587,7 @@
         <v>563</v>
       </c>
       <c r="B564" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7586,7 +7595,7 @@
         <v>564</v>
       </c>
       <c r="B565" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7594,7 +7603,7 @@
         <v>565</v>
       </c>
       <c r="B566" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7610,7 +7619,7 @@
         <v>567</v>
       </c>
       <c r="B568" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7618,7 +7627,7 @@
         <v>568</v>
       </c>
       <c r="B569" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7634,7 +7643,7 @@
         <v>570</v>
       </c>
       <c r="B571" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7642,7 +7651,7 @@
         <v>571</v>
       </c>
       <c r="B572" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7650,7 +7659,7 @@
         <v>572</v>
       </c>
       <c r="B573" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7658,7 +7667,7 @@
         <v>573</v>
       </c>
       <c r="B574" s="1">
-        <v>940</v>
+        <v>960</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7666,7 +7675,7 @@
         <v>574</v>
       </c>
       <c r="B575" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7682,7 +7691,7 @@
         <v>576</v>
       </c>
       <c r="B577" s="1">
-        <v>940</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7690,7 +7699,7 @@
         <v>577</v>
       </c>
       <c r="B578" s="1">
-        <v>860</v>
+        <v>940</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7698,7 +7707,7 @@
         <v>578</v>
       </c>
       <c r="B579" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7706,7 +7715,7 @@
         <v>579</v>
       </c>
       <c r="B580" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7714,7 +7723,7 @@
         <v>580</v>
       </c>
       <c r="B581" s="1">
-        <v>960</v>
+        <v>920</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7722,7 +7731,7 @@
         <v>581</v>
       </c>
       <c r="B582" s="1">
-        <v>680</v>
+        <v>960</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7730,7 +7739,7 @@
         <v>582</v>
       </c>
       <c r="B583" s="1">
-        <v>840</v>
+        <v>680</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7738,7 +7747,7 @@
         <v>583</v>
       </c>
       <c r="B584" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7746,7 +7755,7 @@
         <v>584</v>
       </c>
       <c r="B585" s="1">
-        <v>580</v>
+        <v>780</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7754,7 +7763,7 @@
         <v>585</v>
       </c>
       <c r="B586" s="1">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7762,7 +7771,7 @@
         <v>586</v>
       </c>
       <c r="B587" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7770,7 +7779,7 @@
         <v>587</v>
       </c>
       <c r="B588" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7778,7 +7787,7 @@
         <v>588</v>
       </c>
       <c r="B589" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7786,7 +7795,7 @@
         <v>589</v>
       </c>
       <c r="B590" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7794,7 +7803,7 @@
         <v>590</v>
       </c>
       <c r="B591" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7802,7 +7811,7 @@
         <v>591</v>
       </c>
       <c r="B592" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7810,7 +7819,7 @@
         <v>592</v>
       </c>
       <c r="B593" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7818,7 +7827,7 @@
         <v>593</v>
       </c>
       <c r="B594" s="1">
-        <v>600</v>
+        <v>960</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7826,7 +7835,7 @@
         <v>594</v>
       </c>
       <c r="B595" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7834,7 +7843,7 @@
         <v>595</v>
       </c>
       <c r="B596" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7842,7 +7851,7 @@
         <v>596</v>
       </c>
       <c r="B597" s="1">
-        <v>540</v>
+        <v>720</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7850,7 +7859,7 @@
         <v>597</v>
       </c>
       <c r="B598" s="1">
-        <v>1100</v>
+        <v>780</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7858,7 +7867,7 @@
         <v>598</v>
       </c>
       <c r="B599" s="1">
-        <v>1060</v>
+        <v>540</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7874,7 +7883,7 @@
         <v>600</v>
       </c>
       <c r="B601" s="1">
-        <v>1100</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7882,7 +7891,7 @@
         <v>601</v>
       </c>
       <c r="B602" s="1">
-        <v>1080</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7890,7 +7899,7 @@
         <v>602</v>
       </c>
       <c r="B603" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7898,7 +7907,7 @@
         <v>603</v>
       </c>
       <c r="B604" s="1">
-        <v>840</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7906,7 +7915,7 @@
         <v>604</v>
       </c>
       <c r="B605" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7914,7 +7923,7 @@
         <v>605</v>
       </c>
       <c r="B606" s="1">
-        <v>560</v>
+        <v>840</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7922,7 +7931,7 @@
         <v>606</v>
       </c>
       <c r="B607" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7930,7 +7939,7 @@
         <v>607</v>
       </c>
       <c r="B608" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7938,7 +7947,7 @@
         <v>608</v>
       </c>
       <c r="B609" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7946,7 +7955,7 @@
         <v>609</v>
       </c>
       <c r="B610" s="1">
-        <v>980</v>
+        <v>620</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7954,7 +7963,7 @@
         <v>610</v>
       </c>
       <c r="B611" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7962,7 +7971,7 @@
         <v>611</v>
       </c>
       <c r="B612" s="1">
-        <v>760</v>
+        <v>980</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7970,7 +7979,7 @@
         <v>612</v>
       </c>
       <c r="B613" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7978,7 +7987,7 @@
         <v>613</v>
       </c>
       <c r="B614" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -7994,7 +8003,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -8002,7 +8011,7 @@
         <v>616</v>
       </c>
       <c r="B617" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -8018,7 +8027,7 @@
         <v>618</v>
       </c>
       <c r="B619" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -8026,7 +8035,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -8034,7 +8043,7 @@
         <v>620</v>
       </c>
       <c r="B621" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -8050,7 +8059,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -8058,7 +8067,7 @@
         <v>623</v>
       </c>
       <c r="B624" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -8066,7 +8075,7 @@
         <v>624</v>
       </c>
       <c r="B625" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -8074,7 +8083,7 @@
         <v>625</v>
       </c>
       <c r="B626" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -8090,7 +8099,7 @@
         <v>627</v>
       </c>
       <c r="B628" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -8098,7 +8107,7 @@
         <v>628</v>
       </c>
       <c r="B629" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -8114,7 +8123,7 @@
         <v>630</v>
       </c>
       <c r="B631" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -8122,7 +8131,7 @@
         <v>631</v>
       </c>
       <c r="B632" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -8130,7 +8139,7 @@
         <v>632</v>
       </c>
       <c r="B633" s="1">
-        <v>820</v>
+        <v>860</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -8138,7 +8147,7 @@
         <v>633</v>
       </c>
       <c r="B634" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -8146,7 +8155,7 @@
         <v>634</v>
       </c>
       <c r="B635" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -8154,7 +8163,7 @@
         <v>635</v>
       </c>
       <c r="B636" s="1">
-        <v>1400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -8170,7 +8179,7 @@
         <v>637</v>
       </c>
       <c r="B638" s="1">
-        <v>660</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -8178,7 +8187,7 @@
         <v>638</v>
       </c>
       <c r="B639" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -8186,7 +8195,7 @@
         <v>639</v>
       </c>
       <c r="B640" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -8194,7 +8203,7 @@
         <v>640</v>
       </c>
       <c r="B641" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -8202,7 +8211,7 @@
         <v>641</v>
       </c>
       <c r="B642" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -8210,7 +8219,7 @@
         <v>642</v>
       </c>
       <c r="B643" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -8218,7 +8227,7 @@
         <v>643</v>
       </c>
       <c r="B644" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -8226,7 +8235,7 @@
         <v>644</v>
       </c>
       <c r="B645" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -8234,7 +8243,7 @@
         <v>645</v>
       </c>
       <c r="B646" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -8242,7 +8251,7 @@
         <v>646</v>
       </c>
       <c r="B647" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -8250,7 +8259,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -8258,7 +8267,7 @@
         <v>648</v>
       </c>
       <c r="B649" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -8266,7 +8275,7 @@
         <v>649</v>
       </c>
       <c r="B650" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -8274,7 +8283,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -8282,7 +8291,7 @@
         <v>651</v>
       </c>
       <c r="B652" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -8298,7 +8307,7 @@
         <v>653</v>
       </c>
       <c r="B654" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -8306,7 +8315,7 @@
         <v>654</v>
       </c>
       <c r="B655" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -8314,7 +8323,7 @@
         <v>655</v>
       </c>
       <c r="B656" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -8322,7 +8331,7 @@
         <v>656</v>
       </c>
       <c r="B657" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -8330,7 +8339,7 @@
         <v>657</v>
       </c>
       <c r="B658" s="1">
-        <v>4000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -8338,7 +8347,7 @@
         <v>658</v>
       </c>
       <c r="B659" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -8346,7 +8355,7 @@
         <v>659</v>
       </c>
       <c r="B660" s="1">
-        <v>720</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -8354,7 +8363,7 @@
         <v>660</v>
       </c>
       <c r="B661" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -8362,7 +8371,7 @@
         <v>661</v>
       </c>
       <c r="B662" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -8370,7 +8379,7 @@
         <v>662</v>
       </c>
       <c r="B663" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -8378,7 +8387,7 @@
         <v>663</v>
       </c>
       <c r="B664" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -8386,7 +8395,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -8394,7 +8403,7 @@
         <v>665</v>
       </c>
       <c r="B666" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -8402,7 +8411,7 @@
         <v>666</v>
       </c>
       <c r="B667" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -8410,7 +8419,7 @@
         <v>667</v>
       </c>
       <c r="B668" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -8418,7 +8427,7 @@
         <v>668</v>
       </c>
       <c r="B669" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -8426,7 +8435,7 @@
         <v>669</v>
       </c>
       <c r="B670" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -8434,7 +8443,7 @@
         <v>670</v>
       </c>
       <c r="B671" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -8450,7 +8459,7 @@
         <v>672</v>
       </c>
       <c r="B673" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -8466,7 +8475,7 @@
         <v>674</v>
       </c>
       <c r="B675" s="1">
-        <v>980</v>
+        <v>900</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8474,7 +8483,7 @@
         <v>675</v>
       </c>
       <c r="B676" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -8482,7 +8491,7 @@
         <v>676</v>
       </c>
       <c r="B677" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8490,7 +8499,7 @@
         <v>677</v>
       </c>
       <c r="B678" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8498,7 +8507,7 @@
         <v>678</v>
       </c>
       <c r="B679" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8506,7 +8515,7 @@
         <v>679</v>
       </c>
       <c r="B680" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8514,7 +8523,7 @@
         <v>680</v>
       </c>
       <c r="B681" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8522,7 +8531,7 @@
         <v>681</v>
       </c>
       <c r="B682" s="1">
-        <v>860</v>
+        <v>680</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8538,7 +8547,7 @@
         <v>683</v>
       </c>
       <c r="B684" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8554,7 +8563,7 @@
         <v>685</v>
       </c>
       <c r="B686" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8562,7 +8571,7 @@
         <v>686</v>
       </c>
       <c r="B687" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8570,7 +8579,7 @@
         <v>687</v>
       </c>
       <c r="B688" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8578,7 +8587,7 @@
         <v>688</v>
       </c>
       <c r="B689" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8586,7 +8595,7 @@
         <v>689</v>
       </c>
       <c r="B690" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8594,7 +8603,7 @@
         <v>690</v>
       </c>
       <c r="B691" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8602,7 +8611,7 @@
         <v>691</v>
       </c>
       <c r="B692" s="1">
-        <v>840</v>
+        <v>800</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8610,7 +8619,7 @@
         <v>692</v>
       </c>
       <c r="B693" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8618,7 +8627,7 @@
         <v>693</v>
       </c>
       <c r="B694" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8626,7 +8635,7 @@
         <v>694</v>
       </c>
       <c r="B695" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8634,7 +8643,7 @@
         <v>695</v>
       </c>
       <c r="B696" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8650,7 +8659,7 @@
         <v>697</v>
       </c>
       <c r="B698" s="1">
-        <v>880</v>
+        <v>640</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8658,7 +8667,7 @@
         <v>698</v>
       </c>
       <c r="B699" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8666,7 +8675,7 @@
         <v>699</v>
       </c>
       <c r="B700" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8674,7 +8683,7 @@
         <v>700</v>
       </c>
       <c r="B701" s="1">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8682,7 +8691,7 @@
         <v>701</v>
       </c>
       <c r="B702" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8698,7 +8707,7 @@
         <v>703</v>
       </c>
       <c r="B704" s="1">
-        <v>800</v>
+        <v>820</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8706,7 +8715,7 @@
         <v>704</v>
       </c>
       <c r="B705" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8722,7 +8731,7 @@
         <v>706</v>
       </c>
       <c r="B707" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8730,7 +8739,7 @@
         <v>707</v>
       </c>
       <c r="B708" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8738,7 +8747,7 @@
         <v>708</v>
       </c>
       <c r="B709" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8746,7 +8755,7 @@
         <v>709</v>
       </c>
       <c r="B710" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8754,7 +8763,7 @@
         <v>710</v>
       </c>
       <c r="B711" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8762,7 +8771,7 @@
         <v>711</v>
       </c>
       <c r="B712" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8770,7 +8779,7 @@
         <v>712</v>
       </c>
       <c r="B713" s="1">
-        <v>880</v>
+        <v>960</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8778,7 +8787,7 @@
         <v>713</v>
       </c>
       <c r="B714" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8786,7 +8795,7 @@
         <v>714</v>
       </c>
       <c r="B715" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8794,7 +8803,7 @@
         <v>715</v>
       </c>
       <c r="B716" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8802,7 +8811,7 @@
         <v>716</v>
       </c>
       <c r="B717" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8810,7 +8819,7 @@
         <v>717</v>
       </c>
       <c r="B718" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8818,7 +8827,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="1">
-        <v>1020</v>
+        <v>640</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8834,7 +8843,7 @@
         <v>720</v>
       </c>
       <c r="B721" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8842,7 +8851,7 @@
         <v>721</v>
       </c>
       <c r="B722" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8850,7 +8859,7 @@
         <v>722</v>
       </c>
       <c r="B723" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8858,7 +8867,7 @@
         <v>723</v>
       </c>
       <c r="B724" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8866,7 +8875,7 @@
         <v>724</v>
       </c>
       <c r="B725" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8874,7 +8883,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8882,7 +8891,7 @@
         <v>726</v>
       </c>
       <c r="B727" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8898,7 +8907,7 @@
         <v>728</v>
       </c>
       <c r="B729" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8906,7 +8915,7 @@
         <v>729</v>
       </c>
       <c r="B730" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8914,7 +8923,7 @@
         <v>730</v>
       </c>
       <c r="B731" s="1">
-        <v>680</v>
+        <v>820</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8922,7 +8931,7 @@
         <v>731</v>
       </c>
       <c r="B732" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -8930,7 +8939,7 @@
         <v>732</v>
       </c>
       <c r="B733" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -8938,7 +8947,7 @@
         <v>733</v>
       </c>
       <c r="B734" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -8946,7 +8955,7 @@
         <v>734</v>
       </c>
       <c r="B735" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -8954,7 +8963,7 @@
         <v>735</v>
       </c>
       <c r="B736" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -8970,7 +8979,7 @@
         <v>737</v>
       </c>
       <c r="B738" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="739" spans="1:2">
@@ -8978,7 +8987,7 @@
         <v>738</v>
       </c>
       <c r="B739" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="740" spans="1:2">
@@ -8986,7 +8995,7 @@
         <v>739</v>
       </c>
       <c r="B740" s="1">
-        <v>1100</v>
+        <v>840</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -8994,7 +9003,7 @@
         <v>740</v>
       </c>
       <c r="B741" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="742" spans="1:2">
@@ -9002,7 +9011,7 @@
         <v>741</v>
       </c>
       <c r="B742" s="1">
-        <v>940</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -9010,7 +9019,7 @@
         <v>742</v>
       </c>
       <c r="B743" s="1">
-        <v>820</v>
+        <v>940</v>
       </c>
     </row>
     <row r="744" spans="1:2">
@@ -9018,7 +9027,7 @@
         <v>743</v>
       </c>
       <c r="B744" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="745" spans="1:2">
@@ -9026,7 +9035,7 @@
         <v>744</v>
       </c>
       <c r="B745" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -9034,7 +9043,7 @@
         <v>745</v>
       </c>
       <c r="B746" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="747" spans="1:2">
@@ -9042,7 +9051,7 @@
         <v>746</v>
       </c>
       <c r="B747" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="748" spans="1:2">
@@ -9050,7 +9059,7 @@
         <v>747</v>
       </c>
       <c r="B748" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="749" spans="1:2">
@@ -9058,7 +9067,7 @@
         <v>748</v>
       </c>
       <c r="B749" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -9066,7 +9075,7 @@
         <v>749</v>
       </c>
       <c r="B750" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="751" spans="1:2">
@@ -9082,7 +9091,7 @@
         <v>751</v>
       </c>
       <c r="B752" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="753" spans="1:2">
@@ -9090,7 +9099,7 @@
         <v>752</v>
       </c>
       <c r="B753" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="754" spans="1:2">
@@ -9098,7 +9107,7 @@
         <v>753</v>
       </c>
       <c r="B754" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -9106,7 +9115,7 @@
         <v>754</v>
       </c>
       <c r="B755" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="756" spans="1:2">
@@ -9114,7 +9123,7 @@
         <v>755</v>
       </c>
       <c r="B756" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="757" spans="1:2">
@@ -9122,7 +9131,7 @@
         <v>756</v>
       </c>
       <c r="B757" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="758" spans="1:2">
@@ -9138,7 +9147,7 @@
         <v>758</v>
       </c>
       <c r="B759" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="760" spans="1:2">
@@ -9146,7 +9155,7 @@
         <v>759</v>
       </c>
       <c r="B760" s="1">
-        <v>440</v>
+        <v>900</v>
       </c>
     </row>
     <row r="761" spans="1:2">
@@ -9154,7 +9163,7 @@
         <v>760</v>
       </c>
       <c r="B761" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="762" spans="1:2">
@@ -9162,7 +9171,7 @@
         <v>761</v>
       </c>
       <c r="B762" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="763" spans="1:2">
@@ -9170,7 +9179,7 @@
         <v>762</v>
       </c>
       <c r="B763" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="764" spans="1:2">
@@ -9178,7 +9187,7 @@
         <v>763</v>
       </c>
       <c r="B764" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="765" spans="1:2">
@@ -9186,7 +9195,7 @@
         <v>764</v>
       </c>
       <c r="B765" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="766" spans="1:2">
@@ -9194,7 +9203,7 @@
         <v>765</v>
       </c>
       <c r="B766" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="767" spans="1:2">
@@ -9202,7 +9211,7 @@
         <v>766</v>
       </c>
       <c r="B767" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="768" spans="1:2">
@@ -9210,7 +9219,7 @@
         <v>767</v>
       </c>
       <c r="B768" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="769" spans="1:2">
@@ -9218,7 +9227,7 @@
         <v>768</v>
       </c>
       <c r="B769" s="1">
-        <v>880</v>
+        <v>560</v>
       </c>
     </row>
     <row r="770" spans="1:2">
@@ -9226,7 +9235,7 @@
         <v>769</v>
       </c>
       <c r="B770" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="771" spans="1:2">
@@ -9242,7 +9251,7 @@
         <v>771</v>
       </c>
       <c r="B772" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="773" spans="1:2">
@@ -9250,7 +9259,7 @@
         <v>772</v>
       </c>
       <c r="B773" s="1">
-        <v>920</v>
+        <v>880</v>
       </c>
     </row>
     <row r="774" spans="1:2">
@@ -9258,7 +9267,7 @@
         <v>773</v>
       </c>
       <c r="B774" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="775" spans="1:2">
@@ -9266,7 +9275,7 @@
         <v>774</v>
       </c>
       <c r="B775" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="776" spans="1:2">
@@ -9274,7 +9283,7 @@
         <v>775</v>
       </c>
       <c r="B776" s="1">
-        <v>980</v>
+        <v>800</v>
       </c>
     </row>
     <row r="777" spans="1:2">
@@ -9282,7 +9291,7 @@
         <v>776</v>
       </c>
       <c r="B777" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="778" spans="1:2">
@@ -9290,7 +9299,7 @@
         <v>777</v>
       </c>
       <c r="B778" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="779" spans="1:2">
@@ -9298,7 +9307,7 @@
         <v>778</v>
       </c>
       <c r="B779" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="780" spans="1:2">
@@ -9306,7 +9315,7 @@
         <v>779</v>
       </c>
       <c r="B780" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="781" spans="1:2">
@@ -9314,7 +9323,7 @@
         <v>780</v>
       </c>
       <c r="B781" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="782" spans="1:2">
@@ -9322,7 +9331,7 @@
         <v>781</v>
       </c>
       <c r="B782" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="783" spans="1:2">
@@ -9330,7 +9339,7 @@
         <v>782</v>
       </c>
       <c r="B783" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="784" spans="1:2">
@@ -9338,7 +9347,7 @@
         <v>783</v>
       </c>
       <c r="B784" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="785" spans="1:2">
@@ -9346,7 +9355,7 @@
         <v>784</v>
       </c>
       <c r="B785" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="786" spans="1:2">
@@ -9354,7 +9363,7 @@
         <v>785</v>
       </c>
       <c r="B786" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="787" spans="1:2">
@@ -9362,7 +9371,7 @@
         <v>786</v>
       </c>
       <c r="B787" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="788" spans="1:2">
@@ -9370,7 +9379,7 @@
         <v>787</v>
       </c>
       <c r="B788" s="1">
-        <v>660</v>
+        <v>860</v>
       </c>
     </row>
     <row r="789" spans="1:2">
@@ -9378,7 +9387,7 @@
         <v>788</v>
       </c>
       <c r="B789" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="790" spans="1:2">
@@ -9386,7 +9395,7 @@
         <v>789</v>
       </c>
       <c r="B790" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="791" spans="1:2">
@@ -9394,7 +9403,7 @@
         <v>790</v>
       </c>
       <c r="B791" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="792" spans="1:2">
@@ -9402,7 +9411,7 @@
         <v>791</v>
       </c>
       <c r="B792" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="793" spans="1:2">
@@ -9410,7 +9419,7 @@
         <v>792</v>
       </c>
       <c r="B793" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="794" spans="1:2">
@@ -9418,7 +9427,7 @@
         <v>793</v>
       </c>
       <c r="B794" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="795" spans="1:2">
@@ -9426,7 +9435,7 @@
         <v>794</v>
       </c>
       <c r="B795" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="796" spans="1:2">
@@ -9434,7 +9443,7 @@
         <v>795</v>
       </c>
       <c r="B796" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="797" spans="1:2">
@@ -9442,7 +9451,7 @@
         <v>796</v>
       </c>
       <c r="B797" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="798" spans="1:2">
@@ -9450,7 +9459,7 @@
         <v>797</v>
       </c>
       <c r="B798" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="799" spans="1:2">
@@ -9458,7 +9467,7 @@
         <v>798</v>
       </c>
       <c r="B799" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="800" spans="1:2">
@@ -9466,7 +9475,7 @@
         <v>799</v>
       </c>
       <c r="B800" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="801" spans="1:2">
@@ -9474,7 +9483,7 @@
         <v>800</v>
       </c>
       <c r="B801" s="1">
-        <v>800</v>
+        <v>760</v>
       </c>
     </row>
     <row r="802" spans="1:2">
@@ -9482,7 +9491,7 @@
         <v>801</v>
       </c>
       <c r="B802" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="803" spans="1:2">
@@ -9490,7 +9499,7 @@
         <v>802</v>
       </c>
       <c r="B803" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="804" spans="1:2">
@@ -9498,7 +9507,7 @@
         <v>803</v>
       </c>
       <c r="B804" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="805" spans="1:2">
@@ -9506,7 +9515,7 @@
         <v>804</v>
       </c>
       <c r="B805" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="806" spans="1:2">
@@ -9514,7 +9523,7 @@
         <v>805</v>
       </c>
       <c r="B806" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="807" spans="1:2">
@@ -9522,7 +9531,7 @@
         <v>806</v>
       </c>
       <c r="B807" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="808" spans="1:2">
@@ -9530,7 +9539,7 @@
         <v>807</v>
       </c>
       <c r="B808" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="809" spans="1:2">
@@ -9538,7 +9547,7 @@
         <v>808</v>
       </c>
       <c r="B809" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="810" spans="1:2">
@@ -9546,7 +9555,7 @@
         <v>809</v>
       </c>
       <c r="B810" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="811" spans="1:2">
@@ -9554,7 +9563,7 @@
         <v>810</v>
       </c>
       <c r="B811" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="812" spans="1:2">
@@ -9562,7 +9571,7 @@
         <v>811</v>
       </c>
       <c r="B812" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="813" spans="1:2">
@@ -9570,7 +9579,7 @@
         <v>812</v>
       </c>
       <c r="B813" s="1">
-        <v>920</v>
+        <v>600</v>
       </c>
     </row>
     <row r="814" spans="1:2">
@@ -9578,7 +9587,7 @@
         <v>813</v>
       </c>
       <c r="B814" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="815" spans="1:2">
@@ -9586,7 +9595,7 @@
         <v>814</v>
       </c>
       <c r="B815" s="1">
-        <v>1040</v>
+        <v>760</v>
       </c>
     </row>
     <row r="816" spans="1:2">
@@ -9594,7 +9603,7 @@
         <v>815</v>
       </c>
       <c r="B816" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="817" spans="1:2">
@@ -9602,7 +9611,7 @@
         <v>816</v>
       </c>
       <c r="B817" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="818" spans="1:2">
@@ -9610,7 +9619,7 @@
         <v>817</v>
       </c>
       <c r="B818" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="819" spans="1:2">
@@ -9618,7 +9627,7 @@
         <v>818</v>
       </c>
       <c r="B819" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="820" spans="1:2">
@@ -9626,7 +9635,7 @@
         <v>819</v>
       </c>
       <c r="B820" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="821" spans="1:2">
@@ -9634,7 +9643,7 @@
         <v>820</v>
       </c>
       <c r="B821" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="822" spans="1:2">
@@ -9642,7 +9651,7 @@
         <v>821</v>
       </c>
       <c r="B822" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="823" spans="1:2">
@@ -9650,7 +9659,7 @@
         <v>822</v>
       </c>
       <c r="B823" s="1">
-        <v>960</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="824" spans="1:2">
@@ -9658,7 +9667,7 @@
         <v>823</v>
       </c>
       <c r="B824" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="825" spans="1:2">
@@ -9666,7 +9675,7 @@
         <v>824</v>
       </c>
       <c r="B825" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="826" spans="1:2">
@@ -9674,7 +9683,7 @@
         <v>825</v>
       </c>
       <c r="B826" s="1">
-        <v>820</v>
+        <v>960</v>
       </c>
     </row>
     <row r="827" spans="1:2">
@@ -9682,7 +9691,7 @@
         <v>826</v>
       </c>
       <c r="B827" s="1">
-        <v>440</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="828" spans="1:2">
@@ -9690,7 +9699,7 @@
         <v>827</v>
       </c>
       <c r="B828" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="829" spans="1:2">
@@ -9698,7 +9707,7 @@
         <v>828</v>
       </c>
       <c r="B829" s="1">
-        <v>440</v>
+        <v>820</v>
       </c>
     </row>
     <row r="830" spans="1:2">
@@ -9706,7 +9715,7 @@
         <v>829</v>
       </c>
       <c r="B830" s="1">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="831" spans="1:2">
@@ -9722,7 +9731,7 @@
         <v>831</v>
       </c>
       <c r="B832" s="1">
-        <v>820</v>
+        <v>440</v>
       </c>
     </row>
     <row r="833" spans="1:2">
@@ -9730,7 +9739,7 @@
         <v>832</v>
       </c>
       <c r="B833" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="834" spans="1:2">
@@ -9738,7 +9747,7 @@
         <v>833</v>
       </c>
       <c r="B834" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="835" spans="1:2">
@@ -9746,7 +9755,7 @@
         <v>834</v>
       </c>
       <c r="B835" s="1">
-        <v>840</v>
+        <v>820</v>
       </c>
     </row>
     <row r="836" spans="1:2">
@@ -9754,7 +9763,7 @@
         <v>835</v>
       </c>
       <c r="B836" s="1">
-        <v>400</v>
+        <v>820</v>
       </c>
     </row>
     <row r="837" spans="1:2">
@@ -9762,7 +9771,7 @@
         <v>836</v>
       </c>
       <c r="B837" s="1">
-        <v>400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="838" spans="1:2">
@@ -9770,7 +9779,7 @@
         <v>837</v>
       </c>
       <c r="B838" s="1">
-        <v>380</v>
+        <v>840</v>
       </c>
     </row>
     <row r="839" spans="1:2">
@@ -9778,7 +9787,7 @@
         <v>838</v>
       </c>
       <c r="B839" s="1">
-        <v>840</v>
+        <v>400</v>
       </c>
     </row>
     <row r="840" spans="1:2">
@@ -9786,7 +9795,7 @@
         <v>839</v>
       </c>
       <c r="B840" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="841" spans="1:2">
@@ -9802,7 +9811,7 @@
         <v>841</v>
       </c>
       <c r="B842" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="843" spans="1:2">
@@ -9810,7 +9819,7 @@
         <v>842</v>
       </c>
       <c r="B843" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="844" spans="1:2">
@@ -9818,7 +9827,7 @@
         <v>843</v>
       </c>
       <c r="B844" s="1">
-        <v>800</v>
+        <v>380</v>
       </c>
     </row>
     <row r="845" spans="1:2">
@@ -9826,7 +9835,7 @@
         <v>844</v>
       </c>
       <c r="B845" s="1">
-        <v>860</v>
+        <v>520</v>
       </c>
     </row>
     <row r="846" spans="1:2">
@@ -9834,7 +9843,7 @@
         <v>845</v>
       </c>
       <c r="B846" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="847" spans="1:2">
@@ -9842,7 +9851,7 @@
         <v>846</v>
       </c>
       <c r="B847" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="848" spans="1:2">
@@ -9850,7 +9859,7 @@
         <v>847</v>
       </c>
       <c r="B848" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="849" spans="1:2">
@@ -9858,7 +9867,7 @@
         <v>848</v>
       </c>
       <c r="B849" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="850" spans="1:2">
@@ -9866,7 +9875,7 @@
         <v>849</v>
       </c>
       <c r="B850" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="851" spans="1:2">
@@ -9874,7 +9883,7 @@
         <v>850</v>
       </c>
       <c r="B851" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="852" spans="1:2">
@@ -9882,7 +9891,7 @@
         <v>851</v>
       </c>
       <c r="B852" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="853" spans="1:2">
@@ -9890,7 +9899,7 @@
         <v>852</v>
       </c>
       <c r="B853" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="854" spans="1:2">
@@ -9898,7 +9907,7 @@
         <v>853</v>
       </c>
       <c r="B854" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="855" spans="1:2">
@@ -9906,7 +9915,7 @@
         <v>854</v>
       </c>
       <c r="B855" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="856" spans="1:2">
@@ -9914,7 +9923,7 @@
         <v>855</v>
       </c>
       <c r="B856" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="857" spans="1:2">
@@ -9922,7 +9931,7 @@
         <v>856</v>
       </c>
       <c r="B857" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="858" spans="1:2">
@@ -9930,7 +9939,7 @@
         <v>857</v>
       </c>
       <c r="B858" s="1">
-        <v>900</v>
+        <v>500</v>
       </c>
     </row>
     <row r="859" spans="1:2">
@@ -9938,7 +9947,7 @@
         <v>858</v>
       </c>
       <c r="B859" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="860" spans="1:2">
@@ -9946,7 +9955,7 @@
         <v>859</v>
       </c>
       <c r="B860" s="1">
-        <v>920</v>
+        <v>840</v>
       </c>
     </row>
     <row r="861" spans="1:2">
@@ -9954,7 +9963,7 @@
         <v>860</v>
       </c>
       <c r="B861" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="862" spans="1:2">
@@ -9962,7 +9971,7 @@
         <v>861</v>
       </c>
       <c r="B862" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="863" spans="1:2">
@@ -9970,7 +9979,7 @@
         <v>862</v>
       </c>
       <c r="B863" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="864" spans="1:2">
@@ -9978,7 +9987,7 @@
         <v>863</v>
       </c>
       <c r="B864" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="865" spans="1:2">
@@ -9986,7 +9995,7 @@
         <v>864</v>
       </c>
       <c r="B865" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="866" spans="1:2">
@@ -9994,7 +10003,7 @@
         <v>865</v>
       </c>
       <c r="B866" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="867" spans="1:2">
@@ -10002,7 +10011,7 @@
         <v>866</v>
       </c>
       <c r="B867" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="868" spans="1:2">
@@ -10010,7 +10019,7 @@
         <v>867</v>
       </c>
       <c r="B868" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="869" spans="1:2">
@@ -10018,7 +10027,7 @@
         <v>868</v>
       </c>
       <c r="B869" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="870" spans="1:2">
@@ -10026,7 +10035,7 @@
         <v>869</v>
       </c>
       <c r="B870" s="1">
-        <v>960</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="871" spans="1:2">
@@ -10034,7 +10043,7 @@
         <v>870</v>
       </c>
       <c r="B871" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="872" spans="1:2">
@@ -10042,7 +10051,7 @@
         <v>871</v>
       </c>
       <c r="B872" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="873" spans="1:2">
@@ -10050,7 +10059,7 @@
         <v>872</v>
       </c>
       <c r="B873" s="1">
-        <v>820</v>
+        <v>960</v>
       </c>
     </row>
     <row r="874" spans="1:2">
@@ -10058,7 +10067,7 @@
         <v>873</v>
       </c>
       <c r="B874" s="1">
-        <v>440</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="875" spans="1:2">
@@ -10066,7 +10075,7 @@
         <v>874</v>
       </c>
       <c r="B875" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="876" spans="1:2">
@@ -10074,7 +10083,7 @@
         <v>875</v>
       </c>
       <c r="B876" s="1">
-        <v>440</v>
+        <v>820</v>
       </c>
     </row>
     <row r="877" spans="1:2">
@@ -10082,7 +10091,7 @@
         <v>876</v>
       </c>
       <c r="B877" s="1">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="878" spans="1:2">
@@ -10098,7 +10107,7 @@
         <v>878</v>
       </c>
       <c r="B879" s="1">
-        <v>820</v>
+        <v>440</v>
       </c>
     </row>
     <row r="880" spans="1:2">
@@ -10106,7 +10115,7 @@
         <v>879</v>
       </c>
       <c r="B880" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="881" spans="1:2">
@@ -10114,7 +10123,7 @@
         <v>880</v>
       </c>
       <c r="B881" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="882" spans="1:2">
@@ -10122,7 +10131,7 @@
         <v>881</v>
       </c>
       <c r="B882" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="883" spans="1:2">
@@ -10130,7 +10139,7 @@
         <v>882</v>
       </c>
       <c r="B883" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="884" spans="1:2">
@@ -10138,7 +10147,7 @@
         <v>883</v>
       </c>
       <c r="B884" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="885" spans="1:2">
@@ -10146,7 +10155,7 @@
         <v>884</v>
       </c>
       <c r="B885" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="886" spans="1:2">
@@ -10154,7 +10163,7 @@
         <v>885</v>
       </c>
       <c r="B886" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="887" spans="1:2">
@@ -10162,7 +10171,7 @@
         <v>886</v>
       </c>
       <c r="B887" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="888" spans="1:2">
@@ -10170,7 +10179,7 @@
         <v>887</v>
       </c>
       <c r="B888" s="1">
-        <v>440</v>
+        <v>480</v>
       </c>
     </row>
     <row r="889" spans="1:2">
@@ -10178,7 +10187,7 @@
         <v>888</v>
       </c>
       <c r="B889" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="890" spans="1:2">
@@ -10186,7 +10195,7 @@
         <v>889</v>
       </c>
       <c r="B890" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="891" spans="1:2">
@@ -10194,7 +10203,7 @@
         <v>890</v>
       </c>
       <c r="B891" s="1">
-        <v>820</v>
+        <v>440</v>
       </c>
     </row>
     <row r="892" spans="1:2">
@@ -10202,7 +10211,7 @@
         <v>891</v>
       </c>
       <c r="B892" s="1">
-        <v>660</v>
+        <v>380</v>
       </c>
     </row>
     <row r="893" spans="1:2">
@@ -10210,7 +10219,7 @@
         <v>892</v>
       </c>
       <c r="B893" s="1">
-        <v>580</v>
+        <v>600</v>
       </c>
     </row>
     <row r="894" spans="1:2">
@@ -10218,7 +10227,7 @@
         <v>893</v>
       </c>
       <c r="B894" s="1">
-        <v>560</v>
+        <v>820</v>
       </c>
     </row>
     <row r="895" spans="1:2">
@@ -10226,7 +10235,7 @@
         <v>894</v>
       </c>
       <c r="B895" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="896" spans="1:2">
@@ -10234,7 +10243,7 @@
         <v>895</v>
       </c>
       <c r="B896" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="897" spans="1:2">
@@ -10250,6 +10259,30 @@
         <v>897</v>
       </c>
       <c r="B898" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="899" spans="1:2">
+      <c r="A899" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="B899" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="900" spans="1:2">
+      <c r="A900" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="B900" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="901" spans="1:2">
+      <c r="A901" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B901" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="903">
   <si>
     <t>Наименование</t>
   </si>
@@ -617,6 +617,9 @@
     <t>Midnight Project - Кот i  Сабака, РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Midnight Project - КОТОСРЕДА (IPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>MIKKELLER  Peter, Pale and Mary (APA), РОЗЛИВ, Дания</t>
   </si>
   <si>
@@ -1887,6 +1890,9 @@
   </si>
   <si>
     <t>вынос_Midnight Project - Кот i  Сабака, РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Midnight Project - КОТОСРЕДА (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_Mitra and Horror Brewing - Ultra Special Secret Butt Kicking Technique (Cold IPA), РОЗЛИВ, Россия</t>
@@ -3071,7 +3077,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B901"/>
+  <dimension ref="A1:B903"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -4683,7 +4689,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="1">
-        <v>460</v>
+        <v>980</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4691,7 +4697,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4699,7 +4705,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="1">
-        <v>720</v>
+        <v>580</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4707,7 +4713,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4715,7 +4721,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4723,7 +4729,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="1">
-        <v>260</v>
+        <v>780</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4739,7 +4745,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4755,7 +4761,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4763,7 +4769,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4771,7 +4777,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4779,7 +4785,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="1">
-        <v>500</v>
+        <v>760</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4787,7 +4793,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4795,7 +4801,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="1">
-        <v>740</v>
+        <v>400</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4803,7 +4809,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4811,7 +4817,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4819,7 +4825,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4827,7 +4833,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4835,7 +4841,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4843,7 +4849,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4859,7 +4865,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4867,7 +4873,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4875,7 +4881,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4883,7 +4889,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4891,7 +4897,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="1">
-        <v>580</v>
+        <v>860</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4899,7 +4905,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4907,7 +4913,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="1">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4915,7 +4921,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4923,7 +4929,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4931,7 +4937,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4939,7 +4945,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4947,7 +4953,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4955,7 +4961,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4963,7 +4969,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4971,7 +4977,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4979,7 +4985,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4987,7 +4993,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="1">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4995,7 +5001,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="1">
-        <v>480</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -5003,7 +5009,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -5011,7 +5017,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -5019,7 +5025,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -5027,7 +5033,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -5035,7 +5041,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -5043,7 +5049,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -5051,7 +5057,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -5059,7 +5065,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -5067,7 +5073,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="1">
-        <v>900</v>
+        <v>520</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -5075,7 +5081,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -5083,7 +5089,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -5091,7 +5097,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -5099,7 +5105,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -5115,7 +5121,7 @@
         <v>254</v>
       </c>
       <c r="B255" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -5131,7 +5137,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -5139,7 +5145,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -5147,7 +5153,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -5155,7 +5161,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -5163,7 +5169,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -5171,7 +5177,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -5179,7 +5185,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="1">
-        <v>960</v>
+        <v>840</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -5187,7 +5193,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -5203,7 +5209,7 @@
         <v>265</v>
       </c>
       <c r="B266" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -5211,7 +5217,7 @@
         <v>266</v>
       </c>
       <c r="B267" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -5219,7 +5225,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -5227,7 +5233,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -5235,7 +5241,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -5243,7 +5249,7 @@
         <v>270</v>
       </c>
       <c r="B271" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -5259,7 +5265,7 @@
         <v>272</v>
       </c>
       <c r="B273" s="1">
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -5267,7 +5273,7 @@
         <v>273</v>
       </c>
       <c r="B274" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -5275,7 +5281,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="1">
-        <v>758</v>
+        <v>500</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -5283,7 +5289,7 @@
         <v>275</v>
       </c>
       <c r="B276" s="1">
-        <v>2273</v>
+        <v>758</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -5291,7 +5297,7 @@
         <v>276</v>
       </c>
       <c r="B277" s="1">
-        <v>1515</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -5299,7 +5305,7 @@
         <v>277</v>
       </c>
       <c r="B278" s="1">
-        <v>520</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -5307,7 +5313,7 @@
         <v>278</v>
       </c>
       <c r="B279" s="1">
-        <v>4000</v>
+        <v>520</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -5315,7 +5321,7 @@
         <v>279</v>
       </c>
       <c r="B280" s="1">
-        <v>560</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -5323,7 +5329,7 @@
         <v>280</v>
       </c>
       <c r="B281" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -5331,7 +5337,7 @@
         <v>281</v>
       </c>
       <c r="B282" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -5347,7 +5353,7 @@
         <v>283</v>
       </c>
       <c r="B284" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -5355,7 +5361,7 @@
         <v>284</v>
       </c>
       <c r="B285" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -5363,7 +5369,7 @@
         <v>285</v>
       </c>
       <c r="B286" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5371,7 +5377,7 @@
         <v>286</v>
       </c>
       <c r="B287" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5379,7 +5385,7 @@
         <v>287</v>
       </c>
       <c r="B288" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5387,7 +5393,7 @@
         <v>288</v>
       </c>
       <c r="B289" s="1">
-        <v>680</v>
+        <v>520</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5395,7 +5401,7 @@
         <v>289</v>
       </c>
       <c r="B290" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5403,7 +5409,7 @@
         <v>290</v>
       </c>
       <c r="B291" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5411,7 +5417,7 @@
         <v>291</v>
       </c>
       <c r="B292" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5419,7 +5425,7 @@
         <v>292</v>
       </c>
       <c r="B293" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5427,7 +5433,7 @@
         <v>293</v>
       </c>
       <c r="B294" s="1">
-        <v>660</v>
+        <v>380</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5435,7 +5441,7 @@
         <v>294</v>
       </c>
       <c r="B295" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5443,7 +5449,7 @@
         <v>295</v>
       </c>
       <c r="B296" s="1">
-        <v>540</v>
+        <v>900</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5451,7 +5457,7 @@
         <v>296</v>
       </c>
       <c r="B297" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5459,7 +5465,7 @@
         <v>297</v>
       </c>
       <c r="B298" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5467,7 +5473,7 @@
         <v>298</v>
       </c>
       <c r="B299" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5475,7 +5481,7 @@
         <v>299</v>
       </c>
       <c r="B300" s="1">
-        <v>460</v>
+        <v>580</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5483,7 +5489,7 @@
         <v>300</v>
       </c>
       <c r="B301" s="1">
-        <v>520</v>
+        <v>460</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5491,7 +5497,7 @@
         <v>301</v>
       </c>
       <c r="B302" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5499,7 +5505,7 @@
         <v>302</v>
       </c>
       <c r="B303" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5507,7 +5513,7 @@
         <v>303</v>
       </c>
       <c r="B304" s="1">
-        <v>860</v>
+        <v>900</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5515,7 +5521,7 @@
         <v>304</v>
       </c>
       <c r="B305" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5539,7 +5545,7 @@
         <v>307</v>
       </c>
       <c r="B308" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5555,7 +5561,7 @@
         <v>309</v>
       </c>
       <c r="B310" s="1">
-        <v>980</v>
+        <v>560</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5563,7 +5569,7 @@
         <v>310</v>
       </c>
       <c r="B311" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5579,7 +5585,7 @@
         <v>312</v>
       </c>
       <c r="B313" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5587,7 +5593,7 @@
         <v>313</v>
       </c>
       <c r="B314" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5595,7 +5601,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5603,7 +5609,7 @@
         <v>315</v>
       </c>
       <c r="B316" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5611,7 +5617,7 @@
         <v>316</v>
       </c>
       <c r="B317" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5619,7 +5625,7 @@
         <v>317</v>
       </c>
       <c r="B318" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5627,7 +5633,7 @@
         <v>318</v>
       </c>
       <c r="B319" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5635,7 +5641,7 @@
         <v>319</v>
       </c>
       <c r="B320" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5643,7 +5649,7 @@
         <v>320</v>
       </c>
       <c r="B321" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5651,7 +5657,7 @@
         <v>321</v>
       </c>
       <c r="B322" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5659,7 +5665,7 @@
         <v>322</v>
       </c>
       <c r="B323" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5667,7 +5673,7 @@
         <v>323</v>
       </c>
       <c r="B324" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5675,7 +5681,7 @@
         <v>324</v>
       </c>
       <c r="B325" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5683,7 +5689,7 @@
         <v>325</v>
       </c>
       <c r="B326" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5691,7 +5697,7 @@
         <v>326</v>
       </c>
       <c r="B327" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5699,7 +5705,7 @@
         <v>327</v>
       </c>
       <c r="B328" s="1">
-        <v>520</v>
+        <v>680</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5707,7 +5713,7 @@
         <v>328</v>
       </c>
       <c r="B329" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5715,7 +5721,7 @@
         <v>329</v>
       </c>
       <c r="B330" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5723,7 +5729,7 @@
         <v>330</v>
       </c>
       <c r="B331" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5731,7 +5737,7 @@
         <v>331</v>
       </c>
       <c r="B332" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5739,7 +5745,7 @@
         <v>332</v>
       </c>
       <c r="B333" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5747,7 +5753,7 @@
         <v>333</v>
       </c>
       <c r="B334" s="1">
-        <v>580</v>
+        <v>840</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5755,7 +5761,7 @@
         <v>334</v>
       </c>
       <c r="B335" s="1">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5763,7 +5769,7 @@
         <v>335</v>
       </c>
       <c r="B336" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5771,7 +5777,7 @@
         <v>336</v>
       </c>
       <c r="B337" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5779,7 +5785,7 @@
         <v>337</v>
       </c>
       <c r="B338" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5787,7 +5793,7 @@
         <v>338</v>
       </c>
       <c r="B339" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5795,7 +5801,7 @@
         <v>339</v>
       </c>
       <c r="B340" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5803,7 +5809,7 @@
         <v>340</v>
       </c>
       <c r="B341" s="1">
-        <v>1000</v>
+        <v>880</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5811,7 +5817,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="1">
-        <v>520</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5819,7 +5825,7 @@
         <v>342</v>
       </c>
       <c r="B343" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5827,7 +5833,7 @@
         <v>343</v>
       </c>
       <c r="B344" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5835,7 +5841,7 @@
         <v>344</v>
       </c>
       <c r="B345" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5843,7 +5849,7 @@
         <v>345</v>
       </c>
       <c r="B346" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5851,7 +5857,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="1">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5859,7 +5865,7 @@
         <v>347</v>
       </c>
       <c r="B348" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5867,7 +5873,7 @@
         <v>348</v>
       </c>
       <c r="B349" s="1">
-        <v>320</v>
+        <v>520</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5875,7 +5881,7 @@
         <v>349</v>
       </c>
       <c r="B350" s="1">
-        <v>540</v>
+        <v>320</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5883,7 +5889,7 @@
         <v>350</v>
       </c>
       <c r="B351" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5891,7 +5897,7 @@
         <v>351</v>
       </c>
       <c r="B352" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5907,7 +5913,7 @@
         <v>353</v>
       </c>
       <c r="B354" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5915,7 +5921,7 @@
         <v>354</v>
       </c>
       <c r="B355" s="1">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5923,7 +5929,7 @@
         <v>355</v>
       </c>
       <c r="B356" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5931,7 +5937,7 @@
         <v>356</v>
       </c>
       <c r="B357" s="1">
-        <v>480</v>
+        <v>800</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5939,7 +5945,7 @@
         <v>357</v>
       </c>
       <c r="B358" s="1">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5947,7 +5953,7 @@
         <v>358</v>
       </c>
       <c r="B359" s="1">
-        <v>520</v>
+        <v>800</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5955,7 +5961,7 @@
         <v>359</v>
       </c>
       <c r="B360" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5963,7 +5969,7 @@
         <v>360</v>
       </c>
       <c r="B361" s="1">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5971,7 +5977,7 @@
         <v>361</v>
       </c>
       <c r="B362" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5987,7 +5993,7 @@
         <v>363</v>
       </c>
       <c r="B364" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -6003,7 +6009,7 @@
         <v>365</v>
       </c>
       <c r="B366" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -6011,7 +6017,7 @@
         <v>366</v>
       </c>
       <c r="B367" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -6019,7 +6025,7 @@
         <v>367</v>
       </c>
       <c r="B368" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -6027,7 +6033,7 @@
         <v>368</v>
       </c>
       <c r="B369" s="1">
-        <v>880</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -6035,7 +6041,7 @@
         <v>369</v>
       </c>
       <c r="B370" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -6043,7 +6049,7 @@
         <v>370</v>
       </c>
       <c r="B371" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -6051,7 +6057,7 @@
         <v>371</v>
       </c>
       <c r="B372" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -6059,7 +6065,7 @@
         <v>372</v>
       </c>
       <c r="B373" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -6067,7 +6073,7 @@
         <v>373</v>
       </c>
       <c r="B374" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -6075,7 +6081,7 @@
         <v>374</v>
       </c>
       <c r="B375" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -6083,7 +6089,7 @@
         <v>375</v>
       </c>
       <c r="B376" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -6091,7 +6097,7 @@
         <v>376</v>
       </c>
       <c r="B377" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -6107,7 +6113,7 @@
         <v>378</v>
       </c>
       <c r="B379" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -6123,7 +6129,7 @@
         <v>380</v>
       </c>
       <c r="B381" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -6131,7 +6137,7 @@
         <v>381</v>
       </c>
       <c r="B382" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -6139,7 +6145,7 @@
         <v>382</v>
       </c>
       <c r="B383" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -6147,7 +6153,7 @@
         <v>383</v>
       </c>
       <c r="B384" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -6155,7 +6161,7 @@
         <v>384</v>
       </c>
       <c r="B385" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -6163,7 +6169,7 @@
         <v>385</v>
       </c>
       <c r="B386" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -6171,7 +6177,7 @@
         <v>386</v>
       </c>
       <c r="B387" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -6179,7 +6185,7 @@
         <v>387</v>
       </c>
       <c r="B388" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -6187,7 +6193,7 @@
         <v>388</v>
       </c>
       <c r="B389" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -6195,7 +6201,7 @@
         <v>389</v>
       </c>
       <c r="B390" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -6203,7 +6209,7 @@
         <v>390</v>
       </c>
       <c r="B391" s="1">
-        <v>640</v>
+        <v>480</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -6211,7 +6217,7 @@
         <v>391</v>
       </c>
       <c r="B392" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -6219,7 +6225,7 @@
         <v>392</v>
       </c>
       <c r="B393" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -6227,7 +6233,7 @@
         <v>393</v>
       </c>
       <c r="B394" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -6235,7 +6241,7 @@
         <v>394</v>
       </c>
       <c r="B395" s="1">
-        <v>520</v>
+        <v>860</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -6243,7 +6249,7 @@
         <v>395</v>
       </c>
       <c r="B396" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -6251,7 +6257,7 @@
         <v>396</v>
       </c>
       <c r="B397" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -6267,7 +6273,7 @@
         <v>398</v>
       </c>
       <c r="B399" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -6275,7 +6281,7 @@
         <v>399</v>
       </c>
       <c r="B400" s="1">
-        <v>700</v>
+        <v>420</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -6283,7 +6289,7 @@
         <v>400</v>
       </c>
       <c r="B401" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -6291,7 +6297,7 @@
         <v>401</v>
       </c>
       <c r="B402" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -6299,7 +6305,7 @@
         <v>402</v>
       </c>
       <c r="B403" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -6307,7 +6313,7 @@
         <v>403</v>
       </c>
       <c r="B404" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -6315,7 +6321,7 @@
         <v>404</v>
       </c>
       <c r="B405" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -6323,7 +6329,7 @@
         <v>405</v>
       </c>
       <c r="B406" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -6331,7 +6337,7 @@
         <v>406</v>
       </c>
       <c r="B407" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -6339,7 +6345,7 @@
         <v>407</v>
       </c>
       <c r="B408" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -6347,7 +6353,7 @@
         <v>408</v>
       </c>
       <c r="B409" s="1">
-        <v>440</v>
+        <v>620</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -6355,7 +6361,7 @@
         <v>409</v>
       </c>
       <c r="B410" s="1">
-        <v>1100</v>
+        <v>440</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -6371,7 +6377,7 @@
         <v>411</v>
       </c>
       <c r="B412" s="1">
-        <v>320</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -6379,7 +6385,7 @@
         <v>412</v>
       </c>
       <c r="B413" s="1">
-        <v>940</v>
+        <v>320</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -6387,7 +6393,7 @@
         <v>413</v>
       </c>
       <c r="B414" s="1">
-        <v>320</v>
+        <v>940</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -6395,7 +6401,7 @@
         <v>414</v>
       </c>
       <c r="B415" s="1">
-        <v>960</v>
+        <v>320</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -6403,7 +6409,7 @@
         <v>415</v>
       </c>
       <c r="B416" s="1">
-        <v>820</v>
+        <v>960</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -6411,7 +6417,7 @@
         <v>416</v>
       </c>
       <c r="B417" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -6419,7 +6425,7 @@
         <v>417</v>
       </c>
       <c r="B418" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -6435,7 +6441,7 @@
         <v>419</v>
       </c>
       <c r="B420" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -6443,7 +6449,7 @@
         <v>420</v>
       </c>
       <c r="B421" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -6459,7 +6465,7 @@
         <v>422</v>
       </c>
       <c r="B423" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -6467,7 +6473,7 @@
         <v>423</v>
       </c>
       <c r="B424" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -6475,7 +6481,7 @@
         <v>424</v>
       </c>
       <c r="B425" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -6483,7 +6489,7 @@
         <v>425</v>
       </c>
       <c r="B426" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -6491,7 +6497,7 @@
         <v>426</v>
       </c>
       <c r="B427" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -6499,7 +6505,7 @@
         <v>427</v>
       </c>
       <c r="B428" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6507,7 +6513,7 @@
         <v>428</v>
       </c>
       <c r="B429" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6523,7 +6529,7 @@
         <v>430</v>
       </c>
       <c r="B431" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6531,7 +6537,7 @@
         <v>431</v>
       </c>
       <c r="B432" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6539,7 +6545,7 @@
         <v>432</v>
       </c>
       <c r="B433" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6547,7 +6553,7 @@
         <v>433</v>
       </c>
       <c r="B434" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6555,7 +6561,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6563,7 +6569,7 @@
         <v>435</v>
       </c>
       <c r="B436" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6571,7 +6577,7 @@
         <v>436</v>
       </c>
       <c r="B437" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6579,7 +6585,7 @@
         <v>437</v>
       </c>
       <c r="B438" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6587,7 +6593,7 @@
         <v>438</v>
       </c>
       <c r="B439" s="1">
-        <v>700</v>
+        <v>440</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6595,7 +6601,7 @@
         <v>439</v>
       </c>
       <c r="B440" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6611,7 +6617,7 @@
         <v>441</v>
       </c>
       <c r="B442" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6619,7 +6625,7 @@
         <v>442</v>
       </c>
       <c r="B443" s="1">
-        <v>560</v>
+        <v>800</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6627,7 +6633,7 @@
         <v>443</v>
       </c>
       <c r="B444" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6635,7 +6641,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6643,7 +6649,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6651,7 +6657,7 @@
         <v>446</v>
       </c>
       <c r="B447" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6659,7 +6665,7 @@
         <v>447</v>
       </c>
       <c r="B448" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6667,7 +6673,7 @@
         <v>448</v>
       </c>
       <c r="B449" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6675,7 +6681,7 @@
         <v>449</v>
       </c>
       <c r="B450" s="1">
-        <v>720</v>
+        <v>620</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6683,7 +6689,7 @@
         <v>450</v>
       </c>
       <c r="B451" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6691,7 +6697,7 @@
         <v>451</v>
       </c>
       <c r="B452" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6707,7 +6713,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6715,7 +6721,7 @@
         <v>454</v>
       </c>
       <c r="B455" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6723,7 +6729,7 @@
         <v>455</v>
       </c>
       <c r="B456" s="1">
-        <v>900</v>
+        <v>880</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6731,7 +6737,7 @@
         <v>456</v>
       </c>
       <c r="B457" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6739,7 +6745,7 @@
         <v>457</v>
       </c>
       <c r="B458" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6747,7 +6753,7 @@
         <v>458</v>
       </c>
       <c r="B459" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6755,7 +6761,7 @@
         <v>459</v>
       </c>
       <c r="B460" s="1">
-        <v>800</v>
+        <v>920</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6763,7 +6769,7 @@
         <v>460</v>
       </c>
       <c r="B461" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6771,7 +6777,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6779,7 +6785,7 @@
         <v>462</v>
       </c>
       <c r="B463" s="1">
-        <v>980</v>
+        <v>940</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6787,7 +6793,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6795,7 +6801,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6803,7 +6809,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6811,7 +6817,7 @@
         <v>466</v>
       </c>
       <c r="B467" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6819,7 +6825,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6835,7 +6841,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6843,7 +6849,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6851,7 +6857,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="1">
-        <v>640</v>
+        <v>920</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6859,7 +6865,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6867,7 +6873,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6875,7 +6881,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="1">
-        <v>960</v>
+        <v>820</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6883,7 +6889,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6891,7 +6897,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6899,7 +6905,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6907,7 +6913,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="1">
-        <v>860</v>
+        <v>640</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6915,7 +6921,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6923,7 +6929,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6931,7 +6937,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6939,7 +6945,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6947,7 +6953,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6955,7 +6961,7 @@
         <v>484</v>
       </c>
       <c r="B485" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6963,7 +6969,7 @@
         <v>485</v>
       </c>
       <c r="B486" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6971,7 +6977,7 @@
         <v>486</v>
       </c>
       <c r="B487" s="1">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6979,7 +6985,7 @@
         <v>487</v>
       </c>
       <c r="B488" s="1">
-        <v>620</v>
+        <v>480</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6987,7 +6993,7 @@
         <v>488</v>
       </c>
       <c r="B489" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6995,7 +7001,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -7003,7 +7009,7 @@
         <v>490</v>
       </c>
       <c r="B491" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -7011,7 +7017,7 @@
         <v>491</v>
       </c>
       <c r="B492" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -7019,7 +7025,7 @@
         <v>492</v>
       </c>
       <c r="B493" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -7027,7 +7033,7 @@
         <v>493</v>
       </c>
       <c r="B494" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -7035,7 +7041,7 @@
         <v>494</v>
       </c>
       <c r="B495" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -7043,7 +7049,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="1">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -7051,7 +7057,7 @@
         <v>496</v>
       </c>
       <c r="B497" s="1">
-        <v>840</v>
+        <v>480</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -7059,7 +7065,7 @@
         <v>497</v>
       </c>
       <c r="B498" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -7067,7 +7073,7 @@
         <v>498</v>
       </c>
       <c r="B499" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -7075,7 +7081,7 @@
         <v>499</v>
       </c>
       <c r="B500" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -7091,7 +7097,7 @@
         <v>501</v>
       </c>
       <c r="B502" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -7099,7 +7105,7 @@
         <v>502</v>
       </c>
       <c r="B503" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -7107,7 +7113,7 @@
         <v>503</v>
       </c>
       <c r="B504" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -7115,7 +7121,7 @@
         <v>504</v>
       </c>
       <c r="B505" s="1">
-        <v>880</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -7131,7 +7137,7 @@
         <v>506</v>
       </c>
       <c r="B507" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -7139,7 +7145,7 @@
         <v>507</v>
       </c>
       <c r="B508" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -7147,7 +7153,7 @@
         <v>508</v>
       </c>
       <c r="B509" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -7155,7 +7161,7 @@
         <v>509</v>
       </c>
       <c r="B510" s="1">
-        <v>1100</v>
+        <v>660</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -7163,7 +7169,7 @@
         <v>510</v>
       </c>
       <c r="B511" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -7171,7 +7177,7 @@
         <v>511</v>
       </c>
       <c r="B512" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -7179,7 +7185,7 @@
         <v>512</v>
       </c>
       <c r="B513" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -7187,7 +7193,7 @@
         <v>513</v>
       </c>
       <c r="B514" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -7195,7 +7201,7 @@
         <v>514</v>
       </c>
       <c r="B515" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -7211,7 +7217,7 @@
         <v>516</v>
       </c>
       <c r="B517" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -7219,7 +7225,7 @@
         <v>517</v>
       </c>
       <c r="B518" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -7227,7 +7233,7 @@
         <v>518</v>
       </c>
       <c r="B519" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -7235,7 +7241,7 @@
         <v>519</v>
       </c>
       <c r="B520" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -7243,7 +7249,7 @@
         <v>520</v>
       </c>
       <c r="B521" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -7251,7 +7257,7 @@
         <v>521</v>
       </c>
       <c r="B522" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -7267,7 +7273,7 @@
         <v>523</v>
       </c>
       <c r="B524" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -7275,7 +7281,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -7283,7 +7289,7 @@
         <v>525</v>
       </c>
       <c r="B526" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -7291,7 +7297,7 @@
         <v>526</v>
       </c>
       <c r="B527" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -7299,7 +7305,7 @@
         <v>527</v>
       </c>
       <c r="B528" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -7307,7 +7313,7 @@
         <v>528</v>
       </c>
       <c r="B529" s="1">
-        <v>840</v>
+        <v>620</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -7315,7 +7321,7 @@
         <v>529</v>
       </c>
       <c r="B530" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -7323,7 +7329,7 @@
         <v>530</v>
       </c>
       <c r="B531" s="1">
-        <v>1060</v>
+        <v>880</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -7331,7 +7337,7 @@
         <v>531</v>
       </c>
       <c r="B532" s="1">
-        <v>860</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -7347,7 +7353,7 @@
         <v>533</v>
       </c>
       <c r="B534" s="1">
-        <v>800</v>
+        <v>860</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -7355,7 +7361,7 @@
         <v>534</v>
       </c>
       <c r="B535" s="1">
-        <v>860</v>
+        <v>800</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -7363,7 +7369,7 @@
         <v>535</v>
       </c>
       <c r="B536" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -7371,7 +7377,7 @@
         <v>536</v>
       </c>
       <c r="B537" s="1">
-        <v>760</v>
+        <v>960</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -7379,7 +7385,7 @@
         <v>537</v>
       </c>
       <c r="B538" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -7387,7 +7393,7 @@
         <v>538</v>
       </c>
       <c r="B539" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -7395,7 +7401,7 @@
         <v>539</v>
       </c>
       <c r="B540" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -7411,7 +7417,7 @@
         <v>541</v>
       </c>
       <c r="B542" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -7419,7 +7425,7 @@
         <v>542</v>
       </c>
       <c r="B543" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -7427,7 +7433,7 @@
         <v>543</v>
       </c>
       <c r="B544" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -7443,7 +7449,7 @@
         <v>545</v>
       </c>
       <c r="B546" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -7451,7 +7457,7 @@
         <v>546</v>
       </c>
       <c r="B547" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -7459,7 +7465,7 @@
         <v>547</v>
       </c>
       <c r="B548" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -7467,7 +7473,7 @@
         <v>548</v>
       </c>
       <c r="B549" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -7475,7 +7481,7 @@
         <v>549</v>
       </c>
       <c r="B550" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -7483,7 +7489,7 @@
         <v>550</v>
       </c>
       <c r="B551" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -7491,7 +7497,7 @@
         <v>551</v>
       </c>
       <c r="B552" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7499,7 +7505,7 @@
         <v>552</v>
       </c>
       <c r="B553" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7507,7 +7513,7 @@
         <v>553</v>
       </c>
       <c r="B554" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7523,7 +7529,7 @@
         <v>555</v>
       </c>
       <c r="B556" s="1">
-        <v>880</v>
+        <v>700</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7531,7 +7537,7 @@
         <v>556</v>
       </c>
       <c r="B557" s="1">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7539,7 +7545,7 @@
         <v>557</v>
       </c>
       <c r="B558" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7547,7 +7553,7 @@
         <v>558</v>
       </c>
       <c r="B559" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7555,7 +7561,7 @@
         <v>559</v>
       </c>
       <c r="B560" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7563,7 +7569,7 @@
         <v>560</v>
       </c>
       <c r="B561" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7571,7 +7577,7 @@
         <v>561</v>
       </c>
       <c r="B562" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7579,7 +7585,7 @@
         <v>562</v>
       </c>
       <c r="B563" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7587,7 +7593,7 @@
         <v>563</v>
       </c>
       <c r="B564" s="1">
-        <v>640</v>
+        <v>880</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7595,7 +7601,7 @@
         <v>564</v>
       </c>
       <c r="B565" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7603,7 +7609,7 @@
         <v>565</v>
       </c>
       <c r="B566" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7611,7 +7617,7 @@
         <v>566</v>
       </c>
       <c r="B567" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7627,7 +7633,7 @@
         <v>568</v>
       </c>
       <c r="B569" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7635,7 +7641,7 @@
         <v>569</v>
       </c>
       <c r="B570" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7651,7 +7657,7 @@
         <v>571</v>
       </c>
       <c r="B572" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7659,7 +7665,7 @@
         <v>572</v>
       </c>
       <c r="B573" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7667,7 +7673,7 @@
         <v>573</v>
       </c>
       <c r="B574" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7675,7 +7681,7 @@
         <v>574</v>
       </c>
       <c r="B575" s="1">
-        <v>940</v>
+        <v>960</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7683,7 +7689,7 @@
         <v>575</v>
       </c>
       <c r="B576" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7699,7 +7705,7 @@
         <v>577</v>
       </c>
       <c r="B578" s="1">
-        <v>940</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7707,7 +7713,7 @@
         <v>578</v>
       </c>
       <c r="B579" s="1">
-        <v>860</v>
+        <v>940</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7715,7 +7721,7 @@
         <v>579</v>
       </c>
       <c r="B580" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7723,7 +7729,7 @@
         <v>580</v>
       </c>
       <c r="B581" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7731,7 +7737,7 @@
         <v>581</v>
       </c>
       <c r="B582" s="1">
-        <v>960</v>
+        <v>920</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7739,7 +7745,7 @@
         <v>582</v>
       </c>
       <c r="B583" s="1">
-        <v>680</v>
+        <v>960</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7747,7 +7753,7 @@
         <v>583</v>
       </c>
       <c r="B584" s="1">
-        <v>840</v>
+        <v>680</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7755,7 +7761,7 @@
         <v>584</v>
       </c>
       <c r="B585" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7763,7 +7769,7 @@
         <v>585</v>
       </c>
       <c r="B586" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7771,7 +7777,7 @@
         <v>586</v>
       </c>
       <c r="B587" s="1">
-        <v>580</v>
+        <v>880</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7779,7 +7785,7 @@
         <v>587</v>
       </c>
       <c r="B588" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7787,7 +7793,7 @@
         <v>588</v>
       </c>
       <c r="B589" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7795,7 +7801,7 @@
         <v>589</v>
       </c>
       <c r="B590" s="1">
-        <v>620</v>
+        <v>860</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7803,7 +7809,7 @@
         <v>590</v>
       </c>
       <c r="B591" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7811,7 +7817,7 @@
         <v>591</v>
       </c>
       <c r="B592" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7819,7 +7825,7 @@
         <v>592</v>
       </c>
       <c r="B593" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7827,7 +7833,7 @@
         <v>593</v>
       </c>
       <c r="B594" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7835,7 +7841,7 @@
         <v>594</v>
       </c>
       <c r="B595" s="1">
-        <v>900</v>
+        <v>960</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7843,7 +7849,7 @@
         <v>595</v>
       </c>
       <c r="B596" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7851,7 +7857,7 @@
         <v>596</v>
       </c>
       <c r="B597" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7859,7 +7865,7 @@
         <v>597</v>
       </c>
       <c r="B598" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7867,7 +7873,7 @@
         <v>598</v>
       </c>
       <c r="B599" s="1">
-        <v>540</v>
+        <v>780</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7875,7 +7881,7 @@
         <v>599</v>
       </c>
       <c r="B600" s="1">
-        <v>1100</v>
+        <v>540</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7883,7 +7889,7 @@
         <v>600</v>
       </c>
       <c r="B601" s="1">
-        <v>1060</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7891,7 +7897,7 @@
         <v>601</v>
       </c>
       <c r="B602" s="1">
-        <v>1100</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7907,7 +7913,7 @@
         <v>603</v>
       </c>
       <c r="B604" s="1">
-        <v>1080</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7915,7 +7921,7 @@
         <v>604</v>
       </c>
       <c r="B605" s="1">
-        <v>840</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7931,7 +7937,7 @@
         <v>606</v>
       </c>
       <c r="B607" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7939,7 +7945,7 @@
         <v>607</v>
       </c>
       <c r="B608" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7947,7 +7953,7 @@
         <v>608</v>
       </c>
       <c r="B609" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7955,7 +7961,7 @@
         <v>609</v>
       </c>
       <c r="B610" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7963,7 +7969,7 @@
         <v>610</v>
       </c>
       <c r="B611" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7971,7 +7977,7 @@
         <v>611</v>
       </c>
       <c r="B612" s="1">
-        <v>980</v>
+        <v>860</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7979,7 +7985,7 @@
         <v>612</v>
       </c>
       <c r="B613" s="1">
-        <v>740</v>
+        <v>980</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7987,7 +7993,7 @@
         <v>613</v>
       </c>
       <c r="B614" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -7995,7 +8001,7 @@
         <v>614</v>
       </c>
       <c r="B615" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -8019,7 +8025,7 @@
         <v>617</v>
       </c>
       <c r="B618" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -8043,7 +8049,7 @@
         <v>620</v>
       </c>
       <c r="B621" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -8051,7 +8057,7 @@
         <v>621</v>
       </c>
       <c r="B622" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -8059,7 +8065,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -8067,7 +8073,7 @@
         <v>623</v>
       </c>
       <c r="B624" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -8075,7 +8081,7 @@
         <v>624</v>
       </c>
       <c r="B625" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -8083,7 +8089,7 @@
         <v>625</v>
       </c>
       <c r="B626" s="1">
-        <v>800</v>
+        <v>980</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -8091,7 +8097,7 @@
         <v>626</v>
       </c>
       <c r="B627" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -8099,7 +8105,7 @@
         <v>627</v>
       </c>
       <c r="B628" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -8115,7 +8121,7 @@
         <v>629</v>
       </c>
       <c r="B630" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -8123,7 +8129,7 @@
         <v>630</v>
       </c>
       <c r="B631" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -8139,7 +8145,7 @@
         <v>632</v>
       </c>
       <c r="B633" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -8147,7 +8153,7 @@
         <v>633</v>
       </c>
       <c r="B634" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -8155,7 +8161,7 @@
         <v>634</v>
       </c>
       <c r="B635" s="1">
-        <v>820</v>
+        <v>860</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -8163,7 +8169,7 @@
         <v>635</v>
       </c>
       <c r="B636" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -8171,7 +8177,7 @@
         <v>636</v>
       </c>
       <c r="B637" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -8179,7 +8185,7 @@
         <v>637</v>
       </c>
       <c r="B638" s="1">
-        <v>1400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -8195,7 +8201,7 @@
         <v>639</v>
       </c>
       <c r="B640" s="1">
-        <v>660</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -8203,7 +8209,7 @@
         <v>640</v>
       </c>
       <c r="B641" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -8211,7 +8217,7 @@
         <v>641</v>
       </c>
       <c r="B642" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -8219,7 +8225,7 @@
         <v>642</v>
       </c>
       <c r="B643" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -8227,7 +8233,7 @@
         <v>643</v>
       </c>
       <c r="B644" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -8235,7 +8241,7 @@
         <v>644</v>
       </c>
       <c r="B645" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -8243,7 +8249,7 @@
         <v>645</v>
       </c>
       <c r="B646" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -8251,7 +8257,7 @@
         <v>646</v>
       </c>
       <c r="B647" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -8259,7 +8265,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -8267,7 +8273,7 @@
         <v>648</v>
       </c>
       <c r="B649" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -8275,7 +8281,7 @@
         <v>649</v>
       </c>
       <c r="B650" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -8283,7 +8289,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -8291,7 +8297,7 @@
         <v>651</v>
       </c>
       <c r="B652" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -8299,7 +8305,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -8307,7 +8313,7 @@
         <v>653</v>
       </c>
       <c r="B654" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -8323,7 +8329,7 @@
         <v>655</v>
       </c>
       <c r="B656" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -8331,7 +8337,7 @@
         <v>656</v>
       </c>
       <c r="B657" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -8339,7 +8345,7 @@
         <v>657</v>
       </c>
       <c r="B658" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -8347,7 +8353,7 @@
         <v>658</v>
       </c>
       <c r="B659" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -8355,7 +8361,7 @@
         <v>659</v>
       </c>
       <c r="B660" s="1">
-        <v>4000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -8363,7 +8369,7 @@
         <v>660</v>
       </c>
       <c r="B661" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -8371,7 +8377,7 @@
         <v>661</v>
       </c>
       <c r="B662" s="1">
-        <v>720</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -8379,7 +8385,7 @@
         <v>662</v>
       </c>
       <c r="B663" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -8387,7 +8393,7 @@
         <v>663</v>
       </c>
       <c r="B664" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -8395,7 +8401,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -8403,7 +8409,7 @@
         <v>665</v>
       </c>
       <c r="B666" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -8411,7 +8417,7 @@
         <v>666</v>
       </c>
       <c r="B667" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -8419,7 +8425,7 @@
         <v>667</v>
       </c>
       <c r="B668" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -8427,7 +8433,7 @@
         <v>668</v>
       </c>
       <c r="B669" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -8435,7 +8441,7 @@
         <v>669</v>
       </c>
       <c r="B670" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -8443,7 +8449,7 @@
         <v>670</v>
       </c>
       <c r="B671" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -8451,7 +8457,7 @@
         <v>671</v>
       </c>
       <c r="B672" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -8459,7 +8465,7 @@
         <v>672</v>
       </c>
       <c r="B673" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -8475,7 +8481,7 @@
         <v>674</v>
       </c>
       <c r="B675" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8491,7 +8497,7 @@
         <v>676</v>
       </c>
       <c r="B677" s="1">
-        <v>980</v>
+        <v>900</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8499,7 +8505,7 @@
         <v>677</v>
       </c>
       <c r="B678" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8507,7 +8513,7 @@
         <v>678</v>
       </c>
       <c r="B679" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8515,7 +8521,7 @@
         <v>679</v>
       </c>
       <c r="B680" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8523,7 +8529,7 @@
         <v>680</v>
       </c>
       <c r="B681" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8531,7 +8537,7 @@
         <v>681</v>
       </c>
       <c r="B682" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8539,7 +8545,7 @@
         <v>682</v>
       </c>
       <c r="B683" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8547,7 +8553,7 @@
         <v>683</v>
       </c>
       <c r="B684" s="1">
-        <v>860</v>
+        <v>680</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8563,7 +8569,7 @@
         <v>685</v>
       </c>
       <c r="B686" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8579,7 +8585,7 @@
         <v>687</v>
       </c>
       <c r="B688" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8587,7 +8593,7 @@
         <v>688</v>
       </c>
       <c r="B689" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8595,7 +8601,7 @@
         <v>689</v>
       </c>
       <c r="B690" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8603,7 +8609,7 @@
         <v>690</v>
       </c>
       <c r="B691" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8611,7 +8617,7 @@
         <v>691</v>
       </c>
       <c r="B692" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8619,7 +8625,7 @@
         <v>692</v>
       </c>
       <c r="B693" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8627,7 +8633,7 @@
         <v>693</v>
       </c>
       <c r="B694" s="1">
-        <v>840</v>
+        <v>800</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8635,7 +8641,7 @@
         <v>694</v>
       </c>
       <c r="B695" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8643,7 +8649,7 @@
         <v>695</v>
       </c>
       <c r="B696" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8651,7 +8657,7 @@
         <v>696</v>
       </c>
       <c r="B697" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8659,7 +8665,7 @@
         <v>697</v>
       </c>
       <c r="B698" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8675,7 +8681,7 @@
         <v>699</v>
       </c>
       <c r="B700" s="1">
-        <v>880</v>
+        <v>640</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8683,7 +8689,7 @@
         <v>700</v>
       </c>
       <c r="B701" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8691,7 +8697,7 @@
         <v>701</v>
       </c>
       <c r="B702" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8699,7 +8705,7 @@
         <v>702</v>
       </c>
       <c r="B703" s="1">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8707,7 +8713,7 @@
         <v>703</v>
       </c>
       <c r="B704" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8723,7 +8729,7 @@
         <v>705</v>
       </c>
       <c r="B706" s="1">
-        <v>800</v>
+        <v>820</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8731,7 +8737,7 @@
         <v>706</v>
       </c>
       <c r="B707" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8747,7 +8753,7 @@
         <v>708</v>
       </c>
       <c r="B709" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8755,7 +8761,7 @@
         <v>709</v>
       </c>
       <c r="B710" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8763,7 +8769,7 @@
         <v>710</v>
       </c>
       <c r="B711" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8771,7 +8777,7 @@
         <v>711</v>
       </c>
       <c r="B712" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8779,7 +8785,7 @@
         <v>712</v>
       </c>
       <c r="B713" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8787,7 +8793,7 @@
         <v>713</v>
       </c>
       <c r="B714" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8795,7 +8801,7 @@
         <v>714</v>
       </c>
       <c r="B715" s="1">
-        <v>880</v>
+        <v>960</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8803,7 +8809,7 @@
         <v>715</v>
       </c>
       <c r="B716" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8811,7 +8817,7 @@
         <v>716</v>
       </c>
       <c r="B717" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8819,7 +8825,7 @@
         <v>717</v>
       </c>
       <c r="B718" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8827,7 +8833,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8835,7 +8841,7 @@
         <v>719</v>
       </c>
       <c r="B720" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8843,7 +8849,7 @@
         <v>720</v>
       </c>
       <c r="B721" s="1">
-        <v>1020</v>
+        <v>640</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8859,7 +8865,7 @@
         <v>722</v>
       </c>
       <c r="B723" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8867,7 +8873,7 @@
         <v>723</v>
       </c>
       <c r="B724" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8875,7 +8881,7 @@
         <v>724</v>
       </c>
       <c r="B725" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8883,7 +8889,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8891,7 +8897,7 @@
         <v>726</v>
       </c>
       <c r="B727" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8899,7 +8905,7 @@
         <v>727</v>
       </c>
       <c r="B728" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8907,7 +8913,7 @@
         <v>728</v>
       </c>
       <c r="B729" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8923,7 +8929,7 @@
         <v>730</v>
       </c>
       <c r="B731" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8931,7 +8937,7 @@
         <v>731</v>
       </c>
       <c r="B732" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -8939,7 +8945,7 @@
         <v>732</v>
       </c>
       <c r="B733" s="1">
-        <v>680</v>
+        <v>820</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -8947,7 +8953,7 @@
         <v>733</v>
       </c>
       <c r="B734" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -8955,7 +8961,7 @@
         <v>734</v>
       </c>
       <c r="B735" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -8963,7 +8969,7 @@
         <v>735</v>
       </c>
       <c r="B736" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -8971,7 +8977,7 @@
         <v>736</v>
       </c>
       <c r="B737" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -8979,7 +8985,7 @@
         <v>737</v>
       </c>
       <c r="B738" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="739" spans="1:2">
@@ -8995,7 +9001,7 @@
         <v>739</v>
       </c>
       <c r="B740" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -9003,7 +9009,7 @@
         <v>740</v>
       </c>
       <c r="B741" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="742" spans="1:2">
@@ -9011,7 +9017,7 @@
         <v>741</v>
       </c>
       <c r="B742" s="1">
-        <v>1100</v>
+        <v>840</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -9019,7 +9025,7 @@
         <v>742</v>
       </c>
       <c r="B743" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="744" spans="1:2">
@@ -9027,7 +9033,7 @@
         <v>743</v>
       </c>
       <c r="B744" s="1">
-        <v>940</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="745" spans="1:2">
@@ -9035,7 +9041,7 @@
         <v>744</v>
       </c>
       <c r="B745" s="1">
-        <v>820</v>
+        <v>940</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -9043,7 +9049,7 @@
         <v>745</v>
       </c>
       <c r="B746" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="747" spans="1:2">
@@ -9051,7 +9057,7 @@
         <v>746</v>
       </c>
       <c r="B747" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="748" spans="1:2">
@@ -9059,7 +9065,7 @@
         <v>747</v>
       </c>
       <c r="B748" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="749" spans="1:2">
@@ -9067,7 +9073,7 @@
         <v>748</v>
       </c>
       <c r="B749" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -9075,7 +9081,7 @@
         <v>749</v>
       </c>
       <c r="B750" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="751" spans="1:2">
@@ -9083,7 +9089,7 @@
         <v>750</v>
       </c>
       <c r="B751" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="752" spans="1:2">
@@ -9091,7 +9097,7 @@
         <v>751</v>
       </c>
       <c r="B752" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="753" spans="1:2">
@@ -9107,7 +9113,7 @@
         <v>753</v>
       </c>
       <c r="B754" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -9115,7 +9121,7 @@
         <v>754</v>
       </c>
       <c r="B755" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="756" spans="1:2">
@@ -9123,7 +9129,7 @@
         <v>755</v>
       </c>
       <c r="B756" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="757" spans="1:2">
@@ -9131,7 +9137,7 @@
         <v>756</v>
       </c>
       <c r="B757" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="758" spans="1:2">
@@ -9139,7 +9145,7 @@
         <v>757</v>
       </c>
       <c r="B758" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="759" spans="1:2">
@@ -9147,7 +9153,7 @@
         <v>758</v>
       </c>
       <c r="B759" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="760" spans="1:2">
@@ -9163,7 +9169,7 @@
         <v>760</v>
       </c>
       <c r="B761" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="762" spans="1:2">
@@ -9171,7 +9177,7 @@
         <v>761</v>
       </c>
       <c r="B762" s="1">
-        <v>440</v>
+        <v>900</v>
       </c>
     </row>
     <row r="763" spans="1:2">
@@ -9179,7 +9185,7 @@
         <v>762</v>
       </c>
       <c r="B763" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="764" spans="1:2">
@@ -9187,7 +9193,7 @@
         <v>763</v>
       </c>
       <c r="B764" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="765" spans="1:2">
@@ -9195,7 +9201,7 @@
         <v>764</v>
       </c>
       <c r="B765" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="766" spans="1:2">
@@ -9203,7 +9209,7 @@
         <v>765</v>
       </c>
       <c r="B766" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="767" spans="1:2">
@@ -9211,7 +9217,7 @@
         <v>766</v>
       </c>
       <c r="B767" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="768" spans="1:2">
@@ -9219,7 +9225,7 @@
         <v>767</v>
       </c>
       <c r="B768" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="769" spans="1:2">
@@ -9227,7 +9233,7 @@
         <v>768</v>
       </c>
       <c r="B769" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="770" spans="1:2">
@@ -9235,7 +9241,7 @@
         <v>769</v>
       </c>
       <c r="B770" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="771" spans="1:2">
@@ -9243,7 +9249,7 @@
         <v>770</v>
       </c>
       <c r="B771" s="1">
-        <v>880</v>
+        <v>560</v>
       </c>
     </row>
     <row r="772" spans="1:2">
@@ -9251,7 +9257,7 @@
         <v>771</v>
       </c>
       <c r="B772" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="773" spans="1:2">
@@ -9267,7 +9273,7 @@
         <v>773</v>
       </c>
       <c r="B774" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="775" spans="1:2">
@@ -9275,7 +9281,7 @@
         <v>774</v>
       </c>
       <c r="B775" s="1">
-        <v>920</v>
+        <v>880</v>
       </c>
     </row>
     <row r="776" spans="1:2">
@@ -9283,7 +9289,7 @@
         <v>775</v>
       </c>
       <c r="B776" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="777" spans="1:2">
@@ -9291,7 +9297,7 @@
         <v>776</v>
       </c>
       <c r="B777" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="778" spans="1:2">
@@ -9299,7 +9305,7 @@
         <v>777</v>
       </c>
       <c r="B778" s="1">
-        <v>980</v>
+        <v>800</v>
       </c>
     </row>
     <row r="779" spans="1:2">
@@ -9307,7 +9313,7 @@
         <v>778</v>
       </c>
       <c r="B779" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="780" spans="1:2">
@@ -9315,7 +9321,7 @@
         <v>779</v>
       </c>
       <c r="B780" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="781" spans="1:2">
@@ -9323,7 +9329,7 @@
         <v>780</v>
       </c>
       <c r="B781" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="782" spans="1:2">
@@ -9331,7 +9337,7 @@
         <v>781</v>
       </c>
       <c r="B782" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="783" spans="1:2">
@@ -9339,7 +9345,7 @@
         <v>782</v>
       </c>
       <c r="B783" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="784" spans="1:2">
@@ -9347,7 +9353,7 @@
         <v>783</v>
       </c>
       <c r="B784" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="785" spans="1:2">
@@ -9355,7 +9361,7 @@
         <v>784</v>
       </c>
       <c r="B785" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="786" spans="1:2">
@@ -9363,7 +9369,7 @@
         <v>785</v>
       </c>
       <c r="B786" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="787" spans="1:2">
@@ -9371,7 +9377,7 @@
         <v>786</v>
       </c>
       <c r="B787" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="788" spans="1:2">
@@ -9379,7 +9385,7 @@
         <v>787</v>
       </c>
       <c r="B788" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="789" spans="1:2">
@@ -9387,7 +9393,7 @@
         <v>788</v>
       </c>
       <c r="B789" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="790" spans="1:2">
@@ -9395,7 +9401,7 @@
         <v>789</v>
       </c>
       <c r="B790" s="1">
-        <v>660</v>
+        <v>860</v>
       </c>
     </row>
     <row r="791" spans="1:2">
@@ -9403,7 +9409,7 @@
         <v>790</v>
       </c>
       <c r="B791" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="792" spans="1:2">
@@ -9411,7 +9417,7 @@
         <v>791</v>
       </c>
       <c r="B792" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="793" spans="1:2">
@@ -9419,7 +9425,7 @@
         <v>792</v>
       </c>
       <c r="B793" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="794" spans="1:2">
@@ -9427,7 +9433,7 @@
         <v>793</v>
       </c>
       <c r="B794" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="795" spans="1:2">
@@ -9435,7 +9441,7 @@
         <v>794</v>
       </c>
       <c r="B795" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="796" spans="1:2">
@@ -9443,7 +9449,7 @@
         <v>795</v>
       </c>
       <c r="B796" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="797" spans="1:2">
@@ -9451,7 +9457,7 @@
         <v>796</v>
       </c>
       <c r="B797" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="798" spans="1:2">
@@ -9459,7 +9465,7 @@
         <v>797</v>
       </c>
       <c r="B798" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="799" spans="1:2">
@@ -9467,7 +9473,7 @@
         <v>798</v>
       </c>
       <c r="B799" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="800" spans="1:2">
@@ -9475,7 +9481,7 @@
         <v>799</v>
       </c>
       <c r="B800" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="801" spans="1:2">
@@ -9483,7 +9489,7 @@
         <v>800</v>
       </c>
       <c r="B801" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="802" spans="1:2">
@@ -9491,7 +9497,7 @@
         <v>801</v>
       </c>
       <c r="B802" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="803" spans="1:2">
@@ -9499,7 +9505,7 @@
         <v>802</v>
       </c>
       <c r="B803" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="804" spans="1:2">
@@ -9507,7 +9513,7 @@
         <v>803</v>
       </c>
       <c r="B804" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="805" spans="1:2">
@@ -9515,7 +9521,7 @@
         <v>804</v>
       </c>
       <c r="B805" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="806" spans="1:2">
@@ -9523,7 +9529,7 @@
         <v>805</v>
       </c>
       <c r="B806" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="807" spans="1:2">
@@ -9531,7 +9537,7 @@
         <v>806</v>
       </c>
       <c r="B807" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="808" spans="1:2">
@@ -9539,7 +9545,7 @@
         <v>807</v>
       </c>
       <c r="B808" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="809" spans="1:2">
@@ -9547,7 +9553,7 @@
         <v>808</v>
       </c>
       <c r="B809" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="810" spans="1:2">
@@ -9555,7 +9561,7 @@
         <v>809</v>
       </c>
       <c r="B810" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="811" spans="1:2">
@@ -9563,7 +9569,7 @@
         <v>810</v>
       </c>
       <c r="B811" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="812" spans="1:2">
@@ -9571,7 +9577,7 @@
         <v>811</v>
       </c>
       <c r="B812" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="813" spans="1:2">
@@ -9579,7 +9585,7 @@
         <v>812</v>
       </c>
       <c r="B813" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="814" spans="1:2">
@@ -9587,7 +9593,7 @@
         <v>813</v>
       </c>
       <c r="B814" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="815" spans="1:2">
@@ -9595,7 +9601,7 @@
         <v>814</v>
       </c>
       <c r="B815" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="816" spans="1:2">
@@ -9603,7 +9609,7 @@
         <v>815</v>
       </c>
       <c r="B816" s="1">
-        <v>920</v>
+        <v>500</v>
       </c>
     </row>
     <row r="817" spans="1:2">
@@ -9611,7 +9617,7 @@
         <v>816</v>
       </c>
       <c r="B817" s="1">
-        <v>1000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="818" spans="1:2">
@@ -9619,7 +9625,7 @@
         <v>817</v>
       </c>
       <c r="B818" s="1">
-        <v>1040</v>
+        <v>920</v>
       </c>
     </row>
     <row r="819" spans="1:2">
@@ -9627,7 +9633,7 @@
         <v>818</v>
       </c>
       <c r="B819" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="820" spans="1:2">
@@ -9635,7 +9641,7 @@
         <v>819</v>
       </c>
       <c r="B820" s="1">
-        <v>940</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="821" spans="1:2">
@@ -9643,7 +9649,7 @@
         <v>820</v>
       </c>
       <c r="B821" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="822" spans="1:2">
@@ -9651,7 +9657,7 @@
         <v>821</v>
       </c>
       <c r="B822" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="823" spans="1:2">
@@ -9659,7 +9665,7 @@
         <v>822</v>
       </c>
       <c r="B823" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="824" spans="1:2">
@@ -9667,7 +9673,7 @@
         <v>823</v>
       </c>
       <c r="B824" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="825" spans="1:2">
@@ -9675,7 +9681,7 @@
         <v>824</v>
       </c>
       <c r="B825" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="826" spans="1:2">
@@ -9683,7 +9689,7 @@
         <v>825</v>
       </c>
       <c r="B826" s="1">
-        <v>960</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="827" spans="1:2">
@@ -9691,7 +9697,7 @@
         <v>826</v>
       </c>
       <c r="B827" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="828" spans="1:2">
@@ -9699,7 +9705,7 @@
         <v>827</v>
       </c>
       <c r="B828" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="829" spans="1:2">
@@ -9707,7 +9713,7 @@
         <v>828</v>
       </c>
       <c r="B829" s="1">
-        <v>820</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="830" spans="1:2">
@@ -9715,7 +9721,7 @@
         <v>829</v>
       </c>
       <c r="B830" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="831" spans="1:2">
@@ -9723,7 +9729,7 @@
         <v>830</v>
       </c>
       <c r="B831" s="1">
-        <v>500</v>
+        <v>820</v>
       </c>
     </row>
     <row r="832" spans="1:2">
@@ -9739,7 +9745,7 @@
         <v>832</v>
       </c>
       <c r="B833" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="834" spans="1:2">
@@ -9747,7 +9753,7 @@
         <v>833</v>
       </c>
       <c r="B834" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="835" spans="1:2">
@@ -9755,7 +9761,7 @@
         <v>834</v>
       </c>
       <c r="B835" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="836" spans="1:2">
@@ -9763,7 +9769,7 @@
         <v>835</v>
       </c>
       <c r="B836" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="837" spans="1:2">
@@ -9771,7 +9777,7 @@
         <v>836</v>
       </c>
       <c r="B837" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="838" spans="1:2">
@@ -9779,7 +9785,7 @@
         <v>837</v>
       </c>
       <c r="B838" s="1">
-        <v>840</v>
+        <v>820</v>
       </c>
     </row>
     <row r="839" spans="1:2">
@@ -9787,7 +9793,7 @@
         <v>838</v>
       </c>
       <c r="B839" s="1">
-        <v>400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="840" spans="1:2">
@@ -9795,7 +9801,7 @@
         <v>839</v>
       </c>
       <c r="B840" s="1">
-        <v>400</v>
+        <v>840</v>
       </c>
     </row>
     <row r="841" spans="1:2">
@@ -9803,7 +9809,7 @@
         <v>840</v>
       </c>
       <c r="B841" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="842" spans="1:2">
@@ -9811,7 +9817,7 @@
         <v>841</v>
       </c>
       <c r="B842" s="1">
-        <v>840</v>
+        <v>400</v>
       </c>
     </row>
     <row r="843" spans="1:2">
@@ -9827,7 +9833,7 @@
         <v>843</v>
       </c>
       <c r="B844" s="1">
-        <v>380</v>
+        <v>840</v>
       </c>
     </row>
     <row r="845" spans="1:2">
@@ -9835,7 +9841,7 @@
         <v>844</v>
       </c>
       <c r="B845" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="846" spans="1:2">
@@ -9843,7 +9849,7 @@
         <v>845</v>
       </c>
       <c r="B846" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="847" spans="1:2">
@@ -9851,7 +9857,7 @@
         <v>846</v>
       </c>
       <c r="B847" s="1">
-        <v>800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="848" spans="1:2">
@@ -9859,7 +9865,7 @@
         <v>847</v>
       </c>
       <c r="B848" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="849" spans="1:2">
@@ -9867,7 +9873,7 @@
         <v>848</v>
       </c>
       <c r="B849" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="850" spans="1:2">
@@ -9875,7 +9881,7 @@
         <v>849</v>
       </c>
       <c r="B850" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="851" spans="1:2">
@@ -9883,7 +9889,7 @@
         <v>850</v>
       </c>
       <c r="B851" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="852" spans="1:2">
@@ -9891,7 +9897,7 @@
         <v>851</v>
       </c>
       <c r="B852" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="853" spans="1:2">
@@ -9899,7 +9905,7 @@
         <v>852</v>
       </c>
       <c r="B853" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="854" spans="1:2">
@@ -9907,7 +9913,7 @@
         <v>853</v>
       </c>
       <c r="B854" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="855" spans="1:2">
@@ -9915,7 +9921,7 @@
         <v>854</v>
       </c>
       <c r="B855" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="856" spans="1:2">
@@ -9923,7 +9929,7 @@
         <v>855</v>
       </c>
       <c r="B856" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="857" spans="1:2">
@@ -9931,7 +9937,7 @@
         <v>856</v>
       </c>
       <c r="B857" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="858" spans="1:2">
@@ -9939,7 +9945,7 @@
         <v>857</v>
       </c>
       <c r="B858" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="859" spans="1:2">
@@ -9947,7 +9953,7 @@
         <v>858</v>
       </c>
       <c r="B859" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="860" spans="1:2">
@@ -9955,7 +9961,7 @@
         <v>859</v>
       </c>
       <c r="B860" s="1">
-        <v>840</v>
+        <v>500</v>
       </c>
     </row>
     <row r="861" spans="1:2">
@@ -9963,7 +9969,7 @@
         <v>860</v>
       </c>
       <c r="B861" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="862" spans="1:2">
@@ -9971,7 +9977,7 @@
         <v>861</v>
       </c>
       <c r="B862" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="863" spans="1:2">
@@ -9979,7 +9985,7 @@
         <v>862</v>
       </c>
       <c r="B863" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="864" spans="1:2">
@@ -9987,7 +9993,7 @@
         <v>863</v>
       </c>
       <c r="B864" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="865" spans="1:2">
@@ -9995,7 +10001,7 @@
         <v>864</v>
       </c>
       <c r="B865" s="1">
-        <v>1040</v>
+        <v>920</v>
       </c>
     </row>
     <row r="866" spans="1:2">
@@ -10003,7 +10009,7 @@
         <v>865</v>
       </c>
       <c r="B866" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="867" spans="1:2">
@@ -10011,7 +10017,7 @@
         <v>866</v>
       </c>
       <c r="B867" s="1">
-        <v>940</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="868" spans="1:2">
@@ -10019,7 +10025,7 @@
         <v>867</v>
       </c>
       <c r="B868" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="869" spans="1:2">
@@ -10027,7 +10033,7 @@
         <v>868</v>
       </c>
       <c r="B869" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="870" spans="1:2">
@@ -10035,7 +10041,7 @@
         <v>869</v>
       </c>
       <c r="B870" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="871" spans="1:2">
@@ -10043,7 +10049,7 @@
         <v>870</v>
       </c>
       <c r="B871" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="872" spans="1:2">
@@ -10051,7 +10057,7 @@
         <v>871</v>
       </c>
       <c r="B872" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="873" spans="1:2">
@@ -10059,7 +10065,7 @@
         <v>872</v>
       </c>
       <c r="B873" s="1">
-        <v>960</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="874" spans="1:2">
@@ -10067,7 +10073,7 @@
         <v>873</v>
       </c>
       <c r="B874" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="875" spans="1:2">
@@ -10075,7 +10081,7 @@
         <v>874</v>
       </c>
       <c r="B875" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="876" spans="1:2">
@@ -10083,7 +10089,7 @@
         <v>875</v>
       </c>
       <c r="B876" s="1">
-        <v>820</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="877" spans="1:2">
@@ -10091,7 +10097,7 @@
         <v>876</v>
       </c>
       <c r="B877" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="878" spans="1:2">
@@ -10099,7 +10105,7 @@
         <v>877</v>
       </c>
       <c r="B878" s="1">
-        <v>500</v>
+        <v>820</v>
       </c>
     </row>
     <row r="879" spans="1:2">
@@ -10115,7 +10121,7 @@
         <v>879</v>
       </c>
       <c r="B880" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="881" spans="1:2">
@@ -10123,7 +10129,7 @@
         <v>880</v>
       </c>
       <c r="B881" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="882" spans="1:2">
@@ -10131,7 +10137,7 @@
         <v>881</v>
       </c>
       <c r="B882" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="883" spans="1:2">
@@ -10139,7 +10145,7 @@
         <v>882</v>
       </c>
       <c r="B883" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="884" spans="1:2">
@@ -10147,7 +10153,7 @@
         <v>883</v>
       </c>
       <c r="B884" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="885" spans="1:2">
@@ -10163,7 +10169,7 @@
         <v>885</v>
       </c>
       <c r="B886" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="887" spans="1:2">
@@ -10171,7 +10177,7 @@
         <v>886</v>
       </c>
       <c r="B887" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="888" spans="1:2">
@@ -10187,7 +10193,7 @@
         <v>888</v>
       </c>
       <c r="B889" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="890" spans="1:2">
@@ -10195,7 +10201,7 @@
         <v>889</v>
       </c>
       <c r="B890" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="891" spans="1:2">
@@ -10203,7 +10209,7 @@
         <v>890</v>
       </c>
       <c r="B891" s="1">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="892" spans="1:2">
@@ -10211,7 +10217,7 @@
         <v>891</v>
       </c>
       <c r="B892" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="893" spans="1:2">
@@ -10219,7 +10225,7 @@
         <v>892</v>
       </c>
       <c r="B893" s="1">
-        <v>600</v>
+        <v>440</v>
       </c>
     </row>
     <row r="894" spans="1:2">
@@ -10227,7 +10233,7 @@
         <v>893</v>
       </c>
       <c r="B894" s="1">
-        <v>820</v>
+        <v>380</v>
       </c>
     </row>
     <row r="895" spans="1:2">
@@ -10235,7 +10241,7 @@
         <v>894</v>
       </c>
       <c r="B895" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="896" spans="1:2">
@@ -10243,7 +10249,7 @@
         <v>895</v>
       </c>
       <c r="B896" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="897" spans="1:2">
@@ -10251,7 +10257,7 @@
         <v>896</v>
       </c>
       <c r="B897" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="898" spans="1:2">
@@ -10267,7 +10273,7 @@
         <v>898</v>
       </c>
       <c r="B899" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="900" spans="1:2">
@@ -10275,7 +10281,7 @@
         <v>899</v>
       </c>
       <c r="B900" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="901" spans="1:2">
@@ -10283,6 +10289,22 @@
         <v>900</v>
       </c>
       <c r="B901" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="902" spans="1:2">
+      <c r="A902" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="B902" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="903" spans="1:2">
+      <c r="A903" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="B903" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -2474,10 +2474,10 @@
     <t>вынос_Осьминогец - Ванна Мотуеки (NEIPA),  Розлив, Россия</t>
   </si>
   <si>
-    <t>вынос_Осьминогец - Делирий (Strong Fruit Beer),  Розлив, Россия</t>
-  </si>
-  <si>
-    <t>вынос_Осьминогец - Делирий Красный (Fruit Beer),  Розлив, Россия</t>
+    <t>вынос_Осьминогец - Делирий (Fruit Beer),  Розлив, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Осьминогец - Делирий Красный (Strong Fruit Beer),  Розлив, Россия</t>
   </si>
   <si>
     <t>вынос_Осьминогец - Ежевичный Джип (Fruit Gose),  Розлив, Россия</t>
@@ -2615,10 +2615,10 @@
     <t>Осьминогец - Ванна Мотуеки (NEIPA),  Розлив, Россия</t>
   </si>
   <si>
-    <t>Осьминогец - Делирий (Strong Fruit Beer),  Розлив, Россия</t>
-  </si>
-  <si>
-    <t>Осьминогец - Делирий Красный (Fruit Beer),  Розлив, Россия</t>
+    <t>Осьминогец - Делирий (Fruit Beer),  Розлив, Россия</t>
+  </si>
+  <si>
+    <t>Осьминогец - Делирий Красный (Strong Fruit Beer),  Розлив, Россия</t>
   </si>
   <si>
     <t>Осьминогец - Ежевичный Джип (Fruit Gose),  Розлив, Россия</t>
@@ -9641,7 +9641,7 @@
         <v>819</v>
       </c>
       <c r="B820" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="821" spans="1:2">
@@ -9649,7 +9649,7 @@
         <v>820</v>
       </c>
       <c r="B821" s="1">
-        <v>940</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="822" spans="1:2">
@@ -10017,7 +10017,7 @@
         <v>866</v>
       </c>
       <c r="B867" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="868" spans="1:2">
@@ -10025,7 +10025,7 @@
         <v>867</v>
       </c>
       <c r="B868" s="1">
-        <v>940</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="869" spans="1:2">

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="903">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="905">
   <si>
     <t>Наименование</t>
   </si>
@@ -605,6 +605,9 @@
     <t>Midnight Project - Just: Hefeweisse, РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Midnight Project - Red Alert (American Red Ale), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Midnight Project - Staying Safe in the Summer Heat, РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1884,6 +1887,9 @@
   </si>
   <si>
     <t>вынос_Midnight Project - Just: Hefeweisse, РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Midnight Project - Red Alert (American Red Ale), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_Midnight Project - Zhigulikeller (IPL), РОЗЛИВ, Россия</t>
@@ -3077,7 +3083,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B903"/>
+  <dimension ref="A1:B905"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -3705,7 +3711,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -3713,7 +3719,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -4657,7 +4663,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4665,7 +4671,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4673,7 +4679,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4681,7 +4687,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4689,7 +4695,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="1">
-        <v>980</v>
+        <v>700</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4697,7 +4703,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="1">
-        <v>460</v>
+        <v>980</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4705,7 +4711,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4713,7 +4719,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="1">
-        <v>720</v>
+        <v>580</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4721,7 +4727,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4729,7 +4735,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4737,7 +4743,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="1">
-        <v>260</v>
+        <v>780</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4753,7 +4759,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4769,7 +4775,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4777,7 +4783,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4785,7 +4791,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4793,7 +4799,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="1">
-        <v>500</v>
+        <v>760</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4801,7 +4807,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4809,7 +4815,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="1">
-        <v>740</v>
+        <v>400</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4817,7 +4823,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4825,7 +4831,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4833,7 +4839,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4841,7 +4847,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4849,7 +4855,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4857,7 +4863,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4873,7 +4879,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4881,7 +4887,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4889,7 +4895,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4897,7 +4903,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4905,7 +4911,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="1">
-        <v>580</v>
+        <v>860</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4913,7 +4919,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4921,7 +4927,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="1">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4929,7 +4935,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4937,7 +4943,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4945,7 +4951,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4953,7 +4959,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4961,7 +4967,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4969,7 +4975,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4977,7 +4983,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4985,7 +4991,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4993,7 +4999,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -5001,7 +5007,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="1">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -5009,7 +5015,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="1">
-        <v>480</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -5017,7 +5023,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -5025,7 +5031,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -5033,7 +5039,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -5041,7 +5047,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -5049,7 +5055,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -5057,7 +5063,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -5065,7 +5071,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -5073,7 +5079,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -5081,7 +5087,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="1">
-        <v>900</v>
+        <v>520</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -5089,7 +5095,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -5097,7 +5103,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -5105,7 +5111,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -5113,7 +5119,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -5129,7 +5135,7 @@
         <v>255</v>
       </c>
       <c r="B256" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -5145,7 +5151,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -5153,7 +5159,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -5161,7 +5167,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -5169,7 +5175,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -5177,7 +5183,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -5185,7 +5191,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -5193,7 +5199,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="1">
-        <v>960</v>
+        <v>840</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -5201,7 +5207,7 @@
         <v>264</v>
       </c>
       <c r="B265" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -5217,7 +5223,7 @@
         <v>266</v>
       </c>
       <c r="B267" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -5225,7 +5231,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -5233,7 +5239,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -5241,7 +5247,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -5249,7 +5255,7 @@
         <v>270</v>
       </c>
       <c r="B271" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -5257,7 +5263,7 @@
         <v>271</v>
       </c>
       <c r="B272" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -5273,7 +5279,7 @@
         <v>273</v>
       </c>
       <c r="B274" s="1">
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -5281,7 +5287,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -5289,7 +5295,7 @@
         <v>275</v>
       </c>
       <c r="B276" s="1">
-        <v>758</v>
+        <v>500</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -5297,7 +5303,7 @@
         <v>276</v>
       </c>
       <c r="B277" s="1">
-        <v>2273</v>
+        <v>758</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -5305,7 +5311,7 @@
         <v>277</v>
       </c>
       <c r="B278" s="1">
-        <v>1515</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -5313,7 +5319,7 @@
         <v>278</v>
       </c>
       <c r="B279" s="1">
-        <v>520</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -5321,7 +5327,7 @@
         <v>279</v>
       </c>
       <c r="B280" s="1">
-        <v>4000</v>
+        <v>520</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -5329,7 +5335,7 @@
         <v>280</v>
       </c>
       <c r="B281" s="1">
-        <v>560</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -5337,7 +5343,7 @@
         <v>281</v>
       </c>
       <c r="B282" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -5345,7 +5351,7 @@
         <v>282</v>
       </c>
       <c r="B283" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -5361,7 +5367,7 @@
         <v>284</v>
       </c>
       <c r="B285" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -5369,7 +5375,7 @@
         <v>285</v>
       </c>
       <c r="B286" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5377,7 +5383,7 @@
         <v>286</v>
       </c>
       <c r="B287" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5385,7 +5391,7 @@
         <v>287</v>
       </c>
       <c r="B288" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5393,7 +5399,7 @@
         <v>288</v>
       </c>
       <c r="B289" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5401,7 +5407,7 @@
         <v>289</v>
       </c>
       <c r="B290" s="1">
-        <v>680</v>
+        <v>520</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5409,7 +5415,7 @@
         <v>290</v>
       </c>
       <c r="B291" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5417,7 +5423,7 @@
         <v>291</v>
       </c>
       <c r="B292" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5425,7 +5431,7 @@
         <v>292</v>
       </c>
       <c r="B293" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5433,7 +5439,7 @@
         <v>293</v>
       </c>
       <c r="B294" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5441,7 +5447,7 @@
         <v>294</v>
       </c>
       <c r="B295" s="1">
-        <v>660</v>
+        <v>380</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5449,7 +5455,7 @@
         <v>295</v>
       </c>
       <c r="B296" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5457,7 +5463,7 @@
         <v>296</v>
       </c>
       <c r="B297" s="1">
-        <v>540</v>
+        <v>900</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5465,7 +5471,7 @@
         <v>297</v>
       </c>
       <c r="B298" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5473,7 +5479,7 @@
         <v>298</v>
       </c>
       <c r="B299" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5481,7 +5487,7 @@
         <v>299</v>
       </c>
       <c r="B300" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5489,7 +5495,7 @@
         <v>300</v>
       </c>
       <c r="B301" s="1">
-        <v>460</v>
+        <v>580</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5497,7 +5503,7 @@
         <v>301</v>
       </c>
       <c r="B302" s="1">
-        <v>520</v>
+        <v>460</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5505,7 +5511,7 @@
         <v>302</v>
       </c>
       <c r="B303" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5513,7 +5519,7 @@
         <v>303</v>
       </c>
       <c r="B304" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5521,7 +5527,7 @@
         <v>304</v>
       </c>
       <c r="B305" s="1">
-        <v>860</v>
+        <v>900</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5529,7 +5535,7 @@
         <v>305</v>
       </c>
       <c r="B306" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5553,7 +5559,7 @@
         <v>308</v>
       </c>
       <c r="B309" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5569,7 +5575,7 @@
         <v>310</v>
       </c>
       <c r="B311" s="1">
-        <v>980</v>
+        <v>560</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5577,7 +5583,7 @@
         <v>311</v>
       </c>
       <c r="B312" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5593,7 +5599,7 @@
         <v>313</v>
       </c>
       <c r="B314" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5601,7 +5607,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5609,7 +5615,7 @@
         <v>315</v>
       </c>
       <c r="B316" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5617,7 +5623,7 @@
         <v>316</v>
       </c>
       <c r="B317" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5625,7 +5631,7 @@
         <v>317</v>
       </c>
       <c r="B318" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5633,7 +5639,7 @@
         <v>318</v>
       </c>
       <c r="B319" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5641,7 +5647,7 @@
         <v>319</v>
       </c>
       <c r="B320" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5649,7 +5655,7 @@
         <v>320</v>
       </c>
       <c r="B321" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5657,7 +5663,7 @@
         <v>321</v>
       </c>
       <c r="B322" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5665,7 +5671,7 @@
         <v>322</v>
       </c>
       <c r="B323" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5673,7 +5679,7 @@
         <v>323</v>
       </c>
       <c r="B324" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5681,7 +5687,7 @@
         <v>324</v>
       </c>
       <c r="B325" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5689,7 +5695,7 @@
         <v>325</v>
       </c>
       <c r="B326" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5697,7 +5703,7 @@
         <v>326</v>
       </c>
       <c r="B327" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5705,7 +5711,7 @@
         <v>327</v>
       </c>
       <c r="B328" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5713,7 +5719,7 @@
         <v>328</v>
       </c>
       <c r="B329" s="1">
-        <v>520</v>
+        <v>680</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5721,7 +5727,7 @@
         <v>329</v>
       </c>
       <c r="B330" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5729,7 +5735,7 @@
         <v>330</v>
       </c>
       <c r="B331" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5737,7 +5743,7 @@
         <v>331</v>
       </c>
       <c r="B332" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5745,7 +5751,7 @@
         <v>332</v>
       </c>
       <c r="B333" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5753,7 +5759,7 @@
         <v>333</v>
       </c>
       <c r="B334" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5761,7 +5767,7 @@
         <v>334</v>
       </c>
       <c r="B335" s="1">
-        <v>580</v>
+        <v>840</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5769,7 +5775,7 @@
         <v>335</v>
       </c>
       <c r="B336" s="1">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5777,7 +5783,7 @@
         <v>336</v>
       </c>
       <c r="B337" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5785,7 +5791,7 @@
         <v>337</v>
       </c>
       <c r="B338" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5793,7 +5799,7 @@
         <v>338</v>
       </c>
       <c r="B339" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5801,7 +5807,7 @@
         <v>339</v>
       </c>
       <c r="B340" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5809,7 +5815,7 @@
         <v>340</v>
       </c>
       <c r="B341" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5817,7 +5823,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="1">
-        <v>1000</v>
+        <v>880</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5825,7 +5831,7 @@
         <v>342</v>
       </c>
       <c r="B343" s="1">
-        <v>520</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5833,7 +5839,7 @@
         <v>343</v>
       </c>
       <c r="B344" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5841,7 +5847,7 @@
         <v>344</v>
       </c>
       <c r="B345" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5849,7 +5855,7 @@
         <v>345</v>
       </c>
       <c r="B346" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5857,7 +5863,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5865,7 +5871,7 @@
         <v>347</v>
       </c>
       <c r="B348" s="1">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5873,7 +5879,7 @@
         <v>348</v>
       </c>
       <c r="B349" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5881,7 +5887,7 @@
         <v>349</v>
       </c>
       <c r="B350" s="1">
-        <v>320</v>
+        <v>520</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5889,7 +5895,7 @@
         <v>350</v>
       </c>
       <c r="B351" s="1">
-        <v>540</v>
+        <v>320</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5897,7 +5903,7 @@
         <v>351</v>
       </c>
       <c r="B352" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5905,7 +5911,7 @@
         <v>352</v>
       </c>
       <c r="B353" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5921,7 +5927,7 @@
         <v>354</v>
       </c>
       <c r="B355" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5929,7 +5935,7 @@
         <v>355</v>
       </c>
       <c r="B356" s="1">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5937,7 +5943,7 @@
         <v>356</v>
       </c>
       <c r="B357" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5945,7 +5951,7 @@
         <v>357</v>
       </c>
       <c r="B358" s="1">
-        <v>480</v>
+        <v>800</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5953,7 +5959,7 @@
         <v>358</v>
       </c>
       <c r="B359" s="1">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5961,7 +5967,7 @@
         <v>359</v>
       </c>
       <c r="B360" s="1">
-        <v>520</v>
+        <v>800</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5969,7 +5975,7 @@
         <v>360</v>
       </c>
       <c r="B361" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5977,7 +5983,7 @@
         <v>361</v>
       </c>
       <c r="B362" s="1">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5985,7 +5991,7 @@
         <v>362</v>
       </c>
       <c r="B363" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -6001,7 +6007,7 @@
         <v>364</v>
       </c>
       <c r="B365" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -6017,7 +6023,7 @@
         <v>366</v>
       </c>
       <c r="B367" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -6025,7 +6031,7 @@
         <v>367</v>
       </c>
       <c r="B368" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -6033,7 +6039,7 @@
         <v>368</v>
       </c>
       <c r="B369" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -6041,7 +6047,7 @@
         <v>369</v>
       </c>
       <c r="B370" s="1">
-        <v>880</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -6049,7 +6055,7 @@
         <v>370</v>
       </c>
       <c r="B371" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -6057,7 +6063,7 @@
         <v>371</v>
       </c>
       <c r="B372" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -6065,7 +6071,7 @@
         <v>372</v>
       </c>
       <c r="B373" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -6073,7 +6079,7 @@
         <v>373</v>
       </c>
       <c r="B374" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -6081,7 +6087,7 @@
         <v>374</v>
       </c>
       <c r="B375" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -6089,7 +6095,7 @@
         <v>375</v>
       </c>
       <c r="B376" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -6097,7 +6103,7 @@
         <v>376</v>
       </c>
       <c r="B377" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -6105,7 +6111,7 @@
         <v>377</v>
       </c>
       <c r="B378" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -6121,7 +6127,7 @@
         <v>379</v>
       </c>
       <c r="B380" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -6137,7 +6143,7 @@
         <v>381</v>
       </c>
       <c r="B382" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -6145,7 +6151,7 @@
         <v>382</v>
       </c>
       <c r="B383" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -6153,7 +6159,7 @@
         <v>383</v>
       </c>
       <c r="B384" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -6161,7 +6167,7 @@
         <v>384</v>
       </c>
       <c r="B385" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -6169,7 +6175,7 @@
         <v>385</v>
       </c>
       <c r="B386" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -6177,7 +6183,7 @@
         <v>386</v>
       </c>
       <c r="B387" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -6185,7 +6191,7 @@
         <v>387</v>
       </c>
       <c r="B388" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -6193,7 +6199,7 @@
         <v>388</v>
       </c>
       <c r="B389" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -6201,7 +6207,7 @@
         <v>389</v>
       </c>
       <c r="B390" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -6209,7 +6215,7 @@
         <v>390</v>
       </c>
       <c r="B391" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -6217,7 +6223,7 @@
         <v>391</v>
       </c>
       <c r="B392" s="1">
-        <v>640</v>
+        <v>480</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -6225,7 +6231,7 @@
         <v>392</v>
       </c>
       <c r="B393" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -6233,7 +6239,7 @@
         <v>393</v>
       </c>
       <c r="B394" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -6241,7 +6247,7 @@
         <v>394</v>
       </c>
       <c r="B395" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -6249,7 +6255,7 @@
         <v>395</v>
       </c>
       <c r="B396" s="1">
-        <v>520</v>
+        <v>860</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -6257,7 +6263,7 @@
         <v>396</v>
       </c>
       <c r="B397" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -6265,7 +6271,7 @@
         <v>397</v>
       </c>
       <c r="B398" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -6281,7 +6287,7 @@
         <v>399</v>
       </c>
       <c r="B400" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -6289,7 +6295,7 @@
         <v>400</v>
       </c>
       <c r="B401" s="1">
-        <v>700</v>
+        <v>420</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -6297,7 +6303,7 @@
         <v>401</v>
       </c>
       <c r="B402" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -6305,7 +6311,7 @@
         <v>402</v>
       </c>
       <c r="B403" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -6313,7 +6319,7 @@
         <v>403</v>
       </c>
       <c r="B404" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -6321,7 +6327,7 @@
         <v>404</v>
       </c>
       <c r="B405" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -6329,7 +6335,7 @@
         <v>405</v>
       </c>
       <c r="B406" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -6337,7 +6343,7 @@
         <v>406</v>
       </c>
       <c r="B407" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -6345,7 +6351,7 @@
         <v>407</v>
       </c>
       <c r="B408" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -6353,7 +6359,7 @@
         <v>408</v>
       </c>
       <c r="B409" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -6361,7 +6367,7 @@
         <v>409</v>
       </c>
       <c r="B410" s="1">
-        <v>440</v>
+        <v>620</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -6369,7 +6375,7 @@
         <v>410</v>
       </c>
       <c r="B411" s="1">
-        <v>1100</v>
+        <v>440</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -6385,7 +6391,7 @@
         <v>412</v>
       </c>
       <c r="B413" s="1">
-        <v>320</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -6393,7 +6399,7 @@
         <v>413</v>
       </c>
       <c r="B414" s="1">
-        <v>940</v>
+        <v>320</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -6401,7 +6407,7 @@
         <v>414</v>
       </c>
       <c r="B415" s="1">
-        <v>320</v>
+        <v>940</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -6409,7 +6415,7 @@
         <v>415</v>
       </c>
       <c r="B416" s="1">
-        <v>960</v>
+        <v>320</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -6417,7 +6423,7 @@
         <v>416</v>
       </c>
       <c r="B417" s="1">
-        <v>820</v>
+        <v>960</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -6425,7 +6431,7 @@
         <v>417</v>
       </c>
       <c r="B418" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -6433,7 +6439,7 @@
         <v>418</v>
       </c>
       <c r="B419" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -6449,7 +6455,7 @@
         <v>420</v>
       </c>
       <c r="B421" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -6457,7 +6463,7 @@
         <v>421</v>
       </c>
       <c r="B422" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -6473,7 +6479,7 @@
         <v>423</v>
       </c>
       <c r="B424" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -6481,7 +6487,7 @@
         <v>424</v>
       </c>
       <c r="B425" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -6489,7 +6495,7 @@
         <v>425</v>
       </c>
       <c r="B426" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -6497,7 +6503,7 @@
         <v>426</v>
       </c>
       <c r="B427" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -6505,7 +6511,7 @@
         <v>427</v>
       </c>
       <c r="B428" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6513,7 +6519,7 @@
         <v>428</v>
       </c>
       <c r="B429" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6521,7 +6527,7 @@
         <v>429</v>
       </c>
       <c r="B430" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6537,7 +6543,7 @@
         <v>431</v>
       </c>
       <c r="B432" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6545,7 +6551,7 @@
         <v>432</v>
       </c>
       <c r="B433" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6553,7 +6559,7 @@
         <v>433</v>
       </c>
       <c r="B434" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6561,7 +6567,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6569,7 +6575,7 @@
         <v>435</v>
       </c>
       <c r="B436" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6577,7 +6583,7 @@
         <v>436</v>
       </c>
       <c r="B437" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6585,7 +6591,7 @@
         <v>437</v>
       </c>
       <c r="B438" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6593,7 +6599,7 @@
         <v>438</v>
       </c>
       <c r="B439" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6601,7 +6607,7 @@
         <v>439</v>
       </c>
       <c r="B440" s="1">
-        <v>700</v>
+        <v>440</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6609,7 +6615,7 @@
         <v>440</v>
       </c>
       <c r="B441" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6625,7 +6631,7 @@
         <v>442</v>
       </c>
       <c r="B443" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6633,7 +6639,7 @@
         <v>443</v>
       </c>
       <c r="B444" s="1">
-        <v>560</v>
+        <v>800</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6641,7 +6647,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6649,7 +6655,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6657,7 +6663,7 @@
         <v>446</v>
       </c>
       <c r="B447" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6665,7 +6671,7 @@
         <v>447</v>
       </c>
       <c r="B448" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6673,7 +6679,7 @@
         <v>448</v>
       </c>
       <c r="B449" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6681,7 +6687,7 @@
         <v>449</v>
       </c>
       <c r="B450" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6689,7 +6695,7 @@
         <v>450</v>
       </c>
       <c r="B451" s="1">
-        <v>720</v>
+        <v>620</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6697,7 +6703,7 @@
         <v>451</v>
       </c>
       <c r="B452" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6705,7 +6711,7 @@
         <v>452</v>
       </c>
       <c r="B453" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6721,7 +6727,7 @@
         <v>454</v>
       </c>
       <c r="B455" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6729,7 +6735,7 @@
         <v>455</v>
       </c>
       <c r="B456" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6737,7 +6743,7 @@
         <v>456</v>
       </c>
       <c r="B457" s="1">
-        <v>900</v>
+        <v>880</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6745,7 +6751,7 @@
         <v>457</v>
       </c>
       <c r="B458" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6753,7 +6759,7 @@
         <v>458</v>
       </c>
       <c r="B459" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6761,7 +6767,7 @@
         <v>459</v>
       </c>
       <c r="B460" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6769,7 +6775,7 @@
         <v>460</v>
       </c>
       <c r="B461" s="1">
-        <v>800</v>
+        <v>920</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6777,7 +6783,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6785,7 +6791,7 @@
         <v>462</v>
       </c>
       <c r="B463" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6793,7 +6799,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="1">
-        <v>980</v>
+        <v>940</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6801,7 +6807,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6809,7 +6815,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6817,7 +6823,7 @@
         <v>466</v>
       </c>
       <c r="B467" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6825,7 +6831,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6833,7 +6839,7 @@
         <v>468</v>
       </c>
       <c r="B469" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6849,7 +6855,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6857,7 +6863,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6865,7 +6871,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="1">
-        <v>640</v>
+        <v>920</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6873,7 +6879,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6881,7 +6887,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6889,7 +6895,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="1">
-        <v>960</v>
+        <v>820</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6897,7 +6903,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6905,7 +6911,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6913,7 +6919,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6921,7 +6927,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="1">
-        <v>860</v>
+        <v>640</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6929,7 +6935,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6937,7 +6943,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6945,7 +6951,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6953,7 +6959,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6961,7 +6967,7 @@
         <v>484</v>
       </c>
       <c r="B485" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6969,7 +6975,7 @@
         <v>485</v>
       </c>
       <c r="B486" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6977,7 +6983,7 @@
         <v>486</v>
       </c>
       <c r="B487" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6985,7 +6991,7 @@
         <v>487</v>
       </c>
       <c r="B488" s="1">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6993,7 +6999,7 @@
         <v>488</v>
       </c>
       <c r="B489" s="1">
-        <v>620</v>
+        <v>480</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -7001,7 +7007,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -7009,7 +7015,7 @@
         <v>490</v>
       </c>
       <c r="B491" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -7017,7 +7023,7 @@
         <v>491</v>
       </c>
       <c r="B492" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -7025,7 +7031,7 @@
         <v>492</v>
       </c>
       <c r="B493" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -7033,7 +7039,7 @@
         <v>493</v>
       </c>
       <c r="B494" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -7041,7 +7047,7 @@
         <v>494</v>
       </c>
       <c r="B495" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -7049,7 +7055,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -7057,7 +7063,7 @@
         <v>496</v>
       </c>
       <c r="B497" s="1">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -7065,7 +7071,7 @@
         <v>497</v>
       </c>
       <c r="B498" s="1">
-        <v>840</v>
+        <v>480</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -7073,7 +7079,7 @@
         <v>498</v>
       </c>
       <c r="B499" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -7081,7 +7087,7 @@
         <v>499</v>
       </c>
       <c r="B500" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -7089,7 +7095,7 @@
         <v>500</v>
       </c>
       <c r="B501" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -7105,7 +7111,7 @@
         <v>502</v>
       </c>
       <c r="B503" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -7113,7 +7119,7 @@
         <v>503</v>
       </c>
       <c r="B504" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -7121,7 +7127,7 @@
         <v>504</v>
       </c>
       <c r="B505" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -7129,7 +7135,7 @@
         <v>505</v>
       </c>
       <c r="B506" s="1">
-        <v>880</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -7145,7 +7151,7 @@
         <v>507</v>
       </c>
       <c r="B508" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -7153,7 +7159,7 @@
         <v>508</v>
       </c>
       <c r="B509" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -7161,7 +7167,7 @@
         <v>509</v>
       </c>
       <c r="B510" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -7169,7 +7175,7 @@
         <v>510</v>
       </c>
       <c r="B511" s="1">
-        <v>1100</v>
+        <v>660</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -7177,7 +7183,7 @@
         <v>511</v>
       </c>
       <c r="B512" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -7185,7 +7191,7 @@
         <v>512</v>
       </c>
       <c r="B513" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -7193,7 +7199,7 @@
         <v>513</v>
       </c>
       <c r="B514" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -7201,7 +7207,7 @@
         <v>514</v>
       </c>
       <c r="B515" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -7209,7 +7215,7 @@
         <v>515</v>
       </c>
       <c r="B516" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -7225,7 +7231,7 @@
         <v>517</v>
       </c>
       <c r="B518" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -7233,7 +7239,7 @@
         <v>518</v>
       </c>
       <c r="B519" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -7241,7 +7247,7 @@
         <v>519</v>
       </c>
       <c r="B520" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -7249,7 +7255,7 @@
         <v>520</v>
       </c>
       <c r="B521" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -7257,7 +7263,7 @@
         <v>521</v>
       </c>
       <c r="B522" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -7265,7 +7271,7 @@
         <v>522</v>
       </c>
       <c r="B523" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -7281,7 +7287,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -7289,7 +7295,7 @@
         <v>525</v>
       </c>
       <c r="B526" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -7297,7 +7303,7 @@
         <v>526</v>
       </c>
       <c r="B527" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -7305,7 +7311,7 @@
         <v>527</v>
       </c>
       <c r="B528" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -7313,7 +7319,7 @@
         <v>528</v>
       </c>
       <c r="B529" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -7321,7 +7327,7 @@
         <v>529</v>
       </c>
       <c r="B530" s="1">
-        <v>840</v>
+        <v>620</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -7329,7 +7335,7 @@
         <v>530</v>
       </c>
       <c r="B531" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -7337,7 +7343,7 @@
         <v>531</v>
       </c>
       <c r="B532" s="1">
-        <v>1060</v>
+        <v>880</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -7345,7 +7351,7 @@
         <v>532</v>
       </c>
       <c r="B533" s="1">
-        <v>860</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -7361,7 +7367,7 @@
         <v>534</v>
       </c>
       <c r="B535" s="1">
-        <v>800</v>
+        <v>860</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -7369,7 +7375,7 @@
         <v>535</v>
       </c>
       <c r="B536" s="1">
-        <v>860</v>
+        <v>800</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -7377,7 +7383,7 @@
         <v>536</v>
       </c>
       <c r="B537" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -7385,7 +7391,7 @@
         <v>537</v>
       </c>
       <c r="B538" s="1">
-        <v>760</v>
+        <v>960</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -7393,7 +7399,7 @@
         <v>538</v>
       </c>
       <c r="B539" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -7401,7 +7407,7 @@
         <v>539</v>
       </c>
       <c r="B540" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -7409,7 +7415,7 @@
         <v>540</v>
       </c>
       <c r="B541" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -7425,7 +7431,7 @@
         <v>542</v>
       </c>
       <c r="B543" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -7433,7 +7439,7 @@
         <v>543</v>
       </c>
       <c r="B544" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -7441,7 +7447,7 @@
         <v>544</v>
       </c>
       <c r="B545" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -7457,7 +7463,7 @@
         <v>546</v>
       </c>
       <c r="B547" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -7465,7 +7471,7 @@
         <v>547</v>
       </c>
       <c r="B548" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -7473,7 +7479,7 @@
         <v>548</v>
       </c>
       <c r="B549" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -7481,7 +7487,7 @@
         <v>549</v>
       </c>
       <c r="B550" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -7489,7 +7495,7 @@
         <v>550</v>
       </c>
       <c r="B551" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -7497,7 +7503,7 @@
         <v>551</v>
       </c>
       <c r="B552" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7505,7 +7511,7 @@
         <v>552</v>
       </c>
       <c r="B553" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7513,7 +7519,7 @@
         <v>553</v>
       </c>
       <c r="B554" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7521,7 +7527,7 @@
         <v>554</v>
       </c>
       <c r="B555" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7537,7 +7543,7 @@
         <v>556</v>
       </c>
       <c r="B557" s="1">
-        <v>880</v>
+        <v>700</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7545,7 +7551,7 @@
         <v>557</v>
       </c>
       <c r="B558" s="1">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7553,7 +7559,7 @@
         <v>558</v>
       </c>
       <c r="B559" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7561,7 +7567,7 @@
         <v>559</v>
       </c>
       <c r="B560" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7569,7 +7575,7 @@
         <v>560</v>
       </c>
       <c r="B561" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7577,7 +7583,7 @@
         <v>561</v>
       </c>
       <c r="B562" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7585,7 +7591,7 @@
         <v>562</v>
       </c>
       <c r="B563" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7593,7 +7599,7 @@
         <v>563</v>
       </c>
       <c r="B564" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7601,7 +7607,7 @@
         <v>564</v>
       </c>
       <c r="B565" s="1">
-        <v>640</v>
+        <v>880</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7609,7 +7615,7 @@
         <v>565</v>
       </c>
       <c r="B566" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7617,7 +7623,7 @@
         <v>566</v>
       </c>
       <c r="B567" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7625,7 +7631,7 @@
         <v>567</v>
       </c>
       <c r="B568" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7641,7 +7647,7 @@
         <v>569</v>
       </c>
       <c r="B570" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7649,7 +7655,7 @@
         <v>570</v>
       </c>
       <c r="B571" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7665,7 +7671,7 @@
         <v>572</v>
       </c>
       <c r="B573" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7673,7 +7679,7 @@
         <v>573</v>
       </c>
       <c r="B574" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7681,7 +7687,7 @@
         <v>574</v>
       </c>
       <c r="B575" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7689,7 +7695,7 @@
         <v>575</v>
       </c>
       <c r="B576" s="1">
-        <v>940</v>
+        <v>960</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7697,7 +7703,7 @@
         <v>576</v>
       </c>
       <c r="B577" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7713,7 +7719,7 @@
         <v>578</v>
       </c>
       <c r="B579" s="1">
-        <v>940</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7721,7 +7727,7 @@
         <v>579</v>
       </c>
       <c r="B580" s="1">
-        <v>860</v>
+        <v>940</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7729,7 +7735,7 @@
         <v>580</v>
       </c>
       <c r="B581" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7737,7 +7743,7 @@
         <v>581</v>
       </c>
       <c r="B582" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7745,7 +7751,7 @@
         <v>582</v>
       </c>
       <c r="B583" s="1">
-        <v>960</v>
+        <v>920</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7753,7 +7759,7 @@
         <v>583</v>
       </c>
       <c r="B584" s="1">
-        <v>680</v>
+        <v>960</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7761,7 +7767,7 @@
         <v>584</v>
       </c>
       <c r="B585" s="1">
-        <v>840</v>
+        <v>680</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7769,7 +7775,7 @@
         <v>585</v>
       </c>
       <c r="B586" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7777,7 +7783,7 @@
         <v>586</v>
       </c>
       <c r="B587" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7785,7 +7791,7 @@
         <v>587</v>
       </c>
       <c r="B588" s="1">
-        <v>580</v>
+        <v>880</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7793,7 +7799,7 @@
         <v>588</v>
       </c>
       <c r="B589" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7801,7 +7807,7 @@
         <v>589</v>
       </c>
       <c r="B590" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7809,7 +7815,7 @@
         <v>590</v>
       </c>
       <c r="B591" s="1">
-        <v>620</v>
+        <v>860</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7817,7 +7823,7 @@
         <v>591</v>
       </c>
       <c r="B592" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7825,7 +7831,7 @@
         <v>592</v>
       </c>
       <c r="B593" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7833,7 +7839,7 @@
         <v>593</v>
       </c>
       <c r="B594" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7841,7 +7847,7 @@
         <v>594</v>
       </c>
       <c r="B595" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7849,7 +7855,7 @@
         <v>595</v>
       </c>
       <c r="B596" s="1">
-        <v>900</v>
+        <v>960</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7857,7 +7863,7 @@
         <v>596</v>
       </c>
       <c r="B597" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7865,7 +7871,7 @@
         <v>597</v>
       </c>
       <c r="B598" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7873,7 +7879,7 @@
         <v>598</v>
       </c>
       <c r="B599" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7881,7 +7887,7 @@
         <v>599</v>
       </c>
       <c r="B600" s="1">
-        <v>540</v>
+        <v>780</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7889,7 +7895,7 @@
         <v>600</v>
       </c>
       <c r="B601" s="1">
-        <v>1100</v>
+        <v>540</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7897,7 +7903,7 @@
         <v>601</v>
       </c>
       <c r="B602" s="1">
-        <v>1060</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7905,7 +7911,7 @@
         <v>602</v>
       </c>
       <c r="B603" s="1">
-        <v>1100</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7921,7 +7927,7 @@
         <v>604</v>
       </c>
       <c r="B605" s="1">
-        <v>1080</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7929,7 +7935,7 @@
         <v>605</v>
       </c>
       <c r="B606" s="1">
-        <v>840</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7945,7 +7951,7 @@
         <v>607</v>
       </c>
       <c r="B608" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7953,7 +7959,7 @@
         <v>608</v>
       </c>
       <c r="B609" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7961,7 +7967,7 @@
         <v>609</v>
       </c>
       <c r="B610" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7969,7 +7975,7 @@
         <v>610</v>
       </c>
       <c r="B611" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7977,7 +7983,7 @@
         <v>611</v>
       </c>
       <c r="B612" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7985,7 +7991,7 @@
         <v>612</v>
       </c>
       <c r="B613" s="1">
-        <v>980</v>
+        <v>860</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7993,7 +7999,7 @@
         <v>613</v>
       </c>
       <c r="B614" s="1">
-        <v>740</v>
+        <v>980</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -8001,7 +8007,7 @@
         <v>614</v>
       </c>
       <c r="B615" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -8009,7 +8015,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -8033,7 +8039,7 @@
         <v>618</v>
       </c>
       <c r="B619" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -8057,7 +8063,7 @@
         <v>621</v>
       </c>
       <c r="B622" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -8065,7 +8071,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -8073,7 +8079,7 @@
         <v>623</v>
       </c>
       <c r="B624" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -8081,7 +8087,7 @@
         <v>624</v>
       </c>
       <c r="B625" s="1">
-        <v>700</v>
+        <v>960</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -8089,7 +8095,7 @@
         <v>625</v>
       </c>
       <c r="B626" s="1">
-        <v>980</v>
+        <v>840</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -8097,7 +8103,7 @@
         <v>626</v>
       </c>
       <c r="B627" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -8105,7 +8111,7 @@
         <v>627</v>
       </c>
       <c r="B628" s="1">
-        <v>800</v>
+        <v>980</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -8113,7 +8119,7 @@
         <v>628</v>
       </c>
       <c r="B629" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -8121,7 +8127,7 @@
         <v>629</v>
       </c>
       <c r="B630" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -8137,7 +8143,7 @@
         <v>631</v>
       </c>
       <c r="B632" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -8145,7 +8151,7 @@
         <v>632</v>
       </c>
       <c r="B633" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -8161,7 +8167,7 @@
         <v>634</v>
       </c>
       <c r="B635" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -8169,7 +8175,7 @@
         <v>635</v>
       </c>
       <c r="B636" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -8177,7 +8183,7 @@
         <v>636</v>
       </c>
       <c r="B637" s="1">
-        <v>820</v>
+        <v>860</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -8185,7 +8191,7 @@
         <v>637</v>
       </c>
       <c r="B638" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -8193,7 +8199,7 @@
         <v>638</v>
       </c>
       <c r="B639" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -8201,7 +8207,7 @@
         <v>639</v>
       </c>
       <c r="B640" s="1">
-        <v>1400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -8217,7 +8223,7 @@
         <v>641</v>
       </c>
       <c r="B642" s="1">
-        <v>660</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -8225,7 +8231,7 @@
         <v>642</v>
       </c>
       <c r="B643" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -8233,7 +8239,7 @@
         <v>643</v>
       </c>
       <c r="B644" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -8241,7 +8247,7 @@
         <v>644</v>
       </c>
       <c r="B645" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -8249,7 +8255,7 @@
         <v>645</v>
       </c>
       <c r="B646" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -8257,7 +8263,7 @@
         <v>646</v>
       </c>
       <c r="B647" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -8265,7 +8271,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -8273,7 +8279,7 @@
         <v>648</v>
       </c>
       <c r="B649" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -8281,7 +8287,7 @@
         <v>649</v>
       </c>
       <c r="B650" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -8289,7 +8295,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -8297,7 +8303,7 @@
         <v>651</v>
       </c>
       <c r="B652" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -8305,7 +8311,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -8313,7 +8319,7 @@
         <v>653</v>
       </c>
       <c r="B654" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -8321,7 +8327,7 @@
         <v>654</v>
       </c>
       <c r="B655" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -8329,7 +8335,7 @@
         <v>655</v>
       </c>
       <c r="B656" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -8345,7 +8351,7 @@
         <v>657</v>
       </c>
       <c r="B658" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -8353,7 +8359,7 @@
         <v>658</v>
       </c>
       <c r="B659" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -8361,7 +8367,7 @@
         <v>659</v>
       </c>
       <c r="B660" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -8369,7 +8375,7 @@
         <v>660</v>
       </c>
       <c r="B661" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -8377,7 +8383,7 @@
         <v>661</v>
       </c>
       <c r="B662" s="1">
-        <v>4000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -8385,7 +8391,7 @@
         <v>662</v>
       </c>
       <c r="B663" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -8393,7 +8399,7 @@
         <v>663</v>
       </c>
       <c r="B664" s="1">
-        <v>720</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -8401,7 +8407,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -8409,7 +8415,7 @@
         <v>665</v>
       </c>
       <c r="B666" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -8417,7 +8423,7 @@
         <v>666</v>
       </c>
       <c r="B667" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -8425,7 +8431,7 @@
         <v>667</v>
       </c>
       <c r="B668" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -8433,7 +8439,7 @@
         <v>668</v>
       </c>
       <c r="B669" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -8441,7 +8447,7 @@
         <v>669</v>
       </c>
       <c r="B670" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -8449,7 +8455,7 @@
         <v>670</v>
       </c>
       <c r="B671" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -8457,7 +8463,7 @@
         <v>671</v>
       </c>
       <c r="B672" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -8465,7 +8471,7 @@
         <v>672</v>
       </c>
       <c r="B673" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -8473,7 +8479,7 @@
         <v>673</v>
       </c>
       <c r="B674" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -8481,7 +8487,7 @@
         <v>674</v>
       </c>
       <c r="B675" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8497,7 +8503,7 @@
         <v>676</v>
       </c>
       <c r="B677" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8513,7 +8519,7 @@
         <v>678</v>
       </c>
       <c r="B679" s="1">
-        <v>980</v>
+        <v>900</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8521,7 +8527,7 @@
         <v>679</v>
       </c>
       <c r="B680" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8529,7 +8535,7 @@
         <v>680</v>
       </c>
       <c r="B681" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8537,7 +8543,7 @@
         <v>681</v>
       </c>
       <c r="B682" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8545,7 +8551,7 @@
         <v>682</v>
       </c>
       <c r="B683" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8553,7 +8559,7 @@
         <v>683</v>
       </c>
       <c r="B684" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8561,7 +8567,7 @@
         <v>684</v>
       </c>
       <c r="B685" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8569,7 +8575,7 @@
         <v>685</v>
       </c>
       <c r="B686" s="1">
-        <v>860</v>
+        <v>680</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8585,7 +8591,7 @@
         <v>687</v>
       </c>
       <c r="B688" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8601,7 +8607,7 @@
         <v>689</v>
       </c>
       <c r="B690" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8609,7 +8615,7 @@
         <v>690</v>
       </c>
       <c r="B691" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8617,7 +8623,7 @@
         <v>691</v>
       </c>
       <c r="B692" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8625,7 +8631,7 @@
         <v>692</v>
       </c>
       <c r="B693" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8633,7 +8639,7 @@
         <v>693</v>
       </c>
       <c r="B694" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8641,7 +8647,7 @@
         <v>694</v>
       </c>
       <c r="B695" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8649,7 +8655,7 @@
         <v>695</v>
       </c>
       <c r="B696" s="1">
-        <v>840</v>
+        <v>800</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8657,7 +8663,7 @@
         <v>696</v>
       </c>
       <c r="B697" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8665,7 +8671,7 @@
         <v>697</v>
       </c>
       <c r="B698" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8673,7 +8679,7 @@
         <v>698</v>
       </c>
       <c r="B699" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8681,7 +8687,7 @@
         <v>699</v>
       </c>
       <c r="B700" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8697,7 +8703,7 @@
         <v>701</v>
       </c>
       <c r="B702" s="1">
-        <v>880</v>
+        <v>640</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8705,7 +8711,7 @@
         <v>702</v>
       </c>
       <c r="B703" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8713,7 +8719,7 @@
         <v>703</v>
       </c>
       <c r="B704" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8721,7 +8727,7 @@
         <v>704</v>
       </c>
       <c r="B705" s="1">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8729,7 +8735,7 @@
         <v>705</v>
       </c>
       <c r="B706" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8745,7 +8751,7 @@
         <v>707</v>
       </c>
       <c r="B708" s="1">
-        <v>800</v>
+        <v>820</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8753,7 +8759,7 @@
         <v>708</v>
       </c>
       <c r="B709" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8769,7 +8775,7 @@
         <v>710</v>
       </c>
       <c r="B711" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8777,7 +8783,7 @@
         <v>711</v>
       </c>
       <c r="B712" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8785,7 +8791,7 @@
         <v>712</v>
       </c>
       <c r="B713" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8793,7 +8799,7 @@
         <v>713</v>
       </c>
       <c r="B714" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8801,7 +8807,7 @@
         <v>714</v>
       </c>
       <c r="B715" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8809,7 +8815,7 @@
         <v>715</v>
       </c>
       <c r="B716" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8817,7 +8823,7 @@
         <v>716</v>
       </c>
       <c r="B717" s="1">
-        <v>880</v>
+        <v>960</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8825,7 +8831,7 @@
         <v>717</v>
       </c>
       <c r="B718" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8833,7 +8839,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8841,7 +8847,7 @@
         <v>719</v>
       </c>
       <c r="B720" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8849,7 +8855,7 @@
         <v>720</v>
       </c>
       <c r="B721" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8857,7 +8863,7 @@
         <v>721</v>
       </c>
       <c r="B722" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8865,7 +8871,7 @@
         <v>722</v>
       </c>
       <c r="B723" s="1">
-        <v>1020</v>
+        <v>640</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8881,7 +8887,7 @@
         <v>724</v>
       </c>
       <c r="B725" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8889,7 +8895,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8897,7 +8903,7 @@
         <v>726</v>
       </c>
       <c r="B727" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8905,7 +8911,7 @@
         <v>727</v>
       </c>
       <c r="B728" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8913,7 +8919,7 @@
         <v>728</v>
       </c>
       <c r="B729" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8921,7 +8927,7 @@
         <v>729</v>
       </c>
       <c r="B730" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8929,7 +8935,7 @@
         <v>730</v>
       </c>
       <c r="B731" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8945,7 +8951,7 @@
         <v>732</v>
       </c>
       <c r="B733" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -8953,7 +8959,7 @@
         <v>733</v>
       </c>
       <c r="B734" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -8961,7 +8967,7 @@
         <v>734</v>
       </c>
       <c r="B735" s="1">
-        <v>680</v>
+        <v>820</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -8969,7 +8975,7 @@
         <v>735</v>
       </c>
       <c r="B736" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -8977,7 +8983,7 @@
         <v>736</v>
       </c>
       <c r="B737" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -8985,7 +8991,7 @@
         <v>737</v>
       </c>
       <c r="B738" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="739" spans="1:2">
@@ -8993,7 +8999,7 @@
         <v>738</v>
       </c>
       <c r="B739" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="740" spans="1:2">
@@ -9001,7 +9007,7 @@
         <v>739</v>
       </c>
       <c r="B740" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -9017,7 +9023,7 @@
         <v>741</v>
       </c>
       <c r="B742" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -9025,7 +9031,7 @@
         <v>742</v>
       </c>
       <c r="B743" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="744" spans="1:2">
@@ -9033,7 +9039,7 @@
         <v>743</v>
       </c>
       <c r="B744" s="1">
-        <v>1100</v>
+        <v>840</v>
       </c>
     </row>
     <row r="745" spans="1:2">
@@ -9041,7 +9047,7 @@
         <v>744</v>
       </c>
       <c r="B745" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -9049,7 +9055,7 @@
         <v>745</v>
       </c>
       <c r="B746" s="1">
-        <v>940</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="747" spans="1:2">
@@ -9057,7 +9063,7 @@
         <v>746</v>
       </c>
       <c r="B747" s="1">
-        <v>820</v>
+        <v>940</v>
       </c>
     </row>
     <row r="748" spans="1:2">
@@ -9065,7 +9071,7 @@
         <v>747</v>
       </c>
       <c r="B748" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="749" spans="1:2">
@@ -9073,7 +9079,7 @@
         <v>748</v>
       </c>
       <c r="B749" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -9081,7 +9087,7 @@
         <v>749</v>
       </c>
       <c r="B750" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="751" spans="1:2">
@@ -9089,7 +9095,7 @@
         <v>750</v>
       </c>
       <c r="B751" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="752" spans="1:2">
@@ -9097,7 +9103,7 @@
         <v>751</v>
       </c>
       <c r="B752" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="753" spans="1:2">
@@ -9105,7 +9111,7 @@
         <v>752</v>
       </c>
       <c r="B753" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="754" spans="1:2">
@@ -9113,7 +9119,7 @@
         <v>753</v>
       </c>
       <c r="B754" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -9129,7 +9135,7 @@
         <v>755</v>
       </c>
       <c r="B756" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="757" spans="1:2">
@@ -9137,7 +9143,7 @@
         <v>756</v>
       </c>
       <c r="B757" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="758" spans="1:2">
@@ -9145,7 +9151,7 @@
         <v>757</v>
       </c>
       <c r="B758" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="759" spans="1:2">
@@ -9153,7 +9159,7 @@
         <v>758</v>
       </c>
       <c r="B759" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="760" spans="1:2">
@@ -9161,7 +9167,7 @@
         <v>759</v>
       </c>
       <c r="B760" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="761" spans="1:2">
@@ -9169,7 +9175,7 @@
         <v>760</v>
       </c>
       <c r="B761" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="762" spans="1:2">
@@ -9185,7 +9191,7 @@
         <v>762</v>
       </c>
       <c r="B763" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="764" spans="1:2">
@@ -9193,7 +9199,7 @@
         <v>763</v>
       </c>
       <c r="B764" s="1">
-        <v>440</v>
+        <v>900</v>
       </c>
     </row>
     <row r="765" spans="1:2">
@@ -9201,7 +9207,7 @@
         <v>764</v>
       </c>
       <c r="B765" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="766" spans="1:2">
@@ -9209,7 +9215,7 @@
         <v>765</v>
       </c>
       <c r="B766" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="767" spans="1:2">
@@ -9217,7 +9223,7 @@
         <v>766</v>
       </c>
       <c r="B767" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="768" spans="1:2">
@@ -9225,7 +9231,7 @@
         <v>767</v>
       </c>
       <c r="B768" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="769" spans="1:2">
@@ -9233,7 +9239,7 @@
         <v>768</v>
       </c>
       <c r="B769" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="770" spans="1:2">
@@ -9241,7 +9247,7 @@
         <v>769</v>
       </c>
       <c r="B770" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="771" spans="1:2">
@@ -9249,7 +9255,7 @@
         <v>770</v>
       </c>
       <c r="B771" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="772" spans="1:2">
@@ -9257,7 +9263,7 @@
         <v>771</v>
       </c>
       <c r="B772" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="773" spans="1:2">
@@ -9265,7 +9271,7 @@
         <v>772</v>
       </c>
       <c r="B773" s="1">
-        <v>880</v>
+        <v>560</v>
       </c>
     </row>
     <row r="774" spans="1:2">
@@ -9273,7 +9279,7 @@
         <v>773</v>
       </c>
       <c r="B774" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="775" spans="1:2">
@@ -9289,7 +9295,7 @@
         <v>775</v>
       </c>
       <c r="B776" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="777" spans="1:2">
@@ -9297,7 +9303,7 @@
         <v>776</v>
       </c>
       <c r="B777" s="1">
-        <v>920</v>
+        <v>880</v>
       </c>
     </row>
     <row r="778" spans="1:2">
@@ -9305,7 +9311,7 @@
         <v>777</v>
       </c>
       <c r="B778" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="779" spans="1:2">
@@ -9313,7 +9319,7 @@
         <v>778</v>
       </c>
       <c r="B779" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="780" spans="1:2">
@@ -9321,7 +9327,7 @@
         <v>779</v>
       </c>
       <c r="B780" s="1">
-        <v>980</v>
+        <v>800</v>
       </c>
     </row>
     <row r="781" spans="1:2">
@@ -9329,7 +9335,7 @@
         <v>780</v>
       </c>
       <c r="B781" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="782" spans="1:2">
@@ -9337,7 +9343,7 @@
         <v>781</v>
       </c>
       <c r="B782" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="783" spans="1:2">
@@ -9345,7 +9351,7 @@
         <v>782</v>
       </c>
       <c r="B783" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="784" spans="1:2">
@@ -9353,7 +9359,7 @@
         <v>783</v>
       </c>
       <c r="B784" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="785" spans="1:2">
@@ -9361,7 +9367,7 @@
         <v>784</v>
       </c>
       <c r="B785" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="786" spans="1:2">
@@ -9369,7 +9375,7 @@
         <v>785</v>
       </c>
       <c r="B786" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="787" spans="1:2">
@@ -9377,7 +9383,7 @@
         <v>786</v>
       </c>
       <c r="B787" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="788" spans="1:2">
@@ -9385,7 +9391,7 @@
         <v>787</v>
       </c>
       <c r="B788" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="789" spans="1:2">
@@ -9393,7 +9399,7 @@
         <v>788</v>
       </c>
       <c r="B789" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="790" spans="1:2">
@@ -9401,7 +9407,7 @@
         <v>789</v>
       </c>
       <c r="B790" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="791" spans="1:2">
@@ -9409,7 +9415,7 @@
         <v>790</v>
       </c>
       <c r="B791" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="792" spans="1:2">
@@ -9417,7 +9423,7 @@
         <v>791</v>
       </c>
       <c r="B792" s="1">
-        <v>660</v>
+        <v>860</v>
       </c>
     </row>
     <row r="793" spans="1:2">
@@ -9425,7 +9431,7 @@
         <v>792</v>
       </c>
       <c r="B793" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="794" spans="1:2">
@@ -9433,7 +9439,7 @@
         <v>793</v>
       </c>
       <c r="B794" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="795" spans="1:2">
@@ -9441,7 +9447,7 @@
         <v>794</v>
       </c>
       <c r="B795" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="796" spans="1:2">
@@ -9449,7 +9455,7 @@
         <v>795</v>
       </c>
       <c r="B796" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="797" spans="1:2">
@@ -9457,7 +9463,7 @@
         <v>796</v>
       </c>
       <c r="B797" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="798" spans="1:2">
@@ -9465,7 +9471,7 @@
         <v>797</v>
       </c>
       <c r="B798" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="799" spans="1:2">
@@ -9473,7 +9479,7 @@
         <v>798</v>
       </c>
       <c r="B799" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="800" spans="1:2">
@@ -9481,7 +9487,7 @@
         <v>799</v>
       </c>
       <c r="B800" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="801" spans="1:2">
@@ -9489,7 +9495,7 @@
         <v>800</v>
       </c>
       <c r="B801" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="802" spans="1:2">
@@ -9497,7 +9503,7 @@
         <v>801</v>
       </c>
       <c r="B802" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="803" spans="1:2">
@@ -9505,7 +9511,7 @@
         <v>802</v>
       </c>
       <c r="B803" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="804" spans="1:2">
@@ -9513,7 +9519,7 @@
         <v>803</v>
       </c>
       <c r="B804" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="805" spans="1:2">
@@ -9521,7 +9527,7 @@
         <v>804</v>
       </c>
       <c r="B805" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="806" spans="1:2">
@@ -9529,7 +9535,7 @@
         <v>805</v>
       </c>
       <c r="B806" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="807" spans="1:2">
@@ -9537,7 +9543,7 @@
         <v>806</v>
       </c>
       <c r="B807" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="808" spans="1:2">
@@ -9545,7 +9551,7 @@
         <v>807</v>
       </c>
       <c r="B808" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="809" spans="1:2">
@@ -9553,7 +9559,7 @@
         <v>808</v>
       </c>
       <c r="B809" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="810" spans="1:2">
@@ -9561,7 +9567,7 @@
         <v>809</v>
       </c>
       <c r="B810" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="811" spans="1:2">
@@ -9569,7 +9575,7 @@
         <v>810</v>
       </c>
       <c r="B811" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="812" spans="1:2">
@@ -9577,7 +9583,7 @@
         <v>811</v>
       </c>
       <c r="B812" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="813" spans="1:2">
@@ -9585,7 +9591,7 @@
         <v>812</v>
       </c>
       <c r="B813" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="814" spans="1:2">
@@ -9593,7 +9599,7 @@
         <v>813</v>
       </c>
       <c r="B814" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="815" spans="1:2">
@@ -9601,7 +9607,7 @@
         <v>814</v>
       </c>
       <c r="B815" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="816" spans="1:2">
@@ -9609,7 +9615,7 @@
         <v>815</v>
       </c>
       <c r="B816" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="817" spans="1:2">
@@ -9617,7 +9623,7 @@
         <v>816</v>
       </c>
       <c r="B817" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="818" spans="1:2">
@@ -9625,7 +9631,7 @@
         <v>817</v>
       </c>
       <c r="B818" s="1">
-        <v>920</v>
+        <v>500</v>
       </c>
     </row>
     <row r="819" spans="1:2">
@@ -9633,7 +9639,7 @@
         <v>818</v>
       </c>
       <c r="B819" s="1">
-        <v>1000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="820" spans="1:2">
@@ -9641,7 +9647,7 @@
         <v>819</v>
       </c>
       <c r="B820" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="821" spans="1:2">
@@ -9649,7 +9655,7 @@
         <v>820</v>
       </c>
       <c r="B821" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="822" spans="1:2">
@@ -9665,7 +9671,7 @@
         <v>822</v>
       </c>
       <c r="B823" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="824" spans="1:2">
@@ -9673,7 +9679,7 @@
         <v>823</v>
       </c>
       <c r="B824" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="825" spans="1:2">
@@ -9681,7 +9687,7 @@
         <v>824</v>
       </c>
       <c r="B825" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="826" spans="1:2">
@@ -9689,7 +9695,7 @@
         <v>825</v>
       </c>
       <c r="B826" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="827" spans="1:2">
@@ -9697,7 +9703,7 @@
         <v>826</v>
       </c>
       <c r="B827" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="828" spans="1:2">
@@ -9705,7 +9711,7 @@
         <v>827</v>
       </c>
       <c r="B828" s="1">
-        <v>960</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="829" spans="1:2">
@@ -9713,7 +9719,7 @@
         <v>828</v>
       </c>
       <c r="B829" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="830" spans="1:2">
@@ -9721,7 +9727,7 @@
         <v>829</v>
       </c>
       <c r="B830" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="831" spans="1:2">
@@ -9729,7 +9735,7 @@
         <v>830</v>
       </c>
       <c r="B831" s="1">
-        <v>820</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="832" spans="1:2">
@@ -9737,7 +9743,7 @@
         <v>831</v>
       </c>
       <c r="B832" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="833" spans="1:2">
@@ -9745,7 +9751,7 @@
         <v>832</v>
       </c>
       <c r="B833" s="1">
-        <v>500</v>
+        <v>820</v>
       </c>
     </row>
     <row r="834" spans="1:2">
@@ -9761,7 +9767,7 @@
         <v>834</v>
       </c>
       <c r="B835" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="836" spans="1:2">
@@ -9769,7 +9775,7 @@
         <v>835</v>
       </c>
       <c r="B836" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="837" spans="1:2">
@@ -9777,7 +9783,7 @@
         <v>836</v>
       </c>
       <c r="B837" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="838" spans="1:2">
@@ -9785,7 +9791,7 @@
         <v>837</v>
       </c>
       <c r="B838" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="839" spans="1:2">
@@ -9793,7 +9799,7 @@
         <v>838</v>
       </c>
       <c r="B839" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="840" spans="1:2">
@@ -9801,7 +9807,7 @@
         <v>839</v>
       </c>
       <c r="B840" s="1">
-        <v>840</v>
+        <v>820</v>
       </c>
     </row>
     <row r="841" spans="1:2">
@@ -9809,7 +9815,7 @@
         <v>840</v>
       </c>
       <c r="B841" s="1">
-        <v>400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="842" spans="1:2">
@@ -9817,7 +9823,7 @@
         <v>841</v>
       </c>
       <c r="B842" s="1">
-        <v>400</v>
+        <v>840</v>
       </c>
     </row>
     <row r="843" spans="1:2">
@@ -9825,7 +9831,7 @@
         <v>842</v>
       </c>
       <c r="B843" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="844" spans="1:2">
@@ -9833,7 +9839,7 @@
         <v>843</v>
       </c>
       <c r="B844" s="1">
-        <v>840</v>
+        <v>400</v>
       </c>
     </row>
     <row r="845" spans="1:2">
@@ -9849,7 +9855,7 @@
         <v>845</v>
       </c>
       <c r="B846" s="1">
-        <v>380</v>
+        <v>840</v>
       </c>
     </row>
     <row r="847" spans="1:2">
@@ -9857,7 +9863,7 @@
         <v>846</v>
       </c>
       <c r="B847" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="848" spans="1:2">
@@ -9865,7 +9871,7 @@
         <v>847</v>
       </c>
       <c r="B848" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="849" spans="1:2">
@@ -9873,7 +9879,7 @@
         <v>848</v>
       </c>
       <c r="B849" s="1">
-        <v>800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="850" spans="1:2">
@@ -9881,7 +9887,7 @@
         <v>849</v>
       </c>
       <c r="B850" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="851" spans="1:2">
@@ -9889,7 +9895,7 @@
         <v>850</v>
       </c>
       <c r="B851" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="852" spans="1:2">
@@ -9897,7 +9903,7 @@
         <v>851</v>
       </c>
       <c r="B852" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="853" spans="1:2">
@@ -9905,7 +9911,7 @@
         <v>852</v>
       </c>
       <c r="B853" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="854" spans="1:2">
@@ -9913,7 +9919,7 @@
         <v>853</v>
       </c>
       <c r="B854" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="855" spans="1:2">
@@ -9921,7 +9927,7 @@
         <v>854</v>
       </c>
       <c r="B855" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="856" spans="1:2">
@@ -9929,7 +9935,7 @@
         <v>855</v>
       </c>
       <c r="B856" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="857" spans="1:2">
@@ -9937,7 +9943,7 @@
         <v>856</v>
       </c>
       <c r="B857" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="858" spans="1:2">
@@ -9945,7 +9951,7 @@
         <v>857</v>
       </c>
       <c r="B858" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="859" spans="1:2">
@@ -9953,7 +9959,7 @@
         <v>858</v>
       </c>
       <c r="B859" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="860" spans="1:2">
@@ -9961,7 +9967,7 @@
         <v>859</v>
       </c>
       <c r="B860" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="861" spans="1:2">
@@ -9969,7 +9975,7 @@
         <v>860</v>
       </c>
       <c r="B861" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="862" spans="1:2">
@@ -9977,7 +9983,7 @@
         <v>861</v>
       </c>
       <c r="B862" s="1">
-        <v>840</v>
+        <v>500</v>
       </c>
     </row>
     <row r="863" spans="1:2">
@@ -9985,7 +9991,7 @@
         <v>862</v>
       </c>
       <c r="B863" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="864" spans="1:2">
@@ -9993,7 +9999,7 @@
         <v>863</v>
       </c>
       <c r="B864" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="865" spans="1:2">
@@ -10001,7 +10007,7 @@
         <v>864</v>
       </c>
       <c r="B865" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="866" spans="1:2">
@@ -10009,7 +10015,7 @@
         <v>865</v>
       </c>
       <c r="B866" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="867" spans="1:2">
@@ -10017,7 +10023,7 @@
         <v>866</v>
       </c>
       <c r="B867" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="868" spans="1:2">
@@ -10025,7 +10031,7 @@
         <v>867</v>
       </c>
       <c r="B868" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="869" spans="1:2">
@@ -10041,7 +10047,7 @@
         <v>869</v>
       </c>
       <c r="B870" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="871" spans="1:2">
@@ -10049,7 +10055,7 @@
         <v>870</v>
       </c>
       <c r="B871" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="872" spans="1:2">
@@ -10057,7 +10063,7 @@
         <v>871</v>
       </c>
       <c r="B872" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="873" spans="1:2">
@@ -10065,7 +10071,7 @@
         <v>872</v>
       </c>
       <c r="B873" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="874" spans="1:2">
@@ -10073,7 +10079,7 @@
         <v>873</v>
       </c>
       <c r="B874" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="875" spans="1:2">
@@ -10081,7 +10087,7 @@
         <v>874</v>
       </c>
       <c r="B875" s="1">
-        <v>960</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="876" spans="1:2">
@@ -10089,7 +10095,7 @@
         <v>875</v>
       </c>
       <c r="B876" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="877" spans="1:2">
@@ -10097,7 +10103,7 @@
         <v>876</v>
       </c>
       <c r="B877" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="878" spans="1:2">
@@ -10105,7 +10111,7 @@
         <v>877</v>
       </c>
       <c r="B878" s="1">
-        <v>820</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="879" spans="1:2">
@@ -10113,7 +10119,7 @@
         <v>878</v>
       </c>
       <c r="B879" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="880" spans="1:2">
@@ -10121,7 +10127,7 @@
         <v>879</v>
       </c>
       <c r="B880" s="1">
-        <v>500</v>
+        <v>820</v>
       </c>
     </row>
     <row r="881" spans="1:2">
@@ -10137,7 +10143,7 @@
         <v>881</v>
       </c>
       <c r="B882" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="883" spans="1:2">
@@ -10145,7 +10151,7 @@
         <v>882</v>
       </c>
       <c r="B883" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="884" spans="1:2">
@@ -10153,7 +10159,7 @@
         <v>883</v>
       </c>
       <c r="B884" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="885" spans="1:2">
@@ -10161,7 +10167,7 @@
         <v>884</v>
       </c>
       <c r="B885" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="886" spans="1:2">
@@ -10169,7 +10175,7 @@
         <v>885</v>
       </c>
       <c r="B886" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="887" spans="1:2">
@@ -10185,7 +10191,7 @@
         <v>887</v>
       </c>
       <c r="B888" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="889" spans="1:2">
@@ -10193,7 +10199,7 @@
         <v>888</v>
       </c>
       <c r="B889" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="890" spans="1:2">
@@ -10209,7 +10215,7 @@
         <v>890</v>
       </c>
       <c r="B891" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="892" spans="1:2">
@@ -10217,7 +10223,7 @@
         <v>891</v>
       </c>
       <c r="B892" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="893" spans="1:2">
@@ -10225,7 +10231,7 @@
         <v>892</v>
       </c>
       <c r="B893" s="1">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="894" spans="1:2">
@@ -10233,7 +10239,7 @@
         <v>893</v>
       </c>
       <c r="B894" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="895" spans="1:2">
@@ -10241,7 +10247,7 @@
         <v>894</v>
       </c>
       <c r="B895" s="1">
-        <v>600</v>
+        <v>440</v>
       </c>
     </row>
     <row r="896" spans="1:2">
@@ -10249,7 +10255,7 @@
         <v>895</v>
       </c>
       <c r="B896" s="1">
-        <v>820</v>
+        <v>380</v>
       </c>
     </row>
     <row r="897" spans="1:2">
@@ -10257,7 +10263,7 @@
         <v>896</v>
       </c>
       <c r="B897" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="898" spans="1:2">
@@ -10265,7 +10271,7 @@
         <v>897</v>
       </c>
       <c r="B898" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="899" spans="1:2">
@@ -10273,7 +10279,7 @@
         <v>898</v>
       </c>
       <c r="B899" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="900" spans="1:2">
@@ -10289,7 +10295,7 @@
         <v>900</v>
       </c>
       <c r="B901" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="902" spans="1:2">
@@ -10297,7 +10303,7 @@
         <v>901</v>
       </c>
       <c r="B902" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="903" spans="1:2">
@@ -10305,6 +10311,22 @@
         <v>902</v>
       </c>
       <c r="B903" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="904" spans="1:2">
+      <c r="A904" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="B904" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="905" spans="1:2">
+      <c r="A905" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="B905" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="908">
   <si>
     <t>Наименование</t>
   </si>
@@ -29,6 +29,9 @@
     <t xml:space="preserve"> St.Anton - Semi-Dry, РОЗЛИВ</t>
   </si>
   <si>
+    <t xml:space="preserve"> вынос_Stamm - Skopek (Czech Pilsner), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>"Gletcher"-NUT BUTTER (Brown Ale), Розлив, Россия</t>
   </si>
   <si>
@@ -1385,6 +1388,9 @@
     <t>Zagovor  - And Washed Our Hops In The Sea (AIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Zagovor  - Barrio (Mexican Lager), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Zagovor  - Brace Up (Dry Cider), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -2337,6 +2343,9 @@
   </si>
   <si>
     <t>вынос_Zagovor  - And Washed Our Hops In The Sea (AIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Zagovor  - Barrio (Mexican Lager), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_Zagovor  - Brace Up (Dry Cider), РОЗЛИВ, Россия</t>
@@ -3083,7 +3092,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B905"/>
+  <dimension ref="A1:B908"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -3119,7 +3128,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>420</v>
+        <v>800</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3127,7 +3136,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>880</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3143,7 +3152,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>480</v>
+        <v>880</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3167,7 +3176,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3175,7 +3184,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3191,7 +3200,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3215,7 +3224,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>760</v>
+        <v>520</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3223,7 +3232,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>440</v>
+        <v>760</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3231,7 +3240,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>840</v>
+        <v>440</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3239,7 +3248,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3247,7 +3256,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>1100</v>
+        <v>660</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3255,7 +3264,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3263,7 +3272,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>580</v>
+        <v>840</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3279,7 +3288,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>700</v>
+        <v>580</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3287,7 +3296,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>620</v>
+        <v>700</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3295,7 +3304,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>760</v>
+        <v>620</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3303,7 +3312,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3311,7 +3320,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3327,7 +3336,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3335,7 +3344,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3343,7 +3352,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3351,7 +3360,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3359,7 +3368,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3367,7 +3376,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3375,7 +3384,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>620</v>
+        <v>700</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3383,7 +3392,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3391,7 +3400,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3407,7 +3416,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>420</v>
+        <v>600</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3415,7 +3424,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>580</v>
+        <v>420</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3423,7 +3432,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>1000</v>
+        <v>580</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3431,7 +3440,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3439,7 +3448,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3447,7 +3456,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3455,7 +3464,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3463,7 +3472,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>840</v>
+        <v>620</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3471,7 +3480,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -3479,7 +3488,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>1060</v>
+        <v>880</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -3487,7 +3496,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>720</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -3495,7 +3504,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>860</v>
+        <v>720</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -3511,7 +3520,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>800</v>
+        <v>860</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -3519,7 +3528,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>860</v>
+        <v>800</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -3527,7 +3536,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -3535,7 +3544,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>480</v>
+        <v>960</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -3543,7 +3552,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>760</v>
+        <v>480</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -3551,7 +3560,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -3559,7 +3568,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -3567,7 +3576,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -3583,7 +3592,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -3591,7 +3600,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -3599,7 +3608,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -3615,7 +3624,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -3623,7 +3632,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -3631,7 +3640,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -3639,7 +3648,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -3655,7 +3664,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -3663,7 +3672,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -3671,7 +3680,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -3679,7 +3688,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -3687,7 +3696,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -3695,7 +3704,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -3711,7 +3720,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -3727,7 +3736,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -3735,7 +3744,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -3743,7 +3752,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>560</v>
+        <v>680</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -3751,7 +3760,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>880</v>
+        <v>560</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -3759,7 +3768,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -3767,7 +3776,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -3775,7 +3784,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -3783,7 +3792,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -3791,7 +3800,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -3799,7 +3808,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3807,7 +3816,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -3815,7 +3824,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>640</v>
+        <v>880</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3823,7 +3832,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3831,7 +3840,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -3839,7 +3848,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3847,7 +3856,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3855,7 +3864,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3863,7 +3872,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -3871,7 +3880,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3887,7 +3896,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -3895,7 +3904,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3903,7 +3912,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3911,7 +3920,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -3919,7 +3928,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>540</v>
+        <v>560</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3927,7 +3936,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>860</v>
+        <v>540</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3935,7 +3944,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3951,7 +3960,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -3959,7 +3968,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -3967,7 +3976,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>440</v>
+        <v>720</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3975,7 +3984,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3983,7 +3992,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>460</v>
+        <v>560</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3999,7 +4008,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>960</v>
+        <v>460</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -4007,7 +4016,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>940</v>
+        <v>960</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -4015,7 +4024,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -4031,7 +4040,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>660</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -4039,7 +4048,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>480</v>
+        <v>660</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -4047,7 +4056,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>400</v>
+        <v>480</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -4055,7 +4064,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>720</v>
+        <v>400</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -4063,7 +4072,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -4071,7 +4080,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>500</v>
+        <v>560</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -4079,7 +4088,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -4087,7 +4096,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>500</v>
+        <v>760</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -4095,7 +4104,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>940</v>
+        <v>500</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -4103,7 +4112,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>820</v>
+        <v>940</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -4111,7 +4120,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -4119,7 +4128,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -4127,7 +4136,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -4135,7 +4144,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -4143,7 +4152,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -4151,7 +4160,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>680</v>
+        <v>960</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -4159,7 +4168,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>420</v>
+        <v>680</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -4167,7 +4176,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -4175,7 +4184,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -4183,7 +4192,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -4191,7 +4200,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -4199,7 +4208,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -4207,7 +4216,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -4215,7 +4224,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -4223,7 +4232,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -4231,7 +4240,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>580</v>
+        <v>880</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -4239,7 +4248,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -4247,7 +4256,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -4255,7 +4264,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>620</v>
+        <v>860</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -4263,7 +4272,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -4271,7 +4280,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -4279,7 +4288,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -4287,7 +4296,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -4295,7 +4304,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>900</v>
+        <v>960</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -4303,7 +4312,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -4311,7 +4320,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -4319,7 +4328,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -4327,7 +4336,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>500</v>
+        <v>780</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -4335,7 +4344,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>580</v>
+        <v>500</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -4343,7 +4352,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -4351,7 +4360,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -4359,7 +4368,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>1100</v>
+        <v>520</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -4367,7 +4376,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>1060</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -4383,7 +4392,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>1100</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -4399,7 +4408,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -4407,7 +4416,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>1080</v>
+        <v>560</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -4415,12 +4424,12 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>840</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B167" s="1">
         <v>840</v>
@@ -4439,7 +4448,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="1">
-        <v>420</v>
+        <v>840</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -4447,7 +4456,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="1">
-        <v>520</v>
+        <v>420</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -4455,7 +4464,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -4463,7 +4472,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="1">
-        <v>460</v>
+        <v>720</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4471,7 +4480,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="1">
-        <v>560</v>
+        <v>460</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4479,7 +4488,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4487,7 +4496,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4495,7 +4504,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4503,7 +4512,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4511,7 +4520,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="1">
-        <v>980</v>
+        <v>520</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4519,7 +4528,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="1">
-        <v>540</v>
+        <v>980</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4527,7 +4536,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4535,7 +4544,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4543,7 +4552,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4551,7 +4560,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="1">
-        <v>560</v>
+        <v>760</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4559,7 +4568,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="1">
-        <v>1100</v>
+        <v>560</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4591,7 +4600,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4599,7 +4608,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4607,7 +4616,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4615,7 +4624,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4647,7 +4656,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4655,7 +4664,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4663,7 +4672,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4671,7 +4680,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4679,7 +4688,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4687,7 +4696,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4695,7 +4704,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4703,7 +4712,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="1">
-        <v>980</v>
+        <v>700</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4711,7 +4720,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="1">
-        <v>460</v>
+        <v>980</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4719,7 +4728,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4727,7 +4736,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="1">
-        <v>720</v>
+        <v>580</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4735,7 +4744,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4743,7 +4752,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4751,7 +4760,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="1">
-        <v>260</v>
+        <v>780</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4767,7 +4776,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4783,7 +4792,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4791,7 +4800,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4799,7 +4808,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4807,7 +4816,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="1">
-        <v>500</v>
+        <v>760</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4815,7 +4824,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4823,7 +4832,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="1">
-        <v>740</v>
+        <v>400</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4831,7 +4840,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4839,7 +4848,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4847,7 +4856,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4855,7 +4864,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4863,7 +4872,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4871,7 +4880,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4887,7 +4896,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4895,7 +4904,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4903,7 +4912,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4911,7 +4920,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4919,7 +4928,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="1">
-        <v>580</v>
+        <v>860</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4927,7 +4936,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4935,7 +4944,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="1">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4943,7 +4952,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4951,7 +4960,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4959,7 +4968,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4967,7 +4976,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4975,7 +4984,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4983,7 +4992,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4991,7 +5000,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4999,7 +5008,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -5007,7 +5016,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -5015,7 +5024,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="1">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -5023,7 +5032,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="1">
-        <v>480</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -5031,7 +5040,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -5039,7 +5048,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -5047,7 +5056,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -5055,7 +5064,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -5063,7 +5072,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -5071,7 +5080,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -5079,7 +5088,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -5087,7 +5096,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -5095,7 +5104,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="1">
-        <v>900</v>
+        <v>520</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -5103,7 +5112,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -5111,7 +5120,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -5119,7 +5128,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -5127,7 +5136,7 @@
         <v>254</v>
       </c>
       <c r="B255" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -5143,7 +5152,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -5159,7 +5168,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -5167,7 +5176,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -5175,7 +5184,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -5183,7 +5192,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -5191,7 +5200,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -5199,7 +5208,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -5207,7 +5216,7 @@
         <v>264</v>
       </c>
       <c r="B265" s="1">
-        <v>960</v>
+        <v>840</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -5215,7 +5224,7 @@
         <v>265</v>
       </c>
       <c r="B266" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -5231,7 +5240,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -5239,7 +5248,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -5247,7 +5256,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -5255,7 +5264,7 @@
         <v>270</v>
       </c>
       <c r="B271" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -5263,7 +5272,7 @@
         <v>271</v>
       </c>
       <c r="B272" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -5271,7 +5280,7 @@
         <v>272</v>
       </c>
       <c r="B273" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -5287,7 +5296,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="1">
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -5295,7 +5304,7 @@
         <v>275</v>
       </c>
       <c r="B276" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -5303,7 +5312,7 @@
         <v>276</v>
       </c>
       <c r="B277" s="1">
-        <v>758</v>
+        <v>500</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -5311,7 +5320,7 @@
         <v>277</v>
       </c>
       <c r="B278" s="1">
-        <v>2273</v>
+        <v>758</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -5319,7 +5328,7 @@
         <v>278</v>
       </c>
       <c r="B279" s="1">
-        <v>1515</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -5327,7 +5336,7 @@
         <v>279</v>
       </c>
       <c r="B280" s="1">
-        <v>520</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -5335,7 +5344,7 @@
         <v>280</v>
       </c>
       <c r="B281" s="1">
-        <v>4000</v>
+        <v>520</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -5343,7 +5352,7 @@
         <v>281</v>
       </c>
       <c r="B282" s="1">
-        <v>560</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -5351,7 +5360,7 @@
         <v>282</v>
       </c>
       <c r="B283" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -5359,7 +5368,7 @@
         <v>283</v>
       </c>
       <c r="B284" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -5375,7 +5384,7 @@
         <v>285</v>
       </c>
       <c r="B286" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5383,7 +5392,7 @@
         <v>286</v>
       </c>
       <c r="B287" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5391,7 +5400,7 @@
         <v>287</v>
       </c>
       <c r="B288" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5399,7 +5408,7 @@
         <v>288</v>
       </c>
       <c r="B289" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5407,7 +5416,7 @@
         <v>289</v>
       </c>
       <c r="B290" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5415,7 +5424,7 @@
         <v>290</v>
       </c>
       <c r="B291" s="1">
-        <v>680</v>
+        <v>520</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5423,7 +5432,7 @@
         <v>291</v>
       </c>
       <c r="B292" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5431,7 +5440,7 @@
         <v>292</v>
       </c>
       <c r="B293" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5439,7 +5448,7 @@
         <v>293</v>
       </c>
       <c r="B294" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5447,7 +5456,7 @@
         <v>294</v>
       </c>
       <c r="B295" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5455,7 +5464,7 @@
         <v>295</v>
       </c>
       <c r="B296" s="1">
-        <v>660</v>
+        <v>380</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5463,7 +5472,7 @@
         <v>296</v>
       </c>
       <c r="B297" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5471,7 +5480,7 @@
         <v>297</v>
       </c>
       <c r="B298" s="1">
-        <v>540</v>
+        <v>900</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5479,7 +5488,7 @@
         <v>298</v>
       </c>
       <c r="B299" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5487,7 +5496,7 @@
         <v>299</v>
       </c>
       <c r="B300" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5495,7 +5504,7 @@
         <v>300</v>
       </c>
       <c r="B301" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5503,7 +5512,7 @@
         <v>301</v>
       </c>
       <c r="B302" s="1">
-        <v>460</v>
+        <v>580</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5511,7 +5520,7 @@
         <v>302</v>
       </c>
       <c r="B303" s="1">
-        <v>520</v>
+        <v>460</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5519,7 +5528,7 @@
         <v>303</v>
       </c>
       <c r="B304" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5527,7 +5536,7 @@
         <v>304</v>
       </c>
       <c r="B305" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5535,7 +5544,7 @@
         <v>305</v>
       </c>
       <c r="B306" s="1">
-        <v>860</v>
+        <v>900</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5543,7 +5552,7 @@
         <v>306</v>
       </c>
       <c r="B307" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5567,7 +5576,7 @@
         <v>309</v>
       </c>
       <c r="B310" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5583,7 +5592,7 @@
         <v>311</v>
       </c>
       <c r="B312" s="1">
-        <v>980</v>
+        <v>560</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5591,7 +5600,7 @@
         <v>312</v>
       </c>
       <c r="B313" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5607,7 +5616,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5615,7 +5624,7 @@
         <v>315</v>
       </c>
       <c r="B316" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5623,7 +5632,7 @@
         <v>316</v>
       </c>
       <c r="B317" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5631,7 +5640,7 @@
         <v>317</v>
       </c>
       <c r="B318" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5639,7 +5648,7 @@
         <v>318</v>
       </c>
       <c r="B319" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5647,7 +5656,7 @@
         <v>319</v>
       </c>
       <c r="B320" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5655,7 +5664,7 @@
         <v>320</v>
       </c>
       <c r="B321" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5663,7 +5672,7 @@
         <v>321</v>
       </c>
       <c r="B322" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5671,7 +5680,7 @@
         <v>322</v>
       </c>
       <c r="B323" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5679,7 +5688,7 @@
         <v>323</v>
       </c>
       <c r="B324" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5687,7 +5696,7 @@
         <v>324</v>
       </c>
       <c r="B325" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5695,7 +5704,7 @@
         <v>325</v>
       </c>
       <c r="B326" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5703,7 +5712,7 @@
         <v>326</v>
       </c>
       <c r="B327" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5711,7 +5720,7 @@
         <v>327</v>
       </c>
       <c r="B328" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5719,7 +5728,7 @@
         <v>328</v>
       </c>
       <c r="B329" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5727,7 +5736,7 @@
         <v>329</v>
       </c>
       <c r="B330" s="1">
-        <v>520</v>
+        <v>680</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5735,7 +5744,7 @@
         <v>330</v>
       </c>
       <c r="B331" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5743,7 +5752,7 @@
         <v>331</v>
       </c>
       <c r="B332" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5751,7 +5760,7 @@
         <v>332</v>
       </c>
       <c r="B333" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5759,7 +5768,7 @@
         <v>333</v>
       </c>
       <c r="B334" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5767,7 +5776,7 @@
         <v>334</v>
       </c>
       <c r="B335" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5775,7 +5784,7 @@
         <v>335</v>
       </c>
       <c r="B336" s="1">
-        <v>580</v>
+        <v>840</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5783,7 +5792,7 @@
         <v>336</v>
       </c>
       <c r="B337" s="1">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5791,7 +5800,7 @@
         <v>337</v>
       </c>
       <c r="B338" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5799,7 +5808,7 @@
         <v>338</v>
       </c>
       <c r="B339" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5807,7 +5816,7 @@
         <v>339</v>
       </c>
       <c r="B340" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5815,7 +5824,7 @@
         <v>340</v>
       </c>
       <c r="B341" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5823,7 +5832,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5831,7 +5840,7 @@
         <v>342</v>
       </c>
       <c r="B343" s="1">
-        <v>1000</v>
+        <v>880</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5839,7 +5848,7 @@
         <v>343</v>
       </c>
       <c r="B344" s="1">
-        <v>520</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5847,7 +5856,7 @@
         <v>344</v>
       </c>
       <c r="B345" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5855,7 +5864,7 @@
         <v>345</v>
       </c>
       <c r="B346" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5863,7 +5872,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5871,7 +5880,7 @@
         <v>347</v>
       </c>
       <c r="B348" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5879,7 +5888,7 @@
         <v>348</v>
       </c>
       <c r="B349" s="1">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5887,7 +5896,7 @@
         <v>349</v>
       </c>
       <c r="B350" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5895,7 +5904,7 @@
         <v>350</v>
       </c>
       <c r="B351" s="1">
-        <v>320</v>
+        <v>520</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5903,7 +5912,7 @@
         <v>351</v>
       </c>
       <c r="B352" s="1">
-        <v>540</v>
+        <v>320</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5911,7 +5920,7 @@
         <v>352</v>
       </c>
       <c r="B353" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5919,7 +5928,7 @@
         <v>353</v>
       </c>
       <c r="B354" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5935,7 +5944,7 @@
         <v>355</v>
       </c>
       <c r="B356" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5943,7 +5952,7 @@
         <v>356</v>
       </c>
       <c r="B357" s="1">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5951,7 +5960,7 @@
         <v>357</v>
       </c>
       <c r="B358" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5959,7 +5968,7 @@
         <v>358</v>
       </c>
       <c r="B359" s="1">
-        <v>480</v>
+        <v>800</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5967,7 +5976,7 @@
         <v>359</v>
       </c>
       <c r="B360" s="1">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5975,7 +5984,7 @@
         <v>360</v>
       </c>
       <c r="B361" s="1">
-        <v>520</v>
+        <v>800</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5983,7 +5992,7 @@
         <v>361</v>
       </c>
       <c r="B362" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5991,7 +6000,7 @@
         <v>362</v>
       </c>
       <c r="B363" s="1">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5999,7 +6008,7 @@
         <v>363</v>
       </c>
       <c r="B364" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -6015,7 +6024,7 @@
         <v>365</v>
       </c>
       <c r="B366" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -6031,7 +6040,7 @@
         <v>367</v>
       </c>
       <c r="B368" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -6039,7 +6048,7 @@
         <v>368</v>
       </c>
       <c r="B369" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -6047,7 +6056,7 @@
         <v>369</v>
       </c>
       <c r="B370" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -6055,7 +6064,7 @@
         <v>370</v>
       </c>
       <c r="B371" s="1">
-        <v>880</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -6063,7 +6072,7 @@
         <v>371</v>
       </c>
       <c r="B372" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -6071,7 +6080,7 @@
         <v>372</v>
       </c>
       <c r="B373" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -6079,7 +6088,7 @@
         <v>373</v>
       </c>
       <c r="B374" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -6087,7 +6096,7 @@
         <v>374</v>
       </c>
       <c r="B375" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -6095,7 +6104,7 @@
         <v>375</v>
       </c>
       <c r="B376" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -6103,7 +6112,7 @@
         <v>376</v>
       </c>
       <c r="B377" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -6111,7 +6120,7 @@
         <v>377</v>
       </c>
       <c r="B378" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -6119,7 +6128,7 @@
         <v>378</v>
       </c>
       <c r="B379" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -6135,7 +6144,7 @@
         <v>380</v>
       </c>
       <c r="B381" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -6151,7 +6160,7 @@
         <v>382</v>
       </c>
       <c r="B383" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -6159,7 +6168,7 @@
         <v>383</v>
       </c>
       <c r="B384" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -6167,7 +6176,7 @@
         <v>384</v>
       </c>
       <c r="B385" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -6175,7 +6184,7 @@
         <v>385</v>
       </c>
       <c r="B386" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -6183,7 +6192,7 @@
         <v>386</v>
       </c>
       <c r="B387" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -6191,7 +6200,7 @@
         <v>387</v>
       </c>
       <c r="B388" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -6199,7 +6208,7 @@
         <v>388</v>
       </c>
       <c r="B389" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -6207,7 +6216,7 @@
         <v>389</v>
       </c>
       <c r="B390" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -6215,7 +6224,7 @@
         <v>390</v>
       </c>
       <c r="B391" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -6223,7 +6232,7 @@
         <v>391</v>
       </c>
       <c r="B392" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -6231,7 +6240,7 @@
         <v>392</v>
       </c>
       <c r="B393" s="1">
-        <v>640</v>
+        <v>480</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -6239,7 +6248,7 @@
         <v>393</v>
       </c>
       <c r="B394" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -6247,7 +6256,7 @@
         <v>394</v>
       </c>
       <c r="B395" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -6255,7 +6264,7 @@
         <v>395</v>
       </c>
       <c r="B396" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -6263,7 +6272,7 @@
         <v>396</v>
       </c>
       <c r="B397" s="1">
-        <v>520</v>
+        <v>860</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -6271,7 +6280,7 @@
         <v>397</v>
       </c>
       <c r="B398" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -6279,7 +6288,7 @@
         <v>398</v>
       </c>
       <c r="B399" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -6295,7 +6304,7 @@
         <v>400</v>
       </c>
       <c r="B401" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -6303,7 +6312,7 @@
         <v>401</v>
       </c>
       <c r="B402" s="1">
-        <v>700</v>
+        <v>420</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -6311,7 +6320,7 @@
         <v>402</v>
       </c>
       <c r="B403" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -6319,7 +6328,7 @@
         <v>403</v>
       </c>
       <c r="B404" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -6327,7 +6336,7 @@
         <v>404</v>
       </c>
       <c r="B405" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -6335,7 +6344,7 @@
         <v>405</v>
       </c>
       <c r="B406" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -6343,7 +6352,7 @@
         <v>406</v>
       </c>
       <c r="B407" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -6351,7 +6360,7 @@
         <v>407</v>
       </c>
       <c r="B408" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -6359,7 +6368,7 @@
         <v>408</v>
       </c>
       <c r="B409" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -6367,7 +6376,7 @@
         <v>409</v>
       </c>
       <c r="B410" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -6375,7 +6384,7 @@
         <v>410</v>
       </c>
       <c r="B411" s="1">
-        <v>440</v>
+        <v>620</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -6383,7 +6392,7 @@
         <v>411</v>
       </c>
       <c r="B412" s="1">
-        <v>1100</v>
+        <v>440</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -6399,7 +6408,7 @@
         <v>413</v>
       </c>
       <c r="B414" s="1">
-        <v>320</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -6407,7 +6416,7 @@
         <v>414</v>
       </c>
       <c r="B415" s="1">
-        <v>940</v>
+        <v>320</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -6415,7 +6424,7 @@
         <v>415</v>
       </c>
       <c r="B416" s="1">
-        <v>320</v>
+        <v>940</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -6423,7 +6432,7 @@
         <v>416</v>
       </c>
       <c r="B417" s="1">
-        <v>960</v>
+        <v>320</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -6431,7 +6440,7 @@
         <v>417</v>
       </c>
       <c r="B418" s="1">
-        <v>820</v>
+        <v>960</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -6439,7 +6448,7 @@
         <v>418</v>
       </c>
       <c r="B419" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -6447,7 +6456,7 @@
         <v>419</v>
       </c>
       <c r="B420" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -6463,7 +6472,7 @@
         <v>421</v>
       </c>
       <c r="B422" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -6471,7 +6480,7 @@
         <v>422</v>
       </c>
       <c r="B423" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -6487,7 +6496,7 @@
         <v>424</v>
       </c>
       <c r="B425" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -6495,7 +6504,7 @@
         <v>425</v>
       </c>
       <c r="B426" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -6503,7 +6512,7 @@
         <v>426</v>
       </c>
       <c r="B427" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -6511,7 +6520,7 @@
         <v>427</v>
       </c>
       <c r="B428" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6519,7 +6528,7 @@
         <v>428</v>
       </c>
       <c r="B429" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6527,7 +6536,7 @@
         <v>429</v>
       </c>
       <c r="B430" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6535,7 +6544,7 @@
         <v>430</v>
       </c>
       <c r="B431" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6551,7 +6560,7 @@
         <v>432</v>
       </c>
       <c r="B433" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6559,7 +6568,7 @@
         <v>433</v>
       </c>
       <c r="B434" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6567,7 +6576,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6575,7 +6584,7 @@
         <v>435</v>
       </c>
       <c r="B436" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6583,7 +6592,7 @@
         <v>436</v>
       </c>
       <c r="B437" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6591,7 +6600,7 @@
         <v>437</v>
       </c>
       <c r="B438" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6599,7 +6608,7 @@
         <v>438</v>
       </c>
       <c r="B439" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6607,7 +6616,7 @@
         <v>439</v>
       </c>
       <c r="B440" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6615,7 +6624,7 @@
         <v>440</v>
       </c>
       <c r="B441" s="1">
-        <v>700</v>
+        <v>440</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6623,7 +6632,7 @@
         <v>441</v>
       </c>
       <c r="B442" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6639,7 +6648,7 @@
         <v>443</v>
       </c>
       <c r="B444" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6647,7 +6656,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="1">
-        <v>560</v>
+        <v>800</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6655,7 +6664,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6663,7 +6672,7 @@
         <v>446</v>
       </c>
       <c r="B447" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6671,7 +6680,7 @@
         <v>447</v>
       </c>
       <c r="B448" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6679,7 +6688,7 @@
         <v>448</v>
       </c>
       <c r="B449" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6687,7 +6696,7 @@
         <v>449</v>
       </c>
       <c r="B450" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6695,7 +6704,7 @@
         <v>450</v>
       </c>
       <c r="B451" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6703,7 +6712,7 @@
         <v>451</v>
       </c>
       <c r="B452" s="1">
-        <v>720</v>
+        <v>620</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6711,7 +6720,7 @@
         <v>452</v>
       </c>
       <c r="B453" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6719,7 +6728,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6735,7 +6744,7 @@
         <v>455</v>
       </c>
       <c r="B456" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6743,7 +6752,7 @@
         <v>456</v>
       </c>
       <c r="B457" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6751,7 +6760,7 @@
         <v>457</v>
       </c>
       <c r="B458" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6767,7 +6776,7 @@
         <v>459</v>
       </c>
       <c r="B460" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6775,7 +6784,7 @@
         <v>460</v>
       </c>
       <c r="B461" s="1">
-        <v>920</v>
+        <v>880</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6783,7 +6792,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6791,7 +6800,7 @@
         <v>462</v>
       </c>
       <c r="B463" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6799,7 +6808,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="1">
-        <v>940</v>
+        <v>800</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6807,7 +6816,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6815,7 +6824,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6823,7 +6832,7 @@
         <v>466</v>
       </c>
       <c r="B467" s="1">
-        <v>600</v>
+        <v>980</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6831,7 +6840,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="1">
-        <v>760</v>
+        <v>920</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6839,7 +6848,7 @@
         <v>468</v>
       </c>
       <c r="B469" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6847,7 +6856,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="1">
-        <v>620</v>
+        <v>760</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6855,7 +6864,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6863,7 +6872,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6871,7 +6880,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="1">
-        <v>920</v>
+        <v>620</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6879,7 +6888,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="1">
-        <v>640</v>
+        <v>860</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6887,7 +6896,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6895,7 +6904,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="1">
-        <v>820</v>
+        <v>640</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6903,7 +6912,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6911,7 +6920,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6919,7 +6928,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6927,7 +6936,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6935,7 +6944,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6943,7 +6952,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6951,7 +6960,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6959,7 +6968,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="1">
-        <v>660</v>
+        <v>560</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6967,7 +6976,7 @@
         <v>484</v>
       </c>
       <c r="B485" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6975,7 +6984,7 @@
         <v>485</v>
       </c>
       <c r="B486" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6983,7 +6992,7 @@
         <v>486</v>
       </c>
       <c r="B487" s="1">
-        <v>840</v>
+        <v>640</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6991,7 +7000,7 @@
         <v>487</v>
       </c>
       <c r="B488" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6999,7 +7008,7 @@
         <v>488</v>
       </c>
       <c r="B489" s="1">
-        <v>480</v>
+        <v>840</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -7007,7 +7016,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="1">
-        <v>620</v>
+        <v>520</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -7015,7 +7024,7 @@
         <v>490</v>
       </c>
       <c r="B491" s="1">
-        <v>780</v>
+        <v>480</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -7023,7 +7032,7 @@
         <v>491</v>
       </c>
       <c r="B492" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -7031,7 +7040,7 @@
         <v>492</v>
       </c>
       <c r="B493" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -7039,7 +7048,7 @@
         <v>493</v>
       </c>
       <c r="B494" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -7047,7 +7056,7 @@
         <v>494</v>
       </c>
       <c r="B495" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -7055,7 +7064,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -7063,7 +7072,7 @@
         <v>496</v>
       </c>
       <c r="B497" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -7071,7 +7080,7 @@
         <v>497</v>
       </c>
       <c r="B498" s="1">
-        <v>480</v>
+        <v>780</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -7079,7 +7088,7 @@
         <v>498</v>
       </c>
       <c r="B499" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -7087,7 +7096,7 @@
         <v>499</v>
       </c>
       <c r="B500" s="1">
-        <v>660</v>
+        <v>480</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -7095,7 +7104,7 @@
         <v>500</v>
       </c>
       <c r="B501" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -7103,7 +7112,7 @@
         <v>501</v>
       </c>
       <c r="B502" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -7111,7 +7120,7 @@
         <v>502</v>
       </c>
       <c r="B503" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -7119,7 +7128,7 @@
         <v>503</v>
       </c>
       <c r="B504" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -7127,7 +7136,7 @@
         <v>504</v>
       </c>
       <c r="B505" s="1">
-        <v>940</v>
+        <v>440</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -7135,7 +7144,7 @@
         <v>505</v>
       </c>
       <c r="B506" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -7143,7 +7152,7 @@
         <v>506</v>
       </c>
       <c r="B507" s="1">
-        <v>880</v>
+        <v>940</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -7151,7 +7160,7 @@
         <v>507</v>
       </c>
       <c r="B508" s="1">
-        <v>880</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -7159,7 +7168,7 @@
         <v>508</v>
       </c>
       <c r="B509" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -7167,7 +7176,7 @@
         <v>509</v>
       </c>
       <c r="B510" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -7175,7 +7184,7 @@
         <v>510</v>
       </c>
       <c r="B511" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -7183,7 +7192,7 @@
         <v>511</v>
       </c>
       <c r="B512" s="1">
-        <v>1100</v>
+        <v>840</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -7191,7 +7200,7 @@
         <v>512</v>
       </c>
       <c r="B513" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -7199,7 +7208,7 @@
         <v>513</v>
       </c>
       <c r="B514" s="1">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -7207,7 +7216,7 @@
         <v>514</v>
       </c>
       <c r="B515" s="1">
-        <v>760</v>
+        <v>840</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -7215,7 +7224,7 @@
         <v>515</v>
       </c>
       <c r="B516" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -7223,7 +7232,7 @@
         <v>516</v>
       </c>
       <c r="B517" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -7231,7 +7240,7 @@
         <v>517</v>
       </c>
       <c r="B518" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -7239,7 +7248,7 @@
         <v>518</v>
       </c>
       <c r="B519" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -7247,7 +7256,7 @@
         <v>519</v>
       </c>
       <c r="B520" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -7255,7 +7264,7 @@
         <v>520</v>
       </c>
       <c r="B521" s="1">
-        <v>760</v>
+        <v>840</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -7263,7 +7272,7 @@
         <v>521</v>
       </c>
       <c r="B522" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -7271,7 +7280,7 @@
         <v>522</v>
       </c>
       <c r="B523" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -7279,7 +7288,7 @@
         <v>523</v>
       </c>
       <c r="B524" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -7287,7 +7296,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -7295,7 +7304,7 @@
         <v>525</v>
       </c>
       <c r="B526" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -7303,7 +7312,7 @@
         <v>526</v>
       </c>
       <c r="B527" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -7311,7 +7320,7 @@
         <v>527</v>
       </c>
       <c r="B528" s="1">
-        <v>660</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -7319,7 +7328,7 @@
         <v>528</v>
       </c>
       <c r="B529" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -7327,7 +7336,7 @@
         <v>529</v>
       </c>
       <c r="B530" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -7335,7 +7344,7 @@
         <v>530</v>
       </c>
       <c r="B531" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -7343,7 +7352,7 @@
         <v>531</v>
       </c>
       <c r="B532" s="1">
-        <v>880</v>
+        <v>620</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -7351,7 +7360,7 @@
         <v>532</v>
       </c>
       <c r="B533" s="1">
-        <v>1060</v>
+        <v>840</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -7359,7 +7368,7 @@
         <v>533</v>
       </c>
       <c r="B534" s="1">
-        <v>860</v>
+        <v>880</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -7367,7 +7376,7 @@
         <v>534</v>
       </c>
       <c r="B535" s="1">
-        <v>860</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -7375,7 +7384,7 @@
         <v>535</v>
       </c>
       <c r="B536" s="1">
-        <v>800</v>
+        <v>860</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -7391,7 +7400,7 @@
         <v>537</v>
       </c>
       <c r="B538" s="1">
-        <v>960</v>
+        <v>800</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -7399,7 +7408,7 @@
         <v>538</v>
       </c>
       <c r="B539" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -7407,7 +7416,7 @@
         <v>539</v>
       </c>
       <c r="B540" s="1">
-        <v>720</v>
+        <v>960</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -7415,7 +7424,7 @@
         <v>540</v>
       </c>
       <c r="B541" s="1">
-        <v>1000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -7423,7 +7432,7 @@
         <v>541</v>
       </c>
       <c r="B542" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -7431,7 +7440,7 @@
         <v>542</v>
       </c>
       <c r="B543" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -7439,7 +7448,7 @@
         <v>543</v>
       </c>
       <c r="B544" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -7447,7 +7456,7 @@
         <v>544</v>
       </c>
       <c r="B545" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -7455,7 +7464,7 @@
         <v>545</v>
       </c>
       <c r="B546" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -7463,7 +7472,7 @@
         <v>546</v>
       </c>
       <c r="B547" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -7471,7 +7480,7 @@
         <v>547</v>
       </c>
       <c r="B548" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -7479,7 +7488,7 @@
         <v>548</v>
       </c>
       <c r="B549" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -7487,7 +7496,7 @@
         <v>549</v>
       </c>
       <c r="B550" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -7503,7 +7512,7 @@
         <v>551</v>
       </c>
       <c r="B552" s="1">
-        <v>640</v>
+        <v>900</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7511,7 +7520,7 @@
         <v>552</v>
       </c>
       <c r="B553" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7519,7 +7528,7 @@
         <v>553</v>
       </c>
       <c r="B554" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7527,7 +7536,7 @@
         <v>554</v>
       </c>
       <c r="B555" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7535,7 +7544,7 @@
         <v>555</v>
       </c>
       <c r="B556" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7543,7 +7552,7 @@
         <v>556</v>
       </c>
       <c r="B557" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7551,7 +7560,7 @@
         <v>557</v>
       </c>
       <c r="B558" s="1">
-        <v>880</v>
+        <v>700</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7559,7 +7568,7 @@
         <v>558</v>
       </c>
       <c r="B559" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7567,7 +7576,7 @@
         <v>559</v>
       </c>
       <c r="B560" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7591,7 +7600,7 @@
         <v>562</v>
       </c>
       <c r="B563" s="1">
-        <v>920</v>
+        <v>820</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7599,7 +7608,7 @@
         <v>563</v>
       </c>
       <c r="B564" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7607,7 +7616,7 @@
         <v>564</v>
       </c>
       <c r="B565" s="1">
-        <v>880</v>
+        <v>920</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7615,7 +7624,7 @@
         <v>565</v>
       </c>
       <c r="B566" s="1">
-        <v>640</v>
+        <v>600</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7623,7 +7632,7 @@
         <v>566</v>
       </c>
       <c r="B567" s="1">
-        <v>700</v>
+        <v>880</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7631,7 +7640,7 @@
         <v>567</v>
       </c>
       <c r="B568" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7639,7 +7648,7 @@
         <v>568</v>
       </c>
       <c r="B569" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7647,7 +7656,7 @@
         <v>569</v>
       </c>
       <c r="B570" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7655,7 +7664,7 @@
         <v>570</v>
       </c>
       <c r="B571" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7663,7 +7672,7 @@
         <v>571</v>
       </c>
       <c r="B572" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7671,7 +7680,7 @@
         <v>572</v>
       </c>
       <c r="B573" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7679,7 +7688,7 @@
         <v>573</v>
       </c>
       <c r="B574" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7687,7 +7696,7 @@
         <v>574</v>
       </c>
       <c r="B575" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7695,7 +7704,7 @@
         <v>575</v>
       </c>
       <c r="B576" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7703,7 +7712,7 @@
         <v>576</v>
       </c>
       <c r="B577" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7711,7 +7720,7 @@
         <v>577</v>
       </c>
       <c r="B578" s="1">
-        <v>1040</v>
+        <v>960</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7719,7 +7728,7 @@
         <v>578</v>
       </c>
       <c r="B579" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7727,7 +7736,7 @@
         <v>579</v>
       </c>
       <c r="B580" s="1">
-        <v>940</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7735,7 +7744,7 @@
         <v>580</v>
       </c>
       <c r="B581" s="1">
-        <v>860</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7743,7 +7752,7 @@
         <v>581</v>
       </c>
       <c r="B582" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7751,7 +7760,7 @@
         <v>582</v>
       </c>
       <c r="B583" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7759,7 +7768,7 @@
         <v>583</v>
       </c>
       <c r="B584" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7767,7 +7776,7 @@
         <v>584</v>
       </c>
       <c r="B585" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7775,7 +7784,7 @@
         <v>585</v>
       </c>
       <c r="B586" s="1">
-        <v>840</v>
+        <v>960</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7783,7 +7792,7 @@
         <v>586</v>
       </c>
       <c r="B587" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7791,7 +7800,7 @@
         <v>587</v>
       </c>
       <c r="B588" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7799,7 +7808,7 @@
         <v>588</v>
       </c>
       <c r="B589" s="1">
-        <v>580</v>
+        <v>780</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7807,7 +7816,7 @@
         <v>589</v>
       </c>
       <c r="B590" s="1">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7815,7 +7824,7 @@
         <v>590</v>
       </c>
       <c r="B591" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7823,7 +7832,7 @@
         <v>591</v>
       </c>
       <c r="B592" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7831,7 +7840,7 @@
         <v>592</v>
       </c>
       <c r="B593" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7839,7 +7848,7 @@
         <v>593</v>
       </c>
       <c r="B594" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7847,7 +7856,7 @@
         <v>594</v>
       </c>
       <c r="B595" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7855,7 +7864,7 @@
         <v>595</v>
       </c>
       <c r="B596" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7863,7 +7872,7 @@
         <v>596</v>
       </c>
       <c r="B597" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7871,7 +7880,7 @@
         <v>597</v>
       </c>
       <c r="B598" s="1">
-        <v>600</v>
+        <v>960</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7879,7 +7888,7 @@
         <v>598</v>
       </c>
       <c r="B599" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7887,7 +7896,7 @@
         <v>599</v>
       </c>
       <c r="B600" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7895,7 +7904,7 @@
         <v>600</v>
       </c>
       <c r="B601" s="1">
-        <v>540</v>
+        <v>720</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7903,7 +7912,7 @@
         <v>601</v>
       </c>
       <c r="B602" s="1">
-        <v>1100</v>
+        <v>780</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7911,7 +7920,7 @@
         <v>602</v>
       </c>
       <c r="B603" s="1">
-        <v>1060</v>
+        <v>540</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7927,7 +7936,7 @@
         <v>604</v>
       </c>
       <c r="B605" s="1">
-        <v>1100</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7935,7 +7944,7 @@
         <v>605</v>
       </c>
       <c r="B606" s="1">
-        <v>1080</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7943,7 +7952,7 @@
         <v>606</v>
       </c>
       <c r="B607" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7951,7 +7960,7 @@
         <v>607</v>
       </c>
       <c r="B608" s="1">
-        <v>840</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7959,7 +7968,7 @@
         <v>608</v>
       </c>
       <c r="B609" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7967,7 +7976,7 @@
         <v>609</v>
       </c>
       <c r="B610" s="1">
-        <v>560</v>
+        <v>840</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7975,7 +7984,7 @@
         <v>610</v>
       </c>
       <c r="B611" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7983,7 +7992,7 @@
         <v>611</v>
       </c>
       <c r="B612" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7991,7 +8000,7 @@
         <v>612</v>
       </c>
       <c r="B613" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7999,7 +8008,7 @@
         <v>613</v>
       </c>
       <c r="B614" s="1">
-        <v>980</v>
+        <v>620</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -8007,7 +8016,7 @@
         <v>614</v>
       </c>
       <c r="B615" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -8015,7 +8024,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="1">
-        <v>760</v>
+        <v>980</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -8023,7 +8032,7 @@
         <v>616</v>
       </c>
       <c r="B617" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -8031,7 +8040,7 @@
         <v>617</v>
       </c>
       <c r="B618" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -8047,7 +8056,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -8055,7 +8064,7 @@
         <v>620</v>
       </c>
       <c r="B621" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -8071,7 +8080,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -8079,7 +8088,7 @@
         <v>623</v>
       </c>
       <c r="B624" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -8087,7 +8096,7 @@
         <v>624</v>
       </c>
       <c r="B625" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -8095,7 +8104,7 @@
         <v>625</v>
       </c>
       <c r="B626" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -8103,7 +8112,7 @@
         <v>626</v>
       </c>
       <c r="B627" s="1">
-        <v>700</v>
+        <v>960</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -8111,7 +8120,7 @@
         <v>627</v>
       </c>
       <c r="B628" s="1">
-        <v>980</v>
+        <v>840</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -8119,7 +8128,7 @@
         <v>628</v>
       </c>
       <c r="B629" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -8127,7 +8136,7 @@
         <v>629</v>
       </c>
       <c r="B630" s="1">
-        <v>800</v>
+        <v>980</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -8135,7 +8144,7 @@
         <v>630</v>
       </c>
       <c r="B631" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -8143,7 +8152,7 @@
         <v>631</v>
       </c>
       <c r="B632" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -8159,7 +8168,7 @@
         <v>633</v>
       </c>
       <c r="B634" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -8167,7 +8176,7 @@
         <v>634</v>
       </c>
       <c r="B635" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -8183,7 +8192,7 @@
         <v>636</v>
       </c>
       <c r="B637" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -8191,7 +8200,7 @@
         <v>637</v>
       </c>
       <c r="B638" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -8199,7 +8208,7 @@
         <v>638</v>
       </c>
       <c r="B639" s="1">
-        <v>820</v>
+        <v>860</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -8207,7 +8216,7 @@
         <v>639</v>
       </c>
       <c r="B640" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -8215,7 +8224,7 @@
         <v>640</v>
       </c>
       <c r="B641" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -8223,7 +8232,7 @@
         <v>641</v>
       </c>
       <c r="B642" s="1">
-        <v>1400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -8239,7 +8248,7 @@
         <v>643</v>
       </c>
       <c r="B644" s="1">
-        <v>660</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -8247,7 +8256,7 @@
         <v>644</v>
       </c>
       <c r="B645" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -8255,7 +8264,7 @@
         <v>645</v>
       </c>
       <c r="B646" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -8263,7 +8272,7 @@
         <v>646</v>
       </c>
       <c r="B647" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -8271,7 +8280,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -8279,7 +8288,7 @@
         <v>648</v>
       </c>
       <c r="B649" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -8287,7 +8296,7 @@
         <v>649</v>
       </c>
       <c r="B650" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -8295,7 +8304,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -8303,7 +8312,7 @@
         <v>651</v>
       </c>
       <c r="B652" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -8311,7 +8320,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -8319,7 +8328,7 @@
         <v>653</v>
       </c>
       <c r="B654" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -8327,7 +8336,7 @@
         <v>654</v>
       </c>
       <c r="B655" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -8335,7 +8344,7 @@
         <v>655</v>
       </c>
       <c r="B656" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -8343,7 +8352,7 @@
         <v>656</v>
       </c>
       <c r="B657" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -8351,7 +8360,7 @@
         <v>657</v>
       </c>
       <c r="B658" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -8367,7 +8376,7 @@
         <v>659</v>
       </c>
       <c r="B660" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -8375,7 +8384,7 @@
         <v>660</v>
       </c>
       <c r="B661" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -8383,7 +8392,7 @@
         <v>661</v>
       </c>
       <c r="B662" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -8391,7 +8400,7 @@
         <v>662</v>
       </c>
       <c r="B663" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -8399,7 +8408,7 @@
         <v>663</v>
       </c>
       <c r="B664" s="1">
-        <v>4000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -8407,7 +8416,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -8415,7 +8424,7 @@
         <v>665</v>
       </c>
       <c r="B666" s="1">
-        <v>720</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -8423,7 +8432,7 @@
         <v>666</v>
       </c>
       <c r="B667" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -8431,7 +8440,7 @@
         <v>667</v>
       </c>
       <c r="B668" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -8439,7 +8448,7 @@
         <v>668</v>
       </c>
       <c r="B669" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -8447,7 +8456,7 @@
         <v>669</v>
       </c>
       <c r="B670" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -8455,7 +8464,7 @@
         <v>670</v>
       </c>
       <c r="B671" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -8463,7 +8472,7 @@
         <v>671</v>
       </c>
       <c r="B672" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -8471,7 +8480,7 @@
         <v>672</v>
       </c>
       <c r="B673" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -8479,7 +8488,7 @@
         <v>673</v>
       </c>
       <c r="B674" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -8487,7 +8496,7 @@
         <v>674</v>
       </c>
       <c r="B675" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8495,7 +8504,7 @@
         <v>675</v>
       </c>
       <c r="B676" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -8503,7 +8512,7 @@
         <v>676</v>
       </c>
       <c r="B677" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8519,7 +8528,7 @@
         <v>678</v>
       </c>
       <c r="B679" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8535,7 +8544,7 @@
         <v>680</v>
       </c>
       <c r="B681" s="1">
-        <v>980</v>
+        <v>900</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8543,7 +8552,7 @@
         <v>681</v>
       </c>
       <c r="B682" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8551,7 +8560,7 @@
         <v>682</v>
       </c>
       <c r="B683" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8559,7 +8568,7 @@
         <v>683</v>
       </c>
       <c r="B684" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8567,7 +8576,7 @@
         <v>684</v>
       </c>
       <c r="B685" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8575,7 +8584,7 @@
         <v>685</v>
       </c>
       <c r="B686" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8583,7 +8592,7 @@
         <v>686</v>
       </c>
       <c r="B687" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8591,7 +8600,7 @@
         <v>687</v>
       </c>
       <c r="B688" s="1">
-        <v>860</v>
+        <v>680</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8607,7 +8616,7 @@
         <v>689</v>
       </c>
       <c r="B690" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8623,7 +8632,7 @@
         <v>691</v>
       </c>
       <c r="B692" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8631,7 +8640,7 @@
         <v>692</v>
       </c>
       <c r="B693" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8639,7 +8648,7 @@
         <v>693</v>
       </c>
       <c r="B694" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8647,7 +8656,7 @@
         <v>694</v>
       </c>
       <c r="B695" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8655,7 +8664,7 @@
         <v>695</v>
       </c>
       <c r="B696" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8663,7 +8672,7 @@
         <v>696</v>
       </c>
       <c r="B697" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8671,7 +8680,7 @@
         <v>697</v>
       </c>
       <c r="B698" s="1">
-        <v>840</v>
+        <v>800</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8679,7 +8688,7 @@
         <v>698</v>
       </c>
       <c r="B699" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8687,7 +8696,7 @@
         <v>699</v>
       </c>
       <c r="B700" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8695,7 +8704,7 @@
         <v>700</v>
       </c>
       <c r="B701" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8703,7 +8712,7 @@
         <v>701</v>
       </c>
       <c r="B702" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8719,7 +8728,7 @@
         <v>703</v>
       </c>
       <c r="B704" s="1">
-        <v>880</v>
+        <v>640</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8727,7 +8736,7 @@
         <v>704</v>
       </c>
       <c r="B705" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8735,7 +8744,7 @@
         <v>705</v>
       </c>
       <c r="B706" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8743,7 +8752,7 @@
         <v>706</v>
       </c>
       <c r="B707" s="1">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8751,7 +8760,7 @@
         <v>707</v>
       </c>
       <c r="B708" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8767,7 +8776,7 @@
         <v>709</v>
       </c>
       <c r="B710" s="1">
-        <v>800</v>
+        <v>820</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8775,7 +8784,7 @@
         <v>710</v>
       </c>
       <c r="B711" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8791,7 +8800,7 @@
         <v>712</v>
       </c>
       <c r="B713" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8799,7 +8808,7 @@
         <v>713</v>
       </c>
       <c r="B714" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8807,7 +8816,7 @@
         <v>714</v>
       </c>
       <c r="B715" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8815,7 +8824,7 @@
         <v>715</v>
       </c>
       <c r="B716" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8823,7 +8832,7 @@
         <v>716</v>
       </c>
       <c r="B717" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8831,7 +8840,7 @@
         <v>717</v>
       </c>
       <c r="B718" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8839,7 +8848,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="1">
-        <v>880</v>
+        <v>960</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8847,7 +8856,7 @@
         <v>719</v>
       </c>
       <c r="B720" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8855,7 +8864,7 @@
         <v>720</v>
       </c>
       <c r="B721" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8863,7 +8872,7 @@
         <v>721</v>
       </c>
       <c r="B722" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8871,7 +8880,7 @@
         <v>722</v>
       </c>
       <c r="B723" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8879,7 +8888,7 @@
         <v>723</v>
       </c>
       <c r="B724" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8887,7 +8896,7 @@
         <v>724</v>
       </c>
       <c r="B725" s="1">
-        <v>1020</v>
+        <v>640</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8903,7 +8912,7 @@
         <v>726</v>
       </c>
       <c r="B727" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8911,7 +8920,7 @@
         <v>727</v>
       </c>
       <c r="B728" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8919,7 +8928,7 @@
         <v>728</v>
       </c>
       <c r="B729" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8927,7 +8936,7 @@
         <v>729</v>
       </c>
       <c r="B730" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8935,7 +8944,7 @@
         <v>730</v>
       </c>
       <c r="B731" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8943,7 +8952,7 @@
         <v>731</v>
       </c>
       <c r="B732" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -8951,7 +8960,7 @@
         <v>732</v>
       </c>
       <c r="B733" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -8967,7 +8976,7 @@
         <v>734</v>
       </c>
       <c r="B735" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -8975,7 +8984,7 @@
         <v>735</v>
       </c>
       <c r="B736" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -8983,7 +8992,7 @@
         <v>736</v>
       </c>
       <c r="B737" s="1">
-        <v>680</v>
+        <v>820</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -8991,7 +9000,7 @@
         <v>737</v>
       </c>
       <c r="B738" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="739" spans="1:2">
@@ -8999,7 +9008,7 @@
         <v>738</v>
       </c>
       <c r="B739" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="740" spans="1:2">
@@ -9007,7 +9016,7 @@
         <v>739</v>
       </c>
       <c r="B740" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -9015,7 +9024,7 @@
         <v>740</v>
       </c>
       <c r="B741" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="742" spans="1:2">
@@ -9023,7 +9032,7 @@
         <v>741</v>
       </c>
       <c r="B742" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -9039,7 +9048,7 @@
         <v>743</v>
       </c>
       <c r="B744" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="745" spans="1:2">
@@ -9047,7 +9056,7 @@
         <v>744</v>
       </c>
       <c r="B745" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -9055,7 +9064,7 @@
         <v>745</v>
       </c>
       <c r="B746" s="1">
-        <v>1100</v>
+        <v>840</v>
       </c>
     </row>
     <row r="747" spans="1:2">
@@ -9063,7 +9072,7 @@
         <v>746</v>
       </c>
       <c r="B747" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="748" spans="1:2">
@@ -9071,7 +9080,7 @@
         <v>747</v>
       </c>
       <c r="B748" s="1">
-        <v>940</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="749" spans="1:2">
@@ -9079,7 +9088,7 @@
         <v>748</v>
       </c>
       <c r="B749" s="1">
-        <v>820</v>
+        <v>940</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -9087,7 +9096,7 @@
         <v>749</v>
       </c>
       <c r="B750" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="751" spans="1:2">
@@ -9095,7 +9104,7 @@
         <v>750</v>
       </c>
       <c r="B751" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="752" spans="1:2">
@@ -9103,7 +9112,7 @@
         <v>751</v>
       </c>
       <c r="B752" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="753" spans="1:2">
@@ -9111,7 +9120,7 @@
         <v>752</v>
       </c>
       <c r="B753" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="754" spans="1:2">
@@ -9119,7 +9128,7 @@
         <v>753</v>
       </c>
       <c r="B754" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -9127,7 +9136,7 @@
         <v>754</v>
       </c>
       <c r="B755" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="756" spans="1:2">
@@ -9135,7 +9144,7 @@
         <v>755</v>
       </c>
       <c r="B756" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="757" spans="1:2">
@@ -9151,7 +9160,7 @@
         <v>757</v>
       </c>
       <c r="B758" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="759" spans="1:2">
@@ -9159,7 +9168,7 @@
         <v>758</v>
       </c>
       <c r="B759" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="760" spans="1:2">
@@ -9167,7 +9176,7 @@
         <v>759</v>
       </c>
       <c r="B760" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="761" spans="1:2">
@@ -9175,7 +9184,7 @@
         <v>760</v>
       </c>
       <c r="B761" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="762" spans="1:2">
@@ -9183,7 +9192,7 @@
         <v>761</v>
       </c>
       <c r="B762" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="763" spans="1:2">
@@ -9191,7 +9200,7 @@
         <v>762</v>
       </c>
       <c r="B763" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="764" spans="1:2">
@@ -9207,7 +9216,7 @@
         <v>764</v>
       </c>
       <c r="B765" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="766" spans="1:2">
@@ -9215,7 +9224,7 @@
         <v>765</v>
       </c>
       <c r="B766" s="1">
-        <v>440</v>
+        <v>900</v>
       </c>
     </row>
     <row r="767" spans="1:2">
@@ -9223,7 +9232,7 @@
         <v>766</v>
       </c>
       <c r="B767" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="768" spans="1:2">
@@ -9231,7 +9240,7 @@
         <v>767</v>
       </c>
       <c r="B768" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="769" spans="1:2">
@@ -9239,7 +9248,7 @@
         <v>768</v>
       </c>
       <c r="B769" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="770" spans="1:2">
@@ -9247,7 +9256,7 @@
         <v>769</v>
       </c>
       <c r="B770" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="771" spans="1:2">
@@ -9255,7 +9264,7 @@
         <v>770</v>
       </c>
       <c r="B771" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="772" spans="1:2">
@@ -9263,7 +9272,7 @@
         <v>771</v>
       </c>
       <c r="B772" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="773" spans="1:2">
@@ -9271,7 +9280,7 @@
         <v>772</v>
       </c>
       <c r="B773" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="774" spans="1:2">
@@ -9279,7 +9288,7 @@
         <v>773</v>
       </c>
       <c r="B774" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="775" spans="1:2">
@@ -9287,7 +9296,7 @@
         <v>774</v>
       </c>
       <c r="B775" s="1">
-        <v>880</v>
+        <v>560</v>
       </c>
     </row>
     <row r="776" spans="1:2">
@@ -9295,7 +9304,7 @@
         <v>775</v>
       </c>
       <c r="B776" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="777" spans="1:2">
@@ -9303,7 +9312,7 @@
         <v>776</v>
       </c>
       <c r="B777" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="778" spans="1:2">
@@ -9311,7 +9320,7 @@
         <v>777</v>
       </c>
       <c r="B778" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="779" spans="1:2">
@@ -9319,7 +9328,7 @@
         <v>778</v>
       </c>
       <c r="B779" s="1">
-        <v>920</v>
+        <v>800</v>
       </c>
     </row>
     <row r="780" spans="1:2">
@@ -9327,7 +9336,7 @@
         <v>779</v>
       </c>
       <c r="B780" s="1">
-        <v>800</v>
+        <v>880</v>
       </c>
     </row>
     <row r="781" spans="1:2">
@@ -9335,7 +9344,7 @@
         <v>780</v>
       </c>
       <c r="B781" s="1">
-        <v>940</v>
+        <v>780</v>
       </c>
     </row>
     <row r="782" spans="1:2">
@@ -9343,7 +9352,7 @@
         <v>781</v>
       </c>
       <c r="B782" s="1">
-        <v>980</v>
+        <v>920</v>
       </c>
     </row>
     <row r="783" spans="1:2">
@@ -9351,7 +9360,7 @@
         <v>782</v>
       </c>
       <c r="B783" s="1">
-        <v>920</v>
+        <v>800</v>
       </c>
     </row>
     <row r="784" spans="1:2">
@@ -9359,7 +9368,7 @@
         <v>783</v>
       </c>
       <c r="B784" s="1">
-        <v>780</v>
+        <v>940</v>
       </c>
     </row>
     <row r="785" spans="1:2">
@@ -9367,7 +9376,7 @@
         <v>784</v>
       </c>
       <c r="B785" s="1">
-        <v>860</v>
+        <v>980</v>
       </c>
     </row>
     <row r="786" spans="1:2">
@@ -9383,7 +9392,7 @@
         <v>786</v>
       </c>
       <c r="B787" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="788" spans="1:2">
@@ -9391,7 +9400,7 @@
         <v>787</v>
       </c>
       <c r="B788" s="1">
-        <v>820</v>
+        <v>860</v>
       </c>
     </row>
     <row r="789" spans="1:2">
@@ -9399,7 +9408,7 @@
         <v>788</v>
       </c>
       <c r="B789" s="1">
-        <v>960</v>
+        <v>920</v>
       </c>
     </row>
     <row r="790" spans="1:2">
@@ -9407,7 +9416,7 @@
         <v>789</v>
       </c>
       <c r="B790" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="791" spans="1:2">
@@ -9415,7 +9424,7 @@
         <v>790</v>
       </c>
       <c r="B791" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="792" spans="1:2">
@@ -9423,7 +9432,7 @@
         <v>791</v>
       </c>
       <c r="B792" s="1">
-        <v>860</v>
+        <v>960</v>
       </c>
     </row>
     <row r="793" spans="1:2">
@@ -9431,7 +9440,7 @@
         <v>792</v>
       </c>
       <c r="B793" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="794" spans="1:2">
@@ -9439,7 +9448,7 @@
         <v>793</v>
       </c>
       <c r="B794" s="1">
-        <v>660</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="795" spans="1:2">
@@ -9447,7 +9456,7 @@
         <v>794</v>
       </c>
       <c r="B795" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="796" spans="1:2">
@@ -9463,7 +9472,7 @@
         <v>796</v>
       </c>
       <c r="B797" s="1">
-        <v>820</v>
+        <v>660</v>
       </c>
     </row>
     <row r="798" spans="1:2">
@@ -9471,7 +9480,7 @@
         <v>797</v>
       </c>
       <c r="B798" s="1">
-        <v>760</v>
+        <v>840</v>
       </c>
     </row>
     <row r="799" spans="1:2">
@@ -9479,7 +9488,7 @@
         <v>798</v>
       </c>
       <c r="B799" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="800" spans="1:2">
@@ -9487,7 +9496,7 @@
         <v>799</v>
       </c>
       <c r="B800" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="801" spans="1:2">
@@ -9495,7 +9504,7 @@
         <v>800</v>
       </c>
       <c r="B801" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="802" spans="1:2">
@@ -9503,7 +9512,7 @@
         <v>801</v>
       </c>
       <c r="B802" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="803" spans="1:2">
@@ -9511,7 +9520,7 @@
         <v>802</v>
       </c>
       <c r="B803" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="804" spans="1:2">
@@ -9519,7 +9528,7 @@
         <v>803</v>
       </c>
       <c r="B804" s="1">
-        <v>740</v>
+        <v>600</v>
       </c>
     </row>
     <row r="805" spans="1:2">
@@ -9527,7 +9536,7 @@
         <v>804</v>
       </c>
       <c r="B805" s="1">
-        <v>760</v>
+        <v>840</v>
       </c>
     </row>
     <row r="806" spans="1:2">
@@ -9535,7 +9544,7 @@
         <v>805</v>
       </c>
       <c r="B806" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="807" spans="1:2">
@@ -9543,7 +9552,7 @@
         <v>806</v>
       </c>
       <c r="B807" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="808" spans="1:2">
@@ -9551,7 +9560,7 @@
         <v>807</v>
       </c>
       <c r="B808" s="1">
-        <v>800</v>
+        <v>760</v>
       </c>
     </row>
     <row r="809" spans="1:2">
@@ -9559,7 +9568,7 @@
         <v>808</v>
       </c>
       <c r="B809" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="810" spans="1:2">
@@ -9567,7 +9576,7 @@
         <v>809</v>
       </c>
       <c r="B810" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="811" spans="1:2">
@@ -9575,7 +9584,7 @@
         <v>810</v>
       </c>
       <c r="B811" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="812" spans="1:2">
@@ -9583,7 +9592,7 @@
         <v>811</v>
       </c>
       <c r="B812" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="813" spans="1:2">
@@ -9591,7 +9600,7 @@
         <v>812</v>
       </c>
       <c r="B813" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="814" spans="1:2">
@@ -9599,7 +9608,7 @@
         <v>813</v>
       </c>
       <c r="B814" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="815" spans="1:2">
@@ -9607,7 +9616,7 @@
         <v>814</v>
       </c>
       <c r="B815" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="816" spans="1:2">
@@ -9615,7 +9624,7 @@
         <v>815</v>
       </c>
       <c r="B816" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="817" spans="1:2">
@@ -9623,7 +9632,7 @@
         <v>816</v>
       </c>
       <c r="B817" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="818" spans="1:2">
@@ -9631,7 +9640,7 @@
         <v>817</v>
       </c>
       <c r="B818" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="819" spans="1:2">
@@ -9639,7 +9648,7 @@
         <v>818</v>
       </c>
       <c r="B819" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="820" spans="1:2">
@@ -9647,7 +9656,7 @@
         <v>819</v>
       </c>
       <c r="B820" s="1">
-        <v>920</v>
+        <v>600</v>
       </c>
     </row>
     <row r="821" spans="1:2">
@@ -9655,7 +9664,7 @@
         <v>820</v>
       </c>
       <c r="B821" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="822" spans="1:2">
@@ -9663,7 +9672,7 @@
         <v>821</v>
       </c>
       <c r="B822" s="1">
-        <v>940</v>
+        <v>760</v>
       </c>
     </row>
     <row r="823" spans="1:2">
@@ -9671,7 +9680,7 @@
         <v>822</v>
       </c>
       <c r="B823" s="1">
-        <v>1040</v>
+        <v>920</v>
       </c>
     </row>
     <row r="824" spans="1:2">
@@ -9679,7 +9688,7 @@
         <v>823</v>
       </c>
       <c r="B824" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="825" spans="1:2">
@@ -9687,7 +9696,7 @@
         <v>824</v>
       </c>
       <c r="B825" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="826" spans="1:2">
@@ -9703,7 +9712,7 @@
         <v>826</v>
       </c>
       <c r="B827" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="828" spans="1:2">
@@ -9711,7 +9720,7 @@
         <v>827</v>
       </c>
       <c r="B828" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="829" spans="1:2">
@@ -9719,7 +9728,7 @@
         <v>828</v>
       </c>
       <c r="B829" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="830" spans="1:2">
@@ -9727,7 +9736,7 @@
         <v>829</v>
       </c>
       <c r="B830" s="1">
-        <v>960</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="831" spans="1:2">
@@ -9735,7 +9744,7 @@
         <v>830</v>
       </c>
       <c r="B831" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="832" spans="1:2">
@@ -9743,7 +9752,7 @@
         <v>831</v>
       </c>
       <c r="B832" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="833" spans="1:2">
@@ -9751,7 +9760,7 @@
         <v>832</v>
       </c>
       <c r="B833" s="1">
-        <v>820</v>
+        <v>960</v>
       </c>
     </row>
     <row r="834" spans="1:2">
@@ -9759,7 +9768,7 @@
         <v>833</v>
       </c>
       <c r="B834" s="1">
-        <v>440</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="835" spans="1:2">
@@ -9767,7 +9776,7 @@
         <v>834</v>
       </c>
       <c r="B835" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="836" spans="1:2">
@@ -9775,7 +9784,7 @@
         <v>835</v>
       </c>
       <c r="B836" s="1">
-        <v>440</v>
+        <v>820</v>
       </c>
     </row>
     <row r="837" spans="1:2">
@@ -9783,7 +9792,7 @@
         <v>836</v>
       </c>
       <c r="B837" s="1">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="838" spans="1:2">
@@ -9799,7 +9808,7 @@
         <v>838</v>
       </c>
       <c r="B839" s="1">
-        <v>820</v>
+        <v>440</v>
       </c>
     </row>
     <row r="840" spans="1:2">
@@ -9807,7 +9816,7 @@
         <v>839</v>
       </c>
       <c r="B840" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="841" spans="1:2">
@@ -9815,7 +9824,7 @@
         <v>840</v>
       </c>
       <c r="B841" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="842" spans="1:2">
@@ -9823,7 +9832,7 @@
         <v>841</v>
       </c>
       <c r="B842" s="1">
-        <v>840</v>
+        <v>820</v>
       </c>
     </row>
     <row r="843" spans="1:2">
@@ -9831,7 +9840,7 @@
         <v>842</v>
       </c>
       <c r="B843" s="1">
-        <v>400</v>
+        <v>820</v>
       </c>
     </row>
     <row r="844" spans="1:2">
@@ -9839,7 +9848,7 @@
         <v>843</v>
       </c>
       <c r="B844" s="1">
-        <v>400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="845" spans="1:2">
@@ -9847,7 +9856,7 @@
         <v>844</v>
       </c>
       <c r="B845" s="1">
-        <v>380</v>
+        <v>840</v>
       </c>
     </row>
     <row r="846" spans="1:2">
@@ -9855,7 +9864,7 @@
         <v>845</v>
       </c>
       <c r="B846" s="1">
-        <v>840</v>
+        <v>400</v>
       </c>
     </row>
     <row r="847" spans="1:2">
@@ -9863,7 +9872,7 @@
         <v>846</v>
       </c>
       <c r="B847" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="848" spans="1:2">
@@ -9879,7 +9888,7 @@
         <v>848</v>
       </c>
       <c r="B849" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="850" spans="1:2">
@@ -9887,7 +9896,7 @@
         <v>849</v>
       </c>
       <c r="B850" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="851" spans="1:2">
@@ -9895,7 +9904,7 @@
         <v>850</v>
       </c>
       <c r="B851" s="1">
-        <v>800</v>
+        <v>380</v>
       </c>
     </row>
     <row r="852" spans="1:2">
@@ -9903,7 +9912,7 @@
         <v>851</v>
       </c>
       <c r="B852" s="1">
-        <v>860</v>
+        <v>520</v>
       </c>
     </row>
     <row r="853" spans="1:2">
@@ -9911,7 +9920,7 @@
         <v>852</v>
       </c>
       <c r="B853" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="854" spans="1:2">
@@ -9919,7 +9928,7 @@
         <v>853</v>
       </c>
       <c r="B854" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="855" spans="1:2">
@@ -9927,7 +9936,7 @@
         <v>854</v>
       </c>
       <c r="B855" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="856" spans="1:2">
@@ -9935,7 +9944,7 @@
         <v>855</v>
       </c>
       <c r="B856" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="857" spans="1:2">
@@ -9943,7 +9952,7 @@
         <v>856</v>
       </c>
       <c r="B857" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="858" spans="1:2">
@@ -9951,7 +9960,7 @@
         <v>857</v>
       </c>
       <c r="B858" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="859" spans="1:2">
@@ -9959,7 +9968,7 @@
         <v>858</v>
       </c>
       <c r="B859" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="860" spans="1:2">
@@ -9967,7 +9976,7 @@
         <v>859</v>
       </c>
       <c r="B860" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="861" spans="1:2">
@@ -9975,7 +9984,7 @@
         <v>860</v>
       </c>
       <c r="B861" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="862" spans="1:2">
@@ -9983,7 +9992,7 @@
         <v>861</v>
       </c>
       <c r="B862" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="863" spans="1:2">
@@ -9991,7 +10000,7 @@
         <v>862</v>
       </c>
       <c r="B863" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="864" spans="1:2">
@@ -9999,7 +10008,7 @@
         <v>863</v>
       </c>
       <c r="B864" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="865" spans="1:2">
@@ -10007,7 +10016,7 @@
         <v>864</v>
       </c>
       <c r="B865" s="1">
-        <v>900</v>
+        <v>500</v>
       </c>
     </row>
     <row r="866" spans="1:2">
@@ -10015,7 +10024,7 @@
         <v>865</v>
       </c>
       <c r="B866" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="867" spans="1:2">
@@ -10023,7 +10032,7 @@
         <v>866</v>
       </c>
       <c r="B867" s="1">
-        <v>920</v>
+        <v>840</v>
       </c>
     </row>
     <row r="868" spans="1:2">
@@ -10031,7 +10040,7 @@
         <v>867</v>
       </c>
       <c r="B868" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="869" spans="1:2">
@@ -10039,7 +10048,7 @@
         <v>868</v>
       </c>
       <c r="B869" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="870" spans="1:2">
@@ -10047,7 +10056,7 @@
         <v>869</v>
       </c>
       <c r="B870" s="1">
-        <v>1040</v>
+        <v>920</v>
       </c>
     </row>
     <row r="871" spans="1:2">
@@ -10055,7 +10064,7 @@
         <v>870</v>
       </c>
       <c r="B871" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="872" spans="1:2">
@@ -10063,7 +10072,7 @@
         <v>871</v>
       </c>
       <c r="B872" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="873" spans="1:2">
@@ -10079,7 +10088,7 @@
         <v>873</v>
       </c>
       <c r="B874" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="875" spans="1:2">
@@ -10087,7 +10096,7 @@
         <v>874</v>
       </c>
       <c r="B875" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="876" spans="1:2">
@@ -10095,7 +10104,7 @@
         <v>875</v>
       </c>
       <c r="B876" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="877" spans="1:2">
@@ -10103,7 +10112,7 @@
         <v>876</v>
       </c>
       <c r="B877" s="1">
-        <v>960</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="878" spans="1:2">
@@ -10111,7 +10120,7 @@
         <v>877</v>
       </c>
       <c r="B878" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="879" spans="1:2">
@@ -10119,7 +10128,7 @@
         <v>878</v>
       </c>
       <c r="B879" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="880" spans="1:2">
@@ -10127,7 +10136,7 @@
         <v>879</v>
       </c>
       <c r="B880" s="1">
-        <v>820</v>
+        <v>960</v>
       </c>
     </row>
     <row r="881" spans="1:2">
@@ -10135,7 +10144,7 @@
         <v>880</v>
       </c>
       <c r="B881" s="1">
-        <v>440</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="882" spans="1:2">
@@ -10143,7 +10152,7 @@
         <v>881</v>
       </c>
       <c r="B882" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="883" spans="1:2">
@@ -10151,7 +10160,7 @@
         <v>882</v>
       </c>
       <c r="B883" s="1">
-        <v>440</v>
+        <v>820</v>
       </c>
     </row>
     <row r="884" spans="1:2">
@@ -10159,7 +10168,7 @@
         <v>883</v>
       </c>
       <c r="B884" s="1">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="885" spans="1:2">
@@ -10175,7 +10184,7 @@
         <v>885</v>
       </c>
       <c r="B886" s="1">
-        <v>820</v>
+        <v>440</v>
       </c>
     </row>
     <row r="887" spans="1:2">
@@ -10183,7 +10192,7 @@
         <v>886</v>
       </c>
       <c r="B887" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="888" spans="1:2">
@@ -10191,7 +10200,7 @@
         <v>887</v>
       </c>
       <c r="B888" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="889" spans="1:2">
@@ -10199,7 +10208,7 @@
         <v>888</v>
       </c>
       <c r="B889" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="890" spans="1:2">
@@ -10207,7 +10216,7 @@
         <v>889</v>
       </c>
       <c r="B890" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="891" spans="1:2">
@@ -10215,7 +10224,7 @@
         <v>890</v>
       </c>
       <c r="B891" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="892" spans="1:2">
@@ -10223,7 +10232,7 @@
         <v>891</v>
       </c>
       <c r="B892" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="893" spans="1:2">
@@ -10231,7 +10240,7 @@
         <v>892</v>
       </c>
       <c r="B893" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="894" spans="1:2">
@@ -10239,7 +10248,7 @@
         <v>893</v>
       </c>
       <c r="B894" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="895" spans="1:2">
@@ -10247,7 +10256,7 @@
         <v>894</v>
       </c>
       <c r="B895" s="1">
-        <v>440</v>
+        <v>480</v>
       </c>
     </row>
     <row r="896" spans="1:2">
@@ -10255,7 +10264,7 @@
         <v>895</v>
       </c>
       <c r="B896" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="897" spans="1:2">
@@ -10263,7 +10272,7 @@
         <v>896</v>
       </c>
       <c r="B897" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="898" spans="1:2">
@@ -10271,7 +10280,7 @@
         <v>897</v>
       </c>
       <c r="B898" s="1">
-        <v>820</v>
+        <v>440</v>
       </c>
     </row>
     <row r="899" spans="1:2">
@@ -10279,7 +10288,7 @@
         <v>898</v>
       </c>
       <c r="B899" s="1">
-        <v>660</v>
+        <v>380</v>
       </c>
     </row>
     <row r="900" spans="1:2">
@@ -10287,7 +10296,7 @@
         <v>899</v>
       </c>
       <c r="B900" s="1">
-        <v>580</v>
+        <v>600</v>
       </c>
     </row>
     <row r="901" spans="1:2">
@@ -10295,7 +10304,7 @@
         <v>900</v>
       </c>
       <c r="B901" s="1">
-        <v>560</v>
+        <v>820</v>
       </c>
     </row>
     <row r="902" spans="1:2">
@@ -10303,7 +10312,7 @@
         <v>901</v>
       </c>
       <c r="B902" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="903" spans="1:2">
@@ -10311,7 +10320,7 @@
         <v>902</v>
       </c>
       <c r="B903" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="904" spans="1:2">
@@ -10327,6 +10336,30 @@
         <v>904</v>
       </c>
       <c r="B905" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="906" spans="1:2">
+      <c r="A906" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="B906" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="907" spans="1:2">
+      <c r="A907" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="B907" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="908" spans="1:2">
+      <c r="A908" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="B908" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="913">
   <si>
     <t>Наименование</t>
   </si>
@@ -497,6 +497,9 @@
     <t>Jaws, APA, Розлив, Россия</t>
   </si>
   <si>
+    <t>Jungle - Azacca One Love (Session NEIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Jungle - Body Flow (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -506,6 +509,9 @@
     <t>Jungle - Hired Gun (APA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Jungle - NU BREED (American IPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Jungle - Rising High (AIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -986,6 +992,9 @@
     <t>Saliwa - Михалыч (DIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Saliwa - НИГИЛИСТ (NEDIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Saliwa - ПАНАМА (Hazy IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1826,10 +1835,16 @@
     <t>вынос_Jaws - Nitro Stout, РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Jungle - Azacca One Love (Session NEIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Jungle - Body Flow (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_Jungle - Hired Gun (APA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Jungle - NU BREED (American IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_Jungle - Rising High (AIPA), РОЗЛИВ, Россия</t>
@@ -3092,7 +3107,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B908"/>
+  <dimension ref="A1:B913"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -4376,7 +4391,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>1100</v>
+        <v>980</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -4384,7 +4399,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>1060</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -4400,7 +4415,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>1100</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -4408,7 +4423,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -4416,7 +4431,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -4424,7 +4439,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>1080</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -4432,20 +4447,20 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>840</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B169" s="1">
         <v>840</v>
@@ -4456,7 +4471,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="1">
-        <v>420</v>
+        <v>840</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -4464,7 +4479,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -4472,7 +4487,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="1">
-        <v>720</v>
+        <v>420</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4480,7 +4495,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="1">
-        <v>460</v>
+        <v>520</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4488,7 +4503,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4496,7 +4511,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4504,7 +4519,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4512,7 +4527,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4520,7 +4535,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="1">
-        <v>520</v>
+        <v>740</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4528,7 +4543,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="1">
-        <v>980</v>
+        <v>620</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4536,7 +4551,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4544,7 +4559,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="1">
-        <v>580</v>
+        <v>980</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4552,7 +4567,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="1">
-        <v>740</v>
+        <v>540</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4560,7 +4575,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="1">
-        <v>760</v>
+        <v>580</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4568,7 +4583,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="1">
-        <v>560</v>
+        <v>740</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4576,7 +4591,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4584,7 +4599,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="1">
-        <v>1100</v>
+        <v>560</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4608,7 +4623,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4616,7 +4631,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="1">
-        <v>640</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4632,7 +4647,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="1">
-        <v>920</v>
+        <v>640</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4640,7 +4655,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4664,7 +4679,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4672,7 +4687,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4680,7 +4695,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4688,7 +4703,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4696,7 +4711,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="1">
-        <v>840</v>
+        <v>960</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4704,7 +4719,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4712,7 +4727,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4720,7 +4735,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="1">
-        <v>980</v>
+        <v>900</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4728,7 +4743,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="1">
-        <v>460</v>
+        <v>700</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4736,7 +4751,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="1">
-        <v>580</v>
+        <v>980</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4744,7 +4759,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="1">
-        <v>720</v>
+        <v>460</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4752,7 +4767,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="1">
-        <v>660</v>
+        <v>580</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4760,7 +4775,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4768,7 +4783,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="1">
-        <v>260</v>
+        <v>660</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4776,7 +4791,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="1">
-        <v>260</v>
+        <v>780</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4784,7 +4799,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4792,7 +4807,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4800,7 +4815,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4808,7 +4823,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4816,7 +4831,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4824,7 +4839,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4832,7 +4847,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="1">
-        <v>400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4840,7 +4855,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="1">
-        <v>740</v>
+        <v>500</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4848,7 +4863,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="1">
-        <v>680</v>
+        <v>400</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4856,7 +4871,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4864,7 +4879,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="1">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4872,7 +4887,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4880,7 +4895,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="1">
-        <v>680</v>
+        <v>620</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4888,7 +4903,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4896,7 +4911,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4904,7 +4919,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4912,7 +4927,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4920,7 +4935,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="1">
-        <v>580</v>
+        <v>620</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4928,7 +4943,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="1">
-        <v>860</v>
+        <v>520</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4944,7 +4959,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="1">
-        <v>620</v>
+        <v>860</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4952,7 +4967,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4960,7 +4975,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4968,7 +4983,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4976,7 +4991,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4984,7 +4999,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4992,7 +5007,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="1">
-        <v>700</v>
+        <v>580</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -5000,7 +5015,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="1">
-        <v>820</v>
+        <v>540</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -5008,7 +5023,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -5016,7 +5031,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -5024,7 +5039,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -5032,7 +5047,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="1">
-        <v>1400</v>
+        <v>720</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -5040,7 +5055,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="1">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -5048,7 +5063,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="1">
-        <v>720</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -5056,7 +5071,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="1">
-        <v>660</v>
+        <v>480</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -5064,7 +5079,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -5072,7 +5087,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -5080,7 +5095,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="1">
-        <v>740</v>
+        <v>600</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -5088,7 +5103,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -5096,7 +5111,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -5104,7 +5119,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="1">
-        <v>520</v>
+        <v>720</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -5112,7 +5127,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -5120,7 +5135,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -5128,7 +5143,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="1">
-        <v>620</v>
+        <v>900</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -5136,7 +5151,7 @@
         <v>254</v>
       </c>
       <c r="B255" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -5152,7 +5167,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -5160,7 +5175,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -5168,7 +5183,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -5176,7 +5191,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -5184,7 +5199,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -5192,7 +5207,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -5200,7 +5215,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -5216,7 +5231,7 @@
         <v>264</v>
       </c>
       <c r="B265" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -5224,7 +5239,7 @@
         <v>265</v>
       </c>
       <c r="B266" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -5232,7 +5247,7 @@
         <v>266</v>
       </c>
       <c r="B267" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -5240,7 +5255,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -5248,7 +5263,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -5264,7 +5279,7 @@
         <v>270</v>
       </c>
       <c r="B271" s="1">
-        <v>560</v>
+        <v>820</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -5280,7 +5295,7 @@
         <v>272</v>
       </c>
       <c r="B273" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -5288,7 +5303,7 @@
         <v>273</v>
       </c>
       <c r="B274" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -5296,7 +5311,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -5304,7 +5319,7 @@
         <v>275</v>
       </c>
       <c r="B276" s="1">
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -5312,7 +5327,7 @@
         <v>276</v>
       </c>
       <c r="B277" s="1">
-        <v>500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -5320,7 +5335,7 @@
         <v>277</v>
       </c>
       <c r="B278" s="1">
-        <v>758</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -5328,7 +5343,7 @@
         <v>278</v>
       </c>
       <c r="B279" s="1">
-        <v>2273</v>
+        <v>500</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -5336,7 +5351,7 @@
         <v>279</v>
       </c>
       <c r="B280" s="1">
-        <v>1515</v>
+        <v>758</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -5344,7 +5359,7 @@
         <v>280</v>
       </c>
       <c r="B281" s="1">
-        <v>520</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -5352,7 +5367,7 @@
         <v>281</v>
       </c>
       <c r="B282" s="1">
-        <v>4000</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -5360,7 +5375,7 @@
         <v>282</v>
       </c>
       <c r="B283" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -5368,7 +5383,7 @@
         <v>283</v>
       </c>
       <c r="B284" s="1">
-        <v>480</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -5376,7 +5391,7 @@
         <v>284</v>
       </c>
       <c r="B285" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -5384,7 +5399,7 @@
         <v>285</v>
       </c>
       <c r="B286" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5392,7 +5407,7 @@
         <v>286</v>
       </c>
       <c r="B287" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5400,7 +5415,7 @@
         <v>287</v>
       </c>
       <c r="B288" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5408,7 +5423,7 @@
         <v>288</v>
       </c>
       <c r="B289" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5416,7 +5431,7 @@
         <v>289</v>
       </c>
       <c r="B290" s="1">
-        <v>580</v>
+        <v>840</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5424,7 +5439,7 @@
         <v>290</v>
       </c>
       <c r="B291" s="1">
-        <v>520</v>
+        <v>700</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5432,7 +5447,7 @@
         <v>291</v>
       </c>
       <c r="B292" s="1">
-        <v>680</v>
+        <v>580</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5440,7 +5455,7 @@
         <v>292</v>
       </c>
       <c r="B293" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5448,7 +5463,7 @@
         <v>293</v>
       </c>
       <c r="B294" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5456,7 +5471,7 @@
         <v>294</v>
       </c>
       <c r="B295" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5464,7 +5479,7 @@
         <v>295</v>
       </c>
       <c r="B296" s="1">
-        <v>380</v>
+        <v>580</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5472,7 +5487,7 @@
         <v>296</v>
       </c>
       <c r="B297" s="1">
-        <v>660</v>
+        <v>560</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5480,7 +5495,7 @@
         <v>297</v>
       </c>
       <c r="B298" s="1">
-        <v>900</v>
+        <v>380</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5488,7 +5503,7 @@
         <v>298</v>
       </c>
       <c r="B299" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5496,7 +5511,7 @@
         <v>299</v>
       </c>
       <c r="B300" s="1">
-        <v>520</v>
+        <v>900</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5504,7 +5519,7 @@
         <v>300</v>
       </c>
       <c r="B301" s="1">
-        <v>660</v>
+        <v>540</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5512,7 +5527,7 @@
         <v>301</v>
       </c>
       <c r="B302" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5520,7 +5535,7 @@
         <v>302</v>
       </c>
       <c r="B303" s="1">
-        <v>460</v>
+        <v>660</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5528,7 +5543,7 @@
         <v>303</v>
       </c>
       <c r="B304" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5536,7 +5551,7 @@
         <v>304</v>
       </c>
       <c r="B305" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5544,7 +5559,7 @@
         <v>305</v>
       </c>
       <c r="B306" s="1">
-        <v>900</v>
+        <v>520</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5552,7 +5567,7 @@
         <v>306</v>
       </c>
       <c r="B307" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5568,7 +5583,7 @@
         <v>308</v>
       </c>
       <c r="B309" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5584,7 +5599,7 @@
         <v>310</v>
       </c>
       <c r="B311" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5592,7 +5607,7 @@
         <v>311</v>
       </c>
       <c r="B312" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5600,7 +5615,7 @@
         <v>312</v>
       </c>
       <c r="B313" s="1">
-        <v>980</v>
+        <v>560</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5608,7 +5623,7 @@
         <v>313</v>
       </c>
       <c r="B314" s="1">
-        <v>1000</v>
+        <v>560</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5616,7 +5631,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5624,7 +5639,7 @@
         <v>315</v>
       </c>
       <c r="B316" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5632,7 +5647,7 @@
         <v>316</v>
       </c>
       <c r="B317" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5640,7 +5655,7 @@
         <v>317</v>
       </c>
       <c r="B318" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5648,7 +5663,7 @@
         <v>318</v>
       </c>
       <c r="B319" s="1">
-        <v>680</v>
+        <v>940</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5656,7 +5671,7 @@
         <v>319</v>
       </c>
       <c r="B320" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5664,7 +5679,7 @@
         <v>320</v>
       </c>
       <c r="B321" s="1">
-        <v>840</v>
+        <v>680</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5672,7 +5687,7 @@
         <v>321</v>
       </c>
       <c r="B322" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5680,7 +5695,7 @@
         <v>322</v>
       </c>
       <c r="B323" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5688,7 +5703,7 @@
         <v>323</v>
       </c>
       <c r="B324" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5704,7 +5719,7 @@
         <v>325</v>
       </c>
       <c r="B326" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5712,7 +5727,7 @@
         <v>326</v>
       </c>
       <c r="B327" s="1">
-        <v>1020</v>
+        <v>840</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5728,7 +5743,7 @@
         <v>328</v>
       </c>
       <c r="B329" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5736,7 +5751,7 @@
         <v>329</v>
       </c>
       <c r="B330" s="1">
-        <v>680</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5744,7 +5759,7 @@
         <v>330</v>
       </c>
       <c r="B331" s="1">
-        <v>520</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5752,7 +5767,7 @@
         <v>331</v>
       </c>
       <c r="B332" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5760,7 +5775,7 @@
         <v>332</v>
       </c>
       <c r="B333" s="1">
-        <v>800</v>
+        <v>680</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5768,7 +5783,7 @@
         <v>333</v>
       </c>
       <c r="B334" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5776,7 +5791,7 @@
         <v>334</v>
       </c>
       <c r="B335" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5784,7 +5799,7 @@
         <v>335</v>
       </c>
       <c r="B336" s="1">
-        <v>840</v>
+        <v>800</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5792,7 +5807,7 @@
         <v>336</v>
       </c>
       <c r="B337" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5800,7 +5815,7 @@
         <v>337</v>
       </c>
       <c r="B338" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5808,7 +5823,7 @@
         <v>338</v>
       </c>
       <c r="B339" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5816,7 +5831,7 @@
         <v>339</v>
       </c>
       <c r="B340" s="1">
-        <v>720</v>
+        <v>580</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5832,7 +5847,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5840,7 +5855,7 @@
         <v>342</v>
       </c>
       <c r="B343" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5848,7 +5863,7 @@
         <v>343</v>
       </c>
       <c r="B344" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5856,7 +5871,7 @@
         <v>344</v>
       </c>
       <c r="B345" s="1">
-        <v>520</v>
+        <v>720</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5864,7 +5879,7 @@
         <v>345</v>
       </c>
       <c r="B346" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5872,7 +5887,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="1">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5880,7 +5895,7 @@
         <v>347</v>
       </c>
       <c r="B348" s="1">
-        <v>820</v>
+        <v>520</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5888,7 +5903,7 @@
         <v>348</v>
       </c>
       <c r="B349" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5896,7 +5911,7 @@
         <v>349</v>
       </c>
       <c r="B350" s="1">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5904,7 +5919,7 @@
         <v>350</v>
       </c>
       <c r="B351" s="1">
-        <v>520</v>
+        <v>820</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5912,7 +5927,7 @@
         <v>351</v>
       </c>
       <c r="B352" s="1">
-        <v>320</v>
+        <v>600</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5920,7 +5935,7 @@
         <v>352</v>
       </c>
       <c r="B353" s="1">
-        <v>540</v>
+        <v>380</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5928,7 +5943,7 @@
         <v>353</v>
       </c>
       <c r="B354" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5936,7 +5951,7 @@
         <v>354</v>
       </c>
       <c r="B355" s="1">
-        <v>480</v>
+        <v>320</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5944,7 +5959,7 @@
         <v>355</v>
       </c>
       <c r="B356" s="1">
-        <v>480</v>
+        <v>540</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5952,7 +5967,7 @@
         <v>356</v>
       </c>
       <c r="B357" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5960,7 +5975,7 @@
         <v>357</v>
       </c>
       <c r="B358" s="1">
-        <v>500</v>
+        <v>480</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5968,7 +5983,7 @@
         <v>358</v>
       </c>
       <c r="B359" s="1">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5976,7 +5991,7 @@
         <v>359</v>
       </c>
       <c r="B360" s="1">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5984,7 +5999,7 @@
         <v>360</v>
       </c>
       <c r="B361" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5992,7 +6007,7 @@
         <v>361</v>
       </c>
       <c r="B362" s="1">
-        <v>520</v>
+        <v>800</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -6000,7 +6015,7 @@
         <v>362</v>
       </c>
       <c r="B363" s="1">
-        <v>380</v>
+        <v>480</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -6008,7 +6023,7 @@
         <v>363</v>
       </c>
       <c r="B364" s="1">
-        <v>440</v>
+        <v>800</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -6016,7 +6031,7 @@
         <v>364</v>
       </c>
       <c r="B365" s="1">
-        <v>900</v>
+        <v>520</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -6024,7 +6039,7 @@
         <v>365</v>
       </c>
       <c r="B366" s="1">
-        <v>900</v>
+        <v>380</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -6032,7 +6047,7 @@
         <v>366</v>
       </c>
       <c r="B367" s="1">
-        <v>780</v>
+        <v>440</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -6040,7 +6055,7 @@
         <v>367</v>
       </c>
       <c r="B368" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -6048,7 +6063,7 @@
         <v>368</v>
       </c>
       <c r="B369" s="1">
-        <v>860</v>
+        <v>900</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -6056,7 +6071,7 @@
         <v>369</v>
       </c>
       <c r="B370" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -6064,7 +6079,7 @@
         <v>370</v>
       </c>
       <c r="B371" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -6072,7 +6087,7 @@
         <v>371</v>
       </c>
       <c r="B372" s="1">
-        <v>880</v>
+        <v>860</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -6080,7 +6095,7 @@
         <v>372</v>
       </c>
       <c r="B373" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -6088,7 +6103,7 @@
         <v>373</v>
       </c>
       <c r="B374" s="1">
-        <v>840</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -6096,7 +6111,7 @@
         <v>374</v>
       </c>
       <c r="B375" s="1">
-        <v>700</v>
+        <v>880</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -6104,7 +6119,7 @@
         <v>375</v>
       </c>
       <c r="B376" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -6112,7 +6127,7 @@
         <v>376</v>
       </c>
       <c r="B377" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -6120,7 +6135,7 @@
         <v>377</v>
       </c>
       <c r="B378" s="1">
-        <v>1020</v>
+        <v>700</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -6128,7 +6143,7 @@
         <v>378</v>
       </c>
       <c r="B379" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -6136,7 +6151,7 @@
         <v>379</v>
       </c>
       <c r="B380" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -6144,7 +6159,7 @@
         <v>380</v>
       </c>
       <c r="B381" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -6160,7 +6175,7 @@
         <v>382</v>
       </c>
       <c r="B383" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -6168,7 +6183,7 @@
         <v>383</v>
       </c>
       <c r="B384" s="1">
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -6176,7 +6191,7 @@
         <v>384</v>
       </c>
       <c r="B385" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -6184,7 +6199,7 @@
         <v>385</v>
       </c>
       <c r="B386" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -6192,7 +6207,7 @@
         <v>386</v>
       </c>
       <c r="B387" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -6200,7 +6215,7 @@
         <v>387</v>
       </c>
       <c r="B388" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -6208,7 +6223,7 @@
         <v>388</v>
       </c>
       <c r="B389" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -6216,7 +6231,7 @@
         <v>389</v>
       </c>
       <c r="B390" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -6224,7 +6239,7 @@
         <v>390</v>
       </c>
       <c r="B391" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -6232,7 +6247,7 @@
         <v>391</v>
       </c>
       <c r="B392" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -6240,7 +6255,7 @@
         <v>392</v>
       </c>
       <c r="B393" s="1">
-        <v>480</v>
+        <v>820</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -6248,7 +6263,7 @@
         <v>393</v>
       </c>
       <c r="B394" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -6256,7 +6271,7 @@
         <v>394</v>
       </c>
       <c r="B395" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -6264,7 +6279,7 @@
         <v>395</v>
       </c>
       <c r="B396" s="1">
-        <v>920</v>
+        <v>480</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -6272,7 +6287,7 @@
         <v>396</v>
       </c>
       <c r="B397" s="1">
-        <v>860</v>
+        <v>640</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -6280,7 +6295,7 @@
         <v>397</v>
       </c>
       <c r="B398" s="1">
-        <v>520</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -6288,7 +6303,7 @@
         <v>398</v>
       </c>
       <c r="B399" s="1">
-        <v>540</v>
+        <v>920</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -6296,7 +6311,7 @@
         <v>399</v>
       </c>
       <c r="B400" s="1">
-        <v>700</v>
+        <v>860</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -6304,7 +6319,7 @@
         <v>400</v>
       </c>
       <c r="B401" s="1">
-        <v>700</v>
+        <v>520</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -6312,7 +6327,7 @@
         <v>401</v>
       </c>
       <c r="B402" s="1">
-        <v>420</v>
+        <v>540</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -6328,7 +6343,7 @@
         <v>403</v>
       </c>
       <c r="B404" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -6336,7 +6351,7 @@
         <v>404</v>
       </c>
       <c r="B405" s="1">
-        <v>580</v>
+        <v>420</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -6344,7 +6359,7 @@
         <v>405</v>
       </c>
       <c r="B406" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -6352,7 +6367,7 @@
         <v>406</v>
       </c>
       <c r="B407" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -6360,7 +6375,7 @@
         <v>407</v>
       </c>
       <c r="B408" s="1">
-        <v>920</v>
+        <v>580</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -6368,7 +6383,7 @@
         <v>408</v>
       </c>
       <c r="B409" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -6376,7 +6391,7 @@
         <v>409</v>
       </c>
       <c r="B410" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -6384,7 +6399,7 @@
         <v>410</v>
       </c>
       <c r="B411" s="1">
-        <v>620</v>
+        <v>920</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -6392,7 +6407,7 @@
         <v>411</v>
       </c>
       <c r="B412" s="1">
-        <v>440</v>
+        <v>840</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -6400,7 +6415,7 @@
         <v>412</v>
       </c>
       <c r="B413" s="1">
-        <v>1100</v>
+        <v>720</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -6408,7 +6423,7 @@
         <v>413</v>
       </c>
       <c r="B414" s="1">
-        <v>1100</v>
+        <v>620</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -6416,7 +6431,7 @@
         <v>414</v>
       </c>
       <c r="B415" s="1">
-        <v>320</v>
+        <v>440</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -6424,7 +6439,7 @@
         <v>415</v>
       </c>
       <c r="B416" s="1">
-        <v>940</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -6432,7 +6447,7 @@
         <v>416</v>
       </c>
       <c r="B417" s="1">
-        <v>320</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -6440,7 +6455,7 @@
         <v>417</v>
       </c>
       <c r="B418" s="1">
-        <v>960</v>
+        <v>320</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -6448,7 +6463,7 @@
         <v>418</v>
       </c>
       <c r="B419" s="1">
-        <v>820</v>
+        <v>940</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -6456,7 +6471,7 @@
         <v>419</v>
       </c>
       <c r="B420" s="1">
-        <v>1000</v>
+        <v>320</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -6464,7 +6479,7 @@
         <v>420</v>
       </c>
       <c r="B421" s="1">
-        <v>580</v>
+        <v>960</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -6472,7 +6487,7 @@
         <v>421</v>
       </c>
       <c r="B422" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -6480,7 +6495,7 @@
         <v>422</v>
       </c>
       <c r="B423" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -6504,7 +6519,7 @@
         <v>425</v>
       </c>
       <c r="B426" s="1">
-        <v>620</v>
+        <v>900</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -6512,7 +6527,7 @@
         <v>426</v>
       </c>
       <c r="B427" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -6520,7 +6535,7 @@
         <v>427</v>
       </c>
       <c r="B428" s="1">
-        <v>920</v>
+        <v>580</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6528,7 +6543,7 @@
         <v>428</v>
       </c>
       <c r="B429" s="1">
-        <v>1000</v>
+        <v>620</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6536,7 +6551,7 @@
         <v>429</v>
       </c>
       <c r="B430" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6544,7 +6559,7 @@
         <v>430</v>
       </c>
       <c r="B431" s="1">
-        <v>880</v>
+        <v>920</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6552,7 +6567,7 @@
         <v>431</v>
       </c>
       <c r="B432" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6568,7 +6583,7 @@
         <v>433</v>
       </c>
       <c r="B434" s="1">
-        <v>900</v>
+        <v>880</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6576,7 +6591,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6584,7 +6599,7 @@
         <v>435</v>
       </c>
       <c r="B436" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6600,7 +6615,7 @@
         <v>437</v>
       </c>
       <c r="B438" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6608,7 +6623,7 @@
         <v>438</v>
       </c>
       <c r="B439" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6616,7 +6631,7 @@
         <v>439</v>
       </c>
       <c r="B440" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6624,7 +6639,7 @@
         <v>440</v>
       </c>
       <c r="B441" s="1">
-        <v>440</v>
+        <v>680</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6632,7 +6647,7 @@
         <v>441</v>
       </c>
       <c r="B442" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6640,7 +6655,7 @@
         <v>442</v>
       </c>
       <c r="B443" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6648,7 +6663,7 @@
         <v>443</v>
       </c>
       <c r="B444" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6656,7 +6671,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6664,7 +6679,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6672,7 +6687,7 @@
         <v>446</v>
       </c>
       <c r="B447" s="1">
-        <v>760</v>
+        <v>900</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6680,7 +6695,7 @@
         <v>447</v>
       </c>
       <c r="B448" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6688,7 +6703,7 @@
         <v>448</v>
       </c>
       <c r="B449" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6696,7 +6711,7 @@
         <v>449</v>
       </c>
       <c r="B450" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6704,7 +6719,7 @@
         <v>450</v>
       </c>
       <c r="B451" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6712,7 +6727,7 @@
         <v>451</v>
       </c>
       <c r="B452" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6720,7 +6735,7 @@
         <v>452</v>
       </c>
       <c r="B453" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6728,7 +6743,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="1">
-        <v>680</v>
+        <v>560</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6736,7 +6751,7 @@
         <v>454</v>
       </c>
       <c r="B455" s="1">
-        <v>480</v>
+        <v>620</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6744,7 +6759,7 @@
         <v>455</v>
       </c>
       <c r="B456" s="1">
-        <v>480</v>
+        <v>720</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6752,7 +6767,7 @@
         <v>456</v>
       </c>
       <c r="B457" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6760,7 +6775,7 @@
         <v>457</v>
       </c>
       <c r="B458" s="1">
-        <v>840</v>
+        <v>480</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6768,7 +6783,7 @@
         <v>458</v>
       </c>
       <c r="B459" s="1">
-        <v>880</v>
+        <v>480</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6784,7 +6799,7 @@
         <v>460</v>
       </c>
       <c r="B461" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6792,7 +6807,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6800,7 +6815,7 @@
         <v>462</v>
       </c>
       <c r="B463" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6808,7 +6823,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="1">
-        <v>800</v>
+        <v>880</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6816,7 +6831,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6824,7 +6839,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6832,7 +6847,7 @@
         <v>466</v>
       </c>
       <c r="B467" s="1">
-        <v>980</v>
+        <v>800</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6840,7 +6855,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6848,7 +6863,7 @@
         <v>468</v>
       </c>
       <c r="B469" s="1">
-        <v>600</v>
+        <v>940</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6856,7 +6871,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="1">
-        <v>760</v>
+        <v>980</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6864,7 +6879,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6872,7 +6887,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6880,7 +6895,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="1">
-        <v>620</v>
+        <v>760</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6888,7 +6903,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6896,7 +6911,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="1">
-        <v>920</v>
+        <v>620</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6904,7 +6919,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6912,7 +6927,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6920,7 +6935,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6928,7 +6943,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="1">
-        <v>960</v>
+        <v>640</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6936,7 +6951,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6944,7 +6959,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6952,7 +6967,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="1">
-        <v>640</v>
+        <v>960</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6960,7 +6975,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6968,7 +6983,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="1">
-        <v>560</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6976,7 +6991,7 @@
         <v>484</v>
       </c>
       <c r="B485" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6984,7 +6999,7 @@
         <v>485</v>
       </c>
       <c r="B486" s="1">
-        <v>660</v>
+        <v>860</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6992,7 +7007,7 @@
         <v>486</v>
       </c>
       <c r="B487" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -7000,7 +7015,7 @@
         <v>487</v>
       </c>
       <c r="B488" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -7008,7 +7023,7 @@
         <v>488</v>
       </c>
       <c r="B489" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -7016,7 +7031,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="1">
-        <v>520</v>
+        <v>640</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -7024,7 +7039,7 @@
         <v>490</v>
       </c>
       <c r="B491" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -7032,7 +7047,7 @@
         <v>491</v>
       </c>
       <c r="B492" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -7040,7 +7055,7 @@
         <v>492</v>
       </c>
       <c r="B493" s="1">
-        <v>780</v>
+        <v>520</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -7048,7 +7063,7 @@
         <v>493</v>
       </c>
       <c r="B494" s="1">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -7056,7 +7071,7 @@
         <v>494</v>
       </c>
       <c r="B495" s="1">
-        <v>820</v>
+        <v>620</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -7064,7 +7079,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -7072,7 +7087,7 @@
         <v>496</v>
       </c>
       <c r="B497" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -7080,7 +7095,7 @@
         <v>497</v>
       </c>
       <c r="B498" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -7088,7 +7103,7 @@
         <v>498</v>
       </c>
       <c r="B499" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -7096,7 +7111,7 @@
         <v>499</v>
       </c>
       <c r="B500" s="1">
-        <v>480</v>
+        <v>740</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -7104,7 +7119,7 @@
         <v>500</v>
       </c>
       <c r="B501" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -7112,7 +7127,7 @@
         <v>501</v>
       </c>
       <c r="B502" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -7120,7 +7135,7 @@
         <v>502</v>
       </c>
       <c r="B503" s="1">
-        <v>700</v>
+        <v>480</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -7128,7 +7143,7 @@
         <v>503</v>
       </c>
       <c r="B504" s="1">
-        <v>440</v>
+        <v>840</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -7136,7 +7151,7 @@
         <v>504</v>
       </c>
       <c r="B505" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -7144,7 +7159,7 @@
         <v>505</v>
       </c>
       <c r="B506" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -7152,7 +7167,7 @@
         <v>506</v>
       </c>
       <c r="B507" s="1">
-        <v>940</v>
+        <v>440</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -7160,7 +7175,7 @@
         <v>507</v>
       </c>
       <c r="B508" s="1">
-        <v>1100</v>
+        <v>440</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -7168,7 +7183,7 @@
         <v>508</v>
       </c>
       <c r="B509" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -7176,7 +7191,7 @@
         <v>509</v>
       </c>
       <c r="B510" s="1">
-        <v>880</v>
+        <v>940</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -7184,7 +7199,7 @@
         <v>510</v>
       </c>
       <c r="B511" s="1">
-        <v>760</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -7192,7 +7207,7 @@
         <v>511</v>
       </c>
       <c r="B512" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -7200,7 +7215,7 @@
         <v>512</v>
       </c>
       <c r="B513" s="1">
-        <v>660</v>
+        <v>880</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -7208,7 +7223,7 @@
         <v>513</v>
       </c>
       <c r="B514" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -7224,7 +7239,7 @@
         <v>515</v>
       </c>
       <c r="B516" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -7232,7 +7247,7 @@
         <v>516</v>
       </c>
       <c r="B517" s="1">
-        <v>760</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -7248,7 +7263,7 @@
         <v>518</v>
       </c>
       <c r="B519" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -7256,7 +7271,7 @@
         <v>519</v>
       </c>
       <c r="B520" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -7272,7 +7287,7 @@
         <v>521</v>
       </c>
       <c r="B522" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -7280,7 +7295,7 @@
         <v>522</v>
       </c>
       <c r="B523" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -7288,7 +7303,7 @@
         <v>523</v>
       </c>
       <c r="B524" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -7296,7 +7311,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -7304,7 +7319,7 @@
         <v>525</v>
       </c>
       <c r="B526" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -7312,7 +7327,7 @@
         <v>526</v>
       </c>
       <c r="B527" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -7320,7 +7335,7 @@
         <v>527</v>
       </c>
       <c r="B528" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -7328,7 +7343,7 @@
         <v>528</v>
       </c>
       <c r="B529" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -7336,7 +7351,7 @@
         <v>529</v>
       </c>
       <c r="B530" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -7344,7 +7359,7 @@
         <v>530</v>
       </c>
       <c r="B531" s="1">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -7352,7 +7367,7 @@
         <v>531</v>
       </c>
       <c r="B532" s="1">
-        <v>620</v>
+        <v>800</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -7360,7 +7375,7 @@
         <v>532</v>
       </c>
       <c r="B533" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -7368,7 +7383,7 @@
         <v>533</v>
       </c>
       <c r="B534" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -7376,7 +7391,7 @@
         <v>534</v>
       </c>
       <c r="B535" s="1">
-        <v>1060</v>
+        <v>620</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -7384,7 +7399,7 @@
         <v>535</v>
       </c>
       <c r="B536" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -7392,7 +7407,7 @@
         <v>536</v>
       </c>
       <c r="B537" s="1">
-        <v>860</v>
+        <v>880</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -7400,7 +7415,7 @@
         <v>537</v>
       </c>
       <c r="B538" s="1">
-        <v>800</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -7416,7 +7431,7 @@
         <v>539</v>
       </c>
       <c r="B540" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -7424,7 +7439,7 @@
         <v>540</v>
       </c>
       <c r="B541" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -7432,7 +7447,7 @@
         <v>541</v>
       </c>
       <c r="B542" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -7440,7 +7455,7 @@
         <v>542</v>
       </c>
       <c r="B543" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -7448,7 +7463,7 @@
         <v>543</v>
       </c>
       <c r="B544" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -7456,7 +7471,7 @@
         <v>544</v>
       </c>
       <c r="B545" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -7464,7 +7479,7 @@
         <v>545</v>
       </c>
       <c r="B546" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -7472,7 +7487,7 @@
         <v>546</v>
       </c>
       <c r="B547" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -7480,7 +7495,7 @@
         <v>547</v>
       </c>
       <c r="B548" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -7488,7 +7503,7 @@
         <v>548</v>
       </c>
       <c r="B549" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -7504,7 +7519,7 @@
         <v>550</v>
       </c>
       <c r="B551" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -7512,7 +7527,7 @@
         <v>551</v>
       </c>
       <c r="B552" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7520,7 +7535,7 @@
         <v>552</v>
       </c>
       <c r="B553" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7528,7 +7543,7 @@
         <v>553</v>
       </c>
       <c r="B554" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7536,7 +7551,7 @@
         <v>554</v>
       </c>
       <c r="B555" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7544,7 +7559,7 @@
         <v>555</v>
       </c>
       <c r="B556" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7552,7 +7567,7 @@
         <v>556</v>
       </c>
       <c r="B557" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7560,7 +7575,7 @@
         <v>557</v>
       </c>
       <c r="B558" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7568,7 +7583,7 @@
         <v>558</v>
       </c>
       <c r="B559" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7576,7 +7591,7 @@
         <v>559</v>
       </c>
       <c r="B560" s="1">
-        <v>880</v>
+        <v>660</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7584,7 +7599,7 @@
         <v>560</v>
       </c>
       <c r="B561" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7592,7 +7607,7 @@
         <v>561</v>
       </c>
       <c r="B562" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7600,7 +7615,7 @@
         <v>562</v>
       </c>
       <c r="B563" s="1">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7608,7 +7623,7 @@
         <v>563</v>
       </c>
       <c r="B564" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7616,7 +7631,7 @@
         <v>564</v>
       </c>
       <c r="B565" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7624,7 +7639,7 @@
         <v>565</v>
       </c>
       <c r="B566" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7632,7 +7647,7 @@
         <v>566</v>
       </c>
       <c r="B567" s="1">
-        <v>880</v>
+        <v>760</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7640,7 +7655,7 @@
         <v>567</v>
       </c>
       <c r="B568" s="1">
-        <v>640</v>
+        <v>920</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7648,7 +7663,7 @@
         <v>568</v>
       </c>
       <c r="B569" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7656,7 +7671,7 @@
         <v>569</v>
       </c>
       <c r="B570" s="1">
-        <v>600</v>
+        <v>880</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7664,7 +7679,7 @@
         <v>570</v>
       </c>
       <c r="B571" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7672,7 +7687,7 @@
         <v>571</v>
       </c>
       <c r="B572" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7680,7 +7695,7 @@
         <v>572</v>
       </c>
       <c r="B573" s="1">
-        <v>860</v>
+        <v>600</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7688,7 +7703,7 @@
         <v>573</v>
       </c>
       <c r="B574" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7696,7 +7711,7 @@
         <v>574</v>
       </c>
       <c r="B575" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7712,7 +7727,7 @@
         <v>576</v>
       </c>
       <c r="B577" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7720,7 +7735,7 @@
         <v>577</v>
       </c>
       <c r="B578" s="1">
-        <v>960</v>
+        <v>840</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7728,7 +7743,7 @@
         <v>578</v>
       </c>
       <c r="B579" s="1">
-        <v>940</v>
+        <v>860</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7736,7 +7751,7 @@
         <v>579</v>
       </c>
       <c r="B580" s="1">
-        <v>1040</v>
+        <v>720</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7744,7 +7759,7 @@
         <v>580</v>
       </c>
       <c r="B581" s="1">
-        <v>1040</v>
+        <v>960</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7760,7 +7775,7 @@
         <v>582</v>
       </c>
       <c r="B583" s="1">
-        <v>860</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7768,7 +7783,7 @@
         <v>583</v>
       </c>
       <c r="B584" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7776,7 +7791,7 @@
         <v>584</v>
       </c>
       <c r="B585" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7784,7 +7799,7 @@
         <v>585</v>
       </c>
       <c r="B586" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7792,7 +7807,7 @@
         <v>586</v>
       </c>
       <c r="B587" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7800,7 +7815,7 @@
         <v>587</v>
       </c>
       <c r="B588" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7808,7 +7823,7 @@
         <v>588</v>
       </c>
       <c r="B589" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7816,7 +7831,7 @@
         <v>589</v>
       </c>
       <c r="B590" s="1">
-        <v>880</v>
+        <v>680</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7824,7 +7839,7 @@
         <v>590</v>
       </c>
       <c r="B591" s="1">
-        <v>580</v>
+        <v>840</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7832,7 +7847,7 @@
         <v>591</v>
       </c>
       <c r="B592" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7840,7 +7855,7 @@
         <v>592</v>
       </c>
       <c r="B593" s="1">
-        <v>860</v>
+        <v>880</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7848,7 +7863,7 @@
         <v>593</v>
       </c>
       <c r="B594" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7856,7 +7871,7 @@
         <v>594</v>
       </c>
       <c r="B595" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7864,7 +7879,7 @@
         <v>595</v>
       </c>
       <c r="B596" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7872,7 +7887,7 @@
         <v>596</v>
       </c>
       <c r="B597" s="1">
-        <v>700</v>
+        <v>620</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7880,7 +7895,7 @@
         <v>597</v>
       </c>
       <c r="B598" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7888,7 +7903,7 @@
         <v>598</v>
       </c>
       <c r="B599" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7896,7 +7911,7 @@
         <v>599</v>
       </c>
       <c r="B600" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7904,7 +7919,7 @@
         <v>600</v>
       </c>
       <c r="B601" s="1">
-        <v>720</v>
+        <v>960</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7912,7 +7927,7 @@
         <v>601</v>
       </c>
       <c r="B602" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7920,7 +7935,7 @@
         <v>602</v>
       </c>
       <c r="B603" s="1">
-        <v>540</v>
+        <v>600</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7928,7 +7943,7 @@
         <v>603</v>
       </c>
       <c r="B604" s="1">
-        <v>1100</v>
+        <v>720</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7936,7 +7951,7 @@
         <v>604</v>
       </c>
       <c r="B605" s="1">
-        <v>1060</v>
+        <v>780</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7944,7 +7959,7 @@
         <v>605</v>
       </c>
       <c r="B606" s="1">
-        <v>1100</v>
+        <v>540</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7952,7 +7967,7 @@
         <v>606</v>
       </c>
       <c r="B607" s="1">
-        <v>1100</v>
+        <v>980</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7960,7 +7975,7 @@
         <v>607</v>
       </c>
       <c r="B608" s="1">
-        <v>1080</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7968,7 +7983,7 @@
         <v>608</v>
       </c>
       <c r="B609" s="1">
-        <v>840</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7976,7 +7991,7 @@
         <v>609</v>
       </c>
       <c r="B610" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7984,7 +7999,7 @@
         <v>610</v>
       </c>
       <c r="B611" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7992,7 +8007,7 @@
         <v>611</v>
       </c>
       <c r="B612" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -8000,7 +8015,7 @@
         <v>612</v>
       </c>
       <c r="B613" s="1">
-        <v>740</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -8008,7 +8023,7 @@
         <v>613</v>
       </c>
       <c r="B614" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -8016,7 +8031,7 @@
         <v>614</v>
       </c>
       <c r="B615" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -8024,7 +8039,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="1">
-        <v>980</v>
+        <v>720</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -8032,7 +8047,7 @@
         <v>616</v>
       </c>
       <c r="B617" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -8040,7 +8055,7 @@
         <v>617</v>
       </c>
       <c r="B618" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -8048,7 +8063,7 @@
         <v>618</v>
       </c>
       <c r="B619" s="1">
-        <v>1100</v>
+        <v>620</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -8056,7 +8071,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="1">
-        <v>1100</v>
+        <v>860</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -8064,7 +8079,7 @@
         <v>620</v>
       </c>
       <c r="B621" s="1">
-        <v>1100</v>
+        <v>980</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -8072,7 +8087,7 @@
         <v>621</v>
       </c>
       <c r="B622" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -8080,7 +8095,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -8088,7 +8103,7 @@
         <v>623</v>
       </c>
       <c r="B624" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -8096,7 +8111,7 @@
         <v>624</v>
       </c>
       <c r="B625" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -8104,7 +8119,7 @@
         <v>625</v>
       </c>
       <c r="B626" s="1">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -8112,7 +8127,7 @@
         <v>626</v>
       </c>
       <c r="B627" s="1">
-        <v>960</v>
+        <v>920</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -8120,7 +8135,7 @@
         <v>627</v>
       </c>
       <c r="B628" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -8128,7 +8143,7 @@
         <v>628</v>
       </c>
       <c r="B629" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -8136,7 +8151,7 @@
         <v>629</v>
       </c>
       <c r="B630" s="1">
-        <v>980</v>
+        <v>720</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -8144,7 +8159,7 @@
         <v>630</v>
       </c>
       <c r="B631" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -8152,7 +8167,7 @@
         <v>631</v>
       </c>
       <c r="B632" s="1">
-        <v>800</v>
+        <v>960</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -8160,7 +8175,7 @@
         <v>632</v>
       </c>
       <c r="B633" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -8168,7 +8183,7 @@
         <v>633</v>
       </c>
       <c r="B634" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -8176,7 +8191,7 @@
         <v>634</v>
       </c>
       <c r="B635" s="1">
-        <v>740</v>
+        <v>980</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -8184,7 +8199,7 @@
         <v>635</v>
       </c>
       <c r="B636" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -8192,7 +8207,7 @@
         <v>636</v>
       </c>
       <c r="B637" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -8200,7 +8215,7 @@
         <v>637</v>
       </c>
       <c r="B638" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -8208,7 +8223,7 @@
         <v>638</v>
       </c>
       <c r="B639" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -8216,7 +8231,7 @@
         <v>639</v>
       </c>
       <c r="B640" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -8224,7 +8239,7 @@
         <v>640</v>
       </c>
       <c r="B641" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -8232,7 +8247,7 @@
         <v>641</v>
       </c>
       <c r="B642" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -8240,7 +8255,7 @@
         <v>642</v>
       </c>
       <c r="B643" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -8248,7 +8263,7 @@
         <v>643</v>
       </c>
       <c r="B644" s="1">
-        <v>1400</v>
+        <v>860</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -8256,7 +8271,7 @@
         <v>644</v>
       </c>
       <c r="B645" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -8264,7 +8279,7 @@
         <v>645</v>
       </c>
       <c r="B646" s="1">
-        <v>660</v>
+        <v>820</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -8272,7 +8287,7 @@
         <v>646</v>
       </c>
       <c r="B647" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -8280,7 +8295,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -8288,7 +8303,7 @@
         <v>648</v>
       </c>
       <c r="B649" s="1">
-        <v>720</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -8296,7 +8311,7 @@
         <v>649</v>
       </c>
       <c r="B650" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -8304,7 +8319,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -8312,7 +8327,7 @@
         <v>651</v>
       </c>
       <c r="B652" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -8320,7 +8335,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -8328,7 +8343,7 @@
         <v>653</v>
       </c>
       <c r="B654" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -8336,7 +8351,7 @@
         <v>654</v>
       </c>
       <c r="B655" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -8344,7 +8359,7 @@
         <v>655</v>
       </c>
       <c r="B656" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -8352,7 +8367,7 @@
         <v>656</v>
       </c>
       <c r="B657" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -8360,7 +8375,7 @@
         <v>657</v>
       </c>
       <c r="B658" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -8376,7 +8391,7 @@
         <v>659</v>
       </c>
       <c r="B660" s="1">
-        <v>820</v>
+        <v>720</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -8384,7 +8399,7 @@
         <v>660</v>
       </c>
       <c r="B661" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -8392,7 +8407,7 @@
         <v>661</v>
       </c>
       <c r="B662" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -8400,7 +8415,7 @@
         <v>662</v>
       </c>
       <c r="B663" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -8408,7 +8423,7 @@
         <v>663</v>
       </c>
       <c r="B664" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -8416,7 +8431,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="1">
-        <v>800</v>
+        <v>820</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -8424,7 +8439,7 @@
         <v>665</v>
       </c>
       <c r="B666" s="1">
-        <v>4000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -8432,7 +8447,7 @@
         <v>666</v>
       </c>
       <c r="B667" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -8440,7 +8455,7 @@
         <v>667</v>
       </c>
       <c r="B668" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -8448,7 +8463,7 @@
         <v>668</v>
       </c>
       <c r="B669" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -8456,7 +8471,7 @@
         <v>669</v>
       </c>
       <c r="B670" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -8464,7 +8479,7 @@
         <v>670</v>
       </c>
       <c r="B671" s="1">
-        <v>680</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -8472,7 +8487,7 @@
         <v>671</v>
       </c>
       <c r="B672" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -8480,7 +8495,7 @@
         <v>672</v>
       </c>
       <c r="B673" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -8488,7 +8503,7 @@
         <v>673</v>
       </c>
       <c r="B674" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -8496,7 +8511,7 @@
         <v>674</v>
       </c>
       <c r="B675" s="1">
-        <v>540</v>
+        <v>700</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8504,7 +8519,7 @@
         <v>675</v>
       </c>
       <c r="B676" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -8512,7 +8527,7 @@
         <v>676</v>
       </c>
       <c r="B677" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8520,7 +8535,7 @@
         <v>677</v>
       </c>
       <c r="B678" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8528,7 +8543,7 @@
         <v>678</v>
       </c>
       <c r="B679" s="1">
-        <v>860</v>
+        <v>900</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8536,7 +8551,7 @@
         <v>679</v>
       </c>
       <c r="B680" s="1">
-        <v>900</v>
+        <v>540</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8544,7 +8559,7 @@
         <v>680</v>
       </c>
       <c r="B681" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8552,7 +8567,7 @@
         <v>681</v>
       </c>
       <c r="B682" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8560,7 +8575,7 @@
         <v>682</v>
       </c>
       <c r="B683" s="1">
-        <v>980</v>
+        <v>900</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8568,7 +8583,7 @@
         <v>683</v>
       </c>
       <c r="B684" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8576,7 +8591,7 @@
         <v>684</v>
       </c>
       <c r="B685" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8592,7 +8607,7 @@
         <v>686</v>
       </c>
       <c r="B687" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8600,7 +8615,7 @@
         <v>687</v>
       </c>
       <c r="B688" s="1">
-        <v>680</v>
+        <v>980</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8616,7 +8631,7 @@
         <v>689</v>
       </c>
       <c r="B690" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8624,7 +8639,7 @@
         <v>690</v>
       </c>
       <c r="B691" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8632,7 +8647,7 @@
         <v>691</v>
       </c>
       <c r="B692" s="1">
-        <v>840</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8640,7 +8655,7 @@
         <v>692</v>
       </c>
       <c r="B693" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8648,7 +8663,7 @@
         <v>693</v>
       </c>
       <c r="B694" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8656,7 +8671,7 @@
         <v>694</v>
       </c>
       <c r="B695" s="1">
-        <v>1020</v>
+        <v>860</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8672,7 +8687,7 @@
         <v>696</v>
       </c>
       <c r="B697" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8680,7 +8695,7 @@
         <v>697</v>
       </c>
       <c r="B698" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8688,7 +8703,7 @@
         <v>698</v>
       </c>
       <c r="B699" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8696,7 +8711,7 @@
         <v>699</v>
       </c>
       <c r="B700" s="1">
-        <v>840</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8704,7 +8719,7 @@
         <v>700</v>
       </c>
       <c r="B701" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8712,7 +8727,7 @@
         <v>701</v>
       </c>
       <c r="B702" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8720,7 +8735,7 @@
         <v>702</v>
       </c>
       <c r="B703" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8728,7 +8743,7 @@
         <v>703</v>
       </c>
       <c r="B704" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8736,7 +8751,7 @@
         <v>704</v>
       </c>
       <c r="B705" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8744,7 +8759,7 @@
         <v>705</v>
       </c>
       <c r="B706" s="1">
-        <v>880</v>
+        <v>640</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8752,7 +8767,7 @@
         <v>706</v>
       </c>
       <c r="B707" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8760,7 +8775,7 @@
         <v>707</v>
       </c>
       <c r="B708" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8768,7 +8783,7 @@
         <v>708</v>
       </c>
       <c r="B709" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8776,7 +8791,7 @@
         <v>709</v>
       </c>
       <c r="B710" s="1">
-        <v>820</v>
+        <v>720</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8784,7 +8799,7 @@
         <v>710</v>
       </c>
       <c r="B711" s="1">
-        <v>600</v>
+        <v>880</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8792,7 +8807,7 @@
         <v>711</v>
       </c>
       <c r="B712" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8800,7 +8815,7 @@
         <v>712</v>
       </c>
       <c r="B713" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8808,7 +8823,7 @@
         <v>713</v>
       </c>
       <c r="B714" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8816,7 +8831,7 @@
         <v>714</v>
       </c>
       <c r="B715" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8824,7 +8839,7 @@
         <v>715</v>
       </c>
       <c r="B716" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8832,7 +8847,7 @@
         <v>716</v>
       </c>
       <c r="B717" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8848,7 +8863,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="1">
-        <v>960</v>
+        <v>800</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8856,7 +8871,7 @@
         <v>719</v>
       </c>
       <c r="B720" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8864,7 +8879,7 @@
         <v>720</v>
       </c>
       <c r="B721" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8880,7 +8895,7 @@
         <v>722</v>
       </c>
       <c r="B723" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8888,7 +8903,7 @@
         <v>723</v>
       </c>
       <c r="B724" s="1">
-        <v>700</v>
+        <v>960</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8896,7 +8911,7 @@
         <v>724</v>
       </c>
       <c r="B725" s="1">
-        <v>640</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8904,7 +8919,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8912,7 +8927,7 @@
         <v>726</v>
       </c>
       <c r="B727" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8920,7 +8935,7 @@
         <v>727</v>
       </c>
       <c r="B728" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8928,7 +8943,7 @@
         <v>728</v>
       </c>
       <c r="B729" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8936,7 +8951,7 @@
         <v>729</v>
       </c>
       <c r="B730" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8952,7 +8967,7 @@
         <v>731</v>
       </c>
       <c r="B732" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -8960,7 +8975,7 @@
         <v>732</v>
       </c>
       <c r="B733" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -8968,7 +8983,7 @@
         <v>733</v>
       </c>
       <c r="B734" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -8976,7 +8991,7 @@
         <v>734</v>
       </c>
       <c r="B735" s="1">
-        <v>760</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -8984,7 +8999,7 @@
         <v>735</v>
       </c>
       <c r="B736" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -8992,7 +9007,7 @@
         <v>736</v>
       </c>
       <c r="B737" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -9000,7 +9015,7 @@
         <v>737</v>
       </c>
       <c r="B738" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="739" spans="1:2">
@@ -9016,7 +9031,7 @@
         <v>739</v>
       </c>
       <c r="B740" s="1">
-        <v>1000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -9024,7 +9039,7 @@
         <v>740</v>
       </c>
       <c r="B741" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="742" spans="1:2">
@@ -9032,7 +9047,7 @@
         <v>741</v>
       </c>
       <c r="B742" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -9048,7 +9063,7 @@
         <v>743</v>
       </c>
       <c r="B744" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="745" spans="1:2">
@@ -9056,7 +9071,7 @@
         <v>744</v>
       </c>
       <c r="B745" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -9064,7 +9079,7 @@
         <v>745</v>
       </c>
       <c r="B746" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="747" spans="1:2">
@@ -9072,7 +9087,7 @@
         <v>746</v>
       </c>
       <c r="B747" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="748" spans="1:2">
@@ -9080,7 +9095,7 @@
         <v>747</v>
       </c>
       <c r="B748" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="749" spans="1:2">
@@ -9088,7 +9103,7 @@
         <v>748</v>
       </c>
       <c r="B749" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -9096,7 +9111,7 @@
         <v>749</v>
       </c>
       <c r="B750" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="751" spans="1:2">
@@ -9104,7 +9119,7 @@
         <v>750</v>
       </c>
       <c r="B751" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="752" spans="1:2">
@@ -9112,7 +9127,7 @@
         <v>751</v>
       </c>
       <c r="B752" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="753" spans="1:2">
@@ -9120,7 +9135,7 @@
         <v>752</v>
       </c>
       <c r="B753" s="1">
-        <v>900</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="754" spans="1:2">
@@ -9128,7 +9143,7 @@
         <v>753</v>
       </c>
       <c r="B754" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -9136,7 +9151,7 @@
         <v>754</v>
       </c>
       <c r="B755" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="756" spans="1:2">
@@ -9144,7 +9159,7 @@
         <v>755</v>
       </c>
       <c r="B756" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="757" spans="1:2">
@@ -9152,7 +9167,7 @@
         <v>756</v>
       </c>
       <c r="B757" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="758" spans="1:2">
@@ -9160,7 +9175,7 @@
         <v>757</v>
       </c>
       <c r="B758" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="759" spans="1:2">
@@ -9168,7 +9183,7 @@
         <v>758</v>
       </c>
       <c r="B759" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="760" spans="1:2">
@@ -9176,7 +9191,7 @@
         <v>759</v>
       </c>
       <c r="B760" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="761" spans="1:2">
@@ -9184,7 +9199,7 @@
         <v>760</v>
       </c>
       <c r="B761" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="762" spans="1:2">
@@ -9192,7 +9207,7 @@
         <v>761</v>
       </c>
       <c r="B762" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="763" spans="1:2">
@@ -9200,7 +9215,7 @@
         <v>762</v>
       </c>
       <c r="B763" s="1">
-        <v>700</v>
+        <v>880</v>
       </c>
     </row>
     <row r="764" spans="1:2">
@@ -9208,7 +9223,7 @@
         <v>763</v>
       </c>
       <c r="B764" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="765" spans="1:2">
@@ -9216,7 +9231,7 @@
         <v>764</v>
       </c>
       <c r="B765" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="766" spans="1:2">
@@ -9240,7 +9255,7 @@
         <v>767</v>
       </c>
       <c r="B768" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="769" spans="1:2">
@@ -9248,7 +9263,7 @@
         <v>768</v>
       </c>
       <c r="B769" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="770" spans="1:2">
@@ -9256,7 +9271,7 @@
         <v>769</v>
       </c>
       <c r="B770" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="771" spans="1:2">
@@ -9272,7 +9287,7 @@
         <v>771</v>
       </c>
       <c r="B772" s="1">
-        <v>800</v>
+        <v>660</v>
       </c>
     </row>
     <row r="773" spans="1:2">
@@ -9280,7 +9295,7 @@
         <v>772</v>
       </c>
       <c r="B773" s="1">
-        <v>720</v>
+        <v>440</v>
       </c>
     </row>
     <row r="774" spans="1:2">
@@ -9288,7 +9303,7 @@
         <v>773</v>
       </c>
       <c r="B774" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="775" spans="1:2">
@@ -9296,7 +9311,7 @@
         <v>774</v>
       </c>
       <c r="B775" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="776" spans="1:2">
@@ -9312,7 +9327,7 @@
         <v>776</v>
       </c>
       <c r="B777" s="1">
-        <v>840</v>
+        <v>800</v>
       </c>
     </row>
     <row r="778" spans="1:2">
@@ -9320,7 +9335,7 @@
         <v>777</v>
       </c>
       <c r="B778" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="779" spans="1:2">
@@ -9328,7 +9343,7 @@
         <v>778</v>
       </c>
       <c r="B779" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="780" spans="1:2">
@@ -9336,7 +9351,7 @@
         <v>779</v>
       </c>
       <c r="B780" s="1">
-        <v>880</v>
+        <v>560</v>
       </c>
     </row>
     <row r="781" spans="1:2">
@@ -9344,7 +9359,7 @@
         <v>780</v>
       </c>
       <c r="B781" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="782" spans="1:2">
@@ -9352,7 +9367,7 @@
         <v>781</v>
       </c>
       <c r="B782" s="1">
-        <v>920</v>
+        <v>840</v>
       </c>
     </row>
     <row r="783" spans="1:2">
@@ -9360,7 +9375,7 @@
         <v>782</v>
       </c>
       <c r="B783" s="1">
-        <v>800</v>
+        <v>880</v>
       </c>
     </row>
     <row r="784" spans="1:2">
@@ -9368,7 +9383,7 @@
         <v>783</v>
       </c>
       <c r="B784" s="1">
-        <v>940</v>
+        <v>800</v>
       </c>
     </row>
     <row r="785" spans="1:2">
@@ -9376,7 +9391,7 @@
         <v>784</v>
       </c>
       <c r="B785" s="1">
-        <v>980</v>
+        <v>880</v>
       </c>
     </row>
     <row r="786" spans="1:2">
@@ -9384,7 +9399,7 @@
         <v>785</v>
       </c>
       <c r="B786" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="787" spans="1:2">
@@ -9392,7 +9407,7 @@
         <v>786</v>
       </c>
       <c r="B787" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="788" spans="1:2">
@@ -9400,7 +9415,7 @@
         <v>787</v>
       </c>
       <c r="B788" s="1">
-        <v>860</v>
+        <v>800</v>
       </c>
     </row>
     <row r="789" spans="1:2">
@@ -9408,7 +9423,7 @@
         <v>788</v>
       </c>
       <c r="B789" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="790" spans="1:2">
@@ -9416,7 +9431,7 @@
         <v>789</v>
       </c>
       <c r="B790" s="1">
-        <v>680</v>
+        <v>980</v>
       </c>
     </row>
     <row r="791" spans="1:2">
@@ -9424,7 +9439,7 @@
         <v>790</v>
       </c>
       <c r="B791" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="792" spans="1:2">
@@ -9432,7 +9447,7 @@
         <v>791</v>
       </c>
       <c r="B792" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="793" spans="1:2">
@@ -9440,7 +9455,7 @@
         <v>792</v>
       </c>
       <c r="B793" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="794" spans="1:2">
@@ -9448,7 +9463,7 @@
         <v>793</v>
       </c>
       <c r="B794" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="795" spans="1:2">
@@ -9456,7 +9471,7 @@
         <v>794</v>
       </c>
       <c r="B795" s="1">
-        <v>860</v>
+        <v>680</v>
       </c>
     </row>
     <row r="796" spans="1:2">
@@ -9464,7 +9479,7 @@
         <v>795</v>
       </c>
       <c r="B796" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="797" spans="1:2">
@@ -9472,7 +9487,7 @@
         <v>796</v>
       </c>
       <c r="B797" s="1">
-        <v>660</v>
+        <v>960</v>
       </c>
     </row>
     <row r="798" spans="1:2">
@@ -9480,7 +9495,7 @@
         <v>797</v>
       </c>
       <c r="B798" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="799" spans="1:2">
@@ -9488,7 +9503,7 @@
         <v>798</v>
       </c>
       <c r="B799" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="800" spans="1:2">
@@ -9496,7 +9511,7 @@
         <v>799</v>
       </c>
       <c r="B800" s="1">
-        <v>820</v>
+        <v>860</v>
       </c>
     </row>
     <row r="801" spans="1:2">
@@ -9504,7 +9519,7 @@
         <v>800</v>
       </c>
       <c r="B801" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="802" spans="1:2">
@@ -9512,7 +9527,7 @@
         <v>801</v>
       </c>
       <c r="B802" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="803" spans="1:2">
@@ -9520,7 +9535,7 @@
         <v>802</v>
       </c>
       <c r="B803" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="804" spans="1:2">
@@ -9528,7 +9543,7 @@
         <v>803</v>
       </c>
       <c r="B804" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="805" spans="1:2">
@@ -9536,7 +9551,7 @@
         <v>804</v>
       </c>
       <c r="B805" s="1">
-        <v>840</v>
+        <v>820</v>
       </c>
     </row>
     <row r="806" spans="1:2">
@@ -9544,7 +9559,7 @@
         <v>805</v>
       </c>
       <c r="B806" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="807" spans="1:2">
@@ -9560,7 +9575,7 @@
         <v>807</v>
       </c>
       <c r="B808" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="809" spans="1:2">
@@ -9568,7 +9583,7 @@
         <v>808</v>
       </c>
       <c r="B809" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="810" spans="1:2">
@@ -9576,7 +9591,7 @@
         <v>809</v>
       </c>
       <c r="B810" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="811" spans="1:2">
@@ -9584,7 +9599,7 @@
         <v>810</v>
       </c>
       <c r="B811" s="1">
-        <v>800</v>
+        <v>660</v>
       </c>
     </row>
     <row r="812" spans="1:2">
@@ -9592,7 +9607,7 @@
         <v>811</v>
       </c>
       <c r="B812" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="813" spans="1:2">
@@ -9600,7 +9615,7 @@
         <v>812</v>
       </c>
       <c r="B813" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="814" spans="1:2">
@@ -9608,7 +9623,7 @@
         <v>813</v>
       </c>
       <c r="B814" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="815" spans="1:2">
@@ -9616,7 +9631,7 @@
         <v>814</v>
       </c>
       <c r="B815" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="816" spans="1:2">
@@ -9624,7 +9639,7 @@
         <v>815</v>
       </c>
       <c r="B816" s="1">
-        <v>820</v>
+        <v>800</v>
       </c>
     </row>
     <row r="817" spans="1:2">
@@ -9632,7 +9647,7 @@
         <v>816</v>
       </c>
       <c r="B817" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="818" spans="1:2">
@@ -9640,7 +9655,7 @@
         <v>817</v>
       </c>
       <c r="B818" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="819" spans="1:2">
@@ -9648,7 +9663,7 @@
         <v>818</v>
       </c>
       <c r="B819" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="820" spans="1:2">
@@ -9656,7 +9671,7 @@
         <v>819</v>
       </c>
       <c r="B820" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="821" spans="1:2">
@@ -9664,7 +9679,7 @@
         <v>820</v>
       </c>
       <c r="B821" s="1">
-        <v>500</v>
+        <v>820</v>
       </c>
     </row>
     <row r="822" spans="1:2">
@@ -9672,7 +9687,7 @@
         <v>821</v>
       </c>
       <c r="B822" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="823" spans="1:2">
@@ -9680,7 +9695,7 @@
         <v>822</v>
       </c>
       <c r="B823" s="1">
-        <v>920</v>
+        <v>720</v>
       </c>
     </row>
     <row r="824" spans="1:2">
@@ -9688,7 +9703,7 @@
         <v>823</v>
       </c>
       <c r="B824" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="825" spans="1:2">
@@ -9696,7 +9711,7 @@
         <v>824</v>
       </c>
       <c r="B825" s="1">
-        <v>940</v>
+        <v>600</v>
       </c>
     </row>
     <row r="826" spans="1:2">
@@ -9704,7 +9719,7 @@
         <v>825</v>
       </c>
       <c r="B826" s="1">
-        <v>1040</v>
+        <v>500</v>
       </c>
     </row>
     <row r="827" spans="1:2">
@@ -9712,7 +9727,7 @@
         <v>826</v>
       </c>
       <c r="B827" s="1">
-        <v>940</v>
+        <v>760</v>
       </c>
     </row>
     <row r="828" spans="1:2">
@@ -9720,7 +9735,7 @@
         <v>827</v>
       </c>
       <c r="B828" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="829" spans="1:2">
@@ -9728,7 +9743,7 @@
         <v>828</v>
       </c>
       <c r="B829" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="830" spans="1:2">
@@ -9736,7 +9751,7 @@
         <v>829</v>
       </c>
       <c r="B830" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="831" spans="1:2">
@@ -9744,7 +9759,7 @@
         <v>830</v>
       </c>
       <c r="B831" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="832" spans="1:2">
@@ -9752,7 +9767,7 @@
         <v>831</v>
       </c>
       <c r="B832" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="833" spans="1:2">
@@ -9760,7 +9775,7 @@
         <v>832</v>
       </c>
       <c r="B833" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="834" spans="1:2">
@@ -9768,7 +9783,7 @@
         <v>833</v>
       </c>
       <c r="B834" s="1">
-        <v>1100</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="835" spans="1:2">
@@ -9776,7 +9791,7 @@
         <v>834</v>
       </c>
       <c r="B835" s="1">
-        <v>740</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="836" spans="1:2">
@@ -9784,7 +9799,7 @@
         <v>835</v>
       </c>
       <c r="B836" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="837" spans="1:2">
@@ -9792,7 +9807,7 @@
         <v>836</v>
       </c>
       <c r="B837" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="838" spans="1:2">
@@ -9800,7 +9815,7 @@
         <v>837</v>
       </c>
       <c r="B838" s="1">
-        <v>500</v>
+        <v>960</v>
       </c>
     </row>
     <row r="839" spans="1:2">
@@ -9808,7 +9823,7 @@
         <v>838</v>
       </c>
       <c r="B839" s="1">
-        <v>440</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="840" spans="1:2">
@@ -9816,7 +9831,7 @@
         <v>839</v>
       </c>
       <c r="B840" s="1">
-        <v>560</v>
+        <v>740</v>
       </c>
     </row>
     <row r="841" spans="1:2">
@@ -9824,7 +9839,7 @@
         <v>840</v>
       </c>
       <c r="B841" s="1">
-        <v>500</v>
+        <v>820</v>
       </c>
     </row>
     <row r="842" spans="1:2">
@@ -9832,7 +9847,7 @@
         <v>841</v>
       </c>
       <c r="B842" s="1">
-        <v>820</v>
+        <v>440</v>
       </c>
     </row>
     <row r="843" spans="1:2">
@@ -9840,7 +9855,7 @@
         <v>842</v>
       </c>
       <c r="B843" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="844" spans="1:2">
@@ -9848,7 +9863,7 @@
         <v>843</v>
       </c>
       <c r="B844" s="1">
-        <v>760</v>
+        <v>440</v>
       </c>
     </row>
     <row r="845" spans="1:2">
@@ -9856,7 +9871,7 @@
         <v>844</v>
       </c>
       <c r="B845" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="846" spans="1:2">
@@ -9864,7 +9879,7 @@
         <v>845</v>
       </c>
       <c r="B846" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="847" spans="1:2">
@@ -9872,7 +9887,7 @@
         <v>846</v>
       </c>
       <c r="B847" s="1">
-        <v>400</v>
+        <v>820</v>
       </c>
     </row>
     <row r="848" spans="1:2">
@@ -9880,7 +9895,7 @@
         <v>847</v>
       </c>
       <c r="B848" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="849" spans="1:2">
@@ -9888,7 +9903,7 @@
         <v>848</v>
       </c>
       <c r="B849" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="850" spans="1:2">
@@ -9896,7 +9911,7 @@
         <v>849</v>
       </c>
       <c r="B850" s="1">
-        <v>380</v>
+        <v>840</v>
       </c>
     </row>
     <row r="851" spans="1:2">
@@ -9904,7 +9919,7 @@
         <v>850</v>
       </c>
       <c r="B851" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="852" spans="1:2">
@@ -9912,7 +9927,7 @@
         <v>851</v>
       </c>
       <c r="B852" s="1">
-        <v>520</v>
+        <v>400</v>
       </c>
     </row>
     <row r="853" spans="1:2">
@@ -9920,7 +9935,7 @@
         <v>852</v>
       </c>
       <c r="B853" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="854" spans="1:2">
@@ -9928,7 +9943,7 @@
         <v>853</v>
       </c>
       <c r="B854" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="855" spans="1:2">
@@ -9936,7 +9951,7 @@
         <v>854</v>
       </c>
       <c r="B855" s="1">
-        <v>860</v>
+        <v>380</v>
       </c>
     </row>
     <row r="856" spans="1:2">
@@ -9944,7 +9959,7 @@
         <v>855</v>
       </c>
       <c r="B856" s="1">
-        <v>680</v>
+        <v>380</v>
       </c>
     </row>
     <row r="857" spans="1:2">
@@ -9952,7 +9967,7 @@
         <v>856</v>
       </c>
       <c r="B857" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="858" spans="1:2">
@@ -9960,7 +9975,7 @@
         <v>857</v>
       </c>
       <c r="B858" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="859" spans="1:2">
@@ -9968,7 +9983,7 @@
         <v>858</v>
       </c>
       <c r="B859" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="860" spans="1:2">
@@ -9976,7 +9991,7 @@
         <v>859</v>
       </c>
       <c r="B860" s="1">
-        <v>820</v>
+        <v>860</v>
       </c>
     </row>
     <row r="861" spans="1:2">
@@ -9984,7 +9999,7 @@
         <v>860</v>
       </c>
       <c r="B861" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="862" spans="1:2">
@@ -9992,7 +10007,7 @@
         <v>861</v>
       </c>
       <c r="B862" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="863" spans="1:2">
@@ -10000,7 +10015,7 @@
         <v>862</v>
       </c>
       <c r="B863" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="864" spans="1:2">
@@ -10008,7 +10023,7 @@
         <v>863</v>
       </c>
       <c r="B864" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="865" spans="1:2">
@@ -10016,7 +10031,7 @@
         <v>864</v>
       </c>
       <c r="B865" s="1">
-        <v>500</v>
+        <v>820</v>
       </c>
     </row>
     <row r="866" spans="1:2">
@@ -10024,7 +10039,7 @@
         <v>865</v>
       </c>
       <c r="B866" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="867" spans="1:2">
@@ -10032,7 +10047,7 @@
         <v>866</v>
       </c>
       <c r="B867" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="868" spans="1:2">
@@ -10040,7 +10055,7 @@
         <v>867</v>
       </c>
       <c r="B868" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="869" spans="1:2">
@@ -10048,7 +10063,7 @@
         <v>868</v>
       </c>
       <c r="B869" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="870" spans="1:2">
@@ -10056,7 +10071,7 @@
         <v>869</v>
       </c>
       <c r="B870" s="1">
-        <v>920</v>
+        <v>500</v>
       </c>
     </row>
     <row r="871" spans="1:2">
@@ -10064,7 +10079,7 @@
         <v>870</v>
       </c>
       <c r="B871" s="1">
-        <v>1000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="872" spans="1:2">
@@ -10072,7 +10087,7 @@
         <v>871</v>
       </c>
       <c r="B872" s="1">
-        <v>940</v>
+        <v>840</v>
       </c>
     </row>
     <row r="873" spans="1:2">
@@ -10080,7 +10095,7 @@
         <v>872</v>
       </c>
       <c r="B873" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="874" spans="1:2">
@@ -10088,7 +10103,7 @@
         <v>873</v>
       </c>
       <c r="B874" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="875" spans="1:2">
@@ -10096,7 +10111,7 @@
         <v>874</v>
       </c>
       <c r="B875" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="876" spans="1:2">
@@ -10104,7 +10119,7 @@
         <v>875</v>
       </c>
       <c r="B876" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="877" spans="1:2">
@@ -10112,7 +10127,7 @@
         <v>876</v>
       </c>
       <c r="B877" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="878" spans="1:2">
@@ -10120,7 +10135,7 @@
         <v>877</v>
       </c>
       <c r="B878" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="879" spans="1:2">
@@ -10128,7 +10143,7 @@
         <v>878</v>
       </c>
       <c r="B879" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="880" spans="1:2">
@@ -10136,7 +10151,7 @@
         <v>879</v>
       </c>
       <c r="B880" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="881" spans="1:2">
@@ -10144,7 +10159,7 @@
         <v>880</v>
       </c>
       <c r="B881" s="1">
-        <v>1100</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="882" spans="1:2">
@@ -10152,7 +10167,7 @@
         <v>881</v>
       </c>
       <c r="B882" s="1">
-        <v>740</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="883" spans="1:2">
@@ -10160,7 +10175,7 @@
         <v>882</v>
       </c>
       <c r="B883" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="884" spans="1:2">
@@ -10168,7 +10183,7 @@
         <v>883</v>
       </c>
       <c r="B884" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="885" spans="1:2">
@@ -10176,7 +10191,7 @@
         <v>884</v>
       </c>
       <c r="B885" s="1">
-        <v>500</v>
+        <v>960</v>
       </c>
     </row>
     <row r="886" spans="1:2">
@@ -10184,7 +10199,7 @@
         <v>885</v>
       </c>
       <c r="B886" s="1">
-        <v>440</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="887" spans="1:2">
@@ -10192,7 +10207,7 @@
         <v>886</v>
       </c>
       <c r="B887" s="1">
-        <v>560</v>
+        <v>740</v>
       </c>
     </row>
     <row r="888" spans="1:2">
@@ -10200,7 +10215,7 @@
         <v>887</v>
       </c>
       <c r="B888" s="1">
-        <v>500</v>
+        <v>820</v>
       </c>
     </row>
     <row r="889" spans="1:2">
@@ -10208,7 +10223,7 @@
         <v>888</v>
       </c>
       <c r="B889" s="1">
-        <v>820</v>
+        <v>440</v>
       </c>
     </row>
     <row r="890" spans="1:2">
@@ -10216,7 +10231,7 @@
         <v>889</v>
       </c>
       <c r="B890" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="891" spans="1:2">
@@ -10224,7 +10239,7 @@
         <v>890</v>
       </c>
       <c r="B891" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="892" spans="1:2">
@@ -10232,7 +10247,7 @@
         <v>891</v>
       </c>
       <c r="B892" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="893" spans="1:2">
@@ -10240,7 +10255,7 @@
         <v>892</v>
       </c>
       <c r="B893" s="1">
-        <v>480</v>
+        <v>500</v>
       </c>
     </row>
     <row r="894" spans="1:2">
@@ -10248,7 +10263,7 @@
         <v>893</v>
       </c>
       <c r="B894" s="1">
-        <v>480</v>
+        <v>820</v>
       </c>
     </row>
     <row r="895" spans="1:2">
@@ -10256,7 +10271,7 @@
         <v>894</v>
       </c>
       <c r="B895" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="896" spans="1:2">
@@ -10264,7 +10279,7 @@
         <v>895</v>
       </c>
       <c r="B896" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="897" spans="1:2">
@@ -10272,7 +10287,7 @@
         <v>896</v>
       </c>
       <c r="B897" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="898" spans="1:2">
@@ -10280,7 +10295,7 @@
         <v>897</v>
       </c>
       <c r="B898" s="1">
-        <v>440</v>
+        <v>480</v>
       </c>
     </row>
     <row r="899" spans="1:2">
@@ -10288,7 +10303,7 @@
         <v>898</v>
       </c>
       <c r="B899" s="1">
-        <v>380</v>
+        <v>480</v>
       </c>
     </row>
     <row r="900" spans="1:2">
@@ -10296,7 +10311,7 @@
         <v>899</v>
       </c>
       <c r="B900" s="1">
-        <v>600</v>
+        <v>480</v>
       </c>
     </row>
     <row r="901" spans="1:2">
@@ -10304,7 +10319,7 @@
         <v>900</v>
       </c>
       <c r="B901" s="1">
-        <v>820</v>
+        <v>520</v>
       </c>
     </row>
     <row r="902" spans="1:2">
@@ -10312,7 +10327,7 @@
         <v>901</v>
       </c>
       <c r="B902" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="903" spans="1:2">
@@ -10320,7 +10335,7 @@
         <v>902</v>
       </c>
       <c r="B903" s="1">
-        <v>580</v>
+        <v>440</v>
       </c>
     </row>
     <row r="904" spans="1:2">
@@ -10328,7 +10343,7 @@
         <v>903</v>
       </c>
       <c r="B904" s="1">
-        <v>560</v>
+        <v>380</v>
       </c>
     </row>
     <row r="905" spans="1:2">
@@ -10336,7 +10351,7 @@
         <v>904</v>
       </c>
       <c r="B905" s="1">
-        <v>580</v>
+        <v>600</v>
       </c>
     </row>
     <row r="906" spans="1:2">
@@ -10344,7 +10359,7 @@
         <v>905</v>
       </c>
       <c r="B906" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="907" spans="1:2">
@@ -10352,7 +10367,7 @@
         <v>906</v>
       </c>
       <c r="B907" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="908" spans="1:2">
@@ -10360,6 +10375,46 @@
         <v>907</v>
       </c>
       <c r="B908" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="909" spans="1:2">
+      <c r="A909" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="B909" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="910" spans="1:2">
+      <c r="A910" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="B910" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="911" spans="1:2">
+      <c r="A911" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="B911" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="912" spans="1:2">
+      <c r="A912" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="B912" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="913" spans="1:2">
+      <c r="A913" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="B913" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="913">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="915">
   <si>
     <t>Наименование</t>
   </si>
@@ -209,6 +209,9 @@
     <t>Big Village - Пивной Шлем (NEDIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Big Village - ПОБЕГ (NEIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Big Village - Предисловие (WC IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1662,6 +1665,9 @@
   </si>
   <si>
     <t>вынос_Big Village - Пивной Шлем (NEDIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Big Village - ПОБЕГ (NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_Big Village - Предисловие (WC IPA), РОЗЛИВ, Россия</t>
@@ -3107,7 +3113,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B913"/>
+  <dimension ref="A1:B915"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -3623,7 +3629,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -3631,7 +3637,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -3647,7 +3653,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -3655,7 +3661,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -3663,7 +3669,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -3671,7 +3677,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -3687,7 +3693,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -3695,7 +3701,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -3703,7 +3709,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -3711,7 +3717,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -3719,7 +3725,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -3727,7 +3733,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -3743,7 +3749,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -3759,7 +3765,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -3767,7 +3773,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -3775,7 +3781,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>560</v>
+        <v>680</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -3783,7 +3789,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>880</v>
+        <v>560</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -3791,7 +3797,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -3799,7 +3805,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -3807,7 +3813,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -3815,7 +3821,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -3823,7 +3829,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3831,7 +3837,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -3839,7 +3845,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3847,7 +3853,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>640</v>
+        <v>880</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3855,7 +3861,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -3863,7 +3869,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3871,7 +3877,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3879,7 +3885,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3887,7 +3893,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -3895,7 +3901,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3903,7 +3909,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -3919,7 +3925,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3927,7 +3933,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3935,7 +3941,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -3943,7 +3949,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3951,7 +3957,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>540</v>
+        <v>560</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3959,7 +3965,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>860</v>
+        <v>540</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3967,7 +3973,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -3983,7 +3989,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -3991,7 +3997,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3999,7 +4005,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>440</v>
+        <v>720</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -4007,7 +4013,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -4015,7 +4021,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>460</v>
+        <v>560</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -4031,7 +4037,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>960</v>
+        <v>460</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -4039,7 +4045,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>940</v>
+        <v>960</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -4047,7 +4053,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -4063,7 +4069,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>660</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -4071,7 +4077,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>480</v>
+        <v>660</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -4079,7 +4085,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>400</v>
+        <v>480</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -4087,7 +4093,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>720</v>
+        <v>400</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -4095,7 +4101,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -4103,7 +4109,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>500</v>
+        <v>560</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -4111,7 +4117,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -4119,7 +4125,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>500</v>
+        <v>760</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -4127,7 +4133,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>940</v>
+        <v>500</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -4135,7 +4141,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>820</v>
+        <v>940</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -4143,7 +4149,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -4151,7 +4157,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -4159,7 +4165,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -4167,7 +4173,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -4175,7 +4181,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -4183,7 +4189,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>680</v>
+        <v>960</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -4191,7 +4197,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>420</v>
+        <v>680</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -4199,7 +4205,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -4207,7 +4213,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -4215,7 +4221,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -4223,7 +4229,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -4231,7 +4237,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -4239,7 +4245,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -4247,7 +4253,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -4255,7 +4261,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -4263,7 +4269,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>580</v>
+        <v>880</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -4271,7 +4277,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -4279,7 +4285,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -4287,7 +4293,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>620</v>
+        <v>860</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -4295,7 +4301,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -4303,7 +4309,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -4311,7 +4317,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -4319,7 +4325,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -4327,7 +4333,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>900</v>
+        <v>960</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -4335,7 +4341,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -4343,7 +4349,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -4351,7 +4357,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -4359,7 +4365,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>500</v>
+        <v>780</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -4367,7 +4373,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>580</v>
+        <v>500</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -4375,7 +4381,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -4383,7 +4389,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -4391,7 +4397,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>980</v>
+        <v>520</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -4399,7 +4405,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>1100</v>
+        <v>980</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -4407,7 +4413,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>1060</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -4423,7 +4429,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>1000</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -4431,7 +4437,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -4447,7 +4453,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -4455,7 +4461,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>1080</v>
+        <v>560</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4463,12 +4469,12 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>840</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B170" s="1">
         <v>840</v>
@@ -4487,7 +4493,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="1">
-        <v>420</v>
+        <v>840</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4495,7 +4501,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="1">
-        <v>520</v>
+        <v>420</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4503,7 +4509,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4511,7 +4517,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="1">
-        <v>460</v>
+        <v>720</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4519,7 +4525,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="1">
-        <v>560</v>
+        <v>460</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4527,7 +4533,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4535,7 +4541,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4543,7 +4549,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4551,7 +4557,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4559,7 +4565,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="1">
-        <v>980</v>
+        <v>520</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4567,7 +4573,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="1">
-        <v>540</v>
+        <v>980</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4575,7 +4581,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4583,7 +4589,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4591,7 +4597,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4599,7 +4605,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="1">
-        <v>560</v>
+        <v>760</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4607,7 +4613,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="1">
-        <v>1100</v>
+        <v>560</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4639,7 +4645,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4647,7 +4653,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4655,7 +4661,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4663,7 +4669,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4695,7 +4701,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4703,7 +4709,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4711,7 +4717,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4719,7 +4725,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4727,7 +4733,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4735,7 +4741,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4743,7 +4749,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4751,7 +4757,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="1">
-        <v>980</v>
+        <v>700</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4759,7 +4765,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="1">
-        <v>460</v>
+        <v>980</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4767,7 +4773,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4775,7 +4781,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="1">
-        <v>720</v>
+        <v>580</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4783,7 +4789,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4791,7 +4797,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4799,7 +4805,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="1">
-        <v>260</v>
+        <v>780</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4815,7 +4821,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4831,7 +4837,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4839,7 +4845,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4847,7 +4853,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4855,7 +4861,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="1">
-        <v>500</v>
+        <v>760</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4863,7 +4869,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4871,7 +4877,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="1">
-        <v>740</v>
+        <v>400</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4879,7 +4885,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4887,7 +4893,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4895,7 +4901,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4903,7 +4909,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4911,7 +4917,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4919,7 +4925,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4935,7 +4941,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4943,7 +4949,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4951,7 +4957,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4959,7 +4965,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4967,7 +4973,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="1">
-        <v>580</v>
+        <v>860</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4975,7 +4981,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4983,7 +4989,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="1">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4991,7 +4997,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4999,7 +5005,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -5007,7 +5013,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -5015,7 +5021,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -5023,7 +5029,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -5031,7 +5037,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -5039,7 +5045,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -5047,7 +5053,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -5055,7 +5061,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -5063,7 +5069,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="1">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -5071,7 +5077,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="1">
-        <v>480</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -5079,7 +5085,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -5087,7 +5093,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -5095,7 +5101,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -5103,7 +5109,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -5111,7 +5117,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -5119,7 +5125,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -5127,7 +5133,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -5135,7 +5141,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -5143,7 +5149,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="1">
-        <v>900</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -5151,7 +5157,7 @@
         <v>254</v>
       </c>
       <c r="B255" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -5159,7 +5165,7 @@
         <v>255</v>
       </c>
       <c r="B256" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -5167,7 +5173,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -5175,7 +5181,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -5191,7 +5197,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -5207,7 +5213,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -5215,7 +5221,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -5223,7 +5229,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -5231,7 +5237,7 @@
         <v>264</v>
       </c>
       <c r="B265" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -5239,7 +5245,7 @@
         <v>265</v>
       </c>
       <c r="B266" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -5247,7 +5253,7 @@
         <v>266</v>
       </c>
       <c r="B267" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -5255,7 +5261,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="1">
-        <v>960</v>
+        <v>840</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -5263,7 +5269,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -5279,7 +5285,7 @@
         <v>270</v>
       </c>
       <c r="B271" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -5287,7 +5293,7 @@
         <v>271</v>
       </c>
       <c r="B272" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -5295,7 +5301,7 @@
         <v>272</v>
       </c>
       <c r="B273" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -5303,7 +5309,7 @@
         <v>273</v>
       </c>
       <c r="B274" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -5311,7 +5317,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -5319,7 +5325,7 @@
         <v>275</v>
       </c>
       <c r="B276" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -5335,7 +5341,7 @@
         <v>277</v>
       </c>
       <c r="B278" s="1">
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -5343,7 +5349,7 @@
         <v>278</v>
       </c>
       <c r="B279" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -5351,7 +5357,7 @@
         <v>279</v>
       </c>
       <c r="B280" s="1">
-        <v>758</v>
+        <v>500</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -5359,7 +5365,7 @@
         <v>280</v>
       </c>
       <c r="B281" s="1">
-        <v>2273</v>
+        <v>758</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -5367,7 +5373,7 @@
         <v>281</v>
       </c>
       <c r="B282" s="1">
-        <v>1515</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -5375,7 +5381,7 @@
         <v>282</v>
       </c>
       <c r="B283" s="1">
-        <v>520</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -5383,7 +5389,7 @@
         <v>283</v>
       </c>
       <c r="B284" s="1">
-        <v>4000</v>
+        <v>520</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -5391,7 +5397,7 @@
         <v>284</v>
       </c>
       <c r="B285" s="1">
-        <v>560</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -5399,7 +5405,7 @@
         <v>285</v>
       </c>
       <c r="B286" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5407,7 +5413,7 @@
         <v>286</v>
       </c>
       <c r="B287" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5423,7 +5429,7 @@
         <v>288</v>
       </c>
       <c r="B289" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5431,7 +5437,7 @@
         <v>289</v>
       </c>
       <c r="B290" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5439,7 +5445,7 @@
         <v>290</v>
       </c>
       <c r="B291" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5447,7 +5453,7 @@
         <v>291</v>
       </c>
       <c r="B292" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5455,7 +5461,7 @@
         <v>292</v>
       </c>
       <c r="B293" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5463,7 +5469,7 @@
         <v>293</v>
       </c>
       <c r="B294" s="1">
-        <v>680</v>
+        <v>520</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5471,7 +5477,7 @@
         <v>294</v>
       </c>
       <c r="B295" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5479,7 +5485,7 @@
         <v>295</v>
       </c>
       <c r="B296" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5487,7 +5493,7 @@
         <v>296</v>
       </c>
       <c r="B297" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5495,7 +5501,7 @@
         <v>297</v>
       </c>
       <c r="B298" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5503,7 +5509,7 @@
         <v>298</v>
       </c>
       <c r="B299" s="1">
-        <v>660</v>
+        <v>380</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5511,7 +5517,7 @@
         <v>299</v>
       </c>
       <c r="B300" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5519,7 +5525,7 @@
         <v>300</v>
       </c>
       <c r="B301" s="1">
-        <v>540</v>
+        <v>900</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5527,7 +5533,7 @@
         <v>301</v>
       </c>
       <c r="B302" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5535,7 +5541,7 @@
         <v>302</v>
       </c>
       <c r="B303" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5543,7 +5549,7 @@
         <v>303</v>
       </c>
       <c r="B304" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5551,7 +5557,7 @@
         <v>304</v>
       </c>
       <c r="B305" s="1">
-        <v>460</v>
+        <v>580</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5559,7 +5565,7 @@
         <v>305</v>
       </c>
       <c r="B306" s="1">
-        <v>520</v>
+        <v>460</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5567,7 +5573,7 @@
         <v>306</v>
       </c>
       <c r="B307" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5575,7 +5581,7 @@
         <v>307</v>
       </c>
       <c r="B308" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5583,7 +5589,7 @@
         <v>308</v>
       </c>
       <c r="B309" s="1">
-        <v>860</v>
+        <v>900</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5591,7 +5597,7 @@
         <v>309</v>
       </c>
       <c r="B310" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5615,7 +5621,7 @@
         <v>312</v>
       </c>
       <c r="B313" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5631,7 +5637,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="1">
-        <v>980</v>
+        <v>560</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5639,7 +5645,7 @@
         <v>315</v>
       </c>
       <c r="B316" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5655,7 +5661,7 @@
         <v>317</v>
       </c>
       <c r="B318" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5663,7 +5669,7 @@
         <v>318</v>
       </c>
       <c r="B319" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5671,7 +5677,7 @@
         <v>319</v>
       </c>
       <c r="B320" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5679,7 +5685,7 @@
         <v>320</v>
       </c>
       <c r="B321" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5687,7 +5693,7 @@
         <v>321</v>
       </c>
       <c r="B322" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5695,7 +5701,7 @@
         <v>322</v>
       </c>
       <c r="B323" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5703,7 +5709,7 @@
         <v>323</v>
       </c>
       <c r="B324" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5711,7 +5717,7 @@
         <v>324</v>
       </c>
       <c r="B325" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5727,7 +5733,7 @@
         <v>326</v>
       </c>
       <c r="B327" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5735,7 +5741,7 @@
         <v>327</v>
       </c>
       <c r="B328" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5743,7 +5749,7 @@
         <v>328</v>
       </c>
       <c r="B329" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5751,7 +5757,7 @@
         <v>329</v>
       </c>
       <c r="B330" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5759,7 +5765,7 @@
         <v>330</v>
       </c>
       <c r="B331" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5767,7 +5773,7 @@
         <v>331</v>
       </c>
       <c r="B332" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5775,7 +5781,7 @@
         <v>332</v>
       </c>
       <c r="B333" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5783,7 +5789,7 @@
         <v>333</v>
       </c>
       <c r="B334" s="1">
-        <v>520</v>
+        <v>680</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5791,7 +5797,7 @@
         <v>334</v>
       </c>
       <c r="B335" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5799,7 +5805,7 @@
         <v>335</v>
       </c>
       <c r="B336" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5807,7 +5813,7 @@
         <v>336</v>
       </c>
       <c r="B337" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5815,7 +5821,7 @@
         <v>337</v>
       </c>
       <c r="B338" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5823,7 +5829,7 @@
         <v>338</v>
       </c>
       <c r="B339" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5831,7 +5837,7 @@
         <v>339</v>
       </c>
       <c r="B340" s="1">
-        <v>580</v>
+        <v>840</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5839,7 +5845,7 @@
         <v>340</v>
       </c>
       <c r="B341" s="1">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5847,7 +5853,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5855,7 +5861,7 @@
         <v>342</v>
       </c>
       <c r="B343" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5863,7 +5869,7 @@
         <v>343</v>
       </c>
       <c r="B344" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5871,7 +5877,7 @@
         <v>344</v>
       </c>
       <c r="B345" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5879,7 +5885,7 @@
         <v>345</v>
       </c>
       <c r="B346" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5887,7 +5893,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="1">
-        <v>1000</v>
+        <v>880</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5895,7 +5901,7 @@
         <v>347</v>
       </c>
       <c r="B348" s="1">
-        <v>520</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5903,7 +5909,7 @@
         <v>348</v>
       </c>
       <c r="B349" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5911,7 +5917,7 @@
         <v>349</v>
       </c>
       <c r="B350" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5919,7 +5925,7 @@
         <v>350</v>
       </c>
       <c r="B351" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5927,7 +5933,7 @@
         <v>351</v>
       </c>
       <c r="B352" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5935,7 +5941,7 @@
         <v>352</v>
       </c>
       <c r="B353" s="1">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5943,7 +5949,7 @@
         <v>353</v>
       </c>
       <c r="B354" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5951,7 +5957,7 @@
         <v>354</v>
       </c>
       <c r="B355" s="1">
-        <v>320</v>
+        <v>520</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5959,7 +5965,7 @@
         <v>355</v>
       </c>
       <c r="B356" s="1">
-        <v>540</v>
+        <v>320</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5967,7 +5973,7 @@
         <v>356</v>
       </c>
       <c r="B357" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5975,7 +5981,7 @@
         <v>357</v>
       </c>
       <c r="B358" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5991,7 +5997,7 @@
         <v>359</v>
       </c>
       <c r="B360" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5999,7 +6005,7 @@
         <v>360</v>
       </c>
       <c r="B361" s="1">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -6007,7 +6013,7 @@
         <v>361</v>
       </c>
       <c r="B362" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -6015,7 +6021,7 @@
         <v>362</v>
       </c>
       <c r="B363" s="1">
-        <v>480</v>
+        <v>800</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -6023,7 +6029,7 @@
         <v>363</v>
       </c>
       <c r="B364" s="1">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -6031,7 +6037,7 @@
         <v>364</v>
       </c>
       <c r="B365" s="1">
-        <v>520</v>
+        <v>800</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -6039,7 +6045,7 @@
         <v>365</v>
       </c>
       <c r="B366" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -6047,7 +6053,7 @@
         <v>366</v>
       </c>
       <c r="B367" s="1">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -6055,7 +6061,7 @@
         <v>367</v>
       </c>
       <c r="B368" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -6071,7 +6077,7 @@
         <v>369</v>
       </c>
       <c r="B370" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -6087,7 +6093,7 @@
         <v>371</v>
       </c>
       <c r="B372" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -6095,7 +6101,7 @@
         <v>372</v>
       </c>
       <c r="B373" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -6103,7 +6109,7 @@
         <v>373</v>
       </c>
       <c r="B374" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -6111,7 +6117,7 @@
         <v>374</v>
       </c>
       <c r="B375" s="1">
-        <v>880</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -6119,7 +6125,7 @@
         <v>375</v>
       </c>
       <c r="B376" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -6127,7 +6133,7 @@
         <v>376</v>
       </c>
       <c r="B377" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -6135,7 +6141,7 @@
         <v>377</v>
       </c>
       <c r="B378" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -6143,7 +6149,7 @@
         <v>378</v>
       </c>
       <c r="B379" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -6151,7 +6157,7 @@
         <v>379</v>
       </c>
       <c r="B380" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -6159,7 +6165,7 @@
         <v>380</v>
       </c>
       <c r="B381" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -6167,7 +6173,7 @@
         <v>381</v>
       </c>
       <c r="B382" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -6175,7 +6181,7 @@
         <v>382</v>
       </c>
       <c r="B383" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -6191,7 +6197,7 @@
         <v>384</v>
       </c>
       <c r="B385" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -6207,7 +6213,7 @@
         <v>386</v>
       </c>
       <c r="B387" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -6215,7 +6221,7 @@
         <v>387</v>
       </c>
       <c r="B388" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -6223,7 +6229,7 @@
         <v>388</v>
       </c>
       <c r="B389" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -6231,7 +6237,7 @@
         <v>389</v>
       </c>
       <c r="B390" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -6239,7 +6245,7 @@
         <v>390</v>
       </c>
       <c r="B391" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -6247,7 +6253,7 @@
         <v>391</v>
       </c>
       <c r="B392" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -6255,7 +6261,7 @@
         <v>392</v>
       </c>
       <c r="B393" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -6263,7 +6269,7 @@
         <v>393</v>
       </c>
       <c r="B394" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -6271,7 +6277,7 @@
         <v>394</v>
       </c>
       <c r="B395" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -6279,7 +6285,7 @@
         <v>395</v>
       </c>
       <c r="B396" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -6287,7 +6293,7 @@
         <v>396</v>
       </c>
       <c r="B397" s="1">
-        <v>640</v>
+        <v>480</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -6295,7 +6301,7 @@
         <v>397</v>
       </c>
       <c r="B398" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -6303,7 +6309,7 @@
         <v>398</v>
       </c>
       <c r="B399" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -6311,7 +6317,7 @@
         <v>399</v>
       </c>
       <c r="B400" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -6319,7 +6325,7 @@
         <v>400</v>
       </c>
       <c r="B401" s="1">
-        <v>520</v>
+        <v>860</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -6327,7 +6333,7 @@
         <v>401</v>
       </c>
       <c r="B402" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -6335,7 +6341,7 @@
         <v>402</v>
       </c>
       <c r="B403" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -6351,7 +6357,7 @@
         <v>404</v>
       </c>
       <c r="B405" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -6359,7 +6365,7 @@
         <v>405</v>
       </c>
       <c r="B406" s="1">
-        <v>700</v>
+        <v>420</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -6367,7 +6373,7 @@
         <v>406</v>
       </c>
       <c r="B407" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -6375,7 +6381,7 @@
         <v>407</v>
       </c>
       <c r="B408" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -6383,7 +6389,7 @@
         <v>408</v>
       </c>
       <c r="B409" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -6391,7 +6397,7 @@
         <v>409</v>
       </c>
       <c r="B410" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -6399,7 +6405,7 @@
         <v>410</v>
       </c>
       <c r="B411" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -6407,7 +6413,7 @@
         <v>411</v>
       </c>
       <c r="B412" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -6415,7 +6421,7 @@
         <v>412</v>
       </c>
       <c r="B413" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -6423,7 +6429,7 @@
         <v>413</v>
       </c>
       <c r="B414" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -6431,7 +6437,7 @@
         <v>414</v>
       </c>
       <c r="B415" s="1">
-        <v>440</v>
+        <v>620</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -6439,7 +6445,7 @@
         <v>415</v>
       </c>
       <c r="B416" s="1">
-        <v>1100</v>
+        <v>440</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -6455,7 +6461,7 @@
         <v>417</v>
       </c>
       <c r="B418" s="1">
-        <v>320</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -6463,7 +6469,7 @@
         <v>418</v>
       </c>
       <c r="B419" s="1">
-        <v>940</v>
+        <v>320</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -6471,7 +6477,7 @@
         <v>419</v>
       </c>
       <c r="B420" s="1">
-        <v>320</v>
+        <v>940</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -6479,7 +6485,7 @@
         <v>420</v>
       </c>
       <c r="B421" s="1">
-        <v>960</v>
+        <v>320</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -6487,7 +6493,7 @@
         <v>421</v>
       </c>
       <c r="B422" s="1">
-        <v>820</v>
+        <v>960</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -6495,7 +6501,7 @@
         <v>422</v>
       </c>
       <c r="B423" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -6503,7 +6509,7 @@
         <v>423</v>
       </c>
       <c r="B424" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -6519,7 +6525,7 @@
         <v>425</v>
       </c>
       <c r="B426" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -6527,7 +6533,7 @@
         <v>426</v>
       </c>
       <c r="B427" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -6543,7 +6549,7 @@
         <v>428</v>
       </c>
       <c r="B429" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6551,7 +6557,7 @@
         <v>429</v>
       </c>
       <c r="B430" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6559,7 +6565,7 @@
         <v>430</v>
       </c>
       <c r="B431" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6567,7 +6573,7 @@
         <v>431</v>
       </c>
       <c r="B432" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6575,7 +6581,7 @@
         <v>432</v>
       </c>
       <c r="B433" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6583,7 +6589,7 @@
         <v>433</v>
       </c>
       <c r="B434" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6591,7 +6597,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6607,7 +6613,7 @@
         <v>436</v>
       </c>
       <c r="B437" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6615,7 +6621,7 @@
         <v>437</v>
       </c>
       <c r="B438" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6623,7 +6629,7 @@
         <v>438</v>
       </c>
       <c r="B439" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6631,7 +6637,7 @@
         <v>439</v>
       </c>
       <c r="B440" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6639,7 +6645,7 @@
         <v>440</v>
       </c>
       <c r="B441" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6647,7 +6653,7 @@
         <v>441</v>
       </c>
       <c r="B442" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6655,7 +6661,7 @@
         <v>442</v>
       </c>
       <c r="B443" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6663,7 +6669,7 @@
         <v>443</v>
       </c>
       <c r="B444" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6671,7 +6677,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="1">
-        <v>700</v>
+        <v>440</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6679,7 +6685,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6695,7 +6701,7 @@
         <v>447</v>
       </c>
       <c r="B448" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6703,7 +6709,7 @@
         <v>448</v>
       </c>
       <c r="B449" s="1">
-        <v>560</v>
+        <v>800</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6711,7 +6717,7 @@
         <v>449</v>
       </c>
       <c r="B450" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6719,7 +6725,7 @@
         <v>450</v>
       </c>
       <c r="B451" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6727,7 +6733,7 @@
         <v>451</v>
       </c>
       <c r="B452" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6735,7 +6741,7 @@
         <v>452</v>
       </c>
       <c r="B453" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6743,7 +6749,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6751,7 +6757,7 @@
         <v>454</v>
       </c>
       <c r="B455" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6759,7 +6765,7 @@
         <v>455</v>
       </c>
       <c r="B456" s="1">
-        <v>720</v>
+        <v>620</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6767,7 +6773,7 @@
         <v>456</v>
       </c>
       <c r="B457" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6775,7 +6781,7 @@
         <v>457</v>
       </c>
       <c r="B458" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6791,7 +6797,7 @@
         <v>459</v>
       </c>
       <c r="B460" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6799,7 +6805,7 @@
         <v>460</v>
       </c>
       <c r="B461" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6807,7 +6813,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6815,7 +6821,7 @@
         <v>462</v>
       </c>
       <c r="B463" s="1">
-        <v>900</v>
+        <v>880</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6823,7 +6829,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6831,7 +6837,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6839,7 +6845,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6847,7 +6853,7 @@
         <v>466</v>
       </c>
       <c r="B467" s="1">
-        <v>800</v>
+        <v>920</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6855,7 +6861,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6863,7 +6869,7 @@
         <v>468</v>
       </c>
       <c r="B469" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6871,7 +6877,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="1">
-        <v>980</v>
+        <v>940</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6879,7 +6885,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6887,7 +6893,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6895,7 +6901,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6903,7 +6909,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6911,7 +6917,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6927,7 +6933,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6935,7 +6941,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6943,7 +6949,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="1">
-        <v>640</v>
+        <v>920</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6951,7 +6957,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6959,7 +6965,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6967,7 +6973,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="1">
-        <v>960</v>
+        <v>820</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6975,7 +6981,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6983,7 +6989,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6991,7 +6997,7 @@
         <v>484</v>
       </c>
       <c r="B485" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6999,7 +7005,7 @@
         <v>485</v>
       </c>
       <c r="B486" s="1">
-        <v>860</v>
+        <v>640</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -7007,7 +7013,7 @@
         <v>486</v>
       </c>
       <c r="B487" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -7015,7 +7021,7 @@
         <v>487</v>
       </c>
       <c r="B488" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -7023,7 +7029,7 @@
         <v>488</v>
       </c>
       <c r="B489" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -7031,7 +7037,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -7039,7 +7045,7 @@
         <v>490</v>
       </c>
       <c r="B491" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -7047,7 +7053,7 @@
         <v>491</v>
       </c>
       <c r="B492" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -7055,7 +7061,7 @@
         <v>492</v>
       </c>
       <c r="B493" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -7063,7 +7069,7 @@
         <v>493</v>
       </c>
       <c r="B494" s="1">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -7071,7 +7077,7 @@
         <v>494</v>
       </c>
       <c r="B495" s="1">
-        <v>620</v>
+        <v>480</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -7079,7 +7085,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -7087,7 +7093,7 @@
         <v>496</v>
       </c>
       <c r="B497" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -7095,7 +7101,7 @@
         <v>497</v>
       </c>
       <c r="B498" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -7103,7 +7109,7 @@
         <v>498</v>
       </c>
       <c r="B499" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -7111,7 +7117,7 @@
         <v>499</v>
       </c>
       <c r="B500" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -7119,7 +7125,7 @@
         <v>500</v>
       </c>
       <c r="B501" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -7127,7 +7133,7 @@
         <v>501</v>
       </c>
       <c r="B502" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -7135,7 +7141,7 @@
         <v>502</v>
       </c>
       <c r="B503" s="1">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -7143,7 +7149,7 @@
         <v>503</v>
       </c>
       <c r="B504" s="1">
-        <v>840</v>
+        <v>480</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -7151,7 +7157,7 @@
         <v>504</v>
       </c>
       <c r="B505" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -7159,7 +7165,7 @@
         <v>505</v>
       </c>
       <c r="B506" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -7167,7 +7173,7 @@
         <v>506</v>
       </c>
       <c r="B507" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -7183,7 +7189,7 @@
         <v>508</v>
       </c>
       <c r="B509" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -7191,7 +7197,7 @@
         <v>509</v>
       </c>
       <c r="B510" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -7199,7 +7205,7 @@
         <v>510</v>
       </c>
       <c r="B511" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -7207,7 +7213,7 @@
         <v>511</v>
       </c>
       <c r="B512" s="1">
-        <v>880</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -7223,7 +7229,7 @@
         <v>513</v>
       </c>
       <c r="B514" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -7231,7 +7237,7 @@
         <v>514</v>
       </c>
       <c r="B515" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -7239,7 +7245,7 @@
         <v>515</v>
       </c>
       <c r="B516" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -7247,7 +7253,7 @@
         <v>516</v>
       </c>
       <c r="B517" s="1">
-        <v>1100</v>
+        <v>660</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -7255,7 +7261,7 @@
         <v>517</v>
       </c>
       <c r="B518" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -7263,7 +7269,7 @@
         <v>518</v>
       </c>
       <c r="B519" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -7271,7 +7277,7 @@
         <v>519</v>
       </c>
       <c r="B520" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -7279,7 +7285,7 @@
         <v>520</v>
       </c>
       <c r="B521" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -7287,7 +7293,7 @@
         <v>521</v>
       </c>
       <c r="B522" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -7303,7 +7309,7 @@
         <v>523</v>
       </c>
       <c r="B524" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -7311,7 +7317,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -7319,7 +7325,7 @@
         <v>525</v>
       </c>
       <c r="B526" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -7327,7 +7333,7 @@
         <v>526</v>
       </c>
       <c r="B527" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -7335,7 +7341,7 @@
         <v>527</v>
       </c>
       <c r="B528" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -7343,7 +7349,7 @@
         <v>528</v>
       </c>
       <c r="B529" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -7359,7 +7365,7 @@
         <v>530</v>
       </c>
       <c r="B531" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -7367,7 +7373,7 @@
         <v>531</v>
       </c>
       <c r="B532" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -7375,7 +7381,7 @@
         <v>532</v>
       </c>
       <c r="B533" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -7383,7 +7389,7 @@
         <v>533</v>
       </c>
       <c r="B534" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -7391,7 +7397,7 @@
         <v>534</v>
       </c>
       <c r="B535" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -7399,7 +7405,7 @@
         <v>535</v>
       </c>
       <c r="B536" s="1">
-        <v>840</v>
+        <v>620</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -7407,7 +7413,7 @@
         <v>536</v>
       </c>
       <c r="B537" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -7415,7 +7421,7 @@
         <v>537</v>
       </c>
       <c r="B538" s="1">
-        <v>1060</v>
+        <v>880</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -7423,7 +7429,7 @@
         <v>538</v>
       </c>
       <c r="B539" s="1">
-        <v>860</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -7439,7 +7445,7 @@
         <v>540</v>
       </c>
       <c r="B541" s="1">
-        <v>800</v>
+        <v>860</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -7447,7 +7453,7 @@
         <v>541</v>
       </c>
       <c r="B542" s="1">
-        <v>860</v>
+        <v>800</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -7455,7 +7461,7 @@
         <v>542</v>
       </c>
       <c r="B543" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -7463,7 +7469,7 @@
         <v>543</v>
       </c>
       <c r="B544" s="1">
-        <v>760</v>
+        <v>960</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -7471,7 +7477,7 @@
         <v>544</v>
       </c>
       <c r="B545" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -7479,7 +7485,7 @@
         <v>545</v>
       </c>
       <c r="B546" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -7487,7 +7493,7 @@
         <v>546</v>
       </c>
       <c r="B547" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -7503,7 +7509,7 @@
         <v>548</v>
       </c>
       <c r="B549" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -7511,7 +7517,7 @@
         <v>549</v>
       </c>
       <c r="B550" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -7519,7 +7525,7 @@
         <v>550</v>
       </c>
       <c r="B551" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -7527,7 +7533,7 @@
         <v>551</v>
       </c>
       <c r="B552" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7535,7 +7541,7 @@
         <v>552</v>
       </c>
       <c r="B553" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7543,7 +7549,7 @@
         <v>553</v>
       </c>
       <c r="B554" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7551,7 +7557,7 @@
         <v>554</v>
       </c>
       <c r="B555" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7567,7 +7573,7 @@
         <v>556</v>
       </c>
       <c r="B557" s="1">
-        <v>640</v>
+        <v>900</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7575,7 +7581,7 @@
         <v>557</v>
       </c>
       <c r="B558" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7583,7 +7589,7 @@
         <v>558</v>
       </c>
       <c r="B559" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7591,7 +7597,7 @@
         <v>559</v>
       </c>
       <c r="B560" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7599,7 +7605,7 @@
         <v>560</v>
       </c>
       <c r="B561" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7607,7 +7613,7 @@
         <v>561</v>
       </c>
       <c r="B562" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7615,7 +7621,7 @@
         <v>562</v>
       </c>
       <c r="B563" s="1">
-        <v>880</v>
+        <v>700</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7623,7 +7629,7 @@
         <v>563</v>
       </c>
       <c r="B564" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7631,7 +7637,7 @@
         <v>564</v>
       </c>
       <c r="B565" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7655,7 +7661,7 @@
         <v>567</v>
       </c>
       <c r="B568" s="1">
-        <v>920</v>
+        <v>820</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7663,7 +7669,7 @@
         <v>568</v>
       </c>
       <c r="B569" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7671,7 +7677,7 @@
         <v>569</v>
       </c>
       <c r="B570" s="1">
-        <v>880</v>
+        <v>920</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7679,7 +7685,7 @@
         <v>570</v>
       </c>
       <c r="B571" s="1">
-        <v>640</v>
+        <v>600</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7687,7 +7693,7 @@
         <v>571</v>
       </c>
       <c r="B572" s="1">
-        <v>700</v>
+        <v>880</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7695,7 +7701,7 @@
         <v>572</v>
       </c>
       <c r="B573" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7703,7 +7709,7 @@
         <v>573</v>
       </c>
       <c r="B574" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7711,7 +7717,7 @@
         <v>574</v>
       </c>
       <c r="B575" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7719,7 +7725,7 @@
         <v>575</v>
       </c>
       <c r="B576" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7727,7 +7733,7 @@
         <v>576</v>
       </c>
       <c r="B577" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7735,7 +7741,7 @@
         <v>577</v>
       </c>
       <c r="B578" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7743,7 +7749,7 @@
         <v>578</v>
       </c>
       <c r="B579" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7751,7 +7757,7 @@
         <v>579</v>
       </c>
       <c r="B580" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7759,7 +7765,7 @@
         <v>580</v>
       </c>
       <c r="B581" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7767,7 +7773,7 @@
         <v>581</v>
       </c>
       <c r="B582" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7775,7 +7781,7 @@
         <v>582</v>
       </c>
       <c r="B583" s="1">
-        <v>1040</v>
+        <v>960</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7783,7 +7789,7 @@
         <v>583</v>
       </c>
       <c r="B584" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7791,7 +7797,7 @@
         <v>584</v>
       </c>
       <c r="B585" s="1">
-        <v>940</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7799,7 +7805,7 @@
         <v>585</v>
       </c>
       <c r="B586" s="1">
-        <v>860</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7807,7 +7813,7 @@
         <v>586</v>
       </c>
       <c r="B587" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7815,7 +7821,7 @@
         <v>587</v>
       </c>
       <c r="B588" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7823,7 +7829,7 @@
         <v>588</v>
       </c>
       <c r="B589" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7831,7 +7837,7 @@
         <v>589</v>
       </c>
       <c r="B590" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7839,7 +7845,7 @@
         <v>590</v>
       </c>
       <c r="B591" s="1">
-        <v>840</v>
+        <v>960</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7847,7 +7853,7 @@
         <v>591</v>
       </c>
       <c r="B592" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7855,7 +7861,7 @@
         <v>592</v>
       </c>
       <c r="B593" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7863,7 +7869,7 @@
         <v>593</v>
       </c>
       <c r="B594" s="1">
-        <v>580</v>
+        <v>780</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7871,7 +7877,7 @@
         <v>594</v>
       </c>
       <c r="B595" s="1">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7879,7 +7885,7 @@
         <v>595</v>
       </c>
       <c r="B596" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7887,7 +7893,7 @@
         <v>596</v>
       </c>
       <c r="B597" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7895,7 +7901,7 @@
         <v>597</v>
       </c>
       <c r="B598" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7903,7 +7909,7 @@
         <v>598</v>
       </c>
       <c r="B599" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7911,7 +7917,7 @@
         <v>599</v>
       </c>
       <c r="B600" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7919,7 +7925,7 @@
         <v>600</v>
       </c>
       <c r="B601" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7927,7 +7933,7 @@
         <v>601</v>
       </c>
       <c r="B602" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7935,7 +7941,7 @@
         <v>602</v>
       </c>
       <c r="B603" s="1">
-        <v>600</v>
+        <v>960</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7943,7 +7949,7 @@
         <v>603</v>
       </c>
       <c r="B604" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7951,7 +7957,7 @@
         <v>604</v>
       </c>
       <c r="B605" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7959,7 +7965,7 @@
         <v>605</v>
       </c>
       <c r="B606" s="1">
-        <v>540</v>
+        <v>720</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7967,7 +7973,7 @@
         <v>606</v>
       </c>
       <c r="B607" s="1">
-        <v>980</v>
+        <v>780</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7975,7 +7981,7 @@
         <v>607</v>
       </c>
       <c r="B608" s="1">
-        <v>1100</v>
+        <v>540</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7983,7 +7989,7 @@
         <v>608</v>
       </c>
       <c r="B609" s="1">
-        <v>1060</v>
+        <v>980</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7991,7 +7997,7 @@
         <v>609</v>
       </c>
       <c r="B610" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7999,7 +8005,7 @@
         <v>610</v>
       </c>
       <c r="B611" s="1">
-        <v>1100</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -8007,7 +8013,7 @@
         <v>611</v>
       </c>
       <c r="B612" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -8015,7 +8021,7 @@
         <v>612</v>
       </c>
       <c r="B613" s="1">
-        <v>1080</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -8023,7 +8029,7 @@
         <v>613</v>
       </c>
       <c r="B614" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -8031,7 +8037,7 @@
         <v>614</v>
       </c>
       <c r="B615" s="1">
-        <v>840</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -8039,7 +8045,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -8047,7 +8053,7 @@
         <v>616</v>
       </c>
       <c r="B617" s="1">
-        <v>560</v>
+        <v>840</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -8055,7 +8061,7 @@
         <v>617</v>
       </c>
       <c r="B618" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -8063,7 +8069,7 @@
         <v>618</v>
       </c>
       <c r="B619" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -8071,7 +8077,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -8079,7 +8085,7 @@
         <v>620</v>
       </c>
       <c r="B621" s="1">
-        <v>980</v>
+        <v>620</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -8087,7 +8093,7 @@
         <v>621</v>
       </c>
       <c r="B622" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -8095,7 +8101,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="1">
-        <v>760</v>
+        <v>980</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -8103,7 +8109,7 @@
         <v>623</v>
       </c>
       <c r="B624" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -8111,7 +8117,7 @@
         <v>624</v>
       </c>
       <c r="B625" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -8127,7 +8133,7 @@
         <v>626</v>
       </c>
       <c r="B627" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -8135,7 +8141,7 @@
         <v>627</v>
       </c>
       <c r="B628" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -8151,7 +8157,7 @@
         <v>629</v>
       </c>
       <c r="B630" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -8159,7 +8165,7 @@
         <v>630</v>
       </c>
       <c r="B631" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -8167,7 +8173,7 @@
         <v>631</v>
       </c>
       <c r="B632" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -8175,7 +8181,7 @@
         <v>632</v>
       </c>
       <c r="B633" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -8183,7 +8189,7 @@
         <v>633</v>
       </c>
       <c r="B634" s="1">
-        <v>700</v>
+        <v>960</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -8191,7 +8197,7 @@
         <v>634</v>
       </c>
       <c r="B635" s="1">
-        <v>980</v>
+        <v>840</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -8199,7 +8205,7 @@
         <v>635</v>
       </c>
       <c r="B636" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -8207,7 +8213,7 @@
         <v>636</v>
       </c>
       <c r="B637" s="1">
-        <v>800</v>
+        <v>980</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -8215,7 +8221,7 @@
         <v>637</v>
       </c>
       <c r="B638" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -8223,7 +8229,7 @@
         <v>638</v>
       </c>
       <c r="B639" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -8239,7 +8245,7 @@
         <v>640</v>
       </c>
       <c r="B641" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -8247,7 +8253,7 @@
         <v>641</v>
       </c>
       <c r="B642" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -8263,7 +8269,7 @@
         <v>643</v>
       </c>
       <c r="B644" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -8271,7 +8277,7 @@
         <v>644</v>
       </c>
       <c r="B645" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -8279,7 +8285,7 @@
         <v>645</v>
       </c>
       <c r="B646" s="1">
-        <v>820</v>
+        <v>860</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -8287,7 +8293,7 @@
         <v>646</v>
       </c>
       <c r="B647" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -8295,7 +8301,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -8303,7 +8309,7 @@
         <v>648</v>
       </c>
       <c r="B649" s="1">
-        <v>1400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -8319,7 +8325,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="1">
-        <v>660</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -8327,7 +8333,7 @@
         <v>651</v>
       </c>
       <c r="B652" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -8335,7 +8341,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -8343,7 +8349,7 @@
         <v>653</v>
       </c>
       <c r="B654" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -8351,7 +8357,7 @@
         <v>654</v>
       </c>
       <c r="B655" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -8359,7 +8365,7 @@
         <v>655</v>
       </c>
       <c r="B656" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -8367,7 +8373,7 @@
         <v>656</v>
       </c>
       <c r="B657" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -8375,7 +8381,7 @@
         <v>657</v>
       </c>
       <c r="B658" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -8383,7 +8389,7 @@
         <v>658</v>
       </c>
       <c r="B659" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -8391,7 +8397,7 @@
         <v>659</v>
       </c>
       <c r="B660" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -8399,7 +8405,7 @@
         <v>660</v>
       </c>
       <c r="B661" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -8407,7 +8413,7 @@
         <v>661</v>
       </c>
       <c r="B662" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -8415,7 +8421,7 @@
         <v>662</v>
       </c>
       <c r="B663" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -8423,7 +8429,7 @@
         <v>663</v>
       </c>
       <c r="B664" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -8431,7 +8437,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -8447,7 +8453,7 @@
         <v>666</v>
       </c>
       <c r="B667" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -8455,7 +8461,7 @@
         <v>667</v>
       </c>
       <c r="B668" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -8463,7 +8469,7 @@
         <v>668</v>
       </c>
       <c r="B669" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -8471,7 +8477,7 @@
         <v>669</v>
       </c>
       <c r="B670" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -8479,7 +8485,7 @@
         <v>670</v>
       </c>
       <c r="B671" s="1">
-        <v>4000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -8487,7 +8493,7 @@
         <v>671</v>
       </c>
       <c r="B672" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -8495,7 +8501,7 @@
         <v>672</v>
       </c>
       <c r="B673" s="1">
-        <v>720</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -8503,7 +8509,7 @@
         <v>673</v>
       </c>
       <c r="B674" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -8511,7 +8517,7 @@
         <v>674</v>
       </c>
       <c r="B675" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8519,7 +8525,7 @@
         <v>675</v>
       </c>
       <c r="B676" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -8527,7 +8533,7 @@
         <v>676</v>
       </c>
       <c r="B677" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8535,7 +8541,7 @@
         <v>677</v>
       </c>
       <c r="B678" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8543,7 +8549,7 @@
         <v>678</v>
       </c>
       <c r="B679" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8551,7 +8557,7 @@
         <v>679</v>
       </c>
       <c r="B680" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8559,7 +8565,7 @@
         <v>680</v>
       </c>
       <c r="B681" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8567,7 +8573,7 @@
         <v>681</v>
       </c>
       <c r="B682" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8575,7 +8581,7 @@
         <v>682</v>
       </c>
       <c r="B683" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8583,7 +8589,7 @@
         <v>683</v>
       </c>
       <c r="B684" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8599,7 +8605,7 @@
         <v>685</v>
       </c>
       <c r="B686" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8615,7 +8621,7 @@
         <v>687</v>
       </c>
       <c r="B688" s="1">
-        <v>980</v>
+        <v>900</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8623,7 +8629,7 @@
         <v>688</v>
       </c>
       <c r="B689" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8631,7 +8637,7 @@
         <v>689</v>
       </c>
       <c r="B690" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8639,7 +8645,7 @@
         <v>690</v>
       </c>
       <c r="B691" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8647,7 +8653,7 @@
         <v>691</v>
       </c>
       <c r="B692" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8655,7 +8661,7 @@
         <v>692</v>
       </c>
       <c r="B693" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8663,7 +8669,7 @@
         <v>693</v>
       </c>
       <c r="B694" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8671,7 +8677,7 @@
         <v>694</v>
       </c>
       <c r="B695" s="1">
-        <v>860</v>
+        <v>680</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8687,7 +8693,7 @@
         <v>696</v>
       </c>
       <c r="B697" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8703,7 +8709,7 @@
         <v>698</v>
       </c>
       <c r="B699" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8711,7 +8717,7 @@
         <v>699</v>
       </c>
       <c r="B700" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8719,7 +8725,7 @@
         <v>700</v>
       </c>
       <c r="B701" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8727,7 +8733,7 @@
         <v>701</v>
       </c>
       <c r="B702" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8735,7 +8741,7 @@
         <v>702</v>
       </c>
       <c r="B703" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8743,7 +8749,7 @@
         <v>703</v>
       </c>
       <c r="B704" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8751,7 +8757,7 @@
         <v>704</v>
       </c>
       <c r="B705" s="1">
-        <v>840</v>
+        <v>800</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8759,7 +8765,7 @@
         <v>705</v>
       </c>
       <c r="B706" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8767,7 +8773,7 @@
         <v>706</v>
       </c>
       <c r="B707" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8775,7 +8781,7 @@
         <v>707</v>
       </c>
       <c r="B708" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8783,7 +8789,7 @@
         <v>708</v>
       </c>
       <c r="B709" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8799,7 +8805,7 @@
         <v>710</v>
       </c>
       <c r="B711" s="1">
-        <v>880</v>
+        <v>640</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8807,7 +8813,7 @@
         <v>711</v>
       </c>
       <c r="B712" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8815,7 +8821,7 @@
         <v>712</v>
       </c>
       <c r="B713" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8823,7 +8829,7 @@
         <v>713</v>
       </c>
       <c r="B714" s="1">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8831,7 +8837,7 @@
         <v>714</v>
       </c>
       <c r="B715" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8847,7 +8853,7 @@
         <v>716</v>
       </c>
       <c r="B717" s="1">
-        <v>800</v>
+        <v>820</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8855,7 +8861,7 @@
         <v>717</v>
       </c>
       <c r="B718" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8871,7 +8877,7 @@
         <v>719</v>
       </c>
       <c r="B720" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8879,7 +8885,7 @@
         <v>720</v>
       </c>
       <c r="B721" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8887,7 +8893,7 @@
         <v>721</v>
       </c>
       <c r="B722" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8895,7 +8901,7 @@
         <v>722</v>
       </c>
       <c r="B723" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8903,7 +8909,7 @@
         <v>723</v>
       </c>
       <c r="B724" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8911,7 +8917,7 @@
         <v>724</v>
       </c>
       <c r="B725" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8919,7 +8925,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="1">
-        <v>880</v>
+        <v>960</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8927,7 +8933,7 @@
         <v>726</v>
       </c>
       <c r="B727" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8935,7 +8941,7 @@
         <v>727</v>
       </c>
       <c r="B728" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8943,7 +8949,7 @@
         <v>728</v>
       </c>
       <c r="B729" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8951,7 +8957,7 @@
         <v>729</v>
       </c>
       <c r="B730" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8959,7 +8965,7 @@
         <v>730</v>
       </c>
       <c r="B731" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8967,7 +8973,7 @@
         <v>731</v>
       </c>
       <c r="B732" s="1">
-        <v>1020</v>
+        <v>640</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -8983,7 +8989,7 @@
         <v>733</v>
       </c>
       <c r="B734" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -8991,7 +8997,7 @@
         <v>734</v>
       </c>
       <c r="B735" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -8999,7 +9005,7 @@
         <v>735</v>
       </c>
       <c r="B736" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -9007,7 +9013,7 @@
         <v>736</v>
       </c>
       <c r="B737" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -9015,7 +9021,7 @@
         <v>737</v>
       </c>
       <c r="B738" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="739" spans="1:2">
@@ -9023,7 +9029,7 @@
         <v>738</v>
       </c>
       <c r="B739" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="740" spans="1:2">
@@ -9031,7 +9037,7 @@
         <v>739</v>
       </c>
       <c r="B740" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -9047,7 +9053,7 @@
         <v>741</v>
       </c>
       <c r="B742" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -9055,7 +9061,7 @@
         <v>742</v>
       </c>
       <c r="B743" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="744" spans="1:2">
@@ -9063,7 +9069,7 @@
         <v>743</v>
       </c>
       <c r="B744" s="1">
-        <v>680</v>
+        <v>820</v>
       </c>
     </row>
     <row r="745" spans="1:2">
@@ -9071,7 +9077,7 @@
         <v>744</v>
       </c>
       <c r="B745" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -9079,7 +9085,7 @@
         <v>745</v>
       </c>
       <c r="B746" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="747" spans="1:2">
@@ -9087,7 +9093,7 @@
         <v>746</v>
       </c>
       <c r="B747" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="748" spans="1:2">
@@ -9095,7 +9101,7 @@
         <v>747</v>
       </c>
       <c r="B748" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="749" spans="1:2">
@@ -9103,7 +9109,7 @@
         <v>748</v>
       </c>
       <c r="B749" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -9119,7 +9125,7 @@
         <v>750</v>
       </c>
       <c r="B751" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="752" spans="1:2">
@@ -9127,7 +9133,7 @@
         <v>751</v>
       </c>
       <c r="B752" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="753" spans="1:2">
@@ -9135,7 +9141,7 @@
         <v>752</v>
       </c>
       <c r="B753" s="1">
-        <v>1100</v>
+        <v>840</v>
       </c>
     </row>
     <row r="754" spans="1:2">
@@ -9143,7 +9149,7 @@
         <v>753</v>
       </c>
       <c r="B754" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -9151,7 +9157,7 @@
         <v>754</v>
       </c>
       <c r="B755" s="1">
-        <v>940</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="756" spans="1:2">
@@ -9159,7 +9165,7 @@
         <v>755</v>
       </c>
       <c r="B756" s="1">
-        <v>820</v>
+        <v>940</v>
       </c>
     </row>
     <row r="757" spans="1:2">
@@ -9167,7 +9173,7 @@
         <v>756</v>
       </c>
       <c r="B757" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="758" spans="1:2">
@@ -9175,7 +9181,7 @@
         <v>757</v>
       </c>
       <c r="B758" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="759" spans="1:2">
@@ -9183,7 +9189,7 @@
         <v>758</v>
       </c>
       <c r="B759" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="760" spans="1:2">
@@ -9191,7 +9197,7 @@
         <v>759</v>
       </c>
       <c r="B760" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="761" spans="1:2">
@@ -9199,7 +9205,7 @@
         <v>760</v>
       </c>
       <c r="B761" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="762" spans="1:2">
@@ -9207,7 +9213,7 @@
         <v>761</v>
       </c>
       <c r="B762" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="763" spans="1:2">
@@ -9215,7 +9221,7 @@
         <v>762</v>
       </c>
       <c r="B763" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="764" spans="1:2">
@@ -9231,7 +9237,7 @@
         <v>764</v>
       </c>
       <c r="B765" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="766" spans="1:2">
@@ -9239,7 +9245,7 @@
         <v>765</v>
       </c>
       <c r="B766" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="767" spans="1:2">
@@ -9247,7 +9253,7 @@
         <v>766</v>
       </c>
       <c r="B767" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="768" spans="1:2">
@@ -9255,7 +9261,7 @@
         <v>767</v>
       </c>
       <c r="B768" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="769" spans="1:2">
@@ -9263,7 +9269,7 @@
         <v>768</v>
       </c>
       <c r="B769" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="770" spans="1:2">
@@ -9271,7 +9277,7 @@
         <v>769</v>
       </c>
       <c r="B770" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="771" spans="1:2">
@@ -9287,7 +9293,7 @@
         <v>771</v>
       </c>
       <c r="B772" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="773" spans="1:2">
@@ -9295,7 +9301,7 @@
         <v>772</v>
       </c>
       <c r="B773" s="1">
-        <v>440</v>
+        <v>900</v>
       </c>
     </row>
     <row r="774" spans="1:2">
@@ -9303,7 +9309,7 @@
         <v>773</v>
       </c>
       <c r="B774" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="775" spans="1:2">
@@ -9311,7 +9317,7 @@
         <v>774</v>
       </c>
       <c r="B775" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="776" spans="1:2">
@@ -9319,7 +9325,7 @@
         <v>775</v>
       </c>
       <c r="B776" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="777" spans="1:2">
@@ -9327,7 +9333,7 @@
         <v>776</v>
       </c>
       <c r="B777" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="778" spans="1:2">
@@ -9335,7 +9341,7 @@
         <v>777</v>
       </c>
       <c r="B778" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="779" spans="1:2">
@@ -9343,7 +9349,7 @@
         <v>778</v>
       </c>
       <c r="B779" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="780" spans="1:2">
@@ -9351,7 +9357,7 @@
         <v>779</v>
       </c>
       <c r="B780" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="781" spans="1:2">
@@ -9359,7 +9365,7 @@
         <v>780</v>
       </c>
       <c r="B781" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="782" spans="1:2">
@@ -9367,7 +9373,7 @@
         <v>781</v>
       </c>
       <c r="B782" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="783" spans="1:2">
@@ -9375,7 +9381,7 @@
         <v>782</v>
       </c>
       <c r="B783" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="784" spans="1:2">
@@ -9383,7 +9389,7 @@
         <v>783</v>
       </c>
       <c r="B784" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="785" spans="1:2">
@@ -9399,7 +9405,7 @@
         <v>785</v>
       </c>
       <c r="B786" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="787" spans="1:2">
@@ -9407,7 +9413,7 @@
         <v>786</v>
       </c>
       <c r="B787" s="1">
-        <v>920</v>
+        <v>880</v>
       </c>
     </row>
     <row r="788" spans="1:2">
@@ -9415,7 +9421,7 @@
         <v>787</v>
       </c>
       <c r="B788" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="789" spans="1:2">
@@ -9423,7 +9429,7 @@
         <v>788</v>
       </c>
       <c r="B789" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="790" spans="1:2">
@@ -9431,7 +9437,7 @@
         <v>789</v>
       </c>
       <c r="B790" s="1">
-        <v>980</v>
+        <v>800</v>
       </c>
     </row>
     <row r="791" spans="1:2">
@@ -9439,7 +9445,7 @@
         <v>790</v>
       </c>
       <c r="B791" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="792" spans="1:2">
@@ -9447,7 +9453,7 @@
         <v>791</v>
       </c>
       <c r="B792" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="793" spans="1:2">
@@ -9455,7 +9461,7 @@
         <v>792</v>
       </c>
       <c r="B793" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="794" spans="1:2">
@@ -9463,7 +9469,7 @@
         <v>793</v>
       </c>
       <c r="B794" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="795" spans="1:2">
@@ -9471,7 +9477,7 @@
         <v>794</v>
       </c>
       <c r="B795" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="796" spans="1:2">
@@ -9479,7 +9485,7 @@
         <v>795</v>
       </c>
       <c r="B796" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="797" spans="1:2">
@@ -9487,7 +9493,7 @@
         <v>796</v>
       </c>
       <c r="B797" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="798" spans="1:2">
@@ -9495,7 +9501,7 @@
         <v>797</v>
       </c>
       <c r="B798" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="799" spans="1:2">
@@ -9503,7 +9509,7 @@
         <v>798</v>
       </c>
       <c r="B799" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="800" spans="1:2">
@@ -9511,7 +9517,7 @@
         <v>799</v>
       </c>
       <c r="B800" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="801" spans="1:2">
@@ -9519,7 +9525,7 @@
         <v>800</v>
       </c>
       <c r="B801" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="802" spans="1:2">
@@ -9527,7 +9533,7 @@
         <v>801</v>
       </c>
       <c r="B802" s="1">
-        <v>660</v>
+        <v>860</v>
       </c>
     </row>
     <row r="803" spans="1:2">
@@ -9535,7 +9541,7 @@
         <v>802</v>
       </c>
       <c r="B803" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="804" spans="1:2">
@@ -9543,7 +9549,7 @@
         <v>803</v>
       </c>
       <c r="B804" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="805" spans="1:2">
@@ -9551,7 +9557,7 @@
         <v>804</v>
       </c>
       <c r="B805" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="806" spans="1:2">
@@ -9559,7 +9565,7 @@
         <v>805</v>
       </c>
       <c r="B806" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="807" spans="1:2">
@@ -9567,7 +9573,7 @@
         <v>806</v>
       </c>
       <c r="B807" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="808" spans="1:2">
@@ -9575,7 +9581,7 @@
         <v>807</v>
       </c>
       <c r="B808" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="809" spans="1:2">
@@ -9583,7 +9589,7 @@
         <v>808</v>
       </c>
       <c r="B809" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="810" spans="1:2">
@@ -9591,7 +9597,7 @@
         <v>809</v>
       </c>
       <c r="B810" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="811" spans="1:2">
@@ -9599,7 +9605,7 @@
         <v>810</v>
       </c>
       <c r="B811" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="812" spans="1:2">
@@ -9607,7 +9613,7 @@
         <v>811</v>
       </c>
       <c r="B812" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="813" spans="1:2">
@@ -9615,7 +9621,7 @@
         <v>812</v>
       </c>
       <c r="B813" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="814" spans="1:2">
@@ -9623,7 +9629,7 @@
         <v>813</v>
       </c>
       <c r="B814" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="815" spans="1:2">
@@ -9631,7 +9637,7 @@
         <v>814</v>
       </c>
       <c r="B815" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="816" spans="1:2">
@@ -9639,7 +9645,7 @@
         <v>815</v>
       </c>
       <c r="B816" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="817" spans="1:2">
@@ -9647,7 +9653,7 @@
         <v>816</v>
       </c>
       <c r="B817" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="818" spans="1:2">
@@ -9655,7 +9661,7 @@
         <v>817</v>
       </c>
       <c r="B818" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="819" spans="1:2">
@@ -9663,7 +9669,7 @@
         <v>818</v>
       </c>
       <c r="B819" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="820" spans="1:2">
@@ -9671,7 +9677,7 @@
         <v>819</v>
       </c>
       <c r="B820" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="821" spans="1:2">
@@ -9679,7 +9685,7 @@
         <v>820</v>
       </c>
       <c r="B821" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="822" spans="1:2">
@@ -9687,7 +9693,7 @@
         <v>821</v>
       </c>
       <c r="B822" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="823" spans="1:2">
@@ -9695,7 +9701,7 @@
         <v>822</v>
       </c>
       <c r="B823" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="824" spans="1:2">
@@ -9703,7 +9709,7 @@
         <v>823</v>
       </c>
       <c r="B824" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="825" spans="1:2">
@@ -9711,7 +9717,7 @@
         <v>824</v>
       </c>
       <c r="B825" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="826" spans="1:2">
@@ -9719,7 +9725,7 @@
         <v>825</v>
       </c>
       <c r="B826" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="827" spans="1:2">
@@ -9727,7 +9733,7 @@
         <v>826</v>
       </c>
       <c r="B827" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="828" spans="1:2">
@@ -9735,7 +9741,7 @@
         <v>827</v>
       </c>
       <c r="B828" s="1">
-        <v>920</v>
+        <v>500</v>
       </c>
     </row>
     <row r="829" spans="1:2">
@@ -9743,7 +9749,7 @@
         <v>828</v>
       </c>
       <c r="B829" s="1">
-        <v>1000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="830" spans="1:2">
@@ -9751,7 +9757,7 @@
         <v>829</v>
       </c>
       <c r="B830" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="831" spans="1:2">
@@ -9759,7 +9765,7 @@
         <v>830</v>
       </c>
       <c r="B831" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="832" spans="1:2">
@@ -9775,7 +9781,7 @@
         <v>832</v>
       </c>
       <c r="B833" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="834" spans="1:2">
@@ -9783,7 +9789,7 @@
         <v>833</v>
       </c>
       <c r="B834" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="835" spans="1:2">
@@ -9791,7 +9797,7 @@
         <v>834</v>
       </c>
       <c r="B835" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="836" spans="1:2">
@@ -9799,7 +9805,7 @@
         <v>835</v>
       </c>
       <c r="B836" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="837" spans="1:2">
@@ -9807,7 +9813,7 @@
         <v>836</v>
       </c>
       <c r="B837" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="838" spans="1:2">
@@ -9815,7 +9821,7 @@
         <v>837</v>
       </c>
       <c r="B838" s="1">
-        <v>960</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="839" spans="1:2">
@@ -9823,7 +9829,7 @@
         <v>838</v>
       </c>
       <c r="B839" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="840" spans="1:2">
@@ -9831,7 +9837,7 @@
         <v>839</v>
       </c>
       <c r="B840" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="841" spans="1:2">
@@ -9839,7 +9845,7 @@
         <v>840</v>
       </c>
       <c r="B841" s="1">
-        <v>820</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="842" spans="1:2">
@@ -9847,7 +9853,7 @@
         <v>841</v>
       </c>
       <c r="B842" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="843" spans="1:2">
@@ -9855,7 +9861,7 @@
         <v>842</v>
       </c>
       <c r="B843" s="1">
-        <v>500</v>
+        <v>820</v>
       </c>
     </row>
     <row r="844" spans="1:2">
@@ -9871,7 +9877,7 @@
         <v>844</v>
       </c>
       <c r="B845" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="846" spans="1:2">
@@ -9879,7 +9885,7 @@
         <v>845</v>
       </c>
       <c r="B846" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="847" spans="1:2">
@@ -9887,7 +9893,7 @@
         <v>846</v>
       </c>
       <c r="B847" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="848" spans="1:2">
@@ -9895,7 +9901,7 @@
         <v>847</v>
       </c>
       <c r="B848" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="849" spans="1:2">
@@ -9903,7 +9909,7 @@
         <v>848</v>
       </c>
       <c r="B849" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="850" spans="1:2">
@@ -9911,7 +9917,7 @@
         <v>849</v>
       </c>
       <c r="B850" s="1">
-        <v>840</v>
+        <v>820</v>
       </c>
     </row>
     <row r="851" spans="1:2">
@@ -9919,7 +9925,7 @@
         <v>850</v>
       </c>
       <c r="B851" s="1">
-        <v>400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="852" spans="1:2">
@@ -9927,7 +9933,7 @@
         <v>851</v>
       </c>
       <c r="B852" s="1">
-        <v>400</v>
+        <v>840</v>
       </c>
     </row>
     <row r="853" spans="1:2">
@@ -9935,7 +9941,7 @@
         <v>852</v>
       </c>
       <c r="B853" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="854" spans="1:2">
@@ -9943,7 +9949,7 @@
         <v>853</v>
       </c>
       <c r="B854" s="1">
-        <v>840</v>
+        <v>400</v>
       </c>
     </row>
     <row r="855" spans="1:2">
@@ -9959,7 +9965,7 @@
         <v>855</v>
       </c>
       <c r="B856" s="1">
-        <v>380</v>
+        <v>840</v>
       </c>
     </row>
     <row r="857" spans="1:2">
@@ -9967,7 +9973,7 @@
         <v>856</v>
       </c>
       <c r="B857" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="858" spans="1:2">
@@ -9975,7 +9981,7 @@
         <v>857</v>
       </c>
       <c r="B858" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="859" spans="1:2">
@@ -9983,7 +9989,7 @@
         <v>858</v>
       </c>
       <c r="B859" s="1">
-        <v>800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="860" spans="1:2">
@@ -9991,7 +9997,7 @@
         <v>859</v>
       </c>
       <c r="B860" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="861" spans="1:2">
@@ -9999,7 +10005,7 @@
         <v>860</v>
       </c>
       <c r="B861" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="862" spans="1:2">
@@ -10007,7 +10013,7 @@
         <v>861</v>
       </c>
       <c r="B862" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="863" spans="1:2">
@@ -10015,7 +10021,7 @@
         <v>862</v>
       </c>
       <c r="B863" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="864" spans="1:2">
@@ -10023,7 +10029,7 @@
         <v>863</v>
       </c>
       <c r="B864" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="865" spans="1:2">
@@ -10031,7 +10037,7 @@
         <v>864</v>
       </c>
       <c r="B865" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="866" spans="1:2">
@@ -10039,7 +10045,7 @@
         <v>865</v>
       </c>
       <c r="B866" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="867" spans="1:2">
@@ -10047,7 +10053,7 @@
         <v>866</v>
       </c>
       <c r="B867" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="868" spans="1:2">
@@ -10055,7 +10061,7 @@
         <v>867</v>
       </c>
       <c r="B868" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="869" spans="1:2">
@@ -10063,7 +10069,7 @@
         <v>868</v>
       </c>
       <c r="B869" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="870" spans="1:2">
@@ -10071,7 +10077,7 @@
         <v>869</v>
       </c>
       <c r="B870" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="871" spans="1:2">
@@ -10079,7 +10085,7 @@
         <v>870</v>
       </c>
       <c r="B871" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="872" spans="1:2">
@@ -10087,7 +10093,7 @@
         <v>871</v>
       </c>
       <c r="B872" s="1">
-        <v>840</v>
+        <v>500</v>
       </c>
     </row>
     <row r="873" spans="1:2">
@@ -10095,7 +10101,7 @@
         <v>872</v>
       </c>
       <c r="B873" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="874" spans="1:2">
@@ -10103,7 +10109,7 @@
         <v>873</v>
       </c>
       <c r="B874" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="875" spans="1:2">
@@ -10111,7 +10117,7 @@
         <v>874</v>
       </c>
       <c r="B875" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="876" spans="1:2">
@@ -10119,7 +10125,7 @@
         <v>875</v>
       </c>
       <c r="B876" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="877" spans="1:2">
@@ -10127,7 +10133,7 @@
         <v>876</v>
       </c>
       <c r="B877" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="878" spans="1:2">
@@ -10135,7 +10141,7 @@
         <v>877</v>
       </c>
       <c r="B878" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="879" spans="1:2">
@@ -10151,7 +10157,7 @@
         <v>879</v>
       </c>
       <c r="B880" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="881" spans="1:2">
@@ -10159,7 +10165,7 @@
         <v>880</v>
       </c>
       <c r="B881" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="882" spans="1:2">
@@ -10167,7 +10173,7 @@
         <v>881</v>
       </c>
       <c r="B882" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="883" spans="1:2">
@@ -10175,7 +10181,7 @@
         <v>882</v>
       </c>
       <c r="B883" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="884" spans="1:2">
@@ -10183,7 +10189,7 @@
         <v>883</v>
       </c>
       <c r="B884" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="885" spans="1:2">
@@ -10191,7 +10197,7 @@
         <v>884</v>
       </c>
       <c r="B885" s="1">
-        <v>960</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="886" spans="1:2">
@@ -10199,7 +10205,7 @@
         <v>885</v>
       </c>
       <c r="B886" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="887" spans="1:2">
@@ -10207,7 +10213,7 @@
         <v>886</v>
       </c>
       <c r="B887" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="888" spans="1:2">
@@ -10215,7 +10221,7 @@
         <v>887</v>
       </c>
       <c r="B888" s="1">
-        <v>820</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="889" spans="1:2">
@@ -10223,7 +10229,7 @@
         <v>888</v>
       </c>
       <c r="B889" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="890" spans="1:2">
@@ -10231,7 +10237,7 @@
         <v>889</v>
       </c>
       <c r="B890" s="1">
-        <v>500</v>
+        <v>820</v>
       </c>
     </row>
     <row r="891" spans="1:2">
@@ -10247,7 +10253,7 @@
         <v>891</v>
       </c>
       <c r="B892" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="893" spans="1:2">
@@ -10255,7 +10261,7 @@
         <v>892</v>
       </c>
       <c r="B893" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="894" spans="1:2">
@@ -10263,7 +10269,7 @@
         <v>893</v>
       </c>
       <c r="B894" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="895" spans="1:2">
@@ -10271,7 +10277,7 @@
         <v>894</v>
       </c>
       <c r="B895" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="896" spans="1:2">
@@ -10279,7 +10285,7 @@
         <v>895</v>
       </c>
       <c r="B896" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="897" spans="1:2">
@@ -10295,7 +10301,7 @@
         <v>897</v>
       </c>
       <c r="B898" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="899" spans="1:2">
@@ -10303,7 +10309,7 @@
         <v>898</v>
       </c>
       <c r="B899" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="900" spans="1:2">
@@ -10319,7 +10325,7 @@
         <v>900</v>
       </c>
       <c r="B901" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="902" spans="1:2">
@@ -10327,7 +10333,7 @@
         <v>901</v>
       </c>
       <c r="B902" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="903" spans="1:2">
@@ -10335,7 +10341,7 @@
         <v>902</v>
       </c>
       <c r="B903" s="1">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="904" spans="1:2">
@@ -10343,7 +10349,7 @@
         <v>903</v>
       </c>
       <c r="B904" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="905" spans="1:2">
@@ -10351,7 +10357,7 @@
         <v>904</v>
       </c>
       <c r="B905" s="1">
-        <v>600</v>
+        <v>440</v>
       </c>
     </row>
     <row r="906" spans="1:2">
@@ -10359,7 +10365,7 @@
         <v>905</v>
       </c>
       <c r="B906" s="1">
-        <v>820</v>
+        <v>380</v>
       </c>
     </row>
     <row r="907" spans="1:2">
@@ -10367,7 +10373,7 @@
         <v>906</v>
       </c>
       <c r="B907" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="908" spans="1:2">
@@ -10375,7 +10381,7 @@
         <v>907</v>
       </c>
       <c r="B908" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="909" spans="1:2">
@@ -10383,7 +10389,7 @@
         <v>908</v>
       </c>
       <c r="B909" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="910" spans="1:2">
@@ -10399,7 +10405,7 @@
         <v>910</v>
       </c>
       <c r="B911" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="912" spans="1:2">
@@ -10407,7 +10413,7 @@
         <v>911</v>
       </c>
       <c r="B912" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="913" spans="1:2">
@@ -10415,6 +10421,22 @@
         <v>912</v>
       </c>
       <c r="B913" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="914" spans="1:2">
+      <c r="A914" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="B914" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="915" spans="1:2">
+      <c r="A915" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="B915" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="916">
   <si>
     <t>Наименование</t>
   </si>
@@ -809,7 +809,7 @@
     <t>Plan B  - Отличный план (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
-    <t>Plan B - Bathory (Red Ale), РОЗЛИВ, Россия</t>
+    <t>Plan B - Bathory, РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>Plan B - Murquell Pilsner (Pils), РОЗЛИВ, Россия</t>
@@ -1995,6 +1995,9 @@
   </si>
   <si>
     <t>вынос_Plan B  - Отличный план (IPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Plan B - Bathory, РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_Plan B - Murquell Pilsner (Pils), РОЗЛИВ, Россия</t>
@@ -3113,7 +3116,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B915"/>
+  <dimension ref="A1:B916"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -5237,7 +5240,7 @@
         <v>264</v>
       </c>
       <c r="B265" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -5269,7 +5272,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="1">
-        <v>960</v>
+        <v>980</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -8405,7 +8408,7 @@
         <v>660</v>
       </c>
       <c r="B661" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -8413,7 +8416,7 @@
         <v>661</v>
       </c>
       <c r="B662" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -8421,7 +8424,7 @@
         <v>662</v>
       </c>
       <c r="B663" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -8429,7 +8432,7 @@
         <v>663</v>
       </c>
       <c r="B664" s="1">
-        <v>960</v>
+        <v>840</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -8437,7 +8440,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -8453,7 +8456,7 @@
         <v>666</v>
       </c>
       <c r="B667" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -8461,7 +8464,7 @@
         <v>667</v>
       </c>
       <c r="B668" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -8477,7 +8480,7 @@
         <v>669</v>
       </c>
       <c r="B670" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -8485,7 +8488,7 @@
         <v>670</v>
       </c>
       <c r="B671" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -8501,7 +8504,7 @@
         <v>672</v>
       </c>
       <c r="B673" s="1">
-        <v>4000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -8509,7 +8512,7 @@
         <v>673</v>
       </c>
       <c r="B674" s="1">
-        <v>720</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -8525,7 +8528,7 @@
         <v>675</v>
       </c>
       <c r="B676" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -8533,7 +8536,7 @@
         <v>676</v>
       </c>
       <c r="B677" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8541,7 +8544,7 @@
         <v>677</v>
       </c>
       <c r="B678" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8549,7 +8552,7 @@
         <v>678</v>
       </c>
       <c r="B679" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8557,7 +8560,7 @@
         <v>679</v>
       </c>
       <c r="B680" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8565,7 +8568,7 @@
         <v>680</v>
       </c>
       <c r="B681" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8573,7 +8576,7 @@
         <v>681</v>
       </c>
       <c r="B682" s="1">
-        <v>540</v>
+        <v>900</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8581,7 +8584,7 @@
         <v>682</v>
       </c>
       <c r="B683" s="1">
-        <v>660</v>
+        <v>540</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8589,7 +8592,7 @@
         <v>683</v>
       </c>
       <c r="B684" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8597,7 +8600,7 @@
         <v>684</v>
       </c>
       <c r="B685" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8605,7 +8608,7 @@
         <v>685</v>
       </c>
       <c r="B686" s="1">
-        <v>860</v>
+        <v>900</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8613,7 +8616,7 @@
         <v>686</v>
       </c>
       <c r="B687" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8637,7 +8640,7 @@
         <v>689</v>
       </c>
       <c r="B690" s="1">
-        <v>980</v>
+        <v>900</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8645,7 +8648,7 @@
         <v>690</v>
       </c>
       <c r="B691" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8661,7 +8664,7 @@
         <v>692</v>
       </c>
       <c r="B693" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8669,7 +8672,7 @@
         <v>693</v>
       </c>
       <c r="B694" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8677,7 +8680,7 @@
         <v>694</v>
       </c>
       <c r="B695" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8685,7 +8688,7 @@
         <v>695</v>
       </c>
       <c r="B696" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8693,7 +8696,7 @@
         <v>696</v>
       </c>
       <c r="B697" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8701,7 +8704,7 @@
         <v>697</v>
       </c>
       <c r="B698" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8709,7 +8712,7 @@
         <v>698</v>
       </c>
       <c r="B699" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8717,7 +8720,7 @@
         <v>699</v>
       </c>
       <c r="B700" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8725,7 +8728,7 @@
         <v>700</v>
       </c>
       <c r="B701" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8733,7 +8736,7 @@
         <v>701</v>
       </c>
       <c r="B702" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8741,7 +8744,7 @@
         <v>702</v>
       </c>
       <c r="B703" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8749,7 +8752,7 @@
         <v>703</v>
       </c>
       <c r="B704" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8757,7 +8760,7 @@
         <v>704</v>
       </c>
       <c r="B705" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8765,7 +8768,7 @@
         <v>705</v>
       </c>
       <c r="B706" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8773,7 +8776,7 @@
         <v>706</v>
       </c>
       <c r="B707" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8781,7 +8784,7 @@
         <v>707</v>
       </c>
       <c r="B708" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8789,7 +8792,7 @@
         <v>708</v>
       </c>
       <c r="B709" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8797,7 +8800,7 @@
         <v>709</v>
       </c>
       <c r="B710" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8805,7 +8808,7 @@
         <v>710</v>
       </c>
       <c r="B711" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8813,7 +8816,7 @@
         <v>711</v>
       </c>
       <c r="B712" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8821,7 +8824,7 @@
         <v>712</v>
       </c>
       <c r="B713" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8829,7 +8832,7 @@
         <v>713</v>
       </c>
       <c r="B714" s="1">
-        <v>1000</v>
+        <v>880</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8837,7 +8840,7 @@
         <v>714</v>
       </c>
       <c r="B715" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8845,7 +8848,7 @@
         <v>715</v>
       </c>
       <c r="B716" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8853,7 +8856,7 @@
         <v>716</v>
       </c>
       <c r="B717" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8861,7 +8864,7 @@
         <v>717</v>
       </c>
       <c r="B718" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8869,7 +8872,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8877,7 +8880,7 @@
         <v>719</v>
       </c>
       <c r="B720" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8885,7 +8888,7 @@
         <v>720</v>
       </c>
       <c r="B721" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8893,7 +8896,7 @@
         <v>721</v>
       </c>
       <c r="B722" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8909,7 +8912,7 @@
         <v>723</v>
       </c>
       <c r="B724" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8925,7 +8928,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8933,7 +8936,7 @@
         <v>726</v>
       </c>
       <c r="B727" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8941,7 +8944,7 @@
         <v>727</v>
       </c>
       <c r="B728" s="1">
-        <v>880</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8949,7 +8952,7 @@
         <v>728</v>
       </c>
       <c r="B729" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8957,7 +8960,7 @@
         <v>729</v>
       </c>
       <c r="B730" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8965,7 +8968,7 @@
         <v>730</v>
       </c>
       <c r="B731" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8973,7 +8976,7 @@
         <v>731</v>
       </c>
       <c r="B732" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -8981,7 +8984,7 @@
         <v>732</v>
       </c>
       <c r="B733" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -8989,7 +8992,7 @@
         <v>733</v>
       </c>
       <c r="B734" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -8997,7 +9000,7 @@
         <v>734</v>
       </c>
       <c r="B735" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -9005,7 +9008,7 @@
         <v>735</v>
       </c>
       <c r="B736" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -9021,7 +9024,7 @@
         <v>737</v>
       </c>
       <c r="B738" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="739" spans="1:2">
@@ -9037,7 +9040,7 @@
         <v>739</v>
       </c>
       <c r="B740" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -9045,7 +9048,7 @@
         <v>740</v>
       </c>
       <c r="B741" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="742" spans="1:2">
@@ -9053,7 +9056,7 @@
         <v>741</v>
       </c>
       <c r="B742" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -9061,7 +9064,7 @@
         <v>742</v>
       </c>
       <c r="B743" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="744" spans="1:2">
@@ -9069,7 +9072,7 @@
         <v>743</v>
       </c>
       <c r="B744" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="745" spans="1:2">
@@ -9077,7 +9080,7 @@
         <v>744</v>
       </c>
       <c r="B745" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -9085,7 +9088,7 @@
         <v>745</v>
       </c>
       <c r="B746" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="747" spans="1:2">
@@ -9093,7 +9096,7 @@
         <v>746</v>
       </c>
       <c r="B747" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="748" spans="1:2">
@@ -9101,7 +9104,7 @@
         <v>747</v>
       </c>
       <c r="B748" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="749" spans="1:2">
@@ -9109,7 +9112,7 @@
         <v>748</v>
       </c>
       <c r="B749" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -9117,7 +9120,7 @@
         <v>749</v>
       </c>
       <c r="B750" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="751" spans="1:2">
@@ -9125,7 +9128,7 @@
         <v>750</v>
       </c>
       <c r="B751" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="752" spans="1:2">
@@ -9133,7 +9136,7 @@
         <v>751</v>
       </c>
       <c r="B752" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="753" spans="1:2">
@@ -9141,7 +9144,7 @@
         <v>752</v>
       </c>
       <c r="B753" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="754" spans="1:2">
@@ -9149,7 +9152,7 @@
         <v>753</v>
       </c>
       <c r="B754" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -9157,7 +9160,7 @@
         <v>754</v>
       </c>
       <c r="B755" s="1">
-        <v>1100</v>
+        <v>720</v>
       </c>
     </row>
     <row r="756" spans="1:2">
@@ -9165,7 +9168,7 @@
         <v>755</v>
       </c>
       <c r="B756" s="1">
-        <v>940</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="757" spans="1:2">
@@ -9181,7 +9184,7 @@
         <v>757</v>
       </c>
       <c r="B758" s="1">
-        <v>820</v>
+        <v>940</v>
       </c>
     </row>
     <row r="759" spans="1:2">
@@ -9189,7 +9192,7 @@
         <v>758</v>
       </c>
       <c r="B759" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="760" spans="1:2">
@@ -9197,7 +9200,7 @@
         <v>759</v>
       </c>
       <c r="B760" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="761" spans="1:2">
@@ -9213,7 +9216,7 @@
         <v>761</v>
       </c>
       <c r="B762" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="763" spans="1:2">
@@ -9221,7 +9224,7 @@
         <v>762</v>
       </c>
       <c r="B763" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="764" spans="1:2">
@@ -9229,7 +9232,7 @@
         <v>763</v>
       </c>
       <c r="B764" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="765" spans="1:2">
@@ -9237,7 +9240,7 @@
         <v>764</v>
       </c>
       <c r="B765" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="766" spans="1:2">
@@ -9245,7 +9248,7 @@
         <v>765</v>
       </c>
       <c r="B766" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="767" spans="1:2">
@@ -9261,7 +9264,7 @@
         <v>767</v>
       </c>
       <c r="B768" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="769" spans="1:2">
@@ -9269,7 +9272,7 @@
         <v>768</v>
       </c>
       <c r="B769" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="770" spans="1:2">
@@ -9277,7 +9280,7 @@
         <v>769</v>
       </c>
       <c r="B770" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="771" spans="1:2">
@@ -9285,7 +9288,7 @@
         <v>770</v>
       </c>
       <c r="B771" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="772" spans="1:2">
@@ -9293,7 +9296,7 @@
         <v>771</v>
       </c>
       <c r="B772" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="773" spans="1:2">
@@ -9301,7 +9304,7 @@
         <v>772</v>
       </c>
       <c r="B773" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="774" spans="1:2">
@@ -9309,7 +9312,7 @@
         <v>773</v>
       </c>
       <c r="B774" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="775" spans="1:2">
@@ -9317,7 +9320,7 @@
         <v>774</v>
       </c>
       <c r="B775" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="776" spans="1:2">
@@ -9325,7 +9328,7 @@
         <v>775</v>
       </c>
       <c r="B776" s="1">
-        <v>700</v>
+        <v>440</v>
       </c>
     </row>
     <row r="777" spans="1:2">
@@ -9333,7 +9336,7 @@
         <v>776</v>
       </c>
       <c r="B777" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="778" spans="1:2">
@@ -9349,7 +9352,7 @@
         <v>778</v>
       </c>
       <c r="B779" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="780" spans="1:2">
@@ -9357,7 +9360,7 @@
         <v>779</v>
       </c>
       <c r="B780" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="781" spans="1:2">
@@ -9365,7 +9368,7 @@
         <v>780</v>
       </c>
       <c r="B781" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="782" spans="1:2">
@@ -9373,7 +9376,7 @@
         <v>781</v>
       </c>
       <c r="B782" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="783" spans="1:2">
@@ -9381,7 +9384,7 @@
         <v>782</v>
       </c>
       <c r="B783" s="1">
-        <v>900</v>
+        <v>560</v>
       </c>
     </row>
     <row r="784" spans="1:2">
@@ -9389,7 +9392,7 @@
         <v>783</v>
       </c>
       <c r="B784" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="785" spans="1:2">
@@ -9397,7 +9400,7 @@
         <v>784</v>
       </c>
       <c r="B785" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="786" spans="1:2">
@@ -9405,7 +9408,7 @@
         <v>785</v>
       </c>
       <c r="B786" s="1">
-        <v>800</v>
+        <v>880</v>
       </c>
     </row>
     <row r="787" spans="1:2">
@@ -9413,7 +9416,7 @@
         <v>786</v>
       </c>
       <c r="B787" s="1">
-        <v>880</v>
+        <v>800</v>
       </c>
     </row>
     <row r="788" spans="1:2">
@@ -9421,7 +9424,7 @@
         <v>787</v>
       </c>
       <c r="B788" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="789" spans="1:2">
@@ -9429,7 +9432,7 @@
         <v>788</v>
       </c>
       <c r="B789" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="790" spans="1:2">
@@ -9437,7 +9440,7 @@
         <v>789</v>
       </c>
       <c r="B790" s="1">
-        <v>800</v>
+        <v>920</v>
       </c>
     </row>
     <row r="791" spans="1:2">
@@ -9445,7 +9448,7 @@
         <v>790</v>
       </c>
       <c r="B791" s="1">
-        <v>940</v>
+        <v>800</v>
       </c>
     </row>
     <row r="792" spans="1:2">
@@ -9453,7 +9456,7 @@
         <v>791</v>
       </c>
       <c r="B792" s="1">
-        <v>980</v>
+        <v>940</v>
       </c>
     </row>
     <row r="793" spans="1:2">
@@ -9461,7 +9464,7 @@
         <v>792</v>
       </c>
       <c r="B793" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="794" spans="1:2">
@@ -9469,7 +9472,7 @@
         <v>793</v>
       </c>
       <c r="B794" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="795" spans="1:2">
@@ -9477,7 +9480,7 @@
         <v>794</v>
       </c>
       <c r="B795" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="796" spans="1:2">
@@ -9485,7 +9488,7 @@
         <v>795</v>
       </c>
       <c r="B796" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="797" spans="1:2">
@@ -9493,7 +9496,7 @@
         <v>796</v>
       </c>
       <c r="B797" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="798" spans="1:2">
@@ -9501,7 +9504,7 @@
         <v>797</v>
       </c>
       <c r="B798" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="799" spans="1:2">
@@ -9509,7 +9512,7 @@
         <v>798</v>
       </c>
       <c r="B799" s="1">
-        <v>960</v>
+        <v>820</v>
       </c>
     </row>
     <row r="800" spans="1:2">
@@ -9517,7 +9520,7 @@
         <v>799</v>
       </c>
       <c r="B800" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="801" spans="1:2">
@@ -9525,7 +9528,7 @@
         <v>800</v>
       </c>
       <c r="B801" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="802" spans="1:2">
@@ -9533,7 +9536,7 @@
         <v>801</v>
       </c>
       <c r="B802" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="803" spans="1:2">
@@ -9541,7 +9544,7 @@
         <v>802</v>
       </c>
       <c r="B803" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="804" spans="1:2">
@@ -9549,7 +9552,7 @@
         <v>803</v>
       </c>
       <c r="B804" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="805" spans="1:2">
@@ -9557,7 +9560,7 @@
         <v>804</v>
       </c>
       <c r="B805" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="806" spans="1:2">
@@ -9565,7 +9568,7 @@
         <v>805</v>
       </c>
       <c r="B806" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="807" spans="1:2">
@@ -9573,7 +9576,7 @@
         <v>806</v>
       </c>
       <c r="B807" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="808" spans="1:2">
@@ -9581,7 +9584,7 @@
         <v>807</v>
       </c>
       <c r="B808" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="809" spans="1:2">
@@ -9589,7 +9592,7 @@
         <v>808</v>
       </c>
       <c r="B809" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="810" spans="1:2">
@@ -9597,7 +9600,7 @@
         <v>809</v>
       </c>
       <c r="B810" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="811" spans="1:2">
@@ -9605,7 +9608,7 @@
         <v>810</v>
       </c>
       <c r="B811" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="812" spans="1:2">
@@ -9613,7 +9616,7 @@
         <v>811</v>
       </c>
       <c r="B812" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="813" spans="1:2">
@@ -9621,7 +9624,7 @@
         <v>812</v>
       </c>
       <c r="B813" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="814" spans="1:2">
@@ -9629,7 +9632,7 @@
         <v>813</v>
       </c>
       <c r="B814" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="815" spans="1:2">
@@ -9637,7 +9640,7 @@
         <v>814</v>
       </c>
       <c r="B815" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="816" spans="1:2">
@@ -9645,7 +9648,7 @@
         <v>815</v>
       </c>
       <c r="B816" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="817" spans="1:2">
@@ -9653,7 +9656,7 @@
         <v>816</v>
       </c>
       <c r="B817" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="818" spans="1:2">
@@ -9661,7 +9664,7 @@
         <v>817</v>
       </c>
       <c r="B818" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="819" spans="1:2">
@@ -9669,7 +9672,7 @@
         <v>818</v>
       </c>
       <c r="B819" s="1">
-        <v>860</v>
+        <v>800</v>
       </c>
     </row>
     <row r="820" spans="1:2">
@@ -9677,7 +9680,7 @@
         <v>819</v>
       </c>
       <c r="B820" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="821" spans="1:2">
@@ -9685,7 +9688,7 @@
         <v>820</v>
       </c>
       <c r="B821" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="822" spans="1:2">
@@ -9693,7 +9696,7 @@
         <v>821</v>
       </c>
       <c r="B822" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="823" spans="1:2">
@@ -9701,7 +9704,7 @@
         <v>822</v>
       </c>
       <c r="B823" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="824" spans="1:2">
@@ -9709,7 +9712,7 @@
         <v>823</v>
       </c>
       <c r="B824" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="825" spans="1:2">
@@ -9725,7 +9728,7 @@
         <v>825</v>
       </c>
       <c r="B826" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="827" spans="1:2">
@@ -9741,7 +9744,7 @@
         <v>827</v>
       </c>
       <c r="B828" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="829" spans="1:2">
@@ -9749,7 +9752,7 @@
         <v>828</v>
       </c>
       <c r="B829" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="830" spans="1:2">
@@ -9757,7 +9760,7 @@
         <v>829</v>
       </c>
       <c r="B830" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="831" spans="1:2">
@@ -9765,7 +9768,7 @@
         <v>830</v>
       </c>
       <c r="B831" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="832" spans="1:2">
@@ -9773,7 +9776,7 @@
         <v>831</v>
       </c>
       <c r="B832" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="833" spans="1:2">
@@ -9781,7 +9784,7 @@
         <v>832</v>
       </c>
       <c r="B833" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="834" spans="1:2">
@@ -9789,7 +9792,7 @@
         <v>833</v>
       </c>
       <c r="B834" s="1">
-        <v>940</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="835" spans="1:2">
@@ -9797,7 +9800,7 @@
         <v>834</v>
       </c>
       <c r="B835" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="836" spans="1:2">
@@ -9805,7 +9808,7 @@
         <v>835</v>
       </c>
       <c r="B836" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="837" spans="1:2">
@@ -9813,7 +9816,7 @@
         <v>836</v>
       </c>
       <c r="B837" s="1">
-        <v>1100</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="838" spans="1:2">
@@ -9821,7 +9824,7 @@
         <v>837</v>
       </c>
       <c r="B838" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="839" spans="1:2">
@@ -9837,7 +9840,7 @@
         <v>839</v>
       </c>
       <c r="B840" s="1">
-        <v>960</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="841" spans="1:2">
@@ -9845,7 +9848,7 @@
         <v>840</v>
       </c>
       <c r="B841" s="1">
-        <v>1100</v>
+        <v>960</v>
       </c>
     </row>
     <row r="842" spans="1:2">
@@ -9853,7 +9856,7 @@
         <v>841</v>
       </c>
       <c r="B842" s="1">
-        <v>740</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="843" spans="1:2">
@@ -9861,7 +9864,7 @@
         <v>842</v>
       </c>
       <c r="B843" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="844" spans="1:2">
@@ -9869,7 +9872,7 @@
         <v>843</v>
       </c>
       <c r="B844" s="1">
-        <v>440</v>
+        <v>820</v>
       </c>
     </row>
     <row r="845" spans="1:2">
@@ -9877,7 +9880,7 @@
         <v>844</v>
       </c>
       <c r="B845" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="846" spans="1:2">
@@ -9885,7 +9888,7 @@
         <v>845</v>
       </c>
       <c r="B846" s="1">
-        <v>440</v>
+        <v>500</v>
       </c>
     </row>
     <row r="847" spans="1:2">
@@ -9893,7 +9896,7 @@
         <v>846</v>
       </c>
       <c r="B847" s="1">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="848" spans="1:2">
@@ -9901,7 +9904,7 @@
         <v>847</v>
       </c>
       <c r="B848" s="1">
-        <v>500</v>
+        <v>560</v>
       </c>
     </row>
     <row r="849" spans="1:2">
@@ -9909,7 +9912,7 @@
         <v>848</v>
       </c>
       <c r="B849" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="850" spans="1:2">
@@ -9925,7 +9928,7 @@
         <v>850</v>
       </c>
       <c r="B851" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="852" spans="1:2">
@@ -9933,7 +9936,7 @@
         <v>851</v>
       </c>
       <c r="B852" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="853" spans="1:2">
@@ -9941,7 +9944,7 @@
         <v>852</v>
       </c>
       <c r="B853" s="1">
-        <v>400</v>
+        <v>840</v>
       </c>
     </row>
     <row r="854" spans="1:2">
@@ -9957,7 +9960,7 @@
         <v>854</v>
       </c>
       <c r="B855" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="856" spans="1:2">
@@ -9965,7 +9968,7 @@
         <v>855</v>
       </c>
       <c r="B856" s="1">
-        <v>840</v>
+        <v>380</v>
       </c>
     </row>
     <row r="857" spans="1:2">
@@ -9973,7 +9976,7 @@
         <v>856</v>
       </c>
       <c r="B857" s="1">
-        <v>380</v>
+        <v>840</v>
       </c>
     </row>
     <row r="858" spans="1:2">
@@ -9989,7 +9992,7 @@
         <v>858</v>
       </c>
       <c r="B859" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="860" spans="1:2">
@@ -9997,7 +10000,7 @@
         <v>859</v>
       </c>
       <c r="B860" s="1">
-        <v>700</v>
+        <v>520</v>
       </c>
     </row>
     <row r="861" spans="1:2">
@@ -10005,7 +10008,7 @@
         <v>860</v>
       </c>
       <c r="B861" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="862" spans="1:2">
@@ -10013,7 +10016,7 @@
         <v>861</v>
       </c>
       <c r="B862" s="1">
-        <v>860</v>
+        <v>800</v>
       </c>
     </row>
     <row r="863" spans="1:2">
@@ -10021,7 +10024,7 @@
         <v>862</v>
       </c>
       <c r="B863" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="864" spans="1:2">
@@ -10029,7 +10032,7 @@
         <v>863</v>
       </c>
       <c r="B864" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="865" spans="1:2">
@@ -10045,7 +10048,7 @@
         <v>865</v>
       </c>
       <c r="B866" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="867" spans="1:2">
@@ -10053,7 +10056,7 @@
         <v>866</v>
       </c>
       <c r="B867" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="868" spans="1:2">
@@ -10061,7 +10064,7 @@
         <v>867</v>
       </c>
       <c r="B868" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="869" spans="1:2">
@@ -10077,7 +10080,7 @@
         <v>869</v>
       </c>
       <c r="B870" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="871" spans="1:2">
@@ -10093,7 +10096,7 @@
         <v>871</v>
       </c>
       <c r="B872" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="873" spans="1:2">
@@ -10101,7 +10104,7 @@
         <v>872</v>
       </c>
       <c r="B873" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="874" spans="1:2">
@@ -10109,7 +10112,7 @@
         <v>873</v>
       </c>
       <c r="B874" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="875" spans="1:2">
@@ -10117,7 +10120,7 @@
         <v>874</v>
       </c>
       <c r="B875" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="876" spans="1:2">
@@ -10133,7 +10136,7 @@
         <v>876</v>
       </c>
       <c r="B877" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="878" spans="1:2">
@@ -10141,7 +10144,7 @@
         <v>877</v>
       </c>
       <c r="B878" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="879" spans="1:2">
@@ -10149,7 +10152,7 @@
         <v>878</v>
       </c>
       <c r="B879" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="880" spans="1:2">
@@ -10157,7 +10160,7 @@
         <v>879</v>
       </c>
       <c r="B880" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="881" spans="1:2">
@@ -10165,7 +10168,7 @@
         <v>880</v>
       </c>
       <c r="B881" s="1">
-        <v>940</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="882" spans="1:2">
@@ -10173,7 +10176,7 @@
         <v>881</v>
       </c>
       <c r="B882" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="883" spans="1:2">
@@ -10181,7 +10184,7 @@
         <v>882</v>
       </c>
       <c r="B883" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="884" spans="1:2">
@@ -10189,7 +10192,7 @@
         <v>883</v>
       </c>
       <c r="B884" s="1">
-        <v>1100</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="885" spans="1:2">
@@ -10197,7 +10200,7 @@
         <v>884</v>
       </c>
       <c r="B885" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="886" spans="1:2">
@@ -10213,7 +10216,7 @@
         <v>886</v>
       </c>
       <c r="B887" s="1">
-        <v>960</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="888" spans="1:2">
@@ -10221,7 +10224,7 @@
         <v>887</v>
       </c>
       <c r="B888" s="1">
-        <v>1100</v>
+        <v>960</v>
       </c>
     </row>
     <row r="889" spans="1:2">
@@ -10229,7 +10232,7 @@
         <v>888</v>
       </c>
       <c r="B889" s="1">
-        <v>740</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="890" spans="1:2">
@@ -10237,7 +10240,7 @@
         <v>889</v>
       </c>
       <c r="B890" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="891" spans="1:2">
@@ -10245,7 +10248,7 @@
         <v>890</v>
       </c>
       <c r="B891" s="1">
-        <v>440</v>
+        <v>820</v>
       </c>
     </row>
     <row r="892" spans="1:2">
@@ -10253,7 +10256,7 @@
         <v>891</v>
       </c>
       <c r="B892" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="893" spans="1:2">
@@ -10261,7 +10264,7 @@
         <v>892</v>
       </c>
       <c r="B893" s="1">
-        <v>440</v>
+        <v>500</v>
       </c>
     </row>
     <row r="894" spans="1:2">
@@ -10269,7 +10272,7 @@
         <v>893</v>
       </c>
       <c r="B894" s="1">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="895" spans="1:2">
@@ -10277,7 +10280,7 @@
         <v>894</v>
       </c>
       <c r="B895" s="1">
-        <v>500</v>
+        <v>560</v>
       </c>
     </row>
     <row r="896" spans="1:2">
@@ -10285,7 +10288,7 @@
         <v>895</v>
       </c>
       <c r="B896" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="897" spans="1:2">
@@ -10293,7 +10296,7 @@
         <v>896</v>
       </c>
       <c r="B897" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="898" spans="1:2">
@@ -10317,7 +10320,7 @@
         <v>899</v>
       </c>
       <c r="B900" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="901" spans="1:2">
@@ -10341,7 +10344,7 @@
         <v>902</v>
       </c>
       <c r="B903" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="904" spans="1:2">
@@ -10357,7 +10360,7 @@
         <v>904</v>
       </c>
       <c r="B905" s="1">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="906" spans="1:2">
@@ -10365,7 +10368,7 @@
         <v>905</v>
       </c>
       <c r="B906" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="907" spans="1:2">
@@ -10373,7 +10376,7 @@
         <v>906</v>
       </c>
       <c r="B907" s="1">
-        <v>600</v>
+        <v>380</v>
       </c>
     </row>
     <row r="908" spans="1:2">
@@ -10381,7 +10384,7 @@
         <v>907</v>
       </c>
       <c r="B908" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="909" spans="1:2">
@@ -10389,7 +10392,7 @@
         <v>908</v>
       </c>
       <c r="B909" s="1">
-        <v>660</v>
+        <v>820</v>
       </c>
     </row>
     <row r="910" spans="1:2">
@@ -10397,7 +10400,7 @@
         <v>909</v>
       </c>
       <c r="B910" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="911" spans="1:2">
@@ -10405,7 +10408,7 @@
         <v>910</v>
       </c>
       <c r="B911" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="912" spans="1:2">
@@ -10413,7 +10416,7 @@
         <v>911</v>
       </c>
       <c r="B912" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="913" spans="1:2">
@@ -10421,7 +10424,7 @@
         <v>912</v>
       </c>
       <c r="B913" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="914" spans="1:2">
@@ -10429,7 +10432,7 @@
         <v>913</v>
       </c>
       <c r="B914" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="915" spans="1:2">
@@ -10437,6 +10440,14 @@
         <v>914</v>
       </c>
       <c r="B915" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="916" spans="1:2">
+      <c r="A916" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="B916" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="918">
   <si>
     <t>Наименование</t>
   </si>
@@ -404,6 +404,9 @@
     <t>Ganza - Ascension (NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Ganza - MILK MANIAC Ананас (milkshake), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Ganza - MILK MANIAC Гуава (milkshake), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1296,6 +1299,9 @@
   </si>
   <si>
     <t>Verhaeghe - BARBE RUBY (Fruit Beer), РОЗЛИВ, Бельгия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vostok Brouwerij - Savior (Сухой Сидр), РОЗЛИВ, Россия </t>
   </si>
   <si>
     <t>Weihenstephaner HEFE WEISSBIER, Розлив, Германия</t>
@@ -3116,7 +3122,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B916"/>
+  <dimension ref="A1:B918"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -4160,7 +4166,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -4168,7 +4174,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -4176,7 +4182,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -4184,7 +4190,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -4192,7 +4198,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -4200,7 +4206,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>680</v>
+        <v>960</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -4208,7 +4214,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>420</v>
+        <v>680</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -4216,7 +4222,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -4224,7 +4230,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -4232,7 +4238,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -4240,7 +4246,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -4248,7 +4254,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -4256,7 +4262,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -4264,7 +4270,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -4272,7 +4278,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -4280,7 +4286,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>580</v>
+        <v>880</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -4288,7 +4294,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -4296,7 +4302,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -4304,7 +4310,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>620</v>
+        <v>860</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -4312,7 +4318,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -4320,7 +4326,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -4328,7 +4334,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -4336,7 +4342,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -4344,7 +4350,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>900</v>
+        <v>960</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -4352,7 +4358,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -4360,7 +4366,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -4368,7 +4374,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -4376,7 +4382,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>500</v>
+        <v>780</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -4384,7 +4390,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>580</v>
+        <v>500</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -4392,7 +4398,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -4400,7 +4406,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -4408,7 +4414,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>980</v>
+        <v>520</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -4416,7 +4422,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>1100</v>
+        <v>980</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -4424,7 +4430,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>1060</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -4440,7 +4446,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>1000</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -4448,7 +4454,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -4464,7 +4470,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4472,7 +4478,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>1080</v>
+        <v>560</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -4480,12 +4486,12 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>840</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B171" s="1">
         <v>840</v>
@@ -4504,7 +4510,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="1">
-        <v>420</v>
+        <v>840</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4512,7 +4518,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="1">
-        <v>520</v>
+        <v>420</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4520,7 +4526,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4528,7 +4534,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="1">
-        <v>460</v>
+        <v>720</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4536,7 +4542,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="1">
-        <v>560</v>
+        <v>460</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4544,7 +4550,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4552,7 +4558,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4560,7 +4566,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4568,7 +4574,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4576,7 +4582,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="1">
-        <v>980</v>
+        <v>520</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4584,7 +4590,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="1">
-        <v>540</v>
+        <v>980</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4592,7 +4598,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4600,7 +4606,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4608,7 +4614,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4616,7 +4622,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="1">
-        <v>560</v>
+        <v>760</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4624,7 +4630,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="1">
-        <v>1100</v>
+        <v>560</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4656,7 +4662,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4664,7 +4670,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4672,7 +4678,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4680,7 +4686,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4712,7 +4718,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4720,7 +4726,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4728,7 +4734,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4736,7 +4742,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4744,7 +4750,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4752,7 +4758,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4760,7 +4766,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4768,7 +4774,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="1">
-        <v>980</v>
+        <v>700</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4776,7 +4782,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="1">
-        <v>460</v>
+        <v>980</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4784,7 +4790,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4792,7 +4798,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="1">
-        <v>720</v>
+        <v>580</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4800,7 +4806,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4808,7 +4814,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4816,7 +4822,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="1">
-        <v>260</v>
+        <v>780</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4832,7 +4838,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4848,7 +4854,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4856,7 +4862,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4864,7 +4870,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4872,7 +4878,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="1">
-        <v>500</v>
+        <v>760</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4880,7 +4886,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4888,7 +4894,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="1">
-        <v>740</v>
+        <v>400</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4896,7 +4902,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4904,7 +4910,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4912,7 +4918,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4920,7 +4926,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4928,7 +4934,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4936,7 +4942,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4952,7 +4958,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4960,7 +4966,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4968,7 +4974,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4976,7 +4982,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4984,7 +4990,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="1">
-        <v>580</v>
+        <v>860</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4992,7 +4998,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -5000,7 +5006,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="1">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -5008,7 +5014,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -5016,7 +5022,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -5024,7 +5030,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -5032,7 +5038,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -5040,7 +5046,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -5048,7 +5054,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -5056,7 +5062,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -5064,7 +5070,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -5072,7 +5078,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -5080,7 +5086,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="1">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -5088,7 +5094,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="1">
-        <v>480</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -5096,7 +5102,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -5104,7 +5110,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -5112,7 +5118,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -5120,7 +5126,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -5128,7 +5134,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -5136,7 +5142,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -5144,7 +5150,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -5152,7 +5158,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -5160,7 +5166,7 @@
         <v>254</v>
       </c>
       <c r="B255" s="1">
-        <v>900</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -5168,7 +5174,7 @@
         <v>255</v>
       </c>
       <c r="B256" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -5176,7 +5182,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -5184,7 +5190,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -5192,7 +5198,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -5208,7 +5214,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -5224,7 +5230,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -5232,7 +5238,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -5240,7 +5246,7 @@
         <v>264</v>
       </c>
       <c r="B265" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -5248,7 +5254,7 @@
         <v>265</v>
       </c>
       <c r="B266" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -5256,7 +5262,7 @@
         <v>266</v>
       </c>
       <c r="B267" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -5264,7 +5270,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -5272,7 +5278,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="1">
-        <v>980</v>
+        <v>840</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -5280,7 +5286,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -5296,7 +5302,7 @@
         <v>271</v>
       </c>
       <c r="B272" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -5304,7 +5310,7 @@
         <v>272</v>
       </c>
       <c r="B273" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -5312,7 +5318,7 @@
         <v>273</v>
       </c>
       <c r="B274" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -5320,7 +5326,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -5328,7 +5334,7 @@
         <v>275</v>
       </c>
       <c r="B276" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -5336,7 +5342,7 @@
         <v>276</v>
       </c>
       <c r="B277" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -5352,7 +5358,7 @@
         <v>278</v>
       </c>
       <c r="B279" s="1">
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -5360,7 +5366,7 @@
         <v>279</v>
       </c>
       <c r="B280" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -5368,7 +5374,7 @@
         <v>280</v>
       </c>
       <c r="B281" s="1">
-        <v>758</v>
+        <v>500</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -5376,7 +5382,7 @@
         <v>281</v>
       </c>
       <c r="B282" s="1">
-        <v>2273</v>
+        <v>758</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -5384,7 +5390,7 @@
         <v>282</v>
       </c>
       <c r="B283" s="1">
-        <v>1515</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -5392,7 +5398,7 @@
         <v>283</v>
       </c>
       <c r="B284" s="1">
-        <v>520</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -5400,7 +5406,7 @@
         <v>284</v>
       </c>
       <c r="B285" s="1">
-        <v>4000</v>
+        <v>520</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -5408,7 +5414,7 @@
         <v>285</v>
       </c>
       <c r="B286" s="1">
-        <v>560</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5416,7 +5422,7 @@
         <v>286</v>
       </c>
       <c r="B287" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5424,7 +5430,7 @@
         <v>287</v>
       </c>
       <c r="B288" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5440,7 +5446,7 @@
         <v>289</v>
       </c>
       <c r="B290" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5448,7 +5454,7 @@
         <v>290</v>
       </c>
       <c r="B291" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5456,7 +5462,7 @@
         <v>291</v>
       </c>
       <c r="B292" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5464,7 +5470,7 @@
         <v>292</v>
       </c>
       <c r="B293" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5472,7 +5478,7 @@
         <v>293</v>
       </c>
       <c r="B294" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5480,7 +5486,7 @@
         <v>294</v>
       </c>
       <c r="B295" s="1">
-        <v>680</v>
+        <v>520</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5488,7 +5494,7 @@
         <v>295</v>
       </c>
       <c r="B296" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5496,7 +5502,7 @@
         <v>296</v>
       </c>
       <c r="B297" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5504,7 +5510,7 @@
         <v>297</v>
       </c>
       <c r="B298" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5512,7 +5518,7 @@
         <v>298</v>
       </c>
       <c r="B299" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5520,7 +5526,7 @@
         <v>299</v>
       </c>
       <c r="B300" s="1">
-        <v>660</v>
+        <v>380</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5528,7 +5534,7 @@
         <v>300</v>
       </c>
       <c r="B301" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5536,7 +5542,7 @@
         <v>301</v>
       </c>
       <c r="B302" s="1">
-        <v>540</v>
+        <v>900</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5544,7 +5550,7 @@
         <v>302</v>
       </c>
       <c r="B303" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5552,7 +5558,7 @@
         <v>303</v>
       </c>
       <c r="B304" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5560,7 +5566,7 @@
         <v>304</v>
       </c>
       <c r="B305" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5568,7 +5574,7 @@
         <v>305</v>
       </c>
       <c r="B306" s="1">
-        <v>460</v>
+        <v>580</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5576,7 +5582,7 @@
         <v>306</v>
       </c>
       <c r="B307" s="1">
-        <v>520</v>
+        <v>460</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5584,7 +5590,7 @@
         <v>307</v>
       </c>
       <c r="B308" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5592,7 +5598,7 @@
         <v>308</v>
       </c>
       <c r="B309" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5600,7 +5606,7 @@
         <v>309</v>
       </c>
       <c r="B310" s="1">
-        <v>860</v>
+        <v>900</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5608,7 +5614,7 @@
         <v>310</v>
       </c>
       <c r="B311" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5632,7 +5638,7 @@
         <v>313</v>
       </c>
       <c r="B314" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5648,7 +5654,7 @@
         <v>315</v>
       </c>
       <c r="B316" s="1">
-        <v>980</v>
+        <v>560</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5656,7 +5662,7 @@
         <v>316</v>
       </c>
       <c r="B317" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5672,7 +5678,7 @@
         <v>318</v>
       </c>
       <c r="B319" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5680,7 +5686,7 @@
         <v>319</v>
       </c>
       <c r="B320" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5688,7 +5694,7 @@
         <v>320</v>
       </c>
       <c r="B321" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5696,7 +5702,7 @@
         <v>321</v>
       </c>
       <c r="B322" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5704,7 +5710,7 @@
         <v>322</v>
       </c>
       <c r="B323" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5712,7 +5718,7 @@
         <v>323</v>
       </c>
       <c r="B324" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5720,7 +5726,7 @@
         <v>324</v>
       </c>
       <c r="B325" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5728,7 +5734,7 @@
         <v>325</v>
       </c>
       <c r="B326" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5744,7 +5750,7 @@
         <v>327</v>
       </c>
       <c r="B328" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5752,7 +5758,7 @@
         <v>328</v>
       </c>
       <c r="B329" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5760,7 +5766,7 @@
         <v>329</v>
       </c>
       <c r="B330" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5768,7 +5774,7 @@
         <v>330</v>
       </c>
       <c r="B331" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5776,7 +5782,7 @@
         <v>331</v>
       </c>
       <c r="B332" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5784,7 +5790,7 @@
         <v>332</v>
       </c>
       <c r="B333" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5792,7 +5798,7 @@
         <v>333</v>
       </c>
       <c r="B334" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5800,7 +5806,7 @@
         <v>334</v>
       </c>
       <c r="B335" s="1">
-        <v>520</v>
+        <v>680</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5808,7 +5814,7 @@
         <v>335</v>
       </c>
       <c r="B336" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5816,7 +5822,7 @@
         <v>336</v>
       </c>
       <c r="B337" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5824,7 +5830,7 @@
         <v>337</v>
       </c>
       <c r="B338" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5832,7 +5838,7 @@
         <v>338</v>
       </c>
       <c r="B339" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5840,7 +5846,7 @@
         <v>339</v>
       </c>
       <c r="B340" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5848,7 +5854,7 @@
         <v>340</v>
       </c>
       <c r="B341" s="1">
-        <v>580</v>
+        <v>840</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5856,7 +5862,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="1">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5864,7 +5870,7 @@
         <v>342</v>
       </c>
       <c r="B343" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5872,7 +5878,7 @@
         <v>343</v>
       </c>
       <c r="B344" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5880,7 +5886,7 @@
         <v>344</v>
       </c>
       <c r="B345" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5888,7 +5894,7 @@
         <v>345</v>
       </c>
       <c r="B346" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5896,7 +5902,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5904,7 +5910,7 @@
         <v>347</v>
       </c>
       <c r="B348" s="1">
-        <v>1000</v>
+        <v>880</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5912,7 +5918,7 @@
         <v>348</v>
       </c>
       <c r="B349" s="1">
-        <v>520</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5920,7 +5926,7 @@
         <v>349</v>
       </c>
       <c r="B350" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5928,7 +5934,7 @@
         <v>350</v>
       </c>
       <c r="B351" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5936,7 +5942,7 @@
         <v>351</v>
       </c>
       <c r="B352" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5944,7 +5950,7 @@
         <v>352</v>
       </c>
       <c r="B353" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5952,7 +5958,7 @@
         <v>353</v>
       </c>
       <c r="B354" s="1">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5960,7 +5966,7 @@
         <v>354</v>
       </c>
       <c r="B355" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5968,7 +5974,7 @@
         <v>355</v>
       </c>
       <c r="B356" s="1">
-        <v>320</v>
+        <v>520</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5976,7 +5982,7 @@
         <v>356</v>
       </c>
       <c r="B357" s="1">
-        <v>540</v>
+        <v>320</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5984,7 +5990,7 @@
         <v>357</v>
       </c>
       <c r="B358" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5992,7 +5998,7 @@
         <v>358</v>
       </c>
       <c r="B359" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -6008,7 +6014,7 @@
         <v>360</v>
       </c>
       <c r="B361" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -6016,7 +6022,7 @@
         <v>361</v>
       </c>
       <c r="B362" s="1">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -6024,7 +6030,7 @@
         <v>362</v>
       </c>
       <c r="B363" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -6032,7 +6038,7 @@
         <v>363</v>
       </c>
       <c r="B364" s="1">
-        <v>480</v>
+        <v>800</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -6040,7 +6046,7 @@
         <v>364</v>
       </c>
       <c r="B365" s="1">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -6048,7 +6054,7 @@
         <v>365</v>
       </c>
       <c r="B366" s="1">
-        <v>520</v>
+        <v>800</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -6056,7 +6062,7 @@
         <v>366</v>
       </c>
       <c r="B367" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -6064,7 +6070,7 @@
         <v>367</v>
       </c>
       <c r="B368" s="1">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -6072,7 +6078,7 @@
         <v>368</v>
       </c>
       <c r="B369" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -6088,7 +6094,7 @@
         <v>370</v>
       </c>
       <c r="B371" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -6104,7 +6110,7 @@
         <v>372</v>
       </c>
       <c r="B373" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -6112,7 +6118,7 @@
         <v>373</v>
       </c>
       <c r="B374" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -6120,7 +6126,7 @@
         <v>374</v>
       </c>
       <c r="B375" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -6128,7 +6134,7 @@
         <v>375</v>
       </c>
       <c r="B376" s="1">
-        <v>880</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -6136,7 +6142,7 @@
         <v>376</v>
       </c>
       <c r="B377" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -6144,7 +6150,7 @@
         <v>377</v>
       </c>
       <c r="B378" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -6152,7 +6158,7 @@
         <v>378</v>
       </c>
       <c r="B379" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -6160,7 +6166,7 @@
         <v>379</v>
       </c>
       <c r="B380" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -6168,7 +6174,7 @@
         <v>380</v>
       </c>
       <c r="B381" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -6176,7 +6182,7 @@
         <v>381</v>
       </c>
       <c r="B382" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -6184,7 +6190,7 @@
         <v>382</v>
       </c>
       <c r="B383" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -6192,7 +6198,7 @@
         <v>383</v>
       </c>
       <c r="B384" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -6208,7 +6214,7 @@
         <v>385</v>
       </c>
       <c r="B386" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -6224,7 +6230,7 @@
         <v>387</v>
       </c>
       <c r="B388" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -6232,7 +6238,7 @@
         <v>388</v>
       </c>
       <c r="B389" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -6240,7 +6246,7 @@
         <v>389</v>
       </c>
       <c r="B390" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -6248,7 +6254,7 @@
         <v>390</v>
       </c>
       <c r="B391" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -6256,7 +6262,7 @@
         <v>391</v>
       </c>
       <c r="B392" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -6264,7 +6270,7 @@
         <v>392</v>
       </c>
       <c r="B393" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -6272,7 +6278,7 @@
         <v>393</v>
       </c>
       <c r="B394" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -6280,7 +6286,7 @@
         <v>394</v>
       </c>
       <c r="B395" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -6288,7 +6294,7 @@
         <v>395</v>
       </c>
       <c r="B396" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -6296,7 +6302,7 @@
         <v>396</v>
       </c>
       <c r="B397" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -6304,7 +6310,7 @@
         <v>397</v>
       </c>
       <c r="B398" s="1">
-        <v>640</v>
+        <v>480</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -6312,7 +6318,7 @@
         <v>398</v>
       </c>
       <c r="B399" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -6320,7 +6326,7 @@
         <v>399</v>
       </c>
       <c r="B400" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -6328,7 +6334,7 @@
         <v>400</v>
       </c>
       <c r="B401" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -6336,7 +6342,7 @@
         <v>401</v>
       </c>
       <c r="B402" s="1">
-        <v>520</v>
+        <v>860</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -6344,7 +6350,7 @@
         <v>402</v>
       </c>
       <c r="B403" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -6352,7 +6358,7 @@
         <v>403</v>
       </c>
       <c r="B404" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -6368,7 +6374,7 @@
         <v>405</v>
       </c>
       <c r="B406" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -6376,7 +6382,7 @@
         <v>406</v>
       </c>
       <c r="B407" s="1">
-        <v>700</v>
+        <v>420</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -6384,7 +6390,7 @@
         <v>407</v>
       </c>
       <c r="B408" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -6392,7 +6398,7 @@
         <v>408</v>
       </c>
       <c r="B409" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -6400,7 +6406,7 @@
         <v>409</v>
       </c>
       <c r="B410" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -6408,7 +6414,7 @@
         <v>410</v>
       </c>
       <c r="B411" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -6416,7 +6422,7 @@
         <v>411</v>
       </c>
       <c r="B412" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -6424,7 +6430,7 @@
         <v>412</v>
       </c>
       <c r="B413" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -6432,7 +6438,7 @@
         <v>413</v>
       </c>
       <c r="B414" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -6440,7 +6446,7 @@
         <v>414</v>
       </c>
       <c r="B415" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -6448,7 +6454,7 @@
         <v>415</v>
       </c>
       <c r="B416" s="1">
-        <v>440</v>
+        <v>620</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -6456,7 +6462,7 @@
         <v>416</v>
       </c>
       <c r="B417" s="1">
-        <v>1100</v>
+        <v>440</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -6472,7 +6478,7 @@
         <v>418</v>
       </c>
       <c r="B419" s="1">
-        <v>320</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -6480,7 +6486,7 @@
         <v>419</v>
       </c>
       <c r="B420" s="1">
-        <v>940</v>
+        <v>320</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -6488,7 +6494,7 @@
         <v>420</v>
       </c>
       <c r="B421" s="1">
-        <v>320</v>
+        <v>940</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -6496,7 +6502,7 @@
         <v>421</v>
       </c>
       <c r="B422" s="1">
-        <v>960</v>
+        <v>320</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -6504,7 +6510,7 @@
         <v>422</v>
       </c>
       <c r="B423" s="1">
-        <v>820</v>
+        <v>960</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -6512,7 +6518,7 @@
         <v>423</v>
       </c>
       <c r="B424" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -6520,7 +6526,7 @@
         <v>424</v>
       </c>
       <c r="B425" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -6536,7 +6542,7 @@
         <v>426</v>
       </c>
       <c r="B427" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -6544,7 +6550,7 @@
         <v>427</v>
       </c>
       <c r="B428" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6552,7 +6558,7 @@
         <v>428</v>
       </c>
       <c r="B429" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6560,7 +6566,7 @@
         <v>429</v>
       </c>
       <c r="B430" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6568,7 +6574,7 @@
         <v>430</v>
       </c>
       <c r="B431" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6576,7 +6582,7 @@
         <v>431</v>
       </c>
       <c r="B432" s="1">
-        <v>920</v>
+        <v>620</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6584,7 +6590,7 @@
         <v>432</v>
       </c>
       <c r="B433" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6592,7 +6598,7 @@
         <v>433</v>
       </c>
       <c r="B434" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6600,7 +6606,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6616,7 +6622,7 @@
         <v>436</v>
       </c>
       <c r="B437" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6624,7 +6630,7 @@
         <v>437</v>
       </c>
       <c r="B438" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6632,7 +6638,7 @@
         <v>438</v>
       </c>
       <c r="B439" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6640,7 +6646,7 @@
         <v>439</v>
       </c>
       <c r="B440" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6648,7 +6654,7 @@
         <v>440</v>
       </c>
       <c r="B441" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6656,7 +6662,7 @@
         <v>441</v>
       </c>
       <c r="B442" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6672,7 +6678,7 @@
         <v>443</v>
       </c>
       <c r="B444" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6680,7 +6686,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="1">
-        <v>440</v>
+        <v>900</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6688,7 +6694,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6696,7 +6702,7 @@
         <v>446</v>
       </c>
       <c r="B447" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6704,7 +6710,7 @@
         <v>447</v>
       </c>
       <c r="B448" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6712,7 +6718,7 @@
         <v>448</v>
       </c>
       <c r="B449" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6720,7 +6726,7 @@
         <v>449</v>
       </c>
       <c r="B450" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6728,7 +6734,7 @@
         <v>450</v>
       </c>
       <c r="B451" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6736,7 +6742,7 @@
         <v>451</v>
       </c>
       <c r="B452" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6744,7 +6750,7 @@
         <v>452</v>
       </c>
       <c r="B453" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6752,7 +6758,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6760,7 +6766,7 @@
         <v>454</v>
       </c>
       <c r="B455" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6768,7 +6774,7 @@
         <v>455</v>
       </c>
       <c r="B456" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6776,7 +6782,7 @@
         <v>456</v>
       </c>
       <c r="B457" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6784,7 +6790,7 @@
         <v>457</v>
       </c>
       <c r="B458" s="1">
-        <v>680</v>
+        <v>620</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6792,7 +6798,7 @@
         <v>458</v>
       </c>
       <c r="B459" s="1">
-        <v>480</v>
+        <v>720</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6800,7 +6806,7 @@
         <v>459</v>
       </c>
       <c r="B460" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6808,7 +6814,7 @@
         <v>460</v>
       </c>
       <c r="B461" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6816,7 +6822,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="1">
-        <v>840</v>
+        <v>480</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6824,7 +6830,7 @@
         <v>462</v>
       </c>
       <c r="B463" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6832,7 +6838,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6848,7 +6854,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6856,7 +6862,7 @@
         <v>466</v>
       </c>
       <c r="B467" s="1">
-        <v>920</v>
+        <v>880</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6864,7 +6870,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6872,7 +6878,7 @@
         <v>468</v>
       </c>
       <c r="B469" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6880,7 +6886,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="1">
-        <v>940</v>
+        <v>800</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6888,7 +6894,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6896,7 +6902,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6904,7 +6910,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="1">
-        <v>600</v>
+        <v>980</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6912,7 +6918,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="1">
-        <v>760</v>
+        <v>920</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6920,7 +6926,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6928,7 +6934,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="1">
-        <v>620</v>
+        <v>760</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6936,7 +6942,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6944,7 +6950,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6952,7 +6958,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="1">
-        <v>920</v>
+        <v>620</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6960,7 +6966,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="1">
-        <v>640</v>
+        <v>860</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6968,7 +6974,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6976,7 +6982,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="1">
-        <v>820</v>
+        <v>640</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6984,7 +6990,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6992,7 +6998,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -7000,7 +7006,7 @@
         <v>484</v>
       </c>
       <c r="B485" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -7008,7 +7014,7 @@
         <v>485</v>
       </c>
       <c r="B486" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -7016,7 +7022,7 @@
         <v>486</v>
       </c>
       <c r="B487" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -7024,7 +7030,7 @@
         <v>487</v>
       </c>
       <c r="B488" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -7032,7 +7038,7 @@
         <v>488</v>
       </c>
       <c r="B489" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -7040,7 +7046,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="1">
-        <v>660</v>
+        <v>560</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -7048,7 +7054,7 @@
         <v>490</v>
       </c>
       <c r="B491" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -7056,7 +7062,7 @@
         <v>491</v>
       </c>
       <c r="B492" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -7064,7 +7070,7 @@
         <v>492</v>
       </c>
       <c r="B493" s="1">
-        <v>840</v>
+        <v>640</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -7072,7 +7078,7 @@
         <v>493</v>
       </c>
       <c r="B494" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -7080,7 +7086,7 @@
         <v>494</v>
       </c>
       <c r="B495" s="1">
-        <v>480</v>
+        <v>840</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -7088,7 +7094,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="1">
-        <v>620</v>
+        <v>520</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -7096,7 +7102,7 @@
         <v>496</v>
       </c>
       <c r="B497" s="1">
-        <v>780</v>
+        <v>480</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -7104,7 +7110,7 @@
         <v>497</v>
       </c>
       <c r="B498" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -7112,7 +7118,7 @@
         <v>498</v>
       </c>
       <c r="B499" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -7120,7 +7126,7 @@
         <v>499</v>
       </c>
       <c r="B500" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -7128,7 +7134,7 @@
         <v>500</v>
       </c>
       <c r="B501" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -7136,7 +7142,7 @@
         <v>501</v>
       </c>
       <c r="B502" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -7144,7 +7150,7 @@
         <v>502</v>
       </c>
       <c r="B503" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -7152,7 +7158,7 @@
         <v>503</v>
       </c>
       <c r="B504" s="1">
-        <v>480</v>
+        <v>780</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -7160,7 +7166,7 @@
         <v>504</v>
       </c>
       <c r="B505" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -7168,7 +7174,7 @@
         <v>505</v>
       </c>
       <c r="B506" s="1">
-        <v>660</v>
+        <v>480</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -7176,7 +7182,7 @@
         <v>506</v>
       </c>
       <c r="B507" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -7184,7 +7190,7 @@
         <v>507</v>
       </c>
       <c r="B508" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -7192,7 +7198,7 @@
         <v>508</v>
       </c>
       <c r="B509" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -7200,7 +7206,7 @@
         <v>509</v>
       </c>
       <c r="B510" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -7208,7 +7214,7 @@
         <v>510</v>
       </c>
       <c r="B511" s="1">
-        <v>940</v>
+        <v>440</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -7216,7 +7222,7 @@
         <v>511</v>
       </c>
       <c r="B512" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -7224,7 +7230,7 @@
         <v>512</v>
       </c>
       <c r="B513" s="1">
-        <v>880</v>
+        <v>940</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -7232,7 +7238,7 @@
         <v>513</v>
       </c>
       <c r="B514" s="1">
-        <v>880</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -7240,7 +7246,7 @@
         <v>514</v>
       </c>
       <c r="B515" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -7248,7 +7254,7 @@
         <v>515</v>
       </c>
       <c r="B516" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -7256,7 +7262,7 @@
         <v>516</v>
       </c>
       <c r="B517" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -7264,7 +7270,7 @@
         <v>517</v>
       </c>
       <c r="B518" s="1">
-        <v>1100</v>
+        <v>840</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -7272,7 +7278,7 @@
         <v>518</v>
       </c>
       <c r="B519" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -7280,7 +7286,7 @@
         <v>519</v>
       </c>
       <c r="B520" s="1">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -7288,7 +7294,7 @@
         <v>520</v>
       </c>
       <c r="B521" s="1">
-        <v>760</v>
+        <v>840</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -7296,7 +7302,7 @@
         <v>521</v>
       </c>
       <c r="B522" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -7304,7 +7310,7 @@
         <v>522</v>
       </c>
       <c r="B523" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -7312,7 +7318,7 @@
         <v>523</v>
       </c>
       <c r="B524" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -7320,7 +7326,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -7328,7 +7334,7 @@
         <v>525</v>
       </c>
       <c r="B526" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -7336,7 +7342,7 @@
         <v>526</v>
       </c>
       <c r="B527" s="1">
-        <v>760</v>
+        <v>840</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -7344,7 +7350,7 @@
         <v>527</v>
       </c>
       <c r="B528" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -7352,7 +7358,7 @@
         <v>528</v>
       </c>
       <c r="B529" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -7360,7 +7366,7 @@
         <v>529</v>
       </c>
       <c r="B530" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -7368,7 +7374,7 @@
         <v>530</v>
       </c>
       <c r="B531" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -7376,7 +7382,7 @@
         <v>531</v>
       </c>
       <c r="B532" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -7384,7 +7390,7 @@
         <v>532</v>
       </c>
       <c r="B533" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -7392,7 +7398,7 @@
         <v>533</v>
       </c>
       <c r="B534" s="1">
-        <v>660</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -7400,7 +7406,7 @@
         <v>534</v>
       </c>
       <c r="B535" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -7408,7 +7414,7 @@
         <v>535</v>
       </c>
       <c r="B536" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -7416,7 +7422,7 @@
         <v>536</v>
       </c>
       <c r="B537" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -7424,7 +7430,7 @@
         <v>537</v>
       </c>
       <c r="B538" s="1">
-        <v>880</v>
+        <v>620</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -7432,7 +7438,7 @@
         <v>538</v>
       </c>
       <c r="B539" s="1">
-        <v>1060</v>
+        <v>840</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -7440,7 +7446,7 @@
         <v>539</v>
       </c>
       <c r="B540" s="1">
-        <v>860</v>
+        <v>880</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -7448,7 +7454,7 @@
         <v>540</v>
       </c>
       <c r="B541" s="1">
-        <v>860</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -7456,7 +7462,7 @@
         <v>541</v>
       </c>
       <c r="B542" s="1">
-        <v>800</v>
+        <v>860</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -7472,7 +7478,7 @@
         <v>543</v>
       </c>
       <c r="B544" s="1">
-        <v>960</v>
+        <v>800</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -7480,7 +7486,7 @@
         <v>544</v>
       </c>
       <c r="B545" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -7488,7 +7494,7 @@
         <v>545</v>
       </c>
       <c r="B546" s="1">
-        <v>720</v>
+        <v>960</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -7496,7 +7502,7 @@
         <v>546</v>
       </c>
       <c r="B547" s="1">
-        <v>1000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -7504,7 +7510,7 @@
         <v>547</v>
       </c>
       <c r="B548" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -7512,7 +7518,7 @@
         <v>548</v>
       </c>
       <c r="B549" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -7520,7 +7526,7 @@
         <v>549</v>
       </c>
       <c r="B550" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -7528,7 +7534,7 @@
         <v>550</v>
       </c>
       <c r="B551" s="1">
-        <v>980</v>
+        <v>900</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -7536,7 +7542,7 @@
         <v>551</v>
       </c>
       <c r="B552" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7544,7 +7550,7 @@
         <v>552</v>
       </c>
       <c r="B553" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7552,7 +7558,7 @@
         <v>553</v>
       </c>
       <c r="B554" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7560,7 +7566,7 @@
         <v>554</v>
       </c>
       <c r="B555" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7568,7 +7574,7 @@
         <v>555</v>
       </c>
       <c r="B556" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7576,7 +7582,7 @@
         <v>556</v>
       </c>
       <c r="B557" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7592,7 +7598,7 @@
         <v>558</v>
       </c>
       <c r="B559" s="1">
-        <v>640</v>
+        <v>900</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7600,7 +7606,7 @@
         <v>559</v>
       </c>
       <c r="B560" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7608,7 +7614,7 @@
         <v>560</v>
       </c>
       <c r="B561" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7616,7 +7622,7 @@
         <v>561</v>
       </c>
       <c r="B562" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7624,7 +7630,7 @@
         <v>562</v>
       </c>
       <c r="B563" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7632,7 +7638,7 @@
         <v>563</v>
       </c>
       <c r="B564" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7640,7 +7646,7 @@
         <v>564</v>
       </c>
       <c r="B565" s="1">
-        <v>880</v>
+        <v>700</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7648,7 +7654,7 @@
         <v>565</v>
       </c>
       <c r="B566" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7656,7 +7662,7 @@
         <v>566</v>
       </c>
       <c r="B567" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7680,7 +7686,7 @@
         <v>569</v>
       </c>
       <c r="B570" s="1">
-        <v>920</v>
+        <v>820</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7688,7 +7694,7 @@
         <v>570</v>
       </c>
       <c r="B571" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7696,7 +7702,7 @@
         <v>571</v>
       </c>
       <c r="B572" s="1">
-        <v>880</v>
+        <v>920</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7704,7 +7710,7 @@
         <v>572</v>
       </c>
       <c r="B573" s="1">
-        <v>640</v>
+        <v>600</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7712,7 +7718,7 @@
         <v>573</v>
       </c>
       <c r="B574" s="1">
-        <v>700</v>
+        <v>880</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7720,7 +7726,7 @@
         <v>574</v>
       </c>
       <c r="B575" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7728,7 +7734,7 @@
         <v>575</v>
       </c>
       <c r="B576" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7736,7 +7742,7 @@
         <v>576</v>
       </c>
       <c r="B577" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7744,7 +7750,7 @@
         <v>577</v>
       </c>
       <c r="B578" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7752,7 +7758,7 @@
         <v>578</v>
       </c>
       <c r="B579" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7760,7 +7766,7 @@
         <v>579</v>
       </c>
       <c r="B580" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7768,7 +7774,7 @@
         <v>580</v>
       </c>
       <c r="B581" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7776,7 +7782,7 @@
         <v>581</v>
       </c>
       <c r="B582" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7784,7 +7790,7 @@
         <v>582</v>
       </c>
       <c r="B583" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7792,7 +7798,7 @@
         <v>583</v>
       </c>
       <c r="B584" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7800,7 +7806,7 @@
         <v>584</v>
       </c>
       <c r="B585" s="1">
-        <v>1040</v>
+        <v>960</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7808,7 +7814,7 @@
         <v>585</v>
       </c>
       <c r="B586" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7816,7 +7822,7 @@
         <v>586</v>
       </c>
       <c r="B587" s="1">
-        <v>940</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7824,7 +7830,7 @@
         <v>587</v>
       </c>
       <c r="B588" s="1">
-        <v>860</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7832,7 +7838,7 @@
         <v>588</v>
       </c>
       <c r="B589" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7840,7 +7846,7 @@
         <v>589</v>
       </c>
       <c r="B590" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7848,7 +7854,7 @@
         <v>590</v>
       </c>
       <c r="B591" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7856,7 +7862,7 @@
         <v>591</v>
       </c>
       <c r="B592" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7864,7 +7870,7 @@
         <v>592</v>
       </c>
       <c r="B593" s="1">
-        <v>840</v>
+        <v>960</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7872,7 +7878,7 @@
         <v>593</v>
       </c>
       <c r="B594" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7880,7 +7886,7 @@
         <v>594</v>
       </c>
       <c r="B595" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7888,7 +7894,7 @@
         <v>595</v>
       </c>
       <c r="B596" s="1">
-        <v>580</v>
+        <v>780</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7896,7 +7902,7 @@
         <v>596</v>
       </c>
       <c r="B597" s="1">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7904,7 +7910,7 @@
         <v>597</v>
       </c>
       <c r="B598" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7912,7 +7918,7 @@
         <v>598</v>
       </c>
       <c r="B599" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7920,7 +7926,7 @@
         <v>599</v>
       </c>
       <c r="B600" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7928,7 +7934,7 @@
         <v>600</v>
       </c>
       <c r="B601" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7936,7 +7942,7 @@
         <v>601</v>
       </c>
       <c r="B602" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7944,7 +7950,7 @@
         <v>602</v>
       </c>
       <c r="B603" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7952,7 +7958,7 @@
         <v>603</v>
       </c>
       <c r="B604" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7960,7 +7966,7 @@
         <v>604</v>
       </c>
       <c r="B605" s="1">
-        <v>600</v>
+        <v>960</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7968,7 +7974,7 @@
         <v>605</v>
       </c>
       <c r="B606" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7976,7 +7982,7 @@
         <v>606</v>
       </c>
       <c r="B607" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7984,7 +7990,7 @@
         <v>607</v>
       </c>
       <c r="B608" s="1">
-        <v>540</v>
+        <v>720</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7992,7 +7998,7 @@
         <v>608</v>
       </c>
       <c r="B609" s="1">
-        <v>980</v>
+        <v>780</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -8000,7 +8006,7 @@
         <v>609</v>
       </c>
       <c r="B610" s="1">
-        <v>1100</v>
+        <v>540</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -8008,7 +8014,7 @@
         <v>610</v>
       </c>
       <c r="B611" s="1">
-        <v>1060</v>
+        <v>980</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -8016,7 +8022,7 @@
         <v>611</v>
       </c>
       <c r="B612" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -8024,7 +8030,7 @@
         <v>612</v>
       </c>
       <c r="B613" s="1">
-        <v>1100</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -8032,7 +8038,7 @@
         <v>613</v>
       </c>
       <c r="B614" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -8040,7 +8046,7 @@
         <v>614</v>
       </c>
       <c r="B615" s="1">
-        <v>1080</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -8048,7 +8054,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -8056,7 +8062,7 @@
         <v>616</v>
       </c>
       <c r="B617" s="1">
-        <v>840</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -8064,7 +8070,7 @@
         <v>617</v>
       </c>
       <c r="B618" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -8072,7 +8078,7 @@
         <v>618</v>
       </c>
       <c r="B619" s="1">
-        <v>560</v>
+        <v>840</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -8080,7 +8086,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -8088,7 +8094,7 @@
         <v>620</v>
       </c>
       <c r="B621" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -8096,7 +8102,7 @@
         <v>621</v>
       </c>
       <c r="B622" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -8104,7 +8110,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="1">
-        <v>980</v>
+        <v>620</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -8112,7 +8118,7 @@
         <v>623</v>
       </c>
       <c r="B624" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -8120,7 +8126,7 @@
         <v>624</v>
       </c>
       <c r="B625" s="1">
-        <v>760</v>
+        <v>980</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -8128,7 +8134,7 @@
         <v>625</v>
       </c>
       <c r="B626" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -8136,7 +8142,7 @@
         <v>626</v>
       </c>
       <c r="B627" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -8152,7 +8158,7 @@
         <v>628</v>
       </c>
       <c r="B629" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -8160,7 +8166,7 @@
         <v>629</v>
       </c>
       <c r="B630" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -8176,7 +8182,7 @@
         <v>631</v>
       </c>
       <c r="B632" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -8184,7 +8190,7 @@
         <v>632</v>
       </c>
       <c r="B633" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -8192,7 +8198,7 @@
         <v>633</v>
       </c>
       <c r="B634" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -8200,7 +8206,7 @@
         <v>634</v>
       </c>
       <c r="B635" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -8208,7 +8214,7 @@
         <v>635</v>
       </c>
       <c r="B636" s="1">
-        <v>700</v>
+        <v>960</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -8216,7 +8222,7 @@
         <v>636</v>
       </c>
       <c r="B637" s="1">
-        <v>980</v>
+        <v>840</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -8224,7 +8230,7 @@
         <v>637</v>
       </c>
       <c r="B638" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -8232,7 +8238,7 @@
         <v>638</v>
       </c>
       <c r="B639" s="1">
-        <v>800</v>
+        <v>980</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -8240,7 +8246,7 @@
         <v>639</v>
       </c>
       <c r="B640" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -8248,7 +8254,7 @@
         <v>640</v>
       </c>
       <c r="B641" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -8264,7 +8270,7 @@
         <v>642</v>
       </c>
       <c r="B643" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -8272,7 +8278,7 @@
         <v>643</v>
       </c>
       <c r="B644" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -8288,7 +8294,7 @@
         <v>645</v>
       </c>
       <c r="B646" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -8296,7 +8302,7 @@
         <v>646</v>
       </c>
       <c r="B647" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -8304,7 +8310,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="1">
-        <v>820</v>
+        <v>860</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -8312,7 +8318,7 @@
         <v>648</v>
       </c>
       <c r="B649" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -8320,7 +8326,7 @@
         <v>649</v>
       </c>
       <c r="B650" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -8328,7 +8334,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="1">
-        <v>1400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -8344,7 +8350,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="1">
-        <v>660</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -8352,7 +8358,7 @@
         <v>653</v>
       </c>
       <c r="B654" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -8360,7 +8366,7 @@
         <v>654</v>
       </c>
       <c r="B655" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -8368,7 +8374,7 @@
         <v>655</v>
       </c>
       <c r="B656" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -8376,7 +8382,7 @@
         <v>656</v>
       </c>
       <c r="B657" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -8384,7 +8390,7 @@
         <v>657</v>
       </c>
       <c r="B658" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -8392,7 +8398,7 @@
         <v>658</v>
       </c>
       <c r="B659" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -8400,7 +8406,7 @@
         <v>659</v>
       </c>
       <c r="B660" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -8416,7 +8422,7 @@
         <v>661</v>
       </c>
       <c r="B662" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -8424,7 +8430,7 @@
         <v>662</v>
       </c>
       <c r="B663" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -8432,7 +8438,7 @@
         <v>663</v>
       </c>
       <c r="B664" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -8440,7 +8446,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="1">
-        <v>980</v>
+        <v>720</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -8448,7 +8454,7 @@
         <v>665</v>
       </c>
       <c r="B666" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -8456,7 +8462,7 @@
         <v>666</v>
       </c>
       <c r="B667" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -8464,7 +8470,7 @@
         <v>667</v>
       </c>
       <c r="B668" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -8480,7 +8486,7 @@
         <v>669</v>
       </c>
       <c r="B670" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -8488,7 +8494,7 @@
         <v>670</v>
       </c>
       <c r="B671" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -8496,7 +8502,7 @@
         <v>671</v>
       </c>
       <c r="B672" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -8504,7 +8510,7 @@
         <v>672</v>
       </c>
       <c r="B673" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -8512,7 +8518,7 @@
         <v>673</v>
       </c>
       <c r="B674" s="1">
-        <v>4000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -8520,7 +8526,7 @@
         <v>674</v>
       </c>
       <c r="B675" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8528,7 +8534,7 @@
         <v>675</v>
       </c>
       <c r="B676" s="1">
-        <v>720</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -8536,7 +8542,7 @@
         <v>676</v>
       </c>
       <c r="B677" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8544,7 +8550,7 @@
         <v>677</v>
       </c>
       <c r="B678" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8552,7 +8558,7 @@
         <v>678</v>
       </c>
       <c r="B679" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8560,7 +8566,7 @@
         <v>679</v>
       </c>
       <c r="B680" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8568,7 +8574,7 @@
         <v>680</v>
       </c>
       <c r="B681" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8576,7 +8582,7 @@
         <v>681</v>
       </c>
       <c r="B682" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8584,7 +8590,7 @@
         <v>682</v>
       </c>
       <c r="B683" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8592,7 +8598,7 @@
         <v>683</v>
       </c>
       <c r="B684" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8600,7 +8606,7 @@
         <v>684</v>
       </c>
       <c r="B685" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8608,7 +8614,7 @@
         <v>685</v>
       </c>
       <c r="B686" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8616,7 +8622,7 @@
         <v>686</v>
       </c>
       <c r="B687" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8632,7 +8638,7 @@
         <v>688</v>
       </c>
       <c r="B689" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8648,7 +8654,7 @@
         <v>690</v>
       </c>
       <c r="B691" s="1">
-        <v>980</v>
+        <v>900</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8656,7 +8662,7 @@
         <v>691</v>
       </c>
       <c r="B692" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8664,7 +8670,7 @@
         <v>692</v>
       </c>
       <c r="B693" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8672,7 +8678,7 @@
         <v>693</v>
       </c>
       <c r="B694" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8680,7 +8686,7 @@
         <v>694</v>
       </c>
       <c r="B695" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8688,7 +8694,7 @@
         <v>695</v>
       </c>
       <c r="B696" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8696,7 +8702,7 @@
         <v>696</v>
       </c>
       <c r="B697" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8704,7 +8710,7 @@
         <v>697</v>
       </c>
       <c r="B698" s="1">
-        <v>860</v>
+        <v>680</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8720,7 +8726,7 @@
         <v>699</v>
       </c>
       <c r="B700" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8736,7 +8742,7 @@
         <v>701</v>
       </c>
       <c r="B702" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8744,7 +8750,7 @@
         <v>702</v>
       </c>
       <c r="B703" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8752,7 +8758,7 @@
         <v>703</v>
       </c>
       <c r="B704" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8760,7 +8766,7 @@
         <v>704</v>
       </c>
       <c r="B705" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8768,7 +8774,7 @@
         <v>705</v>
       </c>
       <c r="B706" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8776,7 +8782,7 @@
         <v>706</v>
       </c>
       <c r="B707" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8784,7 +8790,7 @@
         <v>707</v>
       </c>
       <c r="B708" s="1">
-        <v>840</v>
+        <v>800</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8792,7 +8798,7 @@
         <v>708</v>
       </c>
       <c r="B709" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8800,7 +8806,7 @@
         <v>709</v>
       </c>
       <c r="B710" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8808,7 +8814,7 @@
         <v>710</v>
       </c>
       <c r="B711" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8816,7 +8822,7 @@
         <v>711</v>
       </c>
       <c r="B712" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8832,7 +8838,7 @@
         <v>713</v>
       </c>
       <c r="B714" s="1">
-        <v>880</v>
+        <v>640</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8840,7 +8846,7 @@
         <v>714</v>
       </c>
       <c r="B715" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8848,7 +8854,7 @@
         <v>715</v>
       </c>
       <c r="B716" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8856,7 +8862,7 @@
         <v>716</v>
       </c>
       <c r="B717" s="1">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8864,7 +8870,7 @@
         <v>717</v>
       </c>
       <c r="B718" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8880,7 +8886,7 @@
         <v>719</v>
       </c>
       <c r="B720" s="1">
-        <v>800</v>
+        <v>820</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8888,7 +8894,7 @@
         <v>720</v>
       </c>
       <c r="B721" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8904,7 +8910,7 @@
         <v>722</v>
       </c>
       <c r="B723" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8912,7 +8918,7 @@
         <v>723</v>
       </c>
       <c r="B724" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8920,7 +8926,7 @@
         <v>724</v>
       </c>
       <c r="B725" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8928,7 +8934,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8936,7 +8942,7 @@
         <v>726</v>
       </c>
       <c r="B727" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8944,7 +8950,7 @@
         <v>727</v>
       </c>
       <c r="B728" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8952,7 +8958,7 @@
         <v>728</v>
       </c>
       <c r="B729" s="1">
-        <v>880</v>
+        <v>960</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8960,7 +8966,7 @@
         <v>729</v>
       </c>
       <c r="B730" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8968,7 +8974,7 @@
         <v>730</v>
       </c>
       <c r="B731" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8976,7 +8982,7 @@
         <v>731</v>
       </c>
       <c r="B732" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -8984,7 +8990,7 @@
         <v>732</v>
       </c>
       <c r="B733" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -8992,7 +8998,7 @@
         <v>733</v>
       </c>
       <c r="B734" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -9000,7 +9006,7 @@
         <v>734</v>
       </c>
       <c r="B735" s="1">
-        <v>1020</v>
+        <v>640</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -9016,7 +9022,7 @@
         <v>736</v>
       </c>
       <c r="B737" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -9024,7 +9030,7 @@
         <v>737</v>
       </c>
       <c r="B738" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="739" spans="1:2">
@@ -9032,7 +9038,7 @@
         <v>738</v>
       </c>
       <c r="B739" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="740" spans="1:2">
@@ -9040,7 +9046,7 @@
         <v>739</v>
       </c>
       <c r="B740" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -9048,7 +9054,7 @@
         <v>740</v>
       </c>
       <c r="B741" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="742" spans="1:2">
@@ -9056,7 +9062,7 @@
         <v>741</v>
       </c>
       <c r="B742" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -9064,7 +9070,7 @@
         <v>742</v>
       </c>
       <c r="B743" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="744" spans="1:2">
@@ -9080,7 +9086,7 @@
         <v>744</v>
       </c>
       <c r="B745" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -9088,7 +9094,7 @@
         <v>745</v>
       </c>
       <c r="B746" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="747" spans="1:2">
@@ -9096,7 +9102,7 @@
         <v>746</v>
       </c>
       <c r="B747" s="1">
-        <v>680</v>
+        <v>820</v>
       </c>
     </row>
     <row r="748" spans="1:2">
@@ -9104,7 +9110,7 @@
         <v>747</v>
       </c>
       <c r="B748" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="749" spans="1:2">
@@ -9112,7 +9118,7 @@
         <v>748</v>
       </c>
       <c r="B749" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -9120,7 +9126,7 @@
         <v>749</v>
       </c>
       <c r="B750" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="751" spans="1:2">
@@ -9128,7 +9134,7 @@
         <v>750</v>
       </c>
       <c r="B751" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="752" spans="1:2">
@@ -9136,7 +9142,7 @@
         <v>751</v>
       </c>
       <c r="B752" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="753" spans="1:2">
@@ -9152,7 +9158,7 @@
         <v>753</v>
       </c>
       <c r="B754" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -9160,7 +9166,7 @@
         <v>754</v>
       </c>
       <c r="B755" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="756" spans="1:2">
@@ -9168,7 +9174,7 @@
         <v>755</v>
       </c>
       <c r="B756" s="1">
-        <v>1100</v>
+        <v>840</v>
       </c>
     </row>
     <row r="757" spans="1:2">
@@ -9176,7 +9182,7 @@
         <v>756</v>
       </c>
       <c r="B757" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="758" spans="1:2">
@@ -9184,7 +9190,7 @@
         <v>757</v>
       </c>
       <c r="B758" s="1">
-        <v>940</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="759" spans="1:2">
@@ -9192,7 +9198,7 @@
         <v>758</v>
       </c>
       <c r="B759" s="1">
-        <v>820</v>
+        <v>940</v>
       </c>
     </row>
     <row r="760" spans="1:2">
@@ -9200,7 +9206,7 @@
         <v>759</v>
       </c>
       <c r="B760" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="761" spans="1:2">
@@ -9208,7 +9214,7 @@
         <v>760</v>
       </c>
       <c r="B761" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="762" spans="1:2">
@@ -9216,7 +9222,7 @@
         <v>761</v>
       </c>
       <c r="B762" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="763" spans="1:2">
@@ -9224,7 +9230,7 @@
         <v>762</v>
       </c>
       <c r="B763" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="764" spans="1:2">
@@ -9232,7 +9238,7 @@
         <v>763</v>
       </c>
       <c r="B764" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="765" spans="1:2">
@@ -9240,7 +9246,7 @@
         <v>764</v>
       </c>
       <c r="B765" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="766" spans="1:2">
@@ -9248,7 +9254,7 @@
         <v>765</v>
       </c>
       <c r="B766" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="767" spans="1:2">
@@ -9264,7 +9270,7 @@
         <v>767</v>
       </c>
       <c r="B768" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="769" spans="1:2">
@@ -9272,7 +9278,7 @@
         <v>768</v>
       </c>
       <c r="B769" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="770" spans="1:2">
@@ -9280,7 +9286,7 @@
         <v>769</v>
       </c>
       <c r="B770" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="771" spans="1:2">
@@ -9288,7 +9294,7 @@
         <v>770</v>
       </c>
       <c r="B771" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="772" spans="1:2">
@@ -9296,7 +9302,7 @@
         <v>771</v>
       </c>
       <c r="B772" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="773" spans="1:2">
@@ -9304,7 +9310,7 @@
         <v>772</v>
       </c>
       <c r="B773" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="774" spans="1:2">
@@ -9320,7 +9326,7 @@
         <v>774</v>
       </c>
       <c r="B775" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="776" spans="1:2">
@@ -9328,7 +9334,7 @@
         <v>775</v>
       </c>
       <c r="B776" s="1">
-        <v>440</v>
+        <v>900</v>
       </c>
     </row>
     <row r="777" spans="1:2">
@@ -9336,7 +9342,7 @@
         <v>776</v>
       </c>
       <c r="B777" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="778" spans="1:2">
@@ -9344,7 +9350,7 @@
         <v>777</v>
       </c>
       <c r="B778" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="779" spans="1:2">
@@ -9352,7 +9358,7 @@
         <v>778</v>
       </c>
       <c r="B779" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="780" spans="1:2">
@@ -9360,7 +9366,7 @@
         <v>779</v>
       </c>
       <c r="B780" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="781" spans="1:2">
@@ -9368,7 +9374,7 @@
         <v>780</v>
       </c>
       <c r="B781" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="782" spans="1:2">
@@ -9376,7 +9382,7 @@
         <v>781</v>
       </c>
       <c r="B782" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="783" spans="1:2">
@@ -9384,7 +9390,7 @@
         <v>782</v>
       </c>
       <c r="B783" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="784" spans="1:2">
@@ -9392,7 +9398,7 @@
         <v>783</v>
       </c>
       <c r="B784" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="785" spans="1:2">
@@ -9400,7 +9406,7 @@
         <v>784</v>
       </c>
       <c r="B785" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="786" spans="1:2">
@@ -9408,7 +9414,7 @@
         <v>785</v>
       </c>
       <c r="B786" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="787" spans="1:2">
@@ -9416,7 +9422,7 @@
         <v>786</v>
       </c>
       <c r="B787" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="788" spans="1:2">
@@ -9432,7 +9438,7 @@
         <v>788</v>
       </c>
       <c r="B789" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="790" spans="1:2">
@@ -9440,7 +9446,7 @@
         <v>789</v>
       </c>
       <c r="B790" s="1">
-        <v>920</v>
+        <v>880</v>
       </c>
     </row>
     <row r="791" spans="1:2">
@@ -9448,7 +9454,7 @@
         <v>790</v>
       </c>
       <c r="B791" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="792" spans="1:2">
@@ -9456,7 +9462,7 @@
         <v>791</v>
       </c>
       <c r="B792" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="793" spans="1:2">
@@ -9464,7 +9470,7 @@
         <v>792</v>
       </c>
       <c r="B793" s="1">
-        <v>980</v>
+        <v>800</v>
       </c>
     </row>
     <row r="794" spans="1:2">
@@ -9472,7 +9478,7 @@
         <v>793</v>
       </c>
       <c r="B794" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="795" spans="1:2">
@@ -9480,7 +9486,7 @@
         <v>794</v>
       </c>
       <c r="B795" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="796" spans="1:2">
@@ -9488,7 +9494,7 @@
         <v>795</v>
       </c>
       <c r="B796" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="797" spans="1:2">
@@ -9496,7 +9502,7 @@
         <v>796</v>
       </c>
       <c r="B797" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="798" spans="1:2">
@@ -9504,7 +9510,7 @@
         <v>797</v>
       </c>
       <c r="B798" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="799" spans="1:2">
@@ -9512,7 +9518,7 @@
         <v>798</v>
       </c>
       <c r="B799" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="800" spans="1:2">
@@ -9520,7 +9526,7 @@
         <v>799</v>
       </c>
       <c r="B800" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="801" spans="1:2">
@@ -9528,7 +9534,7 @@
         <v>800</v>
       </c>
       <c r="B801" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="802" spans="1:2">
@@ -9536,7 +9542,7 @@
         <v>801</v>
       </c>
       <c r="B802" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="803" spans="1:2">
@@ -9544,7 +9550,7 @@
         <v>802</v>
       </c>
       <c r="B803" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="804" spans="1:2">
@@ -9552,7 +9558,7 @@
         <v>803</v>
       </c>
       <c r="B804" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="805" spans="1:2">
@@ -9560,7 +9566,7 @@
         <v>804</v>
       </c>
       <c r="B805" s="1">
-        <v>660</v>
+        <v>860</v>
       </c>
     </row>
     <row r="806" spans="1:2">
@@ -9568,7 +9574,7 @@
         <v>805</v>
       </c>
       <c r="B806" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="807" spans="1:2">
@@ -9576,7 +9582,7 @@
         <v>806</v>
       </c>
       <c r="B807" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="808" spans="1:2">
@@ -9584,7 +9590,7 @@
         <v>807</v>
       </c>
       <c r="B808" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="809" spans="1:2">
@@ -9592,7 +9598,7 @@
         <v>808</v>
       </c>
       <c r="B809" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="810" spans="1:2">
@@ -9600,7 +9606,7 @@
         <v>809</v>
       </c>
       <c r="B810" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="811" spans="1:2">
@@ -9608,7 +9614,7 @@
         <v>810</v>
       </c>
       <c r="B811" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="812" spans="1:2">
@@ -9616,7 +9622,7 @@
         <v>811</v>
       </c>
       <c r="B812" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="813" spans="1:2">
@@ -9624,7 +9630,7 @@
         <v>812</v>
       </c>
       <c r="B813" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="814" spans="1:2">
@@ -9632,7 +9638,7 @@
         <v>813</v>
       </c>
       <c r="B814" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="815" spans="1:2">
@@ -9640,7 +9646,7 @@
         <v>814</v>
       </c>
       <c r="B815" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="816" spans="1:2">
@@ -9648,7 +9654,7 @@
         <v>815</v>
       </c>
       <c r="B816" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="817" spans="1:2">
@@ -9656,7 +9662,7 @@
         <v>816</v>
       </c>
       <c r="B817" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="818" spans="1:2">
@@ -9664,7 +9670,7 @@
         <v>817</v>
       </c>
       <c r="B818" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="819" spans="1:2">
@@ -9672,7 +9678,7 @@
         <v>818</v>
       </c>
       <c r="B819" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="820" spans="1:2">
@@ -9680,7 +9686,7 @@
         <v>819</v>
       </c>
       <c r="B820" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="821" spans="1:2">
@@ -9688,7 +9694,7 @@
         <v>820</v>
       </c>
       <c r="B821" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="822" spans="1:2">
@@ -9696,7 +9702,7 @@
         <v>821</v>
       </c>
       <c r="B822" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="823" spans="1:2">
@@ -9704,7 +9710,7 @@
         <v>822</v>
       </c>
       <c r="B823" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="824" spans="1:2">
@@ -9712,7 +9718,7 @@
         <v>823</v>
       </c>
       <c r="B824" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="825" spans="1:2">
@@ -9720,7 +9726,7 @@
         <v>824</v>
       </c>
       <c r="B825" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="826" spans="1:2">
@@ -9728,7 +9734,7 @@
         <v>825</v>
       </c>
       <c r="B826" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="827" spans="1:2">
@@ -9736,7 +9742,7 @@
         <v>826</v>
       </c>
       <c r="B827" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="828" spans="1:2">
@@ -9744,7 +9750,7 @@
         <v>827</v>
       </c>
       <c r="B828" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="829" spans="1:2">
@@ -9752,7 +9758,7 @@
         <v>828</v>
       </c>
       <c r="B829" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="830" spans="1:2">
@@ -9760,7 +9766,7 @@
         <v>829</v>
       </c>
       <c r="B830" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="831" spans="1:2">
@@ -9768,7 +9774,7 @@
         <v>830</v>
       </c>
       <c r="B831" s="1">
-        <v>920</v>
+        <v>500</v>
       </c>
     </row>
     <row r="832" spans="1:2">
@@ -9776,7 +9782,7 @@
         <v>831</v>
       </c>
       <c r="B832" s="1">
-        <v>1000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="833" spans="1:2">
@@ -9784,7 +9790,7 @@
         <v>832</v>
       </c>
       <c r="B833" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="834" spans="1:2">
@@ -9792,7 +9798,7 @@
         <v>833</v>
       </c>
       <c r="B834" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="835" spans="1:2">
@@ -9808,7 +9814,7 @@
         <v>835</v>
       </c>
       <c r="B836" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="837" spans="1:2">
@@ -9816,7 +9822,7 @@
         <v>836</v>
       </c>
       <c r="B837" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="838" spans="1:2">
@@ -9824,7 +9830,7 @@
         <v>837</v>
       </c>
       <c r="B838" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="839" spans="1:2">
@@ -9832,7 +9838,7 @@
         <v>838</v>
       </c>
       <c r="B839" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="840" spans="1:2">
@@ -9840,7 +9846,7 @@
         <v>839</v>
       </c>
       <c r="B840" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="841" spans="1:2">
@@ -9848,7 +9854,7 @@
         <v>840</v>
       </c>
       <c r="B841" s="1">
-        <v>960</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="842" spans="1:2">
@@ -9856,7 +9862,7 @@
         <v>841</v>
       </c>
       <c r="B842" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="843" spans="1:2">
@@ -9864,7 +9870,7 @@
         <v>842</v>
       </c>
       <c r="B843" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="844" spans="1:2">
@@ -9872,7 +9878,7 @@
         <v>843</v>
       </c>
       <c r="B844" s="1">
-        <v>820</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="845" spans="1:2">
@@ -9880,7 +9886,7 @@
         <v>844</v>
       </c>
       <c r="B845" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="846" spans="1:2">
@@ -9888,7 +9894,7 @@
         <v>845</v>
       </c>
       <c r="B846" s="1">
-        <v>500</v>
+        <v>820</v>
       </c>
     </row>
     <row r="847" spans="1:2">
@@ -9904,7 +9910,7 @@
         <v>847</v>
       </c>
       <c r="B848" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="849" spans="1:2">
@@ -9912,7 +9918,7 @@
         <v>848</v>
       </c>
       <c r="B849" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="850" spans="1:2">
@@ -9920,7 +9926,7 @@
         <v>849</v>
       </c>
       <c r="B850" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="851" spans="1:2">
@@ -9928,7 +9934,7 @@
         <v>850</v>
       </c>
       <c r="B851" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="852" spans="1:2">
@@ -9936,7 +9942,7 @@
         <v>851</v>
       </c>
       <c r="B852" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="853" spans="1:2">
@@ -9944,7 +9950,7 @@
         <v>852</v>
       </c>
       <c r="B853" s="1">
-        <v>840</v>
+        <v>820</v>
       </c>
     </row>
     <row r="854" spans="1:2">
@@ -9952,7 +9958,7 @@
         <v>853</v>
       </c>
       <c r="B854" s="1">
-        <v>400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="855" spans="1:2">
@@ -9960,7 +9966,7 @@
         <v>854</v>
       </c>
       <c r="B855" s="1">
-        <v>400</v>
+        <v>840</v>
       </c>
     </row>
     <row r="856" spans="1:2">
@@ -9968,7 +9974,7 @@
         <v>855</v>
       </c>
       <c r="B856" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="857" spans="1:2">
@@ -9976,7 +9982,7 @@
         <v>856</v>
       </c>
       <c r="B857" s="1">
-        <v>840</v>
+        <v>400</v>
       </c>
     </row>
     <row r="858" spans="1:2">
@@ -9992,7 +9998,7 @@
         <v>858</v>
       </c>
       <c r="B859" s="1">
-        <v>380</v>
+        <v>840</v>
       </c>
     </row>
     <row r="860" spans="1:2">
@@ -10000,7 +10006,7 @@
         <v>859</v>
       </c>
       <c r="B860" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="861" spans="1:2">
@@ -10008,7 +10014,7 @@
         <v>860</v>
       </c>
       <c r="B861" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="862" spans="1:2">
@@ -10016,7 +10022,7 @@
         <v>861</v>
       </c>
       <c r="B862" s="1">
-        <v>800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="863" spans="1:2">
@@ -10024,7 +10030,7 @@
         <v>862</v>
       </c>
       <c r="B863" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="864" spans="1:2">
@@ -10032,7 +10038,7 @@
         <v>863</v>
       </c>
       <c r="B864" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="865" spans="1:2">
@@ -10040,7 +10046,7 @@
         <v>864</v>
       </c>
       <c r="B865" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="866" spans="1:2">
@@ -10048,7 +10054,7 @@
         <v>865</v>
       </c>
       <c r="B866" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="867" spans="1:2">
@@ -10056,7 +10062,7 @@
         <v>866</v>
       </c>
       <c r="B867" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="868" spans="1:2">
@@ -10064,7 +10070,7 @@
         <v>867</v>
       </c>
       <c r="B868" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="869" spans="1:2">
@@ -10072,7 +10078,7 @@
         <v>868</v>
       </c>
       <c r="B869" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="870" spans="1:2">
@@ -10080,7 +10086,7 @@
         <v>869</v>
       </c>
       <c r="B870" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="871" spans="1:2">
@@ -10088,7 +10094,7 @@
         <v>870</v>
       </c>
       <c r="B871" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="872" spans="1:2">
@@ -10096,7 +10102,7 @@
         <v>871</v>
       </c>
       <c r="B872" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="873" spans="1:2">
@@ -10104,7 +10110,7 @@
         <v>872</v>
       </c>
       <c r="B873" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="874" spans="1:2">
@@ -10112,7 +10118,7 @@
         <v>873</v>
       </c>
       <c r="B874" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="875" spans="1:2">
@@ -10120,7 +10126,7 @@
         <v>874</v>
       </c>
       <c r="B875" s="1">
-        <v>840</v>
+        <v>500</v>
       </c>
     </row>
     <row r="876" spans="1:2">
@@ -10128,7 +10134,7 @@
         <v>875</v>
       </c>
       <c r="B876" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="877" spans="1:2">
@@ -10136,7 +10142,7 @@
         <v>876</v>
       </c>
       <c r="B877" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="878" spans="1:2">
@@ -10144,7 +10150,7 @@
         <v>877</v>
       </c>
       <c r="B878" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="879" spans="1:2">
@@ -10152,7 +10158,7 @@
         <v>878</v>
       </c>
       <c r="B879" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="880" spans="1:2">
@@ -10160,7 +10166,7 @@
         <v>879</v>
       </c>
       <c r="B880" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="881" spans="1:2">
@@ -10168,7 +10174,7 @@
         <v>880</v>
       </c>
       <c r="B881" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="882" spans="1:2">
@@ -10184,7 +10190,7 @@
         <v>882</v>
       </c>
       <c r="B883" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="884" spans="1:2">
@@ -10192,7 +10198,7 @@
         <v>883</v>
       </c>
       <c r="B884" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="885" spans="1:2">
@@ -10200,7 +10206,7 @@
         <v>884</v>
       </c>
       <c r="B885" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="886" spans="1:2">
@@ -10208,7 +10214,7 @@
         <v>885</v>
       </c>
       <c r="B886" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="887" spans="1:2">
@@ -10216,7 +10222,7 @@
         <v>886</v>
       </c>
       <c r="B887" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="888" spans="1:2">
@@ -10224,7 +10230,7 @@
         <v>887</v>
       </c>
       <c r="B888" s="1">
-        <v>960</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="889" spans="1:2">
@@ -10232,7 +10238,7 @@
         <v>888</v>
       </c>
       <c r="B889" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="890" spans="1:2">
@@ -10240,7 +10246,7 @@
         <v>889</v>
       </c>
       <c r="B890" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="891" spans="1:2">
@@ -10248,7 +10254,7 @@
         <v>890</v>
       </c>
       <c r="B891" s="1">
-        <v>820</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="892" spans="1:2">
@@ -10256,7 +10262,7 @@
         <v>891</v>
       </c>
       <c r="B892" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="893" spans="1:2">
@@ -10264,7 +10270,7 @@
         <v>892</v>
       </c>
       <c r="B893" s="1">
-        <v>500</v>
+        <v>820</v>
       </c>
     </row>
     <row r="894" spans="1:2">
@@ -10280,7 +10286,7 @@
         <v>894</v>
       </c>
       <c r="B895" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="896" spans="1:2">
@@ -10288,7 +10294,7 @@
         <v>895</v>
       </c>
       <c r="B896" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="897" spans="1:2">
@@ -10296,7 +10302,7 @@
         <v>896</v>
       </c>
       <c r="B897" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="898" spans="1:2">
@@ -10304,7 +10310,7 @@
         <v>897</v>
       </c>
       <c r="B898" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="899" spans="1:2">
@@ -10312,7 +10318,7 @@
         <v>898</v>
       </c>
       <c r="B899" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="900" spans="1:2">
@@ -10328,7 +10334,7 @@
         <v>900</v>
       </c>
       <c r="B901" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="902" spans="1:2">
@@ -10336,7 +10342,7 @@
         <v>901</v>
       </c>
       <c r="B902" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="903" spans="1:2">
@@ -10352,7 +10358,7 @@
         <v>903</v>
       </c>
       <c r="B904" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="905" spans="1:2">
@@ -10360,7 +10366,7 @@
         <v>904</v>
       </c>
       <c r="B905" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="906" spans="1:2">
@@ -10368,7 +10374,7 @@
         <v>905</v>
       </c>
       <c r="B906" s="1">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="907" spans="1:2">
@@ -10376,7 +10382,7 @@
         <v>906</v>
       </c>
       <c r="B907" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="908" spans="1:2">
@@ -10384,7 +10390,7 @@
         <v>907</v>
       </c>
       <c r="B908" s="1">
-        <v>600</v>
+        <v>440</v>
       </c>
     </row>
     <row r="909" spans="1:2">
@@ -10392,7 +10398,7 @@
         <v>908</v>
       </c>
       <c r="B909" s="1">
-        <v>820</v>
+        <v>380</v>
       </c>
     </row>
     <row r="910" spans="1:2">
@@ -10400,7 +10406,7 @@
         <v>909</v>
       </c>
       <c r="B910" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="911" spans="1:2">
@@ -10408,7 +10414,7 @@
         <v>910</v>
       </c>
       <c r="B911" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="912" spans="1:2">
@@ -10416,7 +10422,7 @@
         <v>911</v>
       </c>
       <c r="B912" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="913" spans="1:2">
@@ -10432,7 +10438,7 @@
         <v>913</v>
       </c>
       <c r="B914" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="915" spans="1:2">
@@ -10440,7 +10446,7 @@
         <v>914</v>
       </c>
       <c r="B915" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="916" spans="1:2">
@@ -10448,6 +10454,22 @@
         <v>915</v>
       </c>
       <c r="B916" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="917" spans="1:2">
+      <c r="A917" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="B917" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="918" spans="1:2">
+      <c r="A918" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="B918" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="923">
   <si>
     <t>Наименование</t>
   </si>
@@ -152,9 +152,6 @@
     <t>Big Village - Big Kid's Toy (Sour), РОЗЛИВ, Россия</t>
   </si>
   <si>
-    <t>Big Village - Crossroad (WC Pils), РОЗЛИВ, Россия</t>
-  </si>
-  <si>
     <t>Big Village - Good Company Inc. (Hoppy Pils), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -218,6 +215,9 @@
     <t>Big Village - Притяжение (WC IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Big Village - Субботний вечер (Black IPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Big Village - Холодный ЦКТ Эля (Cold IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -818,7 +818,7 @@
     <t>Plan B - Murquell Pilsner (Pils), РОЗЛИВ, Россия</t>
   </si>
   <si>
-    <t>Plan B - Rare Bird (Session IPA), РОЗЛИВ, Россия</t>
+    <t>Plan B - Rare Bird (Mosaic/Motueka) (Session IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>Plan B - Rise Of The Zombies (APA), РОЗЛИВ, Россия</t>
@@ -998,6 +998,9 @@
     <t>Saliwa - Михалыч (DIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Saliwa - НАБЛЮДАТЕЛЬ (HBC 638 + CITRA) (IPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Saliwa - НИГИЛИСТ (NEDIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1682,6 +1685,9 @@
     <t>вынос_Big Village - Притяжение (WC IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Big Village - Субботний вечер (Black IPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Big Village - Холодный ЦКТ Эля (Cold IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -2009,7 +2015,7 @@
     <t>вынос_Plan B - Murquell Pilsner (Pils), РОЗЛИВ, Россия</t>
   </si>
   <si>
-    <t>вынос_Plan B - Rare Bird (Session IPA), РОЗЛИВ, Россия</t>
+    <t>вынос_Plan B - Rare Bird (Mosaic/Motueka) (Session IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_Plan B - Rise Of The Zombies (APA), РОЗЛИВ, Россия</t>
@@ -2306,6 +2312,9 @@
     <t>вынос_Verhaeghe - BARBE RUBY (Fruit Beer), РОЗЛИВ, Бельгия</t>
   </si>
   <si>
+    <t xml:space="preserve">вынос_Vostok Brouwerij - Savior (Сухой Сидр), РОЗЛИВ, Россия </t>
+  </si>
+  <si>
     <t>вынос_White Stone  - The Great Eight (DIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -2555,6 +2564,9 @@
     <t>вынос_Петр Петрович - Harbinger of Spring (American Lager), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Петр Петрович - Sprezzatura (Italian Pilsner), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Преснявары - Munich Helles , РОЗЛИВ</t>
   </si>
   <si>
@@ -2694,6 +2706,9 @@
   </si>
   <si>
     <t>Петр Петрович - Harbinger of Spring (American Lager), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>Петр Петрович - Sprezzatura (Italian Pilsner), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>Преснявары - Munich Helles , РОЗЛИВ</t>
@@ -3122,7 +3137,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B918"/>
+  <dimension ref="A1:B923"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -3486,7 +3501,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3494,7 +3509,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3502,7 +3517,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3510,7 +3525,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -3518,7 +3533,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>880</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -3526,7 +3541,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>1060</v>
+        <v>720</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -3534,7 +3549,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -3550,7 +3565,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>860</v>
+        <v>800</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -3558,7 +3573,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>800</v>
+        <v>860</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -3566,7 +3581,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>860</v>
+        <v>960</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -3574,7 +3589,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>960</v>
+        <v>480</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -3582,7 +3597,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>480</v>
+        <v>760</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -3590,7 +3605,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -3598,7 +3613,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -3606,7 +3621,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -3622,7 +3637,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>900</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -3630,7 +3645,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>1100</v>
+        <v>980</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -3638,7 +3653,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>980</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -3646,7 +3661,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -3654,7 +3669,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -5270,7 +5285,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -5750,7 +5765,7 @@
         <v>327</v>
       </c>
       <c r="B328" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5758,7 +5773,7 @@
         <v>328</v>
       </c>
       <c r="B329" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5766,7 +5781,7 @@
         <v>329</v>
       </c>
       <c r="B330" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5774,7 +5789,7 @@
         <v>330</v>
       </c>
       <c r="B331" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5782,7 +5797,7 @@
         <v>331</v>
       </c>
       <c r="B332" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5790,7 +5805,7 @@
         <v>332</v>
       </c>
       <c r="B333" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5798,7 +5813,7 @@
         <v>333</v>
       </c>
       <c r="B334" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5806,7 +5821,7 @@
         <v>334</v>
       </c>
       <c r="B335" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5814,7 +5829,7 @@
         <v>335</v>
       </c>
       <c r="B336" s="1">
-        <v>520</v>
+        <v>680</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5822,7 +5837,7 @@
         <v>336</v>
       </c>
       <c r="B337" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5830,7 +5845,7 @@
         <v>337</v>
       </c>
       <c r="B338" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5838,7 +5853,7 @@
         <v>338</v>
       </c>
       <c r="B339" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5846,7 +5861,7 @@
         <v>339</v>
       </c>
       <c r="B340" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5854,7 +5869,7 @@
         <v>340</v>
       </c>
       <c r="B341" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5862,7 +5877,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="1">
-        <v>580</v>
+        <v>840</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5870,7 +5885,7 @@
         <v>342</v>
       </c>
       <c r="B343" s="1">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5878,7 +5893,7 @@
         <v>343</v>
       </c>
       <c r="B344" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5886,7 +5901,7 @@
         <v>344</v>
       </c>
       <c r="B345" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5894,7 +5909,7 @@
         <v>345</v>
       </c>
       <c r="B346" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5902,7 +5917,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5910,7 +5925,7 @@
         <v>347</v>
       </c>
       <c r="B348" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5918,7 +5933,7 @@
         <v>348</v>
       </c>
       <c r="B349" s="1">
-        <v>1000</v>
+        <v>880</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5926,7 +5941,7 @@
         <v>349</v>
       </c>
       <c r="B350" s="1">
-        <v>520</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5934,7 +5949,7 @@
         <v>350</v>
       </c>
       <c r="B351" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5942,7 +5957,7 @@
         <v>351</v>
       </c>
       <c r="B352" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5950,7 +5965,7 @@
         <v>352</v>
       </c>
       <c r="B353" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5958,7 +5973,7 @@
         <v>353</v>
       </c>
       <c r="B354" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5966,7 +5981,7 @@
         <v>354</v>
       </c>
       <c r="B355" s="1">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5974,7 +5989,7 @@
         <v>355</v>
       </c>
       <c r="B356" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5982,7 +5997,7 @@
         <v>356</v>
       </c>
       <c r="B357" s="1">
-        <v>320</v>
+        <v>520</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5990,7 +6005,7 @@
         <v>357</v>
       </c>
       <c r="B358" s="1">
-        <v>540</v>
+        <v>320</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5998,7 +6013,7 @@
         <v>358</v>
       </c>
       <c r="B359" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -6006,7 +6021,7 @@
         <v>359</v>
       </c>
       <c r="B360" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -6022,7 +6037,7 @@
         <v>361</v>
       </c>
       <c r="B362" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -6030,7 +6045,7 @@
         <v>362</v>
       </c>
       <c r="B363" s="1">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -6038,7 +6053,7 @@
         <v>363</v>
       </c>
       <c r="B364" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -6046,7 +6061,7 @@
         <v>364</v>
       </c>
       <c r="B365" s="1">
-        <v>480</v>
+        <v>800</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -6054,7 +6069,7 @@
         <v>365</v>
       </c>
       <c r="B366" s="1">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -6062,7 +6077,7 @@
         <v>366</v>
       </c>
       <c r="B367" s="1">
-        <v>520</v>
+        <v>800</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -6070,7 +6085,7 @@
         <v>367</v>
       </c>
       <c r="B368" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -6078,7 +6093,7 @@
         <v>368</v>
       </c>
       <c r="B369" s="1">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -6086,7 +6101,7 @@
         <v>369</v>
       </c>
       <c r="B370" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -6102,7 +6117,7 @@
         <v>371</v>
       </c>
       <c r="B372" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -6118,7 +6133,7 @@
         <v>373</v>
       </c>
       <c r="B374" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -6126,7 +6141,7 @@
         <v>374</v>
       </c>
       <c r="B375" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -6134,7 +6149,7 @@
         <v>375</v>
       </c>
       <c r="B376" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -6142,7 +6157,7 @@
         <v>376</v>
       </c>
       <c r="B377" s="1">
-        <v>880</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -6150,7 +6165,7 @@
         <v>377</v>
       </c>
       <c r="B378" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -6158,7 +6173,7 @@
         <v>378</v>
       </c>
       <c r="B379" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -6166,7 +6181,7 @@
         <v>379</v>
       </c>
       <c r="B380" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -6174,7 +6189,7 @@
         <v>380</v>
       </c>
       <c r="B381" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -6182,7 +6197,7 @@
         <v>381</v>
       </c>
       <c r="B382" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -6190,7 +6205,7 @@
         <v>382</v>
       </c>
       <c r="B383" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -6198,7 +6213,7 @@
         <v>383</v>
       </c>
       <c r="B384" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -6206,7 +6221,7 @@
         <v>384</v>
       </c>
       <c r="B385" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -6222,7 +6237,7 @@
         <v>386</v>
       </c>
       <c r="B387" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -6238,7 +6253,7 @@
         <v>388</v>
       </c>
       <c r="B389" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -6246,7 +6261,7 @@
         <v>389</v>
       </c>
       <c r="B390" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -6254,7 +6269,7 @@
         <v>390</v>
       </c>
       <c r="B391" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -6262,7 +6277,7 @@
         <v>391</v>
       </c>
       <c r="B392" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -6270,7 +6285,7 @@
         <v>392</v>
       </c>
       <c r="B393" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -6278,7 +6293,7 @@
         <v>393</v>
       </c>
       <c r="B394" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -6286,7 +6301,7 @@
         <v>394</v>
       </c>
       <c r="B395" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -6294,7 +6309,7 @@
         <v>395</v>
       </c>
       <c r="B396" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -6302,7 +6317,7 @@
         <v>396</v>
       </c>
       <c r="B397" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -6310,7 +6325,7 @@
         <v>397</v>
       </c>
       <c r="B398" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -6318,7 +6333,7 @@
         <v>398</v>
       </c>
       <c r="B399" s="1">
-        <v>640</v>
+        <v>480</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -6326,7 +6341,7 @@
         <v>399</v>
       </c>
       <c r="B400" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -6334,7 +6349,7 @@
         <v>400</v>
       </c>
       <c r="B401" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -6342,7 +6357,7 @@
         <v>401</v>
       </c>
       <c r="B402" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -6350,7 +6365,7 @@
         <v>402</v>
       </c>
       <c r="B403" s="1">
-        <v>520</v>
+        <v>860</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -6358,7 +6373,7 @@
         <v>403</v>
       </c>
       <c r="B404" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -6366,7 +6381,7 @@
         <v>404</v>
       </c>
       <c r="B405" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -6382,7 +6397,7 @@
         <v>406</v>
       </c>
       <c r="B407" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -6390,7 +6405,7 @@
         <v>407</v>
       </c>
       <c r="B408" s="1">
-        <v>700</v>
+        <v>420</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -6398,7 +6413,7 @@
         <v>408</v>
       </c>
       <c r="B409" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -6406,7 +6421,7 @@
         <v>409</v>
       </c>
       <c r="B410" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -6414,7 +6429,7 @@
         <v>410</v>
       </c>
       <c r="B411" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -6422,7 +6437,7 @@
         <v>411</v>
       </c>
       <c r="B412" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -6430,7 +6445,7 @@
         <v>412</v>
       </c>
       <c r="B413" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -6438,7 +6453,7 @@
         <v>413</v>
       </c>
       <c r="B414" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -6446,7 +6461,7 @@
         <v>414</v>
       </c>
       <c r="B415" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -6454,7 +6469,7 @@
         <v>415</v>
       </c>
       <c r="B416" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -6462,7 +6477,7 @@
         <v>416</v>
       </c>
       <c r="B417" s="1">
-        <v>440</v>
+        <v>620</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -6470,7 +6485,7 @@
         <v>417</v>
       </c>
       <c r="B418" s="1">
-        <v>1100</v>
+        <v>440</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -6486,7 +6501,7 @@
         <v>419</v>
       </c>
       <c r="B420" s="1">
-        <v>320</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -6494,7 +6509,7 @@
         <v>420</v>
       </c>
       <c r="B421" s="1">
-        <v>940</v>
+        <v>320</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -6502,7 +6517,7 @@
         <v>421</v>
       </c>
       <c r="B422" s="1">
-        <v>320</v>
+        <v>940</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -6510,7 +6525,7 @@
         <v>422</v>
       </c>
       <c r="B423" s="1">
-        <v>960</v>
+        <v>320</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -6518,7 +6533,7 @@
         <v>423</v>
       </c>
       <c r="B424" s="1">
-        <v>820</v>
+        <v>960</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -6526,7 +6541,7 @@
         <v>424</v>
       </c>
       <c r="B425" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -6534,7 +6549,7 @@
         <v>425</v>
       </c>
       <c r="B426" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -6550,7 +6565,7 @@
         <v>427</v>
       </c>
       <c r="B428" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6566,7 +6581,7 @@
         <v>429</v>
       </c>
       <c r="B430" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6582,7 +6597,7 @@
         <v>431</v>
       </c>
       <c r="B432" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6590,7 +6605,7 @@
         <v>432</v>
       </c>
       <c r="B433" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6598,7 +6613,7 @@
         <v>433</v>
       </c>
       <c r="B434" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6606,7 +6621,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6614,7 +6629,7 @@
         <v>435</v>
       </c>
       <c r="B436" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6622,7 +6637,7 @@
         <v>436</v>
       </c>
       <c r="B437" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6630,7 +6645,7 @@
         <v>437</v>
       </c>
       <c r="B438" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6646,7 +6661,7 @@
         <v>439</v>
       </c>
       <c r="B440" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6654,7 +6669,7 @@
         <v>440</v>
       </c>
       <c r="B441" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6662,7 +6677,7 @@
         <v>441</v>
       </c>
       <c r="B442" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6670,7 +6685,7 @@
         <v>442</v>
       </c>
       <c r="B443" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6678,7 +6693,7 @@
         <v>443</v>
       </c>
       <c r="B444" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6686,7 +6701,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6694,7 +6709,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6702,7 +6717,7 @@
         <v>446</v>
       </c>
       <c r="B447" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6710,7 +6725,7 @@
         <v>447</v>
       </c>
       <c r="B448" s="1">
-        <v>700</v>
+        <v>440</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6718,7 +6733,7 @@
         <v>448</v>
       </c>
       <c r="B449" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6734,7 +6749,7 @@
         <v>450</v>
       </c>
       <c r="B451" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6742,7 +6757,7 @@
         <v>451</v>
       </c>
       <c r="B452" s="1">
-        <v>560</v>
+        <v>800</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6750,7 +6765,7 @@
         <v>452</v>
       </c>
       <c r="B453" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6758,7 +6773,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6766,7 +6781,7 @@
         <v>454</v>
       </c>
       <c r="B455" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6774,7 +6789,7 @@
         <v>455</v>
       </c>
       <c r="B456" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6782,7 +6797,7 @@
         <v>456</v>
       </c>
       <c r="B457" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6790,7 +6805,7 @@
         <v>457</v>
       </c>
       <c r="B458" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6798,7 +6813,7 @@
         <v>458</v>
       </c>
       <c r="B459" s="1">
-        <v>720</v>
+        <v>620</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6806,7 +6821,7 @@
         <v>459</v>
       </c>
       <c r="B460" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6814,7 +6829,7 @@
         <v>460</v>
       </c>
       <c r="B461" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6830,7 +6845,7 @@
         <v>462</v>
       </c>
       <c r="B463" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6838,7 +6853,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6846,7 +6861,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6854,7 +6869,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="1">
-        <v>900</v>
+        <v>880</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6862,7 +6877,7 @@
         <v>466</v>
       </c>
       <c r="B467" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6870,7 +6885,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6878,7 +6893,7 @@
         <v>468</v>
       </c>
       <c r="B469" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6886,7 +6901,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="1">
-        <v>800</v>
+        <v>920</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6894,7 +6909,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6902,7 +6917,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6910,7 +6925,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="1">
-        <v>980</v>
+        <v>940</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6918,7 +6933,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6926,7 +6941,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6934,7 +6949,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6942,7 +6957,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6950,7 +6965,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6966,7 +6981,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6974,7 +6989,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6982,7 +6997,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="1">
-        <v>640</v>
+        <v>920</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6990,7 +7005,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6998,7 +7013,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -7006,7 +7021,7 @@
         <v>484</v>
       </c>
       <c r="B485" s="1">
-        <v>960</v>
+        <v>820</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -7014,7 +7029,7 @@
         <v>485</v>
       </c>
       <c r="B486" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -7022,7 +7037,7 @@
         <v>486</v>
       </c>
       <c r="B487" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -7030,7 +7045,7 @@
         <v>487</v>
       </c>
       <c r="B488" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -7038,7 +7053,7 @@
         <v>488</v>
       </c>
       <c r="B489" s="1">
-        <v>860</v>
+        <v>640</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -7046,7 +7061,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -7054,7 +7069,7 @@
         <v>490</v>
       </c>
       <c r="B491" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -7062,7 +7077,7 @@
         <v>491</v>
       </c>
       <c r="B492" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -7070,7 +7085,7 @@
         <v>492</v>
       </c>
       <c r="B493" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -7078,7 +7093,7 @@
         <v>493</v>
       </c>
       <c r="B494" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -7086,7 +7101,7 @@
         <v>494</v>
       </c>
       <c r="B495" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -7094,7 +7109,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -7102,7 +7117,7 @@
         <v>496</v>
       </c>
       <c r="B497" s="1">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -7110,7 +7125,7 @@
         <v>497</v>
       </c>
       <c r="B498" s="1">
-        <v>620</v>
+        <v>480</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -7118,7 +7133,7 @@
         <v>498</v>
       </c>
       <c r="B499" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -7126,7 +7141,7 @@
         <v>499</v>
       </c>
       <c r="B500" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -7134,7 +7149,7 @@
         <v>500</v>
       </c>
       <c r="B501" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -7142,7 +7157,7 @@
         <v>501</v>
       </c>
       <c r="B502" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -7150,7 +7165,7 @@
         <v>502</v>
       </c>
       <c r="B503" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -7158,7 +7173,7 @@
         <v>503</v>
       </c>
       <c r="B504" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -7166,7 +7181,7 @@
         <v>504</v>
       </c>
       <c r="B505" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -7174,7 +7189,7 @@
         <v>505</v>
       </c>
       <c r="B506" s="1">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -7182,7 +7197,7 @@
         <v>506</v>
       </c>
       <c r="B507" s="1">
-        <v>840</v>
+        <v>480</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -7190,7 +7205,7 @@
         <v>507</v>
       </c>
       <c r="B508" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -7198,7 +7213,7 @@
         <v>508</v>
       </c>
       <c r="B509" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -7206,7 +7221,7 @@
         <v>509</v>
       </c>
       <c r="B510" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -7222,7 +7237,7 @@
         <v>511</v>
       </c>
       <c r="B512" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -7230,7 +7245,7 @@
         <v>512</v>
       </c>
       <c r="B513" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -7238,7 +7253,7 @@
         <v>513</v>
       </c>
       <c r="B514" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -7246,7 +7261,7 @@
         <v>514</v>
       </c>
       <c r="B515" s="1">
-        <v>880</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -7262,7 +7277,7 @@
         <v>516</v>
       </c>
       <c r="B517" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -7270,7 +7285,7 @@
         <v>517</v>
       </c>
       <c r="B518" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -7278,7 +7293,7 @@
         <v>518</v>
       </c>
       <c r="B519" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -7286,7 +7301,7 @@
         <v>519</v>
       </c>
       <c r="B520" s="1">
-        <v>1100</v>
+        <v>660</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -7294,7 +7309,7 @@
         <v>520</v>
       </c>
       <c r="B521" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -7302,7 +7317,7 @@
         <v>521</v>
       </c>
       <c r="B522" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -7310,7 +7325,7 @@
         <v>522</v>
       </c>
       <c r="B523" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -7318,7 +7333,7 @@
         <v>523</v>
       </c>
       <c r="B524" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -7326,7 +7341,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -7342,7 +7357,7 @@
         <v>526</v>
       </c>
       <c r="B527" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -7350,7 +7365,7 @@
         <v>527</v>
       </c>
       <c r="B528" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -7358,7 +7373,7 @@
         <v>528</v>
       </c>
       <c r="B529" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -7366,7 +7381,7 @@
         <v>529</v>
       </c>
       <c r="B530" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -7374,7 +7389,7 @@
         <v>530</v>
       </c>
       <c r="B531" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -7382,7 +7397,7 @@
         <v>531</v>
       </c>
       <c r="B532" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -7398,7 +7413,7 @@
         <v>533</v>
       </c>
       <c r="B534" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -7406,7 +7421,7 @@
         <v>534</v>
       </c>
       <c r="B535" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -7414,7 +7429,7 @@
         <v>535</v>
       </c>
       <c r="B536" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -7422,7 +7437,7 @@
         <v>536</v>
       </c>
       <c r="B537" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -7430,7 +7445,7 @@
         <v>537</v>
       </c>
       <c r="B538" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -7438,7 +7453,7 @@
         <v>538</v>
       </c>
       <c r="B539" s="1">
-        <v>840</v>
+        <v>620</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -7446,7 +7461,7 @@
         <v>539</v>
       </c>
       <c r="B540" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -7454,7 +7469,7 @@
         <v>540</v>
       </c>
       <c r="B541" s="1">
-        <v>1060</v>
+        <v>880</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -7462,7 +7477,7 @@
         <v>541</v>
       </c>
       <c r="B542" s="1">
-        <v>860</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -7478,7 +7493,7 @@
         <v>543</v>
       </c>
       <c r="B544" s="1">
-        <v>800</v>
+        <v>860</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -7486,7 +7501,7 @@
         <v>544</v>
       </c>
       <c r="B545" s="1">
-        <v>860</v>
+        <v>800</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -7494,7 +7509,7 @@
         <v>545</v>
       </c>
       <c r="B546" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -7502,7 +7517,7 @@
         <v>546</v>
       </c>
       <c r="B547" s="1">
-        <v>760</v>
+        <v>960</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -7510,7 +7525,7 @@
         <v>547</v>
       </c>
       <c r="B548" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -7518,7 +7533,7 @@
         <v>548</v>
       </c>
       <c r="B549" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -7526,7 +7541,7 @@
         <v>549</v>
       </c>
       <c r="B550" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -7542,7 +7557,7 @@
         <v>551</v>
       </c>
       <c r="B552" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7550,7 +7565,7 @@
         <v>552</v>
       </c>
       <c r="B553" s="1">
-        <v>980</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7558,7 +7573,7 @@
         <v>553</v>
       </c>
       <c r="B554" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7566,7 +7581,7 @@
         <v>554</v>
       </c>
       <c r="B555" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7582,7 +7597,7 @@
         <v>556</v>
       </c>
       <c r="B557" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7590,7 +7605,7 @@
         <v>557</v>
       </c>
       <c r="B558" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7598,7 +7613,7 @@
         <v>558</v>
       </c>
       <c r="B559" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7614,7 +7629,7 @@
         <v>560</v>
       </c>
       <c r="B561" s="1">
-        <v>640</v>
+        <v>900</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7622,7 +7637,7 @@
         <v>561</v>
       </c>
       <c r="B562" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7630,7 +7645,7 @@
         <v>562</v>
       </c>
       <c r="B563" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7638,7 +7653,7 @@
         <v>563</v>
       </c>
       <c r="B564" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7646,7 +7661,7 @@
         <v>564</v>
       </c>
       <c r="B565" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7654,7 +7669,7 @@
         <v>565</v>
       </c>
       <c r="B566" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7662,7 +7677,7 @@
         <v>566</v>
       </c>
       <c r="B567" s="1">
-        <v>880</v>
+        <v>700</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7670,7 +7685,7 @@
         <v>567</v>
       </c>
       <c r="B568" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7678,7 +7693,7 @@
         <v>568</v>
       </c>
       <c r="B569" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7702,7 +7717,7 @@
         <v>571</v>
       </c>
       <c r="B572" s="1">
-        <v>920</v>
+        <v>820</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7710,7 +7725,7 @@
         <v>572</v>
       </c>
       <c r="B573" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7718,7 +7733,7 @@
         <v>573</v>
       </c>
       <c r="B574" s="1">
-        <v>880</v>
+        <v>920</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7726,7 +7741,7 @@
         <v>574</v>
       </c>
       <c r="B575" s="1">
-        <v>640</v>
+        <v>600</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7734,7 +7749,7 @@
         <v>575</v>
       </c>
       <c r="B576" s="1">
-        <v>700</v>
+        <v>880</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7742,7 +7757,7 @@
         <v>576</v>
       </c>
       <c r="B577" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7750,7 +7765,7 @@
         <v>577</v>
       </c>
       <c r="B578" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7758,7 +7773,7 @@
         <v>578</v>
       </c>
       <c r="B579" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7766,7 +7781,7 @@
         <v>579</v>
       </c>
       <c r="B580" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7774,7 +7789,7 @@
         <v>580</v>
       </c>
       <c r="B581" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7782,7 +7797,7 @@
         <v>581</v>
       </c>
       <c r="B582" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7790,7 +7805,7 @@
         <v>582</v>
       </c>
       <c r="B583" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7798,7 +7813,7 @@
         <v>583</v>
       </c>
       <c r="B584" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7806,7 +7821,7 @@
         <v>584</v>
       </c>
       <c r="B585" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7814,7 +7829,7 @@
         <v>585</v>
       </c>
       <c r="B586" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7822,7 +7837,7 @@
         <v>586</v>
       </c>
       <c r="B587" s="1">
-        <v>1040</v>
+        <v>960</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7830,7 +7845,7 @@
         <v>587</v>
       </c>
       <c r="B588" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7838,7 +7853,7 @@
         <v>588</v>
       </c>
       <c r="B589" s="1">
-        <v>940</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7846,7 +7861,7 @@
         <v>589</v>
       </c>
       <c r="B590" s="1">
-        <v>860</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7854,7 +7869,7 @@
         <v>590</v>
       </c>
       <c r="B591" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7862,7 +7877,7 @@
         <v>591</v>
       </c>
       <c r="B592" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7870,7 +7885,7 @@
         <v>592</v>
       </c>
       <c r="B593" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7878,7 +7893,7 @@
         <v>593</v>
       </c>
       <c r="B594" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7886,7 +7901,7 @@
         <v>594</v>
       </c>
       <c r="B595" s="1">
-        <v>840</v>
+        <v>960</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7894,7 +7909,7 @@
         <v>595</v>
       </c>
       <c r="B596" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7902,7 +7917,7 @@
         <v>596</v>
       </c>
       <c r="B597" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7910,7 +7925,7 @@
         <v>597</v>
       </c>
       <c r="B598" s="1">
-        <v>580</v>
+        <v>780</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7918,7 +7933,7 @@
         <v>598</v>
       </c>
       <c r="B599" s="1">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7926,7 +7941,7 @@
         <v>599</v>
       </c>
       <c r="B600" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7934,7 +7949,7 @@
         <v>600</v>
       </c>
       <c r="B601" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7942,7 +7957,7 @@
         <v>601</v>
       </c>
       <c r="B602" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7950,7 +7965,7 @@
         <v>602</v>
       </c>
       <c r="B603" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7958,7 +7973,7 @@
         <v>603</v>
       </c>
       <c r="B604" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7966,7 +7981,7 @@
         <v>604</v>
       </c>
       <c r="B605" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7974,7 +7989,7 @@
         <v>605</v>
       </c>
       <c r="B606" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7982,7 +7997,7 @@
         <v>606</v>
       </c>
       <c r="B607" s="1">
-        <v>600</v>
+        <v>960</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7990,7 +8005,7 @@
         <v>607</v>
       </c>
       <c r="B608" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7998,7 +8013,7 @@
         <v>608</v>
       </c>
       <c r="B609" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -8006,7 +8021,7 @@
         <v>609</v>
       </c>
       <c r="B610" s="1">
-        <v>540</v>
+        <v>720</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -8014,7 +8029,7 @@
         <v>610</v>
       </c>
       <c r="B611" s="1">
-        <v>980</v>
+        <v>780</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -8022,7 +8037,7 @@
         <v>611</v>
       </c>
       <c r="B612" s="1">
-        <v>1100</v>
+        <v>540</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -8030,7 +8045,7 @@
         <v>612</v>
       </c>
       <c r="B613" s="1">
-        <v>1060</v>
+        <v>980</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -8038,7 +8053,7 @@
         <v>613</v>
       </c>
       <c r="B614" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -8046,7 +8061,7 @@
         <v>614</v>
       </c>
       <c r="B615" s="1">
-        <v>1100</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -8054,7 +8069,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -8062,7 +8077,7 @@
         <v>616</v>
       </c>
       <c r="B617" s="1">
-        <v>1080</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -8070,7 +8085,7 @@
         <v>617</v>
       </c>
       <c r="B618" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -8078,7 +8093,7 @@
         <v>618</v>
       </c>
       <c r="B619" s="1">
-        <v>840</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -8086,7 +8101,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -8094,7 +8109,7 @@
         <v>620</v>
       </c>
       <c r="B621" s="1">
-        <v>560</v>
+        <v>840</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -8102,7 +8117,7 @@
         <v>621</v>
       </c>
       <c r="B622" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -8110,7 +8125,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -8118,7 +8133,7 @@
         <v>623</v>
       </c>
       <c r="B624" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -8126,7 +8141,7 @@
         <v>624</v>
       </c>
       <c r="B625" s="1">
-        <v>980</v>
+        <v>620</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -8134,7 +8149,7 @@
         <v>625</v>
       </c>
       <c r="B626" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -8142,7 +8157,7 @@
         <v>626</v>
       </c>
       <c r="B627" s="1">
-        <v>760</v>
+        <v>980</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -8150,7 +8165,7 @@
         <v>627</v>
       </c>
       <c r="B628" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -8158,7 +8173,7 @@
         <v>628</v>
       </c>
       <c r="B629" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -8174,7 +8189,7 @@
         <v>630</v>
       </c>
       <c r="B631" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -8182,7 +8197,7 @@
         <v>631</v>
       </c>
       <c r="B632" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -8198,7 +8213,7 @@
         <v>633</v>
       </c>
       <c r="B634" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -8206,7 +8221,7 @@
         <v>634</v>
       </c>
       <c r="B635" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -8214,7 +8229,7 @@
         <v>635</v>
       </c>
       <c r="B636" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -8222,7 +8237,7 @@
         <v>636</v>
       </c>
       <c r="B637" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -8230,7 +8245,7 @@
         <v>637</v>
       </c>
       <c r="B638" s="1">
-        <v>700</v>
+        <v>960</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -8238,7 +8253,7 @@
         <v>638</v>
       </c>
       <c r="B639" s="1">
-        <v>980</v>
+        <v>840</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -8246,7 +8261,7 @@
         <v>639</v>
       </c>
       <c r="B640" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -8254,7 +8269,7 @@
         <v>640</v>
       </c>
       <c r="B641" s="1">
-        <v>800</v>
+        <v>980</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -8262,7 +8277,7 @@
         <v>641</v>
       </c>
       <c r="B642" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -8270,7 +8285,7 @@
         <v>642</v>
       </c>
       <c r="B643" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -8286,7 +8301,7 @@
         <v>644</v>
       </c>
       <c r="B645" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -8294,7 +8309,7 @@
         <v>645</v>
       </c>
       <c r="B646" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -8310,7 +8325,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -8318,7 +8333,7 @@
         <v>648</v>
       </c>
       <c r="B649" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -8326,7 +8341,7 @@
         <v>649</v>
       </c>
       <c r="B650" s="1">
-        <v>820</v>
+        <v>860</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -8334,7 +8349,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -8342,7 +8357,7 @@
         <v>651</v>
       </c>
       <c r="B652" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -8350,7 +8365,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="1">
-        <v>1400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -8366,7 +8381,7 @@
         <v>654</v>
       </c>
       <c r="B655" s="1">
-        <v>660</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -8374,7 +8389,7 @@
         <v>655</v>
       </c>
       <c r="B656" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -8382,7 +8397,7 @@
         <v>656</v>
       </c>
       <c r="B657" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -8390,7 +8405,7 @@
         <v>657</v>
       </c>
       <c r="B658" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -8398,7 +8413,7 @@
         <v>658</v>
       </c>
       <c r="B659" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -8406,7 +8421,7 @@
         <v>659</v>
       </c>
       <c r="B660" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -8414,7 +8429,7 @@
         <v>660</v>
       </c>
       <c r="B661" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -8422,7 +8437,7 @@
         <v>661</v>
       </c>
       <c r="B662" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -8438,7 +8453,7 @@
         <v>663</v>
       </c>
       <c r="B664" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -8446,7 +8461,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -8454,7 +8469,7 @@
         <v>665</v>
       </c>
       <c r="B666" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -8462,7 +8477,7 @@
         <v>666</v>
       </c>
       <c r="B667" s="1">
-        <v>980</v>
+        <v>840</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -8470,7 +8485,7 @@
         <v>667</v>
       </c>
       <c r="B668" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -8478,7 +8493,7 @@
         <v>668</v>
       </c>
       <c r="B669" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -8486,7 +8501,7 @@
         <v>669</v>
       </c>
       <c r="B670" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -8502,7 +8517,7 @@
         <v>671</v>
       </c>
       <c r="B672" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -8510,7 +8525,7 @@
         <v>672</v>
       </c>
       <c r="B673" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -8518,7 +8533,7 @@
         <v>673</v>
       </c>
       <c r="B674" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -8526,7 +8541,7 @@
         <v>674</v>
       </c>
       <c r="B675" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8534,7 +8549,7 @@
         <v>675</v>
       </c>
       <c r="B676" s="1">
-        <v>4000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -8542,7 +8557,7 @@
         <v>676</v>
       </c>
       <c r="B677" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8550,7 +8565,7 @@
         <v>677</v>
       </c>
       <c r="B678" s="1">
-        <v>720</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8558,7 +8573,7 @@
         <v>678</v>
       </c>
       <c r="B679" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8566,7 +8581,7 @@
         <v>679</v>
       </c>
       <c r="B680" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8574,7 +8589,7 @@
         <v>680</v>
       </c>
       <c r="B681" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8582,7 +8597,7 @@
         <v>681</v>
       </c>
       <c r="B682" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8590,7 +8605,7 @@
         <v>682</v>
       </c>
       <c r="B683" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8598,7 +8613,7 @@
         <v>683</v>
       </c>
       <c r="B684" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8606,7 +8621,7 @@
         <v>684</v>
       </c>
       <c r="B685" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8614,7 +8629,7 @@
         <v>685</v>
       </c>
       <c r="B686" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8622,7 +8637,7 @@
         <v>686</v>
       </c>
       <c r="B687" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8630,7 +8645,7 @@
         <v>687</v>
       </c>
       <c r="B688" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8638,7 +8653,7 @@
         <v>688</v>
       </c>
       <c r="B689" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8654,7 +8669,7 @@
         <v>690</v>
       </c>
       <c r="B691" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8670,7 +8685,7 @@
         <v>692</v>
       </c>
       <c r="B693" s="1">
-        <v>980</v>
+        <v>900</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8678,7 +8693,7 @@
         <v>693</v>
       </c>
       <c r="B694" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8686,7 +8701,7 @@
         <v>694</v>
       </c>
       <c r="B695" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8694,7 +8709,7 @@
         <v>695</v>
       </c>
       <c r="B696" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8702,7 +8717,7 @@
         <v>696</v>
       </c>
       <c r="B697" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8710,7 +8725,7 @@
         <v>697</v>
       </c>
       <c r="B698" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8718,7 +8733,7 @@
         <v>698</v>
       </c>
       <c r="B699" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8726,7 +8741,7 @@
         <v>699</v>
       </c>
       <c r="B700" s="1">
-        <v>860</v>
+        <v>680</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8742,7 +8757,7 @@
         <v>701</v>
       </c>
       <c r="B702" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8758,7 +8773,7 @@
         <v>703</v>
       </c>
       <c r="B704" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8766,7 +8781,7 @@
         <v>704</v>
       </c>
       <c r="B705" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8774,7 +8789,7 @@
         <v>705</v>
       </c>
       <c r="B706" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8782,7 +8797,7 @@
         <v>706</v>
       </c>
       <c r="B707" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8790,7 +8805,7 @@
         <v>707</v>
       </c>
       <c r="B708" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8798,7 +8813,7 @@
         <v>708</v>
       </c>
       <c r="B709" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8806,7 +8821,7 @@
         <v>709</v>
       </c>
       <c r="B710" s="1">
-        <v>840</v>
+        <v>800</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8814,7 +8829,7 @@
         <v>710</v>
       </c>
       <c r="B711" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8822,7 +8837,7 @@
         <v>711</v>
       </c>
       <c r="B712" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8830,7 +8845,7 @@
         <v>712</v>
       </c>
       <c r="B713" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8838,7 +8853,7 @@
         <v>713</v>
       </c>
       <c r="B714" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8854,7 +8869,7 @@
         <v>715</v>
       </c>
       <c r="B716" s="1">
-        <v>880</v>
+        <v>640</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8862,7 +8877,7 @@
         <v>716</v>
       </c>
       <c r="B717" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8870,7 +8885,7 @@
         <v>717</v>
       </c>
       <c r="B718" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8878,7 +8893,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="1">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8886,7 +8901,7 @@
         <v>719</v>
       </c>
       <c r="B720" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8902,7 +8917,7 @@
         <v>721</v>
       </c>
       <c r="B722" s="1">
-        <v>800</v>
+        <v>820</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8910,7 +8925,7 @@
         <v>722</v>
       </c>
       <c r="B723" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8926,7 +8941,7 @@
         <v>724</v>
       </c>
       <c r="B725" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8934,7 +8949,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8942,7 +8957,7 @@
         <v>726</v>
       </c>
       <c r="B727" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8950,7 +8965,7 @@
         <v>727</v>
       </c>
       <c r="B728" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8958,7 +8973,7 @@
         <v>728</v>
       </c>
       <c r="B729" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8966,7 +8981,7 @@
         <v>729</v>
       </c>
       <c r="B730" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8974,7 +8989,7 @@
         <v>730</v>
       </c>
       <c r="B731" s="1">
-        <v>880</v>
+        <v>960</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8982,7 +8997,7 @@
         <v>731</v>
       </c>
       <c r="B732" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -8990,7 +9005,7 @@
         <v>732</v>
       </c>
       <c r="B733" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -8998,7 +9013,7 @@
         <v>733</v>
       </c>
       <c r="B734" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -9006,7 +9021,7 @@
         <v>734</v>
       </c>
       <c r="B735" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -9014,7 +9029,7 @@
         <v>735</v>
       </c>
       <c r="B736" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -9022,7 +9037,7 @@
         <v>736</v>
       </c>
       <c r="B737" s="1">
-        <v>1020</v>
+        <v>640</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -9038,7 +9053,7 @@
         <v>738</v>
       </c>
       <c r="B739" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="740" spans="1:2">
@@ -9046,7 +9061,7 @@
         <v>739</v>
       </c>
       <c r="B740" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -9054,7 +9069,7 @@
         <v>740</v>
       </c>
       <c r="B741" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="742" spans="1:2">
@@ -9062,7 +9077,7 @@
         <v>741</v>
       </c>
       <c r="B742" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -9070,7 +9085,7 @@
         <v>742</v>
       </c>
       <c r="B743" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="744" spans="1:2">
@@ -9078,7 +9093,7 @@
         <v>743</v>
       </c>
       <c r="B744" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="745" spans="1:2">
@@ -9086,7 +9101,7 @@
         <v>744</v>
       </c>
       <c r="B745" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -9102,7 +9117,7 @@
         <v>746</v>
       </c>
       <c r="B747" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="748" spans="1:2">
@@ -9110,7 +9125,7 @@
         <v>747</v>
       </c>
       <c r="B748" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="749" spans="1:2">
@@ -9118,7 +9133,7 @@
         <v>748</v>
       </c>
       <c r="B749" s="1">
-        <v>680</v>
+        <v>820</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -9126,7 +9141,7 @@
         <v>749</v>
       </c>
       <c r="B750" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="751" spans="1:2">
@@ -9134,7 +9149,7 @@
         <v>750</v>
       </c>
       <c r="B751" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="752" spans="1:2">
@@ -9142,7 +9157,7 @@
         <v>751</v>
       </c>
       <c r="B752" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="753" spans="1:2">
@@ -9150,7 +9165,7 @@
         <v>752</v>
       </c>
       <c r="B753" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="754" spans="1:2">
@@ -9158,7 +9173,7 @@
         <v>753</v>
       </c>
       <c r="B754" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -9174,7 +9189,7 @@
         <v>755</v>
       </c>
       <c r="B756" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="757" spans="1:2">
@@ -9182,7 +9197,7 @@
         <v>756</v>
       </c>
       <c r="B757" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="758" spans="1:2">
@@ -9190,7 +9205,7 @@
         <v>757</v>
       </c>
       <c r="B758" s="1">
-        <v>1100</v>
+        <v>840</v>
       </c>
     </row>
     <row r="759" spans="1:2">
@@ -9198,7 +9213,7 @@
         <v>758</v>
       </c>
       <c r="B759" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="760" spans="1:2">
@@ -9206,7 +9221,7 @@
         <v>759</v>
       </c>
       <c r="B760" s="1">
-        <v>940</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="761" spans="1:2">
@@ -9214,7 +9229,7 @@
         <v>760</v>
       </c>
       <c r="B761" s="1">
-        <v>820</v>
+        <v>940</v>
       </c>
     </row>
     <row r="762" spans="1:2">
@@ -9222,7 +9237,7 @@
         <v>761</v>
       </c>
       <c r="B762" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="763" spans="1:2">
@@ -9230,7 +9245,7 @@
         <v>762</v>
       </c>
       <c r="B763" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="764" spans="1:2">
@@ -9238,7 +9253,7 @@
         <v>763</v>
       </c>
       <c r="B764" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="765" spans="1:2">
@@ -9246,7 +9261,7 @@
         <v>764</v>
       </c>
       <c r="B765" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="766" spans="1:2">
@@ -9254,7 +9269,7 @@
         <v>765</v>
       </c>
       <c r="B766" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="767" spans="1:2">
@@ -9262,7 +9277,7 @@
         <v>766</v>
       </c>
       <c r="B767" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="768" spans="1:2">
@@ -9270,7 +9285,7 @@
         <v>767</v>
       </c>
       <c r="B768" s="1">
-        <v>880</v>
+        <v>920</v>
       </c>
     </row>
     <row r="769" spans="1:2">
@@ -9278,7 +9293,7 @@
         <v>768</v>
       </c>
       <c r="B769" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="770" spans="1:2">
@@ -9294,7 +9309,7 @@
         <v>770</v>
       </c>
       <c r="B771" s="1">
-        <v>900</v>
+        <v>880</v>
       </c>
     </row>
     <row r="772" spans="1:2">
@@ -9302,7 +9317,7 @@
         <v>771</v>
       </c>
       <c r="B772" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="773" spans="1:2">
@@ -9310,7 +9325,7 @@
         <v>772</v>
       </c>
       <c r="B773" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="774" spans="1:2">
@@ -9326,7 +9341,7 @@
         <v>774</v>
       </c>
       <c r="B775" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="776" spans="1:2">
@@ -9334,7 +9349,7 @@
         <v>775</v>
       </c>
       <c r="B776" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="777" spans="1:2">
@@ -9342,7 +9357,7 @@
         <v>776</v>
       </c>
       <c r="B777" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="778" spans="1:2">
@@ -9350,7 +9365,7 @@
         <v>777</v>
       </c>
       <c r="B778" s="1">
-        <v>440</v>
+        <v>680</v>
       </c>
     </row>
     <row r="779" spans="1:2">
@@ -9358,7 +9373,7 @@
         <v>778</v>
       </c>
       <c r="B779" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="780" spans="1:2">
@@ -9366,7 +9381,7 @@
         <v>779</v>
       </c>
       <c r="B780" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="781" spans="1:2">
@@ -9374,7 +9389,7 @@
         <v>780</v>
       </c>
       <c r="B781" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="782" spans="1:2">
@@ -9382,7 +9397,7 @@
         <v>781</v>
       </c>
       <c r="B782" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="783" spans="1:2">
@@ -9390,7 +9405,7 @@
         <v>782</v>
       </c>
       <c r="B783" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="784" spans="1:2">
@@ -9398,7 +9413,7 @@
         <v>783</v>
       </c>
       <c r="B784" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="785" spans="1:2">
@@ -9406,7 +9421,7 @@
         <v>784</v>
       </c>
       <c r="B785" s="1">
-        <v>560</v>
+        <v>800</v>
       </c>
     </row>
     <row r="786" spans="1:2">
@@ -9414,7 +9429,7 @@
         <v>785</v>
       </c>
       <c r="B786" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="787" spans="1:2">
@@ -9422,7 +9437,7 @@
         <v>786</v>
       </c>
       <c r="B787" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="788" spans="1:2">
@@ -9430,7 +9445,7 @@
         <v>787</v>
       </c>
       <c r="B788" s="1">
-        <v>880</v>
+        <v>560</v>
       </c>
     </row>
     <row r="789" spans="1:2">
@@ -9438,7 +9453,7 @@
         <v>788</v>
       </c>
       <c r="B789" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="790" spans="1:2">
@@ -9446,7 +9461,7 @@
         <v>789</v>
       </c>
       <c r="B790" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="791" spans="1:2">
@@ -9454,7 +9469,7 @@
         <v>790</v>
       </c>
       <c r="B791" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="792" spans="1:2">
@@ -9462,7 +9477,7 @@
         <v>791</v>
       </c>
       <c r="B792" s="1">
-        <v>920</v>
+        <v>800</v>
       </c>
     </row>
     <row r="793" spans="1:2">
@@ -9470,7 +9485,7 @@
         <v>792</v>
       </c>
       <c r="B793" s="1">
-        <v>800</v>
+        <v>880</v>
       </c>
     </row>
     <row r="794" spans="1:2">
@@ -9478,7 +9493,7 @@
         <v>793</v>
       </c>
       <c r="B794" s="1">
-        <v>940</v>
+        <v>780</v>
       </c>
     </row>
     <row r="795" spans="1:2">
@@ -9486,7 +9501,7 @@
         <v>794</v>
       </c>
       <c r="B795" s="1">
-        <v>980</v>
+        <v>920</v>
       </c>
     </row>
     <row r="796" spans="1:2">
@@ -9494,7 +9509,7 @@
         <v>795</v>
       </c>
       <c r="B796" s="1">
-        <v>920</v>
+        <v>800</v>
       </c>
     </row>
     <row r="797" spans="1:2">
@@ -9502,7 +9517,7 @@
         <v>796</v>
       </c>
       <c r="B797" s="1">
-        <v>780</v>
+        <v>940</v>
       </c>
     </row>
     <row r="798" spans="1:2">
@@ -9510,7 +9525,7 @@
         <v>797</v>
       </c>
       <c r="B798" s="1">
-        <v>860</v>
+        <v>980</v>
       </c>
     </row>
     <row r="799" spans="1:2">
@@ -9526,7 +9541,7 @@
         <v>799</v>
       </c>
       <c r="B800" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="801" spans="1:2">
@@ -9534,7 +9549,7 @@
         <v>800</v>
       </c>
       <c r="B801" s="1">
-        <v>820</v>
+        <v>860</v>
       </c>
     </row>
     <row r="802" spans="1:2">
@@ -9542,7 +9557,7 @@
         <v>801</v>
       </c>
       <c r="B802" s="1">
-        <v>960</v>
+        <v>920</v>
       </c>
     </row>
     <row r="803" spans="1:2">
@@ -9550,7 +9565,7 @@
         <v>802</v>
       </c>
       <c r="B803" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="804" spans="1:2">
@@ -9558,7 +9573,7 @@
         <v>803</v>
       </c>
       <c r="B804" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="805" spans="1:2">
@@ -9566,7 +9581,7 @@
         <v>804</v>
       </c>
       <c r="B805" s="1">
-        <v>860</v>
+        <v>960</v>
       </c>
     </row>
     <row r="806" spans="1:2">
@@ -9574,7 +9589,7 @@
         <v>805</v>
       </c>
       <c r="B806" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="807" spans="1:2">
@@ -9582,7 +9597,7 @@
         <v>806</v>
       </c>
       <c r="B807" s="1">
-        <v>660</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="808" spans="1:2">
@@ -9590,7 +9605,7 @@
         <v>807</v>
       </c>
       <c r="B808" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="809" spans="1:2">
@@ -9606,7 +9621,7 @@
         <v>809</v>
       </c>
       <c r="B810" s="1">
-        <v>820</v>
+        <v>660</v>
       </c>
     </row>
     <row r="811" spans="1:2">
@@ -9614,7 +9629,7 @@
         <v>810</v>
       </c>
       <c r="B811" s="1">
-        <v>760</v>
+        <v>840</v>
       </c>
     </row>
     <row r="812" spans="1:2">
@@ -9622,7 +9637,7 @@
         <v>811</v>
       </c>
       <c r="B812" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="813" spans="1:2">
@@ -9630,7 +9645,7 @@
         <v>812</v>
       </c>
       <c r="B813" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="814" spans="1:2">
@@ -9638,7 +9653,7 @@
         <v>813</v>
       </c>
       <c r="B814" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="815" spans="1:2">
@@ -9646,7 +9661,7 @@
         <v>814</v>
       </c>
       <c r="B815" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="816" spans="1:2">
@@ -9654,7 +9669,7 @@
         <v>815</v>
       </c>
       <c r="B816" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="817" spans="1:2">
@@ -9662,7 +9677,7 @@
         <v>816</v>
       </c>
       <c r="B817" s="1">
-        <v>740</v>
+        <v>600</v>
       </c>
     </row>
     <row r="818" spans="1:2">
@@ -9670,7 +9685,7 @@
         <v>817</v>
       </c>
       <c r="B818" s="1">
-        <v>760</v>
+        <v>840</v>
       </c>
     </row>
     <row r="819" spans="1:2">
@@ -9678,7 +9693,7 @@
         <v>818</v>
       </c>
       <c r="B819" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="820" spans="1:2">
@@ -9686,7 +9701,7 @@
         <v>819</v>
       </c>
       <c r="B820" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="821" spans="1:2">
@@ -9694,7 +9709,7 @@
         <v>820</v>
       </c>
       <c r="B821" s="1">
-        <v>800</v>
+        <v>760</v>
       </c>
     </row>
     <row r="822" spans="1:2">
@@ -9702,7 +9717,7 @@
         <v>821</v>
       </c>
       <c r="B822" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="823" spans="1:2">
@@ -9710,7 +9725,7 @@
         <v>822</v>
       </c>
       <c r="B823" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="824" spans="1:2">
@@ -9718,7 +9733,7 @@
         <v>823</v>
       </c>
       <c r="B824" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="825" spans="1:2">
@@ -9726,7 +9741,7 @@
         <v>824</v>
       </c>
       <c r="B825" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="826" spans="1:2">
@@ -9734,7 +9749,7 @@
         <v>825</v>
       </c>
       <c r="B826" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="827" spans="1:2">
@@ -9742,7 +9757,7 @@
         <v>826</v>
       </c>
       <c r="B827" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="828" spans="1:2">
@@ -9750,7 +9765,7 @@
         <v>827</v>
       </c>
       <c r="B828" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="829" spans="1:2">
@@ -9758,7 +9773,7 @@
         <v>828</v>
       </c>
       <c r="B829" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="830" spans="1:2">
@@ -9766,7 +9781,7 @@
         <v>829</v>
       </c>
       <c r="B830" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="831" spans="1:2">
@@ -9774,7 +9789,7 @@
         <v>830</v>
       </c>
       <c r="B831" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="832" spans="1:2">
@@ -9782,7 +9797,7 @@
         <v>831</v>
       </c>
       <c r="B832" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="833" spans="1:2">
@@ -9790,7 +9805,7 @@
         <v>832</v>
       </c>
       <c r="B833" s="1">
-        <v>920</v>
+        <v>600</v>
       </c>
     </row>
     <row r="834" spans="1:2">
@@ -9798,7 +9813,7 @@
         <v>833</v>
       </c>
       <c r="B834" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="835" spans="1:2">
@@ -9806,7 +9821,7 @@
         <v>834</v>
       </c>
       <c r="B835" s="1">
-        <v>940</v>
+        <v>760</v>
       </c>
     </row>
     <row r="836" spans="1:2">
@@ -9814,7 +9829,7 @@
         <v>835</v>
       </c>
       <c r="B836" s="1">
-        <v>1040</v>
+        <v>920</v>
       </c>
     </row>
     <row r="837" spans="1:2">
@@ -9822,7 +9837,7 @@
         <v>836</v>
       </c>
       <c r="B837" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="838" spans="1:2">
@@ -9830,7 +9845,7 @@
         <v>837</v>
       </c>
       <c r="B838" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="839" spans="1:2">
@@ -9846,7 +9861,7 @@
         <v>839</v>
       </c>
       <c r="B840" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="841" spans="1:2">
@@ -9854,7 +9869,7 @@
         <v>840</v>
       </c>
       <c r="B841" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="842" spans="1:2">
@@ -9862,7 +9877,7 @@
         <v>841</v>
       </c>
       <c r="B842" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="843" spans="1:2">
@@ -9870,7 +9885,7 @@
         <v>842</v>
       </c>
       <c r="B843" s="1">
-        <v>960</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="844" spans="1:2">
@@ -9878,7 +9893,7 @@
         <v>843</v>
       </c>
       <c r="B844" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="845" spans="1:2">
@@ -9886,7 +9901,7 @@
         <v>844</v>
       </c>
       <c r="B845" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="846" spans="1:2">
@@ -9894,7 +9909,7 @@
         <v>845</v>
       </c>
       <c r="B846" s="1">
-        <v>820</v>
+        <v>960</v>
       </c>
     </row>
     <row r="847" spans="1:2">
@@ -9902,7 +9917,7 @@
         <v>846</v>
       </c>
       <c r="B847" s="1">
-        <v>440</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="848" spans="1:2">
@@ -9910,7 +9925,7 @@
         <v>847</v>
       </c>
       <c r="B848" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="849" spans="1:2">
@@ -9918,7 +9933,7 @@
         <v>848</v>
       </c>
       <c r="B849" s="1">
-        <v>440</v>
+        <v>820</v>
       </c>
     </row>
     <row r="850" spans="1:2">
@@ -9926,7 +9941,7 @@
         <v>849</v>
       </c>
       <c r="B850" s="1">
-        <v>560</v>
+        <v>840</v>
       </c>
     </row>
     <row r="851" spans="1:2">
@@ -9934,7 +9949,7 @@
         <v>850</v>
       </c>
       <c r="B851" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="852" spans="1:2">
@@ -9942,7 +9957,7 @@
         <v>851</v>
       </c>
       <c r="B852" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="853" spans="1:2">
@@ -9950,7 +9965,7 @@
         <v>852</v>
       </c>
       <c r="B853" s="1">
-        <v>820</v>
+        <v>440</v>
       </c>
     </row>
     <row r="854" spans="1:2">
@@ -9958,7 +9973,7 @@
         <v>853</v>
       </c>
       <c r="B854" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="855" spans="1:2">
@@ -9966,7 +9981,7 @@
         <v>854</v>
       </c>
       <c r="B855" s="1">
-        <v>840</v>
+        <v>500</v>
       </c>
     </row>
     <row r="856" spans="1:2">
@@ -9974,7 +9989,7 @@
         <v>855</v>
       </c>
       <c r="B856" s="1">
-        <v>400</v>
+        <v>820</v>
       </c>
     </row>
     <row r="857" spans="1:2">
@@ -9982,7 +9997,7 @@
         <v>856</v>
       </c>
       <c r="B857" s="1">
-        <v>400</v>
+        <v>820</v>
       </c>
     </row>
     <row r="858" spans="1:2">
@@ -9990,7 +10005,7 @@
         <v>857</v>
       </c>
       <c r="B858" s="1">
-        <v>380</v>
+        <v>760</v>
       </c>
     </row>
     <row r="859" spans="1:2">
@@ -10006,7 +10021,7 @@
         <v>859</v>
       </c>
       <c r="B860" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="861" spans="1:2">
@@ -10014,7 +10029,7 @@
         <v>860</v>
       </c>
       <c r="B861" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="862" spans="1:2">
@@ -10022,7 +10037,7 @@
         <v>861</v>
       </c>
       <c r="B862" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="863" spans="1:2">
@@ -10030,7 +10045,7 @@
         <v>862</v>
       </c>
       <c r="B863" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="864" spans="1:2">
@@ -10038,7 +10053,7 @@
         <v>863</v>
       </c>
       <c r="B864" s="1">
-        <v>800</v>
+        <v>380</v>
       </c>
     </row>
     <row r="865" spans="1:2">
@@ -10046,7 +10061,7 @@
         <v>864</v>
       </c>
       <c r="B865" s="1">
-        <v>860</v>
+        <v>380</v>
       </c>
     </row>
     <row r="866" spans="1:2">
@@ -10054,7 +10069,7 @@
         <v>865</v>
       </c>
       <c r="B866" s="1">
-        <v>680</v>
+        <v>520</v>
       </c>
     </row>
     <row r="867" spans="1:2">
@@ -10062,7 +10077,7 @@
         <v>866</v>
       </c>
       <c r="B867" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="868" spans="1:2">
@@ -10070,7 +10085,7 @@
         <v>867</v>
       </c>
       <c r="B868" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="869" spans="1:2">
@@ -10078,7 +10093,7 @@
         <v>868</v>
       </c>
       <c r="B869" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="870" spans="1:2">
@@ -10086,7 +10101,7 @@
         <v>869</v>
       </c>
       <c r="B870" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="871" spans="1:2">
@@ -10094,7 +10109,7 @@
         <v>870</v>
       </c>
       <c r="B871" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="872" spans="1:2">
@@ -10102,7 +10117,7 @@
         <v>871</v>
       </c>
       <c r="B872" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="873" spans="1:2">
@@ -10110,7 +10125,7 @@
         <v>872</v>
       </c>
       <c r="B873" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="874" spans="1:2">
@@ -10118,7 +10133,7 @@
         <v>873</v>
       </c>
       <c r="B874" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="875" spans="1:2">
@@ -10126,7 +10141,7 @@
         <v>874</v>
       </c>
       <c r="B875" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="876" spans="1:2">
@@ -10134,7 +10149,7 @@
         <v>875</v>
       </c>
       <c r="B876" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="877" spans="1:2">
@@ -10142,7 +10157,7 @@
         <v>876</v>
       </c>
       <c r="B877" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="878" spans="1:2">
@@ -10150,7 +10165,7 @@
         <v>877</v>
       </c>
       <c r="B878" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="879" spans="1:2">
@@ -10158,7 +10173,7 @@
         <v>878</v>
       </c>
       <c r="B879" s="1">
-        <v>900</v>
+        <v>500</v>
       </c>
     </row>
     <row r="880" spans="1:2">
@@ -10166,7 +10181,7 @@
         <v>879</v>
       </c>
       <c r="B880" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="881" spans="1:2">
@@ -10174,7 +10189,7 @@
         <v>880</v>
       </c>
       <c r="B881" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="882" spans="1:2">
@@ -10182,7 +10197,7 @@
         <v>881</v>
       </c>
       <c r="B882" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="883" spans="1:2">
@@ -10190,7 +10205,7 @@
         <v>882</v>
       </c>
       <c r="B883" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="884" spans="1:2">
@@ -10198,7 +10213,7 @@
         <v>883</v>
       </c>
       <c r="B884" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="885" spans="1:2">
@@ -10206,7 +10221,7 @@
         <v>884</v>
       </c>
       <c r="B885" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="886" spans="1:2">
@@ -10214,7 +10229,7 @@
         <v>885</v>
       </c>
       <c r="B886" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="887" spans="1:2">
@@ -10222,7 +10237,7 @@
         <v>886</v>
       </c>
       <c r="B887" s="1">
-        <v>1100</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="888" spans="1:2">
@@ -10230,7 +10245,7 @@
         <v>887</v>
       </c>
       <c r="B888" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="889" spans="1:2">
@@ -10238,7 +10253,7 @@
         <v>888</v>
       </c>
       <c r="B889" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="890" spans="1:2">
@@ -10246,7 +10261,7 @@
         <v>889</v>
       </c>
       <c r="B890" s="1">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="891" spans="1:2">
@@ -10262,7 +10277,7 @@
         <v>891</v>
       </c>
       <c r="B892" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="893" spans="1:2">
@@ -10270,7 +10285,7 @@
         <v>892</v>
       </c>
       <c r="B893" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="894" spans="1:2">
@@ -10278,7 +10293,7 @@
         <v>893</v>
       </c>
       <c r="B894" s="1">
-        <v>440</v>
+        <v>960</v>
       </c>
     </row>
     <row r="895" spans="1:2">
@@ -10286,7 +10301,7 @@
         <v>894</v>
       </c>
       <c r="B895" s="1">
-        <v>500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="896" spans="1:2">
@@ -10294,7 +10309,7 @@
         <v>895</v>
       </c>
       <c r="B896" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="897" spans="1:2">
@@ -10302,7 +10317,7 @@
         <v>896</v>
       </c>
       <c r="B897" s="1">
-        <v>560</v>
+        <v>820</v>
       </c>
     </row>
     <row r="898" spans="1:2">
@@ -10310,7 +10325,7 @@
         <v>897</v>
       </c>
       <c r="B898" s="1">
-        <v>500</v>
+        <v>840</v>
       </c>
     </row>
     <row r="899" spans="1:2">
@@ -10318,7 +10333,7 @@
         <v>898</v>
       </c>
       <c r="B899" s="1">
-        <v>820</v>
+        <v>440</v>
       </c>
     </row>
     <row r="900" spans="1:2">
@@ -10326,7 +10341,7 @@
         <v>899</v>
       </c>
       <c r="B900" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="901" spans="1:2">
@@ -10334,7 +10349,7 @@
         <v>900</v>
       </c>
       <c r="B901" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="902" spans="1:2">
@@ -10342,7 +10357,7 @@
         <v>901</v>
       </c>
       <c r="B902" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="903" spans="1:2">
@@ -10350,7 +10365,7 @@
         <v>902</v>
       </c>
       <c r="B903" s="1">
-        <v>480</v>
+        <v>500</v>
       </c>
     </row>
     <row r="904" spans="1:2">
@@ -10358,7 +10373,7 @@
         <v>903</v>
       </c>
       <c r="B904" s="1">
-        <v>480</v>
+        <v>820</v>
       </c>
     </row>
     <row r="905" spans="1:2">
@@ -10366,7 +10381,7 @@
         <v>904</v>
       </c>
       <c r="B905" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="906" spans="1:2">
@@ -10374,7 +10389,7 @@
         <v>905</v>
       </c>
       <c r="B906" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="907" spans="1:2">
@@ -10382,7 +10397,7 @@
         <v>906</v>
       </c>
       <c r="B907" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="908" spans="1:2">
@@ -10390,7 +10405,7 @@
         <v>907</v>
       </c>
       <c r="B908" s="1">
-        <v>440</v>
+        <v>480</v>
       </c>
     </row>
     <row r="909" spans="1:2">
@@ -10398,7 +10413,7 @@
         <v>908</v>
       </c>
       <c r="B909" s="1">
-        <v>380</v>
+        <v>480</v>
       </c>
     </row>
     <row r="910" spans="1:2">
@@ -10406,7 +10421,7 @@
         <v>909</v>
       </c>
       <c r="B910" s="1">
-        <v>600</v>
+        <v>480</v>
       </c>
     </row>
     <row r="911" spans="1:2">
@@ -10414,7 +10429,7 @@
         <v>910</v>
       </c>
       <c r="B911" s="1">
-        <v>820</v>
+        <v>520</v>
       </c>
     </row>
     <row r="912" spans="1:2">
@@ -10422,7 +10437,7 @@
         <v>911</v>
       </c>
       <c r="B912" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="913" spans="1:2">
@@ -10430,7 +10445,7 @@
         <v>912</v>
       </c>
       <c r="B913" s="1">
-        <v>580</v>
+        <v>440</v>
       </c>
     </row>
     <row r="914" spans="1:2">
@@ -10438,7 +10453,7 @@
         <v>913</v>
       </c>
       <c r="B914" s="1">
-        <v>560</v>
+        <v>380</v>
       </c>
     </row>
     <row r="915" spans="1:2">
@@ -10446,7 +10461,7 @@
         <v>914</v>
       </c>
       <c r="B915" s="1">
-        <v>580</v>
+        <v>600</v>
       </c>
     </row>
     <row r="916" spans="1:2">
@@ -10454,7 +10469,7 @@
         <v>915</v>
       </c>
       <c r="B916" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="917" spans="1:2">
@@ -10462,7 +10477,7 @@
         <v>916</v>
       </c>
       <c r="B917" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="918" spans="1:2">
@@ -10470,6 +10485,46 @@
         <v>917</v>
       </c>
       <c r="B918" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="919" spans="1:2">
+      <c r="A919" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="B919" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="920" spans="1:2">
+      <c r="A920" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="B920" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="921" spans="1:2">
+      <c r="A921" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="B921" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="922" spans="1:2">
+      <c r="A922" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="B922" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="923" spans="1:2">
+      <c r="A923" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="B923" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -6253,7 +6253,7 @@
         <v>388</v>
       </c>
       <c r="B389" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -9093,7 +9093,7 @@
         <v>743</v>
       </c>
       <c r="B744" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="745" spans="1:2">

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="932">
   <si>
     <t>Наименование</t>
   </si>
@@ -248,6 +248,9 @@
     <t>Black Cat "О Май Сад!"  (Sour), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Black Cat &amp; Let Me Brew - Головы Кошек. Черная (Fruited Wheat Beer), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Black Cat - ABC Азбука (AIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -464,6 +467,9 @@
     <t>Horror Brewing - Death From Above (IPA),  РОЗЛИВ ,Россия</t>
   </si>
   <si>
+    <t>Horror Brewing - Great Idea, Mr. Monish! (Session IPA),  РОЗЛИВ ,Россия</t>
+  </si>
+  <si>
     <t>Horror Brewing - GROOVIPA (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -488,9 +494,15 @@
     <t>Horror Brewing - Same Shit Different Day V.2 (Pils), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Horror Brewing - Same Shit Different Day V.3 (Pils), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Horror Brewing - Tripod (English Pale Ale), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Horror Brewing - Yamantau (Black IPA),  РОЗЛИВ ,Россия</t>
+  </si>
+  <si>
     <t>Jaws "MOTOR AWAY" Pale Ale , розлив, Россия</t>
   </si>
   <si>
@@ -1712,6 +1724,9 @@
     <t>вынос_Black Cat "О Май Сад!"  (Sour), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Black Cat &amp; Let Me Brew - Головы Кошек. Черная (Fruited Wheat Beer), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Black Cat - ABC Азбука (AIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1823,6 +1838,9 @@
     <t>вынос_Horror Brewing - Death From Above (IPA),  РОЗЛИВ ,Россия</t>
   </si>
   <si>
+    <t>вынос_Horror Brewing - Great Idea, Mr. Monish! (Session IPA),  РОЗЛИВ ,Россия</t>
+  </si>
+  <si>
     <t>вынос_Horror Brewing - GROOVIPA (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1847,9 +1865,15 @@
     <t>вынос_Horror Brewing - Same Shit Different Day V.2 (Pils), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Horror Brewing - Same Shit Different Day V.3 (Pils), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Horror Brewing - Tripod (English Pale Ale), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Horror Brewing - Yamantau (Black IPA),  РОЗЛИВ ,Россия</t>
+  </si>
+  <si>
     <t>вынос_Jaws - Nitro Stout, РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -2472,6 +2496,9 @@
   </si>
   <si>
     <t>вынос_ZAVOD- Framework Gose (), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">вынос__Леонида Леврана - Старый Изборск, РОЗЛИВ, Россия </t>
   </si>
   <si>
     <t xml:space="preserve">вынос_Бродилка - Сухой Сидр, РОЗЛИВ, Россия </t>
@@ -3137,7 +3164,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B923"/>
+  <dimension ref="A1:B932"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -3757,7 +3784,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>660</v>
+        <v>980</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -3765,7 +3792,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -3781,7 +3808,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -3797,7 +3824,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -3805,7 +3832,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -3813,7 +3840,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>560</v>
+        <v>680</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -3821,7 +3848,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>880</v>
+        <v>560</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -3829,7 +3856,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -3837,7 +3864,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -3845,7 +3872,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -3853,7 +3880,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3861,7 +3888,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -3869,7 +3896,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3877,7 +3904,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3885,7 +3912,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>640</v>
+        <v>880</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -3893,7 +3920,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3901,7 +3928,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3909,7 +3936,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3917,7 +3944,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -3925,7 +3952,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3933,7 +3960,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -3941,7 +3968,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -3957,7 +3984,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3965,7 +3992,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -3973,7 +4000,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3981,7 +4008,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3989,7 +4016,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>540</v>
+        <v>560</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3997,7 +4024,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>860</v>
+        <v>540</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -4005,7 +4032,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -4021,7 +4048,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -4029,7 +4056,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -4037,7 +4064,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>440</v>
+        <v>720</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -4045,7 +4072,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -4053,7 +4080,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>460</v>
+        <v>560</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -4069,7 +4096,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>960</v>
+        <v>460</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -4077,7 +4104,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>940</v>
+        <v>960</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -4085,7 +4112,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -4101,7 +4128,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>660</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -4109,7 +4136,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>480</v>
+        <v>660</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -4117,7 +4144,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>400</v>
+        <v>480</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -4125,7 +4152,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>720</v>
+        <v>400</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -4133,7 +4160,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -4141,7 +4168,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>500</v>
+        <v>560</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -4149,7 +4176,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -4157,7 +4184,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>500</v>
+        <v>760</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -4165,7 +4192,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>940</v>
+        <v>500</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -4173,7 +4200,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>820</v>
+        <v>940</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -4189,7 +4216,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -4197,7 +4224,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -4205,7 +4232,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -4213,7 +4240,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -4221,7 +4248,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -4229,7 +4256,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>680</v>
+        <v>960</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -4237,7 +4264,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>420</v>
+        <v>680</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -4245,7 +4272,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -4253,7 +4280,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -4261,7 +4288,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -4269,7 +4296,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -4277,7 +4304,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -4285,7 +4312,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -4293,7 +4320,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -4301,7 +4328,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -4309,7 +4336,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>580</v>
+        <v>880</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -4317,7 +4344,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -4325,7 +4352,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -4333,7 +4360,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>620</v>
+        <v>860</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -4349,7 +4376,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -4357,7 +4384,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -4365,7 +4392,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -4373,7 +4400,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -4381,7 +4408,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>600</v>
+        <v>960</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -4389,7 +4416,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -4397,7 +4424,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -4405,7 +4432,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -4413,7 +4440,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>580</v>
+        <v>800</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -4421,7 +4448,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>540</v>
+        <v>780</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -4429,7 +4456,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>520</v>
+        <v>920</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -4437,7 +4464,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>980</v>
+        <v>500</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -4445,7 +4472,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>1100</v>
+        <v>580</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -4453,7 +4480,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>1060</v>
+        <v>540</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -4461,7 +4488,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>1060</v>
+        <v>520</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -4469,7 +4496,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -4485,7 +4512,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>1100</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4493,7 +4520,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>560</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -4501,7 +4528,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>1080</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -4509,39 +4536,39 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>420</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4549,7 +4576,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4557,7 +4584,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="1">
-        <v>460</v>
+        <v>840</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4565,7 +4592,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="1">
-        <v>560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4573,7 +4600,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4581,7 +4608,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4589,7 +4616,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="1">
-        <v>620</v>
+        <v>460</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4597,7 +4624,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4605,7 +4632,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="1">
-        <v>980</v>
+        <v>580</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4613,7 +4640,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="1">
-        <v>540</v>
+        <v>740</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4621,7 +4648,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="1">
-        <v>580</v>
+        <v>620</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4629,7 +4656,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4637,7 +4664,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="1">
-        <v>760</v>
+        <v>980</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4645,7 +4672,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4653,7 +4680,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="1">
-        <v>1100</v>
+        <v>580</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4661,7 +4688,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4669,7 +4696,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4677,7 +4704,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="1">
-        <v>1100</v>
+        <v>560</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4685,7 +4712,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4693,7 +4720,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="1">
-        <v>640</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4701,7 +4728,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4709,7 +4736,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4717,7 +4744,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4725,7 +4752,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="1">
-        <v>920</v>
+        <v>640</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4733,7 +4760,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4741,7 +4768,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4749,7 +4776,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4757,7 +4784,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="1">
-        <v>960</v>
+        <v>920</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4765,7 +4792,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4773,7 +4800,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4781,7 +4808,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4789,7 +4816,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="1">
-        <v>700</v>
+        <v>960</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4797,7 +4824,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="1">
-        <v>980</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4805,7 +4832,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="1">
-        <v>460</v>
+        <v>840</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4813,7 +4840,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4821,7 +4848,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4829,7 +4856,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="1">
-        <v>660</v>
+        <v>980</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4837,7 +4864,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="1">
-        <v>780</v>
+        <v>460</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4845,7 +4872,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="1">
-        <v>260</v>
+        <v>580</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4853,7 +4880,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="1">
-        <v>260</v>
+        <v>720</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4861,7 +4888,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4869,7 +4896,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="1">
-        <v>440</v>
+        <v>780</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4877,7 +4904,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="1">
-        <v>800</v>
+        <v>260</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4885,7 +4912,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="1">
-        <v>740</v>
+        <v>260</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4893,7 +4920,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="1">
-        <v>760</v>
+        <v>440</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4901,7 +4928,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4909,7 +4936,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="1">
-        <v>400</v>
+        <v>800</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4925,7 +4952,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4933,7 +4960,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="1">
-        <v>780</v>
+        <v>500</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4941,7 +4968,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="1">
-        <v>620</v>
+        <v>400</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4949,7 +4976,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4965,7 +4992,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="1">
-        <v>580</v>
+        <v>780</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4973,7 +5000,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="1">
-        <v>580</v>
+        <v>620</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4981,7 +5008,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="1">
-        <v>620</v>
+        <v>640</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4989,7 +5016,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="1">
-        <v>520</v>
+        <v>680</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -5005,7 +5032,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -5013,7 +5040,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="1">
-        <v>580</v>
+        <v>620</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -5021,7 +5048,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="1">
-        <v>620</v>
+        <v>520</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -5029,7 +5056,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -5037,7 +5064,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -5045,7 +5072,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -5053,7 +5080,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="1">
-        <v>580</v>
+        <v>620</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -5069,7 +5096,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="1">
-        <v>700</v>
+        <v>560</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -5077,7 +5104,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="1">
-        <v>820</v>
+        <v>520</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -5085,7 +5112,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="1">
-        <v>760</v>
+        <v>580</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -5093,7 +5120,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="1">
-        <v>720</v>
+        <v>540</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -5101,7 +5128,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -5109,7 +5136,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="1">
-        <v>1400</v>
+        <v>820</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -5117,7 +5144,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="1">
-        <v>480</v>
+        <v>760</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -5133,7 +5160,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -5141,7 +5168,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="1">
-        <v>600</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -5149,7 +5176,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="1">
-        <v>700</v>
+        <v>480</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -5157,7 +5184,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -5165,7 +5192,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="1">
-        <v>720</v>
+        <v>660</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -5173,7 +5200,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -5181,7 +5208,7 @@
         <v>254</v>
       </c>
       <c r="B255" s="1">
-        <v>520</v>
+        <v>700</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -5189,7 +5216,7 @@
         <v>255</v>
       </c>
       <c r="B256" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -5197,7 +5224,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -5205,7 +5232,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -5213,7 +5240,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -5221,7 +5248,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="1">
-        <v>620</v>
+        <v>900</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -5229,7 +5256,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -5237,7 +5264,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -5245,7 +5272,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -5253,7 +5280,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -5261,7 +5288,7 @@
         <v>264</v>
       </c>
       <c r="B265" s="1">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -5269,7 +5296,7 @@
         <v>265</v>
       </c>
       <c r="B266" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -5277,7 +5304,7 @@
         <v>266</v>
       </c>
       <c r="B267" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -5285,7 +5312,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -5293,7 +5320,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -5301,7 +5328,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="1">
-        <v>980</v>
+        <v>900</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -5317,7 +5344,7 @@
         <v>271</v>
       </c>
       <c r="B272" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -5325,7 +5352,7 @@
         <v>272</v>
       </c>
       <c r="B273" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -5333,7 +5360,7 @@
         <v>273</v>
       </c>
       <c r="B274" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -5341,7 +5368,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -5357,7 +5384,7 @@
         <v>276</v>
       </c>
       <c r="B277" s="1">
-        <v>640</v>
+        <v>820</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -5365,7 +5392,7 @@
         <v>277</v>
       </c>
       <c r="B278" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -5373,7 +5400,7 @@
         <v>278</v>
       </c>
       <c r="B279" s="1">
-        <v>800</v>
+        <v>560</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -5381,7 +5408,7 @@
         <v>279</v>
       </c>
       <c r="B280" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -5389,7 +5416,7 @@
         <v>280</v>
       </c>
       <c r="B281" s="1">
-        <v>500</v>
+        <v>640</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -5397,7 +5424,7 @@
         <v>281</v>
       </c>
       <c r="B282" s="1">
-        <v>758</v>
+        <v>800</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -5405,7 +5432,7 @@
         <v>282</v>
       </c>
       <c r="B283" s="1">
-        <v>2273</v>
+        <v>800</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -5413,7 +5440,7 @@
         <v>283</v>
       </c>
       <c r="B284" s="1">
-        <v>1515</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -5421,7 +5448,7 @@
         <v>284</v>
       </c>
       <c r="B285" s="1">
-        <v>520</v>
+        <v>500</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -5429,7 +5456,7 @@
         <v>285</v>
       </c>
       <c r="B286" s="1">
-        <v>4000</v>
+        <v>758</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5437,7 +5464,7 @@
         <v>286</v>
       </c>
       <c r="B287" s="1">
-        <v>560</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5445,7 +5472,7 @@
         <v>287</v>
       </c>
       <c r="B288" s="1">
-        <v>480</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5453,7 +5480,7 @@
         <v>288</v>
       </c>
       <c r="B289" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5461,7 +5488,7 @@
         <v>289</v>
       </c>
       <c r="B290" s="1">
-        <v>720</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5469,7 +5496,7 @@
         <v>290</v>
       </c>
       <c r="B291" s="1">
-        <v>660</v>
+        <v>560</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5477,7 +5504,7 @@
         <v>291</v>
       </c>
       <c r="B292" s="1">
-        <v>840</v>
+        <v>480</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5485,7 +5512,7 @@
         <v>292</v>
       </c>
       <c r="B293" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5493,7 +5520,7 @@
         <v>293</v>
       </c>
       <c r="B294" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5501,7 +5528,7 @@
         <v>294</v>
       </c>
       <c r="B295" s="1">
-        <v>520</v>
+        <v>660</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5509,7 +5536,7 @@
         <v>295</v>
       </c>
       <c r="B296" s="1">
-        <v>680</v>
+        <v>840</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5517,7 +5544,7 @@
         <v>296</v>
       </c>
       <c r="B297" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5533,7 +5560,7 @@
         <v>298</v>
       </c>
       <c r="B299" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5541,7 +5568,7 @@
         <v>299</v>
       </c>
       <c r="B300" s="1">
-        <v>380</v>
+        <v>680</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5549,7 +5576,7 @@
         <v>300</v>
       </c>
       <c r="B301" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5557,7 +5584,7 @@
         <v>301</v>
       </c>
       <c r="B302" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5565,7 +5592,7 @@
         <v>302</v>
       </c>
       <c r="B303" s="1">
-        <v>540</v>
+        <v>560</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5573,7 +5600,7 @@
         <v>303</v>
       </c>
       <c r="B304" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5589,7 +5616,7 @@
         <v>305</v>
       </c>
       <c r="B306" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5597,7 +5624,7 @@
         <v>306</v>
       </c>
       <c r="B307" s="1">
-        <v>460</v>
+        <v>540</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5613,7 +5640,7 @@
         <v>308</v>
       </c>
       <c r="B309" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5621,7 +5648,7 @@
         <v>309</v>
       </c>
       <c r="B310" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5629,7 +5656,7 @@
         <v>310</v>
       </c>
       <c r="B311" s="1">
-        <v>860</v>
+        <v>460</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5637,7 +5664,7 @@
         <v>311</v>
       </c>
       <c r="B312" s="1">
-        <v>900</v>
+        <v>520</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5645,7 +5672,7 @@
         <v>312</v>
       </c>
       <c r="B313" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5661,7 +5688,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5669,7 +5696,7 @@
         <v>315</v>
       </c>
       <c r="B316" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5677,7 +5704,7 @@
         <v>316</v>
       </c>
       <c r="B317" s="1">
-        <v>980</v>
+        <v>900</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5685,7 +5712,7 @@
         <v>317</v>
       </c>
       <c r="B318" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5693,7 +5720,7 @@
         <v>318</v>
       </c>
       <c r="B319" s="1">
-        <v>1000</v>
+        <v>560</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5701,7 +5728,7 @@
         <v>319</v>
       </c>
       <c r="B320" s="1">
-        <v>900</v>
+        <v>560</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5709,7 +5736,7 @@
         <v>320</v>
       </c>
       <c r="B321" s="1">
-        <v>940</v>
+        <v>980</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5717,7 +5744,7 @@
         <v>321</v>
       </c>
       <c r="B322" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5725,7 +5752,7 @@
         <v>322</v>
       </c>
       <c r="B323" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5733,7 +5760,7 @@
         <v>323</v>
       </c>
       <c r="B324" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5741,7 +5768,7 @@
         <v>324</v>
       </c>
       <c r="B325" s="1">
-        <v>840</v>
+        <v>940</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5749,7 +5776,7 @@
         <v>325</v>
       </c>
       <c r="B326" s="1">
-        <v>860</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5757,7 +5784,7 @@
         <v>326</v>
       </c>
       <c r="B327" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5765,7 +5792,7 @@
         <v>327</v>
       </c>
       <c r="B328" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5773,7 +5800,7 @@
         <v>328</v>
       </c>
       <c r="B329" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5781,7 +5808,7 @@
         <v>329</v>
       </c>
       <c r="B330" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5797,7 +5824,7 @@
         <v>331</v>
       </c>
       <c r="B332" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5805,7 +5832,7 @@
         <v>332</v>
       </c>
       <c r="B333" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5813,7 +5840,7 @@
         <v>333</v>
       </c>
       <c r="B334" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5821,7 +5848,7 @@
         <v>334</v>
       </c>
       <c r="B335" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5829,7 +5856,7 @@
         <v>335</v>
       </c>
       <c r="B336" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5837,7 +5864,7 @@
         <v>336</v>
       </c>
       <c r="B337" s="1">
-        <v>520</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5845,7 +5872,7 @@
         <v>337</v>
       </c>
       <c r="B338" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5853,7 +5880,7 @@
         <v>338</v>
       </c>
       <c r="B339" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5861,7 +5888,7 @@
         <v>339</v>
       </c>
       <c r="B340" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5869,7 +5896,7 @@
         <v>340</v>
       </c>
       <c r="B341" s="1">
-        <v>700</v>
+        <v>520</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5877,7 +5904,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="1">
-        <v>840</v>
+        <v>640</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5885,7 +5912,7 @@
         <v>342</v>
       </c>
       <c r="B343" s="1">
-        <v>580</v>
+        <v>800</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5893,7 +5920,7 @@
         <v>343</v>
       </c>
       <c r="B344" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5901,7 +5928,7 @@
         <v>344</v>
       </c>
       <c r="B345" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5909,7 +5936,7 @@
         <v>345</v>
       </c>
       <c r="B346" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5917,7 +5944,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="1">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5925,7 +5952,7 @@
         <v>347</v>
       </c>
       <c r="B348" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5933,7 +5960,7 @@
         <v>348</v>
       </c>
       <c r="B349" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5941,7 +5968,7 @@
         <v>349</v>
       </c>
       <c r="B350" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5949,7 +5976,7 @@
         <v>350</v>
       </c>
       <c r="B351" s="1">
-        <v>520</v>
+        <v>640</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5957,7 +5984,7 @@
         <v>351</v>
       </c>
       <c r="B352" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5965,7 +5992,7 @@
         <v>352</v>
       </c>
       <c r="B353" s="1">
-        <v>600</v>
+        <v>880</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5973,7 +6000,7 @@
         <v>353</v>
       </c>
       <c r="B354" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5981,7 +6008,7 @@
         <v>354</v>
       </c>
       <c r="B355" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5989,7 +6016,7 @@
         <v>355</v>
       </c>
       <c r="B356" s="1">
-        <v>380</v>
+        <v>740</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5997,7 +6024,7 @@
         <v>356</v>
       </c>
       <c r="B357" s="1">
-        <v>520</v>
+        <v>600</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -6005,7 +6032,7 @@
         <v>357</v>
       </c>
       <c r="B358" s="1">
-        <v>320</v>
+        <v>820</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -6013,7 +6040,7 @@
         <v>358</v>
       </c>
       <c r="B359" s="1">
-        <v>540</v>
+        <v>600</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -6021,7 +6048,7 @@
         <v>359</v>
       </c>
       <c r="B360" s="1">
-        <v>560</v>
+        <v>380</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -6029,7 +6056,7 @@
         <v>360</v>
       </c>
       <c r="B361" s="1">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -6037,7 +6064,7 @@
         <v>361</v>
       </c>
       <c r="B362" s="1">
-        <v>480</v>
+        <v>320</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -6045,7 +6072,7 @@
         <v>362</v>
       </c>
       <c r="B363" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -6053,7 +6080,7 @@
         <v>363</v>
       </c>
       <c r="B364" s="1">
-        <v>500</v>
+        <v>560</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -6061,7 +6088,7 @@
         <v>364</v>
       </c>
       <c r="B365" s="1">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -6077,7 +6104,7 @@
         <v>366</v>
       </c>
       <c r="B367" s="1">
-        <v>800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -6085,7 +6112,7 @@
         <v>367</v>
       </c>
       <c r="B368" s="1">
-        <v>520</v>
+        <v>500</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -6093,7 +6120,7 @@
         <v>368</v>
       </c>
       <c r="B369" s="1">
-        <v>380</v>
+        <v>800</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -6101,7 +6128,7 @@
         <v>369</v>
       </c>
       <c r="B370" s="1">
-        <v>440</v>
+        <v>480</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -6109,7 +6136,7 @@
         <v>370</v>
       </c>
       <c r="B371" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -6117,7 +6144,7 @@
         <v>371</v>
       </c>
       <c r="B372" s="1">
-        <v>900</v>
+        <v>520</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -6125,7 +6152,7 @@
         <v>372</v>
       </c>
       <c r="B373" s="1">
-        <v>780</v>
+        <v>380</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -6133,7 +6160,7 @@
         <v>373</v>
       </c>
       <c r="B374" s="1">
-        <v>780</v>
+        <v>440</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -6141,7 +6168,7 @@
         <v>374</v>
       </c>
       <c r="B375" s="1">
-        <v>860</v>
+        <v>900</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -6149,7 +6176,7 @@
         <v>375</v>
       </c>
       <c r="B376" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -6157,7 +6184,7 @@
         <v>376</v>
       </c>
       <c r="B377" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -6165,7 +6192,7 @@
         <v>377</v>
       </c>
       <c r="B378" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -6173,7 +6200,7 @@
         <v>378</v>
       </c>
       <c r="B379" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -6181,7 +6208,7 @@
         <v>379</v>
       </c>
       <c r="B380" s="1">
-        <v>840</v>
+        <v>960</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -6189,7 +6216,7 @@
         <v>380</v>
       </c>
       <c r="B381" s="1">
-        <v>700</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -6197,7 +6224,7 @@
         <v>381</v>
       </c>
       <c r="B382" s="1">
-        <v>640</v>
+        <v>880</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -6213,7 +6240,7 @@
         <v>383</v>
       </c>
       <c r="B384" s="1">
-        <v>1020</v>
+        <v>840</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -6221,7 +6248,7 @@
         <v>384</v>
       </c>
       <c r="B385" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -6229,7 +6256,7 @@
         <v>385</v>
       </c>
       <c r="B386" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -6237,7 +6264,7 @@
         <v>386</v>
       </c>
       <c r="B387" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -6245,7 +6272,7 @@
         <v>387</v>
       </c>
       <c r="B388" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -6253,7 +6280,7 @@
         <v>388</v>
       </c>
       <c r="B389" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -6261,7 +6288,7 @@
         <v>389</v>
       </c>
       <c r="B390" s="1">
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -6269,7 +6296,7 @@
         <v>390</v>
       </c>
       <c r="B391" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -6277,7 +6304,7 @@
         <v>391</v>
       </c>
       <c r="B392" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -6285,7 +6312,7 @@
         <v>392</v>
       </c>
       <c r="B393" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -6293,7 +6320,7 @@
         <v>393</v>
       </c>
       <c r="B394" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -6301,7 +6328,7 @@
         <v>394</v>
       </c>
       <c r="B395" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -6309,7 +6336,7 @@
         <v>395</v>
       </c>
       <c r="B396" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -6317,7 +6344,7 @@
         <v>396</v>
       </c>
       <c r="B397" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -6333,7 +6360,7 @@
         <v>398</v>
       </c>
       <c r="B399" s="1">
-        <v>480</v>
+        <v>740</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -6341,7 +6368,7 @@
         <v>399</v>
       </c>
       <c r="B400" s="1">
-        <v>640</v>
+        <v>820</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -6349,7 +6376,7 @@
         <v>400</v>
       </c>
       <c r="B401" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -6357,7 +6384,7 @@
         <v>401</v>
       </c>
       <c r="B402" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -6365,7 +6392,7 @@
         <v>402</v>
       </c>
       <c r="B403" s="1">
-        <v>860</v>
+        <v>480</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -6373,7 +6400,7 @@
         <v>403</v>
       </c>
       <c r="B404" s="1">
-        <v>520</v>
+        <v>640</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -6381,7 +6408,7 @@
         <v>404</v>
       </c>
       <c r="B405" s="1">
-        <v>540</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -6389,7 +6416,7 @@
         <v>405</v>
       </c>
       <c r="B406" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -6397,7 +6424,7 @@
         <v>406</v>
       </c>
       <c r="B407" s="1">
-        <v>700</v>
+        <v>860</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -6405,7 +6432,7 @@
         <v>407</v>
       </c>
       <c r="B408" s="1">
-        <v>420</v>
+        <v>520</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -6413,7 +6440,7 @@
         <v>408</v>
       </c>
       <c r="B409" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -6421,7 +6448,7 @@
         <v>409</v>
       </c>
       <c r="B410" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -6429,7 +6456,7 @@
         <v>410</v>
       </c>
       <c r="B411" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -6437,7 +6464,7 @@
         <v>411</v>
       </c>
       <c r="B412" s="1">
-        <v>740</v>
+        <v>420</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -6445,7 +6472,7 @@
         <v>412</v>
       </c>
       <c r="B413" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -6453,7 +6480,7 @@
         <v>413</v>
       </c>
       <c r="B414" s="1">
-        <v>920</v>
+        <v>720</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -6461,7 +6488,7 @@
         <v>414</v>
       </c>
       <c r="B415" s="1">
-        <v>840</v>
+        <v>580</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -6469,7 +6496,7 @@
         <v>415</v>
       </c>
       <c r="B416" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -6477,7 +6504,7 @@
         <v>416</v>
       </c>
       <c r="B417" s="1">
-        <v>620</v>
+        <v>900</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -6485,7 +6512,7 @@
         <v>417</v>
       </c>
       <c r="B418" s="1">
-        <v>440</v>
+        <v>920</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -6493,7 +6520,7 @@
         <v>418</v>
       </c>
       <c r="B419" s="1">
-        <v>1100</v>
+        <v>840</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -6501,7 +6528,7 @@
         <v>419</v>
       </c>
       <c r="B420" s="1">
-        <v>1100</v>
+        <v>720</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -6509,7 +6536,7 @@
         <v>420</v>
       </c>
       <c r="B421" s="1">
-        <v>320</v>
+        <v>620</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -6517,7 +6544,7 @@
         <v>421</v>
       </c>
       <c r="B422" s="1">
-        <v>940</v>
+        <v>440</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -6525,7 +6552,7 @@
         <v>422</v>
       </c>
       <c r="B423" s="1">
-        <v>320</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -6533,7 +6560,7 @@
         <v>423</v>
       </c>
       <c r="B424" s="1">
-        <v>960</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -6541,7 +6568,7 @@
         <v>424</v>
       </c>
       <c r="B425" s="1">
-        <v>820</v>
+        <v>320</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -6549,7 +6576,7 @@
         <v>425</v>
       </c>
       <c r="B426" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -6557,7 +6584,7 @@
         <v>426</v>
       </c>
       <c r="B427" s="1">
-        <v>580</v>
+        <v>320</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -6565,7 +6592,7 @@
         <v>427</v>
       </c>
       <c r="B428" s="1">
-        <v>580</v>
+        <v>960</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6573,7 +6600,7 @@
         <v>428</v>
       </c>
       <c r="B429" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6581,7 +6608,7 @@
         <v>429</v>
       </c>
       <c r="B430" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6605,7 +6632,7 @@
         <v>432</v>
       </c>
       <c r="B433" s="1">
-        <v>620</v>
+        <v>900</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6621,7 +6648,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="1">
-        <v>920</v>
+        <v>580</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6629,7 +6656,7 @@
         <v>435</v>
       </c>
       <c r="B436" s="1">
-        <v>1000</v>
+        <v>580</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6637,7 +6664,7 @@
         <v>436</v>
       </c>
       <c r="B437" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6645,7 +6672,7 @@
         <v>437</v>
       </c>
       <c r="B438" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6653,7 +6680,7 @@
         <v>438</v>
       </c>
       <c r="B439" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6661,7 +6688,7 @@
         <v>439</v>
       </c>
       <c r="B440" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6669,7 +6696,7 @@
         <v>440</v>
       </c>
       <c r="B441" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6677,7 +6704,7 @@
         <v>441</v>
       </c>
       <c r="B442" s="1">
-        <v>660</v>
+        <v>880</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6685,7 +6712,7 @@
         <v>442</v>
       </c>
       <c r="B443" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6693,7 +6720,7 @@
         <v>443</v>
       </c>
       <c r="B444" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6701,7 +6728,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6709,7 +6736,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6717,7 +6744,7 @@
         <v>446</v>
       </c>
       <c r="B447" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6725,7 +6752,7 @@
         <v>447</v>
       </c>
       <c r="B448" s="1">
-        <v>440</v>
+        <v>900</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6733,7 +6760,7 @@
         <v>448</v>
       </c>
       <c r="B449" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6749,7 +6776,7 @@
         <v>450</v>
       </c>
       <c r="B451" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6757,7 +6784,7 @@
         <v>451</v>
       </c>
       <c r="B452" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6765,7 +6792,7 @@
         <v>452</v>
       </c>
       <c r="B453" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6773,7 +6800,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="1">
-        <v>760</v>
+        <v>900</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6781,7 +6808,7 @@
         <v>454</v>
       </c>
       <c r="B455" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6789,7 +6816,7 @@
         <v>455</v>
       </c>
       <c r="B456" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6797,7 +6824,7 @@
         <v>456</v>
       </c>
       <c r="B457" s="1">
-        <v>600</v>
+        <v>560</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6805,7 +6832,7 @@
         <v>457</v>
       </c>
       <c r="B458" s="1">
-        <v>560</v>
+        <v>760</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6813,7 +6840,7 @@
         <v>458</v>
       </c>
       <c r="B459" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6829,7 +6856,7 @@
         <v>460</v>
       </c>
       <c r="B461" s="1">
-        <v>680</v>
+        <v>600</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6837,7 +6864,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6845,7 +6872,7 @@
         <v>462</v>
       </c>
       <c r="B463" s="1">
-        <v>480</v>
+        <v>620</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6853,7 +6880,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6861,7 +6888,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="1">
-        <v>840</v>
+        <v>680</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6869,7 +6896,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="1">
-        <v>880</v>
+        <v>480</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6877,7 +6904,7 @@
         <v>466</v>
       </c>
       <c r="B467" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6885,7 +6912,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6893,7 +6920,7 @@
         <v>468</v>
       </c>
       <c r="B469" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6901,7 +6928,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="1">
-        <v>920</v>
+        <v>880</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6909,7 +6936,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6917,7 +6944,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6925,7 +6952,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="1">
-        <v>940</v>
+        <v>780</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6933,7 +6960,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="1">
-        <v>980</v>
+        <v>920</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6941,7 +6968,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="1">
-        <v>920</v>
+        <v>800</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6949,7 +6976,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6957,7 +6984,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="1">
-        <v>760</v>
+        <v>940</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6965,7 +6992,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6973,7 +7000,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="1">
-        <v>620</v>
+        <v>920</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6981,7 +7008,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6989,7 +7016,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6997,7 +7024,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -7005,7 +7032,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -7013,7 +7040,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="1">
-        <v>680</v>
+        <v>620</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -7021,7 +7048,7 @@
         <v>484</v>
       </c>
       <c r="B485" s="1">
-        <v>820</v>
+        <v>860</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -7029,7 +7056,7 @@
         <v>485</v>
       </c>
       <c r="B486" s="1">
-        <v>960</v>
+        <v>920</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -7037,7 +7064,7 @@
         <v>486</v>
       </c>
       <c r="B487" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -7045,7 +7072,7 @@
         <v>487</v>
       </c>
       <c r="B488" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -7053,7 +7080,7 @@
         <v>488</v>
       </c>
       <c r="B489" s="1">
-        <v>640</v>
+        <v>820</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -7061,7 +7088,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="1">
-        <v>860</v>
+        <v>960</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -7069,7 +7096,7 @@
         <v>490</v>
       </c>
       <c r="B491" s="1">
-        <v>560</v>
+        <v>740</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -7077,7 +7104,7 @@
         <v>491</v>
       </c>
       <c r="B492" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -7085,7 +7112,7 @@
         <v>492</v>
       </c>
       <c r="B493" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -7093,7 +7120,7 @@
         <v>493</v>
       </c>
       <c r="B494" s="1">
-        <v>640</v>
+        <v>860</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -7109,7 +7136,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -7117,7 +7144,7 @@
         <v>496</v>
       </c>
       <c r="B497" s="1">
-        <v>520</v>
+        <v>660</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -7125,7 +7152,7 @@
         <v>497</v>
       </c>
       <c r="B498" s="1">
-        <v>480</v>
+        <v>640</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -7133,7 +7160,7 @@
         <v>498</v>
       </c>
       <c r="B499" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -7141,7 +7168,7 @@
         <v>499</v>
       </c>
       <c r="B500" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -7149,7 +7176,7 @@
         <v>500</v>
       </c>
       <c r="B501" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -7157,7 +7184,7 @@
         <v>501</v>
       </c>
       <c r="B502" s="1">
-        <v>820</v>
+        <v>480</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -7165,7 +7192,7 @@
         <v>502</v>
       </c>
       <c r="B503" s="1">
-        <v>760</v>
+        <v>620</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -7173,7 +7200,7 @@
         <v>503</v>
       </c>
       <c r="B504" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -7181,7 +7208,7 @@
         <v>504</v>
       </c>
       <c r="B505" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -7189,7 +7216,7 @@
         <v>505</v>
       </c>
       <c r="B506" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -7197,7 +7224,7 @@
         <v>506</v>
       </c>
       <c r="B507" s="1">
-        <v>480</v>
+        <v>760</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -7205,7 +7232,7 @@
         <v>507</v>
       </c>
       <c r="B508" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -7213,7 +7240,7 @@
         <v>508</v>
       </c>
       <c r="B509" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -7221,7 +7248,7 @@
         <v>509</v>
       </c>
       <c r="B510" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -7229,7 +7256,7 @@
         <v>510</v>
       </c>
       <c r="B511" s="1">
-        <v>440</v>
+        <v>480</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -7237,7 +7264,7 @@
         <v>511</v>
       </c>
       <c r="B512" s="1">
-        <v>440</v>
+        <v>840</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -7245,7 +7272,7 @@
         <v>512</v>
       </c>
       <c r="B513" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -7253,7 +7280,7 @@
         <v>513</v>
       </c>
       <c r="B514" s="1">
-        <v>940</v>
+        <v>700</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -7261,7 +7288,7 @@
         <v>514</v>
       </c>
       <c r="B515" s="1">
-        <v>1100</v>
+        <v>440</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -7269,7 +7296,7 @@
         <v>515</v>
       </c>
       <c r="B516" s="1">
-        <v>880</v>
+        <v>440</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -7277,7 +7304,7 @@
         <v>516</v>
       </c>
       <c r="B517" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -7285,7 +7312,7 @@
         <v>517</v>
       </c>
       <c r="B518" s="1">
-        <v>760</v>
+        <v>940</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -7293,7 +7320,7 @@
         <v>518</v>
       </c>
       <c r="B519" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -7301,7 +7328,7 @@
         <v>519</v>
       </c>
       <c r="B520" s="1">
-        <v>660</v>
+        <v>880</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -7309,7 +7336,7 @@
         <v>520</v>
       </c>
       <c r="B521" s="1">
-        <v>1100</v>
+        <v>880</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -7317,7 +7344,7 @@
         <v>521</v>
       </c>
       <c r="B522" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -7325,7 +7352,7 @@
         <v>522</v>
       </c>
       <c r="B523" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -7333,7 +7360,7 @@
         <v>523</v>
       </c>
       <c r="B524" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -7341,7 +7368,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -7349,7 +7376,7 @@
         <v>525</v>
       </c>
       <c r="B526" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -7357,7 +7384,7 @@
         <v>526</v>
       </c>
       <c r="B527" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -7365,7 +7392,7 @@
         <v>527</v>
       </c>
       <c r="B528" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -7373,7 +7400,7 @@
         <v>528</v>
       </c>
       <c r="B529" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -7381,7 +7408,7 @@
         <v>529</v>
       </c>
       <c r="B530" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -7389,7 +7416,7 @@
         <v>530</v>
       </c>
       <c r="B531" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -7397,7 +7424,7 @@
         <v>531</v>
       </c>
       <c r="B532" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -7405,7 +7432,7 @@
         <v>532</v>
       </c>
       <c r="B533" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -7413,7 +7440,7 @@
         <v>533</v>
       </c>
       <c r="B534" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -7421,7 +7448,7 @@
         <v>534</v>
       </c>
       <c r="B535" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -7429,7 +7456,7 @@
         <v>535</v>
       </c>
       <c r="B536" s="1">
-        <v>800</v>
+        <v>860</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -7437,7 +7464,7 @@
         <v>536</v>
       </c>
       <c r="B537" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -7453,7 +7480,7 @@
         <v>538</v>
       </c>
       <c r="B539" s="1">
-        <v>620</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -7461,7 +7488,7 @@
         <v>539</v>
       </c>
       <c r="B540" s="1">
-        <v>840</v>
+        <v>800</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -7469,7 +7496,7 @@
         <v>540</v>
       </c>
       <c r="B541" s="1">
-        <v>880</v>
+        <v>660</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -7477,7 +7504,7 @@
         <v>541</v>
       </c>
       <c r="B542" s="1">
-        <v>1060</v>
+        <v>600</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -7485,7 +7512,7 @@
         <v>542</v>
       </c>
       <c r="B543" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -7493,7 +7520,7 @@
         <v>543</v>
       </c>
       <c r="B544" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -7501,7 +7528,7 @@
         <v>544</v>
       </c>
       <c r="B545" s="1">
-        <v>800</v>
+        <v>880</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -7509,7 +7536,7 @@
         <v>545</v>
       </c>
       <c r="B546" s="1">
-        <v>860</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -7517,7 +7544,7 @@
         <v>546</v>
       </c>
       <c r="B547" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -7525,7 +7552,7 @@
         <v>547</v>
       </c>
       <c r="B548" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -7533,7 +7560,7 @@
         <v>548</v>
       </c>
       <c r="B549" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -7541,7 +7568,7 @@
         <v>549</v>
       </c>
       <c r="B550" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -7549,7 +7576,7 @@
         <v>550</v>
       </c>
       <c r="B551" s="1">
-        <v>900</v>
+        <v>960</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -7557,7 +7584,7 @@
         <v>551</v>
       </c>
       <c r="B552" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7565,7 +7592,7 @@
         <v>552</v>
       </c>
       <c r="B553" s="1">
-        <v>1100</v>
+        <v>720</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7573,7 +7600,7 @@
         <v>553</v>
       </c>
       <c r="B554" s="1">
-        <v>980</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7581,7 +7608,7 @@
         <v>554</v>
       </c>
       <c r="B555" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7589,7 +7616,7 @@
         <v>555</v>
       </c>
       <c r="B556" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7597,7 +7624,7 @@
         <v>556</v>
       </c>
       <c r="B557" s="1">
-        <v>980</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7605,7 +7632,7 @@
         <v>557</v>
       </c>
       <c r="B558" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7621,7 +7648,7 @@
         <v>559</v>
       </c>
       <c r="B560" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7629,7 +7656,7 @@
         <v>560</v>
       </c>
       <c r="B561" s="1">
-        <v>900</v>
+        <v>980</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7637,7 +7664,7 @@
         <v>561</v>
       </c>
       <c r="B562" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7645,7 +7672,7 @@
         <v>562</v>
       </c>
       <c r="B563" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7653,7 +7680,7 @@
         <v>563</v>
       </c>
       <c r="B564" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7669,7 +7696,7 @@
         <v>565</v>
       </c>
       <c r="B566" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7677,7 +7704,7 @@
         <v>566</v>
       </c>
       <c r="B567" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7685,7 +7712,7 @@
         <v>567</v>
       </c>
       <c r="B568" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7693,7 +7720,7 @@
         <v>568</v>
       </c>
       <c r="B569" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7701,7 +7728,7 @@
         <v>569</v>
       </c>
       <c r="B570" s="1">
-        <v>820</v>
+        <v>980</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7709,7 +7736,7 @@
         <v>570</v>
       </c>
       <c r="B571" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7717,7 +7744,7 @@
         <v>571</v>
       </c>
       <c r="B572" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7725,7 +7752,7 @@
         <v>572</v>
       </c>
       <c r="B573" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7733,7 +7760,7 @@
         <v>573</v>
       </c>
       <c r="B574" s="1">
-        <v>920</v>
+        <v>880</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7741,7 +7768,7 @@
         <v>574</v>
       </c>
       <c r="B575" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7749,7 +7776,7 @@
         <v>575</v>
       </c>
       <c r="B576" s="1">
-        <v>880</v>
+        <v>760</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7757,7 +7784,7 @@
         <v>576</v>
       </c>
       <c r="B577" s="1">
-        <v>640</v>
+        <v>820</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7765,7 +7792,7 @@
         <v>577</v>
       </c>
       <c r="B578" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7773,7 +7800,7 @@
         <v>578</v>
       </c>
       <c r="B579" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7781,7 +7808,7 @@
         <v>579</v>
       </c>
       <c r="B580" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7789,7 +7816,7 @@
         <v>580</v>
       </c>
       <c r="B581" s="1">
-        <v>560</v>
+        <v>880</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7797,7 +7824,7 @@
         <v>581</v>
       </c>
       <c r="B582" s="1">
-        <v>860</v>
+        <v>640</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7805,7 +7832,7 @@
         <v>582</v>
       </c>
       <c r="B583" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7813,7 +7840,7 @@
         <v>583</v>
       </c>
       <c r="B584" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7821,7 +7848,7 @@
         <v>584</v>
       </c>
       <c r="B585" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7829,7 +7856,7 @@
         <v>585</v>
       </c>
       <c r="B586" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7837,7 +7864,7 @@
         <v>586</v>
       </c>
       <c r="B587" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7845,7 +7872,7 @@
         <v>587</v>
       </c>
       <c r="B588" s="1">
-        <v>940</v>
+        <v>840</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7853,7 +7880,7 @@
         <v>588</v>
       </c>
       <c r="B589" s="1">
-        <v>1040</v>
+        <v>840</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7861,7 +7888,7 @@
         <v>589</v>
       </c>
       <c r="B590" s="1">
-        <v>1040</v>
+        <v>860</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7869,7 +7896,7 @@
         <v>590</v>
       </c>
       <c r="B591" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7877,7 +7904,7 @@
         <v>591</v>
       </c>
       <c r="B592" s="1">
-        <v>860</v>
+        <v>960</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7885,7 +7912,7 @@
         <v>592</v>
       </c>
       <c r="B593" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7893,7 +7920,7 @@
         <v>593</v>
       </c>
       <c r="B594" s="1">
-        <v>920</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7901,7 +7928,7 @@
         <v>594</v>
       </c>
       <c r="B595" s="1">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7909,7 +7936,7 @@
         <v>595</v>
       </c>
       <c r="B596" s="1">
-        <v>680</v>
+        <v>940</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7917,7 +7944,7 @@
         <v>596</v>
       </c>
       <c r="B597" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7925,7 +7952,7 @@
         <v>597</v>
       </c>
       <c r="B598" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7933,7 +7960,7 @@
         <v>598</v>
       </c>
       <c r="B599" s="1">
-        <v>880</v>
+        <v>920</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7941,7 +7968,7 @@
         <v>599</v>
       </c>
       <c r="B600" s="1">
-        <v>580</v>
+        <v>960</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7949,7 +7976,7 @@
         <v>600</v>
       </c>
       <c r="B601" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7957,7 +7984,7 @@
         <v>601</v>
       </c>
       <c r="B602" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7965,7 +7992,7 @@
         <v>602</v>
       </c>
       <c r="B603" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7973,7 +8000,7 @@
         <v>603</v>
       </c>
       <c r="B604" s="1">
-        <v>900</v>
+        <v>880</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7981,7 +8008,7 @@
         <v>604</v>
       </c>
       <c r="B605" s="1">
-        <v>780</v>
+        <v>580</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7989,7 +8016,7 @@
         <v>605</v>
       </c>
       <c r="B606" s="1">
-        <v>700</v>
+        <v>820</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7997,7 +8024,7 @@
         <v>606</v>
       </c>
       <c r="B607" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -8013,7 +8040,7 @@
         <v>608</v>
       </c>
       <c r="B609" s="1">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -8021,7 +8048,7 @@
         <v>609</v>
       </c>
       <c r="B610" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -8037,7 +8064,7 @@
         <v>611</v>
       </c>
       <c r="B612" s="1">
-        <v>540</v>
+        <v>700</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -8045,7 +8072,7 @@
         <v>612</v>
       </c>
       <c r="B613" s="1">
-        <v>980</v>
+        <v>960</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -8053,7 +8080,7 @@
         <v>613</v>
       </c>
       <c r="B614" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -8061,7 +8088,7 @@
         <v>614</v>
       </c>
       <c r="B615" s="1">
-        <v>1060</v>
+        <v>600</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -8069,7 +8096,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -8077,7 +8104,7 @@
         <v>616</v>
       </c>
       <c r="B617" s="1">
-        <v>1100</v>
+        <v>800</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -8085,7 +8112,7 @@
         <v>617</v>
       </c>
       <c r="B618" s="1">
-        <v>1100</v>
+        <v>780</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -8093,7 +8120,7 @@
         <v>618</v>
       </c>
       <c r="B619" s="1">
-        <v>1080</v>
+        <v>920</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -8101,7 +8128,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="1">
-        <v>840</v>
+        <v>540</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -8109,7 +8136,7 @@
         <v>620</v>
       </c>
       <c r="B621" s="1">
-        <v>840</v>
+        <v>980</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -8117,7 +8144,7 @@
         <v>621</v>
       </c>
       <c r="B622" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -8125,7 +8152,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="1">
-        <v>560</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -8133,7 +8160,7 @@
         <v>623</v>
       </c>
       <c r="B624" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -8141,7 +8168,7 @@
         <v>624</v>
       </c>
       <c r="B625" s="1">
-        <v>620</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -8149,7 +8176,7 @@
         <v>625</v>
       </c>
       <c r="B626" s="1">
-        <v>860</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -8157,7 +8184,7 @@
         <v>626</v>
       </c>
       <c r="B627" s="1">
-        <v>980</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -8165,7 +8192,7 @@
         <v>627</v>
       </c>
       <c r="B628" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -8173,7 +8200,7 @@
         <v>628</v>
       </c>
       <c r="B629" s="1">
-        <v>760</v>
+        <v>840</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -8181,7 +8208,7 @@
         <v>629</v>
       </c>
       <c r="B630" s="1">
-        <v>1100</v>
+        <v>720</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -8189,7 +8216,7 @@
         <v>630</v>
       </c>
       <c r="B631" s="1">
-        <v>1100</v>
+        <v>560</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -8197,7 +8224,7 @@
         <v>631</v>
       </c>
       <c r="B632" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -8205,7 +8232,7 @@
         <v>632</v>
       </c>
       <c r="B633" s="1">
-        <v>920</v>
+        <v>620</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -8213,7 +8240,7 @@
         <v>633</v>
       </c>
       <c r="B634" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -8221,7 +8248,7 @@
         <v>634</v>
       </c>
       <c r="B635" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -8229,7 +8256,7 @@
         <v>635</v>
       </c>
       <c r="B636" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -8237,7 +8264,7 @@
         <v>636</v>
       </c>
       <c r="B637" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -8245,7 +8272,7 @@
         <v>637</v>
       </c>
       <c r="B638" s="1">
-        <v>960</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -8253,7 +8280,7 @@
         <v>638</v>
       </c>
       <c r="B639" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -8261,7 +8288,7 @@
         <v>639</v>
       </c>
       <c r="B640" s="1">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -8269,7 +8296,7 @@
         <v>640</v>
       </c>
       <c r="B641" s="1">
-        <v>980</v>
+        <v>920</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -8277,7 +8304,7 @@
         <v>641</v>
       </c>
       <c r="B642" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -8285,7 +8312,7 @@
         <v>642</v>
       </c>
       <c r="B643" s="1">
-        <v>800</v>
+        <v>920</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -8293,7 +8320,7 @@
         <v>643</v>
       </c>
       <c r="B644" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -8301,7 +8328,7 @@
         <v>644</v>
       </c>
       <c r="B645" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -8309,7 +8336,7 @@
         <v>645</v>
       </c>
       <c r="B646" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -8317,7 +8344,7 @@
         <v>646</v>
       </c>
       <c r="B647" s="1">
-        <v>680</v>
+        <v>840</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -8325,7 +8352,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -8333,7 +8360,7 @@
         <v>648</v>
       </c>
       <c r="B649" s="1">
-        <v>680</v>
+        <v>980</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -8341,7 +8368,7 @@
         <v>649</v>
       </c>
       <c r="B650" s="1">
-        <v>860</v>
+        <v>720</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -8349,7 +8376,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -8357,7 +8384,7 @@
         <v>651</v>
       </c>
       <c r="B652" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -8373,7 +8400,7 @@
         <v>653</v>
       </c>
       <c r="B654" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -8381,7 +8408,7 @@
         <v>654</v>
       </c>
       <c r="B655" s="1">
-        <v>1400</v>
+        <v>680</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -8389,7 +8416,7 @@
         <v>655</v>
       </c>
       <c r="B656" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -8397,7 +8424,7 @@
         <v>656</v>
       </c>
       <c r="B657" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -8405,7 +8432,7 @@
         <v>657</v>
       </c>
       <c r="B658" s="1">
-        <v>700</v>
+        <v>860</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -8413,7 +8440,7 @@
         <v>658</v>
       </c>
       <c r="B659" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -8421,7 +8448,7 @@
         <v>659</v>
       </c>
       <c r="B660" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -8429,7 +8456,7 @@
         <v>660</v>
       </c>
       <c r="B661" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -8437,7 +8464,7 @@
         <v>661</v>
       </c>
       <c r="B662" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -8445,7 +8472,7 @@
         <v>662</v>
       </c>
       <c r="B663" s="1">
-        <v>900</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -8453,7 +8480,7 @@
         <v>663</v>
       </c>
       <c r="B664" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -8461,7 +8488,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -8469,7 +8496,7 @@
         <v>665</v>
       </c>
       <c r="B666" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -8477,7 +8504,7 @@
         <v>666</v>
       </c>
       <c r="B667" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -8485,7 +8512,7 @@
         <v>667</v>
       </c>
       <c r="B668" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -8493,7 +8520,7 @@
         <v>668</v>
       </c>
       <c r="B669" s="1">
-        <v>980</v>
+        <v>780</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -8501,7 +8528,7 @@
         <v>669</v>
       </c>
       <c r="B670" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -8509,7 +8536,7 @@
         <v>670</v>
       </c>
       <c r="B671" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -8517,7 +8544,7 @@
         <v>671</v>
       </c>
       <c r="B672" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -8525,7 +8552,7 @@
         <v>672</v>
       </c>
       <c r="B673" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -8541,7 +8568,7 @@
         <v>674</v>
       </c>
       <c r="B675" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8549,7 +8576,7 @@
         <v>675</v>
       </c>
       <c r="B676" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -8557,7 +8584,7 @@
         <v>676</v>
       </c>
       <c r="B677" s="1">
-        <v>800</v>
+        <v>980</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8565,7 +8592,7 @@
         <v>677</v>
       </c>
       <c r="B678" s="1">
-        <v>4000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8573,7 +8600,7 @@
         <v>678</v>
       </c>
       <c r="B679" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8581,7 +8608,7 @@
         <v>679</v>
       </c>
       <c r="B680" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8589,7 +8616,7 @@
         <v>680</v>
       </c>
       <c r="B681" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8597,7 +8624,7 @@
         <v>681</v>
       </c>
       <c r="B682" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8605,7 +8632,7 @@
         <v>682</v>
       </c>
       <c r="B683" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8613,7 +8640,7 @@
         <v>683</v>
       </c>
       <c r="B684" s="1">
-        <v>640</v>
+        <v>800</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8621,7 +8648,7 @@
         <v>684</v>
       </c>
       <c r="B685" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8629,7 +8656,7 @@
         <v>685</v>
       </c>
       <c r="B686" s="1">
-        <v>900</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8637,7 +8664,7 @@
         <v>686</v>
       </c>
       <c r="B687" s="1">
-        <v>540</v>
+        <v>720</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8645,7 +8672,7 @@
         <v>687</v>
       </c>
       <c r="B688" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8653,7 +8680,7 @@
         <v>688</v>
       </c>
       <c r="B689" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8661,7 +8688,7 @@
         <v>689</v>
       </c>
       <c r="B690" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8669,7 +8696,7 @@
         <v>690</v>
       </c>
       <c r="B691" s="1">
-        <v>860</v>
+        <v>680</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8677,7 +8704,7 @@
         <v>691</v>
       </c>
       <c r="B692" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8685,7 +8712,7 @@
         <v>692</v>
       </c>
       <c r="B693" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8701,7 +8728,7 @@
         <v>694</v>
       </c>
       <c r="B695" s="1">
-        <v>980</v>
+        <v>540</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8709,7 +8736,7 @@
         <v>695</v>
       </c>
       <c r="B696" s="1">
-        <v>1000</v>
+        <v>660</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8717,7 +8744,7 @@
         <v>696</v>
       </c>
       <c r="B697" s="1">
-        <v>1000</v>
+        <v>580</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8733,7 +8760,7 @@
         <v>698</v>
       </c>
       <c r="B699" s="1">
-        <v>1040</v>
+        <v>860</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8741,7 +8768,7 @@
         <v>699</v>
       </c>
       <c r="B700" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8749,7 +8776,7 @@
         <v>700</v>
       </c>
       <c r="B701" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8757,7 +8784,7 @@
         <v>701</v>
       </c>
       <c r="B702" s="1">
-        <v>860</v>
+        <v>900</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8765,7 +8792,7 @@
         <v>702</v>
       </c>
       <c r="B703" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8773,7 +8800,7 @@
         <v>703</v>
       </c>
       <c r="B704" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8797,7 +8824,7 @@
         <v>706</v>
       </c>
       <c r="B707" s="1">
-        <v>1020</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8805,7 +8832,7 @@
         <v>707</v>
       </c>
       <c r="B708" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8813,7 +8840,7 @@
         <v>708</v>
       </c>
       <c r="B709" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8821,7 +8848,7 @@
         <v>709</v>
       </c>
       <c r="B710" s="1">
-        <v>800</v>
+        <v>860</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8829,7 +8856,7 @@
         <v>710</v>
       </c>
       <c r="B711" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8845,7 +8872,7 @@
         <v>712</v>
       </c>
       <c r="B713" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8853,7 +8880,7 @@
         <v>713</v>
       </c>
       <c r="B714" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8861,7 +8888,7 @@
         <v>714</v>
       </c>
       <c r="B715" s="1">
-        <v>720</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8869,7 +8896,7 @@
         <v>715</v>
       </c>
       <c r="B716" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8877,7 +8904,7 @@
         <v>716</v>
       </c>
       <c r="B717" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8885,7 +8912,7 @@
         <v>717</v>
       </c>
       <c r="B718" s="1">
-        <v>880</v>
+        <v>800</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8893,7 +8920,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8901,7 +8928,7 @@
         <v>719</v>
       </c>
       <c r="B720" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8909,7 +8936,7 @@
         <v>720</v>
       </c>
       <c r="B721" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8917,7 +8944,7 @@
         <v>721</v>
       </c>
       <c r="B722" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8925,7 +8952,7 @@
         <v>722</v>
       </c>
       <c r="B723" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8933,7 +8960,7 @@
         <v>723</v>
       </c>
       <c r="B724" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8941,7 +8968,7 @@
         <v>724</v>
       </c>
       <c r="B725" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8949,7 +8976,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="1">
-        <v>800</v>
+        <v>880</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8957,7 +8984,7 @@
         <v>726</v>
       </c>
       <c r="B727" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8965,7 +8992,7 @@
         <v>727</v>
       </c>
       <c r="B728" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8973,7 +9000,7 @@
         <v>728</v>
       </c>
       <c r="B729" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8981,7 +9008,7 @@
         <v>729</v>
       </c>
       <c r="B730" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8989,7 +9016,7 @@
         <v>730</v>
       </c>
       <c r="B731" s="1">
-        <v>960</v>
+        <v>600</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8997,7 +9024,7 @@
         <v>731</v>
       </c>
       <c r="B732" s="1">
-        <v>1020</v>
+        <v>800</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -9005,7 +9032,7 @@
         <v>732</v>
       </c>
       <c r="B733" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -9013,7 +9040,7 @@
         <v>733</v>
       </c>
       <c r="B734" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -9021,7 +9048,7 @@
         <v>734</v>
       </c>
       <c r="B735" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -9029,7 +9056,7 @@
         <v>735</v>
       </c>
       <c r="B736" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -9037,7 +9064,7 @@
         <v>736</v>
       </c>
       <c r="B737" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -9053,7 +9080,7 @@
         <v>738</v>
       </c>
       <c r="B739" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="740" spans="1:2">
@@ -9061,7 +9088,7 @@
         <v>739</v>
       </c>
       <c r="B740" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -9069,7 +9096,7 @@
         <v>740</v>
       </c>
       <c r="B741" s="1">
-        <v>1000</v>
+        <v>880</v>
       </c>
     </row>
     <row r="742" spans="1:2">
@@ -9077,7 +9104,7 @@
         <v>741</v>
       </c>
       <c r="B742" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -9085,7 +9112,7 @@
         <v>742</v>
       </c>
       <c r="B743" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="744" spans="1:2">
@@ -9093,7 +9120,7 @@
         <v>743</v>
       </c>
       <c r="B744" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="745" spans="1:2">
@@ -9101,7 +9128,7 @@
         <v>744</v>
       </c>
       <c r="B745" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -9109,7 +9136,7 @@
         <v>745</v>
       </c>
       <c r="B746" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="747" spans="1:2">
@@ -9117,7 +9144,7 @@
         <v>746</v>
       </c>
       <c r="B747" s="1">
-        <v>760</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="748" spans="1:2">
@@ -9125,7 +9152,7 @@
         <v>747</v>
       </c>
       <c r="B748" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="749" spans="1:2">
@@ -9133,7 +9160,7 @@
         <v>748</v>
       </c>
       <c r="B749" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -9141,7 +9168,7 @@
         <v>749</v>
       </c>
       <c r="B750" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="751" spans="1:2">
@@ -9149,7 +9176,7 @@
         <v>750</v>
       </c>
       <c r="B751" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="752" spans="1:2">
@@ -9157,7 +9184,7 @@
         <v>751</v>
       </c>
       <c r="B752" s="1">
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="753" spans="1:2">
@@ -9165,7 +9192,7 @@
         <v>752</v>
       </c>
       <c r="B753" s="1">
-        <v>920</v>
+        <v>720</v>
       </c>
     </row>
     <row r="754" spans="1:2">
@@ -9173,7 +9200,7 @@
         <v>753</v>
       </c>
       <c r="B754" s="1">
-        <v>860</v>
+        <v>680</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -9181,7 +9208,7 @@
         <v>754</v>
       </c>
       <c r="B755" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="756" spans="1:2">
@@ -9189,7 +9216,7 @@
         <v>755</v>
       </c>
       <c r="B756" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="757" spans="1:2">
@@ -9197,7 +9224,7 @@
         <v>756</v>
       </c>
       <c r="B757" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="758" spans="1:2">
@@ -9205,7 +9232,7 @@
         <v>757</v>
       </c>
       <c r="B758" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="759" spans="1:2">
@@ -9213,7 +9240,7 @@
         <v>758</v>
       </c>
       <c r="B759" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="760" spans="1:2">
@@ -9221,7 +9248,7 @@
         <v>759</v>
       </c>
       <c r="B760" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="761" spans="1:2">
@@ -9229,7 +9256,7 @@
         <v>760</v>
       </c>
       <c r="B761" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="762" spans="1:2">
@@ -9237,7 +9264,7 @@
         <v>761</v>
       </c>
       <c r="B762" s="1">
-        <v>940</v>
+        <v>860</v>
       </c>
     </row>
     <row r="763" spans="1:2">
@@ -9245,7 +9272,7 @@
         <v>762</v>
       </c>
       <c r="B763" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="764" spans="1:2">
@@ -9253,7 +9280,7 @@
         <v>763</v>
       </c>
       <c r="B764" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="765" spans="1:2">
@@ -9261,7 +9288,7 @@
         <v>764</v>
       </c>
       <c r="B765" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="766" spans="1:2">
@@ -9269,7 +9296,7 @@
         <v>765</v>
       </c>
       <c r="B766" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="767" spans="1:2">
@@ -9277,7 +9304,7 @@
         <v>766</v>
       </c>
       <c r="B767" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="768" spans="1:2">
@@ -9285,7 +9312,7 @@
         <v>767</v>
       </c>
       <c r="B768" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="769" spans="1:2">
@@ -9293,7 +9320,7 @@
         <v>768</v>
       </c>
       <c r="B769" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="770" spans="1:2">
@@ -9301,7 +9328,7 @@
         <v>769</v>
       </c>
       <c r="B770" s="1">
-        <v>780</v>
+        <v>940</v>
       </c>
     </row>
     <row r="771" spans="1:2">
@@ -9309,7 +9336,7 @@
         <v>770</v>
       </c>
       <c r="B771" s="1">
-        <v>880</v>
+        <v>820</v>
       </c>
     </row>
     <row r="772" spans="1:2">
@@ -9317,7 +9344,7 @@
         <v>771</v>
       </c>
       <c r="B772" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="773" spans="1:2">
@@ -9325,7 +9352,7 @@
         <v>772</v>
       </c>
       <c r="B773" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="774" spans="1:2">
@@ -9341,7 +9368,7 @@
         <v>774</v>
       </c>
       <c r="B775" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="776" spans="1:2">
@@ -9349,7 +9376,7 @@
         <v>775</v>
       </c>
       <c r="B776" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="777" spans="1:2">
@@ -9357,7 +9384,7 @@
         <v>776</v>
       </c>
       <c r="B777" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="778" spans="1:2">
@@ -9365,7 +9392,7 @@
         <v>777</v>
       </c>
       <c r="B778" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="779" spans="1:2">
@@ -9373,7 +9400,7 @@
         <v>778</v>
       </c>
       <c r="B779" s="1">
-        <v>900</v>
+        <v>880</v>
       </c>
     </row>
     <row r="780" spans="1:2">
@@ -9381,7 +9408,7 @@
         <v>779</v>
       </c>
       <c r="B780" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="781" spans="1:2">
@@ -9389,7 +9416,7 @@
         <v>780</v>
       </c>
       <c r="B781" s="1">
-        <v>440</v>
+        <v>780</v>
       </c>
     </row>
     <row r="782" spans="1:2">
@@ -9397,7 +9424,7 @@
         <v>781</v>
       </c>
       <c r="B782" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="783" spans="1:2">
@@ -9405,7 +9432,7 @@
         <v>782</v>
       </c>
       <c r="B783" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="784" spans="1:2">
@@ -9413,7 +9440,7 @@
         <v>783</v>
       </c>
       <c r="B784" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="785" spans="1:2">
@@ -9421,7 +9448,7 @@
         <v>784</v>
       </c>
       <c r="B785" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="786" spans="1:2">
@@ -9429,7 +9456,7 @@
         <v>785</v>
       </c>
       <c r="B786" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="787" spans="1:2">
@@ -9437,7 +9464,7 @@
         <v>786</v>
       </c>
       <c r="B787" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="788" spans="1:2">
@@ -9445,7 +9472,7 @@
         <v>787</v>
       </c>
       <c r="B788" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="789" spans="1:2">
@@ -9453,7 +9480,7 @@
         <v>788</v>
       </c>
       <c r="B789" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="790" spans="1:2">
@@ -9461,7 +9488,7 @@
         <v>789</v>
       </c>
       <c r="B790" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="791" spans="1:2">
@@ -9469,7 +9496,7 @@
         <v>790</v>
       </c>
       <c r="B791" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="792" spans="1:2">
@@ -9477,7 +9504,7 @@
         <v>791</v>
       </c>
       <c r="B792" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="793" spans="1:2">
@@ -9485,7 +9512,7 @@
         <v>792</v>
       </c>
       <c r="B793" s="1">
-        <v>880</v>
+        <v>800</v>
       </c>
     </row>
     <row r="794" spans="1:2">
@@ -9493,7 +9520,7 @@
         <v>793</v>
       </c>
       <c r="B794" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="795" spans="1:2">
@@ -9501,7 +9528,7 @@
         <v>794</v>
       </c>
       <c r="B795" s="1">
-        <v>920</v>
+        <v>600</v>
       </c>
     </row>
     <row r="796" spans="1:2">
@@ -9509,7 +9536,7 @@
         <v>795</v>
       </c>
       <c r="B796" s="1">
-        <v>800</v>
+        <v>560</v>
       </c>
     </row>
     <row r="797" spans="1:2">
@@ -9517,7 +9544,7 @@
         <v>796</v>
       </c>
       <c r="B797" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="798" spans="1:2">
@@ -9525,7 +9552,7 @@
         <v>797</v>
       </c>
       <c r="B798" s="1">
-        <v>980</v>
+        <v>840</v>
       </c>
     </row>
     <row r="799" spans="1:2">
@@ -9533,7 +9560,7 @@
         <v>798</v>
       </c>
       <c r="B799" s="1">
-        <v>920</v>
+        <v>880</v>
       </c>
     </row>
     <row r="800" spans="1:2">
@@ -9541,7 +9568,7 @@
         <v>799</v>
       </c>
       <c r="B800" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="801" spans="1:2">
@@ -9549,7 +9576,7 @@
         <v>800</v>
       </c>
       <c r="B801" s="1">
-        <v>860</v>
+        <v>880</v>
       </c>
     </row>
     <row r="802" spans="1:2">
@@ -9557,7 +9584,7 @@
         <v>801</v>
       </c>
       <c r="B802" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="803" spans="1:2">
@@ -9565,7 +9592,7 @@
         <v>802</v>
       </c>
       <c r="B803" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="804" spans="1:2">
@@ -9573,7 +9600,7 @@
         <v>803</v>
       </c>
       <c r="B804" s="1">
-        <v>820</v>
+        <v>800</v>
       </c>
     </row>
     <row r="805" spans="1:2">
@@ -9581,7 +9608,7 @@
         <v>804</v>
       </c>
       <c r="B805" s="1">
-        <v>960</v>
+        <v>940</v>
       </c>
     </row>
     <row r="806" spans="1:2">
@@ -9589,7 +9616,7 @@
         <v>805</v>
       </c>
       <c r="B806" s="1">
-        <v>740</v>
+        <v>980</v>
       </c>
     </row>
     <row r="807" spans="1:2">
@@ -9597,7 +9624,7 @@
         <v>806</v>
       </c>
       <c r="B807" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="808" spans="1:2">
@@ -9605,7 +9632,7 @@
         <v>807</v>
       </c>
       <c r="B808" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="809" spans="1:2">
@@ -9613,7 +9640,7 @@
         <v>808</v>
       </c>
       <c r="B809" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="810" spans="1:2">
@@ -9621,7 +9648,7 @@
         <v>809</v>
       </c>
       <c r="B810" s="1">
-        <v>660</v>
+        <v>920</v>
       </c>
     </row>
     <row r="811" spans="1:2">
@@ -9629,7 +9656,7 @@
         <v>810</v>
       </c>
       <c r="B811" s="1">
-        <v>840</v>
+        <v>680</v>
       </c>
     </row>
     <row r="812" spans="1:2">
@@ -9637,7 +9664,7 @@
         <v>811</v>
       </c>
       <c r="B812" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="813" spans="1:2">
@@ -9645,7 +9672,7 @@
         <v>812</v>
       </c>
       <c r="B813" s="1">
-        <v>820</v>
+        <v>960</v>
       </c>
     </row>
     <row r="814" spans="1:2">
@@ -9653,7 +9680,7 @@
         <v>813</v>
       </c>
       <c r="B814" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="815" spans="1:2">
@@ -9661,7 +9688,7 @@
         <v>814</v>
       </c>
       <c r="B815" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="816" spans="1:2">
@@ -9669,7 +9696,7 @@
         <v>815</v>
       </c>
       <c r="B816" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="817" spans="1:2">
@@ -9677,7 +9704,7 @@
         <v>816</v>
       </c>
       <c r="B817" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="818" spans="1:2">
@@ -9685,7 +9712,7 @@
         <v>817</v>
       </c>
       <c r="B818" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="819" spans="1:2">
@@ -9693,7 +9720,7 @@
         <v>818</v>
       </c>
       <c r="B819" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="820" spans="1:2">
@@ -9701,7 +9728,7 @@
         <v>819</v>
       </c>
       <c r="B820" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="821" spans="1:2">
@@ -9709,7 +9736,7 @@
         <v>820</v>
       </c>
       <c r="B821" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="822" spans="1:2">
@@ -9717,7 +9744,7 @@
         <v>821</v>
       </c>
       <c r="B822" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="823" spans="1:2">
@@ -9725,7 +9752,7 @@
         <v>822</v>
       </c>
       <c r="B823" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="824" spans="1:2">
@@ -9733,7 +9760,7 @@
         <v>823</v>
       </c>
       <c r="B824" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="825" spans="1:2">
@@ -9741,7 +9768,7 @@
         <v>824</v>
       </c>
       <c r="B825" s="1">
-        <v>860</v>
+        <v>600</v>
       </c>
     </row>
     <row r="826" spans="1:2">
@@ -9749,7 +9776,7 @@
         <v>825</v>
       </c>
       <c r="B826" s="1">
-        <v>680</v>
+        <v>840</v>
       </c>
     </row>
     <row r="827" spans="1:2">
@@ -9757,7 +9784,7 @@
         <v>826</v>
       </c>
       <c r="B827" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="828" spans="1:2">
@@ -9765,7 +9792,7 @@
         <v>827</v>
       </c>
       <c r="B828" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="829" spans="1:2">
@@ -9773,7 +9800,7 @@
         <v>828</v>
       </c>
       <c r="B829" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="830" spans="1:2">
@@ -9781,7 +9808,7 @@
         <v>829</v>
       </c>
       <c r="B830" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="831" spans="1:2">
@@ -9789,7 +9816,7 @@
         <v>830</v>
       </c>
       <c r="B831" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="832" spans="1:2">
@@ -9797,7 +9824,7 @@
         <v>831</v>
       </c>
       <c r="B832" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="833" spans="1:2">
@@ -9805,7 +9832,7 @@
         <v>832</v>
       </c>
       <c r="B833" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="834" spans="1:2">
@@ -9813,7 +9840,7 @@
         <v>833</v>
       </c>
       <c r="B834" s="1">
-        <v>500</v>
+        <v>860</v>
       </c>
     </row>
     <row r="835" spans="1:2">
@@ -9821,7 +9848,7 @@
         <v>834</v>
       </c>
       <c r="B835" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="836" spans="1:2">
@@ -9829,7 +9856,7 @@
         <v>835</v>
       </c>
       <c r="B836" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="837" spans="1:2">
@@ -9837,7 +9864,7 @@
         <v>836</v>
       </c>
       <c r="B837" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="838" spans="1:2">
@@ -9845,7 +9872,7 @@
         <v>837</v>
       </c>
       <c r="B838" s="1">
-        <v>940</v>
+        <v>820</v>
       </c>
     </row>
     <row r="839" spans="1:2">
@@ -9853,7 +9880,7 @@
         <v>838</v>
       </c>
       <c r="B839" s="1">
-        <v>1040</v>
+        <v>720</v>
       </c>
     </row>
     <row r="840" spans="1:2">
@@ -9861,7 +9888,7 @@
         <v>839</v>
       </c>
       <c r="B840" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="841" spans="1:2">
@@ -9869,7 +9896,7 @@
         <v>840</v>
       </c>
       <c r="B841" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="842" spans="1:2">
@@ -9877,7 +9904,7 @@
         <v>841</v>
       </c>
       <c r="B842" s="1">
-        <v>1040</v>
+        <v>600</v>
       </c>
     </row>
     <row r="843" spans="1:2">
@@ -9885,7 +9912,7 @@
         <v>842</v>
       </c>
       <c r="B843" s="1">
-        <v>1100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="844" spans="1:2">
@@ -9893,7 +9920,7 @@
         <v>843</v>
       </c>
       <c r="B844" s="1">
-        <v>1000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="845" spans="1:2">
@@ -9901,7 +9928,7 @@
         <v>844</v>
       </c>
       <c r="B845" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="846" spans="1:2">
@@ -9909,7 +9936,7 @@
         <v>845</v>
       </c>
       <c r="B846" s="1">
-        <v>960</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="847" spans="1:2">
@@ -9917,7 +9944,7 @@
         <v>846</v>
       </c>
       <c r="B847" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="848" spans="1:2">
@@ -9925,7 +9952,7 @@
         <v>847</v>
       </c>
       <c r="B848" s="1">
-        <v>740</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="849" spans="1:2">
@@ -9933,7 +9960,7 @@
         <v>848</v>
       </c>
       <c r="B849" s="1">
-        <v>820</v>
+        <v>940</v>
       </c>
     </row>
     <row r="850" spans="1:2">
@@ -9941,7 +9968,7 @@
         <v>849</v>
       </c>
       <c r="B850" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="851" spans="1:2">
@@ -9949,7 +9976,7 @@
         <v>850</v>
       </c>
       <c r="B851" s="1">
-        <v>440</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="852" spans="1:2">
@@ -9957,7 +9984,7 @@
         <v>851</v>
       </c>
       <c r="B852" s="1">
-        <v>500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="853" spans="1:2">
@@ -9965,7 +9992,7 @@
         <v>852</v>
       </c>
       <c r="B853" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="854" spans="1:2">
@@ -9973,7 +10000,7 @@
         <v>853</v>
       </c>
       <c r="B854" s="1">
-        <v>560</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="855" spans="1:2">
@@ -9981,7 +10008,7 @@
         <v>854</v>
       </c>
       <c r="B855" s="1">
-        <v>500</v>
+        <v>960</v>
       </c>
     </row>
     <row r="856" spans="1:2">
@@ -9989,7 +10016,7 @@
         <v>855</v>
       </c>
       <c r="B856" s="1">
-        <v>820</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="857" spans="1:2">
@@ -9997,7 +10024,7 @@
         <v>856</v>
       </c>
       <c r="B857" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="858" spans="1:2">
@@ -10005,7 +10032,7 @@
         <v>857</v>
       </c>
       <c r="B858" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="859" spans="1:2">
@@ -10021,7 +10048,7 @@
         <v>859</v>
       </c>
       <c r="B860" s="1">
-        <v>400</v>
+        <v>440</v>
       </c>
     </row>
     <row r="861" spans="1:2">
@@ -10029,7 +10056,7 @@
         <v>860</v>
       </c>
       <c r="B861" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="862" spans="1:2">
@@ -10037,7 +10064,7 @@
         <v>861</v>
       </c>
       <c r="B862" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="863" spans="1:2">
@@ -10045,7 +10072,7 @@
         <v>862</v>
       </c>
       <c r="B863" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="864" spans="1:2">
@@ -10053,7 +10080,7 @@
         <v>863</v>
       </c>
       <c r="B864" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="865" spans="1:2">
@@ -10061,7 +10088,7 @@
         <v>864</v>
       </c>
       <c r="B865" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="866" spans="1:2">
@@ -10069,7 +10096,7 @@
         <v>865</v>
       </c>
       <c r="B866" s="1">
-        <v>520</v>
+        <v>820</v>
       </c>
     </row>
     <row r="867" spans="1:2">
@@ -10077,7 +10104,7 @@
         <v>866</v>
       </c>
       <c r="B867" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="868" spans="1:2">
@@ -10085,7 +10112,7 @@
         <v>867</v>
       </c>
       <c r="B868" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="869" spans="1:2">
@@ -10093,7 +10120,7 @@
         <v>868</v>
       </c>
       <c r="B869" s="1">
-        <v>860</v>
+        <v>400</v>
       </c>
     </row>
     <row r="870" spans="1:2">
@@ -10101,7 +10128,7 @@
         <v>869</v>
       </c>
       <c r="B870" s="1">
-        <v>680</v>
+        <v>400</v>
       </c>
     </row>
     <row r="871" spans="1:2">
@@ -10109,7 +10136,7 @@
         <v>870</v>
       </c>
       <c r="B871" s="1">
-        <v>740</v>
+        <v>380</v>
       </c>
     </row>
     <row r="872" spans="1:2">
@@ -10117,7 +10144,7 @@
         <v>871</v>
       </c>
       <c r="B872" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="873" spans="1:2">
@@ -10125,7 +10152,7 @@
         <v>872</v>
       </c>
       <c r="B873" s="1">
-        <v>780</v>
+        <v>380</v>
       </c>
     </row>
     <row r="874" spans="1:2">
@@ -10133,7 +10160,7 @@
         <v>873</v>
       </c>
       <c r="B874" s="1">
-        <v>820</v>
+        <v>380</v>
       </c>
     </row>
     <row r="875" spans="1:2">
@@ -10141,7 +10168,7 @@
         <v>874</v>
       </c>
       <c r="B875" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="876" spans="1:2">
@@ -10149,7 +10176,7 @@
         <v>875</v>
       </c>
       <c r="B876" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="877" spans="1:2">
@@ -10157,7 +10184,7 @@
         <v>876</v>
       </c>
       <c r="B877" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="878" spans="1:2">
@@ -10165,7 +10192,7 @@
         <v>877</v>
       </c>
       <c r="B878" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="879" spans="1:2">
@@ -10173,7 +10200,7 @@
         <v>878</v>
       </c>
       <c r="B879" s="1">
-        <v>500</v>
+        <v>680</v>
       </c>
     </row>
     <row r="880" spans="1:2">
@@ -10181,7 +10208,7 @@
         <v>879</v>
       </c>
       <c r="B880" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="881" spans="1:2">
@@ -10189,7 +10216,7 @@
         <v>880</v>
       </c>
       <c r="B881" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="882" spans="1:2">
@@ -10197,7 +10224,7 @@
         <v>881</v>
       </c>
       <c r="B882" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="883" spans="1:2">
@@ -10205,7 +10232,7 @@
         <v>882</v>
       </c>
       <c r="B883" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="884" spans="1:2">
@@ -10213,7 +10240,7 @@
         <v>883</v>
       </c>
       <c r="B884" s="1">
-        <v>920</v>
+        <v>720</v>
       </c>
     </row>
     <row r="885" spans="1:2">
@@ -10221,7 +10248,7 @@
         <v>884</v>
       </c>
       <c r="B885" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="886" spans="1:2">
@@ -10229,7 +10256,7 @@
         <v>885</v>
       </c>
       <c r="B886" s="1">
-        <v>940</v>
+        <v>600</v>
       </c>
     </row>
     <row r="887" spans="1:2">
@@ -10237,7 +10264,7 @@
         <v>886</v>
       </c>
       <c r="B887" s="1">
-        <v>1040</v>
+        <v>600</v>
       </c>
     </row>
     <row r="888" spans="1:2">
@@ -10245,7 +10272,7 @@
         <v>887</v>
       </c>
       <c r="B888" s="1">
-        <v>940</v>
+        <v>500</v>
       </c>
     </row>
     <row r="889" spans="1:2">
@@ -10253,7 +10280,7 @@
         <v>888</v>
       </c>
       <c r="B889" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="890" spans="1:2">
@@ -10261,7 +10288,7 @@
         <v>889</v>
       </c>
       <c r="B890" s="1">
-        <v>1040</v>
+        <v>840</v>
       </c>
     </row>
     <row r="891" spans="1:2">
@@ -10269,7 +10296,7 @@
         <v>890</v>
       </c>
       <c r="B891" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="892" spans="1:2">
@@ -10277,7 +10304,7 @@
         <v>891</v>
       </c>
       <c r="B892" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="893" spans="1:2">
@@ -10285,7 +10312,7 @@
         <v>892</v>
       </c>
       <c r="B893" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="894" spans="1:2">
@@ -10293,7 +10320,7 @@
         <v>893</v>
       </c>
       <c r="B894" s="1">
-        <v>960</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="895" spans="1:2">
@@ -10301,7 +10328,7 @@
         <v>894</v>
       </c>
       <c r="B895" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="896" spans="1:2">
@@ -10309,7 +10336,7 @@
         <v>895</v>
       </c>
       <c r="B896" s="1">
-        <v>740</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="897" spans="1:2">
@@ -10317,7 +10344,7 @@
         <v>896</v>
       </c>
       <c r="B897" s="1">
-        <v>820</v>
+        <v>940</v>
       </c>
     </row>
     <row r="898" spans="1:2">
@@ -10325,7 +10352,7 @@
         <v>897</v>
       </c>
       <c r="B898" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="899" spans="1:2">
@@ -10333,7 +10360,7 @@
         <v>898</v>
       </c>
       <c r="B899" s="1">
-        <v>440</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="900" spans="1:2">
@@ -10341,7 +10368,7 @@
         <v>899</v>
       </c>
       <c r="B900" s="1">
-        <v>500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="901" spans="1:2">
@@ -10349,7 +10376,7 @@
         <v>900</v>
       </c>
       <c r="B901" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="902" spans="1:2">
@@ -10357,7 +10384,7 @@
         <v>901</v>
       </c>
       <c r="B902" s="1">
-        <v>560</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="903" spans="1:2">
@@ -10365,7 +10392,7 @@
         <v>902</v>
       </c>
       <c r="B903" s="1">
-        <v>500</v>
+        <v>960</v>
       </c>
     </row>
     <row r="904" spans="1:2">
@@ -10373,7 +10400,7 @@
         <v>903</v>
       </c>
       <c r="B904" s="1">
-        <v>820</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="905" spans="1:2">
@@ -10381,7 +10408,7 @@
         <v>904</v>
       </c>
       <c r="B905" s="1">
-        <v>380</v>
+        <v>740</v>
       </c>
     </row>
     <row r="906" spans="1:2">
@@ -10389,7 +10416,7 @@
         <v>905</v>
       </c>
       <c r="B906" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="907" spans="1:2">
@@ -10397,7 +10424,7 @@
         <v>906</v>
       </c>
       <c r="B907" s="1">
-        <v>380</v>
+        <v>840</v>
       </c>
     </row>
     <row r="908" spans="1:2">
@@ -10405,7 +10432,7 @@
         <v>907</v>
       </c>
       <c r="B908" s="1">
-        <v>480</v>
+        <v>440</v>
       </c>
     </row>
     <row r="909" spans="1:2">
@@ -10413,7 +10440,7 @@
         <v>908</v>
       </c>
       <c r="B909" s="1">
-        <v>480</v>
+        <v>500</v>
       </c>
     </row>
     <row r="910" spans="1:2">
@@ -10421,7 +10448,7 @@
         <v>909</v>
       </c>
       <c r="B910" s="1">
-        <v>480</v>
+        <v>440</v>
       </c>
     </row>
     <row r="911" spans="1:2">
@@ -10429,7 +10456,7 @@
         <v>910</v>
       </c>
       <c r="B911" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="912" spans="1:2">
@@ -10437,7 +10464,7 @@
         <v>911</v>
       </c>
       <c r="B912" s="1">
-        <v>520</v>
+        <v>500</v>
       </c>
     </row>
     <row r="913" spans="1:2">
@@ -10445,7 +10472,7 @@
         <v>912</v>
       </c>
       <c r="B913" s="1">
-        <v>440</v>
+        <v>820</v>
       </c>
     </row>
     <row r="914" spans="1:2">
@@ -10461,7 +10488,7 @@
         <v>914</v>
       </c>
       <c r="B915" s="1">
-        <v>600</v>
+        <v>380</v>
       </c>
     </row>
     <row r="916" spans="1:2">
@@ -10469,7 +10496,7 @@
         <v>915</v>
       </c>
       <c r="B916" s="1">
-        <v>820</v>
+        <v>380</v>
       </c>
     </row>
     <row r="917" spans="1:2">
@@ -10477,7 +10504,7 @@
         <v>916</v>
       </c>
       <c r="B917" s="1">
-        <v>660</v>
+        <v>480</v>
       </c>
     </row>
     <row r="918" spans="1:2">
@@ -10485,7 +10512,7 @@
         <v>917</v>
       </c>
       <c r="B918" s="1">
-        <v>580</v>
+        <v>480</v>
       </c>
     </row>
     <row r="919" spans="1:2">
@@ -10493,7 +10520,7 @@
         <v>918</v>
       </c>
       <c r="B919" s="1">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="920" spans="1:2">
@@ -10501,7 +10528,7 @@
         <v>919</v>
       </c>
       <c r="B920" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="921" spans="1:2">
@@ -10509,7 +10536,7 @@
         <v>920</v>
       </c>
       <c r="B921" s="1">
-        <v>620</v>
+        <v>520</v>
       </c>
     </row>
     <row r="922" spans="1:2">
@@ -10517,7 +10544,7 @@
         <v>921</v>
       </c>
       <c r="B922" s="1">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="923" spans="1:2">
@@ -10525,6 +10552,78 @@
         <v>922</v>
       </c>
       <c r="B923" s="1">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="924" spans="1:2">
+      <c r="A924" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="B924" s="1">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="925" spans="1:2">
+      <c r="A925" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="B925" s="1">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="926" spans="1:2">
+      <c r="A926" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="B926" s="1">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="927" spans="1:2">
+      <c r="A927" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="B927" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="928" spans="1:2">
+      <c r="A928" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="B928" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="929" spans="1:2">
+      <c r="A929" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="B929" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="930" spans="1:2">
+      <c r="A930" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="B930" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="931" spans="1:2">
+      <c r="A931" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="B931" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="932" spans="1:2">
+      <c r="A932" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="B932" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="934">
   <si>
     <t>Наименование</t>
   </si>
@@ -1301,6 +1301,9 @@
     <t>Velka Morava - Codename LBD (NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Velka Morava - Nunki (Imperial Stout), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Velka Morava - Take Five (APA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -2325,6 +2328,9 @@
   </si>
   <si>
     <t>вынос_Velka Morava - Jungle Boogie (NEIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Velka Morava - Nunki (Imperial Stout), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_Velka Morava - Take Five (APA), РОЗЛИВ, Россия</t>
@@ -3164,7 +3170,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B932"/>
+  <dimension ref="A1:B934"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -6600,7 +6606,7 @@
         <v>428</v>
       </c>
       <c r="B429" s="1">
-        <v>820</v>
+        <v>980</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6608,7 +6614,7 @@
         <v>429</v>
       </c>
       <c r="B430" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6616,7 +6622,7 @@
         <v>430</v>
       </c>
       <c r="B431" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6632,7 +6638,7 @@
         <v>432</v>
       </c>
       <c r="B433" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6648,7 +6654,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6664,7 +6670,7 @@
         <v>436</v>
       </c>
       <c r="B437" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6672,7 +6678,7 @@
         <v>437</v>
       </c>
       <c r="B438" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6680,7 +6686,7 @@
         <v>438</v>
       </c>
       <c r="B439" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6688,7 +6694,7 @@
         <v>439</v>
       </c>
       <c r="B440" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6696,7 +6702,7 @@
         <v>440</v>
       </c>
       <c r="B441" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6704,7 +6710,7 @@
         <v>441</v>
       </c>
       <c r="B442" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6712,7 +6718,7 @@
         <v>442</v>
       </c>
       <c r="B443" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6728,7 +6734,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6736,7 +6742,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6744,7 +6750,7 @@
         <v>446</v>
       </c>
       <c r="B447" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6752,7 +6758,7 @@
         <v>447</v>
       </c>
       <c r="B448" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6760,7 +6766,7 @@
         <v>448</v>
       </c>
       <c r="B449" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6768,7 +6774,7 @@
         <v>449</v>
       </c>
       <c r="B450" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6776,7 +6782,7 @@
         <v>450</v>
       </c>
       <c r="B451" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6784,7 +6790,7 @@
         <v>451</v>
       </c>
       <c r="B452" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6792,7 +6798,7 @@
         <v>452</v>
       </c>
       <c r="B453" s="1">
-        <v>700</v>
+        <v>440</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6800,7 +6806,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6816,7 +6822,7 @@
         <v>455</v>
       </c>
       <c r="B456" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6824,7 +6830,7 @@
         <v>456</v>
       </c>
       <c r="B457" s="1">
-        <v>560</v>
+        <v>800</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6832,7 +6838,7 @@
         <v>457</v>
       </c>
       <c r="B458" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6840,7 +6846,7 @@
         <v>458</v>
       </c>
       <c r="B459" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6848,7 +6854,7 @@
         <v>459</v>
       </c>
       <c r="B460" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6856,7 +6862,7 @@
         <v>460</v>
       </c>
       <c r="B461" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6864,7 +6870,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6872,7 +6878,7 @@
         <v>462</v>
       </c>
       <c r="B463" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6880,7 +6886,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="1">
-        <v>720</v>
+        <v>620</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6888,7 +6894,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6896,7 +6902,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6912,7 +6918,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6920,7 +6926,7 @@
         <v>468</v>
       </c>
       <c r="B469" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6928,7 +6934,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6936,7 +6942,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="1">
-        <v>900</v>
+        <v>880</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6944,7 +6950,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6952,7 +6958,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6960,7 +6966,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6968,7 +6974,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="1">
-        <v>800</v>
+        <v>920</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6976,7 +6982,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6984,7 +6990,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6992,7 +6998,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="1">
-        <v>980</v>
+        <v>940</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -7000,7 +7006,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -7008,7 +7014,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -7016,7 +7022,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -7024,7 +7030,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -7032,7 +7038,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -7048,7 +7054,7 @@
         <v>484</v>
       </c>
       <c r="B485" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -7056,7 +7062,7 @@
         <v>485</v>
       </c>
       <c r="B486" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -7064,7 +7070,7 @@
         <v>486</v>
       </c>
       <c r="B487" s="1">
-        <v>640</v>
+        <v>920</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -7072,7 +7078,7 @@
         <v>487</v>
       </c>
       <c r="B488" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -7080,7 +7086,7 @@
         <v>488</v>
       </c>
       <c r="B489" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -7088,7 +7094,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="1">
-        <v>960</v>
+        <v>820</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -7096,7 +7102,7 @@
         <v>490</v>
       </c>
       <c r="B491" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -7104,7 +7110,7 @@
         <v>491</v>
       </c>
       <c r="B492" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -7112,7 +7118,7 @@
         <v>492</v>
       </c>
       <c r="B493" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -7120,7 +7126,7 @@
         <v>493</v>
       </c>
       <c r="B494" s="1">
-        <v>860</v>
+        <v>640</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -7128,7 +7134,7 @@
         <v>494</v>
       </c>
       <c r="B495" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -7136,7 +7142,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -7144,7 +7150,7 @@
         <v>496</v>
       </c>
       <c r="B497" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -7152,7 +7158,7 @@
         <v>497</v>
       </c>
       <c r="B498" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -7160,7 +7166,7 @@
         <v>498</v>
       </c>
       <c r="B499" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -7168,7 +7174,7 @@
         <v>499</v>
       </c>
       <c r="B500" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -7176,7 +7182,7 @@
         <v>500</v>
       </c>
       <c r="B501" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -7184,7 +7190,7 @@
         <v>501</v>
       </c>
       <c r="B502" s="1">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -7192,7 +7198,7 @@
         <v>502</v>
       </c>
       <c r="B503" s="1">
-        <v>620</v>
+        <v>480</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -7200,7 +7206,7 @@
         <v>503</v>
       </c>
       <c r="B504" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -7208,7 +7214,7 @@
         <v>504</v>
       </c>
       <c r="B505" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -7216,7 +7222,7 @@
         <v>505</v>
       </c>
       <c r="B506" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -7224,7 +7230,7 @@
         <v>506</v>
       </c>
       <c r="B507" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -7232,7 +7238,7 @@
         <v>507</v>
       </c>
       <c r="B508" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -7240,7 +7246,7 @@
         <v>508</v>
       </c>
       <c r="B509" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -7248,7 +7254,7 @@
         <v>509</v>
       </c>
       <c r="B510" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -7256,7 +7262,7 @@
         <v>510</v>
       </c>
       <c r="B511" s="1">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -7264,7 +7270,7 @@
         <v>511</v>
       </c>
       <c r="B512" s="1">
-        <v>840</v>
+        <v>480</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -7272,7 +7278,7 @@
         <v>512</v>
       </c>
       <c r="B513" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -7280,7 +7286,7 @@
         <v>513</v>
       </c>
       <c r="B514" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -7288,7 +7294,7 @@
         <v>514</v>
       </c>
       <c r="B515" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -7304,7 +7310,7 @@
         <v>516</v>
       </c>
       <c r="B517" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -7312,7 +7318,7 @@
         <v>517</v>
       </c>
       <c r="B518" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -7320,7 +7326,7 @@
         <v>518</v>
       </c>
       <c r="B519" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -7328,7 +7334,7 @@
         <v>519</v>
       </c>
       <c r="B520" s="1">
-        <v>880</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -7344,7 +7350,7 @@
         <v>521</v>
       </c>
       <c r="B522" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -7352,7 +7358,7 @@
         <v>522</v>
       </c>
       <c r="B523" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -7360,7 +7366,7 @@
         <v>523</v>
       </c>
       <c r="B524" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -7368,7 +7374,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="1">
-        <v>1100</v>
+        <v>660</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -7376,7 +7382,7 @@
         <v>525</v>
       </c>
       <c r="B526" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -7384,7 +7390,7 @@
         <v>526</v>
       </c>
       <c r="B527" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -7392,7 +7398,7 @@
         <v>527</v>
       </c>
       <c r="B528" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -7400,7 +7406,7 @@
         <v>528</v>
       </c>
       <c r="B529" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -7408,7 +7414,7 @@
         <v>529</v>
       </c>
       <c r="B530" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -7424,7 +7430,7 @@
         <v>531</v>
       </c>
       <c r="B532" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -7432,7 +7438,7 @@
         <v>532</v>
       </c>
       <c r="B533" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -7440,7 +7446,7 @@
         <v>533</v>
       </c>
       <c r="B534" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -7448,7 +7454,7 @@
         <v>534</v>
       </c>
       <c r="B535" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -7456,7 +7462,7 @@
         <v>535</v>
       </c>
       <c r="B536" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -7464,7 +7470,7 @@
         <v>536</v>
       </c>
       <c r="B537" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -7480,7 +7486,7 @@
         <v>538</v>
       </c>
       <c r="B539" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -7488,7 +7494,7 @@
         <v>539</v>
       </c>
       <c r="B540" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -7496,7 +7502,7 @@
         <v>540</v>
       </c>
       <c r="B541" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -7504,7 +7510,7 @@
         <v>541</v>
       </c>
       <c r="B542" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -7512,7 +7518,7 @@
         <v>542</v>
       </c>
       <c r="B543" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -7520,7 +7526,7 @@
         <v>543</v>
       </c>
       <c r="B544" s="1">
-        <v>840</v>
+        <v>620</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -7528,7 +7534,7 @@
         <v>544</v>
       </c>
       <c r="B545" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -7536,7 +7542,7 @@
         <v>545</v>
       </c>
       <c r="B546" s="1">
-        <v>1060</v>
+        <v>880</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -7544,7 +7550,7 @@
         <v>546</v>
       </c>
       <c r="B547" s="1">
-        <v>860</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -7560,7 +7566,7 @@
         <v>548</v>
       </c>
       <c r="B549" s="1">
-        <v>800</v>
+        <v>860</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -7568,7 +7574,7 @@
         <v>549</v>
       </c>
       <c r="B550" s="1">
-        <v>860</v>
+        <v>800</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -7576,7 +7582,7 @@
         <v>550</v>
       </c>
       <c r="B551" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -7584,7 +7590,7 @@
         <v>551</v>
       </c>
       <c r="B552" s="1">
-        <v>760</v>
+        <v>960</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7592,7 +7598,7 @@
         <v>552</v>
       </c>
       <c r="B553" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7600,7 +7606,7 @@
         <v>553</v>
       </c>
       <c r="B554" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7608,7 +7614,7 @@
         <v>554</v>
       </c>
       <c r="B555" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7624,7 +7630,7 @@
         <v>556</v>
       </c>
       <c r="B557" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7632,7 +7638,7 @@
         <v>557</v>
       </c>
       <c r="B558" s="1">
-        <v>980</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7640,7 +7646,7 @@
         <v>558</v>
       </c>
       <c r="B559" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7648,7 +7654,7 @@
         <v>559</v>
       </c>
       <c r="B560" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7656,7 +7662,7 @@
         <v>560</v>
       </c>
       <c r="B561" s="1">
-        <v>980</v>
+        <v>920</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7664,7 +7670,7 @@
         <v>561</v>
       </c>
       <c r="B562" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7672,7 +7678,7 @@
         <v>562</v>
       </c>
       <c r="B563" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7680,7 +7686,7 @@
         <v>563</v>
       </c>
       <c r="B564" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7688,7 +7694,7 @@
         <v>564</v>
       </c>
       <c r="B565" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7696,7 +7702,7 @@
         <v>565</v>
       </c>
       <c r="B566" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7704,7 +7710,7 @@
         <v>566</v>
       </c>
       <c r="B567" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7712,7 +7718,7 @@
         <v>567</v>
       </c>
       <c r="B568" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7720,7 +7726,7 @@
         <v>568</v>
       </c>
       <c r="B569" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7728,7 +7734,7 @@
         <v>569</v>
       </c>
       <c r="B570" s="1">
-        <v>980</v>
+        <v>900</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7736,7 +7742,7 @@
         <v>570</v>
       </c>
       <c r="B571" s="1">
-        <v>660</v>
+        <v>980</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7744,7 +7750,7 @@
         <v>571</v>
       </c>
       <c r="B572" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7760,7 +7766,7 @@
         <v>573</v>
       </c>
       <c r="B574" s="1">
-        <v>880</v>
+        <v>700</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7768,7 +7774,7 @@
         <v>574</v>
       </c>
       <c r="B575" s="1">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7776,7 +7782,7 @@
         <v>575</v>
       </c>
       <c r="B576" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7784,7 +7790,7 @@
         <v>576</v>
       </c>
       <c r="B577" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7792,7 +7798,7 @@
         <v>577</v>
       </c>
       <c r="B578" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7800,7 +7806,7 @@
         <v>578</v>
       </c>
       <c r="B579" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7808,7 +7814,7 @@
         <v>579</v>
       </c>
       <c r="B580" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7816,7 +7822,7 @@
         <v>580</v>
       </c>
       <c r="B581" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7824,7 +7830,7 @@
         <v>581</v>
       </c>
       <c r="B582" s="1">
-        <v>640</v>
+        <v>880</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7832,7 +7838,7 @@
         <v>582</v>
       </c>
       <c r="B583" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7840,7 +7846,7 @@
         <v>583</v>
       </c>
       <c r="B584" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7848,7 +7854,7 @@
         <v>584</v>
       </c>
       <c r="B585" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7864,7 +7870,7 @@
         <v>586</v>
       </c>
       <c r="B587" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7872,7 +7878,7 @@
         <v>587</v>
       </c>
       <c r="B588" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7888,7 +7894,7 @@
         <v>589</v>
       </c>
       <c r="B590" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7896,7 +7902,7 @@
         <v>590</v>
       </c>
       <c r="B591" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7904,7 +7910,7 @@
         <v>591</v>
       </c>
       <c r="B592" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7912,7 +7918,7 @@
         <v>592</v>
       </c>
       <c r="B593" s="1">
-        <v>940</v>
+        <v>960</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7920,7 +7926,7 @@
         <v>593</v>
       </c>
       <c r="B594" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7936,7 +7942,7 @@
         <v>595</v>
       </c>
       <c r="B596" s="1">
-        <v>940</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7944,7 +7950,7 @@
         <v>596</v>
       </c>
       <c r="B597" s="1">
-        <v>860</v>
+        <v>940</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7952,7 +7958,7 @@
         <v>597</v>
       </c>
       <c r="B598" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7960,7 +7966,7 @@
         <v>598</v>
       </c>
       <c r="B599" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7968,7 +7974,7 @@
         <v>599</v>
       </c>
       <c r="B600" s="1">
-        <v>960</v>
+        <v>920</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7976,7 +7982,7 @@
         <v>600</v>
       </c>
       <c r="B601" s="1">
-        <v>680</v>
+        <v>960</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7984,7 +7990,7 @@
         <v>601</v>
       </c>
       <c r="B602" s="1">
-        <v>840</v>
+        <v>680</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7992,7 +7998,7 @@
         <v>602</v>
       </c>
       <c r="B603" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -8000,7 +8006,7 @@
         <v>603</v>
       </c>
       <c r="B604" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -8008,7 +8014,7 @@
         <v>604</v>
       </c>
       <c r="B605" s="1">
-        <v>580</v>
+        <v>880</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -8016,7 +8022,7 @@
         <v>605</v>
       </c>
       <c r="B606" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -8024,7 +8030,7 @@
         <v>606</v>
       </c>
       <c r="B607" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -8032,7 +8038,7 @@
         <v>607</v>
       </c>
       <c r="B608" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -8040,7 +8046,7 @@
         <v>608</v>
       </c>
       <c r="B609" s="1">
-        <v>620</v>
+        <v>900</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -8048,7 +8054,7 @@
         <v>609</v>
       </c>
       <c r="B610" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -8056,7 +8062,7 @@
         <v>610</v>
       </c>
       <c r="B611" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -8064,7 +8070,7 @@
         <v>611</v>
       </c>
       <c r="B612" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -8072,7 +8078,7 @@
         <v>612</v>
       </c>
       <c r="B613" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -8080,7 +8086,7 @@
         <v>613</v>
       </c>
       <c r="B614" s="1">
-        <v>900</v>
+        <v>960</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -8088,7 +8094,7 @@
         <v>614</v>
       </c>
       <c r="B615" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -8096,7 +8102,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -8104,7 +8110,7 @@
         <v>616</v>
       </c>
       <c r="B617" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -8112,7 +8118,7 @@
         <v>617</v>
       </c>
       <c r="B618" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -8120,7 +8126,7 @@
         <v>618</v>
       </c>
       <c r="B619" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -8128,7 +8134,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="1">
-        <v>540</v>
+        <v>920</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -8136,7 +8142,7 @@
         <v>620</v>
       </c>
       <c r="B621" s="1">
-        <v>980</v>
+        <v>540</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -8144,7 +8150,7 @@
         <v>621</v>
       </c>
       <c r="B622" s="1">
-        <v>1100</v>
+        <v>980</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -8152,7 +8158,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="1">
-        <v>1060</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -8160,7 +8166,7 @@
         <v>623</v>
       </c>
       <c r="B624" s="1">
-        <v>1000</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -8168,7 +8174,7 @@
         <v>624</v>
       </c>
       <c r="B625" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -8184,7 +8190,7 @@
         <v>626</v>
       </c>
       <c r="B627" s="1">
-        <v>1080</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -8192,7 +8198,7 @@
         <v>627</v>
       </c>
       <c r="B628" s="1">
-        <v>840</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -8208,7 +8214,7 @@
         <v>629</v>
       </c>
       <c r="B630" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -8216,7 +8222,7 @@
         <v>630</v>
       </c>
       <c r="B631" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -8224,7 +8230,7 @@
         <v>631</v>
       </c>
       <c r="B632" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -8232,7 +8238,7 @@
         <v>632</v>
       </c>
       <c r="B633" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -8240,7 +8246,7 @@
         <v>633</v>
       </c>
       <c r="B634" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -8248,7 +8254,7 @@
         <v>634</v>
       </c>
       <c r="B635" s="1">
-        <v>980</v>
+        <v>860</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -8256,7 +8262,7 @@
         <v>635</v>
       </c>
       <c r="B636" s="1">
-        <v>740</v>
+        <v>980</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -8264,7 +8270,7 @@
         <v>636</v>
       </c>
       <c r="B637" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -8272,7 +8278,7 @@
         <v>637</v>
       </c>
       <c r="B638" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -8296,7 +8302,7 @@
         <v>640</v>
       </c>
       <c r="B641" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -8320,7 +8326,7 @@
         <v>643</v>
       </c>
       <c r="B644" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -8328,7 +8334,7 @@
         <v>644</v>
       </c>
       <c r="B645" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -8336,7 +8342,7 @@
         <v>645</v>
       </c>
       <c r="B646" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -8344,7 +8350,7 @@
         <v>646</v>
       </c>
       <c r="B647" s="1">
-        <v>840</v>
+        <v>960</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -8352,7 +8358,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -8360,7 +8366,7 @@
         <v>648</v>
       </c>
       <c r="B649" s="1">
-        <v>980</v>
+        <v>700</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -8368,7 +8374,7 @@
         <v>649</v>
       </c>
       <c r="B650" s="1">
-        <v>720</v>
+        <v>980</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -8376,7 +8382,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -8384,7 +8390,7 @@
         <v>651</v>
       </c>
       <c r="B652" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -8392,7 +8398,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -8400,7 +8406,7 @@
         <v>653</v>
       </c>
       <c r="B654" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -8408,7 +8414,7 @@
         <v>654</v>
       </c>
       <c r="B655" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -8416,7 +8422,7 @@
         <v>655</v>
       </c>
       <c r="B656" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -8424,7 +8430,7 @@
         <v>656</v>
       </c>
       <c r="B657" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -8432,7 +8438,7 @@
         <v>657</v>
       </c>
       <c r="B658" s="1">
-        <v>860</v>
+        <v>680</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -8440,7 +8446,7 @@
         <v>658</v>
       </c>
       <c r="B659" s="1">
-        <v>700</v>
+        <v>860</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -8448,7 +8454,7 @@
         <v>659</v>
       </c>
       <c r="B660" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -8456,7 +8462,7 @@
         <v>660</v>
       </c>
       <c r="B661" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -8464,7 +8470,7 @@
         <v>661</v>
       </c>
       <c r="B662" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -8472,7 +8478,7 @@
         <v>662</v>
       </c>
       <c r="B663" s="1">
-        <v>1400</v>
+        <v>720</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -8480,7 +8486,7 @@
         <v>663</v>
       </c>
       <c r="B664" s="1">
-        <v>720</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -8488,7 +8494,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -8496,7 +8502,7 @@
         <v>665</v>
       </c>
       <c r="B666" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -8504,7 +8510,7 @@
         <v>666</v>
       </c>
       <c r="B667" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -8512,7 +8518,7 @@
         <v>667</v>
       </c>
       <c r="B668" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -8520,7 +8526,7 @@
         <v>668</v>
       </c>
       <c r="B669" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -8528,7 +8534,7 @@
         <v>669</v>
       </c>
       <c r="B670" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -8544,7 +8550,7 @@
         <v>671</v>
       </c>
       <c r="B672" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -8552,7 +8558,7 @@
         <v>672</v>
       </c>
       <c r="B673" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -8560,7 +8566,7 @@
         <v>673</v>
       </c>
       <c r="B674" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -8568,7 +8574,7 @@
         <v>674</v>
       </c>
       <c r="B675" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8584,7 +8590,7 @@
         <v>676</v>
       </c>
       <c r="B677" s="1">
-        <v>980</v>
+        <v>840</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8592,7 +8598,7 @@
         <v>677</v>
       </c>
       <c r="B678" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8608,7 +8614,7 @@
         <v>679</v>
       </c>
       <c r="B680" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8616,7 +8622,7 @@
         <v>680</v>
       </c>
       <c r="B681" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8632,7 +8638,7 @@
         <v>682</v>
       </c>
       <c r="B683" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8640,7 +8646,7 @@
         <v>683</v>
       </c>
       <c r="B684" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8656,7 +8662,7 @@
         <v>685</v>
       </c>
       <c r="B686" s="1">
-        <v>4000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8664,7 +8670,7 @@
         <v>686</v>
       </c>
       <c r="B687" s="1">
-        <v>720</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8680,7 +8686,7 @@
         <v>688</v>
       </c>
       <c r="B689" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8688,7 +8694,7 @@
         <v>689</v>
       </c>
       <c r="B690" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8696,7 +8702,7 @@
         <v>690</v>
       </c>
       <c r="B691" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8704,7 +8710,7 @@
         <v>691</v>
       </c>
       <c r="B692" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8712,7 +8718,7 @@
         <v>692</v>
       </c>
       <c r="B693" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8720,7 +8726,7 @@
         <v>693</v>
       </c>
       <c r="B694" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8728,7 +8734,7 @@
         <v>694</v>
       </c>
       <c r="B695" s="1">
-        <v>540</v>
+        <v>900</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8736,7 +8742,7 @@
         <v>695</v>
       </c>
       <c r="B696" s="1">
-        <v>660</v>
+        <v>540</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8744,7 +8750,7 @@
         <v>696</v>
       </c>
       <c r="B697" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8752,7 +8758,7 @@
         <v>697</v>
       </c>
       <c r="B698" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8760,7 +8766,7 @@
         <v>698</v>
       </c>
       <c r="B699" s="1">
-        <v>860</v>
+        <v>900</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8768,7 +8774,7 @@
         <v>699</v>
       </c>
       <c r="B700" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8792,7 +8798,7 @@
         <v>702</v>
       </c>
       <c r="B703" s="1">
-        <v>980</v>
+        <v>900</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8800,7 +8806,7 @@
         <v>703</v>
       </c>
       <c r="B704" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8816,7 +8822,7 @@
         <v>705</v>
       </c>
       <c r="B706" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8824,7 +8830,7 @@
         <v>706</v>
       </c>
       <c r="B707" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8832,7 +8838,7 @@
         <v>707</v>
       </c>
       <c r="B708" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8840,7 +8846,7 @@
         <v>708</v>
       </c>
       <c r="B709" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8848,7 +8854,7 @@
         <v>709</v>
       </c>
       <c r="B710" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8856,7 +8862,7 @@
         <v>710</v>
       </c>
       <c r="B711" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8864,7 +8870,7 @@
         <v>711</v>
       </c>
       <c r="B712" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8872,7 +8878,7 @@
         <v>712</v>
       </c>
       <c r="B713" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8880,7 +8886,7 @@
         <v>713</v>
       </c>
       <c r="B714" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8888,7 +8894,7 @@
         <v>714</v>
       </c>
       <c r="B715" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8896,7 +8902,7 @@
         <v>715</v>
       </c>
       <c r="B716" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8904,7 +8910,7 @@
         <v>716</v>
       </c>
       <c r="B717" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8912,7 +8918,7 @@
         <v>717</v>
       </c>
       <c r="B718" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8920,7 +8926,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8928,7 +8934,7 @@
         <v>719</v>
       </c>
       <c r="B720" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8936,7 +8942,7 @@
         <v>720</v>
       </c>
       <c r="B721" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8944,7 +8950,7 @@
         <v>721</v>
       </c>
       <c r="B722" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8952,7 +8958,7 @@
         <v>722</v>
       </c>
       <c r="B723" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8960,7 +8966,7 @@
         <v>723</v>
       </c>
       <c r="B724" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8968,7 +8974,7 @@
         <v>724</v>
       </c>
       <c r="B725" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8976,7 +8982,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8984,7 +8990,7 @@
         <v>726</v>
       </c>
       <c r="B727" s="1">
-        <v>1000</v>
+        <v>880</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8992,7 +8998,7 @@
         <v>727</v>
       </c>
       <c r="B728" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -9000,7 +9006,7 @@
         <v>728</v>
       </c>
       <c r="B729" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -9008,7 +9014,7 @@
         <v>729</v>
       </c>
       <c r="B730" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -9016,7 +9022,7 @@
         <v>730</v>
       </c>
       <c r="B731" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -9024,7 +9030,7 @@
         <v>731</v>
       </c>
       <c r="B732" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -9032,7 +9038,7 @@
         <v>732</v>
       </c>
       <c r="B733" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -9040,7 +9046,7 @@
         <v>733</v>
       </c>
       <c r="B734" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -9048,7 +9054,7 @@
         <v>734</v>
       </c>
       <c r="B735" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -9064,7 +9070,7 @@
         <v>736</v>
       </c>
       <c r="B737" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -9080,7 +9086,7 @@
         <v>738</v>
       </c>
       <c r="B739" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="740" spans="1:2">
@@ -9088,7 +9094,7 @@
         <v>739</v>
       </c>
       <c r="B740" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -9096,7 +9102,7 @@
         <v>740</v>
       </c>
       <c r="B741" s="1">
-        <v>880</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="742" spans="1:2">
@@ -9104,7 +9110,7 @@
         <v>741</v>
       </c>
       <c r="B742" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -9112,7 +9118,7 @@
         <v>742</v>
       </c>
       <c r="B743" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="744" spans="1:2">
@@ -9120,7 +9126,7 @@
         <v>743</v>
       </c>
       <c r="B744" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="745" spans="1:2">
@@ -9128,7 +9134,7 @@
         <v>744</v>
       </c>
       <c r="B745" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -9136,7 +9142,7 @@
         <v>745</v>
       </c>
       <c r="B746" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="747" spans="1:2">
@@ -9144,7 +9150,7 @@
         <v>746</v>
       </c>
       <c r="B747" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="748" spans="1:2">
@@ -9152,7 +9158,7 @@
         <v>747</v>
       </c>
       <c r="B748" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="749" spans="1:2">
@@ -9160,7 +9166,7 @@
         <v>748</v>
       </c>
       <c r="B749" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -9176,7 +9182,7 @@
         <v>750</v>
       </c>
       <c r="B751" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="752" spans="1:2">
@@ -9184,7 +9190,7 @@
         <v>751</v>
       </c>
       <c r="B752" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="753" spans="1:2">
@@ -9192,7 +9198,7 @@
         <v>752</v>
       </c>
       <c r="B753" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="754" spans="1:2">
@@ -9200,7 +9206,7 @@
         <v>753</v>
       </c>
       <c r="B754" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -9208,7 +9214,7 @@
         <v>754</v>
       </c>
       <c r="B755" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="756" spans="1:2">
@@ -9216,7 +9222,7 @@
         <v>755</v>
       </c>
       <c r="B756" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="757" spans="1:2">
@@ -9224,7 +9230,7 @@
         <v>756</v>
       </c>
       <c r="B757" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="758" spans="1:2">
@@ -9232,7 +9238,7 @@
         <v>757</v>
       </c>
       <c r="B758" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="759" spans="1:2">
@@ -9240,7 +9246,7 @@
         <v>758</v>
       </c>
       <c r="B759" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="760" spans="1:2">
@@ -9248,7 +9254,7 @@
         <v>759</v>
       </c>
       <c r="B760" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="761" spans="1:2">
@@ -9256,7 +9262,7 @@
         <v>760</v>
       </c>
       <c r="B761" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="762" spans="1:2">
@@ -9264,7 +9270,7 @@
         <v>761</v>
       </c>
       <c r="B762" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="763" spans="1:2">
@@ -9272,7 +9278,7 @@
         <v>762</v>
       </c>
       <c r="B763" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="764" spans="1:2">
@@ -9280,7 +9286,7 @@
         <v>763</v>
       </c>
       <c r="B764" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="765" spans="1:2">
@@ -9288,7 +9294,7 @@
         <v>764</v>
       </c>
       <c r="B765" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="766" spans="1:2">
@@ -9296,7 +9302,7 @@
         <v>765</v>
       </c>
       <c r="B766" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="767" spans="1:2">
@@ -9304,7 +9310,7 @@
         <v>766</v>
       </c>
       <c r="B767" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="768" spans="1:2">
@@ -9312,7 +9318,7 @@
         <v>767</v>
       </c>
       <c r="B768" s="1">
-        <v>1100</v>
+        <v>720</v>
       </c>
     </row>
     <row r="769" spans="1:2">
@@ -9320,7 +9326,7 @@
         <v>768</v>
       </c>
       <c r="B769" s="1">
-        <v>940</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="770" spans="1:2">
@@ -9336,7 +9342,7 @@
         <v>770</v>
       </c>
       <c r="B771" s="1">
-        <v>820</v>
+        <v>940</v>
       </c>
     </row>
     <row r="772" spans="1:2">
@@ -9344,7 +9350,7 @@
         <v>771</v>
       </c>
       <c r="B772" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="773" spans="1:2">
@@ -9352,7 +9358,7 @@
         <v>772</v>
       </c>
       <c r="B773" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="774" spans="1:2">
@@ -9360,7 +9366,7 @@
         <v>773</v>
       </c>
       <c r="B774" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="775" spans="1:2">
@@ -9376,7 +9382,7 @@
         <v>775</v>
       </c>
       <c r="B776" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="777" spans="1:2">
@@ -9384,7 +9390,7 @@
         <v>776</v>
       </c>
       <c r="B777" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="778" spans="1:2">
@@ -9392,7 +9398,7 @@
         <v>777</v>
       </c>
       <c r="B778" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="779" spans="1:2">
@@ -9400,7 +9406,7 @@
         <v>778</v>
       </c>
       <c r="B779" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="780" spans="1:2">
@@ -9416,7 +9422,7 @@
         <v>780</v>
       </c>
       <c r="B781" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="782" spans="1:2">
@@ -9424,7 +9430,7 @@
         <v>781</v>
       </c>
       <c r="B782" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="783" spans="1:2">
@@ -9432,7 +9438,7 @@
         <v>782</v>
       </c>
       <c r="B783" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="784" spans="1:2">
@@ -9440,7 +9446,7 @@
         <v>783</v>
       </c>
       <c r="B784" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="785" spans="1:2">
@@ -9448,7 +9454,7 @@
         <v>784</v>
       </c>
       <c r="B785" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="786" spans="1:2">
@@ -9456,7 +9462,7 @@
         <v>785</v>
       </c>
       <c r="B786" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="787" spans="1:2">
@@ -9472,7 +9478,7 @@
         <v>787</v>
       </c>
       <c r="B788" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="789" spans="1:2">
@@ -9480,7 +9486,7 @@
         <v>788</v>
       </c>
       <c r="B789" s="1">
-        <v>440</v>
+        <v>900</v>
       </c>
     </row>
     <row r="790" spans="1:2">
@@ -9488,7 +9494,7 @@
         <v>789</v>
       </c>
       <c r="B790" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="791" spans="1:2">
@@ -9496,7 +9502,7 @@
         <v>790</v>
       </c>
       <c r="B791" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="792" spans="1:2">
@@ -9504,7 +9510,7 @@
         <v>791</v>
       </c>
       <c r="B792" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="793" spans="1:2">
@@ -9512,7 +9518,7 @@
         <v>792</v>
       </c>
       <c r="B793" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="794" spans="1:2">
@@ -9520,7 +9526,7 @@
         <v>793</v>
       </c>
       <c r="B794" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="795" spans="1:2">
@@ -9528,7 +9534,7 @@
         <v>794</v>
       </c>
       <c r="B795" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="796" spans="1:2">
@@ -9536,7 +9542,7 @@
         <v>795</v>
       </c>
       <c r="B796" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="797" spans="1:2">
@@ -9544,7 +9550,7 @@
         <v>796</v>
       </c>
       <c r="B797" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="798" spans="1:2">
@@ -9552,7 +9558,7 @@
         <v>797</v>
       </c>
       <c r="B798" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="799" spans="1:2">
@@ -9560,7 +9566,7 @@
         <v>798</v>
       </c>
       <c r="B799" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="800" spans="1:2">
@@ -9568,7 +9574,7 @@
         <v>799</v>
       </c>
       <c r="B800" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="801" spans="1:2">
@@ -9584,7 +9590,7 @@
         <v>801</v>
       </c>
       <c r="B802" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="803" spans="1:2">
@@ -9592,7 +9598,7 @@
         <v>802</v>
       </c>
       <c r="B803" s="1">
-        <v>920</v>
+        <v>880</v>
       </c>
     </row>
     <row r="804" spans="1:2">
@@ -9600,7 +9606,7 @@
         <v>803</v>
       </c>
       <c r="B804" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="805" spans="1:2">
@@ -9608,7 +9614,7 @@
         <v>804</v>
       </c>
       <c r="B805" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="806" spans="1:2">
@@ -9616,7 +9622,7 @@
         <v>805</v>
       </c>
       <c r="B806" s="1">
-        <v>980</v>
+        <v>800</v>
       </c>
     </row>
     <row r="807" spans="1:2">
@@ -9624,7 +9630,7 @@
         <v>806</v>
       </c>
       <c r="B807" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="808" spans="1:2">
@@ -9632,7 +9638,7 @@
         <v>807</v>
       </c>
       <c r="B808" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="809" spans="1:2">
@@ -9640,7 +9646,7 @@
         <v>808</v>
       </c>
       <c r="B809" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="810" spans="1:2">
@@ -9648,7 +9654,7 @@
         <v>809</v>
       </c>
       <c r="B810" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="811" spans="1:2">
@@ -9656,7 +9662,7 @@
         <v>810</v>
       </c>
       <c r="B811" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="812" spans="1:2">
@@ -9664,7 +9670,7 @@
         <v>811</v>
       </c>
       <c r="B812" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="813" spans="1:2">
@@ -9672,7 +9678,7 @@
         <v>812</v>
       </c>
       <c r="B813" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="814" spans="1:2">
@@ -9680,7 +9686,7 @@
         <v>813</v>
       </c>
       <c r="B814" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="815" spans="1:2">
@@ -9688,7 +9694,7 @@
         <v>814</v>
       </c>
       <c r="B815" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="816" spans="1:2">
@@ -9696,7 +9702,7 @@
         <v>815</v>
       </c>
       <c r="B816" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="817" spans="1:2">
@@ -9704,7 +9710,7 @@
         <v>816</v>
       </c>
       <c r="B817" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="818" spans="1:2">
@@ -9712,7 +9718,7 @@
         <v>817</v>
       </c>
       <c r="B818" s="1">
-        <v>660</v>
+        <v>860</v>
       </c>
     </row>
     <row r="819" spans="1:2">
@@ -9720,7 +9726,7 @@
         <v>818</v>
       </c>
       <c r="B819" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="820" spans="1:2">
@@ -9728,7 +9734,7 @@
         <v>819</v>
       </c>
       <c r="B820" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="821" spans="1:2">
@@ -9736,7 +9742,7 @@
         <v>820</v>
       </c>
       <c r="B821" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="822" spans="1:2">
@@ -9744,7 +9750,7 @@
         <v>821</v>
       </c>
       <c r="B822" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="823" spans="1:2">
@@ -9752,7 +9758,7 @@
         <v>822</v>
       </c>
       <c r="B823" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="824" spans="1:2">
@@ -9760,7 +9766,7 @@
         <v>823</v>
       </c>
       <c r="B824" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="825" spans="1:2">
@@ -9768,7 +9774,7 @@
         <v>824</v>
       </c>
       <c r="B825" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="826" spans="1:2">
@@ -9776,7 +9782,7 @@
         <v>825</v>
       </c>
       <c r="B826" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="827" spans="1:2">
@@ -9784,7 +9790,7 @@
         <v>826</v>
       </c>
       <c r="B827" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="828" spans="1:2">
@@ -9792,7 +9798,7 @@
         <v>827</v>
       </c>
       <c r="B828" s="1">
-        <v>960</v>
+        <v>840</v>
       </c>
     </row>
     <row r="829" spans="1:2">
@@ -9800,7 +9806,7 @@
         <v>828</v>
       </c>
       <c r="B829" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="830" spans="1:2">
@@ -9808,7 +9814,7 @@
         <v>829</v>
       </c>
       <c r="B830" s="1">
-        <v>760</v>
+        <v>960</v>
       </c>
     </row>
     <row r="831" spans="1:2">
@@ -9816,7 +9822,7 @@
         <v>830</v>
       </c>
       <c r="B831" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="832" spans="1:2">
@@ -9824,7 +9830,7 @@
         <v>831</v>
       </c>
       <c r="B832" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="833" spans="1:2">
@@ -9832,7 +9838,7 @@
         <v>832</v>
       </c>
       <c r="B833" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="834" spans="1:2">
@@ -9840,7 +9846,7 @@
         <v>833</v>
       </c>
       <c r="B834" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="835" spans="1:2">
@@ -9848,7 +9854,7 @@
         <v>834</v>
       </c>
       <c r="B835" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="836" spans="1:2">
@@ -9856,7 +9862,7 @@
         <v>835</v>
       </c>
       <c r="B836" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="837" spans="1:2">
@@ -9864,7 +9870,7 @@
         <v>836</v>
       </c>
       <c r="B837" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="838" spans="1:2">
@@ -9872,7 +9878,7 @@
         <v>837</v>
       </c>
       <c r="B838" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="839" spans="1:2">
@@ -9880,7 +9886,7 @@
         <v>838</v>
       </c>
       <c r="B839" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="840" spans="1:2">
@@ -9888,7 +9894,7 @@
         <v>839</v>
       </c>
       <c r="B840" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="841" spans="1:2">
@@ -9896,7 +9902,7 @@
         <v>840</v>
       </c>
       <c r="B841" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="842" spans="1:2">
@@ -9904,7 +9910,7 @@
         <v>841</v>
       </c>
       <c r="B842" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="843" spans="1:2">
@@ -9912,7 +9918,7 @@
         <v>842</v>
       </c>
       <c r="B843" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="844" spans="1:2">
@@ -9920,7 +9926,7 @@
         <v>843</v>
       </c>
       <c r="B844" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="845" spans="1:2">
@@ -9928,7 +9934,7 @@
         <v>844</v>
       </c>
       <c r="B845" s="1">
-        <v>920</v>
+        <v>500</v>
       </c>
     </row>
     <row r="846" spans="1:2">
@@ -9936,7 +9942,7 @@
         <v>845</v>
       </c>
       <c r="B846" s="1">
-        <v>1000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="847" spans="1:2">
@@ -9944,7 +9950,7 @@
         <v>846</v>
       </c>
       <c r="B847" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="848" spans="1:2">
@@ -9952,7 +9958,7 @@
         <v>847</v>
       </c>
       <c r="B848" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="849" spans="1:2">
@@ -9968,7 +9974,7 @@
         <v>849</v>
       </c>
       <c r="B850" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="851" spans="1:2">
@@ -9976,7 +9982,7 @@
         <v>850</v>
       </c>
       <c r="B851" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="852" spans="1:2">
@@ -9984,7 +9990,7 @@
         <v>851</v>
       </c>
       <c r="B852" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="853" spans="1:2">
@@ -9992,7 +9998,7 @@
         <v>852</v>
       </c>
       <c r="B853" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="854" spans="1:2">
@@ -10000,7 +10006,7 @@
         <v>853</v>
       </c>
       <c r="B854" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="855" spans="1:2">
@@ -10008,7 +10014,7 @@
         <v>854</v>
       </c>
       <c r="B855" s="1">
-        <v>960</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="856" spans="1:2">
@@ -10016,7 +10022,7 @@
         <v>855</v>
       </c>
       <c r="B856" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="857" spans="1:2">
@@ -10024,7 +10030,7 @@
         <v>856</v>
       </c>
       <c r="B857" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="858" spans="1:2">
@@ -10032,7 +10038,7 @@
         <v>857</v>
       </c>
       <c r="B858" s="1">
-        <v>820</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="859" spans="1:2">
@@ -10040,7 +10046,7 @@
         <v>858</v>
       </c>
       <c r="B859" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="860" spans="1:2">
@@ -10048,7 +10054,7 @@
         <v>859</v>
       </c>
       <c r="B860" s="1">
-        <v>440</v>
+        <v>820</v>
       </c>
     </row>
     <row r="861" spans="1:2">
@@ -10056,7 +10062,7 @@
         <v>860</v>
       </c>
       <c r="B861" s="1">
-        <v>500</v>
+        <v>840</v>
       </c>
     </row>
     <row r="862" spans="1:2">
@@ -10072,7 +10078,7 @@
         <v>862</v>
       </c>
       <c r="B863" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="864" spans="1:2">
@@ -10080,7 +10086,7 @@
         <v>863</v>
       </c>
       <c r="B864" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="865" spans="1:2">
@@ -10088,7 +10094,7 @@
         <v>864</v>
       </c>
       <c r="B865" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="866" spans="1:2">
@@ -10096,7 +10102,7 @@
         <v>865</v>
       </c>
       <c r="B866" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="867" spans="1:2">
@@ -10104,7 +10110,7 @@
         <v>866</v>
       </c>
       <c r="B867" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="868" spans="1:2">
@@ -10112,7 +10118,7 @@
         <v>867</v>
       </c>
       <c r="B868" s="1">
-        <v>840</v>
+        <v>820</v>
       </c>
     </row>
     <row r="869" spans="1:2">
@@ -10120,7 +10126,7 @@
         <v>868</v>
       </c>
       <c r="B869" s="1">
-        <v>400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="870" spans="1:2">
@@ -10128,7 +10134,7 @@
         <v>869</v>
       </c>
       <c r="B870" s="1">
-        <v>400</v>
+        <v>840</v>
       </c>
     </row>
     <row r="871" spans="1:2">
@@ -10136,7 +10142,7 @@
         <v>870</v>
       </c>
       <c r="B871" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="872" spans="1:2">
@@ -10144,7 +10150,7 @@
         <v>871</v>
       </c>
       <c r="B872" s="1">
-        <v>960</v>
+        <v>400</v>
       </c>
     </row>
     <row r="873" spans="1:2">
@@ -10160,7 +10166,7 @@
         <v>873</v>
       </c>
       <c r="B874" s="1">
-        <v>380</v>
+        <v>960</v>
       </c>
     </row>
     <row r="875" spans="1:2">
@@ -10168,7 +10174,7 @@
         <v>874</v>
       </c>
       <c r="B875" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="876" spans="1:2">
@@ -10176,7 +10182,7 @@
         <v>875</v>
       </c>
       <c r="B876" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="877" spans="1:2">
@@ -10184,7 +10190,7 @@
         <v>876</v>
       </c>
       <c r="B877" s="1">
-        <v>800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="878" spans="1:2">
@@ -10192,7 +10198,7 @@
         <v>877</v>
       </c>
       <c r="B878" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="879" spans="1:2">
@@ -10200,7 +10206,7 @@
         <v>878</v>
       </c>
       <c r="B879" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="880" spans="1:2">
@@ -10208,7 +10214,7 @@
         <v>879</v>
       </c>
       <c r="B880" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="881" spans="1:2">
@@ -10216,7 +10222,7 @@
         <v>880</v>
       </c>
       <c r="B881" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="882" spans="1:2">
@@ -10224,7 +10230,7 @@
         <v>881</v>
       </c>
       <c r="B882" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="883" spans="1:2">
@@ -10232,7 +10238,7 @@
         <v>882</v>
       </c>
       <c r="B883" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="884" spans="1:2">
@@ -10240,7 +10246,7 @@
         <v>883</v>
       </c>
       <c r="B884" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="885" spans="1:2">
@@ -10248,7 +10254,7 @@
         <v>884</v>
       </c>
       <c r="B885" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="886" spans="1:2">
@@ -10256,7 +10262,7 @@
         <v>885</v>
       </c>
       <c r="B886" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="887" spans="1:2">
@@ -10264,7 +10270,7 @@
         <v>886</v>
       </c>
       <c r="B887" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="888" spans="1:2">
@@ -10272,7 +10278,7 @@
         <v>887</v>
       </c>
       <c r="B888" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="889" spans="1:2">
@@ -10280,7 +10286,7 @@
         <v>888</v>
       </c>
       <c r="B889" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="890" spans="1:2">
@@ -10288,7 +10294,7 @@
         <v>889</v>
       </c>
       <c r="B890" s="1">
-        <v>840</v>
+        <v>500</v>
       </c>
     </row>
     <row r="891" spans="1:2">
@@ -10296,7 +10302,7 @@
         <v>890</v>
       </c>
       <c r="B891" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="892" spans="1:2">
@@ -10304,7 +10310,7 @@
         <v>891</v>
       </c>
       <c r="B892" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="893" spans="1:2">
@@ -10312,7 +10318,7 @@
         <v>892</v>
       </c>
       <c r="B893" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="894" spans="1:2">
@@ -10320,7 +10326,7 @@
         <v>893</v>
       </c>
       <c r="B894" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="895" spans="1:2">
@@ -10328,7 +10334,7 @@
         <v>894</v>
       </c>
       <c r="B895" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="896" spans="1:2">
@@ -10336,7 +10342,7 @@
         <v>895</v>
       </c>
       <c r="B896" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="897" spans="1:2">
@@ -10352,7 +10358,7 @@
         <v>897</v>
       </c>
       <c r="B898" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="899" spans="1:2">
@@ -10360,7 +10366,7 @@
         <v>898</v>
       </c>
       <c r="B899" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="900" spans="1:2">
@@ -10368,7 +10374,7 @@
         <v>899</v>
       </c>
       <c r="B900" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="901" spans="1:2">
@@ -10376,7 +10382,7 @@
         <v>900</v>
       </c>
       <c r="B901" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="902" spans="1:2">
@@ -10384,7 +10390,7 @@
         <v>901</v>
       </c>
       <c r="B902" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="903" spans="1:2">
@@ -10392,7 +10398,7 @@
         <v>902</v>
       </c>
       <c r="B903" s="1">
-        <v>960</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="904" spans="1:2">
@@ -10400,7 +10406,7 @@
         <v>903</v>
       </c>
       <c r="B904" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="905" spans="1:2">
@@ -10408,7 +10414,7 @@
         <v>904</v>
       </c>
       <c r="B905" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="906" spans="1:2">
@@ -10416,7 +10422,7 @@
         <v>905</v>
       </c>
       <c r="B906" s="1">
-        <v>820</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="907" spans="1:2">
@@ -10424,7 +10430,7 @@
         <v>906</v>
       </c>
       <c r="B907" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="908" spans="1:2">
@@ -10432,7 +10438,7 @@
         <v>907</v>
       </c>
       <c r="B908" s="1">
-        <v>440</v>
+        <v>820</v>
       </c>
     </row>
     <row r="909" spans="1:2">
@@ -10440,7 +10446,7 @@
         <v>908</v>
       </c>
       <c r="B909" s="1">
-        <v>500</v>
+        <v>840</v>
       </c>
     </row>
     <row r="910" spans="1:2">
@@ -10456,7 +10462,7 @@
         <v>910</v>
       </c>
       <c r="B911" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="912" spans="1:2">
@@ -10464,7 +10470,7 @@
         <v>911</v>
       </c>
       <c r="B912" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="913" spans="1:2">
@@ -10472,7 +10478,7 @@
         <v>912</v>
       </c>
       <c r="B913" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="914" spans="1:2">
@@ -10480,7 +10486,7 @@
         <v>913</v>
       </c>
       <c r="B914" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="915" spans="1:2">
@@ -10488,7 +10494,7 @@
         <v>914</v>
       </c>
       <c r="B915" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="916" spans="1:2">
@@ -10504,7 +10510,7 @@
         <v>916</v>
       </c>
       <c r="B917" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="918" spans="1:2">
@@ -10512,7 +10518,7 @@
         <v>917</v>
       </c>
       <c r="B918" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="919" spans="1:2">
@@ -10528,7 +10534,7 @@
         <v>919</v>
       </c>
       <c r="B920" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="921" spans="1:2">
@@ -10536,7 +10542,7 @@
         <v>920</v>
       </c>
       <c r="B921" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="922" spans="1:2">
@@ -10544,7 +10550,7 @@
         <v>921</v>
       </c>
       <c r="B922" s="1">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="923" spans="1:2">
@@ -10552,7 +10558,7 @@
         <v>922</v>
       </c>
       <c r="B923" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="924" spans="1:2">
@@ -10560,7 +10566,7 @@
         <v>923</v>
       </c>
       <c r="B924" s="1">
-        <v>600</v>
+        <v>440</v>
       </c>
     </row>
     <row r="925" spans="1:2">
@@ -10568,7 +10574,7 @@
         <v>924</v>
       </c>
       <c r="B925" s="1">
-        <v>820</v>
+        <v>380</v>
       </c>
     </row>
     <row r="926" spans="1:2">
@@ -10576,7 +10582,7 @@
         <v>925</v>
       </c>
       <c r="B926" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="927" spans="1:2">
@@ -10584,7 +10590,7 @@
         <v>926</v>
       </c>
       <c r="B927" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="928" spans="1:2">
@@ -10592,7 +10598,7 @@
         <v>927</v>
       </c>
       <c r="B928" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="929" spans="1:2">
@@ -10608,7 +10614,7 @@
         <v>929</v>
       </c>
       <c r="B930" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="931" spans="1:2">
@@ -10616,7 +10622,7 @@
         <v>930</v>
       </c>
       <c r="B931" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="932" spans="1:2">
@@ -10624,6 +10630,22 @@
         <v>931</v>
       </c>
       <c r="B932" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="933" spans="1:2">
+      <c r="A933" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="B933" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="934" spans="1:2">
+      <c r="A934" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="B934" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="934">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="938">
   <si>
     <t>Наименование</t>
   </si>
@@ -278,6 +278,9 @@
     <t>Borodachy Brewery - Синтез (IPL), Розлив, Беларусь</t>
   </si>
   <si>
+    <t>Borodachy Brewery - Синтез: Pink Boost &amp; Nectaron (IPL), Розлив, Беларусь</t>
+  </si>
+  <si>
     <t>Boxing Wizard - Maythorn (APA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -524,6 +527,9 @@
     <t>Jungle - Citra One Love (Session NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Jungle - Fresh Swing (Session White IPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Jungle - Hired Gun (APA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1742,6 +1748,9 @@
     <t>вынос_Borodachy Brewery - Синтез (IPL), Розлив, Беларусь</t>
   </si>
   <si>
+    <t>вынос_Borodachy Brewery - Синтез: Pink Boost &amp; Nectaron (IPL), Розлив, Беларусь</t>
+  </si>
+  <si>
     <t>вынос_Boxing Wizard - Maythorn (APA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1884,6 +1893,9 @@
   </si>
   <si>
     <t>вынос_Jungle - Body Flow (IPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Jungle - Fresh Swing (Session White IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_Jungle - Hired Gun (APA), РОЗЛИВ, Россия</t>
@@ -3170,7 +3182,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B934"/>
+  <dimension ref="A1:B938"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -3870,7 +3882,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -3878,7 +3890,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -3886,7 +3898,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3894,7 +3906,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -3902,7 +3914,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3910,7 +3922,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3918,7 +3930,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -3926,7 +3938,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>640</v>
+        <v>880</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3934,7 +3946,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3942,7 +3954,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3950,7 +3962,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -3958,7 +3970,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3966,7 +3978,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -3974,7 +3986,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -3982,7 +3994,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3998,7 +4010,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -4006,7 +4018,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -4014,7 +4026,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -4022,7 +4034,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -4030,7 +4042,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>540</v>
+        <v>560</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -4038,7 +4050,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>860</v>
+        <v>540</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -4046,7 +4058,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -4062,7 +4074,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -4070,7 +4082,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -4078,7 +4090,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>440</v>
+        <v>720</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -4086,7 +4098,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -4094,7 +4106,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>460</v>
+        <v>560</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -4110,7 +4122,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>960</v>
+        <v>460</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -4118,7 +4130,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>940</v>
+        <v>960</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -4126,7 +4138,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -4142,7 +4154,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>660</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -4150,7 +4162,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>480</v>
+        <v>660</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -4158,7 +4170,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>400</v>
+        <v>480</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -4166,7 +4178,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>720</v>
+        <v>400</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -4174,7 +4186,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -4182,7 +4194,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>500</v>
+        <v>560</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -4190,7 +4202,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -4198,7 +4210,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>500</v>
+        <v>760</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -4206,7 +4218,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>940</v>
+        <v>500</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -4214,7 +4226,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>820</v>
+        <v>940</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -4230,7 +4242,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -4238,7 +4250,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -4246,7 +4258,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -4254,7 +4266,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -4262,7 +4274,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -4270,7 +4282,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>680</v>
+        <v>960</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -4278,7 +4290,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>420</v>
+        <v>680</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -4286,7 +4298,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -4294,7 +4306,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -4302,7 +4314,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -4310,7 +4322,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -4318,7 +4330,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -4326,7 +4338,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -4334,7 +4346,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -4342,7 +4354,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -4350,7 +4362,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>580</v>
+        <v>880</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -4358,7 +4370,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -4366,7 +4378,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -4374,7 +4386,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -4382,7 +4394,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>620</v>
+        <v>900</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -4390,7 +4402,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -4398,7 +4410,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -4406,7 +4418,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -4414,7 +4426,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -4422,7 +4434,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>900</v>
+        <v>960</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -4430,7 +4442,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -4438,7 +4450,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -4446,7 +4458,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -4454,7 +4466,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -4462,7 +4474,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -4470,7 +4482,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>500</v>
+        <v>920</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -4478,7 +4490,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>580</v>
+        <v>500</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -4486,7 +4498,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -4494,7 +4506,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -4502,7 +4514,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>980</v>
+        <v>520</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -4510,7 +4522,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>1100</v>
+        <v>980</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -4518,7 +4530,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>1060</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4542,7 +4554,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>1100</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -4550,7 +4562,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4558,7 +4570,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4566,7 +4578,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>1080</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4574,20 +4586,20 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>840</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B177" s="1">
         <v>840</v>
@@ -4598,7 +4610,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="1">
-        <v>420</v>
+        <v>840</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4606,7 +4618,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4614,7 +4626,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="1">
-        <v>720</v>
+        <v>420</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4622,7 +4634,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="1">
-        <v>460</v>
+        <v>520</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4630,7 +4642,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4638,7 +4650,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4646,7 +4658,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4654,7 +4666,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4662,7 +4674,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="1">
-        <v>520</v>
+        <v>740</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4670,7 +4682,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="1">
-        <v>980</v>
+        <v>620</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4678,7 +4690,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4686,7 +4698,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="1">
-        <v>580</v>
+        <v>980</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4694,7 +4706,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="1">
-        <v>740</v>
+        <v>540</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4702,7 +4714,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="1">
-        <v>760</v>
+        <v>580</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4710,7 +4722,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="1">
-        <v>560</v>
+        <v>740</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4718,7 +4730,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4726,7 +4738,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="1">
-        <v>1100</v>
+        <v>560</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4750,7 +4762,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4758,7 +4770,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="1">
-        <v>640</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4774,7 +4786,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="1">
-        <v>920</v>
+        <v>640</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4782,7 +4794,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4806,7 +4818,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4814,7 +4826,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4822,7 +4834,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4830,7 +4842,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4838,7 +4850,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="1">
-        <v>840</v>
+        <v>960</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4846,7 +4858,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4854,7 +4866,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4862,7 +4874,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="1">
-        <v>980</v>
+        <v>900</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4870,7 +4882,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="1">
-        <v>460</v>
+        <v>700</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4878,7 +4890,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="1">
-        <v>580</v>
+        <v>980</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4886,7 +4898,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="1">
-        <v>720</v>
+        <v>460</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4894,7 +4906,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="1">
-        <v>660</v>
+        <v>580</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4902,7 +4914,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4910,7 +4922,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="1">
-        <v>260</v>
+        <v>660</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4918,7 +4930,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="1">
-        <v>260</v>
+        <v>780</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4926,7 +4938,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4934,7 +4946,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4942,7 +4954,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4950,7 +4962,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4958,7 +4970,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4966,7 +4978,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4974,7 +4986,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="1">
-        <v>400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4982,7 +4994,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="1">
-        <v>740</v>
+        <v>500</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4990,7 +5002,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="1">
-        <v>680</v>
+        <v>400</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4998,7 +5010,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -5006,7 +5018,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="1">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -5014,7 +5026,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -5022,7 +5034,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="1">
-        <v>680</v>
+        <v>620</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -5030,7 +5042,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -5038,7 +5050,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -5046,7 +5058,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -5054,7 +5066,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -5062,7 +5074,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="1">
-        <v>580</v>
+        <v>620</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -5070,7 +5082,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="1">
-        <v>860</v>
+        <v>520</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -5086,7 +5098,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="1">
-        <v>620</v>
+        <v>860</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -5094,7 +5106,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -5102,7 +5114,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -5110,7 +5122,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -5118,7 +5130,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -5126,7 +5138,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -5134,7 +5146,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="1">
-        <v>700</v>
+        <v>580</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -5142,7 +5154,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="1">
-        <v>820</v>
+        <v>540</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -5150,7 +5162,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -5158,7 +5170,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -5166,7 +5178,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -5174,7 +5186,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="1">
-        <v>1400</v>
+        <v>720</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -5182,7 +5194,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="1">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -5190,7 +5202,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="1">
-        <v>720</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -5198,7 +5210,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="1">
-        <v>660</v>
+        <v>480</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -5206,7 +5218,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -5214,7 +5226,7 @@
         <v>254</v>
       </c>
       <c r="B255" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -5222,7 +5234,7 @@
         <v>255</v>
       </c>
       <c r="B256" s="1">
-        <v>740</v>
+        <v>600</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -5230,7 +5242,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -5238,7 +5250,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -5246,7 +5258,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="1">
-        <v>520</v>
+        <v>720</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -5254,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -5262,7 +5274,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -5270,7 +5282,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="1">
-        <v>620</v>
+        <v>900</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -5278,7 +5290,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -5294,7 +5306,7 @@
         <v>264</v>
       </c>
       <c r="B265" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -5302,7 +5314,7 @@
         <v>265</v>
       </c>
       <c r="B266" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -5310,7 +5322,7 @@
         <v>266</v>
       </c>
       <c r="B267" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -5318,7 +5330,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -5326,7 +5338,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -5342,7 +5354,7 @@
         <v>270</v>
       </c>
       <c r="B271" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -5350,7 +5362,7 @@
         <v>271</v>
       </c>
       <c r="B272" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -5358,7 +5370,7 @@
         <v>272</v>
       </c>
       <c r="B273" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -5366,7 +5378,7 @@
         <v>273</v>
       </c>
       <c r="B274" s="1">
-        <v>980</v>
+        <v>840</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -5374,7 +5386,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -5382,7 +5394,7 @@
         <v>275</v>
       </c>
       <c r="B276" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -5390,7 +5402,7 @@
         <v>276</v>
       </c>
       <c r="B277" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -5406,7 +5418,7 @@
         <v>278</v>
       </c>
       <c r="B279" s="1">
-        <v>560</v>
+        <v>820</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -5422,7 +5434,7 @@
         <v>280</v>
       </c>
       <c r="B281" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -5430,7 +5442,7 @@
         <v>281</v>
       </c>
       <c r="B282" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -5438,7 +5450,7 @@
         <v>282</v>
       </c>
       <c r="B283" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -5446,7 +5458,7 @@
         <v>283</v>
       </c>
       <c r="B284" s="1">
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -5454,7 +5466,7 @@
         <v>284</v>
       </c>
       <c r="B285" s="1">
-        <v>500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -5462,7 +5474,7 @@
         <v>285</v>
       </c>
       <c r="B286" s="1">
-        <v>758</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5470,7 +5482,7 @@
         <v>286</v>
       </c>
       <c r="B287" s="1">
-        <v>2273</v>
+        <v>500</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5478,7 +5490,7 @@
         <v>287</v>
       </c>
       <c r="B288" s="1">
-        <v>1515</v>
+        <v>758</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5486,7 +5498,7 @@
         <v>288</v>
       </c>
       <c r="B289" s="1">
-        <v>520</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5494,7 +5506,7 @@
         <v>289</v>
       </c>
       <c r="B290" s="1">
-        <v>4000</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5502,7 +5514,7 @@
         <v>290</v>
       </c>
       <c r="B291" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5510,7 +5522,7 @@
         <v>291</v>
       </c>
       <c r="B292" s="1">
-        <v>480</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5518,7 +5530,7 @@
         <v>292</v>
       </c>
       <c r="B293" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5526,7 +5538,7 @@
         <v>293</v>
       </c>
       <c r="B294" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5534,7 +5546,7 @@
         <v>294</v>
       </c>
       <c r="B295" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5542,7 +5554,7 @@
         <v>295</v>
       </c>
       <c r="B296" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5550,7 +5562,7 @@
         <v>296</v>
       </c>
       <c r="B297" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5558,7 +5570,7 @@
         <v>297</v>
       </c>
       <c r="B298" s="1">
-        <v>580</v>
+        <v>840</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5566,7 +5578,7 @@
         <v>298</v>
       </c>
       <c r="B299" s="1">
-        <v>520</v>
+        <v>700</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5574,7 +5586,7 @@
         <v>299</v>
       </c>
       <c r="B300" s="1">
-        <v>680</v>
+        <v>580</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5582,7 +5594,7 @@
         <v>300</v>
       </c>
       <c r="B301" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5590,7 +5602,7 @@
         <v>301</v>
       </c>
       <c r="B302" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5598,7 +5610,7 @@
         <v>302</v>
       </c>
       <c r="B303" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5606,7 +5618,7 @@
         <v>303</v>
       </c>
       <c r="B304" s="1">
-        <v>380</v>
+        <v>580</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5614,7 +5626,7 @@
         <v>304</v>
       </c>
       <c r="B305" s="1">
-        <v>660</v>
+        <v>560</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5622,7 +5634,7 @@
         <v>305</v>
       </c>
       <c r="B306" s="1">
-        <v>900</v>
+        <v>380</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5630,7 +5642,7 @@
         <v>306</v>
       </c>
       <c r="B307" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5638,7 +5650,7 @@
         <v>307</v>
       </c>
       <c r="B308" s="1">
-        <v>520</v>
+        <v>900</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5646,7 +5658,7 @@
         <v>308</v>
       </c>
       <c r="B309" s="1">
-        <v>660</v>
+        <v>540</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5654,7 +5666,7 @@
         <v>309</v>
       </c>
       <c r="B310" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5662,7 +5674,7 @@
         <v>310</v>
       </c>
       <c r="B311" s="1">
-        <v>460</v>
+        <v>660</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5670,7 +5682,7 @@
         <v>311</v>
       </c>
       <c r="B312" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5678,7 +5690,7 @@
         <v>312</v>
       </c>
       <c r="B313" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5686,7 +5698,7 @@
         <v>313</v>
       </c>
       <c r="B314" s="1">
-        <v>900</v>
+        <v>520</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5694,7 +5706,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5710,7 +5722,7 @@
         <v>316</v>
       </c>
       <c r="B317" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5726,7 +5738,7 @@
         <v>318</v>
       </c>
       <c r="B319" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5734,7 +5746,7 @@
         <v>319</v>
       </c>
       <c r="B320" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5742,7 +5754,7 @@
         <v>320</v>
       </c>
       <c r="B321" s="1">
-        <v>980</v>
+        <v>560</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5750,7 +5762,7 @@
         <v>321</v>
       </c>
       <c r="B322" s="1">
-        <v>1000</v>
+        <v>560</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5758,7 +5770,7 @@
         <v>322</v>
       </c>
       <c r="B323" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5766,7 +5778,7 @@
         <v>323</v>
       </c>
       <c r="B324" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5774,7 +5786,7 @@
         <v>324</v>
       </c>
       <c r="B325" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5782,7 +5794,7 @@
         <v>325</v>
       </c>
       <c r="B326" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5790,7 +5802,7 @@
         <v>326</v>
       </c>
       <c r="B327" s="1">
-        <v>680</v>
+        <v>940</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5798,7 +5810,7 @@
         <v>327</v>
       </c>
       <c r="B328" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5806,7 +5818,7 @@
         <v>328</v>
       </c>
       <c r="B329" s="1">
-        <v>840</v>
+        <v>680</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5814,7 +5826,7 @@
         <v>329</v>
       </c>
       <c r="B330" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5822,7 +5834,7 @@
         <v>330</v>
       </c>
       <c r="B331" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5830,7 +5842,7 @@
         <v>331</v>
       </c>
       <c r="B332" s="1">
-        <v>940</v>
+        <v>860</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5846,7 +5858,7 @@
         <v>333</v>
       </c>
       <c r="B334" s="1">
-        <v>840</v>
+        <v>940</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5862,7 +5874,7 @@
         <v>335</v>
       </c>
       <c r="B336" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5870,7 +5882,7 @@
         <v>336</v>
       </c>
       <c r="B337" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5878,7 +5890,7 @@
         <v>337</v>
       </c>
       <c r="B338" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5886,7 +5898,7 @@
         <v>338</v>
       </c>
       <c r="B339" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5894,7 +5906,7 @@
         <v>339</v>
       </c>
       <c r="B340" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5902,7 +5914,7 @@
         <v>340</v>
       </c>
       <c r="B341" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5910,7 +5922,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5918,7 +5930,7 @@
         <v>342</v>
       </c>
       <c r="B343" s="1">
-        <v>800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5926,7 +5938,7 @@
         <v>343</v>
       </c>
       <c r="B344" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5934,7 +5946,7 @@
         <v>344</v>
       </c>
       <c r="B345" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5942,7 +5954,7 @@
         <v>345</v>
       </c>
       <c r="B346" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5950,7 +5962,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5958,7 +5970,7 @@
         <v>347</v>
       </c>
       <c r="B348" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5966,7 +5978,7 @@
         <v>348</v>
       </c>
       <c r="B349" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5974,7 +5986,7 @@
         <v>349</v>
       </c>
       <c r="B350" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5982,7 +5994,7 @@
         <v>350</v>
       </c>
       <c r="B351" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5998,7 +6010,7 @@
         <v>352</v>
       </c>
       <c r="B353" s="1">
-        <v>880</v>
+        <v>640</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -6006,7 +6018,7 @@
         <v>353</v>
       </c>
       <c r="B354" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -6014,7 +6026,7 @@
         <v>354</v>
       </c>
       <c r="B355" s="1">
-        <v>520</v>
+        <v>880</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -6022,7 +6034,7 @@
         <v>355</v>
       </c>
       <c r="B356" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -6030,7 +6042,7 @@
         <v>356</v>
       </c>
       <c r="B357" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -6038,7 +6050,7 @@
         <v>357</v>
       </c>
       <c r="B358" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -6054,7 +6066,7 @@
         <v>359</v>
       </c>
       <c r="B360" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -6062,7 +6074,7 @@
         <v>360</v>
       </c>
       <c r="B361" s="1">
-        <v>520</v>
+        <v>600</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -6070,7 +6082,7 @@
         <v>361</v>
       </c>
       <c r="B362" s="1">
-        <v>320</v>
+        <v>380</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -6078,7 +6090,7 @@
         <v>362</v>
       </c>
       <c r="B363" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -6086,7 +6098,7 @@
         <v>363</v>
       </c>
       <c r="B364" s="1">
-        <v>560</v>
+        <v>320</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -6094,7 +6106,7 @@
         <v>364</v>
       </c>
       <c r="B365" s="1">
-        <v>480</v>
+        <v>540</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -6102,7 +6114,7 @@
         <v>365</v>
       </c>
       <c r="B366" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -6110,7 +6122,7 @@
         <v>366</v>
       </c>
       <c r="B367" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -6118,7 +6130,7 @@
         <v>367</v>
       </c>
       <c r="B368" s="1">
-        <v>500</v>
+        <v>480</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -6126,7 +6138,7 @@
         <v>368</v>
       </c>
       <c r="B369" s="1">
-        <v>800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -6134,7 +6146,7 @@
         <v>369</v>
       </c>
       <c r="B370" s="1">
-        <v>480</v>
+        <v>500</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -6150,7 +6162,7 @@
         <v>371</v>
       </c>
       <c r="B372" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -6158,7 +6170,7 @@
         <v>372</v>
       </c>
       <c r="B373" s="1">
-        <v>380</v>
+        <v>800</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -6166,7 +6178,7 @@
         <v>373</v>
       </c>
       <c r="B374" s="1">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -6174,7 +6186,7 @@
         <v>374</v>
       </c>
       <c r="B375" s="1">
-        <v>900</v>
+        <v>380</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -6182,7 +6194,7 @@
         <v>375</v>
       </c>
       <c r="B376" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -6190,7 +6202,7 @@
         <v>376</v>
       </c>
       <c r="B377" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -6198,7 +6210,7 @@
         <v>377</v>
       </c>
       <c r="B378" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -6206,7 +6218,7 @@
         <v>378</v>
       </c>
       <c r="B379" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -6214,7 +6226,7 @@
         <v>379</v>
       </c>
       <c r="B380" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -6222,7 +6234,7 @@
         <v>380</v>
       </c>
       <c r="B381" s="1">
-        <v>1020</v>
+        <v>860</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -6230,7 +6242,7 @@
         <v>381</v>
       </c>
       <c r="B382" s="1">
-        <v>880</v>
+        <v>960</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -6238,7 +6250,7 @@
         <v>382</v>
       </c>
       <c r="B383" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -6246,7 +6258,7 @@
         <v>383</v>
       </c>
       <c r="B384" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -6254,7 +6266,7 @@
         <v>384</v>
       </c>
       <c r="B385" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -6262,7 +6274,7 @@
         <v>385</v>
       </c>
       <c r="B386" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -6270,7 +6282,7 @@
         <v>386</v>
       </c>
       <c r="B387" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -6278,7 +6290,7 @@
         <v>387</v>
       </c>
       <c r="B388" s="1">
-        <v>1020</v>
+        <v>640</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -6294,7 +6306,7 @@
         <v>389</v>
       </c>
       <c r="B390" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -6302,7 +6314,7 @@
         <v>390</v>
       </c>
       <c r="B391" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -6310,7 +6322,7 @@
         <v>391</v>
       </c>
       <c r="B392" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -6318,7 +6330,7 @@
         <v>392</v>
       </c>
       <c r="B393" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -6326,7 +6338,7 @@
         <v>393</v>
       </c>
       <c r="B394" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -6342,7 +6354,7 @@
         <v>395</v>
       </c>
       <c r="B396" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -6350,7 +6362,7 @@
         <v>396</v>
       </c>
       <c r="B397" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -6366,7 +6378,7 @@
         <v>398</v>
       </c>
       <c r="B399" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -6374,7 +6386,7 @@
         <v>399</v>
       </c>
       <c r="B400" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -6390,7 +6402,7 @@
         <v>401</v>
       </c>
       <c r="B402" s="1">
-        <v>680</v>
+        <v>820</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -6398,7 +6410,7 @@
         <v>402</v>
       </c>
       <c r="B403" s="1">
-        <v>480</v>
+        <v>740</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -6406,7 +6418,7 @@
         <v>403</v>
       </c>
       <c r="B404" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -6414,7 +6426,7 @@
         <v>404</v>
       </c>
       <c r="B405" s="1">
-        <v>1000</v>
+        <v>480</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -6422,7 +6434,7 @@
         <v>405</v>
       </c>
       <c r="B406" s="1">
-        <v>920</v>
+        <v>640</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -6430,7 +6442,7 @@
         <v>406</v>
       </c>
       <c r="B407" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -6438,7 +6450,7 @@
         <v>407</v>
       </c>
       <c r="B408" s="1">
-        <v>520</v>
+        <v>920</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -6446,7 +6458,7 @@
         <v>408</v>
       </c>
       <c r="B409" s="1">
-        <v>540</v>
+        <v>860</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -6454,7 +6466,7 @@
         <v>409</v>
       </c>
       <c r="B410" s="1">
-        <v>700</v>
+        <v>520</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -6462,7 +6474,7 @@
         <v>410</v>
       </c>
       <c r="B411" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -6470,7 +6482,7 @@
         <v>411</v>
       </c>
       <c r="B412" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -6486,7 +6498,7 @@
         <v>413</v>
       </c>
       <c r="B414" s="1">
-        <v>720</v>
+        <v>420</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -6494,7 +6506,7 @@
         <v>414</v>
       </c>
       <c r="B415" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -6502,7 +6514,7 @@
         <v>415</v>
       </c>
       <c r="B416" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -6510,7 +6522,7 @@
         <v>416</v>
       </c>
       <c r="B417" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -6518,7 +6530,7 @@
         <v>417</v>
       </c>
       <c r="B418" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -6526,7 +6538,7 @@
         <v>418</v>
       </c>
       <c r="B419" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -6534,7 +6546,7 @@
         <v>419</v>
       </c>
       <c r="B420" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -6542,7 +6554,7 @@
         <v>420</v>
       </c>
       <c r="B421" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -6550,7 +6562,7 @@
         <v>421</v>
       </c>
       <c r="B422" s="1">
-        <v>440</v>
+        <v>720</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -6558,7 +6570,7 @@
         <v>422</v>
       </c>
       <c r="B423" s="1">
-        <v>1100</v>
+        <v>620</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -6566,7 +6578,7 @@
         <v>423</v>
       </c>
       <c r="B424" s="1">
-        <v>1100</v>
+        <v>440</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -6574,7 +6586,7 @@
         <v>424</v>
       </c>
       <c r="B425" s="1">
-        <v>320</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -6582,7 +6594,7 @@
         <v>425</v>
       </c>
       <c r="B426" s="1">
-        <v>940</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -6598,7 +6610,7 @@
         <v>427</v>
       </c>
       <c r="B428" s="1">
-        <v>960</v>
+        <v>940</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6606,7 +6618,7 @@
         <v>428</v>
       </c>
       <c r="B429" s="1">
-        <v>980</v>
+        <v>320</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6614,7 +6626,7 @@
         <v>429</v>
       </c>
       <c r="B430" s="1">
-        <v>820</v>
+        <v>960</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6622,7 +6634,7 @@
         <v>430</v>
       </c>
       <c r="B431" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6630,7 +6642,7 @@
         <v>431</v>
       </c>
       <c r="B432" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6638,7 +6650,7 @@
         <v>432</v>
       </c>
       <c r="B433" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6646,7 +6658,7 @@
         <v>433</v>
       </c>
       <c r="B434" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6654,7 +6666,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6662,7 +6674,7 @@
         <v>435</v>
       </c>
       <c r="B436" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6670,7 +6682,7 @@
         <v>436</v>
       </c>
       <c r="B437" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6678,7 +6690,7 @@
         <v>437</v>
       </c>
       <c r="B438" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6686,7 +6698,7 @@
         <v>438</v>
       </c>
       <c r="B439" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6694,7 +6706,7 @@
         <v>439</v>
       </c>
       <c r="B440" s="1">
-        <v>920</v>
+        <v>620</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6702,7 +6714,7 @@
         <v>440</v>
       </c>
       <c r="B441" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6710,7 +6722,7 @@
         <v>441</v>
       </c>
       <c r="B442" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6718,7 +6730,7 @@
         <v>442</v>
       </c>
       <c r="B443" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6734,7 +6746,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6742,7 +6754,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6750,7 +6762,7 @@
         <v>446</v>
       </c>
       <c r="B447" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6758,7 +6770,7 @@
         <v>447</v>
       </c>
       <c r="B448" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6766,7 +6778,7 @@
         <v>448</v>
       </c>
       <c r="B449" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6774,7 +6786,7 @@
         <v>449</v>
       </c>
       <c r="B450" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6790,7 +6802,7 @@
         <v>451</v>
       </c>
       <c r="B452" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6798,7 +6810,7 @@
         <v>452</v>
       </c>
       <c r="B453" s="1">
-        <v>440</v>
+        <v>900</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6806,7 +6818,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6814,7 +6826,7 @@
         <v>454</v>
       </c>
       <c r="B455" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6822,7 +6834,7 @@
         <v>455</v>
       </c>
       <c r="B456" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6830,7 +6842,7 @@
         <v>456</v>
       </c>
       <c r="B457" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6838,7 +6850,7 @@
         <v>457</v>
       </c>
       <c r="B458" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6846,7 +6858,7 @@
         <v>458</v>
       </c>
       <c r="B459" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6854,7 +6866,7 @@
         <v>459</v>
       </c>
       <c r="B460" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6862,7 +6874,7 @@
         <v>460</v>
       </c>
       <c r="B461" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6870,7 +6882,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6878,7 +6890,7 @@
         <v>462</v>
       </c>
       <c r="B463" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6886,7 +6898,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6894,7 +6906,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6902,7 +6914,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="1">
-        <v>680</v>
+        <v>620</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6910,7 +6922,7 @@
         <v>466</v>
       </c>
       <c r="B467" s="1">
-        <v>480</v>
+        <v>720</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6918,7 +6930,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6926,7 +6938,7 @@
         <v>468</v>
       </c>
       <c r="B469" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6934,7 +6946,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="1">
-        <v>840</v>
+        <v>480</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6942,7 +6954,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6950,7 +6962,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6966,7 +6978,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6974,7 +6986,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="1">
-        <v>920</v>
+        <v>880</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6982,7 +6994,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6990,7 +7002,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6998,7 +7010,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="1">
-        <v>940</v>
+        <v>800</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -7006,7 +7018,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -7014,7 +7026,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -7022,7 +7034,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="1">
-        <v>600</v>
+        <v>980</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -7030,7 +7042,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="1">
-        <v>760</v>
+        <v>920</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -7038,7 +7050,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -7046,7 +7058,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="1">
-        <v>620</v>
+        <v>760</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -7054,7 +7066,7 @@
         <v>484</v>
       </c>
       <c r="B485" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -7062,7 +7074,7 @@
         <v>485</v>
       </c>
       <c r="B486" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -7070,7 +7082,7 @@
         <v>486</v>
       </c>
       <c r="B487" s="1">
-        <v>920</v>
+        <v>620</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -7078,7 +7090,7 @@
         <v>487</v>
       </c>
       <c r="B488" s="1">
-        <v>640</v>
+        <v>860</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -7086,7 +7098,7 @@
         <v>488</v>
       </c>
       <c r="B489" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -7094,7 +7106,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="1">
-        <v>820</v>
+        <v>640</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -7102,7 +7114,7 @@
         <v>490</v>
       </c>
       <c r="B491" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -7110,7 +7122,7 @@
         <v>491</v>
       </c>
       <c r="B492" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -7118,7 +7130,7 @@
         <v>492</v>
       </c>
       <c r="B493" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -7126,7 +7138,7 @@
         <v>493</v>
       </c>
       <c r="B494" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -7134,7 +7146,7 @@
         <v>494</v>
       </c>
       <c r="B495" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -7142,7 +7154,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -7150,7 +7162,7 @@
         <v>496</v>
       </c>
       <c r="B497" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -7158,7 +7170,7 @@
         <v>497</v>
       </c>
       <c r="B498" s="1">
-        <v>660</v>
+        <v>560</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -7166,7 +7178,7 @@
         <v>498</v>
       </c>
       <c r="B499" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -7174,7 +7186,7 @@
         <v>499</v>
       </c>
       <c r="B500" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -7182,7 +7194,7 @@
         <v>500</v>
       </c>
       <c r="B501" s="1">
-        <v>840</v>
+        <v>640</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -7190,7 +7202,7 @@
         <v>501</v>
       </c>
       <c r="B502" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -7198,7 +7210,7 @@
         <v>502</v>
       </c>
       <c r="B503" s="1">
-        <v>480</v>
+        <v>840</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -7206,7 +7218,7 @@
         <v>503</v>
       </c>
       <c r="B504" s="1">
-        <v>620</v>
+        <v>520</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -7214,7 +7226,7 @@
         <v>504</v>
       </c>
       <c r="B505" s="1">
-        <v>780</v>
+        <v>480</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -7222,7 +7234,7 @@
         <v>505</v>
       </c>
       <c r="B506" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -7230,7 +7242,7 @@
         <v>506</v>
       </c>
       <c r="B507" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -7238,7 +7250,7 @@
         <v>507</v>
       </c>
       <c r="B508" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -7246,7 +7258,7 @@
         <v>508</v>
       </c>
       <c r="B509" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -7254,7 +7266,7 @@
         <v>509</v>
       </c>
       <c r="B510" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -7262,7 +7274,7 @@
         <v>510</v>
       </c>
       <c r="B511" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -7270,7 +7282,7 @@
         <v>511</v>
       </c>
       <c r="B512" s="1">
-        <v>480</v>
+        <v>780</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -7278,7 +7290,7 @@
         <v>512</v>
       </c>
       <c r="B513" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -7286,7 +7298,7 @@
         <v>513</v>
       </c>
       <c r="B514" s="1">
-        <v>660</v>
+        <v>480</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -7294,7 +7306,7 @@
         <v>514</v>
       </c>
       <c r="B515" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -7302,7 +7314,7 @@
         <v>515</v>
       </c>
       <c r="B516" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -7310,7 +7322,7 @@
         <v>516</v>
       </c>
       <c r="B517" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -7318,7 +7330,7 @@
         <v>517</v>
       </c>
       <c r="B518" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -7326,7 +7338,7 @@
         <v>518</v>
       </c>
       <c r="B519" s="1">
-        <v>940</v>
+        <v>440</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -7334,7 +7346,7 @@
         <v>519</v>
       </c>
       <c r="B520" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -7342,7 +7354,7 @@
         <v>520</v>
       </c>
       <c r="B521" s="1">
-        <v>880</v>
+        <v>940</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -7350,7 +7362,7 @@
         <v>521</v>
       </c>
       <c r="B522" s="1">
-        <v>880</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -7358,7 +7370,7 @@
         <v>522</v>
       </c>
       <c r="B523" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -7366,7 +7378,7 @@
         <v>523</v>
       </c>
       <c r="B524" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -7374,7 +7386,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -7382,7 +7394,7 @@
         <v>525</v>
       </c>
       <c r="B526" s="1">
-        <v>1100</v>
+        <v>840</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -7390,7 +7402,7 @@
         <v>526</v>
       </c>
       <c r="B527" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -7398,7 +7410,7 @@
         <v>527</v>
       </c>
       <c r="B528" s="1">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -7406,7 +7418,7 @@
         <v>528</v>
       </c>
       <c r="B529" s="1">
-        <v>760</v>
+        <v>840</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -7414,7 +7426,7 @@
         <v>529</v>
       </c>
       <c r="B530" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -7422,7 +7434,7 @@
         <v>530</v>
       </c>
       <c r="B531" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -7430,7 +7442,7 @@
         <v>531</v>
       </c>
       <c r="B532" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -7438,7 +7450,7 @@
         <v>532</v>
       </c>
       <c r="B533" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -7446,7 +7458,7 @@
         <v>533</v>
       </c>
       <c r="B534" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -7454,7 +7466,7 @@
         <v>534</v>
       </c>
       <c r="B535" s="1">
-        <v>760</v>
+        <v>840</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -7462,7 +7474,7 @@
         <v>535</v>
       </c>
       <c r="B536" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -7470,7 +7482,7 @@
         <v>536</v>
       </c>
       <c r="B537" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -7478,7 +7490,7 @@
         <v>537</v>
       </c>
       <c r="B538" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -7486,7 +7498,7 @@
         <v>538</v>
       </c>
       <c r="B539" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -7494,7 +7506,7 @@
         <v>539</v>
       </c>
       <c r="B540" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -7502,7 +7514,7 @@
         <v>540</v>
       </c>
       <c r="B541" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -7510,7 +7522,7 @@
         <v>541</v>
       </c>
       <c r="B542" s="1">
-        <v>660</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -7518,7 +7530,7 @@
         <v>542</v>
       </c>
       <c r="B543" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -7526,7 +7538,7 @@
         <v>543</v>
       </c>
       <c r="B544" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -7534,7 +7546,7 @@
         <v>544</v>
       </c>
       <c r="B545" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -7542,7 +7554,7 @@
         <v>545</v>
       </c>
       <c r="B546" s="1">
-        <v>880</v>
+        <v>620</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -7550,7 +7562,7 @@
         <v>546</v>
       </c>
       <c r="B547" s="1">
-        <v>1060</v>
+        <v>840</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -7558,7 +7570,7 @@
         <v>547</v>
       </c>
       <c r="B548" s="1">
-        <v>860</v>
+        <v>880</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -7566,7 +7578,7 @@
         <v>548</v>
       </c>
       <c r="B549" s="1">
-        <v>860</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -7574,7 +7586,7 @@
         <v>549</v>
       </c>
       <c r="B550" s="1">
-        <v>800</v>
+        <v>860</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -7590,7 +7602,7 @@
         <v>551</v>
       </c>
       <c r="B552" s="1">
-        <v>960</v>
+        <v>800</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7598,7 +7610,7 @@
         <v>552</v>
       </c>
       <c r="B553" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7606,7 +7618,7 @@
         <v>553</v>
       </c>
       <c r="B554" s="1">
-        <v>720</v>
+        <v>960</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7614,7 +7626,7 @@
         <v>554</v>
       </c>
       <c r="B555" s="1">
-        <v>1000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7622,7 +7634,7 @@
         <v>555</v>
       </c>
       <c r="B556" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7630,7 +7642,7 @@
         <v>556</v>
       </c>
       <c r="B557" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7638,7 +7650,7 @@
         <v>557</v>
       </c>
       <c r="B558" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7646,7 +7658,7 @@
         <v>558</v>
       </c>
       <c r="B559" s="1">
-        <v>980</v>
+        <v>900</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7654,7 +7666,7 @@
         <v>559</v>
       </c>
       <c r="B560" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7662,7 +7674,7 @@
         <v>560</v>
       </c>
       <c r="B561" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7670,7 +7682,7 @@
         <v>561</v>
       </c>
       <c r="B562" s="1">
-        <v>980</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7686,7 +7698,7 @@
         <v>563</v>
       </c>
       <c r="B564" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7694,7 +7706,7 @@
         <v>564</v>
       </c>
       <c r="B565" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7702,7 +7714,7 @@
         <v>565</v>
       </c>
       <c r="B566" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7718,7 +7730,7 @@
         <v>567</v>
       </c>
       <c r="B568" s="1">
-        <v>640</v>
+        <v>900</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7726,7 +7738,7 @@
         <v>568</v>
       </c>
       <c r="B569" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7734,7 +7746,7 @@
         <v>569</v>
       </c>
       <c r="B570" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7742,7 +7754,7 @@
         <v>570</v>
       </c>
       <c r="B571" s="1">
-        <v>980</v>
+        <v>800</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7750,7 +7762,7 @@
         <v>571</v>
       </c>
       <c r="B572" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7758,7 +7770,7 @@
         <v>572</v>
       </c>
       <c r="B573" s="1">
-        <v>700</v>
+        <v>980</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7766,7 +7778,7 @@
         <v>573</v>
       </c>
       <c r="B574" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7774,7 +7786,7 @@
         <v>574</v>
       </c>
       <c r="B575" s="1">
-        <v>880</v>
+        <v>700</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7782,7 +7794,7 @@
         <v>575</v>
       </c>
       <c r="B576" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7790,7 +7802,7 @@
         <v>576</v>
       </c>
       <c r="B577" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7798,7 +7810,7 @@
         <v>577</v>
       </c>
       <c r="B578" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7806,7 +7818,7 @@
         <v>578</v>
       </c>
       <c r="B579" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7814,7 +7826,7 @@
         <v>579</v>
       </c>
       <c r="B580" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7822,7 +7834,7 @@
         <v>580</v>
       </c>
       <c r="B581" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7830,7 +7842,7 @@
         <v>581</v>
       </c>
       <c r="B582" s="1">
-        <v>880</v>
+        <v>760</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7838,7 +7850,7 @@
         <v>582</v>
       </c>
       <c r="B583" s="1">
-        <v>640</v>
+        <v>920</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7846,7 +7858,7 @@
         <v>583</v>
       </c>
       <c r="B584" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7854,7 +7866,7 @@
         <v>584</v>
       </c>
       <c r="B585" s="1">
-        <v>600</v>
+        <v>880</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7862,7 +7874,7 @@
         <v>585</v>
       </c>
       <c r="B586" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7870,7 +7882,7 @@
         <v>586</v>
       </c>
       <c r="B587" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7878,7 +7890,7 @@
         <v>587</v>
       </c>
       <c r="B588" s="1">
-        <v>860</v>
+        <v>600</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7886,7 +7898,7 @@
         <v>588</v>
       </c>
       <c r="B589" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7894,7 +7906,7 @@
         <v>589</v>
       </c>
       <c r="B590" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7910,7 +7922,7 @@
         <v>591</v>
       </c>
       <c r="B592" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7918,7 +7930,7 @@
         <v>592</v>
       </c>
       <c r="B593" s="1">
-        <v>960</v>
+        <v>840</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7926,7 +7938,7 @@
         <v>593</v>
       </c>
       <c r="B594" s="1">
-        <v>940</v>
+        <v>860</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7934,7 +7946,7 @@
         <v>594</v>
       </c>
       <c r="B595" s="1">
-        <v>1040</v>
+        <v>720</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7942,7 +7954,7 @@
         <v>595</v>
       </c>
       <c r="B596" s="1">
-        <v>1040</v>
+        <v>960</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7958,7 +7970,7 @@
         <v>597</v>
       </c>
       <c r="B598" s="1">
-        <v>860</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7966,7 +7978,7 @@
         <v>598</v>
       </c>
       <c r="B599" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7974,7 +7986,7 @@
         <v>599</v>
       </c>
       <c r="B600" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7982,7 +7994,7 @@
         <v>600</v>
       </c>
       <c r="B601" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7990,7 +8002,7 @@
         <v>601</v>
       </c>
       <c r="B602" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7998,7 +8010,7 @@
         <v>602</v>
       </c>
       <c r="B603" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -8006,7 +8018,7 @@
         <v>603</v>
       </c>
       <c r="B604" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -8014,7 +8026,7 @@
         <v>604</v>
       </c>
       <c r="B605" s="1">
-        <v>880</v>
+        <v>680</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -8022,7 +8034,7 @@
         <v>605</v>
       </c>
       <c r="B606" s="1">
-        <v>580</v>
+        <v>840</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -8030,7 +8042,7 @@
         <v>606</v>
       </c>
       <c r="B607" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -8038,7 +8050,7 @@
         <v>607</v>
       </c>
       <c r="B608" s="1">
-        <v>860</v>
+        <v>880</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -8046,7 +8058,7 @@
         <v>608</v>
       </c>
       <c r="B609" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -8054,7 +8066,7 @@
         <v>609</v>
       </c>
       <c r="B610" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -8062,7 +8074,7 @@
         <v>610</v>
       </c>
       <c r="B611" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -8070,7 +8082,7 @@
         <v>611</v>
       </c>
       <c r="B612" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -8078,7 +8090,7 @@
         <v>612</v>
       </c>
       <c r="B613" s="1">
-        <v>700</v>
+        <v>620</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -8086,7 +8098,7 @@
         <v>613</v>
       </c>
       <c r="B614" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -8094,7 +8106,7 @@
         <v>614</v>
       </c>
       <c r="B615" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -8102,7 +8114,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -8110,7 +8122,7 @@
         <v>616</v>
       </c>
       <c r="B617" s="1">
-        <v>720</v>
+        <v>960</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -8118,7 +8130,7 @@
         <v>617</v>
       </c>
       <c r="B618" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -8126,7 +8138,7 @@
         <v>618</v>
       </c>
       <c r="B619" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -8134,7 +8146,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="1">
-        <v>920</v>
+        <v>720</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -8142,7 +8154,7 @@
         <v>620</v>
       </c>
       <c r="B621" s="1">
-        <v>540</v>
+        <v>800</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -8150,7 +8162,7 @@
         <v>621</v>
       </c>
       <c r="B622" s="1">
-        <v>980</v>
+        <v>780</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -8158,7 +8170,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="1">
-        <v>1100</v>
+        <v>920</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -8166,7 +8178,7 @@
         <v>623</v>
       </c>
       <c r="B624" s="1">
-        <v>1060</v>
+        <v>540</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -8174,7 +8186,7 @@
         <v>624</v>
       </c>
       <c r="B625" s="1">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -8190,7 +8202,7 @@
         <v>626</v>
       </c>
       <c r="B627" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -8198,7 +8210,7 @@
         <v>627</v>
       </c>
       <c r="B628" s="1">
-        <v>1080</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -8206,7 +8218,7 @@
         <v>628</v>
       </c>
       <c r="B629" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -8214,7 +8226,7 @@
         <v>629</v>
       </c>
       <c r="B630" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -8222,7 +8234,7 @@
         <v>630</v>
       </c>
       <c r="B631" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -8230,7 +8242,7 @@
         <v>631</v>
       </c>
       <c r="B632" s="1">
-        <v>560</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -8238,7 +8250,7 @@
         <v>632</v>
       </c>
       <c r="B633" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -8246,7 +8258,7 @@
         <v>633</v>
       </c>
       <c r="B634" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -8254,7 +8266,7 @@
         <v>634</v>
       </c>
       <c r="B635" s="1">
-        <v>860</v>
+        <v>720</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -8262,7 +8274,7 @@
         <v>635</v>
       </c>
       <c r="B636" s="1">
-        <v>980</v>
+        <v>560</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -8278,7 +8290,7 @@
         <v>637</v>
       </c>
       <c r="B638" s="1">
-        <v>760</v>
+        <v>620</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -8286,7 +8298,7 @@
         <v>638</v>
       </c>
       <c r="B639" s="1">
-        <v>1100</v>
+        <v>860</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -8294,7 +8306,7 @@
         <v>639</v>
       </c>
       <c r="B640" s="1">
-        <v>1100</v>
+        <v>980</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -8302,7 +8314,7 @@
         <v>640</v>
       </c>
       <c r="B641" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -8310,7 +8322,7 @@
         <v>641</v>
       </c>
       <c r="B642" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -8318,7 +8330,7 @@
         <v>642</v>
       </c>
       <c r="B643" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -8326,7 +8338,7 @@
         <v>643</v>
       </c>
       <c r="B644" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -8334,7 +8346,7 @@
         <v>644</v>
       </c>
       <c r="B645" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -8342,7 +8354,7 @@
         <v>645</v>
       </c>
       <c r="B646" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -8350,7 +8362,7 @@
         <v>646</v>
       </c>
       <c r="B647" s="1">
-        <v>960</v>
+        <v>920</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -8358,7 +8370,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -8366,7 +8378,7 @@
         <v>648</v>
       </c>
       <c r="B649" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -8374,7 +8386,7 @@
         <v>649</v>
       </c>
       <c r="B650" s="1">
-        <v>980</v>
+        <v>700</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -8382,7 +8394,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="1">
-        <v>720</v>
+        <v>960</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -8390,7 +8402,7 @@
         <v>651</v>
       </c>
       <c r="B652" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -8398,7 +8410,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -8406,7 +8418,7 @@
         <v>653</v>
       </c>
       <c r="B654" s="1">
-        <v>760</v>
+        <v>980</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -8414,7 +8426,7 @@
         <v>654</v>
       </c>
       <c r="B655" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -8422,7 +8434,7 @@
         <v>655</v>
       </c>
       <c r="B656" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -8430,7 +8442,7 @@
         <v>656</v>
       </c>
       <c r="B657" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -8438,7 +8450,7 @@
         <v>657</v>
       </c>
       <c r="B658" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -8446,7 +8458,7 @@
         <v>658</v>
       </c>
       <c r="B659" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -8454,7 +8466,7 @@
         <v>659</v>
       </c>
       <c r="B660" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -8462,7 +8474,7 @@
         <v>660</v>
       </c>
       <c r="B661" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -8470,7 +8482,7 @@
         <v>661</v>
       </c>
       <c r="B662" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -8478,7 +8490,7 @@
         <v>662</v>
       </c>
       <c r="B663" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -8486,7 +8498,7 @@
         <v>663</v>
       </c>
       <c r="B664" s="1">
-        <v>1400</v>
+        <v>700</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -8494,7 +8506,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -8502,7 +8514,7 @@
         <v>665</v>
       </c>
       <c r="B666" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -8510,7 +8522,7 @@
         <v>666</v>
       </c>
       <c r="B667" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -8518,7 +8530,7 @@
         <v>667</v>
       </c>
       <c r="B668" s="1">
-        <v>740</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -8534,7 +8546,7 @@
         <v>669</v>
       </c>
       <c r="B670" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -8542,7 +8554,7 @@
         <v>670</v>
       </c>
       <c r="B671" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -8550,7 +8562,7 @@
         <v>671</v>
       </c>
       <c r="B672" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -8558,7 +8570,7 @@
         <v>672</v>
       </c>
       <c r="B673" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -8566,7 +8578,7 @@
         <v>673</v>
       </c>
       <c r="B674" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -8574,7 +8586,7 @@
         <v>674</v>
       </c>
       <c r="B675" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8582,7 +8594,7 @@
         <v>675</v>
       </c>
       <c r="B676" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -8590,7 +8602,7 @@
         <v>676</v>
       </c>
       <c r="B677" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8598,7 +8610,7 @@
         <v>677</v>
       </c>
       <c r="B678" s="1">
-        <v>980</v>
+        <v>900</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8614,7 +8626,7 @@
         <v>679</v>
       </c>
       <c r="B680" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8622,7 +8634,7 @@
         <v>680</v>
       </c>
       <c r="B681" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8630,7 +8642,7 @@
         <v>681</v>
       </c>
       <c r="B682" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8646,7 +8658,7 @@
         <v>683</v>
       </c>
       <c r="B684" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8654,7 +8666,7 @@
         <v>684</v>
       </c>
       <c r="B685" s="1">
-        <v>800</v>
+        <v>820</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8662,7 +8674,7 @@
         <v>685</v>
       </c>
       <c r="B686" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8670,7 +8682,7 @@
         <v>686</v>
       </c>
       <c r="B687" s="1">
-        <v>4000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8678,7 +8690,7 @@
         <v>687</v>
       </c>
       <c r="B688" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8686,7 +8698,7 @@
         <v>688</v>
       </c>
       <c r="B689" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8694,7 +8706,7 @@
         <v>689</v>
       </c>
       <c r="B690" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8702,7 +8714,7 @@
         <v>690</v>
       </c>
       <c r="B691" s="1">
-        <v>700</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8710,7 +8722,7 @@
         <v>691</v>
       </c>
       <c r="B692" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8718,7 +8730,7 @@
         <v>692</v>
       </c>
       <c r="B693" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8734,7 +8746,7 @@
         <v>694</v>
       </c>
       <c r="B695" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8742,7 +8754,7 @@
         <v>695</v>
       </c>
       <c r="B696" s="1">
-        <v>540</v>
+        <v>680</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8750,7 +8762,7 @@
         <v>696</v>
       </c>
       <c r="B697" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8758,7 +8770,7 @@
         <v>697</v>
       </c>
       <c r="B698" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8774,7 +8786,7 @@
         <v>699</v>
       </c>
       <c r="B700" s="1">
-        <v>860</v>
+        <v>540</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8782,7 +8794,7 @@
         <v>700</v>
       </c>
       <c r="B701" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8790,7 +8802,7 @@
         <v>701</v>
       </c>
       <c r="B702" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8806,7 +8818,7 @@
         <v>703</v>
       </c>
       <c r="B704" s="1">
-        <v>980</v>
+        <v>860</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8814,7 +8826,7 @@
         <v>704</v>
       </c>
       <c r="B705" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8822,7 +8834,7 @@
         <v>705</v>
       </c>
       <c r="B706" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8838,7 +8850,7 @@
         <v>707</v>
       </c>
       <c r="B708" s="1">
-        <v>1040</v>
+        <v>980</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8846,7 +8858,7 @@
         <v>708</v>
       </c>
       <c r="B709" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8862,7 +8874,7 @@
         <v>710</v>
       </c>
       <c r="B711" s="1">
-        <v>860</v>
+        <v>900</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8870,7 +8882,7 @@
         <v>711</v>
       </c>
       <c r="B712" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8878,7 +8890,7 @@
         <v>712</v>
       </c>
       <c r="B713" s="1">
-        <v>840</v>
+        <v>680</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8894,7 +8906,7 @@
         <v>714</v>
       </c>
       <c r="B715" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8902,7 +8914,7 @@
         <v>715</v>
       </c>
       <c r="B716" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8910,7 +8922,7 @@
         <v>716</v>
       </c>
       <c r="B717" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8918,7 +8930,7 @@
         <v>717</v>
       </c>
       <c r="B718" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8926,7 +8938,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8934,7 +8946,7 @@
         <v>719</v>
       </c>
       <c r="B720" s="1">
-        <v>700</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8942,7 +8954,7 @@
         <v>720</v>
       </c>
       <c r="B721" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8950,7 +8962,7 @@
         <v>721</v>
       </c>
       <c r="B722" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8958,7 +8970,7 @@
         <v>722</v>
       </c>
       <c r="B723" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8966,7 +8978,7 @@
         <v>723</v>
       </c>
       <c r="B724" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8974,7 +8986,7 @@
         <v>724</v>
       </c>
       <c r="B725" s="1">
-        <v>640</v>
+        <v>840</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8982,7 +8994,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8990,7 +9002,7 @@
         <v>726</v>
       </c>
       <c r="B727" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8998,7 +9010,7 @@
         <v>727</v>
       </c>
       <c r="B728" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -9006,7 +9018,7 @@
         <v>728</v>
       </c>
       <c r="B729" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -9014,7 +9026,7 @@
         <v>729</v>
       </c>
       <c r="B730" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -9022,7 +9034,7 @@
         <v>730</v>
       </c>
       <c r="B731" s="1">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -9030,7 +9042,7 @@
         <v>731</v>
       </c>
       <c r="B732" s="1">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -9038,7 +9050,7 @@
         <v>732</v>
       </c>
       <c r="B733" s="1">
-        <v>800</v>
+        <v>740</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -9046,7 +9058,7 @@
         <v>733</v>
       </c>
       <c r="B734" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -9054,7 +9066,7 @@
         <v>734</v>
       </c>
       <c r="B735" s="1">
-        <v>800</v>
+        <v>820</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -9062,7 +9074,7 @@
         <v>735</v>
       </c>
       <c r="B736" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -9070,7 +9082,7 @@
         <v>736</v>
       </c>
       <c r="B737" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -9086,7 +9098,7 @@
         <v>738</v>
       </c>
       <c r="B739" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="740" spans="1:2">
@@ -9094,7 +9106,7 @@
         <v>739</v>
       </c>
       <c r="B740" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -9102,7 +9114,7 @@
         <v>740</v>
       </c>
       <c r="B741" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="742" spans="1:2">
@@ -9110,7 +9122,7 @@
         <v>741</v>
       </c>
       <c r="B742" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -9126,7 +9138,7 @@
         <v>743</v>
       </c>
       <c r="B744" s="1">
-        <v>840</v>
+        <v>960</v>
       </c>
     </row>
     <row r="745" spans="1:2">
@@ -9134,7 +9146,7 @@
         <v>744</v>
       </c>
       <c r="B745" s="1">
-        <v>700</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -9142,7 +9154,7 @@
         <v>745</v>
       </c>
       <c r="B746" s="1">
-        <v>640</v>
+        <v>880</v>
       </c>
     </row>
     <row r="747" spans="1:2">
@@ -9158,7 +9170,7 @@
         <v>747</v>
       </c>
       <c r="B748" s="1">
-        <v>1020</v>
+        <v>840</v>
       </c>
     </row>
     <row r="749" spans="1:2">
@@ -9166,7 +9178,7 @@
         <v>748</v>
       </c>
       <c r="B749" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -9174,7 +9186,7 @@
         <v>749</v>
       </c>
       <c r="B750" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="751" spans="1:2">
@@ -9182,7 +9194,7 @@
         <v>750</v>
       </c>
       <c r="B751" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="752" spans="1:2">
@@ -9190,7 +9202,7 @@
         <v>751</v>
       </c>
       <c r="B752" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="753" spans="1:2">
@@ -9198,7 +9210,7 @@
         <v>752</v>
       </c>
       <c r="B753" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="754" spans="1:2">
@@ -9206,7 +9218,7 @@
         <v>753</v>
       </c>
       <c r="B754" s="1">
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -9214,7 +9226,7 @@
         <v>754</v>
       </c>
       <c r="B755" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="756" spans="1:2">
@@ -9222,7 +9234,7 @@
         <v>755</v>
       </c>
       <c r="B756" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="757" spans="1:2">
@@ -9230,7 +9242,7 @@
         <v>756</v>
       </c>
       <c r="B757" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="758" spans="1:2">
@@ -9238,7 +9250,7 @@
         <v>757</v>
       </c>
       <c r="B758" s="1">
-        <v>820</v>
+        <v>720</v>
       </c>
     </row>
     <row r="759" spans="1:2">
@@ -9246,7 +9258,7 @@
         <v>758</v>
       </c>
       <c r="B759" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="760" spans="1:2">
@@ -9254,7 +9266,7 @@
         <v>759</v>
       </c>
       <c r="B760" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="761" spans="1:2">
@@ -9262,7 +9274,7 @@
         <v>760</v>
       </c>
       <c r="B761" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="762" spans="1:2">
@@ -9270,7 +9282,7 @@
         <v>761</v>
       </c>
       <c r="B762" s="1">
-        <v>920</v>
+        <v>820</v>
       </c>
     </row>
     <row r="763" spans="1:2">
@@ -9278,7 +9290,7 @@
         <v>762</v>
       </c>
       <c r="B763" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="764" spans="1:2">
@@ -9286,7 +9298,7 @@
         <v>763</v>
       </c>
       <c r="B764" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="765" spans="1:2">
@@ -9294,7 +9306,7 @@
         <v>764</v>
       </c>
       <c r="B765" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="766" spans="1:2">
@@ -9302,7 +9314,7 @@
         <v>765</v>
       </c>
       <c r="B766" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="767" spans="1:2">
@@ -9310,7 +9322,7 @@
         <v>766</v>
       </c>
       <c r="B767" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="768" spans="1:2">
@@ -9318,7 +9330,7 @@
         <v>767</v>
       </c>
       <c r="B768" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="769" spans="1:2">
@@ -9326,7 +9338,7 @@
         <v>768</v>
       </c>
       <c r="B769" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="770" spans="1:2">
@@ -9334,7 +9346,7 @@
         <v>769</v>
       </c>
       <c r="B770" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="771" spans="1:2">
@@ -9342,7 +9354,7 @@
         <v>770</v>
       </c>
       <c r="B771" s="1">
-        <v>940</v>
+        <v>840</v>
       </c>
     </row>
     <row r="772" spans="1:2">
@@ -9350,7 +9362,7 @@
         <v>771</v>
       </c>
       <c r="B772" s="1">
-        <v>980</v>
+        <v>720</v>
       </c>
     </row>
     <row r="773" spans="1:2">
@@ -9358,7 +9370,7 @@
         <v>772</v>
       </c>
       <c r="B773" s="1">
-        <v>820</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="774" spans="1:2">
@@ -9366,7 +9378,7 @@
         <v>773</v>
       </c>
       <c r="B774" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="775" spans="1:2">
@@ -9374,7 +9386,7 @@
         <v>774</v>
       </c>
       <c r="B775" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="776" spans="1:2">
@@ -9382,7 +9394,7 @@
         <v>775</v>
       </c>
       <c r="B776" s="1">
-        <v>900</v>
+        <v>980</v>
       </c>
     </row>
     <row r="777" spans="1:2">
@@ -9390,7 +9402,7 @@
         <v>776</v>
       </c>
       <c r="B777" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="778" spans="1:2">
@@ -9398,7 +9410,7 @@
         <v>777</v>
       </c>
       <c r="B778" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="779" spans="1:2">
@@ -9406,7 +9418,7 @@
         <v>778</v>
       </c>
       <c r="B779" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="780" spans="1:2">
@@ -9414,7 +9426,7 @@
         <v>779</v>
       </c>
       <c r="B780" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="781" spans="1:2">
@@ -9422,7 +9434,7 @@
         <v>780</v>
       </c>
       <c r="B781" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="782" spans="1:2">
@@ -9430,7 +9442,7 @@
         <v>781</v>
       </c>
       <c r="B782" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="783" spans="1:2">
@@ -9438,7 +9450,7 @@
         <v>782</v>
       </c>
       <c r="B783" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="784" spans="1:2">
@@ -9446,7 +9458,7 @@
         <v>783</v>
       </c>
       <c r="B784" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="785" spans="1:2">
@@ -9454,7 +9466,7 @@
         <v>784</v>
       </c>
       <c r="B785" s="1">
-        <v>660</v>
+        <v>880</v>
       </c>
     </row>
     <row r="786" spans="1:2">
@@ -9462,7 +9474,7 @@
         <v>785</v>
       </c>
       <c r="B786" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="787" spans="1:2">
@@ -9470,7 +9482,7 @@
         <v>786</v>
       </c>
       <c r="B787" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="788" spans="1:2">
@@ -9478,7 +9490,7 @@
         <v>787</v>
       </c>
       <c r="B788" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="789" spans="1:2">
@@ -9486,7 +9498,7 @@
         <v>788</v>
       </c>
       <c r="B789" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="790" spans="1:2">
@@ -9494,7 +9506,7 @@
         <v>789</v>
       </c>
       <c r="B790" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="791" spans="1:2">
@@ -9502,7 +9514,7 @@
         <v>790</v>
       </c>
       <c r="B791" s="1">
-        <v>440</v>
+        <v>900</v>
       </c>
     </row>
     <row r="792" spans="1:2">
@@ -9510,7 +9522,7 @@
         <v>791</v>
       </c>
       <c r="B792" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="793" spans="1:2">
@@ -9526,7 +9538,7 @@
         <v>793</v>
       </c>
       <c r="B794" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="795" spans="1:2">
@@ -9534,7 +9546,7 @@
         <v>794</v>
       </c>
       <c r="B795" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="796" spans="1:2">
@@ -9542,7 +9554,7 @@
         <v>795</v>
       </c>
       <c r="B796" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="797" spans="1:2">
@@ -9550,7 +9562,7 @@
         <v>796</v>
       </c>
       <c r="B797" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="798" spans="1:2">
@@ -9558,7 +9570,7 @@
         <v>797</v>
       </c>
       <c r="B798" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="799" spans="1:2">
@@ -9566,7 +9578,7 @@
         <v>798</v>
       </c>
       <c r="B799" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="800" spans="1:2">
@@ -9574,7 +9586,7 @@
         <v>799</v>
       </c>
       <c r="B800" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="801" spans="1:2">
@@ -9582,7 +9594,7 @@
         <v>800</v>
       </c>
       <c r="B801" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="802" spans="1:2">
@@ -9590,7 +9602,7 @@
         <v>801</v>
       </c>
       <c r="B802" s="1">
-        <v>800</v>
+        <v>560</v>
       </c>
     </row>
     <row r="803" spans="1:2">
@@ -9598,7 +9610,7 @@
         <v>802</v>
       </c>
       <c r="B803" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="804" spans="1:2">
@@ -9606,7 +9618,7 @@
         <v>803</v>
       </c>
       <c r="B804" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="805" spans="1:2">
@@ -9614,7 +9626,7 @@
         <v>804</v>
       </c>
       <c r="B805" s="1">
-        <v>920</v>
+        <v>880</v>
       </c>
     </row>
     <row r="806" spans="1:2">
@@ -9630,7 +9642,7 @@
         <v>806</v>
       </c>
       <c r="B807" s="1">
-        <v>940</v>
+        <v>880</v>
       </c>
     </row>
     <row r="808" spans="1:2">
@@ -9638,7 +9650,7 @@
         <v>807</v>
       </c>
       <c r="B808" s="1">
-        <v>980</v>
+        <v>780</v>
       </c>
     </row>
     <row r="809" spans="1:2">
@@ -9654,7 +9666,7 @@
         <v>809</v>
       </c>
       <c r="B810" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="811" spans="1:2">
@@ -9662,7 +9674,7 @@
         <v>810</v>
       </c>
       <c r="B811" s="1">
-        <v>860</v>
+        <v>940</v>
       </c>
     </row>
     <row r="812" spans="1:2">
@@ -9670,7 +9682,7 @@
         <v>811</v>
       </c>
       <c r="B812" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="813" spans="1:2">
@@ -9678,7 +9690,7 @@
         <v>812</v>
       </c>
       <c r="B813" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="814" spans="1:2">
@@ -9686,7 +9698,7 @@
         <v>813</v>
       </c>
       <c r="B814" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="815" spans="1:2">
@@ -9694,7 +9706,7 @@
         <v>814</v>
       </c>
       <c r="B815" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="816" spans="1:2">
@@ -9702,7 +9714,7 @@
         <v>815</v>
       </c>
       <c r="B816" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="817" spans="1:2">
@@ -9710,7 +9722,7 @@
         <v>816</v>
       </c>
       <c r="B817" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="818" spans="1:2">
@@ -9718,7 +9730,7 @@
         <v>817</v>
       </c>
       <c r="B818" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="819" spans="1:2">
@@ -9726,7 +9738,7 @@
         <v>818</v>
       </c>
       <c r="B819" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="820" spans="1:2">
@@ -9734,7 +9746,7 @@
         <v>819</v>
       </c>
       <c r="B820" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="821" spans="1:2">
@@ -9742,7 +9754,7 @@
         <v>820</v>
       </c>
       <c r="B821" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="822" spans="1:2">
@@ -9750,7 +9762,7 @@
         <v>821</v>
       </c>
       <c r="B822" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="823" spans="1:2">
@@ -9758,7 +9770,7 @@
         <v>822</v>
       </c>
       <c r="B823" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="824" spans="1:2">
@@ -9766,7 +9778,7 @@
         <v>823</v>
       </c>
       <c r="B824" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="825" spans="1:2">
@@ -9774,7 +9786,7 @@
         <v>824</v>
       </c>
       <c r="B825" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="826" spans="1:2">
@@ -9790,7 +9802,7 @@
         <v>826</v>
       </c>
       <c r="B827" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="828" spans="1:2">
@@ -9798,7 +9810,7 @@
         <v>827</v>
       </c>
       <c r="B828" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="829" spans="1:2">
@@ -9806,7 +9818,7 @@
         <v>828</v>
       </c>
       <c r="B829" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="830" spans="1:2">
@@ -9814,7 +9826,7 @@
         <v>829</v>
       </c>
       <c r="B830" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="831" spans="1:2">
@@ -9822,7 +9834,7 @@
         <v>830</v>
       </c>
       <c r="B831" s="1">
-        <v>740</v>
+        <v>600</v>
       </c>
     </row>
     <row r="832" spans="1:2">
@@ -9830,7 +9842,7 @@
         <v>831</v>
       </c>
       <c r="B832" s="1">
-        <v>760</v>
+        <v>840</v>
       </c>
     </row>
     <row r="833" spans="1:2">
@@ -9838,7 +9850,7 @@
         <v>832</v>
       </c>
       <c r="B833" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="834" spans="1:2">
@@ -9846,7 +9858,7 @@
         <v>833</v>
       </c>
       <c r="B834" s="1">
-        <v>700</v>
+        <v>960</v>
       </c>
     </row>
     <row r="835" spans="1:2">
@@ -9854,7 +9866,7 @@
         <v>834</v>
       </c>
       <c r="B835" s="1">
-        <v>800</v>
+        <v>740</v>
       </c>
     </row>
     <row r="836" spans="1:2">
@@ -9862,7 +9874,7 @@
         <v>835</v>
       </c>
       <c r="B836" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="837" spans="1:2">
@@ -9870,7 +9882,7 @@
         <v>836</v>
       </c>
       <c r="B837" s="1">
-        <v>680</v>
+        <v>840</v>
       </c>
     </row>
     <row r="838" spans="1:2">
@@ -9878,7 +9890,7 @@
         <v>837</v>
       </c>
       <c r="B838" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="839" spans="1:2">
@@ -9886,7 +9898,7 @@
         <v>838</v>
       </c>
       <c r="B839" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="840" spans="1:2">
@@ -9894,7 +9906,7 @@
         <v>839</v>
       </c>
       <c r="B840" s="1">
-        <v>820</v>
+        <v>860</v>
       </c>
     </row>
     <row r="841" spans="1:2">
@@ -9902,7 +9914,7 @@
         <v>840</v>
       </c>
       <c r="B841" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="842" spans="1:2">
@@ -9910,7 +9922,7 @@
         <v>841</v>
       </c>
       <c r="B842" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="843" spans="1:2">
@@ -9918,7 +9930,7 @@
         <v>842</v>
       </c>
       <c r="B843" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="844" spans="1:2">
@@ -9926,7 +9938,7 @@
         <v>843</v>
       </c>
       <c r="B844" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="845" spans="1:2">
@@ -9934,7 +9946,7 @@
         <v>844</v>
       </c>
       <c r="B845" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="846" spans="1:2">
@@ -9942,7 +9954,7 @@
         <v>845</v>
       </c>
       <c r="B846" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="847" spans="1:2">
@@ -9950,7 +9962,7 @@
         <v>846</v>
       </c>
       <c r="B847" s="1">
-        <v>920</v>
+        <v>600</v>
       </c>
     </row>
     <row r="848" spans="1:2">
@@ -9958,7 +9970,7 @@
         <v>847</v>
       </c>
       <c r="B848" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="849" spans="1:2">
@@ -9966,7 +9978,7 @@
         <v>848</v>
       </c>
       <c r="B849" s="1">
-        <v>940</v>
+        <v>500</v>
       </c>
     </row>
     <row r="850" spans="1:2">
@@ -9974,7 +9986,7 @@
         <v>849</v>
       </c>
       <c r="B850" s="1">
-        <v>1040</v>
+        <v>760</v>
       </c>
     </row>
     <row r="851" spans="1:2">
@@ -9982,7 +9994,7 @@
         <v>850</v>
       </c>
       <c r="B851" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="852" spans="1:2">
@@ -9990,7 +10002,7 @@
         <v>851</v>
       </c>
       <c r="B852" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="853" spans="1:2">
@@ -9998,7 +10010,7 @@
         <v>852</v>
       </c>
       <c r="B853" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="854" spans="1:2">
@@ -10006,7 +10018,7 @@
         <v>853</v>
       </c>
       <c r="B854" s="1">
-        <v>1100</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="855" spans="1:2">
@@ -10014,7 +10026,7 @@
         <v>854</v>
       </c>
       <c r="B855" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="856" spans="1:2">
@@ -10022,7 +10034,7 @@
         <v>855</v>
       </c>
       <c r="B856" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="857" spans="1:2">
@@ -10030,7 +10042,7 @@
         <v>856</v>
       </c>
       <c r="B857" s="1">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="858" spans="1:2">
@@ -10046,7 +10058,7 @@
         <v>858</v>
       </c>
       <c r="B859" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="860" spans="1:2">
@@ -10054,7 +10066,7 @@
         <v>859</v>
       </c>
       <c r="B860" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="861" spans="1:2">
@@ -10062,7 +10074,7 @@
         <v>860</v>
       </c>
       <c r="B861" s="1">
-        <v>840</v>
+        <v>960</v>
       </c>
     </row>
     <row r="862" spans="1:2">
@@ -10070,7 +10082,7 @@
         <v>861</v>
       </c>
       <c r="B862" s="1">
-        <v>440</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="863" spans="1:2">
@@ -10078,7 +10090,7 @@
         <v>862</v>
       </c>
       <c r="B863" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="864" spans="1:2">
@@ -10086,7 +10098,7 @@
         <v>863</v>
       </c>
       <c r="B864" s="1">
-        <v>440</v>
+        <v>820</v>
       </c>
     </row>
     <row r="865" spans="1:2">
@@ -10094,7 +10106,7 @@
         <v>864</v>
       </c>
       <c r="B865" s="1">
-        <v>560</v>
+        <v>840</v>
       </c>
     </row>
     <row r="866" spans="1:2">
@@ -10102,7 +10114,7 @@
         <v>865</v>
       </c>
       <c r="B866" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="867" spans="1:2">
@@ -10110,7 +10122,7 @@
         <v>866</v>
       </c>
       <c r="B867" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="868" spans="1:2">
@@ -10118,7 +10130,7 @@
         <v>867</v>
       </c>
       <c r="B868" s="1">
-        <v>820</v>
+        <v>440</v>
       </c>
     </row>
     <row r="869" spans="1:2">
@@ -10126,7 +10138,7 @@
         <v>868</v>
       </c>
       <c r="B869" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="870" spans="1:2">
@@ -10134,7 +10146,7 @@
         <v>869</v>
       </c>
       <c r="B870" s="1">
-        <v>840</v>
+        <v>500</v>
       </c>
     </row>
     <row r="871" spans="1:2">
@@ -10142,7 +10154,7 @@
         <v>870</v>
       </c>
       <c r="B871" s="1">
-        <v>400</v>
+        <v>820</v>
       </c>
     </row>
     <row r="872" spans="1:2">
@@ -10150,7 +10162,7 @@
         <v>871</v>
       </c>
       <c r="B872" s="1">
-        <v>400</v>
+        <v>820</v>
       </c>
     </row>
     <row r="873" spans="1:2">
@@ -10158,7 +10170,7 @@
         <v>872</v>
       </c>
       <c r="B873" s="1">
-        <v>380</v>
+        <v>760</v>
       </c>
     </row>
     <row r="874" spans="1:2">
@@ -10166,7 +10178,7 @@
         <v>873</v>
       </c>
       <c r="B874" s="1">
-        <v>960</v>
+        <v>840</v>
       </c>
     </row>
     <row r="875" spans="1:2">
@@ -10174,7 +10186,7 @@
         <v>874</v>
       </c>
       <c r="B875" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="876" spans="1:2">
@@ -10182,7 +10194,7 @@
         <v>875</v>
       </c>
       <c r="B876" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="877" spans="1:2">
@@ -10190,7 +10202,7 @@
         <v>876</v>
       </c>
       <c r="B877" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="878" spans="1:2">
@@ -10198,7 +10210,7 @@
         <v>877</v>
       </c>
       <c r="B878" s="1">
-        <v>700</v>
+        <v>960</v>
       </c>
     </row>
     <row r="879" spans="1:2">
@@ -10206,7 +10218,7 @@
         <v>878</v>
       </c>
       <c r="B879" s="1">
-        <v>800</v>
+        <v>380</v>
       </c>
     </row>
     <row r="880" spans="1:2">
@@ -10214,7 +10226,7 @@
         <v>879</v>
       </c>
       <c r="B880" s="1">
-        <v>860</v>
+        <v>380</v>
       </c>
     </row>
     <row r="881" spans="1:2">
@@ -10222,7 +10234,7 @@
         <v>880</v>
       </c>
       <c r="B881" s="1">
-        <v>680</v>
+        <v>520</v>
       </c>
     </row>
     <row r="882" spans="1:2">
@@ -10230,7 +10242,7 @@
         <v>881</v>
       </c>
       <c r="B882" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="883" spans="1:2">
@@ -10238,7 +10250,7 @@
         <v>882</v>
       </c>
       <c r="B883" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="884" spans="1:2">
@@ -10246,7 +10258,7 @@
         <v>883</v>
       </c>
       <c r="B884" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="885" spans="1:2">
@@ -10254,7 +10266,7 @@
         <v>884</v>
       </c>
       <c r="B885" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="886" spans="1:2">
@@ -10262,7 +10274,7 @@
         <v>885</v>
       </c>
       <c r="B886" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="887" spans="1:2">
@@ -10270,7 +10282,7 @@
         <v>886</v>
       </c>
       <c r="B887" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="888" spans="1:2">
@@ -10278,7 +10290,7 @@
         <v>887</v>
       </c>
       <c r="B888" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="889" spans="1:2">
@@ -10286,7 +10298,7 @@
         <v>888</v>
       </c>
       <c r="B889" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="890" spans="1:2">
@@ -10294,7 +10306,7 @@
         <v>889</v>
       </c>
       <c r="B890" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="891" spans="1:2">
@@ -10302,7 +10314,7 @@
         <v>890</v>
       </c>
       <c r="B891" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="892" spans="1:2">
@@ -10310,7 +10322,7 @@
         <v>891</v>
       </c>
       <c r="B892" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="893" spans="1:2">
@@ -10318,7 +10330,7 @@
         <v>892</v>
       </c>
       <c r="B893" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="894" spans="1:2">
@@ -10326,7 +10338,7 @@
         <v>893</v>
       </c>
       <c r="B894" s="1">
-        <v>900</v>
+        <v>500</v>
       </c>
     </row>
     <row r="895" spans="1:2">
@@ -10334,7 +10346,7 @@
         <v>894</v>
       </c>
       <c r="B895" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="896" spans="1:2">
@@ -10342,7 +10354,7 @@
         <v>895</v>
       </c>
       <c r="B896" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="897" spans="1:2">
@@ -10350,7 +10362,7 @@
         <v>896</v>
       </c>
       <c r="B897" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="898" spans="1:2">
@@ -10358,7 +10370,7 @@
         <v>897</v>
       </c>
       <c r="B898" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="899" spans="1:2">
@@ -10366,7 +10378,7 @@
         <v>898</v>
       </c>
       <c r="B899" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="900" spans="1:2">
@@ -10374,7 +10386,7 @@
         <v>899</v>
       </c>
       <c r="B900" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="901" spans="1:2">
@@ -10382,7 +10394,7 @@
         <v>900</v>
       </c>
       <c r="B901" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="902" spans="1:2">
@@ -10390,7 +10402,7 @@
         <v>901</v>
       </c>
       <c r="B902" s="1">
-        <v>1100</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="903" spans="1:2">
@@ -10398,7 +10410,7 @@
         <v>902</v>
       </c>
       <c r="B903" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="904" spans="1:2">
@@ -10406,7 +10418,7 @@
         <v>903</v>
       </c>
       <c r="B904" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="905" spans="1:2">
@@ -10414,7 +10426,7 @@
         <v>904</v>
       </c>
       <c r="B905" s="1">
-        <v>960</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="906" spans="1:2">
@@ -10430,7 +10442,7 @@
         <v>906</v>
       </c>
       <c r="B907" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="908" spans="1:2">
@@ -10438,7 +10450,7 @@
         <v>907</v>
       </c>
       <c r="B908" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="909" spans="1:2">
@@ -10446,7 +10458,7 @@
         <v>908</v>
       </c>
       <c r="B909" s="1">
-        <v>840</v>
+        <v>960</v>
       </c>
     </row>
     <row r="910" spans="1:2">
@@ -10454,7 +10466,7 @@
         <v>909</v>
       </c>
       <c r="B910" s="1">
-        <v>440</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="911" spans="1:2">
@@ -10462,7 +10474,7 @@
         <v>910</v>
       </c>
       <c r="B911" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="912" spans="1:2">
@@ -10470,7 +10482,7 @@
         <v>911</v>
       </c>
       <c r="B912" s="1">
-        <v>440</v>
+        <v>820</v>
       </c>
     </row>
     <row r="913" spans="1:2">
@@ -10478,7 +10490,7 @@
         <v>912</v>
       </c>
       <c r="B913" s="1">
-        <v>560</v>
+        <v>840</v>
       </c>
     </row>
     <row r="914" spans="1:2">
@@ -10486,7 +10498,7 @@
         <v>913</v>
       </c>
       <c r="B914" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="915" spans="1:2">
@@ -10494,7 +10506,7 @@
         <v>914</v>
       </c>
       <c r="B915" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="916" spans="1:2">
@@ -10502,7 +10514,7 @@
         <v>915</v>
       </c>
       <c r="B916" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="917" spans="1:2">
@@ -10510,7 +10522,7 @@
         <v>916</v>
       </c>
       <c r="B917" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="918" spans="1:2">
@@ -10518,7 +10530,7 @@
         <v>917</v>
       </c>
       <c r="B918" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="919" spans="1:2">
@@ -10526,7 +10538,7 @@
         <v>918</v>
       </c>
       <c r="B919" s="1">
-        <v>480</v>
+        <v>820</v>
       </c>
     </row>
     <row r="920" spans="1:2">
@@ -10534,7 +10546,7 @@
         <v>919</v>
       </c>
       <c r="B920" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="921" spans="1:2">
@@ -10542,7 +10554,7 @@
         <v>920</v>
       </c>
       <c r="B921" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="922" spans="1:2">
@@ -10550,7 +10562,7 @@
         <v>921</v>
       </c>
       <c r="B922" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="923" spans="1:2">
@@ -10558,7 +10570,7 @@
         <v>922</v>
       </c>
       <c r="B923" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="924" spans="1:2">
@@ -10566,7 +10578,7 @@
         <v>923</v>
       </c>
       <c r="B924" s="1">
-        <v>440</v>
+        <v>480</v>
       </c>
     </row>
     <row r="925" spans="1:2">
@@ -10574,7 +10586,7 @@
         <v>924</v>
       </c>
       <c r="B925" s="1">
-        <v>380</v>
+        <v>480</v>
       </c>
     </row>
     <row r="926" spans="1:2">
@@ -10582,7 +10594,7 @@
         <v>925</v>
       </c>
       <c r="B926" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="927" spans="1:2">
@@ -10590,7 +10602,7 @@
         <v>926</v>
       </c>
       <c r="B927" s="1">
-        <v>820</v>
+        <v>520</v>
       </c>
     </row>
     <row r="928" spans="1:2">
@@ -10598,7 +10610,7 @@
         <v>927</v>
       </c>
       <c r="B928" s="1">
-        <v>660</v>
+        <v>440</v>
       </c>
     </row>
     <row r="929" spans="1:2">
@@ -10606,7 +10618,7 @@
         <v>928</v>
       </c>
       <c r="B929" s="1">
-        <v>580</v>
+        <v>380</v>
       </c>
     </row>
     <row r="930" spans="1:2">
@@ -10614,7 +10626,7 @@
         <v>929</v>
       </c>
       <c r="B930" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="931" spans="1:2">
@@ -10622,7 +10634,7 @@
         <v>930</v>
       </c>
       <c r="B931" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="932" spans="1:2">
@@ -10630,7 +10642,7 @@
         <v>931</v>
       </c>
       <c r="B932" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="933" spans="1:2">
@@ -10638,7 +10650,7 @@
         <v>932</v>
       </c>
       <c r="B933" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="934" spans="1:2">
@@ -10646,6 +10658,38 @@
         <v>933</v>
       </c>
       <c r="B934" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="935" spans="1:2">
+      <c r="A935" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="B935" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="936" spans="1:2">
+      <c r="A936" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="B936" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="937" spans="1:2">
+      <c r="A937" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="B937" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="938" spans="1:2">
+      <c r="A938" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="B938" s="1">
         <v>560</v>
       </c>
     </row>
